--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,58 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>76.2 → 64.1</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>76.2</t>
+  </si>
+  <si>
+    <t>64.1</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -3.8%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-3.8%</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -230,7 +281,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,7 +315,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -276,8 +327,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,21 +444,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -403,7 +469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -902,58 +968,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>379.65</v>
+        <v>375</v>
       </c>
       <c r="D2">
-        <v>-0.5600000000000001</v>
+        <v>-1.22</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>379.65</v>
+        <v>375</v>
       </c>
       <c r="G2">
-        <v>-22.55</v>
+        <v>-23.5</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-1.48</v>
+        <v>-2.23</v>
       </c>
       <c r="J2">
-        <v>-7.09</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="K2">
-        <v>-18.32</v>
+        <v>-20.1</v>
       </c>
       <c r="L2">
-        <v>-4.77</v>
+        <v>-5.37</v>
       </c>
       <c r="M2">
-        <v>11.6</v>
+        <v>11.47</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>382.01</v>
+        <v>380.3</v>
       </c>
       <c r="Q2">
-        <v>392.6</v>
+        <v>390.96</v>
       </c>
       <c r="R2">
-        <v>418.52</v>
+        <v>416.63</v>
       </c>
       <c r="S2">
-        <v>435.4</v>
+        <v>435.24</v>
       </c>
       <c r="T2">
-        <v>-12.81</v>
+        <v>-13.84</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +1034,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>23.23</v>
+        <v>20.39</v>
       </c>
       <c r="Z2">
-        <v>-10.26</v>
+        <v>-10.42</v>
       </c>
       <c r="AA2">
-        <v>-10.62</v>
+        <v>-10.58</v>
       </c>
       <c r="AB2">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="AC2">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AD2">
-        <v>5.09</v>
+        <v>3</v>
       </c>
       <c r="AE2">
-        <v>7.44</v>
+        <v>7.96</v>
       </c>
       <c r="AF2">
-        <v>-58.19</v>
+        <v>-11.79</v>
       </c>
       <c r="AG2">
-        <v>411.87</v>
+        <v>410.38</v>
       </c>
       <c r="AH2">
-        <v>373.32</v>
+        <v>371.54</v>
       </c>
       <c r="AI2">
-        <v>400.84</v>
+        <v>399.26</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>57.88</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1081,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3107</v>
+        <v>3029.5</v>
       </c>
       <c r="D3">
-        <v>-0.54</v>
+        <v>-2.49</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,25 +1093,25 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-18.29</v>
+        <v>-20.33</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>3.36</v>
       </c>
       <c r="I3">
-        <v>-1.99</v>
+        <v>-4.13</v>
       </c>
       <c r="J3">
-        <v>-9.369999999999999</v>
+        <v>-11.63</v>
       </c>
       <c r="K3">
-        <v>-0.87</v>
+        <v>-3.45</v>
       </c>
       <c r="L3">
-        <v>-15.94</v>
+        <v>-15.95</v>
       </c>
       <c r="M3">
-        <v>34.04</v>
+        <v>32.99</v>
       </c>
       <c r="N3">
         <v>45</v>
@@ -1054,22 +1120,22 @@
         <v>41</v>
       </c>
       <c r="P3">
-        <v>3140.16</v>
+        <v>3114.06</v>
       </c>
       <c r="Q3">
-        <v>3286.75</v>
+        <v>3268.71</v>
       </c>
       <c r="R3">
-        <v>3277.86</v>
+        <v>3274.43</v>
       </c>
       <c r="S3">
-        <v>3319.48</v>
+        <v>3316.19</v>
       </c>
       <c r="T3">
-        <v>-6.4</v>
+        <v>-8.65</v>
       </c>
       <c r="U3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V3" t="s">
         <v>47</v>
@@ -1078,46 +1144,46 @@
         <v>47</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.79</v>
+        <v>24.66</v>
       </c>
       <c r="Z3">
-        <v>-57.21</v>
+        <v>-66.5</v>
       </c>
       <c r="AA3">
-        <v>-30.59</v>
+        <v>-37.77</v>
       </c>
       <c r="AB3">
-        <v>-26.62</v>
+        <v>-28.72</v>
       </c>
       <c r="AC3">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.81</v>
+        <v>1.74</v>
       </c>
       <c r="AE3">
-        <v>64.36</v>
+        <v>66.2</v>
       </c>
       <c r="AF3">
-        <v>-23.43</v>
+        <v>30.65</v>
       </c>
       <c r="AG3">
-        <v>3533.62</v>
+        <v>3535.62</v>
       </c>
       <c r="AH3">
-        <v>3039.88</v>
+        <v>3001.79</v>
       </c>
       <c r="AI3">
-        <v>3289.73</v>
+        <v>3273.14</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>65.18000000000001</v>
+        <v>68.31999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,37 +1194,37 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>356.15</v>
+        <v>342.3</v>
       </c>
       <c r="D4">
-        <v>-0.86</v>
+        <v>-3.89</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>269.25</v>
+        <v>270.1</v>
       </c>
       <c r="G4">
-        <v>-13.62</v>
+        <v>-16.98</v>
       </c>
       <c r="H4">
-        <v>32.27</v>
+        <v>26.73</v>
       </c>
       <c r="I4">
-        <v>-4.68</v>
+        <v>-8.07</v>
       </c>
       <c r="J4">
-        <v>-10.15</v>
+        <v>-12.25</v>
       </c>
       <c r="K4">
-        <v>19.57</v>
+        <v>14.92</v>
       </c>
       <c r="L4">
-        <v>32.42</v>
+        <v>27.13</v>
       </c>
       <c r="M4">
-        <v>18.04</v>
+        <v>16.53</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1167,19 +1233,19 @@
         <v>79</v>
       </c>
       <c r="P4">
-        <v>365.17</v>
+        <v>359.16</v>
       </c>
       <c r="Q4">
-        <v>375.8</v>
+        <v>373.47</v>
       </c>
       <c r="R4">
-        <v>369.94</v>
+        <v>370.15</v>
       </c>
       <c r="S4">
-        <v>344.62</v>
+        <v>344.58</v>
       </c>
       <c r="T4">
-        <v>3.35</v>
+        <v>-0.66</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1191,46 +1257,46 @@
         <v>48</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>37.71</v>
+        <v>31.27</v>
       </c>
       <c r="Z4">
-        <v>-3.36</v>
+        <v>-5.28</v>
       </c>
       <c r="AA4">
+        <v>-1.05</v>
+      </c>
+      <c r="AB4">
+        <v>-4.22</v>
+      </c>
+      <c r="AC4">
         <v>0</v>
       </c>
-      <c r="AB4">
-        <v>-3.36</v>
-      </c>
-      <c r="AC4">
-        <v>1.23</v>
-      </c>
       <c r="AD4">
-        <v>17.77</v>
+        <v>7.03</v>
       </c>
       <c r="AE4">
-        <v>11.26</v>
+        <v>11.72</v>
       </c>
       <c r="AF4">
-        <v>14.57</v>
+        <v>-26.42</v>
       </c>
       <c r="AG4">
-        <v>394.98</v>
+        <v>396.82</v>
       </c>
       <c r="AH4">
-        <v>356.62</v>
+        <v>350.12</v>
       </c>
       <c r="AI4">
-        <v>388.35</v>
+        <v>385.04</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>23.41</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1307,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>353.05</v>
+        <v>345.9</v>
       </c>
       <c r="D5">
-        <v>-1.84</v>
+        <v>-2.03</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1319,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.28</v>
+        <v>-17.97</v>
       </c>
       <c r="H5">
-        <v>19.98</v>
+        <v>17.55</v>
       </c>
       <c r="I5">
-        <v>-2.58</v>
+        <v>-3.96</v>
       </c>
       <c r="J5">
-        <v>-8</v>
+        <v>-10.13</v>
       </c>
       <c r="K5">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="L5">
-        <v>-4.76</v>
+        <v>-7.09</v>
       </c>
       <c r="M5">
-        <v>4.98</v>
+        <v>4.86</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>361.82</v>
+        <v>358.97</v>
       </c>
       <c r="Q5">
-        <v>369.04</v>
+        <v>367</v>
       </c>
       <c r="R5">
-        <v>375.41</v>
+        <v>374.88</v>
       </c>
       <c r="S5">
-        <v>362.64</v>
+        <v>362.34</v>
       </c>
       <c r="T5">
-        <v>-2.64</v>
+        <v>-4.54</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1373,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.2</v>
+        <v>31.09</v>
       </c>
       <c r="Z5">
-        <v>-4.93</v>
+        <v>-6.01</v>
       </c>
       <c r="AA5">
-        <v>-3.78</v>
+        <v>-4.23</v>
       </c>
       <c r="AB5">
-        <v>-1.15</v>
+        <v>-1.78</v>
       </c>
       <c r="AC5">
-        <v>56.19</v>
+        <v>26.02</v>
       </c>
       <c r="AD5">
-        <v>64.2</v>
+        <v>51.16</v>
       </c>
       <c r="AE5">
-        <v>10.44</v>
+        <v>11.01</v>
       </c>
       <c r="AF5">
-        <v>3.03</v>
+        <v>-10.57</v>
       </c>
       <c r="AG5">
-        <v>387.84</v>
+        <v>386.59</v>
       </c>
       <c r="AH5">
-        <v>350.24</v>
+        <v>347.42</v>
       </c>
       <c r="AI5">
         <v>385.87</v>
@@ -1343,7 +1409,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>40.65</v>
+        <v>43.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1420,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>397.2</v>
+        <v>387.25</v>
       </c>
       <c r="D6">
-        <v>-0.72</v>
+        <v>-2.51</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,25 +1432,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-10.28</v>
+        <v>-12.53</v>
       </c>
       <c r="H6">
-        <v>42.09</v>
+        <v>38.53</v>
       </c>
       <c r="I6">
-        <v>-2.01</v>
+        <v>-3.96</v>
       </c>
       <c r="J6">
-        <v>-2.17</v>
+        <v>-4.5</v>
       </c>
       <c r="K6">
-        <v>14.07</v>
+        <v>12.38</v>
       </c>
       <c r="L6">
-        <v>23.01</v>
+        <v>17.88</v>
       </c>
       <c r="M6">
-        <v>-10.56</v>
+        <v>-11.14</v>
       </c>
       <c r="N6">
         <v>77</v>
@@ -1393,19 +1459,19 @@
         <v>76</v>
       </c>
       <c r="P6">
-        <v>402.22</v>
+        <v>399.03</v>
       </c>
       <c r="Q6">
-        <v>399.93</v>
+        <v>399.01</v>
       </c>
       <c r="R6">
-        <v>400.83</v>
+        <v>400.59</v>
       </c>
       <c r="S6">
-        <v>369.91</v>
+        <v>370.22</v>
       </c>
       <c r="T6">
-        <v>7.38</v>
+        <v>4.6</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1486,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>47.28</v>
+        <v>39.82</v>
       </c>
       <c r="Z6">
-        <v>-0.02</v>
+        <v>-1.05</v>
       </c>
       <c r="AA6">
-        <v>-0.03</v>
+        <v>-0.23</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AC6">
-        <v>58</v>
+        <v>39.25</v>
       </c>
       <c r="AD6">
-        <v>72.87</v>
+        <v>57.6</v>
       </c>
       <c r="AE6">
-        <v>10.91</v>
+        <v>11.31</v>
       </c>
       <c r="AF6">
-        <v>-22.18</v>
+        <v>28.35</v>
       </c>
       <c r="AG6">
-        <v>411.98</v>
+        <v>412.02</v>
       </c>
       <c r="AH6">
-        <v>387.87</v>
+        <v>386</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1456,7 +1522,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>22.86</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1533,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>728.9</v>
+        <v>701.1</v>
       </c>
       <c r="D7">
-        <v>1.38</v>
+        <v>-3.81</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1479,25 +1545,25 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-3.81</v>
       </c>
       <c r="H7">
-        <v>43.92</v>
+        <v>38.43</v>
       </c>
       <c r="I7">
-        <v>5.93</v>
+        <v>1.76</v>
       </c>
       <c r="J7">
-        <v>19.1</v>
+        <v>14.47</v>
       </c>
       <c r="K7">
-        <v>15.71</v>
+        <v>12.36</v>
       </c>
       <c r="L7">
-        <v>14.13</v>
+        <v>10.34</v>
       </c>
       <c r="M7">
-        <v>37.21</v>
+        <v>35.82</v>
       </c>
       <c r="N7">
         <v>88</v>
@@ -1506,19 +1572,19 @@
         <v>78</v>
       </c>
       <c r="P7">
-        <v>698.73</v>
+        <v>701.16</v>
       </c>
       <c r="Q7">
-        <v>656.3099999999999</v>
+        <v>660.27</v>
       </c>
       <c r="R7">
-        <v>614.55</v>
+        <v>616.62</v>
       </c>
       <c r="S7">
-        <v>590.39</v>
+        <v>591</v>
       </c>
       <c r="T7">
-        <v>23.46</v>
+        <v>18.63</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1533,34 +1599,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>76.22</v>
+        <v>64.09</v>
       </c>
       <c r="Z7">
-        <v>26.78</v>
+        <v>26.48</v>
       </c>
       <c r="AA7">
-        <v>20.6</v>
+        <v>21.78</v>
       </c>
       <c r="AB7">
-        <v>6.18</v>
+        <v>4.7</v>
       </c>
       <c r="AC7">
-        <v>71.02</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AD7">
-        <v>60.85</v>
+        <v>65.31</v>
       </c>
       <c r="AE7">
-        <v>24.54</v>
+        <v>25.83</v>
       </c>
       <c r="AF7">
-        <v>150.35</v>
+        <v>-28.17</v>
       </c>
       <c r="AG7">
-        <v>722.36</v>
+        <v>727.13</v>
       </c>
       <c r="AH7">
-        <v>590.26</v>
+        <v>593.4</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1569,7 +1635,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>73.95999999999999</v>
+        <v>72.15000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,37 +1646,37 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>196.73</v>
+        <v>192.4</v>
       </c>
       <c r="D8">
-        <v>0.08</v>
+        <v>-2.2</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>196.57</v>
+        <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-45.66</v>
+        <v>-46.86</v>
       </c>
       <c r="H8">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-5.14</v>
+        <v>-6.39</v>
       </c>
       <c r="J8">
-        <v>-12.13</v>
+        <v>-15.1</v>
       </c>
       <c r="K8">
-        <v>-15.5</v>
+        <v>-16.84</v>
       </c>
       <c r="L8">
-        <v>-44.73</v>
+        <v>-46.14</v>
       </c>
       <c r="M8">
-        <v>-3.45</v>
+        <v>-3.74</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1619,19 +1685,19 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>200.78</v>
+        <v>198.15</v>
       </c>
       <c r="Q8">
-        <v>211.75</v>
+        <v>210.04</v>
       </c>
       <c r="R8">
-        <v>220.04</v>
+        <v>219.24</v>
       </c>
       <c r="S8">
-        <v>257.12</v>
+        <v>256.47</v>
       </c>
       <c r="T8">
-        <v>-23.49</v>
+        <v>-24.98</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1712,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>22.5</v>
+        <v>19.52</v>
       </c>
       <c r="Z8">
-        <v>-6.55</v>
+        <v>-7.1</v>
       </c>
       <c r="AA8">
-        <v>-5.12</v>
+        <v>-5.52</v>
       </c>
       <c r="AB8">
-        <v>-1.43</v>
+        <v>-1.58</v>
       </c>
       <c r="AC8">
         <v>0.68</v>
       </c>
       <c r="AD8">
-        <v>1.66</v>
+        <v>1.03</v>
       </c>
       <c r="AE8">
-        <v>5.84</v>
+        <v>6.05</v>
       </c>
       <c r="AF8">
-        <v>10.87</v>
+        <v>4.1</v>
       </c>
       <c r="AG8">
-        <v>229.55</v>
+        <v>228.39</v>
       </c>
       <c r="AH8">
-        <v>193.95</v>
+        <v>191.69</v>
       </c>
       <c r="AI8">
-        <v>214.31</v>
+        <v>213.64</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>54.09</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1759,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3576</v>
+        <v>3569.2</v>
       </c>
       <c r="D9">
-        <v>0.7</v>
+        <v>-0.19</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,22 +1771,22 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.49</v>
+        <v>-20.64</v>
       </c>
       <c r="H9">
-        <v>8.07</v>
+        <v>7.87</v>
       </c>
       <c r="I9">
-        <v>0.51</v>
+        <v>-2.16</v>
       </c>
       <c r="J9">
-        <v>-1.17</v>
+        <v>-1.9</v>
       </c>
       <c r="K9">
-        <v>-6.53</v>
+        <v>-7.46</v>
       </c>
       <c r="L9">
-        <v>-19.11</v>
+        <v>-18.15</v>
       </c>
       <c r="M9">
         <v>19.77</v>
@@ -1729,22 +1795,22 @@
         <v>34</v>
       </c>
       <c r="O9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P9">
-        <v>3600.38</v>
+        <v>3584.62</v>
       </c>
       <c r="Q9">
-        <v>3575.42</v>
+        <v>3571.97</v>
       </c>
       <c r="R9">
-        <v>3623.9</v>
+        <v>3618.92</v>
       </c>
       <c r="S9">
-        <v>3684.75</v>
+        <v>3683.9</v>
       </c>
       <c r="T9">
-        <v>-2.95</v>
+        <v>-3.11</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1825,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>47.09</v>
+        <v>46.06</v>
       </c>
       <c r="Z9">
-        <v>-12.82</v>
+        <v>-12.68</v>
       </c>
       <c r="AA9">
-        <v>-19.71</v>
+        <v>-18.31</v>
       </c>
       <c r="AB9">
-        <v>6.89</v>
+        <v>5.62</v>
       </c>
       <c r="AC9">
-        <v>47.78</v>
+        <v>43.56</v>
       </c>
       <c r="AD9">
-        <v>63.32</v>
+        <v>50.44</v>
       </c>
       <c r="AE9">
-        <v>63.54</v>
+        <v>62.57</v>
       </c>
       <c r="AF9">
-        <v>13.08</v>
+        <v>-0.35</v>
       </c>
       <c r="AG9">
-        <v>3642.42</v>
+        <v>3632.12</v>
       </c>
       <c r="AH9">
-        <v>3508.42</v>
+        <v>3511.82</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1795,7 +1861,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>29.63</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1872,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1541</v>
+        <v>1575.9</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2.26</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1884,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-12.86</v>
+        <v>-10.89</v>
       </c>
       <c r="H10">
-        <v>16.2</v>
+        <v>18.83</v>
       </c>
       <c r="I10">
-        <v>-3.5</v>
+        <v>0.76</v>
       </c>
       <c r="J10">
-        <v>-5.98</v>
+        <v>-3.48</v>
       </c>
       <c r="K10">
-        <v>8.09</v>
+        <v>8.92</v>
       </c>
       <c r="L10">
-        <v>3.93</v>
+        <v>4.35</v>
       </c>
       <c r="M10">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="P10">
-        <v>1539.56</v>
+        <v>1541.94</v>
       </c>
       <c r="Q10">
-        <v>1586.52</v>
+        <v>1584.82</v>
       </c>
       <c r="R10">
-        <v>1577.26</v>
+        <v>1580.64</v>
       </c>
       <c r="S10">
-        <v>1518.04</v>
+        <v>1518.32</v>
       </c>
       <c r="T10">
-        <v>1.51</v>
+        <v>3.79</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1938,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>41.54</v>
+        <v>49.07</v>
       </c>
       <c r="Z10">
-        <v>-12.65</v>
+        <v>-11.11</v>
       </c>
       <c r="AA10">
-        <v>-1.01</v>
+        <v>-3.03</v>
       </c>
       <c r="AB10">
-        <v>-11.63</v>
+        <v>-8.08</v>
       </c>
       <c r="AC10">
-        <v>15.58</v>
+        <v>34.65</v>
       </c>
       <c r="AD10">
-        <v>7.04</v>
+        <v>18.59</v>
       </c>
       <c r="AE10">
-        <v>39.25</v>
+        <v>43.04</v>
       </c>
       <c r="AF10">
-        <v>1.03</v>
+        <v>34.5</v>
       </c>
       <c r="AG10">
-        <v>1656.32</v>
+        <v>1653.87</v>
       </c>
       <c r="AH10">
-        <v>1516.72</v>
+        <v>1515.76</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1908,7 +1974,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>34.73</v>
+        <v>33.35</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1314 +2135,1338 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-7.26</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-7.09</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.17</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-7.09</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="7">
         <v>-9.369999999999999</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-11.63</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-9.25</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="7">
         <v>-10.15</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="7">
+        <v>-12.25</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-6.06</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="7">
         <v>-8</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="7">
+        <v>-10.13</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.68</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="7">
         <v>-2.17</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="7">
+        <v>-4.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>17.87</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="7">
         <v>19.1</v>
       </c>
-      <c r="E12" s="6">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="7">
+        <v>14.47</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-12.59</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C15" s="7">
         <v>-12.13</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D15" s="7">
+        <v>-15.1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C16" s="7">
         <v>-1.17</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D16" s="7">
+        <v>-1.9</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="5">
-        <v>-6.1</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C17" s="7">
         <v>-5.98</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-3.48</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C18" s="7">
         <v>-1.48</v>
       </c>
-      <c r="E16" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D18" s="7">
+        <v>-2.23</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-0.83</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C19" s="7">
         <v>-1.99</v>
       </c>
-      <c r="E17" s="7">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D19" s="7">
+        <v>-4.13</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-4.47</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C20" s="7">
         <v>-4.68</v>
       </c>
-      <c r="E18" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D20" s="7">
+        <v>-8.07</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C21" s="7">
+        <v>-2.58</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-3.96</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.01</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.96</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>5.93</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-4.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-5.14</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-6.39</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.16</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="E26" s="9">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-4.77</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-5.37</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-15.94</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-15.95</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>32.42</v>
+      </c>
+      <c r="D29" s="7">
+        <v>27.13</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-5.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-4.76</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-7.09</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>23.01</v>
+      </c>
+      <c r="D31" s="7">
+        <v>17.88</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-5.13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>14.13</v>
+      </c>
+      <c r="D32" s="7">
+        <v>10.34</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-44.73</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-46.14</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-19.11</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-18.15</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>3.93</v>
+      </c>
+      <c r="D35" s="7">
+        <v>4.35</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-18.32</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-20.1</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-0.87</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-3.45</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>19.57</v>
+      </c>
+      <c r="D38" s="7">
+        <v>14.92</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>5.8</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>14.07</v>
+      </c>
+      <c r="D40" s="7">
+        <v>12.38</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>15.71</v>
+      </c>
+      <c r="D41" s="7">
+        <v>12.36</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-3.35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-15.5</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-16.84</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-6.53</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-7.46</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>8.09</v>
+      </c>
+      <c r="D44" s="7">
+        <v>8.92</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-22.55</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-23.5</v>
+      </c>
+      <c r="E45" s="8">
         <v>-0.95</v>
       </c>
-      <c r="D19" s="5">
-        <v>-2.58</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-18.29</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-20.33</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-13.62</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-16.98</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-16.28</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-17.97</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.01</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-10.28</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-12.53</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>10.02</v>
-      </c>
-      <c r="D21" s="5">
-        <v>5.93</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-4.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-3.81</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-3.81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-5.45</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-5.14</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-45.66</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-46.86</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-0.1</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.51</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-20.49</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-20.64</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-4.52</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-3.5</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-12.86</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-10.89</v>
+      </c>
+      <c r="E53" s="9">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-4.36</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-4.77</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>379.65</v>
+      </c>
+      <c r="D54" s="7">
+        <v>375</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-12.28</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-15.94</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>3107</v>
+      </c>
+      <c r="D55" s="7">
+        <v>3029.5</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-77.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>33.4</v>
-      </c>
-      <c r="D27" s="5">
-        <v>32.42</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>356.15</v>
+      </c>
+      <c r="D56" s="7">
+        <v>342.3</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-13.85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-3.06</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-4.76</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>353.05</v>
+      </c>
+      <c r="D57" s="7">
+        <v>345.9</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-7.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>24.62</v>
-      </c>
-      <c r="D29" s="5">
-        <v>23.01</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>397.2</v>
+      </c>
+      <c r="D58" s="7">
+        <v>387.25</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-9.949999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>12.85</v>
-      </c>
-      <c r="D30" s="5">
-        <v>14.13</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>728.9</v>
+      </c>
+      <c r="D59" s="7">
+        <v>701.1</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-27.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-44.16</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-44.73</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>196.73</v>
+      </c>
+      <c r="D60" s="7">
+        <v>192.4</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-19.45</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-19.11</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>3576</v>
+      </c>
+      <c r="D61" s="7">
+        <v>3569.2</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>5.55</v>
-      </c>
-      <c r="D33" s="5">
-        <v>3.93</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1541</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1575.9</v>
+      </c>
+      <c r="E62" s="9">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-15.29</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-18.32</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>23.23</v>
+      </c>
+      <c r="D63" s="7">
+        <v>20.39</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-0.87</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>29.79</v>
+      </c>
+      <c r="D64" s="7">
+        <v>24.66</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-5.13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>23.43</v>
-      </c>
-      <c r="D36" s="5">
-        <v>19.57</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>37.71</v>
+      </c>
+      <c r="D65" s="7">
+        <v>31.27</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>9.5</v>
-      </c>
-      <c r="D37" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>35.2</v>
+      </c>
+      <c r="D66" s="7">
+        <v>31.09</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-4.11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>18.48</v>
-      </c>
-      <c r="D38" s="5">
-        <v>14.07</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-4.41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>47.28</v>
+      </c>
+      <c r="D67" s="7">
+        <v>39.82</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-7.46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>15.71</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>76.22</v>
+      </c>
+      <c r="D68" s="7">
+        <v>64.09</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-12.13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-16.52</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-15.5</v>
-      </c>
-      <c r="E40" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="D69" s="7">
+        <v>19.52</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-4.12</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-6.53</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>47.09</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46.06</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>6.76</v>
-      </c>
-      <c r="D42" s="5">
-        <v>8.09</v>
-      </c>
-      <c r="E42" s="6">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>41.54</v>
+      </c>
+      <c r="D71" s="7">
+        <v>49.07</v>
+      </c>
+      <c r="E71" s="9">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-22.11</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-22.55</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-58.19</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-11.79</v>
+      </c>
+      <c r="E72" s="9">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-17.85</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-18.29</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-23.43</v>
+      </c>
+      <c r="D73" s="7">
+        <v>30.65</v>
+      </c>
+      <c r="E73" s="9">
+        <v>54.08</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-12.87</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-13.62</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>14.57</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-26.42</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-40.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-14.71</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-16.28</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>3.03</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-10.57</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-13.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-10.28</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-22.18</v>
+      </c>
+      <c r="D76" s="7">
+        <v>28.35</v>
+      </c>
+      <c r="E76" s="9">
+        <v>50.53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>150.35</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-28.17</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-178.52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-45.71</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-45.66</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>10.87</v>
+      </c>
+      <c r="D78" s="7">
+        <v>4.1</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-6.77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-21.05</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-20.49</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>13.08</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-0.35</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-13.43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-13.72</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-12.86</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>381.8</v>
-      </c>
-      <c r="D51" s="5">
-        <v>379.65</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>3123.8</v>
-      </c>
-      <c r="D52" s="5">
-        <v>3107</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-16.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>359.25</v>
-      </c>
-      <c r="D53" s="5">
-        <v>356.15</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>359.65</v>
-      </c>
-      <c r="D54" s="5">
-        <v>353.05</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-6.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>400.1</v>
-      </c>
-      <c r="D55" s="5">
-        <v>397.2</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>718.95</v>
-      </c>
-      <c r="D56" s="5">
-        <v>728.9</v>
-      </c>
-      <c r="E56" s="6">
-        <v>9.949999999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>196.57</v>
-      </c>
-      <c r="D57" s="5">
-        <v>196.73</v>
-      </c>
-      <c r="E57" s="6">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>3551</v>
-      </c>
-      <c r="D58" s="5">
-        <v>3576</v>
-      </c>
-      <c r="E58" s="6">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1525.8</v>
-      </c>
-      <c r="D59" s="5">
-        <v>1541</v>
-      </c>
-      <c r="E59" s="6">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="5">
-        <v>34</v>
-      </c>
-      <c r="D60" s="5">
-        <v>23</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>88</v>
-      </c>
-      <c r="D61" s="5">
-        <v>77</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>77</v>
-      </c>
-      <c r="D62" s="5">
-        <v>88</v>
-      </c>
-      <c r="E62" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5">
-        <v>23</v>
-      </c>
-      <c r="D63" s="5">
-        <v>34</v>
-      </c>
-      <c r="E63" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>24.7</v>
-      </c>
-      <c r="D64" s="5">
-        <v>23.23</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>31.09</v>
-      </c>
-      <c r="D65" s="5">
-        <v>29.79</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>39.4</v>
-      </c>
-      <c r="D66" s="5">
-        <v>37.71</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>39.7</v>
-      </c>
-      <c r="D67" s="5">
-        <v>35.2</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>49.8</v>
-      </c>
-      <c r="D68" s="5">
-        <v>47.28</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>74.62</v>
-      </c>
-      <c r="D69" s="5">
-        <v>76.22</v>
-      </c>
-      <c r="E69" s="6">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>22.09</v>
-      </c>
-      <c r="D70" s="5">
-        <v>22.5</v>
-      </c>
-      <c r="E70" s="6">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>42.71</v>
-      </c>
-      <c r="D71" s="5">
-        <v>47.09</v>
-      </c>
-      <c r="E71" s="6">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="5">
-        <v>37.83</v>
-      </c>
-      <c r="D72" s="5">
-        <v>41.54</v>
-      </c>
-      <c r="E72" s="6">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="3" t="s">
+      <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="5">
-        <v>28.97</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-58.19</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-87.16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>26.07</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-23.43</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-49.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>30.93</v>
-      </c>
-      <c r="D75" s="5">
-        <v>14.57</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-16.36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-33.86</v>
-      </c>
-      <c r="D76" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="E76" s="6">
-        <v>36.89</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-38.02</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-22.18</v>
-      </c>
-      <c r="E77" s="6">
-        <v>15.84</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>245.57</v>
-      </c>
-      <c r="D78" s="5">
-        <v>150.35</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-95.22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>183.21</v>
-      </c>
-      <c r="D79" s="5">
-        <v>10.87</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-172.34</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>2.72</v>
-      </c>
-      <c r="D80" s="5">
-        <v>13.08</v>
-      </c>
-      <c r="E80" s="6">
-        <v>10.36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="5">
-        <v>-33.01</v>
-      </c>
-      <c r="D81" s="5">
+      <c r="C80" s="7">
         <v>1.03</v>
       </c>
-      <c r="E81" s="6">
-        <v>34.04</v>
+      <c r="D80" s="7">
+        <v>34.5</v>
+      </c>
+      <c r="E80" s="9">
+        <v>33.47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3396,60 +3486,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>44.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>40.1</v>
-      </c>
-      <c r="E2" s="10">
-        <v>40</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-4.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>2.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>36.2</v>
+      </c>
+      <c r="E2" s="12">
+        <v>30</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-5.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>30</v>
       </c>
     </row>
@@ -3551,61 +3641,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3721</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3404</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="A2" s="15">
+        <v>0.3582</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3299</v>
+      </c>
+      <c r="C2" s="15">
         <v>0.1977</v>
       </c>
-      <c r="D2" s="13">
-        <v>0.1804</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.116</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0498</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0458</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0345</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.1056</v>
+      <c r="D2" s="15">
+        <v>0.1653</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1147</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0486</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0454</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0374</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1114</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>76.2 → 64.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>76.2</t>
-  </si>
-  <si>
-    <t>64.1</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -3.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.7 → 31.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>24.7</t>
+  </si>
+  <si>
+    <t>31.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -281,7 +257,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,7 +291,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -327,15 +303,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,19 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -452,15 +415,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -469,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -968,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>375</v>
+        <v>375.8</v>
       </c>
       <c r="D2">
-        <v>-1.22</v>
+        <v>0.21</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -980,46 +942,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-23.5</v>
+        <v>-23.34</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="I2">
-        <v>-2.23</v>
+        <v>-1.98</v>
       </c>
       <c r="J2">
-        <v>-8.029999999999999</v>
+        <v>-7.84</v>
       </c>
       <c r="K2">
-        <v>-20.1</v>
+        <v>-17.8</v>
       </c>
       <c r="L2">
-        <v>-5.37</v>
+        <v>-4.95</v>
       </c>
       <c r="M2">
-        <v>11.47</v>
+        <v>11.89</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O2">
         <v>39</v>
       </c>
       <c r="P2">
-        <v>380.3</v>
+        <v>378.78</v>
       </c>
       <c r="Q2">
-        <v>390.96</v>
+        <v>389.26</v>
       </c>
       <c r="R2">
-        <v>416.63</v>
+        <v>414.81</v>
       </c>
       <c r="S2">
-        <v>435.24</v>
+        <v>435.09</v>
       </c>
       <c r="T2">
-        <v>-13.84</v>
+        <v>-13.63</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1034,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>20.39</v>
+        <v>22.15</v>
       </c>
       <c r="Z2">
-        <v>-10.42</v>
+        <v>-10.36</v>
       </c>
       <c r="AA2">
-        <v>-10.58</v>
+        <v>-10.53</v>
       </c>
       <c r="AB2">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AC2">
-        <v>1.58</v>
+        <v>6.53</v>
       </c>
       <c r="AD2">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="AE2">
-        <v>7.96</v>
+        <v>8.31</v>
       </c>
       <c r="AF2">
-        <v>-11.79</v>
+        <v>14.48</v>
       </c>
       <c r="AG2">
-        <v>410.38</v>
+        <v>407.69</v>
       </c>
       <c r="AH2">
-        <v>371.54</v>
+        <v>370.84</v>
       </c>
       <c r="AI2">
-        <v>399.26</v>
+        <v>398.26</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>60.78</v>
+        <v>63.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1081,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3029.5</v>
+        <v>3070</v>
       </c>
       <c r="D3">
-        <v>-2.49</v>
+        <v>1.34</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1093,46 +1055,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-20.33</v>
+        <v>-19.26</v>
       </c>
       <c r="H3">
-        <v>3.36</v>
+        <v>4.74</v>
       </c>
       <c r="I3">
-        <v>-4.13</v>
+        <v>-2.85</v>
       </c>
       <c r="J3">
-        <v>-11.63</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K3">
-        <v>-3.45</v>
+        <v>-2.01</v>
       </c>
       <c r="L3">
-        <v>-15.95</v>
+        <v>-14.62</v>
       </c>
       <c r="M3">
-        <v>32.99</v>
+        <v>33.28</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="P3">
-        <v>3114.06</v>
+        <v>3096.06</v>
       </c>
       <c r="Q3">
-        <v>3268.71</v>
+        <v>3251.13</v>
       </c>
       <c r="R3">
-        <v>3274.43</v>
+        <v>3271.9</v>
       </c>
       <c r="S3">
-        <v>3316.19</v>
+        <v>3313.14</v>
       </c>
       <c r="T3">
-        <v>-8.65</v>
+        <v>-7.34</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1147,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>24.66</v>
+        <v>31.32</v>
       </c>
       <c r="Z3">
-        <v>-66.5</v>
+        <v>-69.78</v>
       </c>
       <c r="AA3">
-        <v>-37.77</v>
+        <v>-44.17</v>
       </c>
       <c r="AB3">
-        <v>-28.72</v>
+        <v>-25.61</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AD3">
-        <v>1.74</v>
+        <v>3.76</v>
       </c>
       <c r="AE3">
-        <v>66.2</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AF3">
-        <v>30.65</v>
+        <v>38.95</v>
       </c>
       <c r="AG3">
-        <v>3535.62</v>
+        <v>3521.94</v>
       </c>
       <c r="AH3">
-        <v>3001.79</v>
+        <v>2980.32</v>
       </c>
       <c r="AI3">
         <v>3273.14</v>
@@ -1183,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>68.31999999999999</v>
+        <v>71.04000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1194,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>342.3</v>
+        <v>345.05</v>
       </c>
       <c r="D4">
-        <v>-3.89</v>
+        <v>0.8</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1206,46 +1168,46 @@
         <v>270.1</v>
       </c>
       <c r="G4">
-        <v>-16.98</v>
+        <v>-16.31</v>
       </c>
       <c r="H4">
-        <v>26.73</v>
+        <v>27.75</v>
       </c>
       <c r="I4">
-        <v>-8.07</v>
+        <v>-7.83</v>
       </c>
       <c r="J4">
-        <v>-12.25</v>
+        <v>-11.28</v>
       </c>
       <c r="K4">
-        <v>14.92</v>
+        <v>15.98</v>
       </c>
       <c r="L4">
-        <v>27.13</v>
+        <v>27.09</v>
       </c>
       <c r="M4">
-        <v>16.53</v>
+        <v>16.59</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P4">
-        <v>359.16</v>
+        <v>353.3</v>
       </c>
       <c r="Q4">
-        <v>373.47</v>
+        <v>371.41</v>
       </c>
       <c r="R4">
-        <v>370.15</v>
+        <v>370.41</v>
       </c>
       <c r="S4">
-        <v>344.58</v>
+        <v>344.49</v>
       </c>
       <c r="T4">
-        <v>-0.66</v>
+        <v>0.16</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1257,46 +1219,46 @@
         <v>48</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4">
-        <v>31.27</v>
+        <v>33.69</v>
       </c>
       <c r="Z4">
-        <v>-5.28</v>
+        <v>-6.5</v>
       </c>
       <c r="AA4">
-        <v>-1.05</v>
+        <v>-2.14</v>
       </c>
       <c r="AB4">
-        <v>-4.22</v>
+        <v>-4.35</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD4">
-        <v>7.03</v>
+        <v>1.64</v>
       </c>
       <c r="AE4">
-        <v>11.72</v>
+        <v>11.33</v>
       </c>
       <c r="AF4">
-        <v>-26.42</v>
+        <v>-39.61</v>
       </c>
       <c r="AG4">
-        <v>396.82</v>
+        <v>397.17</v>
       </c>
       <c r="AH4">
-        <v>350.12</v>
+        <v>345.66</v>
       </c>
       <c r="AI4">
-        <v>385.04</v>
+        <v>378.22</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>27.54</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1307,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>345.9</v>
+        <v>344.15</v>
       </c>
       <c r="D5">
-        <v>-2.03</v>
+        <v>-0.51</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1319,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-17.97</v>
+        <v>-18.39</v>
       </c>
       <c r="H5">
-        <v>17.55</v>
+        <v>16.96</v>
       </c>
       <c r="I5">
-        <v>-3.96</v>
+        <v>-6.01</v>
       </c>
       <c r="J5">
-        <v>-10.13</v>
+        <v>-10.99</v>
       </c>
       <c r="K5">
-        <v>0.9</v>
+        <v>-0.65</v>
       </c>
       <c r="L5">
-        <v>-7.09</v>
+        <v>-5.56</v>
       </c>
       <c r="M5">
-        <v>4.86</v>
+        <v>5.05</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>358.97</v>
+        <v>354.57</v>
       </c>
       <c r="Q5">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="R5">
-        <v>374.88</v>
+        <v>374.35</v>
       </c>
       <c r="S5">
-        <v>362.34</v>
+        <v>361.98</v>
       </c>
       <c r="T5">
-        <v>-4.54</v>
+        <v>-4.93</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1373,43 +1335,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.09</v>
+        <v>30.16</v>
       </c>
       <c r="Z5">
-        <v>-6.01</v>
+        <v>-6.92</v>
       </c>
       <c r="AA5">
-        <v>-4.23</v>
+        <v>-4.77</v>
       </c>
       <c r="AB5">
-        <v>-1.78</v>
+        <v>-2.15</v>
       </c>
       <c r="AC5">
-        <v>26.02</v>
+        <v>9.74</v>
       </c>
       <c r="AD5">
-        <v>51.16</v>
+        <v>30.65</v>
       </c>
       <c r="AE5">
-        <v>11.01</v>
+        <v>11.25</v>
       </c>
       <c r="AF5">
-        <v>-10.57</v>
+        <v>-26.34</v>
       </c>
       <c r="AG5">
-        <v>386.59</v>
+        <v>385.37</v>
       </c>
       <c r="AH5">
-        <v>347.42</v>
+        <v>344.64</v>
       </c>
       <c r="AI5">
-        <v>385.87</v>
+        <v>379.96</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>43.01</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1420,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>387.25</v>
+        <v>386.8</v>
       </c>
       <c r="D6">
-        <v>-2.51</v>
+        <v>-0.12</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1432,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-12.53</v>
+        <v>-12.63</v>
       </c>
       <c r="H6">
-        <v>38.53</v>
+        <v>38.37</v>
       </c>
       <c r="I6">
-        <v>-3.96</v>
+        <v>-5.39</v>
       </c>
       <c r="J6">
-        <v>-4.5</v>
+        <v>-4.61</v>
       </c>
       <c r="K6">
-        <v>12.38</v>
+        <v>12.12</v>
       </c>
       <c r="L6">
-        <v>17.88</v>
+        <v>17.46</v>
       </c>
       <c r="M6">
-        <v>-11.14</v>
+        <v>-11.25</v>
       </c>
       <c r="N6">
         <v>77</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>399.03</v>
+        <v>394.62</v>
       </c>
       <c r="Q6">
-        <v>399.01</v>
+        <v>398.13</v>
       </c>
       <c r="R6">
-        <v>400.59</v>
+        <v>400.49</v>
       </c>
       <c r="S6">
-        <v>370.22</v>
+        <v>370.52</v>
       </c>
       <c r="T6">
-        <v>4.6</v>
+        <v>4.39</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1486,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>39.82</v>
+        <v>39.52</v>
       </c>
       <c r="Z6">
-        <v>-1.05</v>
+        <v>-1.88</v>
       </c>
       <c r="AA6">
-        <v>-0.23</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AB6">
-        <v>-0.8100000000000001</v>
+        <v>-1.31</v>
       </c>
       <c r="AC6">
-        <v>39.25</v>
+        <v>22.37</v>
       </c>
       <c r="AD6">
-        <v>57.6</v>
+        <v>39.87</v>
       </c>
       <c r="AE6">
-        <v>11.31</v>
+        <v>11.26</v>
       </c>
       <c r="AF6">
-        <v>28.35</v>
+        <v>3.91</v>
       </c>
       <c r="AG6">
-        <v>412.02</v>
+        <v>411.94</v>
       </c>
       <c r="AH6">
-        <v>386</v>
+        <v>384.31</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1522,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.75</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1533,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>701.1</v>
+        <v>692.95</v>
       </c>
       <c r="D7">
-        <v>-3.81</v>
+        <v>-1.16</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1545,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-3.81</v>
+        <v>-4.93</v>
       </c>
       <c r="H7">
-        <v>38.43</v>
+        <v>36.82</v>
       </c>
       <c r="I7">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="J7">
-        <v>14.47</v>
+        <v>11.41</v>
       </c>
       <c r="K7">
-        <v>12.36</v>
+        <v>12.69</v>
       </c>
       <c r="L7">
-        <v>10.34</v>
+        <v>9.07</v>
       </c>
       <c r="M7">
-        <v>35.82</v>
+        <v>35.04</v>
       </c>
       <c r="N7">
         <v>88</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P7">
-        <v>701.16</v>
+        <v>703.62</v>
       </c>
       <c r="Q7">
-        <v>660.27</v>
+        <v>663.87</v>
       </c>
       <c r="R7">
-        <v>616.62</v>
+        <v>618.42</v>
       </c>
       <c r="S7">
-        <v>591</v>
+        <v>591.59</v>
       </c>
       <c r="T7">
-        <v>18.63</v>
+        <v>17.13</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1599,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>64.09</v>
+        <v>61.02</v>
       </c>
       <c r="Z7">
-        <v>26.48</v>
+        <v>25.29</v>
       </c>
       <c r="AA7">
-        <v>21.78</v>
+        <v>22.48</v>
       </c>
       <c r="AB7">
-        <v>4.7</v>
+        <v>2.81</v>
       </c>
       <c r="AC7">
-        <v>67.40000000000001</v>
+        <v>35.86</v>
       </c>
       <c r="AD7">
-        <v>65.31</v>
+        <v>58.09</v>
       </c>
       <c r="AE7">
-        <v>25.83</v>
+        <v>25.98</v>
       </c>
       <c r="AF7">
-        <v>-28.17</v>
+        <v>-53.73</v>
       </c>
       <c r="AG7">
-        <v>727.13</v>
+        <v>729.5599999999999</v>
       </c>
       <c r="AH7">
-        <v>593.4</v>
+        <v>598.1799999999999</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1635,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>72.15000000000001</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1646,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>192.4</v>
+        <v>193.51</v>
       </c>
       <c r="D8">
-        <v>-2.2</v>
+        <v>0.58</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1658,25 +1620,25 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-46.86</v>
+        <v>-46.55</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="I8">
-        <v>-6.39</v>
+        <v>-5.93</v>
       </c>
       <c r="J8">
-        <v>-15.1</v>
+        <v>-14.61</v>
       </c>
       <c r="K8">
-        <v>-16.84</v>
+        <v>-16.28</v>
       </c>
       <c r="L8">
-        <v>-46.14</v>
+        <v>-45.98</v>
       </c>
       <c r="M8">
-        <v>-3.74</v>
+        <v>-3.39</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1685,19 +1647,19 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>198.15</v>
+        <v>195.71</v>
       </c>
       <c r="Q8">
-        <v>210.04</v>
+        <v>208.65</v>
       </c>
       <c r="R8">
-        <v>219.24</v>
+        <v>218.45</v>
       </c>
       <c r="S8">
-        <v>256.47</v>
+        <v>255.84</v>
       </c>
       <c r="T8">
-        <v>-24.98</v>
+        <v>-24.36</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1712,43 +1674,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>19.52</v>
+        <v>22.36</v>
       </c>
       <c r="Z8">
-        <v>-7.1</v>
+        <v>-7.36</v>
       </c>
       <c r="AA8">
-        <v>-5.52</v>
+        <v>-5.89</v>
       </c>
       <c r="AB8">
-        <v>-1.58</v>
+        <v>-1.48</v>
       </c>
       <c r="AC8">
-        <v>0.68</v>
+        <v>7.29</v>
       </c>
       <c r="AD8">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AE8">
-        <v>6.05</v>
+        <v>6.18</v>
       </c>
       <c r="AF8">
-        <v>4.1</v>
+        <v>-19.53</v>
       </c>
       <c r="AG8">
-        <v>228.39</v>
+        <v>227.6</v>
       </c>
       <c r="AH8">
-        <v>191.69</v>
+        <v>189.7</v>
       </c>
       <c r="AI8">
-        <v>213.64</v>
+        <v>210.65</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>57.51</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1759,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3569.2</v>
+        <v>3524.8</v>
       </c>
       <c r="D9">
-        <v>-0.19</v>
+        <v>-1.24</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1771,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.64</v>
+        <v>-21.63</v>
       </c>
       <c r="H9">
-        <v>7.87</v>
+        <v>6.52</v>
       </c>
       <c r="I9">
-        <v>-2.16</v>
+        <v>-2.97</v>
       </c>
       <c r="J9">
-        <v>-1.9</v>
+        <v>-3.12</v>
       </c>
       <c r="K9">
-        <v>-7.46</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L9">
-        <v>-18.15</v>
+        <v>-18</v>
       </c>
       <c r="M9">
-        <v>19.77</v>
+        <v>19.71</v>
       </c>
       <c r="N9">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O9">
         <v>39</v>
       </c>
       <c r="P9">
-        <v>3584.62</v>
+        <v>3563.06</v>
       </c>
       <c r="Q9">
-        <v>3571.97</v>
+        <v>3568.51</v>
       </c>
       <c r="R9">
-        <v>3618.92</v>
+        <v>3613.96</v>
       </c>
       <c r="S9">
-        <v>3683.9</v>
+        <v>3682.72</v>
       </c>
       <c r="T9">
-        <v>-3.11</v>
+        <v>-4.29</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1825,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.06</v>
+        <v>39.91</v>
       </c>
       <c r="Z9">
-        <v>-12.68</v>
+        <v>-15.97</v>
       </c>
       <c r="AA9">
-        <v>-18.31</v>
+        <v>-17.84</v>
       </c>
       <c r="AB9">
-        <v>5.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC9">
-        <v>43.56</v>
+        <v>39.88</v>
       </c>
       <c r="AD9">
-        <v>50.44</v>
+        <v>43.74</v>
       </c>
       <c r="AE9">
-        <v>62.57</v>
+        <v>62.34</v>
       </c>
       <c r="AF9">
-        <v>-0.35</v>
+        <v>38.25</v>
       </c>
       <c r="AG9">
-        <v>3632.12</v>
+        <v>3631.23</v>
       </c>
       <c r="AH9">
-        <v>3511.82</v>
+        <v>3505.79</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1861,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.44</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1872,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1575.9</v>
+        <v>1558</v>
       </c>
       <c r="D10">
-        <v>2.26</v>
+        <v>-1.14</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1884,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-10.89</v>
+        <v>-11.9</v>
       </c>
       <c r="H10">
-        <v>18.83</v>
+        <v>17.48</v>
       </c>
       <c r="I10">
-        <v>0.76</v>
+        <v>-0.06</v>
       </c>
       <c r="J10">
-        <v>-3.48</v>
+        <v>-3.23</v>
       </c>
       <c r="K10">
-        <v>8.92</v>
+        <v>6.54</v>
       </c>
       <c r="L10">
-        <v>4.35</v>
+        <v>3.49</v>
       </c>
       <c r="M10">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P10">
-        <v>1541.94</v>
+        <v>1541.74</v>
       </c>
       <c r="Q10">
-        <v>1584.82</v>
+        <v>1583.12</v>
       </c>
       <c r="R10">
-        <v>1580.64</v>
+        <v>1582.85</v>
       </c>
       <c r="S10">
-        <v>1518.32</v>
+        <v>1518.56</v>
       </c>
       <c r="T10">
-        <v>3.79</v>
+        <v>2.6</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1938,34 +1900,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>49.07</v>
+        <v>45.81</v>
       </c>
       <c r="Z10">
-        <v>-11.11</v>
+        <v>-11.21</v>
       </c>
       <c r="AA10">
-        <v>-3.03</v>
+        <v>-4.67</v>
       </c>
       <c r="AB10">
-        <v>-8.08</v>
+        <v>-6.54</v>
       </c>
       <c r="AC10">
-        <v>34.65</v>
+        <v>44.25</v>
       </c>
       <c r="AD10">
-        <v>18.59</v>
+        <v>31.49</v>
       </c>
       <c r="AE10">
-        <v>43.04</v>
+        <v>42.9</v>
       </c>
       <c r="AF10">
-        <v>34.5</v>
+        <v>-21.56</v>
       </c>
       <c r="AG10">
-        <v>1653.87</v>
+        <v>1653.09</v>
       </c>
       <c r="AH10">
-        <v>1515.76</v>
+        <v>1513.14</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1974,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>33.35</v>
+        <v>29.65</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2173,1300 +2135,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.84</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-11.63</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.25</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-11.28</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-10.13</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-10.99</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-4.61</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>14.47</v>
+      </c>
+      <c r="D12" s="6">
+        <v>11.41</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-15.1</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-14.61</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.9</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-3.12</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.48</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.85</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-8.07</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-7.83</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.96</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-6.01</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.96</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-5.39</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.81</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-6.39</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-5.93</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-2.16</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-0.06</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-5.37</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-4.95</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-15.95</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-14.62</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>27.13</v>
+      </c>
+      <c r="D27" s="6">
+        <v>27.09</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
         <v>-7.09</v>
       </c>
-      <c r="D9" s="7">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D28" s="6">
+        <v>-5.56</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>17.88</v>
+      </c>
+      <c r="D29" s="6">
+        <v>17.46</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>10.34</v>
+      </c>
+      <c r="D30" s="6">
+        <v>9.07</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-46.14</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-45.98</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-18.15</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-18</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>4.35</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.49</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-20.1</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-17.8</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-11.63</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-3.45</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.01</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-10.15</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-12.25</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>14.92</v>
+      </c>
+      <c r="D36" s="6">
+        <v>15.98</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-8</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-10.13</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.65</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-2.17</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>12.38</v>
+      </c>
+      <c r="D38" s="6">
+        <v>12.12</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>19.1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>14.47</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-4.63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>12.36</v>
+      </c>
+      <c r="D39" s="6">
+        <v>12.69</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-12.13</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-15.1</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-16.84</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-16.28</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.9</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-7.46</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-5.98</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="E17" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>8.92</v>
+      </c>
+      <c r="D42" s="6">
+        <v>6.54</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1.48</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.23</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-23.5</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-23.34</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.99</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-4.13</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-20.33</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-19.26</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-4.68</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-8.07</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-16.98</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-16.31</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-2.58</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-3.96</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-17.97</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-18.39</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-2.01</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.96</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-12.53</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-12.63</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>5.93</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-3.81</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-4.93</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-46.86</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-46.55</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-20.64</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-21.63</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-10.89</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-11.9</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>375</v>
+      </c>
+      <c r="D52" s="6">
+        <v>375.8</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3029.5</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3070</v>
+      </c>
+      <c r="E53" s="7">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>342.3</v>
+      </c>
+      <c r="D54" s="6">
+        <v>345.05</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>345.9</v>
+      </c>
+      <c r="D55" s="6">
+        <v>344.15</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>387.25</v>
+      </c>
+      <c r="D56" s="6">
+        <v>386.8</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>701.1</v>
+      </c>
+      <c r="D57" s="6">
+        <v>692.95</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-8.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>192.4</v>
+      </c>
+      <c r="D58" s="6">
+        <v>193.51</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3569.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3524.8</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-44.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1575.9</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1558</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-17.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>23</v>
+      </c>
+      <c r="D61" s="6">
+        <v>34</v>
+      </c>
+      <c r="E61" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>34</v>
+      </c>
+      <c r="D62" s="6">
+        <v>23</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>20.39</v>
+      </c>
+      <c r="D63" s="6">
+        <v>22.15</v>
+      </c>
+      <c r="E63" s="7">
         <v>1.76</v>
       </c>
-      <c r="E23" s="8">
-        <v>-4.17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>24.66</v>
+      </c>
+      <c r="D64" s="6">
+        <v>31.32</v>
+      </c>
+      <c r="E64" s="7">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>31.27</v>
+      </c>
+      <c r="D65" s="6">
+        <v>33.69</v>
+      </c>
+      <c r="E65" s="7">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>31.09</v>
+      </c>
+      <c r="D66" s="6">
+        <v>30.16</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>39.82</v>
+      </c>
+      <c r="D67" s="6">
+        <v>39.52</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>64.09</v>
+      </c>
+      <c r="D68" s="6">
+        <v>61.02</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-5.14</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-6.39</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>19.52</v>
+      </c>
+      <c r="D69" s="6">
+        <v>22.36</v>
+      </c>
+      <c r="E69" s="7">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0.51</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-2.16</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>46.06</v>
+      </c>
+      <c r="D70" s="6">
+        <v>39.91</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0.76</v>
-      </c>
-      <c r="E26" s="9">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>49.07</v>
+      </c>
+      <c r="D71" s="6">
+        <v>45.81</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-4.77</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-5.37</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-11.79</v>
+      </c>
+      <c r="D72" s="6">
+        <v>14.48</v>
+      </c>
+      <c r="E72" s="7">
+        <v>26.27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-15.94</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-15.95</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>30.65</v>
+      </c>
+      <c r="D73" s="6">
+        <v>38.95</v>
+      </c>
+      <c r="E73" s="7">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>32.42</v>
-      </c>
-      <c r="D29" s="7">
-        <v>27.13</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-5.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-26.42</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-39.61</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-13.19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-4.76</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-7.09</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-10.57</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-26.34</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-15.77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>23.01</v>
-      </c>
-      <c r="D31" s="7">
-        <v>17.88</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-5.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>28.35</v>
+      </c>
+      <c r="D76" s="6">
+        <v>3.91</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-24.44</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>14.13</v>
-      </c>
-      <c r="D32" s="7">
-        <v>10.34</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-28.17</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-53.73</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-25.56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-44.73</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-46.14</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-19.53</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-23.63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-19.11</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-18.15</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="D79" s="6">
+        <v>38.25</v>
+      </c>
+      <c r="E79" s="7">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>3.93</v>
-      </c>
-      <c r="D35" s="7">
-        <v>4.35</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-18.32</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-20.1</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-0.87</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-3.45</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>19.57</v>
-      </c>
-      <c r="D38" s="7">
-        <v>14.92</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>5.8</v>
-      </c>
-      <c r="D39" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>14.07</v>
-      </c>
-      <c r="D40" s="7">
-        <v>12.38</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>15.71</v>
-      </c>
-      <c r="D41" s="7">
-        <v>12.36</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-15.5</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-16.84</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-6.53</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-7.46</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>8.09</v>
-      </c>
-      <c r="D44" s="7">
-        <v>8.92</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-22.55</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-23.5</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-18.29</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-20.33</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-13.62</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-16.98</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-3.36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-16.28</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-17.97</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-10.28</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-12.53</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-3.81</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-3.81</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-45.66</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-46.86</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-20.49</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-20.64</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-12.86</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-10.89</v>
-      </c>
-      <c r="E53" s="9">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>379.65</v>
-      </c>
-      <c r="D54" s="7">
-        <v>375</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>3107</v>
-      </c>
-      <c r="D55" s="7">
-        <v>3029.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-77.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>356.15</v>
-      </c>
-      <c r="D56" s="7">
-        <v>342.3</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-13.85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>353.05</v>
-      </c>
-      <c r="D57" s="7">
-        <v>345.9</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-7.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>397.2</v>
-      </c>
-      <c r="D58" s="7">
-        <v>387.25</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-9.949999999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>728.9</v>
-      </c>
-      <c r="D59" s="7">
-        <v>701.1</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-27.8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>196.73</v>
-      </c>
-      <c r="D60" s="7">
-        <v>192.4</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-4.33</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>3576</v>
-      </c>
-      <c r="D61" s="7">
-        <v>3569.2</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1541</v>
-      </c>
-      <c r="D62" s="7">
-        <v>1575.9</v>
-      </c>
-      <c r="E62" s="9">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>23.23</v>
-      </c>
-      <c r="D63" s="7">
-        <v>20.39</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>29.79</v>
-      </c>
-      <c r="D64" s="7">
-        <v>24.66</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-5.13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>37.71</v>
-      </c>
-      <c r="D65" s="7">
-        <v>31.27</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-6.44</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>35.2</v>
-      </c>
-      <c r="D66" s="7">
-        <v>31.09</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-4.11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>47.28</v>
-      </c>
-      <c r="D67" s="7">
-        <v>39.82</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-7.46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>76.22</v>
-      </c>
-      <c r="D68" s="7">
-        <v>64.09</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-12.13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>22.5</v>
-      </c>
-      <c r="D69" s="7">
-        <v>19.52</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>47.09</v>
-      </c>
-      <c r="D70" s="7">
-        <v>46.06</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>41.54</v>
-      </c>
-      <c r="D71" s="7">
-        <v>49.07</v>
-      </c>
-      <c r="E71" s="9">
-        <v>7.53</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="7">
-        <v>-58.19</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-11.79</v>
-      </c>
-      <c r="E72" s="9">
-        <v>46.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-23.43</v>
-      </c>
-      <c r="D73" s="7">
-        <v>30.65</v>
-      </c>
-      <c r="E73" s="9">
-        <v>54.08</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>14.57</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-26.42</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-40.99</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>3.03</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-10.57</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-13.6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-22.18</v>
-      </c>
-      <c r="D76" s="7">
-        <v>28.35</v>
-      </c>
-      <c r="E76" s="9">
-        <v>50.53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>150.35</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-28.17</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-178.52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>10.87</v>
-      </c>
-      <c r="D78" s="7">
-        <v>4.1</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-6.77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>13.08</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-0.35</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-13.43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>1.03</v>
-      </c>
-      <c r="D80" s="7">
+      <c r="C80" s="6">
         <v>34.5</v>
       </c>
-      <c r="E80" s="9">
-        <v>33.47</v>
+      <c r="D80" s="6">
+        <v>-21.56</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-56.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3486,60 +3442,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>44.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>36.2</v>
       </c>
-      <c r="E2" s="12">
-        <v>30</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-5.8</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-6</v>
+      </c>
+      <c r="G2" s="11">
         <v>0.2</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -3641,61 +3597,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3582</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3299</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1977</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1653</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1147</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0486</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0454</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0374</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1114</v>
+      <c r="A2" s="14">
+        <v>0.3504</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3328</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1971</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1659</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1189</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0505</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0453</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0339</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1125</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,43 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-4.9% → -1.2%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-4.9%</t>
+  </si>
+  <si>
+    <t>-1.2%</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>24.7 → 31.3</t>
+    <t>22.1 → 39.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>24.7</t>
-  </si>
-  <si>
-    <t>31.3</t>
+    <t>22.1</t>
+  </si>
+  <si>
+    <t>39.9</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +439,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,10 +955,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>375.8</v>
+        <v>385.7</v>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>2.63</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +967,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-23.34</v>
+        <v>-21.32</v>
       </c>
       <c r="H2">
-        <v>0.21</v>
+        <v>2.85</v>
       </c>
       <c r="I2">
-        <v>-1.98</v>
+        <v>1.06</v>
       </c>
       <c r="J2">
-        <v>-7.84</v>
+        <v>-5.86</v>
       </c>
       <c r="K2">
-        <v>-17.8</v>
+        <v>-15.47</v>
       </c>
       <c r="L2">
-        <v>-4.95</v>
+        <v>-3.48</v>
       </c>
       <c r="M2">
-        <v>11.89</v>
+        <v>11.6</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>378.78</v>
+        <v>379.59</v>
       </c>
       <c r="Q2">
-        <v>389.26</v>
+        <v>388.22</v>
       </c>
       <c r="R2">
-        <v>414.81</v>
+        <v>413.51</v>
       </c>
       <c r="S2">
-        <v>435.09</v>
+        <v>434.99</v>
       </c>
       <c r="T2">
-        <v>-13.63</v>
+        <v>-11.33</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1021,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>22.15</v>
+        <v>39.9</v>
       </c>
       <c r="Z2">
-        <v>-10.36</v>
+        <v>-9.41</v>
       </c>
       <c r="AA2">
-        <v>-10.53</v>
+        <v>-10.31</v>
       </c>
       <c r="AB2">
-        <v>0.17</v>
+        <v>0.9</v>
       </c>
       <c r="AC2">
-        <v>6.53</v>
+        <v>39.86</v>
       </c>
       <c r="AD2">
-        <v>3.26</v>
+        <v>15.99</v>
       </c>
       <c r="AE2">
-        <v>8.31</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AF2">
-        <v>14.48</v>
+        <v>15.93</v>
       </c>
       <c r="AG2">
-        <v>407.69</v>
+        <v>404.76</v>
       </c>
       <c r="AH2">
-        <v>370.84</v>
+        <v>371.67</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1032,7 +1057,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>63.44</v>
+        <v>57.19</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1068,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3070</v>
+        <v>3076.5</v>
       </c>
       <c r="D3">
-        <v>1.34</v>
+        <v>0.21</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1080,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-19.26</v>
+        <v>-19.09</v>
       </c>
       <c r="H3">
-        <v>4.74</v>
+        <v>4.96</v>
       </c>
       <c r="I3">
-        <v>-2.85</v>
+        <v>-2.33</v>
       </c>
       <c r="J3">
-        <v>-9.449999999999999</v>
+        <v>-10.08</v>
       </c>
       <c r="K3">
-        <v>-2.01</v>
+        <v>-1.91</v>
       </c>
       <c r="L3">
-        <v>-14.62</v>
+        <v>-14.3</v>
       </c>
       <c r="M3">
-        <v>33.28</v>
+        <v>33.43</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>3096.06</v>
+        <v>3081.36</v>
       </c>
       <c r="Q3">
-        <v>3251.13</v>
+        <v>3234.21</v>
       </c>
       <c r="R3">
-        <v>3271.9</v>
+        <v>3271.38</v>
       </c>
       <c r="S3">
-        <v>3313.14</v>
+        <v>3309.73</v>
       </c>
       <c r="T3">
-        <v>-7.34</v>
+        <v>-7.05</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1134,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.32</v>
+        <v>32.35</v>
       </c>
       <c r="Z3">
-        <v>-69.78</v>
+        <v>-71.04000000000001</v>
       </c>
       <c r="AA3">
-        <v>-44.17</v>
+        <v>-49.55</v>
       </c>
       <c r="AB3">
-        <v>-25.61</v>
+        <v>-21.5</v>
       </c>
       <c r="AC3">
-        <v>9.859999999999999</v>
+        <v>21.25</v>
       </c>
       <c r="AD3">
-        <v>3.76</v>
+        <v>10.37</v>
       </c>
       <c r="AE3">
-        <v>66.93000000000001</v>
+        <v>67.92</v>
       </c>
       <c r="AF3">
-        <v>38.95</v>
+        <v>6.81</v>
       </c>
       <c r="AG3">
-        <v>3521.94</v>
+        <v>3504.2</v>
       </c>
       <c r="AH3">
-        <v>2980.32</v>
+        <v>2964.21</v>
       </c>
       <c r="AI3">
         <v>3273.14</v>
@@ -1145,7 +1170,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>71.04000000000001</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1181,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>345.05</v>
+        <v>345.7</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>0.19</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,25 +1193,25 @@
         <v>270.1</v>
       </c>
       <c r="G4">
-        <v>-16.31</v>
+        <v>-16.15</v>
       </c>
       <c r="H4">
-        <v>27.75</v>
+        <v>27.99</v>
       </c>
       <c r="I4">
-        <v>-7.83</v>
+        <v>-4.96</v>
       </c>
       <c r="J4">
-        <v>-11.28</v>
+        <v>-10.49</v>
       </c>
       <c r="K4">
-        <v>15.98</v>
+        <v>16.77</v>
       </c>
       <c r="L4">
-        <v>27.09</v>
+        <v>27.4</v>
       </c>
       <c r="M4">
-        <v>16.59</v>
+        <v>15.87</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1195,61 +1220,61 @@
         <v>81</v>
       </c>
       <c r="P4">
-        <v>353.3</v>
+        <v>349.69</v>
       </c>
       <c r="Q4">
-        <v>371.41</v>
+        <v>369.22</v>
       </c>
       <c r="R4">
-        <v>370.41</v>
+        <v>370.69</v>
       </c>
       <c r="S4">
-        <v>344.49</v>
+        <v>344.36</v>
       </c>
       <c r="T4">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="U4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V4" t="s">
         <v>48</v>
       </c>
       <c r="W4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>33.69</v>
+        <v>34.28</v>
       </c>
       <c r="Z4">
-        <v>-6.5</v>
+        <v>-7.33</v>
       </c>
       <c r="AA4">
-        <v>-2.14</v>
+        <v>-3.18</v>
       </c>
       <c r="AB4">
-        <v>-4.35</v>
+        <v>-4.15</v>
       </c>
       <c r="AC4">
-        <v>3.68</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AD4">
-        <v>1.64</v>
+        <v>4.28</v>
       </c>
       <c r="AE4">
-        <v>11.33</v>
+        <v>11.18</v>
       </c>
       <c r="AF4">
-        <v>-39.61</v>
+        <v>-8.08</v>
       </c>
       <c r="AG4">
-        <v>397.17</v>
+        <v>395.91</v>
       </c>
       <c r="AH4">
-        <v>345.66</v>
+        <v>342.53</v>
       </c>
       <c r="AI4">
         <v>378.22</v>
@@ -1258,7 +1283,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>31.12</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1294,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>344.15</v>
+        <v>363.7</v>
       </c>
       <c r="D5">
-        <v>-0.51</v>
+        <v>5.68</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1306,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-18.39</v>
+        <v>-13.75</v>
       </c>
       <c r="H5">
-        <v>16.96</v>
+        <v>23.6</v>
       </c>
       <c r="I5">
-        <v>-6.01</v>
+        <v>-1.73</v>
       </c>
       <c r="J5">
-        <v>-10.99</v>
+        <v>-5.32</v>
       </c>
       <c r="K5">
-        <v>-0.65</v>
+        <v>3.87</v>
       </c>
       <c r="L5">
-        <v>-5.56</v>
+        <v>-0.45</v>
       </c>
       <c r="M5">
-        <v>5.05</v>
+        <v>6.02</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>354.57</v>
+        <v>353.29</v>
       </c>
       <c r="Q5">
-        <v>365</v>
+        <v>364.5</v>
       </c>
       <c r="R5">
-        <v>374.35</v>
+        <v>374.44</v>
       </c>
       <c r="S5">
-        <v>361.98</v>
+        <v>361.7</v>
       </c>
       <c r="T5">
-        <v>-4.93</v>
+        <v>0.55</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1332,37 +1357,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>30.16</v>
+        <v>48.62</v>
       </c>
       <c r="Z5">
-        <v>-6.92</v>
+        <v>-6</v>
       </c>
       <c r="AA5">
-        <v>-4.77</v>
+        <v>-5.01</v>
       </c>
       <c r="AB5">
-        <v>-2.15</v>
+        <v>-0.99</v>
       </c>
       <c r="AC5">
-        <v>9.74</v>
+        <v>34.02</v>
       </c>
       <c r="AD5">
-        <v>30.65</v>
+        <v>23.26</v>
       </c>
       <c r="AE5">
-        <v>11.25</v>
+        <v>12.15</v>
       </c>
       <c r="AF5">
-        <v>-26.34</v>
+        <v>52.47</v>
       </c>
       <c r="AG5">
-        <v>385.37</v>
+        <v>384.46</v>
       </c>
       <c r="AH5">
-        <v>344.64</v>
+        <v>344.55</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1371,7 +1396,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>46.1</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1407,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>386.8</v>
+        <v>389.55</v>
       </c>
       <c r="D6">
-        <v>-0.12</v>
+        <v>0.71</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1419,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-12.63</v>
+        <v>-12.01</v>
       </c>
       <c r="H6">
-        <v>38.37</v>
+        <v>39.35</v>
       </c>
       <c r="I6">
-        <v>-5.39</v>
+        <v>-3.04</v>
       </c>
       <c r="J6">
-        <v>-4.61</v>
+        <v>-3.71</v>
       </c>
       <c r="K6">
-        <v>12.12</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L6">
-        <v>17.46</v>
+        <v>16.32</v>
       </c>
       <c r="M6">
-        <v>-11.25</v>
+        <v>-11.39</v>
       </c>
       <c r="N6">
         <v>77</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P6">
-        <v>394.62</v>
+        <v>392.18</v>
       </c>
       <c r="Q6">
-        <v>398.13</v>
+        <v>397.29</v>
       </c>
       <c r="R6">
-        <v>400.49</v>
+        <v>400.63</v>
       </c>
       <c r="S6">
-        <v>370.52</v>
+        <v>370.84</v>
       </c>
       <c r="T6">
-        <v>4.39</v>
+        <v>5.04</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1473,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>39.52</v>
+        <v>42.41</v>
       </c>
       <c r="Z6">
-        <v>-1.88</v>
+        <v>-2.28</v>
       </c>
       <c r="AA6">
-        <v>-0.5600000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="AB6">
-        <v>-1.31</v>
+        <v>-1.38</v>
       </c>
       <c r="AC6">
-        <v>22.37</v>
+        <v>14.37</v>
       </c>
       <c r="AD6">
-        <v>39.87</v>
+        <v>25.33</v>
       </c>
       <c r="AE6">
-        <v>11.26</v>
+        <v>11.01</v>
       </c>
       <c r="AF6">
-        <v>3.91</v>
+        <v>-70.42</v>
       </c>
       <c r="AG6">
-        <v>411.94</v>
+        <v>411.05</v>
       </c>
       <c r="AH6">
-        <v>384.31</v>
+        <v>383.53</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1484,7 +1509,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>25.08</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1520,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>692.95</v>
+        <v>720.2</v>
       </c>
       <c r="D7">
-        <v>-1.16</v>
+        <v>3.93</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1507,46 +1532,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-4.93</v>
+        <v>-1.19</v>
       </c>
       <c r="H7">
-        <v>36.82</v>
+        <v>42.21</v>
       </c>
       <c r="I7">
-        <v>1.81</v>
+        <v>6.51</v>
       </c>
       <c r="J7">
-        <v>11.41</v>
+        <v>15.99</v>
       </c>
       <c r="K7">
-        <v>12.69</v>
+        <v>13.83</v>
       </c>
       <c r="L7">
-        <v>9.07</v>
+        <v>14.89</v>
       </c>
       <c r="M7">
-        <v>35.04</v>
+        <v>36.49</v>
       </c>
       <c r="N7">
         <v>88</v>
       </c>
       <c r="O7">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>703.62</v>
+        <v>712.42</v>
       </c>
       <c r="Q7">
-        <v>663.87</v>
+        <v>669.1900000000001</v>
       </c>
       <c r="R7">
-        <v>618.42</v>
+        <v>621.16</v>
       </c>
       <c r="S7">
-        <v>591.59</v>
+        <v>592.25</v>
       </c>
       <c r="T7">
-        <v>17.13</v>
+        <v>21.6</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,34 +1586,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>61.02</v>
+        <v>66.75</v>
       </c>
       <c r="Z7">
-        <v>25.29</v>
+        <v>26.25</v>
       </c>
       <c r="AA7">
-        <v>22.48</v>
+        <v>23.24</v>
       </c>
       <c r="AB7">
-        <v>2.81</v>
+        <v>3.01</v>
       </c>
       <c r="AC7">
-        <v>35.86</v>
+        <v>15.1</v>
       </c>
       <c r="AD7">
-        <v>58.09</v>
+        <v>39.45</v>
       </c>
       <c r="AE7">
-        <v>25.98</v>
+        <v>26.48</v>
       </c>
       <c r="AF7">
-        <v>-53.73</v>
+        <v>-7.98</v>
       </c>
       <c r="AG7">
-        <v>729.5599999999999</v>
+        <v>735.05</v>
       </c>
       <c r="AH7">
-        <v>598.1799999999999</v>
+        <v>603.3200000000001</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1597,7 +1622,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>66.18000000000001</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1633,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>193.51</v>
+        <v>195.17</v>
       </c>
       <c r="D8">
-        <v>0.58</v>
+        <v>0.86</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1620,25 +1645,25 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-46.55</v>
+        <v>-46.09</v>
       </c>
       <c r="H8">
-        <v>0.58</v>
+        <v>1.44</v>
       </c>
       <c r="I8">
-        <v>-5.93</v>
+        <v>-2.1</v>
       </c>
       <c r="J8">
-        <v>-14.61</v>
+        <v>-11.84</v>
       </c>
       <c r="K8">
-        <v>-16.28</v>
+        <v>-16.21</v>
       </c>
       <c r="L8">
-        <v>-45.98</v>
+        <v>-45.36</v>
       </c>
       <c r="M8">
-        <v>-3.39</v>
+        <v>-3.67</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1647,19 +1672,19 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>195.71</v>
+        <v>194.88</v>
       </c>
       <c r="Q8">
-        <v>208.65</v>
+        <v>207.43</v>
       </c>
       <c r="R8">
-        <v>218.45</v>
+        <v>217.71</v>
       </c>
       <c r="S8">
-        <v>255.84</v>
+        <v>255.23</v>
       </c>
       <c r="T8">
-        <v>-24.36</v>
+        <v>-23.53</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1699,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>22.36</v>
+        <v>26.54</v>
       </c>
       <c r="Z8">
         <v>-7.36</v>
       </c>
       <c r="AA8">
-        <v>-5.89</v>
+        <v>-6.18</v>
       </c>
       <c r="AB8">
-        <v>-1.48</v>
+        <v>-1.18</v>
       </c>
       <c r="AC8">
-        <v>7.29</v>
+        <v>22.96</v>
       </c>
       <c r="AD8">
-        <v>2.88</v>
+        <v>10.31</v>
       </c>
       <c r="AE8">
-        <v>6.18</v>
+        <v>6.24</v>
       </c>
       <c r="AF8">
-        <v>-19.53</v>
+        <v>6.11</v>
       </c>
       <c r="AG8">
-        <v>227.6</v>
+        <v>226.57</v>
       </c>
       <c r="AH8">
-        <v>189.7</v>
+        <v>188.29</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1710,7 +1735,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>60.89</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1746,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3524.8</v>
+        <v>3552.9</v>
       </c>
       <c r="D9">
-        <v>-1.24</v>
+        <v>0.8</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1733,25 +1758,25 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.63</v>
+        <v>-21</v>
       </c>
       <c r="H9">
-        <v>6.52</v>
+        <v>7.37</v>
       </c>
       <c r="I9">
-        <v>-2.97</v>
+        <v>-1.15</v>
       </c>
       <c r="J9">
-        <v>-3.12</v>
+        <v>-1.14</v>
       </c>
       <c r="K9">
-        <v>-8.710000000000001</v>
+        <v>-8.25</v>
       </c>
       <c r="L9">
-        <v>-18</v>
+        <v>-17.55</v>
       </c>
       <c r="M9">
-        <v>19.71</v>
+        <v>20.33</v>
       </c>
       <c r="N9">
         <v>23</v>
@@ -1760,19 +1785,19 @@
         <v>39</v>
       </c>
       <c r="P9">
-        <v>3563.06</v>
+        <v>3554.78</v>
       </c>
       <c r="Q9">
-        <v>3568.51</v>
+        <v>3566.72</v>
       </c>
       <c r="R9">
-        <v>3613.96</v>
+        <v>3610.14</v>
       </c>
       <c r="S9">
-        <v>3682.72</v>
+        <v>3681.84</v>
       </c>
       <c r="T9">
-        <v>-4.29</v>
+        <v>-3.5</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1812,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.91</v>
+        <v>44.92</v>
       </c>
       <c r="Z9">
-        <v>-15.97</v>
+        <v>-16.12</v>
       </c>
       <c r="AA9">
-        <v>-17.84</v>
+        <v>-17.49</v>
       </c>
       <c r="AB9">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AC9">
-        <v>39.88</v>
+        <v>37.02</v>
       </c>
       <c r="AD9">
-        <v>43.74</v>
+        <v>40.15</v>
       </c>
       <c r="AE9">
-        <v>62.34</v>
+        <v>61.71</v>
       </c>
       <c r="AF9">
-        <v>38.25</v>
+        <v>-21.52</v>
       </c>
       <c r="AG9">
-        <v>3631.23</v>
+        <v>3629.04</v>
       </c>
       <c r="AH9">
-        <v>3505.79</v>
+        <v>3504.39</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1823,7 +1848,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.28</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1859,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="D10">
-        <v>-1.14</v>
+        <v>0.19</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,22 +1871,22 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.9</v>
+        <v>-11.73</v>
       </c>
       <c r="H10">
-        <v>17.48</v>
+        <v>17.7</v>
       </c>
       <c r="I10">
-        <v>-0.06</v>
+        <v>3.51</v>
       </c>
       <c r="J10">
-        <v>-3.23</v>
+        <v>-1.95</v>
       </c>
       <c r="K10">
-        <v>6.54</v>
+        <v>7.83</v>
       </c>
       <c r="L10">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="M10">
         <v>4.53</v>
@@ -1870,64 +1895,64 @@
         <v>66</v>
       </c>
       <c r="O10">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P10">
-        <v>1541.74</v>
+        <v>1552.34</v>
       </c>
       <c r="Q10">
-        <v>1583.12</v>
+        <v>1581.68</v>
       </c>
       <c r="R10">
-        <v>1582.85</v>
+        <v>1585.5</v>
       </c>
       <c r="S10">
-        <v>1518.56</v>
+        <v>1518.78</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="U10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V10" t="s">
         <v>48</v>
       </c>
       <c r="W10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>45.81</v>
+        <v>46.46</v>
       </c>
       <c r="Z10">
-        <v>-11.21</v>
+        <v>-10.91</v>
       </c>
       <c r="AA10">
-        <v>-4.67</v>
+        <v>-5.92</v>
       </c>
       <c r="AB10">
-        <v>-6.54</v>
+        <v>-5</v>
       </c>
       <c r="AC10">
-        <v>44.25</v>
+        <v>50.16</v>
       </c>
       <c r="AD10">
-        <v>31.49</v>
+        <v>43.02</v>
       </c>
       <c r="AE10">
-        <v>42.9</v>
+        <v>42.1</v>
       </c>
       <c r="AF10">
-        <v>-21.56</v>
+        <v>45.56</v>
       </c>
       <c r="AG10">
-        <v>1653.09</v>
+        <v>1652.25</v>
       </c>
       <c r="AH10">
-        <v>1513.14</v>
+        <v>1511.1</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1936,7 +1961,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>29.65</v>
+        <v>25.78</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2142,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1294 +2160,1360 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
+      <c r="A6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-7.84</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.19</v>
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-7.84</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-5.86</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-11.63</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C13" s="7">
         <v>-9.449999999999999</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-10.08</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-12.25</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C14" s="7">
         <v>-11.28</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-10.49</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-10.13</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C15" s="7">
         <v>-10.99</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-5.32</v>
+      </c>
+      <c r="E15" s="8">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-4.5</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C16" s="7">
         <v>-4.61</v>
       </c>
-      <c r="E11" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-3.71</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>14.47</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C17" s="7">
         <v>11.41</v>
       </c>
-      <c r="E12" s="8">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D17" s="7">
+        <v>15.99</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-15.1</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C18" s="7">
         <v>-14.61</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-11.84</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>-1.9</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C19" s="7">
         <v>-3.12</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D19" s="7">
+        <v>-1.14</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C20" s="7">
+        <v>-3.23</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.95</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.85</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-2.33</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-7.83</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.96</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-6.01</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.73</v>
+      </c>
+      <c r="E24" s="8">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-5.39</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-3.04</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>1.81</v>
+      </c>
+      <c r="D26" s="7">
+        <v>6.51</v>
+      </c>
+      <c r="E26" s="8">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-5.93</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-2.1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-2.97</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-1.15</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-0.06</v>
+      </c>
+      <c r="D29" s="7">
+        <v>3.51</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-4.95</v>
+      </c>
+      <c r="D30" s="7">
         <v>-3.48</v>
       </c>
-      <c r="D15" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="E30" s="8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-14.62</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-14.3</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>27.09</v>
+      </c>
+      <c r="D32" s="7">
+        <v>27.4</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-5.56</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="E33" s="8">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>17.46</v>
+      </c>
+      <c r="D34" s="7">
+        <v>16.32</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>9.07</v>
+      </c>
+      <c r="D35" s="7">
+        <v>14.89</v>
+      </c>
+      <c r="E35" s="8">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-45.98</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-45.36</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-18</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-17.55</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="7">
+        <v>3.49</v>
+      </c>
+      <c r="D38" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-17.8</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-15.47</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-2.01</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-1.91</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-8.07</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-7.83</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>15.98</v>
+      </c>
+      <c r="D41" s="7">
+        <v>16.77</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.96</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-6.01</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-0.65</v>
+      </c>
+      <c r="D42" s="7">
+        <v>3.87</v>
+      </c>
+      <c r="E42" s="8">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.96</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.39</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>12.12</v>
+      </c>
+      <c r="D43" s="7">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1.76</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.81</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>12.69</v>
+      </c>
+      <c r="D44" s="7">
+        <v>13.83</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-5.93</v>
-      </c>
-      <c r="E22" s="7">
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-16.28</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-16.21</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-8.25</v>
+      </c>
+      <c r="E46" s="8">
         <v>0.46</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="7">
+        <v>6.54</v>
+      </c>
+      <c r="D47" s="7">
+        <v>7.83</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-23.34</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-21.32</v>
+      </c>
+      <c r="E48" s="8">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-19.26</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-19.09</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-16.31</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-16.15</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-18.39</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-13.75</v>
+      </c>
+      <c r="E51" s="8">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-12.63</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-12.01</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-4.93</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-1.19</v>
+      </c>
+      <c r="E53" s="8">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-46.55</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-46.09</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-2.16</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="7">
+        <v>-21.63</v>
+      </c>
+      <c r="D55" s="7">
+        <v>-21</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.76</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-0.06</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="7">
+        <v>-11.9</v>
+      </c>
+      <c r="D56" s="7">
+        <v>-11.73</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>375.8</v>
+      </c>
+      <c r="D57" s="7">
+        <v>385.7</v>
+      </c>
+      <c r="E57" s="8">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-15.95</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-14.62</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>3070</v>
+      </c>
+      <c r="D58" s="7">
+        <v>3076.5</v>
+      </c>
+      <c r="E58" s="8">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>27.13</v>
-      </c>
-      <c r="D27" s="6">
-        <v>27.09</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>345.05</v>
+      </c>
+      <c r="D59" s="7">
+        <v>345.7</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-7.09</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-5.56</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>344.15</v>
+      </c>
+      <c r="D60" s="7">
+        <v>363.7</v>
+      </c>
+      <c r="E60" s="8">
+        <v>19.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>17.88</v>
-      </c>
-      <c r="D29" s="6">
-        <v>17.46</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>386.8</v>
+      </c>
+      <c r="D61" s="7">
+        <v>389.55</v>
+      </c>
+      <c r="E61" s="8">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>10.34</v>
-      </c>
-      <c r="D30" s="6">
-        <v>9.07</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>692.95</v>
+      </c>
+      <c r="D62" s="7">
+        <v>720.2</v>
+      </c>
+      <c r="E62" s="8">
+        <v>27.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-46.14</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-45.98</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>193.51</v>
+      </c>
+      <c r="D63" s="7">
+        <v>195.17</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-18.15</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-18</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="7">
+        <v>3524.8</v>
+      </c>
+      <c r="D64" s="7">
+        <v>3552.9</v>
+      </c>
+      <c r="E64" s="8">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>4.35</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.49</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="7">
+        <v>1558</v>
+      </c>
+      <c r="D65" s="7">
+        <v>1561</v>
+      </c>
+      <c r="E65" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-20.1</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-17.8</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>22.15</v>
+      </c>
+      <c r="D66" s="7">
+        <v>39.9</v>
+      </c>
+      <c r="E66" s="8">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-2.01</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>31.32</v>
+      </c>
+      <c r="D67" s="7">
+        <v>32.35</v>
+      </c>
+      <c r="E67" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>14.92</v>
-      </c>
-      <c r="D36" s="6">
-        <v>15.98</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>33.69</v>
+      </c>
+      <c r="D68" s="7">
+        <v>34.28</v>
+      </c>
+      <c r="E68" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.65</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>30.16</v>
+      </c>
+      <c r="D69" s="7">
+        <v>48.62</v>
+      </c>
+      <c r="E69" s="8">
+        <v>18.46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>12.38</v>
-      </c>
-      <c r="D38" s="6">
-        <v>12.12</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>39.52</v>
+      </c>
+      <c r="D70" s="7">
+        <v>42.41</v>
+      </c>
+      <c r="E70" s="8">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>12.36</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12.69</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>61.02</v>
+      </c>
+      <c r="D71" s="7">
+        <v>66.75</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-16.84</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-16.28</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>22.36</v>
+      </c>
+      <c r="D72" s="7">
+        <v>26.54</v>
+      </c>
+      <c r="E72" s="8">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-7.46</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>39.91</v>
+      </c>
+      <c r="D73" s="7">
+        <v>44.92</v>
+      </c>
+      <c r="E73" s="8">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>8.92</v>
-      </c>
-      <c r="D42" s="6">
-        <v>6.54</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>45.81</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46.46</v>
+      </c>
+      <c r="E74" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-23.5</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-23.34</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>14.48</v>
+      </c>
+      <c r="D75" s="7">
+        <v>15.93</v>
+      </c>
+      <c r="E75" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-20.33</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-19.26</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>38.95</v>
+      </c>
+      <c r="D76" s="7">
+        <v>6.81</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-32.14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-16.98</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-16.31</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-39.61</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-8.08</v>
+      </c>
+      <c r="E77" s="8">
+        <v>31.53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-17.97</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.39</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-26.34</v>
+      </c>
+      <c r="D78" s="7">
+        <v>52.47</v>
+      </c>
+      <c r="E78" s="8">
+        <v>78.81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-12.53</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-12.63</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>3.91</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-70.42</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-74.33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-3.81</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-4.93</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-53.73</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-7.98</v>
+      </c>
+      <c r="E80" s="8">
+        <v>45.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-46.86</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-46.55</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-19.53</v>
+      </c>
+      <c r="D81" s="7">
+        <v>6.11</v>
+      </c>
+      <c r="E81" s="8">
+        <v>25.64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-20.64</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-21.63</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>38.25</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-21.52</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-59.77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-10.89</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>375</v>
-      </c>
-      <c r="D52" s="6">
-        <v>375.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3029.5</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3070</v>
-      </c>
-      <c r="E53" s="7">
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>342.3</v>
-      </c>
-      <c r="D54" s="6">
-        <v>345.05</v>
-      </c>
-      <c r="E54" s="7">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>345.9</v>
-      </c>
-      <c r="D55" s="6">
-        <v>344.15</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>387.25</v>
-      </c>
-      <c r="D56" s="6">
-        <v>386.8</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>701.1</v>
-      </c>
-      <c r="D57" s="6">
-        <v>692.95</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-8.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>192.4</v>
-      </c>
-      <c r="D58" s="6">
-        <v>193.51</v>
-      </c>
-      <c r="E58" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>3569.2</v>
-      </c>
-      <c r="D59" s="6">
-        <v>3524.8</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-44.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1575.9</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1558</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-17.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>23</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="6">
-        <v>23</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>20.39</v>
-      </c>
-      <c r="D63" s="6">
-        <v>22.15</v>
-      </c>
-      <c r="E63" s="7">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>24.66</v>
-      </c>
-      <c r="D64" s="6">
-        <v>31.32</v>
-      </c>
-      <c r="E64" s="7">
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>31.27</v>
-      </c>
-      <c r="D65" s="6">
-        <v>33.69</v>
-      </c>
-      <c r="E65" s="7">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>31.09</v>
-      </c>
-      <c r="D66" s="6">
-        <v>30.16</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>39.82</v>
-      </c>
-      <c r="D67" s="6">
-        <v>39.52</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>64.09</v>
-      </c>
-      <c r="D68" s="6">
-        <v>61.02</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>19.52</v>
-      </c>
-      <c r="D69" s="6">
-        <v>22.36</v>
-      </c>
-      <c r="E69" s="7">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>46.06</v>
-      </c>
-      <c r="D70" s="6">
-        <v>39.91</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-6.15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>49.07</v>
-      </c>
-      <c r="D71" s="6">
-        <v>45.81</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-11.79</v>
-      </c>
-      <c r="D72" s="6">
-        <v>14.48</v>
-      </c>
-      <c r="E72" s="7">
-        <v>26.27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>30.65</v>
-      </c>
-      <c r="D73" s="6">
-        <v>38.95</v>
-      </c>
-      <c r="E73" s="7">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-26.42</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-39.61</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-13.19</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-10.57</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-26.34</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-15.77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>28.35</v>
-      </c>
-      <c r="D76" s="6">
-        <v>3.91</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-24.44</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-28.17</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-53.73</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-25.56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-19.53</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-23.63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-0.35</v>
-      </c>
-      <c r="D79" s="6">
-        <v>38.25</v>
-      </c>
-      <c r="E79" s="7">
-        <v>38.6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>34.5</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C83" s="7">
         <v>-21.56</v>
       </c>
-      <c r="E80" s="8">
-        <v>-56.06</v>
+      <c r="D83" s="7">
+        <v>45.56</v>
+      </c>
+      <c r="E83" s="8">
+        <v>67.12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3442,61 +3533,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>36.2</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>42.5</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-3.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1.1</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
-        <v>30</v>
+      <c r="I2" s="12">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3597,61 +3688,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3504</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3328</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1971</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1659</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1189</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0505</v>
-      </c>
-      <c r="G2" s="14">
+      <c r="A2" s="15">
+        <v>0.3649</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3343</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2033</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1587</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.116</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0602</v>
+      </c>
+      <c r="G2" s="15">
         <v>0.0453</v>
       </c>
-      <c r="H2" s="14">
-        <v>-0.0339</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1125</v>
+      <c r="H2" s="15">
+        <v>-0.0367</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1139</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,40 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-4.9% → -1.2%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-4.9%</t>
-  </si>
-  <si>
-    <t>-1.2%</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.6 → 50.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.6</t>
+  </si>
+  <si>
+    <t>50.6</t>
   </si>
   <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>22.1 → 39.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>22.1</t>
-  </si>
-  <si>
-    <t>39.9</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>26.5 → 35.8</t>
+  </si>
+  <si>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>35.8</t>
+  </si>
+  <si>
+    <t>44.9 → 55.2</t>
+  </si>
+  <si>
+    <t>44.9</t>
+  </si>
+  <si>
+    <t>55.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -431,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -439,7 +436,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -815,7 +811,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -955,10 +952,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>385.7</v>
+        <v>387.15</v>
       </c>
       <c r="D2">
-        <v>2.63</v>
+        <v>0.38</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -967,46 +964,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-21.32</v>
+        <v>-21.02</v>
       </c>
       <c r="H2">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="I2">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="J2">
-        <v>-5.86</v>
+        <v>-4.8</v>
       </c>
       <c r="K2">
-        <v>-15.47</v>
+        <v>-16.56</v>
       </c>
       <c r="L2">
-        <v>-3.48</v>
+        <v>-3.02</v>
       </c>
       <c r="M2">
-        <v>11.6</v>
+        <v>12.49</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>379.59</v>
+        <v>380.66</v>
       </c>
       <c r="Q2">
-        <v>388.22</v>
+        <v>387.38</v>
       </c>
       <c r="R2">
-        <v>413.51</v>
+        <v>412.01</v>
       </c>
       <c r="S2">
-        <v>434.99</v>
+        <v>434.87</v>
       </c>
       <c r="T2">
-        <v>-11.33</v>
+        <v>-10.97</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1021,34 +1018,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.9</v>
+        <v>41.99</v>
       </c>
       <c r="Z2">
-        <v>-9.41</v>
+        <v>-8.44</v>
       </c>
       <c r="AA2">
-        <v>-10.31</v>
+        <v>-9.94</v>
       </c>
       <c r="AB2">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="AC2">
+        <v>73.19</v>
+      </c>
+      <c r="AD2">
         <v>39.86</v>
       </c>
-      <c r="AD2">
-        <v>15.99</v>
-      </c>
       <c r="AE2">
-        <v>8.880000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AF2">
-        <v>15.93</v>
+        <v>54.85</v>
       </c>
       <c r="AG2">
-        <v>404.76</v>
+        <v>402.22</v>
       </c>
       <c r="AH2">
-        <v>371.67</v>
+        <v>372.55</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1057,7 +1054,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>57.19</v>
+        <v>50.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1068,10 +1065,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3076.5</v>
+        <v>3052</v>
       </c>
       <c r="D3">
-        <v>0.21</v>
+        <v>-0.8</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1080,46 +1077,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-19.09</v>
+        <v>-19.73</v>
       </c>
       <c r="H3">
-        <v>4.96</v>
+        <v>4.12</v>
       </c>
       <c r="I3">
-        <v>-2.33</v>
+        <v>-2.3</v>
       </c>
       <c r="J3">
-        <v>-10.08</v>
+        <v>-10.63</v>
       </c>
       <c r="K3">
-        <v>-1.91</v>
+        <v>-0.74</v>
       </c>
       <c r="L3">
-        <v>-14.3</v>
+        <v>-13.55</v>
       </c>
       <c r="M3">
-        <v>33.43</v>
+        <v>33.84</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>3081.36</v>
+        <v>3067</v>
       </c>
       <c r="Q3">
-        <v>3234.21</v>
+        <v>3215.57</v>
       </c>
       <c r="R3">
-        <v>3271.38</v>
+        <v>3270.71</v>
       </c>
       <c r="S3">
-        <v>3309.73</v>
+        <v>3306.29</v>
       </c>
       <c r="T3">
-        <v>-7.05</v>
+        <v>-7.69</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1134,34 +1131,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.35</v>
+        <v>30.49</v>
       </c>
       <c r="Z3">
-        <v>-71.04000000000001</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="AA3">
-        <v>-49.55</v>
+        <v>-54.27</v>
       </c>
       <c r="AB3">
-        <v>-21.5</v>
+        <v>-18.9</v>
       </c>
       <c r="AC3">
-        <v>21.25</v>
+        <v>32.36</v>
       </c>
       <c r="AD3">
-        <v>10.37</v>
+        <v>21.15</v>
       </c>
       <c r="AE3">
-        <v>67.92</v>
+        <v>66.37</v>
       </c>
       <c r="AF3">
-        <v>6.81</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="AG3">
-        <v>3504.2</v>
+        <v>3481.61</v>
       </c>
       <c r="AH3">
-        <v>2964.21</v>
+        <v>2949.52</v>
       </c>
       <c r="AI3">
         <v>3273.14</v>
@@ -1170,7 +1167,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>70.11</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1181,37 +1178,37 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>345.7</v>
+        <v>353.3</v>
       </c>
       <c r="D4">
-        <v>0.19</v>
+        <v>2.2</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>270.1</v>
+        <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-16.15</v>
+        <v>-14.31</v>
       </c>
       <c r="H4">
-        <v>27.99</v>
+        <v>29.44</v>
       </c>
       <c r="I4">
-        <v>-4.96</v>
+        <v>-1.66</v>
       </c>
       <c r="J4">
-        <v>-10.49</v>
+        <v>-9.32</v>
       </c>
       <c r="K4">
-        <v>16.77</v>
+        <v>20.13</v>
       </c>
       <c r="L4">
-        <v>27.4</v>
+        <v>30.8</v>
       </c>
       <c r="M4">
-        <v>15.87</v>
+        <v>16.81</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1220,19 +1217,19 @@
         <v>81</v>
       </c>
       <c r="P4">
-        <v>349.69</v>
+        <v>348.5</v>
       </c>
       <c r="Q4">
-        <v>369.22</v>
+        <v>367.76</v>
       </c>
       <c r="R4">
-        <v>370.69</v>
+        <v>371.02</v>
       </c>
       <c r="S4">
-        <v>344.36</v>
+        <v>344.28</v>
       </c>
       <c r="T4">
-        <v>0.39</v>
+        <v>2.62</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1247,34 +1244,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>34.28</v>
+        <v>40.9</v>
       </c>
       <c r="Z4">
-        <v>-7.33</v>
+        <v>-7.29</v>
       </c>
       <c r="AA4">
-        <v>-3.18</v>
+        <v>-4</v>
       </c>
       <c r="AB4">
-        <v>-4.15</v>
+        <v>-3.29</v>
       </c>
       <c r="AC4">
-        <v>9.140000000000001</v>
+        <v>26.59</v>
       </c>
       <c r="AD4">
-        <v>4.28</v>
+        <v>13.14</v>
       </c>
       <c r="AE4">
-        <v>11.18</v>
+        <v>11.19</v>
       </c>
       <c r="AF4">
-        <v>-8.08</v>
+        <v>70.03</v>
       </c>
       <c r="AG4">
-        <v>395.91</v>
+        <v>394.59</v>
       </c>
       <c r="AH4">
-        <v>342.53</v>
+        <v>340.93</v>
       </c>
       <c r="AI4">
         <v>378.22</v>
@@ -1283,7 +1280,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>31.39</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1294,10 +1291,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>363.7</v>
+        <v>366.4</v>
       </c>
       <c r="D5">
-        <v>5.68</v>
+        <v>0.74</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1306,46 +1303,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-13.75</v>
+        <v>-13.11</v>
       </c>
       <c r="H5">
-        <v>23.6</v>
+        <v>24.52</v>
       </c>
       <c r="I5">
-        <v>-1.73</v>
+        <v>1.88</v>
       </c>
       <c r="J5">
-        <v>-5.32</v>
+        <v>-1.95</v>
       </c>
       <c r="K5">
-        <v>3.87</v>
+        <v>3.99</v>
       </c>
       <c r="L5">
-        <v>-0.45</v>
+        <v>0.65</v>
       </c>
       <c r="M5">
-        <v>6.02</v>
+        <v>6.58</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>353.29</v>
+        <v>354.64</v>
       </c>
       <c r="Q5">
-        <v>364.5</v>
+        <v>363.96</v>
       </c>
       <c r="R5">
-        <v>374.44</v>
+        <v>374.41</v>
       </c>
       <c r="S5">
-        <v>361.7</v>
+        <v>361.42</v>
       </c>
       <c r="T5">
-        <v>0.55</v>
+        <v>1.38</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1360,34 +1357,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>48.62</v>
+        <v>50.56</v>
       </c>
       <c r="Z5">
-        <v>-6</v>
+        <v>-4.99</v>
       </c>
       <c r="AA5">
         <v>-5.01</v>
       </c>
       <c r="AB5">
-        <v>-0.99</v>
+        <v>0.02</v>
       </c>
       <c r="AC5">
-        <v>34.02</v>
+        <v>66.19</v>
       </c>
       <c r="AD5">
-        <v>23.26</v>
+        <v>36.65</v>
       </c>
       <c r="AE5">
-        <v>12.15</v>
+        <v>12.29</v>
       </c>
       <c r="AF5">
-        <v>52.47</v>
+        <v>32.24</v>
       </c>
       <c r="AG5">
-        <v>384.46</v>
+        <v>383.03</v>
       </c>
       <c r="AH5">
-        <v>344.55</v>
+        <v>344.9</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1396,7 +1393,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>41.6</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1407,10 +1404,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>389.55</v>
+        <v>392.75</v>
       </c>
       <c r="D6">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1419,46 +1416,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-12.01</v>
+        <v>-11.28</v>
       </c>
       <c r="H6">
-        <v>39.35</v>
+        <v>40.49</v>
       </c>
       <c r="I6">
-        <v>-3.04</v>
+        <v>-1.84</v>
       </c>
       <c r="J6">
-        <v>-3.71</v>
+        <v>-3.32</v>
       </c>
       <c r="K6">
-        <v>9.869999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="L6">
-        <v>16.32</v>
+        <v>11.93</v>
       </c>
       <c r="M6">
-        <v>-11.39</v>
+        <v>-10.94</v>
       </c>
       <c r="N6">
         <v>77</v>
       </c>
       <c r="O6">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P6">
-        <v>392.18</v>
+        <v>390.71</v>
       </c>
       <c r="Q6">
-        <v>397.29</v>
+        <v>396.6</v>
       </c>
       <c r="R6">
-        <v>400.63</v>
+        <v>400.7</v>
       </c>
       <c r="S6">
-        <v>370.84</v>
+        <v>371.18</v>
       </c>
       <c r="T6">
-        <v>5.04</v>
+        <v>5.81</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1473,34 +1470,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.41</v>
+        <v>45.66</v>
       </c>
       <c r="Z6">
-        <v>-2.28</v>
+        <v>-2.32</v>
       </c>
       <c r="AA6">
-        <v>-0.91</v>
+        <v>-1.19</v>
       </c>
       <c r="AB6">
-        <v>-1.38</v>
+        <v>-1.13</v>
       </c>
       <c r="AC6">
-        <v>14.37</v>
+        <v>23.95</v>
       </c>
       <c r="AD6">
-        <v>25.33</v>
+        <v>20.23</v>
       </c>
       <c r="AE6">
-        <v>11.01</v>
+        <v>10.74</v>
       </c>
       <c r="AF6">
-        <v>-70.42</v>
+        <v>-10.18</v>
       </c>
       <c r="AG6">
-        <v>411.05</v>
+        <v>409.76</v>
       </c>
       <c r="AH6">
-        <v>383.53</v>
+        <v>383.43</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1509,7 +1506,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.8</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1520,10 +1517,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>720.2</v>
+        <v>717.55</v>
       </c>
       <c r="D7">
-        <v>3.93</v>
+        <v>-0.37</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1532,46 +1529,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-1.19</v>
+        <v>-1.56</v>
       </c>
       <c r="H7">
-        <v>42.21</v>
+        <v>41.68</v>
       </c>
       <c r="I7">
-        <v>6.51</v>
+        <v>-0.19</v>
       </c>
       <c r="J7">
-        <v>15.99</v>
+        <v>16.88</v>
       </c>
       <c r="K7">
-        <v>13.83</v>
+        <v>13.78</v>
       </c>
       <c r="L7">
-        <v>14.89</v>
+        <v>12.41</v>
       </c>
       <c r="M7">
-        <v>36.49</v>
+        <v>36.83</v>
       </c>
       <c r="N7">
         <v>88</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P7">
-        <v>712.42</v>
+        <v>712.14</v>
       </c>
       <c r="Q7">
-        <v>669.1900000000001</v>
+        <v>674.53</v>
       </c>
       <c r="R7">
-        <v>621.16</v>
+        <v>623.6900000000001</v>
       </c>
       <c r="S7">
-        <v>592.25</v>
+        <v>592.89</v>
       </c>
       <c r="T7">
-        <v>21.6</v>
+        <v>21.03</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1586,34 +1583,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>66.75</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="Z7">
-        <v>26.25</v>
+        <v>26.49</v>
       </c>
       <c r="AA7">
-        <v>23.24</v>
+        <v>23.89</v>
       </c>
       <c r="AB7">
-        <v>3.01</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>15.1</v>
+        <v>22.91</v>
       </c>
       <c r="AD7">
-        <v>39.45</v>
+        <v>24.62</v>
       </c>
       <c r="AE7">
-        <v>26.48</v>
+        <v>25.57</v>
       </c>
       <c r="AF7">
-        <v>-7.98</v>
+        <v>-63.66</v>
       </c>
       <c r="AG7">
-        <v>735.05</v>
+        <v>737.6799999999999</v>
       </c>
       <c r="AH7">
-        <v>603.3200000000001</v>
+        <v>611.38</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1622,7 +1619,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>63</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1633,10 +1630,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>195.17</v>
+        <v>199.29</v>
       </c>
       <c r="D8">
-        <v>0.86</v>
+        <v>2.11</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1645,25 +1642,25 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-46.09</v>
+        <v>-44.96</v>
       </c>
       <c r="H8">
-        <v>1.44</v>
+        <v>3.58</v>
       </c>
       <c r="I8">
-        <v>-2.1</v>
+        <v>1.38</v>
       </c>
       <c r="J8">
-        <v>-11.84</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K8">
-        <v>-16.21</v>
+        <v>-15.2</v>
       </c>
       <c r="L8">
-        <v>-45.36</v>
+        <v>-44.72</v>
       </c>
       <c r="M8">
-        <v>-3.67</v>
+        <v>-3.51</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1672,19 +1669,19 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>194.88</v>
+        <v>195.42</v>
       </c>
       <c r="Q8">
-        <v>207.43</v>
+        <v>206.34</v>
       </c>
       <c r="R8">
-        <v>217.71</v>
+        <v>217.06</v>
       </c>
       <c r="S8">
-        <v>255.23</v>
+        <v>254.63</v>
       </c>
       <c r="T8">
-        <v>-23.53</v>
+        <v>-21.73</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1699,34 +1696,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>26.54</v>
+        <v>35.78</v>
       </c>
       <c r="Z8">
-        <v>-7.36</v>
+        <v>-6.94</v>
       </c>
       <c r="AA8">
-        <v>-6.18</v>
+        <v>-6.33</v>
       </c>
       <c r="AB8">
-        <v>-1.18</v>
+        <v>-0.6</v>
       </c>
       <c r="AC8">
-        <v>22.96</v>
+        <v>56.29</v>
       </c>
       <c r="AD8">
-        <v>10.31</v>
+        <v>28.85</v>
       </c>
       <c r="AE8">
         <v>6.24</v>
       </c>
       <c r="AF8">
-        <v>6.11</v>
+        <v>25.13</v>
       </c>
       <c r="AG8">
-        <v>226.57</v>
+        <v>224.68</v>
       </c>
       <c r="AH8">
-        <v>188.29</v>
+        <v>188.01</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1735,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>60.3</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1746,10 +1743,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3552.9</v>
+        <v>3625.1</v>
       </c>
       <c r="D9">
-        <v>0.8</v>
+        <v>2.03</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1758,46 +1755,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21</v>
+        <v>-19.4</v>
       </c>
       <c r="H9">
-        <v>7.37</v>
+        <v>9.56</v>
       </c>
       <c r="I9">
-        <v>-1.15</v>
+        <v>2.09</v>
       </c>
       <c r="J9">
-        <v>-1.14</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>-8.25</v>
+        <v>-7.7</v>
       </c>
       <c r="L9">
-        <v>-17.55</v>
+        <v>-18.83</v>
       </c>
       <c r="M9">
-        <v>20.33</v>
+        <v>21.06</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>3554.78</v>
+        <v>3569.6</v>
       </c>
       <c r="Q9">
-        <v>3566.72</v>
+        <v>3567.84</v>
       </c>
       <c r="R9">
-        <v>3610.14</v>
+        <v>3607.99</v>
       </c>
       <c r="S9">
-        <v>3681.84</v>
+        <v>3680.45</v>
       </c>
       <c r="T9">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1812,34 +1809,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.92</v>
+        <v>55.24</v>
       </c>
       <c r="Z9">
-        <v>-16.12</v>
+        <v>-10.29</v>
       </c>
       <c r="AA9">
-        <v>-17.49</v>
+        <v>-16.05</v>
       </c>
       <c r="AB9">
-        <v>1.38</v>
+        <v>5.76</v>
       </c>
       <c r="AC9">
-        <v>37.02</v>
+        <v>48.71</v>
       </c>
       <c r="AD9">
-        <v>40.15</v>
+        <v>41.87</v>
       </c>
       <c r="AE9">
-        <v>61.71</v>
+        <v>63.94</v>
       </c>
       <c r="AF9">
-        <v>-21.52</v>
+        <v>-10.92</v>
       </c>
       <c r="AG9">
-        <v>3629.04</v>
+        <v>3633.61</v>
       </c>
       <c r="AH9">
-        <v>3504.39</v>
+        <v>3502.07</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1848,7 +1845,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.42</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1859,10 +1856,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1561</v>
+        <v>1537.1</v>
       </c>
       <c r="D10">
-        <v>0.19</v>
+        <v>-1.53</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1871,46 +1868,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.73</v>
+        <v>-13.08</v>
       </c>
       <c r="H10">
-        <v>17.7</v>
+        <v>15.9</v>
       </c>
       <c r="I10">
-        <v>3.51</v>
+        <v>0.74</v>
       </c>
       <c r="J10">
-        <v>-1.95</v>
+        <v>-3.31</v>
       </c>
       <c r="K10">
-        <v>7.83</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L10">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="M10">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P10">
-        <v>1552.34</v>
+        <v>1554.6</v>
       </c>
       <c r="Q10">
-        <v>1581.68</v>
+        <v>1578.93</v>
       </c>
       <c r="R10">
-        <v>1585.5</v>
+        <v>1587.71</v>
       </c>
       <c r="S10">
-        <v>1518.78</v>
+        <v>1518.82</v>
       </c>
       <c r="T10">
-        <v>2.78</v>
+        <v>1.2</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1925,34 +1922,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>46.46</v>
+        <v>42.17</v>
       </c>
       <c r="Z10">
-        <v>-10.91</v>
+        <v>-12.47</v>
       </c>
       <c r="AA10">
-        <v>-5.92</v>
+        <v>-7.23</v>
       </c>
       <c r="AB10">
-        <v>-5</v>
+        <v>-5.24</v>
       </c>
       <c r="AC10">
-        <v>50.16</v>
+        <v>42.48</v>
       </c>
       <c r="AD10">
-        <v>43.02</v>
+        <v>45.63</v>
       </c>
       <c r="AE10">
-        <v>42.1</v>
+        <v>41.82</v>
       </c>
       <c r="AF10">
-        <v>45.56</v>
+        <v>62.63</v>
       </c>
       <c r="AG10">
-        <v>1652.25</v>
+        <v>1652.03</v>
       </c>
       <c r="AH10">
-        <v>1511.1</v>
+        <v>1505.82</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1961,7 +1958,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>25.78</v>
+        <v>23.64</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2142,7 +2139,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2162,7 +2159,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>62</v>
@@ -2171,1349 +2168,1289 @@
         <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.86</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-4.8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-10.63</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-9.32</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-5.32</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-1.95</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-3.32</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>15.99</v>
+      </c>
+      <c r="D14" s="6">
+        <v>16.88</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-11.84</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1.01</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.95</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.31</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.96</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.73</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.04</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.84</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>6.51</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.19</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-6.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.38</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.09</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3.51</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.74</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-3.48</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-3.02</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-14.3</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-13.55</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>27.4</v>
+      </c>
+      <c r="D29" s="6">
+        <v>30.8</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>16.32</v>
+      </c>
+      <c r="D31" s="6">
+        <v>11.93</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-4.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>14.89</v>
+      </c>
+      <c r="D32" s="6">
+        <v>12.41</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-45.36</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-44.72</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-17.55</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-18.83</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="D35" s="6">
+        <v>2.2</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-7.84</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-5.86</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-15.47</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-16.56</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-10.08</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-1.91</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.74</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>16.77</v>
+      </c>
+      <c r="D38" s="6">
+        <v>20.13</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>3.87</v>
+      </c>
+      <c r="D39" s="6">
+        <v>3.99</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="D40" s="6">
+        <v>10.65</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>13.83</v>
+      </c>
+      <c r="D41" s="6">
+        <v>13.78</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-16.21</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-15.2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-8.25</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-7.7</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>7.83</v>
+      </c>
+      <c r="D44" s="6">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-21.32</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-21.02</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-19.09</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-19.73</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-16.15</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-14.31</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-13.75</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-13.11</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="D49" s="6">
         <v>-11.28</v>
       </c>
-      <c r="D14" s="7">
-        <v>-10.49</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="E49" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-46.09</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-44.96</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-21</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-19.4</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-11.73</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-13.08</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>385.7</v>
+      </c>
+      <c r="D54" s="6">
+        <v>387.15</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>3076.5</v>
+      </c>
+      <c r="D55" s="6">
+        <v>3052</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-24.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>345.7</v>
+      </c>
+      <c r="D56" s="6">
+        <v>353.3</v>
+      </c>
+      <c r="E56" s="7">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-10.99</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-5.32</v>
-      </c>
-      <c r="E15" s="8">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>363.7</v>
+      </c>
+      <c r="D57" s="6">
+        <v>366.4</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-4.61</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>389.55</v>
+      </c>
+      <c r="D58" s="6">
+        <v>392.75</v>
+      </c>
+      <c r="E58" s="7">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>11.41</v>
-      </c>
-      <c r="D17" s="7">
-        <v>15.99</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>720.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>717.55</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-14.61</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-11.84</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>195.17</v>
+      </c>
+      <c r="D60" s="6">
+        <v>199.29</v>
+      </c>
+      <c r="E60" s="7">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-3.12</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>3552.9</v>
+      </c>
+      <c r="D61" s="6">
+        <v>3625.1</v>
+      </c>
+      <c r="E61" s="7">
+        <v>72.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-3.23</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-1.95</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1561</v>
+      </c>
+      <c r="D62" s="6">
+        <v>1537.1</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-23.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="D21" s="7">
-        <v>1.06</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>39.9</v>
+      </c>
+      <c r="D63" s="6">
+        <v>41.99</v>
+      </c>
+      <c r="E63" s="7">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-2.85</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-2.33</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>32.35</v>
+      </c>
+      <c r="D64" s="6">
+        <v>30.49</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-7.83</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.96</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>34.28</v>
+      </c>
+      <c r="D65" s="6">
+        <v>40.9</v>
+      </c>
+      <c r="E65" s="7">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-6.01</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="E24" s="8">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>48.62</v>
+      </c>
+      <c r="D66" s="6">
+        <v>50.56</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-5.39</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.04</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>42.41</v>
+      </c>
+      <c r="D67" s="6">
+        <v>45.66</v>
+      </c>
+      <c r="E67" s="7">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>1.81</v>
-      </c>
-      <c r="D26" s="7">
-        <v>6.51</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>66.75</v>
+      </c>
+      <c r="D68" s="6">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-5.93</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-2.1</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>26.54</v>
+      </c>
+      <c r="D69" s="6">
+        <v>35.78</v>
+      </c>
+      <c r="E69" s="7">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-2.97</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-1.15</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>44.92</v>
+      </c>
+      <c r="D70" s="6">
+        <v>55.24</v>
+      </c>
+      <c r="E70" s="7">
+        <v>10.32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-0.06</v>
-      </c>
-      <c r="D29" s="7">
-        <v>3.51</v>
-      </c>
-      <c r="E29" s="8">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>46.46</v>
+      </c>
+      <c r="D71" s="6">
+        <v>42.17</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-4.95</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>15.93</v>
+      </c>
+      <c r="D72" s="6">
+        <v>54.85</v>
+      </c>
+      <c r="E72" s="7">
+        <v>38.92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-14.62</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-14.3</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>6.81</v>
+      </c>
+      <c r="D73" s="6">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="E73" s="7">
+        <v>60.48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>27.09</v>
-      </c>
-      <c r="D32" s="7">
-        <v>27.4</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-8.08</v>
+      </c>
+      <c r="D74" s="6">
+        <v>70.03</v>
+      </c>
+      <c r="E74" s="7">
+        <v>78.11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-5.56</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="E33" s="8">
-        <v>5.11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>52.47</v>
+      </c>
+      <c r="D75" s="6">
+        <v>32.24</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-20.23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>17.46</v>
-      </c>
-      <c r="D34" s="7">
-        <v>16.32</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-70.42</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-10.18</v>
+      </c>
+      <c r="E76" s="7">
+        <v>60.24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>9.07</v>
-      </c>
-      <c r="D35" s="7">
-        <v>14.89</v>
-      </c>
-      <c r="E35" s="8">
-        <v>5.82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-7.98</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-63.66</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-55.68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-45.98</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-45.36</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>6.11</v>
+      </c>
+      <c r="D78" s="6">
+        <v>25.13</v>
+      </c>
+      <c r="E78" s="7">
+        <v>19.02</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-18</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-17.55</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-21.52</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-10.92</v>
+      </c>
+      <c r="E79" s="7">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="7">
-        <v>3.49</v>
-      </c>
-      <c r="D38" s="7">
-        <v>3.4</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-17.8</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-15.47</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-2.01</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-1.91</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>15.98</v>
-      </c>
-      <c r="D41" s="7">
-        <v>16.77</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-0.65</v>
-      </c>
-      <c r="D42" s="7">
-        <v>3.87</v>
-      </c>
-      <c r="E42" s="8">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>12.12</v>
-      </c>
-      <c r="D43" s="7">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>12.69</v>
-      </c>
-      <c r="D44" s="7">
-        <v>13.83</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-16.28</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-16.21</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-8.25</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="7">
-        <v>6.54</v>
-      </c>
-      <c r="D47" s="7">
-        <v>7.83</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-23.34</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-21.32</v>
-      </c>
-      <c r="E48" s="8">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-19.26</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-19.09</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-16.31</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-16.15</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-18.39</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-13.75</v>
-      </c>
-      <c r="E51" s="8">
-        <v>4.64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-12.63</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-12.01</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-4.93</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-1.19</v>
-      </c>
-      <c r="E53" s="8">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-46.55</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-46.09</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-21.63</v>
-      </c>
-      <c r="D55" s="7">
-        <v>-21</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="7">
-        <v>-11.9</v>
-      </c>
-      <c r="D56" s="7">
-        <v>-11.73</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>375.8</v>
-      </c>
-      <c r="D57" s="7">
-        <v>385.7</v>
-      </c>
-      <c r="E57" s="8">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>3070</v>
-      </c>
-      <c r="D58" s="7">
-        <v>3076.5</v>
-      </c>
-      <c r="E58" s="8">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>345.05</v>
-      </c>
-      <c r="D59" s="7">
-        <v>345.7</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>344.15</v>
-      </c>
-      <c r="D60" s="7">
-        <v>363.7</v>
-      </c>
-      <c r="E60" s="8">
-        <v>19.55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>386.8</v>
-      </c>
-      <c r="D61" s="7">
-        <v>389.55</v>
-      </c>
-      <c r="E61" s="8">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>692.95</v>
-      </c>
-      <c r="D62" s="7">
-        <v>720.2</v>
-      </c>
-      <c r="E62" s="8">
-        <v>27.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>193.51</v>
-      </c>
-      <c r="D63" s="7">
-        <v>195.17</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="7">
-        <v>3524.8</v>
-      </c>
-      <c r="D64" s="7">
-        <v>3552.9</v>
-      </c>
-      <c r="E64" s="8">
-        <v>28.1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" s="7">
-        <v>1558</v>
-      </c>
-      <c r="D65" s="7">
-        <v>1561</v>
-      </c>
-      <c r="E65" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>22.15</v>
-      </c>
-      <c r="D66" s="7">
-        <v>39.9</v>
-      </c>
-      <c r="E66" s="8">
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>31.32</v>
-      </c>
-      <c r="D67" s="7">
-        <v>32.35</v>
-      </c>
-      <c r="E67" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>33.69</v>
-      </c>
-      <c r="D68" s="7">
-        <v>34.28</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>30.16</v>
-      </c>
-      <c r="D69" s="7">
-        <v>48.62</v>
-      </c>
-      <c r="E69" s="8">
-        <v>18.46</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>39.52</v>
-      </c>
-      <c r="D70" s="7">
-        <v>42.41</v>
-      </c>
-      <c r="E70" s="8">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>61.02</v>
-      </c>
-      <c r="D71" s="7">
-        <v>66.75</v>
-      </c>
-      <c r="E71" s="8">
-        <v>5.73</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>22.36</v>
-      </c>
-      <c r="D72" s="7">
-        <v>26.54</v>
-      </c>
-      <c r="E72" s="8">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>39.91</v>
-      </c>
-      <c r="D73" s="7">
-        <v>44.92</v>
-      </c>
-      <c r="E73" s="8">
-        <v>5.01</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>45.81</v>
-      </c>
-      <c r="D74" s="7">
-        <v>46.46</v>
-      </c>
-      <c r="E74" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="7">
-        <v>14.48</v>
-      </c>
-      <c r="D75" s="7">
-        <v>15.93</v>
-      </c>
-      <c r="E75" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>38.95</v>
-      </c>
-      <c r="D76" s="7">
-        <v>6.81</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-32.14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-39.61</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-8.08</v>
-      </c>
-      <c r="E77" s="8">
-        <v>31.53</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-26.34</v>
-      </c>
-      <c r="D78" s="7">
-        <v>52.47</v>
-      </c>
-      <c r="E78" s="8">
-        <v>78.81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>3.91</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-70.42</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-74.33</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-53.73</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-7.98</v>
-      </c>
-      <c r="E80" s="8">
-        <v>45.75</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-19.53</v>
-      </c>
-      <c r="D81" s="7">
-        <v>6.11</v>
-      </c>
-      <c r="E81" s="8">
-        <v>25.64</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>38.25</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-21.52</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-59.77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-21.56</v>
-      </c>
-      <c r="D83" s="7">
+      <c r="C80" s="6">
         <v>45.56</v>
       </c>
-      <c r="E83" s="8">
-        <v>67.12</v>
+      <c r="D80" s="6">
+        <v>62.63</v>
+      </c>
+      <c r="E80" s="7">
+        <v>17.07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3533,60 +3470,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>42.5</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3688,61 +3625,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3649</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3343</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2033</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1587</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.116</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0602</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0453</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0367</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1139</v>
+      <c r="A2" s="14">
+        <v>0.3683</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3384</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2106</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1681</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1249</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0658</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.045</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0351</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1094</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="90">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,37 +196,61 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.6 → 50.6</t>
+    <t>42.0 → 51.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.6</t>
+    <t>42.0</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>45.7 → 51.7</t>
+  </si>
+  <si>
+    <t>45.7</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.6% → -3.0%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.6%</t>
+  </si>
+  <si>
+    <t>-3.0%</t>
+  </si>
+  <si>
+    <t>50.6 → 47.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.6</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.5 → 35.8</t>
-  </si>
-  <si>
-    <t>26.5</t>
-  </si>
-  <si>
-    <t>35.8</t>
-  </si>
-  <si>
-    <t>44.9 → 55.2</t>
-  </si>
-  <si>
-    <t>44.9</t>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>55.2 → 48.1</t>
   </si>
   <si>
     <t>55.2</t>
+  </si>
+  <si>
+    <t>48.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -278,7 +302,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,13 +343,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,6 +384,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -436,14 +473,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -452,7 +491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -811,8 +850,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -952,10 +990,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>387.15</v>
+        <v>395.15</v>
       </c>
       <c r="D2">
-        <v>0.38</v>
+        <v>2.07</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -964,46 +1002,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-21.02</v>
+        <v>-19.39</v>
       </c>
       <c r="H2">
-        <v>3.24</v>
+        <v>5.37</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>4.08</v>
       </c>
       <c r="J2">
-        <v>-4.8</v>
+        <v>-2.14</v>
       </c>
       <c r="K2">
-        <v>-16.56</v>
+        <v>-16.57</v>
       </c>
       <c r="L2">
-        <v>-3.02</v>
+        <v>-1.5</v>
       </c>
       <c r="M2">
-        <v>12.49</v>
+        <v>13.3</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P2">
-        <v>380.66</v>
+        <v>383.76</v>
       </c>
       <c r="Q2">
-        <v>387.38</v>
+        <v>387.09</v>
       </c>
       <c r="R2">
-        <v>412.01</v>
+        <v>410.63</v>
       </c>
       <c r="S2">
-        <v>434.87</v>
+        <v>434.77</v>
       </c>
       <c r="T2">
-        <v>-10.97</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1018,34 +1056,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.99</v>
+        <v>51.91</v>
       </c>
       <c r="Z2">
-        <v>-8.44</v>
+        <v>-6.95</v>
       </c>
       <c r="AA2">
-        <v>-9.94</v>
+        <v>-9.34</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="AC2">
-        <v>73.19</v>
+        <v>100</v>
       </c>
       <c r="AD2">
-        <v>39.86</v>
+        <v>71.02</v>
       </c>
       <c r="AE2">
-        <v>8.859999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="AF2">
-        <v>54.85</v>
+        <v>54.67</v>
       </c>
       <c r="AG2">
-        <v>402.22</v>
+        <v>400.98</v>
       </c>
       <c r="AH2">
-        <v>372.55</v>
+        <v>373.2</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1054,7 +1092,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>50.21</v>
+        <v>46.09</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1065,10 +1103,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3052</v>
+        <v>3055.3</v>
       </c>
       <c r="D3">
-        <v>-0.8</v>
+        <v>0.11</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1077,46 +1115,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-19.73</v>
+        <v>-19.65</v>
       </c>
       <c r="H3">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="I3">
-        <v>-2.3</v>
+        <v>-1.66</v>
       </c>
       <c r="J3">
-        <v>-10.63</v>
+        <v>-10.79</v>
       </c>
       <c r="K3">
-        <v>-0.74</v>
+        <v>-0.26</v>
       </c>
       <c r="L3">
-        <v>-13.55</v>
+        <v>-15.32</v>
       </c>
       <c r="M3">
-        <v>33.84</v>
+        <v>33.81</v>
       </c>
       <c r="N3">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>3067</v>
+        <v>3056.66</v>
       </c>
       <c r="Q3">
-        <v>3215.57</v>
+        <v>3197.72</v>
       </c>
       <c r="R3">
-        <v>3270.71</v>
+        <v>3269.23</v>
       </c>
       <c r="S3">
-        <v>3306.29</v>
+        <v>3302.98</v>
       </c>
       <c r="T3">
-        <v>-7.69</v>
+        <v>-7.5</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1131,43 +1169,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>30.49</v>
+        <v>31.06</v>
       </c>
       <c r="Z3">
-        <v>-73.18000000000001</v>
+        <v>-73.75</v>
       </c>
       <c r="AA3">
-        <v>-54.27</v>
+        <v>-58.17</v>
       </c>
       <c r="AB3">
-        <v>-18.9</v>
+        <v>-15.58</v>
       </c>
       <c r="AC3">
-        <v>32.36</v>
+        <v>36.31</v>
       </c>
       <c r="AD3">
-        <v>21.15</v>
+        <v>29.97</v>
       </c>
       <c r="AE3">
-        <v>66.37</v>
+        <v>64.2</v>
       </c>
       <c r="AF3">
-        <v>67.29000000000001</v>
+        <v>-42.56</v>
       </c>
       <c r="AG3">
-        <v>3481.61</v>
+        <v>3455.99</v>
       </c>
       <c r="AH3">
-        <v>2949.52</v>
+        <v>2939.45</v>
       </c>
       <c r="AI3">
-        <v>3273.14</v>
+        <v>3264.24</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>69.3</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1178,10 +1216,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>353.3</v>
+        <v>354.7</v>
       </c>
       <c r="D4">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1190,25 +1228,25 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-14.31</v>
+        <v>-13.97</v>
       </c>
       <c r="H4">
-        <v>29.44</v>
+        <v>29.95</v>
       </c>
       <c r="I4">
-        <v>-1.66</v>
+        <v>-0.41</v>
       </c>
       <c r="J4">
-        <v>-9.32</v>
+        <v>-7.26</v>
       </c>
       <c r="K4">
-        <v>20.13</v>
+        <v>20.67</v>
       </c>
       <c r="L4">
-        <v>30.8</v>
+        <v>27.34</v>
       </c>
       <c r="M4">
-        <v>16.81</v>
+        <v>16.28</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1217,19 +1255,19 @@
         <v>81</v>
       </c>
       <c r="P4">
-        <v>348.5</v>
+        <v>348.21</v>
       </c>
       <c r="Q4">
-        <v>367.76</v>
+        <v>366.42</v>
       </c>
       <c r="R4">
-        <v>371.02</v>
+        <v>371.3</v>
       </c>
       <c r="S4">
-        <v>344.28</v>
+        <v>344.23</v>
       </c>
       <c r="T4">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1244,34 +1282,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>40.9</v>
+        <v>42.06</v>
       </c>
       <c r="Z4">
-        <v>-7.29</v>
+        <v>-7.06</v>
       </c>
       <c r="AA4">
-        <v>-4</v>
+        <v>-4.61</v>
       </c>
       <c r="AB4">
-        <v>-3.29</v>
+        <v>-2.45</v>
       </c>
       <c r="AC4">
-        <v>26.59</v>
+        <v>42.45</v>
       </c>
       <c r="AD4">
-        <v>13.14</v>
+        <v>26.06</v>
       </c>
       <c r="AE4">
-        <v>11.19</v>
+        <v>10.92</v>
       </c>
       <c r="AF4">
-        <v>70.03</v>
+        <v>-43.75</v>
       </c>
       <c r="AG4">
-        <v>394.59</v>
+        <v>393.02</v>
       </c>
       <c r="AH4">
-        <v>340.93</v>
+        <v>339.81</v>
       </c>
       <c r="AI4">
         <v>378.22</v>
@@ -1280,7 +1318,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>29.48</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1291,10 +1329,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>366.4</v>
+        <v>362.65</v>
       </c>
       <c r="D5">
-        <v>0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1303,46 +1341,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-13.11</v>
+        <v>-14</v>
       </c>
       <c r="H5">
-        <v>24.52</v>
+        <v>23.25</v>
       </c>
       <c r="I5">
-        <v>1.88</v>
+        <v>2.72</v>
       </c>
       <c r="J5">
-        <v>-1.95</v>
+        <v>-3.86</v>
       </c>
       <c r="K5">
-        <v>3.99</v>
+        <v>0.72</v>
       </c>
       <c r="L5">
-        <v>0.65</v>
+        <v>-1.83</v>
       </c>
       <c r="M5">
-        <v>6.58</v>
+        <v>6.48</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>354.64</v>
+        <v>356.56</v>
       </c>
       <c r="Q5">
-        <v>363.96</v>
+        <v>363.11</v>
       </c>
       <c r="R5">
-        <v>374.41</v>
+        <v>374.08</v>
       </c>
       <c r="S5">
-        <v>361.42</v>
+        <v>361.14</v>
       </c>
       <c r="T5">
-        <v>1.38</v>
+        <v>0.42</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1357,34 +1395,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>50.56</v>
+        <v>47.86</v>
       </c>
       <c r="Z5">
-        <v>-4.99</v>
+        <v>-4.45</v>
       </c>
       <c r="AA5">
-        <v>-5.01</v>
+        <v>-4.9</v>
       </c>
       <c r="AB5">
-        <v>0.02</v>
+        <v>0.45</v>
       </c>
       <c r="AC5">
-        <v>66.19</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AD5">
-        <v>36.65</v>
+        <v>65.11</v>
       </c>
       <c r="AE5">
-        <v>12.29</v>
+        <v>12.16</v>
       </c>
       <c r="AF5">
-        <v>32.24</v>
+        <v>11.86</v>
       </c>
       <c r="AG5">
-        <v>383.03</v>
+        <v>380.66</v>
       </c>
       <c r="AH5">
-        <v>344.9</v>
+        <v>345.55</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1393,7 +1431,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>36.12</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1404,10 +1442,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>392.75</v>
+        <v>399.3</v>
       </c>
       <c r="D6">
-        <v>0.82</v>
+        <v>1.67</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1416,46 +1454,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-11.28</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="H6">
-        <v>40.49</v>
+        <v>42.84</v>
       </c>
       <c r="I6">
-        <v>-1.84</v>
+        <v>0.53</v>
       </c>
       <c r="J6">
-        <v>-3.32</v>
+        <v>-1.81</v>
       </c>
       <c r="K6">
-        <v>10.65</v>
+        <v>8.02</v>
       </c>
       <c r="L6">
-        <v>11.93</v>
+        <v>13.68</v>
       </c>
       <c r="M6">
-        <v>-10.94</v>
+        <v>-10.78</v>
       </c>
       <c r="N6">
         <v>77</v>
       </c>
       <c r="O6">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P6">
-        <v>390.71</v>
+        <v>391.13</v>
       </c>
       <c r="Q6">
-        <v>396.6</v>
+        <v>396.5</v>
       </c>
       <c r="R6">
-        <v>400.7</v>
+        <v>400.94</v>
       </c>
       <c r="S6">
-        <v>371.18</v>
+        <v>371.58</v>
       </c>
       <c r="T6">
-        <v>5.81</v>
+        <v>7.46</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1470,34 +1508,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.66</v>
+        <v>51.68</v>
       </c>
       <c r="Z6">
-        <v>-2.32</v>
+        <v>-1.81</v>
       </c>
       <c r="AA6">
-        <v>-1.19</v>
+        <v>-1.31</v>
       </c>
       <c r="AB6">
-        <v>-1.13</v>
+        <v>-0.49</v>
       </c>
       <c r="AC6">
-        <v>23.95</v>
+        <v>43.91</v>
       </c>
       <c r="AD6">
-        <v>20.23</v>
+        <v>27.41</v>
       </c>
       <c r="AE6">
-        <v>10.74</v>
+        <v>11.05</v>
       </c>
       <c r="AF6">
-        <v>-10.18</v>
+        <v>-27.48</v>
       </c>
       <c r="AG6">
-        <v>409.76</v>
+        <v>409.56</v>
       </c>
       <c r="AH6">
-        <v>383.43</v>
+        <v>383.45</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1506,7 +1544,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.37</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1517,10 +1555,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>717.55</v>
+        <v>706.95</v>
       </c>
       <c r="D7">
-        <v>-0.37</v>
+        <v>-1.48</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1529,46 +1567,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-1.56</v>
+        <v>-3.01</v>
       </c>
       <c r="H7">
-        <v>41.68</v>
+        <v>39.59</v>
       </c>
       <c r="I7">
-        <v>-0.19</v>
+        <v>-3.01</v>
       </c>
       <c r="J7">
-        <v>16.88</v>
+        <v>15.78</v>
       </c>
       <c r="K7">
-        <v>13.78</v>
+        <v>10.01</v>
       </c>
       <c r="L7">
-        <v>12.41</v>
+        <v>12.33</v>
       </c>
       <c r="M7">
-        <v>36.83</v>
+        <v>36.64</v>
       </c>
       <c r="N7">
         <v>88</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P7">
-        <v>712.14</v>
+        <v>707.75</v>
       </c>
       <c r="Q7">
-        <v>674.53</v>
+        <v>678.17</v>
       </c>
       <c r="R7">
-        <v>623.6900000000001</v>
+        <v>625.86</v>
       </c>
       <c r="S7">
-        <v>592.89</v>
+        <v>593.5599999999999</v>
       </c>
       <c r="T7">
-        <v>21.03</v>
+        <v>19.1</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1583,34 +1621,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>65.73999999999999</v>
+        <v>61.71</v>
       </c>
       <c r="Z7">
-        <v>26.49</v>
+        <v>25.53</v>
       </c>
       <c r="AA7">
-        <v>23.89</v>
+        <v>24.21</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>1.31</v>
       </c>
       <c r="AC7">
-        <v>22.91</v>
+        <v>24.42</v>
       </c>
       <c r="AD7">
-        <v>24.62</v>
+        <v>20.81</v>
       </c>
       <c r="AE7">
-        <v>25.57</v>
+        <v>26.37</v>
       </c>
       <c r="AF7">
-        <v>-63.66</v>
+        <v>-46.65</v>
       </c>
       <c r="AG7">
-        <v>737.6799999999999</v>
+        <v>739.9</v>
       </c>
       <c r="AH7">
-        <v>611.38</v>
+        <v>616.45</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1619,7 +1657,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>60.25</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1630,10 +1668,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>199.29</v>
+        <v>201.37</v>
       </c>
       <c r="D8">
-        <v>2.11</v>
+        <v>1.04</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1642,46 +1680,46 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.96</v>
+        <v>-44.38</v>
       </c>
       <c r="H8">
-        <v>3.58</v>
+        <v>4.66</v>
       </c>
       <c r="I8">
-        <v>1.38</v>
+        <v>2.36</v>
       </c>
       <c r="J8">
-        <v>-9.199999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="K8">
-        <v>-15.2</v>
+        <v>-17.04</v>
       </c>
       <c r="L8">
-        <v>-44.72</v>
+        <v>-43.44</v>
       </c>
       <c r="M8">
-        <v>-3.51</v>
+        <v>-3.19</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>195.42</v>
+        <v>196.35</v>
       </c>
       <c r="Q8">
-        <v>206.34</v>
+        <v>205.32</v>
       </c>
       <c r="R8">
-        <v>217.06</v>
+        <v>216.42</v>
       </c>
       <c r="S8">
-        <v>254.63</v>
+        <v>254.04</v>
       </c>
       <c r="T8">
-        <v>-21.73</v>
+        <v>-20.73</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1696,34 +1734,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>35.78</v>
+        <v>39.89</v>
       </c>
       <c r="Z8">
-        <v>-6.94</v>
+        <v>-6.36</v>
       </c>
       <c r="AA8">
-        <v>-6.33</v>
+        <v>-6.34</v>
       </c>
       <c r="AB8">
-        <v>-0.6</v>
+        <v>-0.02</v>
       </c>
       <c r="AC8">
-        <v>56.29</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="AD8">
-        <v>28.85</v>
+        <v>54.09</v>
       </c>
       <c r="AE8">
-        <v>6.24</v>
+        <v>6.27</v>
       </c>
       <c r="AF8">
-        <v>25.13</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AG8">
-        <v>224.68</v>
+        <v>222.26</v>
       </c>
       <c r="AH8">
-        <v>188.01</v>
+        <v>188.39</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1732,7 +1770,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>57.27</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1743,10 +1781,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3625.1</v>
+        <v>3572.4</v>
       </c>
       <c r="D9">
-        <v>2.03</v>
+        <v>-1.45</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1755,46 +1793,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.4</v>
+        <v>-20.57</v>
       </c>
       <c r="H9">
-        <v>9.56</v>
+        <v>7.96</v>
       </c>
       <c r="I9">
-        <v>2.09</v>
+        <v>-0.1</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>-0.84</v>
       </c>
       <c r="K9">
-        <v>-7.7</v>
+        <v>-9.9</v>
       </c>
       <c r="L9">
-        <v>-18.83</v>
+        <v>-18.89</v>
       </c>
       <c r="M9">
-        <v>21.06</v>
+        <v>20.99</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>3569.6</v>
+        <v>3568.88</v>
       </c>
       <c r="Q9">
-        <v>3567.84</v>
+        <v>3567.97</v>
       </c>
       <c r="R9">
-        <v>3607.99</v>
+        <v>3603.85</v>
       </c>
       <c r="S9">
-        <v>3680.45</v>
+        <v>3679.24</v>
       </c>
       <c r="T9">
-        <v>-1.5</v>
+        <v>-2.9</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1809,34 +1847,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>55.24</v>
+        <v>48.15</v>
       </c>
       <c r="Z9">
-        <v>-10.29</v>
+        <v>-9.81</v>
       </c>
       <c r="AA9">
-        <v>-16.05</v>
+        <v>-14.81</v>
       </c>
       <c r="AB9">
-        <v>5.76</v>
+        <v>4.99</v>
       </c>
       <c r="AC9">
-        <v>48.71</v>
+        <v>58.48</v>
       </c>
       <c r="AD9">
-        <v>41.87</v>
+        <v>48.07</v>
       </c>
       <c r="AE9">
-        <v>63.94</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AF9">
-        <v>-10.92</v>
+        <v>-39.82</v>
       </c>
       <c r="AG9">
-        <v>3633.61</v>
+        <v>3633.77</v>
       </c>
       <c r="AH9">
-        <v>3502.07</v>
+        <v>3502.17</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1845,7 +1883,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.92</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1856,10 +1894,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1537.1</v>
+        <v>1558.5</v>
       </c>
       <c r="D10">
-        <v>-1.53</v>
+        <v>1.39</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1868,46 +1906,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-13.08</v>
+        <v>-11.87</v>
       </c>
       <c r="H10">
-        <v>15.9</v>
+        <v>17.52</v>
       </c>
       <c r="I10">
-        <v>0.74</v>
+        <v>1.14</v>
       </c>
       <c r="J10">
-        <v>-3.31</v>
+        <v>-2.11</v>
       </c>
       <c r="K10">
-        <v>9.050000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="L10">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="M10">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P10">
-        <v>1554.6</v>
+        <v>1558.1</v>
       </c>
       <c r="Q10">
-        <v>1578.93</v>
+        <v>1577.65</v>
       </c>
       <c r="R10">
-        <v>1587.71</v>
+        <v>1589.79</v>
       </c>
       <c r="S10">
-        <v>1518.82</v>
+        <v>1518.92</v>
       </c>
       <c r="T10">
-        <v>1.2</v>
+        <v>2.61</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1922,34 +1960,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>42.17</v>
+        <v>46.89</v>
       </c>
       <c r="Z10">
-        <v>-12.47</v>
+        <v>-11.84</v>
       </c>
       <c r="AA10">
-        <v>-7.23</v>
+        <v>-8.15</v>
       </c>
       <c r="AB10">
-        <v>-5.24</v>
+        <v>-3.69</v>
       </c>
       <c r="AC10">
-        <v>42.48</v>
+        <v>44.72</v>
       </c>
       <c r="AD10">
-        <v>45.63</v>
+        <v>45.79</v>
       </c>
       <c r="AE10">
-        <v>41.82</v>
+        <v>41.37</v>
       </c>
       <c r="AF10">
-        <v>62.63</v>
+        <v>-50.96</v>
       </c>
       <c r="AG10">
-        <v>1652.03</v>
+        <v>1651.27</v>
       </c>
       <c r="AH10">
-        <v>1505.82</v>
+        <v>1504.03</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1958,7 +1996,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>23.64</v>
+        <v>21.79</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2139,7 +2177,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2159,1298 +2197,1372 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>59</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="C7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.86</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="8">
         <v>-4.8</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D11" s="8">
+        <v>-2.14</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C12" s="8">
         <v>-10.63</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D12" s="8">
+        <v>-10.79</v>
+      </c>
+      <c r="E12" s="10">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C13" s="8">
         <v>-9.32</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D13" s="8">
+        <v>-7.26</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C14" s="8">
         <v>-1.95</v>
       </c>
-      <c r="E12" s="7">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D14" s="8">
+        <v>-3.86</v>
+      </c>
+      <c r="E14" s="10">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C15" s="8">
         <v>-3.32</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D15" s="8">
+        <v>-1.81</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>15.99</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C16" s="8">
         <v>16.88</v>
       </c>
-      <c r="E14" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D16" s="8">
+        <v>15.78</v>
+      </c>
+      <c r="E16" s="10">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
-        <v>-11.84</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C17" s="8">
         <v>-9.199999999999999</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D17" s="8">
+        <v>-8.9</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C18" s="8">
         <v>1.01</v>
       </c>
-      <c r="E16" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D18" s="8">
+        <v>-0.84</v>
+      </c>
+      <c r="E18" s="10">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C19" s="8">
         <v>-3.31</v>
       </c>
-      <c r="E17" s="8">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D19" s="8">
+        <v>-2.11</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>1.06</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C20" s="8">
         <v>1.4</v>
       </c>
-      <c r="E18" s="7">
+      <c r="D20" s="8">
+        <v>4.08</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-2.3</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-1.66</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-1.66</v>
+      </c>
+      <c r="D22" s="8">
+        <v>-0.41</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>1.88</v>
+      </c>
+      <c r="D23" s="8">
+        <v>2.72</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>-1.84</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-0.19</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-3.01</v>
+      </c>
+      <c r="E25" s="10">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1.38</v>
+      </c>
+      <c r="D26" s="8">
+        <v>2.36</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2.09</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-0.1</v>
+      </c>
+      <c r="E27" s="10">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.74</v>
+      </c>
+      <c r="D28" s="8">
+        <v>1.14</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>-3.02</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-1.5</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-13.55</v>
+      </c>
+      <c r="D30" s="8">
+        <v>-15.32</v>
+      </c>
+      <c r="E30" s="10">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>30.8</v>
+      </c>
+      <c r="D31" s="8">
+        <v>27.34</v>
+      </c>
+      <c r="E31" s="10">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-1.83</v>
+      </c>
+      <c r="E32" s="10">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>11.93</v>
+      </c>
+      <c r="D33" s="8">
+        <v>13.68</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8">
+        <v>12.41</v>
+      </c>
+      <c r="D34" s="8">
+        <v>12.33</v>
+      </c>
+      <c r="E34" s="10">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-44.72</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-43.44</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-18.83</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-18.89</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2.2</v>
+      </c>
+      <c r="D37" s="8">
+        <v>2.83</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-16.56</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-16.57</v>
+      </c>
+      <c r="E38" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-0.74</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-0.26</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>20.13</v>
+      </c>
+      <c r="D40" s="8">
+        <v>20.67</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>3.99</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="E41" s="10">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="8">
+        <v>10.65</v>
+      </c>
+      <c r="D42" s="8">
+        <v>8.02</v>
+      </c>
+      <c r="E42" s="10">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="8">
+        <v>13.78</v>
+      </c>
+      <c r="D43" s="8">
+        <v>10.01</v>
+      </c>
+      <c r="E43" s="10">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-15.2</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-17.04</v>
+      </c>
+      <c r="E44" s="10">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-7.7</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-9.9</v>
+      </c>
+      <c r="E45" s="10">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="D46" s="8">
+        <v>8.59</v>
+      </c>
+      <c r="E46" s="10">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-21.02</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-19.39</v>
+      </c>
+      <c r="E47" s="9">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-19.73</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-19.65</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-14.31</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-13.97</v>
+      </c>
+      <c r="E49" s="9">
         <v>0.34</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
+        <v>-13.11</v>
+      </c>
+      <c r="D50" s="8">
+        <v>-14</v>
+      </c>
+      <c r="E50" s="10">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-11.28</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-1.56</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-3.01</v>
+      </c>
+      <c r="E52" s="10">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>-44.96</v>
+      </c>
+      <c r="D53" s="8">
+        <v>-44.38</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-19.4</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-20.57</v>
+      </c>
+      <c r="E54" s="10">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>-13.08</v>
+      </c>
+      <c r="D55" s="8">
+        <v>-11.87</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="8">
+        <v>387.15</v>
+      </c>
+      <c r="D56" s="8">
+        <v>395.15</v>
+      </c>
+      <c r="E56" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.33</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B57" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="8">
+        <v>3052</v>
+      </c>
+      <c r="D57" s="8">
+        <v>3055.3</v>
+      </c>
+      <c r="E57" s="9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-4.96</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="E20" s="7">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8">
+        <v>353.3</v>
+      </c>
+      <c r="D58" s="8">
+        <v>354.7</v>
+      </c>
+      <c r="E58" s="9">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.88</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B59" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="8">
+        <v>366.4</v>
+      </c>
+      <c r="D59" s="8">
+        <v>362.65</v>
+      </c>
+      <c r="E59" s="10">
+        <v>-3.75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.84</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B60" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="8">
+        <v>392.75</v>
+      </c>
+      <c r="D60" s="8">
+        <v>399.3</v>
+      </c>
+      <c r="E60" s="9">
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>6.51</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B61" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="8">
+        <v>717.55</v>
+      </c>
+      <c r="D61" s="8">
+        <v>706.95</v>
+      </c>
+      <c r="E61" s="10">
+        <v>-10.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.38</v>
-      </c>
-      <c r="E24" s="7">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="8">
+        <v>199.29</v>
+      </c>
+      <c r="D62" s="8">
+        <v>201.37</v>
+      </c>
+      <c r="E62" s="9">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D25" s="6">
-        <v>2.09</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B63" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
+        <v>3625.1</v>
+      </c>
+      <c r="D63" s="8">
+        <v>3572.4</v>
+      </c>
+      <c r="E63" s="10">
+        <v>-52.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>3.51</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B64" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="8">
+        <v>1537.1</v>
+      </c>
+      <c r="D64" s="8">
+        <v>1558.5</v>
+      </c>
+      <c r="E64" s="9">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="8">
+        <v>34</v>
+      </c>
+      <c r="D65" s="8">
+        <v>45</v>
+      </c>
+      <c r="E65" s="9">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-3.48</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-3.02</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-14.3</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-13.55</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B66" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="8">
+        <v>45</v>
+      </c>
+      <c r="D66" s="8">
+        <v>34</v>
+      </c>
+      <c r="E66" s="10">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="8">
+        <v>41.99</v>
+      </c>
+      <c r="D67" s="8">
+        <v>51.91</v>
+      </c>
+      <c r="E67" s="9">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="8">
+        <v>30.49</v>
+      </c>
+      <c r="D68" s="8">
+        <v>31.06</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>27.4</v>
-      </c>
-      <c r="D29" s="6">
-        <v>30.8</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B69" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="8">
+        <v>40.9</v>
+      </c>
+      <c r="D69" s="8">
+        <v>42.06</v>
+      </c>
+      <c r="E69" s="9">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-0.45</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B70" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="8">
+        <v>50.56</v>
+      </c>
+      <c r="D70" s="8">
+        <v>47.86</v>
+      </c>
+      <c r="E70" s="10">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>16.32</v>
-      </c>
-      <c r="D31" s="6">
-        <v>11.93</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-4.39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="8">
+        <v>45.66</v>
+      </c>
+      <c r="D71" s="8">
+        <v>51.68</v>
+      </c>
+      <c r="E71" s="9">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>14.89</v>
-      </c>
-      <c r="D32" s="6">
-        <v>12.41</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="8">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="D72" s="8">
+        <v>61.71</v>
+      </c>
+      <c r="E72" s="10">
+        <v>-4.03</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-45.36</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-44.72</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="8">
+        <v>35.78</v>
+      </c>
+      <c r="D73" s="8">
+        <v>39.89</v>
+      </c>
+      <c r="E73" s="9">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-17.55</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-18.83</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="8">
+        <v>55.24</v>
+      </c>
+      <c r="D74" s="8">
+        <v>48.15</v>
+      </c>
+      <c r="E74" s="10">
+        <v>-7.09</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>3.4</v>
-      </c>
-      <c r="D35" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="8">
+        <v>42.17</v>
+      </c>
+      <c r="D75" s="8">
+        <v>46.89</v>
+      </c>
+      <c r="E75" s="9">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-15.47</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-16.56</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B76" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="8">
+        <v>54.85</v>
+      </c>
+      <c r="D76" s="8">
+        <v>54.67</v>
+      </c>
+      <c r="E76" s="10">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-1.91</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.74</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B77" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="8">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="D77" s="8">
+        <v>-42.56</v>
+      </c>
+      <c r="E77" s="10">
+        <v>-109.85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>16.77</v>
-      </c>
-      <c r="D38" s="6">
-        <v>20.13</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B78" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="8">
+        <v>70.03</v>
+      </c>
+      <c r="D78" s="8">
+        <v>-43.75</v>
+      </c>
+      <c r="E78" s="10">
+        <v>-113.78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>3.87</v>
-      </c>
-      <c r="D39" s="6">
-        <v>3.99</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="8">
+        <v>32.24</v>
+      </c>
+      <c r="D79" s="8">
+        <v>11.86</v>
+      </c>
+      <c r="E79" s="10">
+        <v>-20.38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="D40" s="6">
-        <v>10.65</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B80" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="8">
+        <v>-10.18</v>
+      </c>
+      <c r="D80" s="8">
+        <v>-27.48</v>
+      </c>
+      <c r="E80" s="10">
+        <v>-17.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>13.83</v>
-      </c>
-      <c r="D41" s="6">
-        <v>13.78</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="8">
+        <v>-63.66</v>
+      </c>
+      <c r="D81" s="8">
+        <v>-46.65</v>
+      </c>
+      <c r="E81" s="9">
+        <v>17.01</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-16.21</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-15.2</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B82" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="8">
+        <v>25.13</v>
+      </c>
+      <c r="D82" s="8">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="E82" s="10">
+        <v>-35.08</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-8.25</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-7.7</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-10.92</v>
+      </c>
+      <c r="D83" s="8">
+        <v>-39.82</v>
+      </c>
+      <c r="E83" s="10">
+        <v>-28.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>7.83</v>
-      </c>
-      <c r="D44" s="6">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-21.32</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-21.02</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-19.09</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-19.73</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-16.15</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-14.31</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-13.75</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-13.11</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-1.19</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-46.09</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-44.96</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-21</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-19.4</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-11.73</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>385.7</v>
-      </c>
-      <c r="D54" s="6">
-        <v>387.15</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>3076.5</v>
-      </c>
-      <c r="D55" s="6">
-        <v>3052</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-24.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>345.7</v>
-      </c>
-      <c r="D56" s="6">
-        <v>353.3</v>
-      </c>
-      <c r="E56" s="7">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>363.7</v>
-      </c>
-      <c r="D57" s="6">
-        <v>366.4</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>389.55</v>
-      </c>
-      <c r="D58" s="6">
-        <v>392.75</v>
-      </c>
-      <c r="E58" s="7">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>720.2</v>
-      </c>
-      <c r="D59" s="6">
-        <v>717.55</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>195.17</v>
-      </c>
-      <c r="D60" s="6">
-        <v>199.29</v>
-      </c>
-      <c r="E60" s="7">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>3552.9</v>
-      </c>
-      <c r="D61" s="6">
-        <v>3625.1</v>
-      </c>
-      <c r="E61" s="7">
-        <v>72.2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1561</v>
-      </c>
-      <c r="D62" s="6">
-        <v>1537.1</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-23.9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>39.9</v>
-      </c>
-      <c r="D63" s="6">
-        <v>41.99</v>
-      </c>
-      <c r="E63" s="7">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>32.35</v>
-      </c>
-      <c r="D64" s="6">
-        <v>30.49</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>34.28</v>
-      </c>
-      <c r="D65" s="6">
-        <v>40.9</v>
-      </c>
-      <c r="E65" s="7">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>48.62</v>
-      </c>
-      <c r="D66" s="6">
-        <v>50.56</v>
-      </c>
-      <c r="E66" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>42.41</v>
-      </c>
-      <c r="D67" s="6">
-        <v>45.66</v>
-      </c>
-      <c r="E67" s="7">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>66.75</v>
-      </c>
-      <c r="D68" s="6">
-        <v>65.73999999999999</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>26.54</v>
-      </c>
-      <c r="D69" s="6">
-        <v>35.78</v>
-      </c>
-      <c r="E69" s="7">
-        <v>9.24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>44.92</v>
-      </c>
-      <c r="D70" s="6">
-        <v>55.24</v>
-      </c>
-      <c r="E70" s="7">
-        <v>10.32</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>46.46</v>
-      </c>
-      <c r="D71" s="6">
-        <v>42.17</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-4.29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B84" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>15.93</v>
-      </c>
-      <c r="D72" s="6">
-        <v>54.85</v>
-      </c>
-      <c r="E72" s="7">
-        <v>38.92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="D73" s="6">
-        <v>67.29000000000001</v>
-      </c>
-      <c r="E73" s="7">
-        <v>60.48</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="D74" s="6">
-        <v>70.03</v>
-      </c>
-      <c r="E74" s="7">
-        <v>78.11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>52.47</v>
-      </c>
-      <c r="D75" s="6">
-        <v>32.24</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-20.23</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-70.42</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-10.18</v>
-      </c>
-      <c r="E76" s="7">
-        <v>60.24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-7.98</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-63.66</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-55.68</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="D78" s="6">
-        <v>25.13</v>
-      </c>
-      <c r="E78" s="7">
-        <v>19.02</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-21.52</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-10.92</v>
-      </c>
-      <c r="E79" s="7">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>45.56</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C84" s="8">
         <v>62.63</v>
       </c>
-      <c r="E80" s="7">
-        <v>17.07</v>
+      <c r="D84" s="8">
+        <v>-50.96</v>
+      </c>
+      <c r="E84" s="10">
+        <v>-113.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3470,60 +3582,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>81</v>
+      <c r="B1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>45.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="13">
+        <v>46.8</v>
+      </c>
+      <c r="E2" s="13">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="13">
+        <v>-2.4</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="13">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>10</v>
       </c>
     </row>
@@ -3625,61 +3737,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3683</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3384</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2106</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1681</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1249</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0658</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.045</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0351</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1094</v>
+      <c r="A2" s="16">
+        <v>0.3664</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3381</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.2099</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.1628</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.133</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.06480000000000001</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.0435</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.0319</v>
+      </c>
+      <c r="I2" s="16">
+        <v>-0.1078</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,61 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>42.0 → 51.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>42.0</t>
+    <t>51.9 → 47.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.9</t>
   </si>
   <si>
-    <t>45.7 → 51.7</t>
-  </si>
-  <si>
-    <t>45.7</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.6% → -3.0%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.6%</t>
-  </si>
-  <si>
-    <t>-3.0%</t>
-  </si>
-  <si>
-    <t>50.6 → 47.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>55.2 → 48.1</t>
-  </si>
-  <si>
-    <t>55.2</t>
-  </si>
-  <si>
-    <t>48.1</t>
+    <t>47.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -302,7 +257,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,27 +291,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,19 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -473,16 +415,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -491,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -990,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>395.15</v>
+        <v>390.6</v>
       </c>
       <c r="D2">
-        <v>2.07</v>
+        <v>-1.15</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -1002,46 +942,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-19.39</v>
+        <v>-20.32</v>
       </c>
       <c r="H2">
-        <v>5.37</v>
+        <v>4.16</v>
       </c>
       <c r="I2">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="J2">
-        <v>-2.14</v>
+        <v>-2.61</v>
       </c>
       <c r="K2">
-        <v>-16.57</v>
+        <v>-16.72</v>
       </c>
       <c r="L2">
-        <v>-1.5</v>
+        <v>-5.63</v>
       </c>
       <c r="M2">
-        <v>13.3</v>
+        <v>12.76</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>383.76</v>
+        <v>386.88</v>
       </c>
       <c r="Q2">
-        <v>387.09</v>
+        <v>386.65</v>
       </c>
       <c r="R2">
-        <v>410.63</v>
+        <v>409.05</v>
       </c>
       <c r="S2">
-        <v>434.77</v>
+        <v>434.65</v>
       </c>
       <c r="T2">
-        <v>-9.109999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1056,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>51.91</v>
+        <v>46.99</v>
       </c>
       <c r="Z2">
-        <v>-6.95</v>
+        <v>-6.06</v>
       </c>
       <c r="AA2">
-        <v>-9.34</v>
+        <v>-8.68</v>
       </c>
       <c r="AB2">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="AD2">
-        <v>71.02</v>
+        <v>89.33</v>
       </c>
       <c r="AE2">
-        <v>9.41</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AF2">
-        <v>54.67</v>
+        <v>-32.58</v>
       </c>
       <c r="AG2">
-        <v>400.98</v>
+        <v>399.43</v>
       </c>
       <c r="AH2">
-        <v>373.2</v>
+        <v>373.88</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1092,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>46.09</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1103,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3055.3</v>
+        <v>3044.5</v>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>-0.35</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1115,46 +1055,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-19.65</v>
+        <v>-19.93</v>
       </c>
       <c r="H3">
-        <v>4.24</v>
+        <v>3.87</v>
       </c>
       <c r="I3">
-        <v>-1.66</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
-        <v>-10.79</v>
+        <v>-10.78</v>
       </c>
       <c r="K3">
-        <v>-0.26</v>
+        <v>0.24</v>
       </c>
       <c r="L3">
-        <v>-15.32</v>
+        <v>-16.2</v>
       </c>
       <c r="M3">
-        <v>33.81</v>
+        <v>33.21</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>3056.66</v>
+        <v>3059.66</v>
       </c>
       <c r="Q3">
-        <v>3197.72</v>
+        <v>3179.24</v>
       </c>
       <c r="R3">
-        <v>3269.23</v>
+        <v>3266.91</v>
       </c>
       <c r="S3">
-        <v>3302.98</v>
+        <v>3299.95</v>
       </c>
       <c r="T3">
-        <v>-7.5</v>
+        <v>-7.74</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1169,43 +1109,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.06</v>
+        <v>30.18</v>
       </c>
       <c r="Z3">
-        <v>-73.75</v>
+        <v>-74.22</v>
       </c>
       <c r="AA3">
-        <v>-58.17</v>
+        <v>-61.38</v>
       </c>
       <c r="AB3">
-        <v>-15.58</v>
+        <v>-12.84</v>
       </c>
       <c r="AC3">
-        <v>36.31</v>
+        <v>43.18</v>
       </c>
       <c r="AD3">
-        <v>29.97</v>
+        <v>37.28</v>
       </c>
       <c r="AE3">
-        <v>64.2</v>
+        <v>63.8</v>
       </c>
       <c r="AF3">
-        <v>-42.56</v>
+        <v>-6.65</v>
       </c>
       <c r="AG3">
-        <v>3455.99</v>
+        <v>3424.91</v>
       </c>
       <c r="AH3">
-        <v>2939.45</v>
+        <v>2933.57</v>
       </c>
       <c r="AI3">
-        <v>3264.24</v>
+        <v>3255.76</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>68.59999999999999</v>
+        <v>68.73999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1216,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>354.7</v>
+        <v>352.4</v>
       </c>
       <c r="D4">
-        <v>0.4</v>
+        <v>-0.65</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1228,46 +1168,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-13.97</v>
+        <v>-14.53</v>
       </c>
       <c r="H4">
-        <v>29.95</v>
+        <v>29.11</v>
       </c>
       <c r="I4">
-        <v>-0.41</v>
+        <v>2.95</v>
       </c>
       <c r="J4">
-        <v>-7.26</v>
+        <v>-7.65</v>
       </c>
       <c r="K4">
-        <v>20.67</v>
+        <v>21</v>
       </c>
       <c r="L4">
-        <v>27.34</v>
+        <v>24.96</v>
       </c>
       <c r="M4">
-        <v>16.28</v>
+        <v>16.13</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P4">
-        <v>348.21</v>
+        <v>350.23</v>
       </c>
       <c r="Q4">
-        <v>366.42</v>
+        <v>365.1</v>
       </c>
       <c r="R4">
-        <v>371.3</v>
+        <v>371.69</v>
       </c>
       <c r="S4">
-        <v>344.23</v>
+        <v>344.22</v>
       </c>
       <c r="T4">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1282,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>42.06</v>
+        <v>40.65</v>
       </c>
       <c r="Z4">
-        <v>-7.06</v>
+        <v>-6.99</v>
       </c>
       <c r="AA4">
-        <v>-4.61</v>
+        <v>-5.09</v>
       </c>
       <c r="AB4">
-        <v>-2.45</v>
+        <v>-1.9</v>
       </c>
       <c r="AC4">
-        <v>42.45</v>
+        <v>53.99</v>
       </c>
       <c r="AD4">
-        <v>26.06</v>
+        <v>41.01</v>
       </c>
       <c r="AE4">
-        <v>10.92</v>
+        <v>10.64</v>
       </c>
       <c r="AF4">
-        <v>-43.75</v>
+        <v>-5.26</v>
       </c>
       <c r="AG4">
-        <v>393.02</v>
+        <v>391.75</v>
       </c>
       <c r="AH4">
-        <v>339.81</v>
+        <v>338.45</v>
       </c>
       <c r="AI4">
         <v>378.22</v>
@@ -1318,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>27.83</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1329,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>362.65</v>
+        <v>359.05</v>
       </c>
       <c r="D5">
-        <v>-1.02</v>
+        <v>-0.99</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1341,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14</v>
+        <v>-14.86</v>
       </c>
       <c r="H5">
-        <v>23.25</v>
+        <v>22.02</v>
       </c>
       <c r="I5">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
-        <v>-3.86</v>
+        <v>-5.46</v>
       </c>
       <c r="K5">
-        <v>0.72</v>
+        <v>-0.28</v>
       </c>
       <c r="L5">
-        <v>-1.83</v>
+        <v>-6.23</v>
       </c>
       <c r="M5">
-        <v>6.48</v>
+        <v>6.01</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>356.56</v>
+        <v>359.19</v>
       </c>
       <c r="Q5">
-        <v>363.11</v>
+        <v>362.1</v>
       </c>
       <c r="R5">
-        <v>374.08</v>
+        <v>373.69</v>
       </c>
       <c r="S5">
-        <v>361.14</v>
+        <v>360.83</v>
       </c>
       <c r="T5">
-        <v>0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1392,37 +1332,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>47.86</v>
+        <v>45.35</v>
       </c>
       <c r="Z5">
-        <v>-4.45</v>
+        <v>-4.25</v>
       </c>
       <c r="AA5">
-        <v>-4.9</v>
+        <v>-4.77</v>
       </c>
       <c r="AB5">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="AC5">
-        <v>95.09999999999999</v>
+        <v>87.05</v>
       </c>
       <c r="AD5">
-        <v>65.11</v>
+        <v>82.78</v>
       </c>
       <c r="AE5">
-        <v>12.16</v>
+        <v>11.82</v>
       </c>
       <c r="AF5">
-        <v>11.86</v>
+        <v>-23.5</v>
       </c>
       <c r="AG5">
-        <v>380.66</v>
+        <v>378.01</v>
       </c>
       <c r="AH5">
-        <v>345.55</v>
+        <v>346.19</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1431,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.38</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1442,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>399.3</v>
+        <v>400.3</v>
       </c>
       <c r="D6">
-        <v>1.67</v>
+        <v>0.25</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1454,25 +1394,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.800000000000001</v>
+        <v>-9.58</v>
       </c>
       <c r="H6">
-        <v>42.84</v>
+        <v>43.19</v>
       </c>
       <c r="I6">
-        <v>0.53</v>
+        <v>3.37</v>
       </c>
       <c r="J6">
-        <v>-1.81</v>
+        <v>-0.21</v>
       </c>
       <c r="K6">
-        <v>8.02</v>
+        <v>4.35</v>
       </c>
       <c r="L6">
-        <v>13.68</v>
+        <v>12.62</v>
       </c>
       <c r="M6">
-        <v>-10.78</v>
+        <v>-11.25</v>
       </c>
       <c r="N6">
         <v>77</v>
@@ -1481,19 +1421,19 @@
         <v>69</v>
       </c>
       <c r="P6">
-        <v>391.13</v>
+        <v>393.74</v>
       </c>
       <c r="Q6">
-        <v>396.5</v>
+        <v>396.36</v>
       </c>
       <c r="R6">
-        <v>400.94</v>
+        <v>401.3</v>
       </c>
       <c r="S6">
-        <v>371.58</v>
+        <v>372</v>
       </c>
       <c r="T6">
-        <v>7.46</v>
+        <v>7.61</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1508,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.68</v>
+        <v>52.54</v>
       </c>
       <c r="Z6">
-        <v>-1.81</v>
+        <v>-1.3</v>
       </c>
       <c r="AA6">
         <v>-1.31</v>
       </c>
       <c r="AB6">
-        <v>-0.49</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>43.91</v>
+        <v>59.65</v>
       </c>
       <c r="AD6">
-        <v>27.41</v>
+        <v>42.51</v>
       </c>
       <c r="AE6">
-        <v>11.05</v>
+        <v>10.97</v>
       </c>
       <c r="AF6">
-        <v>-27.48</v>
+        <v>-36.67</v>
       </c>
       <c r="AG6">
-        <v>409.56</v>
+        <v>409.18</v>
       </c>
       <c r="AH6">
-        <v>383.45</v>
+        <v>383.55</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1544,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.85</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1555,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>706.95</v>
+        <v>697.35</v>
       </c>
       <c r="D7">
-        <v>-1.48</v>
+        <v>-1.36</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1567,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-3.01</v>
+        <v>-4.33</v>
       </c>
       <c r="H7">
-        <v>39.59</v>
+        <v>37.69</v>
       </c>
       <c r="I7">
-        <v>-3.01</v>
+        <v>-0.53</v>
       </c>
       <c r="J7">
-        <v>15.78</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K7">
-        <v>10.01</v>
+        <v>7.43</v>
       </c>
       <c r="L7">
-        <v>12.33</v>
+        <v>10.47</v>
       </c>
       <c r="M7">
-        <v>36.64</v>
+        <v>35.83</v>
       </c>
       <c r="N7">
         <v>88</v>
       </c>
       <c r="O7">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P7">
-        <v>707.75</v>
+        <v>707</v>
       </c>
       <c r="Q7">
-        <v>678.17</v>
+        <v>681.3</v>
       </c>
       <c r="R7">
-        <v>625.86</v>
+        <v>627.97</v>
       </c>
       <c r="S7">
-        <v>593.5599999999999</v>
+        <v>594.25</v>
       </c>
       <c r="T7">
-        <v>19.1</v>
+        <v>17.35</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1621,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>61.71</v>
+        <v>58.23</v>
       </c>
       <c r="Z7">
-        <v>25.53</v>
+        <v>23.72</v>
       </c>
       <c r="AA7">
-        <v>24.21</v>
+        <v>24.12</v>
       </c>
       <c r="AB7">
-        <v>1.31</v>
+        <v>-0.4</v>
       </c>
       <c r="AC7">
-        <v>24.42</v>
+        <v>11.86</v>
       </c>
       <c r="AD7">
-        <v>20.81</v>
+        <v>19.73</v>
       </c>
       <c r="AE7">
-        <v>26.37</v>
+        <v>25.76</v>
       </c>
       <c r="AF7">
-        <v>-46.65</v>
+        <v>-77.27</v>
       </c>
       <c r="AG7">
-        <v>739.9</v>
+        <v>740.03</v>
       </c>
       <c r="AH7">
-        <v>616.45</v>
+        <v>622.5700000000001</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1657,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>55.21</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1668,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>201.37</v>
+        <v>199.07</v>
       </c>
       <c r="D8">
-        <v>1.04</v>
+        <v>-1.14</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1680,46 +1620,46 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.38</v>
+        <v>-45.02</v>
       </c>
       <c r="H8">
-        <v>4.66</v>
+        <v>3.47</v>
       </c>
       <c r="I8">
-        <v>2.36</v>
+        <v>3.47</v>
       </c>
       <c r="J8">
-        <v>-8.9</v>
+        <v>-10.24</v>
       </c>
       <c r="K8">
-        <v>-17.04</v>
+        <v>-17.1</v>
       </c>
       <c r="L8">
-        <v>-43.44</v>
+        <v>-44.14</v>
       </c>
       <c r="M8">
-        <v>-3.19</v>
+        <v>-3.7</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>196.35</v>
+        <v>197.68</v>
       </c>
       <c r="Q8">
-        <v>205.32</v>
+        <v>204.22</v>
       </c>
       <c r="R8">
-        <v>216.42</v>
+        <v>215.76</v>
       </c>
       <c r="S8">
-        <v>254.04</v>
+        <v>253.46</v>
       </c>
       <c r="T8">
-        <v>-20.73</v>
+        <v>-21.46</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1734,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.89</v>
+        <v>37.06</v>
       </c>
       <c r="Z8">
-        <v>-6.36</v>
+        <v>-6.02</v>
       </c>
       <c r="AA8">
-        <v>-6.34</v>
+        <v>-6.27</v>
       </c>
       <c r="AB8">
-        <v>-0.02</v>
+        <v>0.25</v>
       </c>
       <c r="AC8">
-        <v>83.01000000000001</v>
+        <v>95.38</v>
       </c>
       <c r="AD8">
-        <v>54.09</v>
+        <v>78.23</v>
       </c>
       <c r="AE8">
-        <v>6.27</v>
+        <v>6.1</v>
       </c>
       <c r="AF8">
-        <v>-9.949999999999999</v>
+        <v>-68.94</v>
       </c>
       <c r="AG8">
-        <v>222.26</v>
+        <v>219.65</v>
       </c>
       <c r="AH8">
-        <v>188.39</v>
+        <v>188.8</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1770,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>53.36</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1781,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3572.4</v>
+        <v>3556</v>
       </c>
       <c r="D9">
-        <v>-1.45</v>
+        <v>-0.46</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1793,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.57</v>
+        <v>-20.93</v>
       </c>
       <c r="H9">
-        <v>7.96</v>
+        <v>7.47</v>
       </c>
       <c r="I9">
-        <v>-0.1</v>
+        <v>-0.37</v>
       </c>
       <c r="J9">
-        <v>-0.84</v>
+        <v>-0.39</v>
       </c>
       <c r="K9">
-        <v>-9.9</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L9">
-        <v>-18.89</v>
+        <v>-20.21</v>
       </c>
       <c r="M9">
-        <v>20.99</v>
+        <v>20.53</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P9">
-        <v>3568.88</v>
+        <v>3566.24</v>
       </c>
       <c r="Q9">
-        <v>3567.97</v>
+        <v>3567.82</v>
       </c>
       <c r="R9">
-        <v>3603.85</v>
+        <v>3599.18</v>
       </c>
       <c r="S9">
-        <v>3679.24</v>
+        <v>3678.16</v>
       </c>
       <c r="T9">
-        <v>-2.9</v>
+        <v>-3.32</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1847,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.15</v>
+        <v>46.16</v>
       </c>
       <c r="Z9">
-        <v>-9.81</v>
+        <v>-10.64</v>
       </c>
       <c r="AA9">
-        <v>-14.81</v>
+        <v>-13.97</v>
       </c>
       <c r="AB9">
-        <v>4.99</v>
+        <v>3.33</v>
       </c>
       <c r="AC9">
-        <v>58.48</v>
+        <v>58.14</v>
       </c>
       <c r="AD9">
-        <v>48.07</v>
+        <v>55.11</v>
       </c>
       <c r="AE9">
-        <v>64.43000000000001</v>
+        <v>63.59</v>
       </c>
       <c r="AF9">
-        <v>-39.82</v>
+        <v>-36.13</v>
       </c>
       <c r="AG9">
-        <v>3633.77</v>
+        <v>3633.72</v>
       </c>
       <c r="AH9">
-        <v>3502.17</v>
+        <v>3501.93</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1883,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>24.35</v>
+        <v>23.13</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1894,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1558.5</v>
+        <v>1551.6</v>
       </c>
       <c r="D10">
-        <v>1.39</v>
+        <v>-0.44</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1906,25 +1846,25 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.87</v>
+        <v>-12.26</v>
       </c>
       <c r="H10">
-        <v>17.52</v>
+        <v>17</v>
       </c>
       <c r="I10">
-        <v>1.14</v>
+        <v>-1.54</v>
       </c>
       <c r="J10">
-        <v>-2.11</v>
+        <v>-2.05</v>
       </c>
       <c r="K10">
-        <v>8.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L10">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="M10">
-        <v>4.35</v>
+        <v>3.53</v>
       </c>
       <c r="N10">
         <v>66</v>
@@ -1933,19 +1873,19 @@
         <v>65</v>
       </c>
       <c r="P10">
-        <v>1558.1</v>
+        <v>1553.24</v>
       </c>
       <c r="Q10">
-        <v>1577.65</v>
+        <v>1576.03</v>
       </c>
       <c r="R10">
-        <v>1589.79</v>
+        <v>1590.73</v>
       </c>
       <c r="S10">
-        <v>1518.92</v>
+        <v>1518.97</v>
       </c>
       <c r="T10">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1960,34 +1900,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>46.89</v>
+        <v>45.6</v>
       </c>
       <c r="Z10">
-        <v>-11.84</v>
+        <v>-11.76</v>
       </c>
       <c r="AA10">
-        <v>-8.15</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AB10">
-        <v>-3.69</v>
+        <v>-2.89</v>
       </c>
       <c r="AC10">
-        <v>44.72</v>
+        <v>47.38</v>
       </c>
       <c r="AD10">
-        <v>45.79</v>
+        <v>44.86</v>
       </c>
       <c r="AE10">
-        <v>41.37</v>
+        <v>40.4</v>
       </c>
       <c r="AF10">
-        <v>-50.96</v>
+        <v>-47.9</v>
       </c>
       <c r="AG10">
-        <v>1651.27</v>
+        <v>1650.49</v>
       </c>
       <c r="AH10">
-        <v>1504.03</v>
+        <v>1501.57</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1996,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>21.79</v>
+        <v>20.19</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2195,1374 +2135,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-2.14</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-2.61</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-10.79</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-10.78</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-7.26</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.65</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5.46</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-1.81</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-0.21</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>15.78</v>
+      </c>
+      <c r="D12" s="6">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-8.9</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-10.24</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4.08</v>
+      </c>
+      <c r="D16" s="6">
+        <v>4.16</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.41</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.95</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2.72</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3.37</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-3.01</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3.47</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.37</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.14</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.54</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-4.8</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-2.14</v>
-      </c>
-      <c r="E11" s="9">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-5.63</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-4.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-10.63</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-10.79</v>
-      </c>
-      <c r="E12" s="10">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-15.32</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-16.2</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-9.32</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-7.26</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>27.34</v>
+      </c>
+      <c r="D27" s="6">
+        <v>24.96</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-1.95</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-3.86</v>
-      </c>
-      <c r="E14" s="10">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-1.83</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-6.23</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-3.32</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-1.81</v>
-      </c>
-      <c r="E15" s="9">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>13.68</v>
+      </c>
+      <c r="D29" s="6">
+        <v>12.62</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>16.88</v>
-      </c>
-      <c r="D16" s="8">
-        <v>15.78</v>
-      </c>
-      <c r="E16" s="10">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>12.33</v>
+      </c>
+      <c r="D30" s="6">
+        <v>10.47</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-8.9</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-43.44</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-44.14</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-0.84</v>
-      </c>
-      <c r="E18" s="10">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-18.89</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-20.21</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-3.31</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-2.11</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>2.83</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1.4</v>
-      </c>
-      <c r="D20" s="8">
-        <v>4.08</v>
-      </c>
-      <c r="E20" s="9">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-16.57</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-16.72</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-0.26</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>20.67</v>
+      </c>
+      <c r="D36" s="6">
+        <v>21</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.28</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>8.02</v>
+      </c>
+      <c r="D38" s="6">
+        <v>4.35</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-3.67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>10.01</v>
+      </c>
+      <c r="D39" s="6">
+        <v>7.43</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-17.04</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-17.1</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-9.9</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>8.59</v>
+      </c>
+      <c r="D42" s="6">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-19.39</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-20.32</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-19.65</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-19.93</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-13.97</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-14.53</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-14</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-14.86</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-9.58</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-3.01</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-4.33</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-44.38</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-45.02</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-20.57</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-20.93</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-11.87</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-12.26</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>395.15</v>
+      </c>
+      <c r="D52" s="6">
+        <v>390.6</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3055.3</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3044.5</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>354.7</v>
+      </c>
+      <c r="D54" s="6">
+        <v>352.4</v>
+      </c>
+      <c r="E54" s="7">
         <v>-2.3</v>
       </c>
-      <c r="D21" s="8">
-        <v>-1.66</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>362.65</v>
+      </c>
+      <c r="D55" s="6">
+        <v>359.05</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>399.3</v>
+      </c>
+      <c r="D56" s="6">
+        <v>400.3</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>706.95</v>
+      </c>
+      <c r="D57" s="6">
+        <v>697.35</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>201.37</v>
+      </c>
+      <c r="D58" s="6">
+        <v>199.07</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3572.4</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3556</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-16.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1558.5</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1551.6</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45</v>
+      </c>
+      <c r="D61" s="6">
+        <v>34</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>34</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45</v>
+      </c>
+      <c r="E62" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>51.91</v>
+      </c>
+      <c r="D63" s="6">
+        <v>46.99</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-4.92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>31.06</v>
+      </c>
+      <c r="D64" s="6">
+        <v>30.18</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-1.66</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-0.41</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>42.06</v>
+      </c>
+      <c r="D65" s="6">
+        <v>40.65</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>1.88</v>
-      </c>
-      <c r="D23" s="8">
-        <v>2.72</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>47.86</v>
+      </c>
+      <c r="D66" s="6">
+        <v>45.35</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>-1.84</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.53</v>
-      </c>
-      <c r="E24" s="9">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>51.68</v>
+      </c>
+      <c r="D67" s="6">
+        <v>52.54</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-0.19</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-3.01</v>
-      </c>
-      <c r="E25" s="10">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>61.71</v>
+      </c>
+      <c r="D68" s="6">
+        <v>58.23</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>1.38</v>
-      </c>
-      <c r="D26" s="8">
-        <v>2.36</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>39.89</v>
+      </c>
+      <c r="D69" s="6">
+        <v>37.06</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>2.09</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-0.1</v>
-      </c>
-      <c r="E27" s="10">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>48.15</v>
+      </c>
+      <c r="D70" s="6">
+        <v>46.16</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="D28" s="8">
-        <v>1.14</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>46.89</v>
+      </c>
+      <c r="D71" s="6">
+        <v>45.6</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-3.02</v>
-      </c>
-      <c r="D29" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>54.67</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-32.58</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-87.25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-13.55</v>
-      </c>
-      <c r="D30" s="8">
-        <v>-15.32</v>
-      </c>
-      <c r="E30" s="10">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-42.56</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-6.65</v>
+      </c>
+      <c r="E73" s="8">
+        <v>35.91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>30.8</v>
-      </c>
-      <c r="D31" s="8">
-        <v>27.34</v>
-      </c>
-      <c r="E31" s="10">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-43.75</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-5.26</v>
+      </c>
+      <c r="E74" s="8">
+        <v>38.49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="D32" s="8">
-        <v>-1.83</v>
-      </c>
-      <c r="E32" s="10">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>11.86</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-23.5</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-35.36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>11.93</v>
-      </c>
-      <c r="D33" s="8">
-        <v>13.68</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-27.48</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-36.67</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-9.19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>12.41</v>
-      </c>
-      <c r="D34" s="8">
-        <v>12.33</v>
-      </c>
-      <c r="E34" s="10">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-46.65</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-77.27</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-30.62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>-44.72</v>
-      </c>
-      <c r="D35" s="8">
-        <v>-43.44</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-68.94</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-58.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-18.83</v>
-      </c>
-      <c r="D36" s="8">
-        <v>-18.89</v>
-      </c>
-      <c r="E36" s="10">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-39.82</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-36.13</v>
+      </c>
+      <c r="E79" s="8">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="8">
-        <v>2.2</v>
-      </c>
-      <c r="D37" s="8">
-        <v>2.83</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-16.56</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-16.57</v>
-      </c>
-      <c r="E38" s="10">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-0.74</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-0.26</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>20.13</v>
-      </c>
-      <c r="D40" s="8">
-        <v>20.67</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>3.99</v>
-      </c>
-      <c r="D41" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="E41" s="10">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>10.65</v>
-      </c>
-      <c r="D42" s="8">
-        <v>8.02</v>
-      </c>
-      <c r="E42" s="10">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>13.78</v>
-      </c>
-      <c r="D43" s="8">
-        <v>10.01</v>
-      </c>
-      <c r="E43" s="10">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-15.2</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-17.04</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-7.7</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-9.9</v>
-      </c>
-      <c r="E45" s="10">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="8">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="D46" s="8">
-        <v>8.59</v>
-      </c>
-      <c r="E46" s="10">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-21.02</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-19.39</v>
-      </c>
-      <c r="E47" s="9">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-19.73</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-19.65</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-14.31</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-13.97</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-13.11</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-14</v>
-      </c>
-      <c r="E50" s="10">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-11.28</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="8">
-        <v>-1.56</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-3.01</v>
-      </c>
-      <c r="E52" s="10">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="8">
-        <v>-44.96</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-44.38</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="8">
-        <v>-19.4</v>
-      </c>
-      <c r="D54" s="8">
-        <v>-20.57</v>
-      </c>
-      <c r="E54" s="10">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="8">
-        <v>-13.08</v>
-      </c>
-      <c r="D55" s="8">
-        <v>-11.87</v>
-      </c>
-      <c r="E55" s="9">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="8">
-        <v>387.15</v>
-      </c>
-      <c r="D56" s="8">
-        <v>395.15</v>
-      </c>
-      <c r="E56" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>3052</v>
-      </c>
-      <c r="D57" s="8">
-        <v>3055.3</v>
-      </c>
-      <c r="E57" s="9">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>353.3</v>
-      </c>
-      <c r="D58" s="8">
-        <v>354.7</v>
-      </c>
-      <c r="E58" s="9">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="8">
-        <v>366.4</v>
-      </c>
-      <c r="D59" s="8">
-        <v>362.65</v>
-      </c>
-      <c r="E59" s="10">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="8">
-        <v>392.75</v>
-      </c>
-      <c r="D60" s="8">
-        <v>399.3</v>
-      </c>
-      <c r="E60" s="9">
-        <v>6.55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="8">
-        <v>717.55</v>
-      </c>
-      <c r="D61" s="8">
-        <v>706.95</v>
-      </c>
-      <c r="E61" s="10">
-        <v>-10.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="8">
-        <v>199.29</v>
-      </c>
-      <c r="D62" s="8">
-        <v>201.37</v>
-      </c>
-      <c r="E62" s="9">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="8">
-        <v>3625.1</v>
-      </c>
-      <c r="D63" s="8">
-        <v>3572.4</v>
-      </c>
-      <c r="E63" s="10">
-        <v>-52.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="8">
-        <v>1537.1</v>
-      </c>
-      <c r="D64" s="8">
-        <v>1558.5</v>
-      </c>
-      <c r="E64" s="9">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="8">
-        <v>34</v>
-      </c>
-      <c r="D65" s="8">
-        <v>45</v>
-      </c>
-      <c r="E65" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="8">
-        <v>45</v>
-      </c>
-      <c r="D66" s="8">
-        <v>34</v>
-      </c>
-      <c r="E66" s="10">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="8">
-        <v>41.99</v>
-      </c>
-      <c r="D67" s="8">
-        <v>51.91</v>
-      </c>
-      <c r="E67" s="9">
-        <v>9.92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="8">
-        <v>30.49</v>
-      </c>
-      <c r="D68" s="8">
-        <v>31.06</v>
-      </c>
-      <c r="E68" s="9">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="8">
-        <v>40.9</v>
-      </c>
-      <c r="D69" s="8">
-        <v>42.06</v>
-      </c>
-      <c r="E69" s="9">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="8">
-        <v>50.56</v>
-      </c>
-      <c r="D70" s="8">
-        <v>47.86</v>
-      </c>
-      <c r="E70" s="10">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="8">
-        <v>45.66</v>
-      </c>
-      <c r="D71" s="8">
-        <v>51.68</v>
-      </c>
-      <c r="E71" s="9">
-        <v>6.02</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="8">
-        <v>65.73999999999999</v>
-      </c>
-      <c r="D72" s="8">
-        <v>61.71</v>
-      </c>
-      <c r="E72" s="10">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="8">
-        <v>35.78</v>
-      </c>
-      <c r="D73" s="8">
-        <v>39.89</v>
-      </c>
-      <c r="E73" s="9">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="8">
-        <v>55.24</v>
-      </c>
-      <c r="D74" s="8">
-        <v>48.15</v>
-      </c>
-      <c r="E74" s="10">
-        <v>-7.09</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="8">
-        <v>42.17</v>
-      </c>
-      <c r="D75" s="8">
-        <v>46.89</v>
-      </c>
-      <c r="E75" s="9">
-        <v>4.72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="7" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="8">
-        <v>54.85</v>
-      </c>
-      <c r="D76" s="8">
-        <v>54.67</v>
-      </c>
-      <c r="E76" s="10">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="8">
-        <v>67.29000000000001</v>
-      </c>
-      <c r="D77" s="8">
-        <v>-42.56</v>
-      </c>
-      <c r="E77" s="10">
-        <v>-109.85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="8">
-        <v>70.03</v>
-      </c>
-      <c r="D78" s="8">
-        <v>-43.75</v>
-      </c>
-      <c r="E78" s="10">
-        <v>-113.78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="8">
-        <v>32.24</v>
-      </c>
-      <c r="D79" s="8">
-        <v>11.86</v>
-      </c>
-      <c r="E79" s="10">
-        <v>-20.38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="8">
-        <v>-10.18</v>
-      </c>
-      <c r="D80" s="8">
-        <v>-27.48</v>
-      </c>
-      <c r="E80" s="10">
-        <v>-17.3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="8">
-        <v>-63.66</v>
-      </c>
-      <c r="D81" s="8">
-        <v>-46.65</v>
-      </c>
-      <c r="E81" s="9">
-        <v>17.01</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="8">
-        <v>25.13</v>
-      </c>
-      <c r="D82" s="8">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="E82" s="10">
-        <v>-35.08</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="8">
-        <v>-10.92</v>
-      </c>
-      <c r="D83" s="8">
-        <v>-39.82</v>
-      </c>
-      <c r="E83" s="10">
-        <v>-28.9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="8">
-        <v>62.63</v>
-      </c>
-      <c r="D84" s="8">
+      <c r="C80" s="6">
         <v>-50.96</v>
       </c>
-      <c r="E84" s="10">
-        <v>-113.59</v>
+      <c r="D80" s="6">
+        <v>-47.9</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3582,60 +3442,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>89</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="13">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="14">
+      <c r="B2" s="11">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="13">
-        <v>46.8</v>
-      </c>
-      <c r="E2" s="13">
-        <v>60</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-2.4</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="D2" s="11">
+        <v>44.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3737,61 +3597,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="16">
-        <v>0.3664</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3381</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.2099</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.1628</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.133</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.06480000000000001</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.0435</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.0319</v>
-      </c>
-      <c r="I2" s="16">
-        <v>-0.1078</v>
+      <c r="A2" s="14">
+        <v>0.3583</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3321</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2053</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1613</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1276</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0601</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0353</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.03700000000000001</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1125</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,34 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.9 → 47.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>47.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>390.6</v>
+        <v>384.2</v>
       </c>
       <c r="D2">
-        <v>-1.15</v>
+        <v>-1.64</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +914,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-20.32</v>
+        <v>-21.62</v>
       </c>
       <c r="H2">
-        <v>4.16</v>
+        <v>2.45</v>
       </c>
       <c r="I2">
-        <v>4.16</v>
+        <v>2.24</v>
       </c>
       <c r="J2">
-        <v>-2.61</v>
+        <v>-3.79</v>
       </c>
       <c r="K2">
-        <v>-16.72</v>
+        <v>-18.24</v>
       </c>
       <c r="L2">
-        <v>-5.63</v>
+        <v>-9.92</v>
       </c>
       <c r="M2">
-        <v>12.76</v>
+        <v>11.88</v>
       </c>
       <c r="N2">
+        <v>23</v>
+      </c>
+      <c r="O2">
         <v>34</v>
       </c>
-      <c r="O2">
-        <v>38</v>
-      </c>
       <c r="P2">
-        <v>386.88</v>
+        <v>388.56</v>
       </c>
       <c r="Q2">
-        <v>386.65</v>
+        <v>386.06</v>
       </c>
       <c r="R2">
-        <v>409.05</v>
+        <v>407.57</v>
       </c>
       <c r="S2">
-        <v>434.65</v>
+        <v>434.51</v>
       </c>
       <c r="T2">
-        <v>-10.14</v>
+        <v>-11.58</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.99</v>
+        <v>41.08</v>
       </c>
       <c r="Z2">
-        <v>-6.06</v>
+        <v>-5.81</v>
       </c>
       <c r="AA2">
-        <v>-8.68</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="AB2">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
-        <v>94.8</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="AD2">
-        <v>89.33</v>
+        <v>92.72</v>
       </c>
       <c r="AE2">
-        <v>9.380000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="AF2">
-        <v>-32.58</v>
+        <v>167.41</v>
       </c>
       <c r="AG2">
-        <v>399.43</v>
+        <v>398.1</v>
       </c>
       <c r="AH2">
-        <v>373.88</v>
+        <v>374.03</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1032,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>42.56</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3044.5</v>
+        <v>3035</v>
       </c>
       <c r="D3">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-19.93</v>
+        <v>-20.18</v>
       </c>
       <c r="H3">
-        <v>3.87</v>
+        <v>3.54</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>-1.14</v>
       </c>
       <c r="J3">
-        <v>-10.78</v>
+        <v>-11.1</v>
       </c>
       <c r="K3">
-        <v>0.24</v>
+        <v>-0.96</v>
       </c>
       <c r="L3">
-        <v>-16.2</v>
+        <v>-16.67</v>
       </c>
       <c r="M3">
-        <v>33.21</v>
+        <v>32.92</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P3">
-        <v>3059.66</v>
+        <v>3052.66</v>
       </c>
       <c r="Q3">
-        <v>3179.24</v>
+        <v>3158.84</v>
       </c>
       <c r="R3">
-        <v>3266.91</v>
+        <v>3265.75</v>
       </c>
       <c r="S3">
-        <v>3299.95</v>
+        <v>3296.77</v>
       </c>
       <c r="T3">
-        <v>-7.74</v>
+        <v>-7.94</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,43 +1081,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>30.18</v>
+        <v>29.39</v>
       </c>
       <c r="Z3">
-        <v>-74.22</v>
+        <v>-74.5</v>
       </c>
       <c r="AA3">
-        <v>-61.38</v>
+        <v>-64</v>
       </c>
       <c r="AB3">
-        <v>-12.84</v>
+        <v>-10.5</v>
       </c>
       <c r="AC3">
-        <v>43.18</v>
+        <v>47.72</v>
       </c>
       <c r="AD3">
-        <v>37.28</v>
+        <v>42.4</v>
       </c>
       <c r="AE3">
-        <v>63.8</v>
+        <v>61.36</v>
       </c>
       <c r="AF3">
-        <v>-6.65</v>
+        <v>42.19</v>
       </c>
       <c r="AG3">
-        <v>3424.91</v>
+        <v>3378.69</v>
       </c>
       <c r="AH3">
-        <v>2933.57</v>
+        <v>2938.99</v>
       </c>
       <c r="AI3">
-        <v>3255.76</v>
+        <v>3221.28</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>68.73999999999999</v>
+        <v>69.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>352.4</v>
+        <v>348.6</v>
       </c>
       <c r="D4">
-        <v>-0.65</v>
+        <v>-1.08</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1140,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-14.53</v>
+        <v>-15.45</v>
       </c>
       <c r="H4">
-        <v>29.11</v>
+        <v>27.72</v>
       </c>
       <c r="I4">
-        <v>2.95</v>
+        <v>1.03</v>
       </c>
       <c r="J4">
-        <v>-7.65</v>
+        <v>-7.95</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>12.14</v>
       </c>
       <c r="L4">
-        <v>24.96</v>
+        <v>21.91</v>
       </c>
       <c r="M4">
-        <v>16.13</v>
+        <v>15.35</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>350.23</v>
+        <v>350.94</v>
       </c>
       <c r="Q4">
-        <v>365.1</v>
+        <v>363.46</v>
       </c>
       <c r="R4">
-        <v>371.69</v>
+        <v>372.16</v>
       </c>
       <c r="S4">
         <v>344.22</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>1.27</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>40.65</v>
+        <v>38.36</v>
       </c>
       <c r="Z4">
-        <v>-6.99</v>
+        <v>-7.16</v>
       </c>
       <c r="AA4">
-        <v>-5.09</v>
+        <v>-5.5</v>
       </c>
       <c r="AB4">
-        <v>-1.9</v>
+        <v>-1.65</v>
       </c>
       <c r="AC4">
-        <v>53.99</v>
+        <v>49.39</v>
       </c>
       <c r="AD4">
-        <v>41.01</v>
+        <v>48.61</v>
       </c>
       <c r="AE4">
-        <v>10.64</v>
+        <v>10.54</v>
       </c>
       <c r="AF4">
-        <v>-5.26</v>
+        <v>-63.72</v>
       </c>
       <c r="AG4">
-        <v>391.75</v>
+        <v>389.91</v>
       </c>
       <c r="AH4">
-        <v>338.45</v>
+        <v>337</v>
       </c>
       <c r="AI4">
         <v>378.22</v>
@@ -1258,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>25.75</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>359.05</v>
+        <v>356.6</v>
       </c>
       <c r="D5">
-        <v>-0.99</v>
+        <v>-0.68</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.86</v>
+        <v>-15.44</v>
       </c>
       <c r="H5">
-        <v>22.02</v>
+        <v>21.19</v>
       </c>
       <c r="I5">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="J5">
-        <v>-5.46</v>
+        <v>-5.95</v>
       </c>
       <c r="K5">
-        <v>-0.28</v>
+        <v>-1.26</v>
       </c>
       <c r="L5">
-        <v>-6.23</v>
+        <v>-7.23</v>
       </c>
       <c r="M5">
-        <v>6.01</v>
+        <v>5.4</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>359.19</v>
+        <v>361.68</v>
       </c>
       <c r="Q5">
-        <v>362.1</v>
+        <v>361.1</v>
       </c>
       <c r="R5">
-        <v>373.69</v>
+        <v>373.38</v>
       </c>
       <c r="S5">
-        <v>360.83</v>
+        <v>360.53</v>
       </c>
       <c r="T5">
-        <v>-0.49</v>
+        <v>-1.09</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1307,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>45.35</v>
+        <v>43.67</v>
       </c>
       <c r="Z5">
         <v>-4.25</v>
       </c>
       <c r="AA5">
-        <v>-4.77</v>
+        <v>-4.66</v>
       </c>
       <c r="AB5">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="AC5">
-        <v>87.05</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="AD5">
-        <v>82.78</v>
+        <v>85.98</v>
       </c>
       <c r="AE5">
-        <v>11.82</v>
+        <v>11.65</v>
       </c>
       <c r="AF5">
-        <v>-23.5</v>
+        <v>-1.17</v>
       </c>
       <c r="AG5">
-        <v>378.01</v>
+        <v>375.64</v>
       </c>
       <c r="AH5">
-        <v>346.19</v>
+        <v>346.57</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1371,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>28.03</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>400.3</v>
+        <v>416.55</v>
       </c>
       <c r="D6">
-        <v>0.25</v>
+        <v>4.06</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1366,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.58</v>
+        <v>-5.91</v>
       </c>
       <c r="H6">
-        <v>43.19</v>
+        <v>49.01</v>
       </c>
       <c r="I6">
-        <v>3.37</v>
+        <v>7.69</v>
       </c>
       <c r="J6">
-        <v>-0.21</v>
+        <v>3.34</v>
       </c>
       <c r="K6">
-        <v>4.35</v>
+        <v>10.4</v>
       </c>
       <c r="L6">
-        <v>12.62</v>
+        <v>15.9</v>
       </c>
       <c r="M6">
-        <v>-11.25</v>
+        <v>-10.17</v>
       </c>
       <c r="N6">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>393.74</v>
+        <v>399.69</v>
       </c>
       <c r="Q6">
-        <v>396.36</v>
+        <v>397.21</v>
       </c>
       <c r="R6">
-        <v>401.3</v>
+        <v>401.75</v>
       </c>
       <c r="S6">
-        <v>372</v>
+        <v>372.48</v>
       </c>
       <c r="T6">
-        <v>7.61</v>
+        <v>11.83</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>52.54</v>
+        <v>63.85</v>
       </c>
       <c r="Z6">
-        <v>-1.3</v>
+        <v>0.41</v>
       </c>
       <c r="AA6">
-        <v>-1.31</v>
+        <v>-0.97</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>1.38</v>
       </c>
       <c r="AC6">
-        <v>59.65</v>
+        <v>79.86</v>
       </c>
       <c r="AD6">
-        <v>42.51</v>
+        <v>61.14</v>
       </c>
       <c r="AE6">
-        <v>10.97</v>
+        <v>11.96</v>
       </c>
       <c r="AF6">
-        <v>-36.67</v>
+        <v>287.74</v>
       </c>
       <c r="AG6">
-        <v>409.18</v>
+        <v>412.85</v>
       </c>
       <c r="AH6">
-        <v>383.55</v>
+        <v>381.56</v>
       </c>
       <c r="AI6">
-        <v>372.35</v>
+        <v>376.69</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>22.52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>697.35</v>
+        <v>702.75</v>
       </c>
       <c r="D7">
-        <v>-1.36</v>
+        <v>0.77</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1507,46 +1479,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-4.33</v>
+        <v>-3.59</v>
       </c>
       <c r="H7">
-        <v>37.69</v>
+        <v>38.76</v>
       </c>
       <c r="I7">
-        <v>-0.53</v>
+        <v>1.41</v>
       </c>
       <c r="J7">
-        <v>9.970000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="K7">
-        <v>7.43</v>
+        <v>8.32</v>
       </c>
       <c r="L7">
-        <v>10.47</v>
+        <v>11.57</v>
       </c>
       <c r="M7">
-        <v>35.83</v>
+        <v>36.15</v>
       </c>
       <c r="N7">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>707</v>
+        <v>708.96</v>
       </c>
       <c r="Q7">
-        <v>681.3</v>
+        <v>684.61</v>
       </c>
       <c r="R7">
-        <v>627.97</v>
+        <v>630.25</v>
       </c>
       <c r="S7">
-        <v>594.25</v>
+        <v>594.9</v>
       </c>
       <c r="T7">
-        <v>17.35</v>
+        <v>18.13</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,34 +1533,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>58.23</v>
+        <v>59.61</v>
       </c>
       <c r="Z7">
-        <v>23.72</v>
+        <v>22.46</v>
       </c>
       <c r="AA7">
-        <v>24.12</v>
+        <v>23.78</v>
       </c>
       <c r="AB7">
-        <v>-0.4</v>
+        <v>-1.32</v>
       </c>
       <c r="AC7">
-        <v>11.86</v>
+        <v>4.07</v>
       </c>
       <c r="AD7">
-        <v>19.73</v>
+        <v>13.45</v>
       </c>
       <c r="AE7">
-        <v>25.76</v>
+        <v>26.25</v>
       </c>
       <c r="AF7">
-        <v>-77.27</v>
+        <v>-2.82</v>
       </c>
       <c r="AG7">
-        <v>740.03</v>
+        <v>740.1</v>
       </c>
       <c r="AH7">
-        <v>622.5700000000001</v>
+        <v>629.13</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1597,7 +1569,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>50.31</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1580,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>199.07</v>
+        <v>201.39</v>
       </c>
       <c r="D8">
-        <v>-1.14</v>
+        <v>1.17</v>
       </c>
       <c r="E8">
-        <v>362.05</v>
+        <v>360.5</v>
       </c>
       <c r="F8">
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-45.02</v>
+        <v>-44.14</v>
       </c>
       <c r="H8">
-        <v>3.47</v>
+        <v>4.67</v>
       </c>
       <c r="I8">
-        <v>3.47</v>
+        <v>4.07</v>
       </c>
       <c r="J8">
-        <v>-10.24</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="K8">
-        <v>-17.1</v>
+        <v>-15.92</v>
       </c>
       <c r="L8">
-        <v>-44.14</v>
+        <v>-44.38</v>
       </c>
       <c r="M8">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>197.68</v>
+        <v>199.26</v>
       </c>
       <c r="Q8">
-        <v>204.22</v>
+        <v>203.34</v>
       </c>
       <c r="R8">
-        <v>215.76</v>
+        <v>215.28</v>
       </c>
       <c r="S8">
-        <v>253.46</v>
+        <v>252.89</v>
       </c>
       <c r="T8">
-        <v>-21.46</v>
+        <v>-20.37</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1646,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>37.06</v>
+        <v>41.56</v>
       </c>
       <c r="Z8">
-        <v>-6.02</v>
+        <v>-5.5</v>
       </c>
       <c r="AA8">
-        <v>-6.27</v>
+        <v>-6.12</v>
       </c>
       <c r="AB8">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="AC8">
         <v>95.38</v>
       </c>
       <c r="AD8">
-        <v>78.23</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="AE8">
         <v>6.1</v>
       </c>
       <c r="AF8">
-        <v>-68.94</v>
+        <v>-3.52</v>
       </c>
       <c r="AG8">
-        <v>219.65</v>
+        <v>217.11</v>
       </c>
       <c r="AH8">
-        <v>188.8</v>
+        <v>189.56</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1710,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>49.98</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3556</v>
+        <v>3559.3</v>
       </c>
       <c r="D9">
-        <v>-0.46</v>
+        <v>0.09</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1733,46 +1705,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.93</v>
+        <v>-20.86</v>
       </c>
       <c r="H9">
-        <v>7.47</v>
+        <v>7.57</v>
       </c>
       <c r="I9">
-        <v>-0.37</v>
+        <v>0.98</v>
       </c>
       <c r="J9">
-        <v>-0.39</v>
+        <v>0.01</v>
       </c>
       <c r="K9">
-        <v>-9.220000000000001</v>
+        <v>-9.83</v>
       </c>
       <c r="L9">
-        <v>-20.21</v>
+        <v>-19.86</v>
       </c>
       <c r="M9">
-        <v>20.53</v>
+        <v>20.29</v>
       </c>
       <c r="N9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O9">
         <v>35</v>
       </c>
       <c r="P9">
-        <v>3566.24</v>
+        <v>3573.14</v>
       </c>
       <c r="Q9">
-        <v>3567.82</v>
+        <v>3568.21</v>
       </c>
       <c r="R9">
-        <v>3599.18</v>
+        <v>3595.23</v>
       </c>
       <c r="S9">
-        <v>3678.16</v>
+        <v>3677.19</v>
       </c>
       <c r="T9">
-        <v>-3.32</v>
+        <v>-3.21</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.16</v>
+        <v>46.64</v>
       </c>
       <c r="Z9">
-        <v>-10.64</v>
+        <v>-10.9</v>
       </c>
       <c r="AA9">
-        <v>-13.97</v>
+        <v>-13.36</v>
       </c>
       <c r="AB9">
-        <v>3.33</v>
+        <v>2.46</v>
       </c>
       <c r="AC9">
-        <v>58.14</v>
+        <v>42.32</v>
       </c>
       <c r="AD9">
-        <v>55.11</v>
+        <v>52.98</v>
       </c>
       <c r="AE9">
-        <v>63.59</v>
+        <v>61.32</v>
       </c>
       <c r="AF9">
-        <v>-36.13</v>
+        <v>-41.45</v>
       </c>
       <c r="AG9">
-        <v>3633.72</v>
+        <v>3633.79</v>
       </c>
       <c r="AH9">
-        <v>3501.93</v>
+        <v>3502.62</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1823,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.13</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1551.6</v>
+        <v>1557</v>
       </c>
       <c r="D10">
-        <v>-0.44</v>
+        <v>0.35</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-12.26</v>
+        <v>-11.95</v>
       </c>
       <c r="H10">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="I10">
-        <v>-1.54</v>
+        <v>-0.06</v>
       </c>
       <c r="J10">
-        <v>-2.05</v>
+        <v>-1.7</v>
       </c>
       <c r="K10">
-        <v>9.609999999999999</v>
+        <v>6.53</v>
       </c>
       <c r="L10">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="M10">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P10">
-        <v>1553.24</v>
+        <v>1553.04</v>
       </c>
       <c r="Q10">
-        <v>1576.03</v>
+        <v>1573.89</v>
       </c>
       <c r="R10">
-        <v>1590.73</v>
+        <v>1592.18</v>
       </c>
       <c r="S10">
-        <v>1518.97</v>
+        <v>1518.95</v>
       </c>
       <c r="T10">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1872,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>45.6</v>
+        <v>46.84</v>
       </c>
       <c r="Z10">
-        <v>-11.76</v>
+        <v>-11.13</v>
       </c>
       <c r="AA10">
-        <v>-8.869999999999999</v>
+        <v>-9.32</v>
       </c>
       <c r="AB10">
-        <v>-2.89</v>
+        <v>-1.81</v>
       </c>
       <c r="AC10">
-        <v>47.38</v>
+        <v>63.88</v>
       </c>
       <c r="AD10">
-        <v>44.86</v>
+        <v>51.99</v>
       </c>
       <c r="AE10">
-        <v>40.4</v>
+        <v>38.85</v>
       </c>
       <c r="AF10">
-        <v>-47.9</v>
+        <v>-55.93</v>
       </c>
       <c r="AG10">
-        <v>1650.49</v>
+        <v>1647.92</v>
       </c>
       <c r="AH10">
-        <v>1501.57</v>
+        <v>1499.85</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1936,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.19</v>
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2097,47 +2069,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2145,1278 +2082,1312 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-2.61</v>
       </c>
-      <c r="E7" s="7">
+      <c r="D7" s="5">
+        <v>-3.79</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-10.78</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-11.1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-7.65</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-7.95</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-5.46</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.95</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.21</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3.34</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D12" s="5">
+        <v>10.71</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-10.24</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.39</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.05</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1.7</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4.16</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2.24</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.14</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="D19" s="5">
+        <v>3.62</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="D20" s="5">
+        <v>7.69</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-0.53</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3.47</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-0.37</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-1.54</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-0.06</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-5.63</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-9.92</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-16.2</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-16.67</v>
+      </c>
+      <c r="E26" s="6">
         <v>-0.47</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>24.96</v>
+      </c>
+      <c r="D27" s="5">
+        <v>21.91</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-6.23</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-7.23</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>12.62</v>
+      </c>
+      <c r="D29" s="5">
+        <v>15.9</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>10.47</v>
+      </c>
+      <c r="D30" s="5">
+        <v>11.57</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-44.14</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-44.38</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-20.21</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-19.86</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1.46</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-16.72</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-18.24</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-10.79</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-10.78</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>0.24</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-0.96</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-7.65</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>21</v>
+      </c>
+      <c r="D36" s="5">
+        <v>12.14</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-8.859999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.46</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-0.28</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-1.26</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.81</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-0.21</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>4.35</v>
+      </c>
+      <c r="D38" s="5">
+        <v>10.4</v>
+      </c>
+      <c r="E38" s="7">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>15.78</v>
-      </c>
-      <c r="D12" s="6">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-5.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>7.43</v>
+      </c>
+      <c r="D39" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-10.24</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-17.1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-15.92</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-9.83</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="D42" s="5">
+        <v>6.53</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-3.08</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>4.08</v>
-      </c>
-      <c r="D16" s="6">
-        <v>4.16</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-20.32</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-21.62</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-19.93</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-20.18</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.41</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2.95</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-14.53</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-15.45</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2.72</v>
-      </c>
-      <c r="D19" s="6">
-        <v>3.8</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-14.86</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-15.44</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.53</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3.37</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-9.58</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-5.91</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.53</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-4.33</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-3.59</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3.47</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-45.02</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-44.14</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-20.93</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-20.86</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1.14</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.54</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-12.26</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-11.95</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>390.6</v>
+      </c>
+      <c r="D52" s="5">
+        <v>384.2</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3044.5</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3035</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-9.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>352.4</v>
+      </c>
+      <c r="D54" s="5">
+        <v>348.6</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>359.05</v>
+      </c>
+      <c r="D55" s="5">
+        <v>356.6</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>400.3</v>
+      </c>
+      <c r="D56" s="5">
+        <v>416.55</v>
+      </c>
+      <c r="E56" s="7">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>697.35</v>
+      </c>
+      <c r="D57" s="5">
+        <v>702.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>199.07</v>
+      </c>
+      <c r="D58" s="5">
+        <v>201.39</v>
+      </c>
+      <c r="E58" s="7">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>3556</v>
+      </c>
+      <c r="D59" s="5">
+        <v>3559.3</v>
+      </c>
+      <c r="E59" s="7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1551.6</v>
+      </c>
+      <c r="D60" s="5">
+        <v>1557</v>
+      </c>
+      <c r="E60" s="7">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>34</v>
+      </c>
+      <c r="D61" s="5">
+        <v>23</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>77</v>
+      </c>
+      <c r="D62" s="5">
+        <v>88</v>
+      </c>
+      <c r="E62" s="7">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-5.63</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="5">
+        <v>88</v>
+      </c>
+      <c r="D63" s="5">
+        <v>77</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="5">
+        <v>23</v>
+      </c>
+      <c r="D64" s="5">
+        <v>34</v>
+      </c>
+      <c r="E64" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>46.99</v>
+      </c>
+      <c r="D65" s="5">
+        <v>41.08</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-5.91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-15.32</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-16.2</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>30.18</v>
+      </c>
+      <c r="D66" s="5">
+        <v>29.39</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>27.34</v>
-      </c>
-      <c r="D27" s="6">
-        <v>24.96</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>40.65</v>
+      </c>
+      <c r="D67" s="5">
+        <v>38.36</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-1.83</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-6.23</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>45.35</v>
+      </c>
+      <c r="D68" s="5">
+        <v>43.67</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>13.68</v>
-      </c>
-      <c r="D29" s="6">
-        <v>12.62</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>52.54</v>
+      </c>
+      <c r="D69" s="5">
+        <v>63.85</v>
+      </c>
+      <c r="E69" s="7">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>12.33</v>
-      </c>
-      <c r="D30" s="6">
-        <v>10.47</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>58.23</v>
+      </c>
+      <c r="D70" s="5">
+        <v>59.61</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-43.44</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-44.14</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>37.06</v>
+      </c>
+      <c r="D71" s="5">
+        <v>41.56</v>
+      </c>
+      <c r="E71" s="7">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-18.89</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-20.21</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="5">
+        <v>46.16</v>
+      </c>
+      <c r="D72" s="5">
+        <v>46.64</v>
+      </c>
+      <c r="E72" s="7">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1.33</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="5">
+        <v>45.6</v>
+      </c>
+      <c r="D73" s="5">
+        <v>46.84</v>
+      </c>
+      <c r="E73" s="7">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-16.57</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-16.72</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-32.58</v>
+      </c>
+      <c r="D74" s="5">
+        <v>167.41</v>
+      </c>
+      <c r="E74" s="7">
+        <v>199.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="D35" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-6.65</v>
+      </c>
+      <c r="D75" s="5">
+        <v>42.19</v>
+      </c>
+      <c r="E75" s="7">
+        <v>48.84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>20.67</v>
-      </c>
-      <c r="D36" s="6">
-        <v>21</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-5.26</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-63.72</v>
+      </c>
+      <c r="E76" s="6">
+        <v>-58.46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-23.5</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-1.17</v>
+      </c>
+      <c r="E77" s="7">
+        <v>22.33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>8.02</v>
-      </c>
-      <c r="D38" s="6">
-        <v>4.35</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-3.67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-36.67</v>
+      </c>
+      <c r="D78" s="5">
+        <v>287.74</v>
+      </c>
+      <c r="E78" s="7">
+        <v>324.41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>10.01</v>
-      </c>
-      <c r="D39" s="6">
-        <v>7.43</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>-77.27</v>
+      </c>
+      <c r="D79" s="5">
+        <v>-2.82</v>
+      </c>
+      <c r="E79" s="7">
+        <v>74.45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-17.04</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-17.1</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="5">
+        <v>-68.94</v>
+      </c>
+      <c r="D80" s="5">
+        <v>-3.52</v>
+      </c>
+      <c r="E80" s="7">
+        <v>65.42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-9.9</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="5">
+        <v>-36.13</v>
+      </c>
+      <c r="D81" s="5">
+        <v>-41.45</v>
+      </c>
+      <c r="E81" s="6">
+        <v>-5.32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>8.59</v>
-      </c>
-      <c r="D42" s="6">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-19.39</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-20.32</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-19.65</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-19.93</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-13.97</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-14.53</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-14</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-14.86</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-9.58</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-4.33</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-44.38</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-45.02</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-20.57</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-20.93</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-11.87</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-12.26</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>395.15</v>
-      </c>
-      <c r="D52" s="6">
-        <v>390.6</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3055.3</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3044.5</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-10.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>354.7</v>
-      </c>
-      <c r="D54" s="6">
-        <v>352.4</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>362.65</v>
-      </c>
-      <c r="D55" s="6">
-        <v>359.05</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>399.3</v>
-      </c>
-      <c r="D56" s="6">
-        <v>400.3</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>706.95</v>
-      </c>
-      <c r="D57" s="6">
-        <v>697.35</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-9.6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>201.37</v>
-      </c>
-      <c r="D58" s="6">
-        <v>199.07</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>3572.4</v>
-      </c>
-      <c r="D59" s="6">
-        <v>3556</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-16.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1558.5</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1551.6</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>51.91</v>
-      </c>
-      <c r="D63" s="6">
-        <v>46.99</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-4.92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>31.06</v>
-      </c>
-      <c r="D64" s="6">
-        <v>30.18</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>42.06</v>
-      </c>
-      <c r="D65" s="6">
-        <v>40.65</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>47.86</v>
-      </c>
-      <c r="D66" s="6">
-        <v>45.35</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>51.68</v>
-      </c>
-      <c r="D67" s="6">
-        <v>52.54</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>61.71</v>
-      </c>
-      <c r="D68" s="6">
-        <v>58.23</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>39.89</v>
-      </c>
-      <c r="D69" s="6">
-        <v>37.06</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>48.15</v>
-      </c>
-      <c r="D70" s="6">
-        <v>46.16</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>46.89</v>
-      </c>
-      <c r="D71" s="6">
-        <v>45.6</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>54.67</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-32.58</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-87.25</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-42.56</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-6.65</v>
-      </c>
-      <c r="E73" s="8">
-        <v>35.91</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-43.75</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-5.26</v>
-      </c>
-      <c r="E74" s="8">
-        <v>38.49</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>11.86</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-23.5</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-35.36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-27.48</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-36.67</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-9.19</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-46.65</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-77.27</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-30.62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-68.94</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-58.99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-39.82</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-36.13</v>
-      </c>
-      <c r="E79" s="8">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-50.96</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C82" s="5">
         <v>-47.9</v>
       </c>
-      <c r="E80" s="8">
-        <v>3.06</v>
+      <c r="D82" s="5">
+        <v>-55.93</v>
+      </c>
+      <c r="E82" s="6">
+        <v>-8.029999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3442,60 +3413,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>45.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3597,61 +3568,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3583</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3321</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2053</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1613</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1276</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0601</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0353</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.03700000000000001</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1125</v>
+      <c r="A2" s="13">
+        <v>0.3615</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3292</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2029</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1535</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1188</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.05400000000000001</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0349</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.035</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1017</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -264,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>384.2</v>
+        <v>388.95</v>
       </c>
       <c r="D2">
-        <v>-1.64</v>
+        <v>1.24</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +914,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-21.62</v>
+        <v>-20.65</v>
       </c>
       <c r="H2">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="I2">
-        <v>2.24</v>
+        <v>0.84</v>
       </c>
       <c r="J2">
-        <v>-3.79</v>
+        <v>-1.77</v>
       </c>
       <c r="K2">
-        <v>-18.24</v>
+        <v>-17.47</v>
       </c>
       <c r="L2">
-        <v>-9.92</v>
+        <v>-9.43</v>
       </c>
       <c r="M2">
-        <v>11.88</v>
+        <v>12.54</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>388.56</v>
+        <v>389.21</v>
       </c>
       <c r="Q2">
-        <v>386.06</v>
+        <v>385.66</v>
       </c>
       <c r="R2">
-        <v>407.57</v>
+        <v>406.12</v>
       </c>
       <c r="S2">
-        <v>434.51</v>
+        <v>434.41</v>
       </c>
       <c r="T2">
-        <v>-11.58</v>
+        <v>-10.47</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.08</v>
+        <v>46.46</v>
       </c>
       <c r="Z2">
-        <v>-5.81</v>
+        <v>-5.16</v>
       </c>
       <c r="AA2">
-        <v>-8.109999999999999</v>
+        <v>-7.52</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AC2">
-        <v>83.34999999999999</v>
+        <v>77.59</v>
       </c>
       <c r="AD2">
-        <v>92.72</v>
+        <v>85.25</v>
       </c>
       <c r="AE2">
-        <v>9.57</v>
+        <v>9.59</v>
       </c>
       <c r="AF2">
-        <v>167.41</v>
+        <v>-25.5</v>
       </c>
       <c r="AG2">
-        <v>398.1</v>
+        <v>396.65</v>
       </c>
       <c r="AH2">
-        <v>374.03</v>
+        <v>374.68</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>38.02</v>
+        <v>34.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3035</v>
+        <v>2982.7</v>
       </c>
       <c r="D3">
-        <v>-0.31</v>
+        <v>-1.72</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-20.18</v>
+        <v>-21.56</v>
       </c>
       <c r="H3">
-        <v>3.54</v>
+        <v>1.76</v>
       </c>
       <c r="I3">
-        <v>-1.14</v>
+        <v>-3.05</v>
       </c>
       <c r="J3">
-        <v>-11.1</v>
+        <v>-13.37</v>
       </c>
       <c r="K3">
-        <v>-0.96</v>
+        <v>-6.27</v>
       </c>
       <c r="L3">
-        <v>-16.67</v>
+        <v>-16.97</v>
       </c>
       <c r="M3">
-        <v>32.92</v>
+        <v>31.73</v>
       </c>
       <c r="N3">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P3">
-        <v>3052.66</v>
+        <v>3033.9</v>
       </c>
       <c r="Q3">
-        <v>3158.84</v>
+        <v>3138.07</v>
       </c>
       <c r="R3">
-        <v>3265.75</v>
+        <v>3263.74</v>
       </c>
       <c r="S3">
-        <v>3296.77</v>
+        <v>3293.1</v>
       </c>
       <c r="T3">
-        <v>-7.94</v>
+        <v>-9.43</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1081,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.39</v>
+        <v>25.45</v>
       </c>
       <c r="Z3">
-        <v>-74.5</v>
+        <v>-78.04000000000001</v>
       </c>
       <c r="AA3">
-        <v>-64</v>
+        <v>-66.81</v>
       </c>
       <c r="AB3">
-        <v>-10.5</v>
+        <v>-11.23</v>
       </c>
       <c r="AC3">
-        <v>47.72</v>
+        <v>36.52</v>
       </c>
       <c r="AD3">
-        <v>42.4</v>
+        <v>42.47</v>
       </c>
       <c r="AE3">
-        <v>61.36</v>
+        <v>61</v>
       </c>
       <c r="AF3">
-        <v>42.19</v>
+        <v>0.34</v>
       </c>
       <c r="AG3">
-        <v>3378.69</v>
+        <v>3340.52</v>
       </c>
       <c r="AH3">
-        <v>2938.99</v>
+        <v>2935.61</v>
       </c>
       <c r="AI3">
-        <v>3221.28</v>
+        <v>3193.85</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>69.28</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>348.6</v>
+        <v>339.9</v>
       </c>
       <c r="D4">
-        <v>-1.08</v>
+        <v>-2.5</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,46 +1140,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-15.45</v>
+        <v>-17.56</v>
       </c>
       <c r="H4">
-        <v>27.72</v>
+        <v>24.53</v>
       </c>
       <c r="I4">
-        <v>1.03</v>
+        <v>-1.68</v>
       </c>
       <c r="J4">
-        <v>-7.95</v>
+        <v>-10.89</v>
       </c>
       <c r="K4">
-        <v>12.14</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>21.91</v>
+        <v>17.39</v>
       </c>
       <c r="M4">
-        <v>15.35</v>
+        <v>15.15</v>
       </c>
       <c r="N4">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>350.94</v>
+        <v>349.78</v>
       </c>
       <c r="Q4">
-        <v>363.46</v>
+        <v>361.18</v>
       </c>
       <c r="R4">
-        <v>372.16</v>
+        <v>372.46</v>
       </c>
       <c r="S4">
-        <v>344.22</v>
+        <v>344.09</v>
       </c>
       <c r="T4">
-        <v>1.27</v>
+        <v>-1.22</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1191,46 +1191,46 @@
         <v>47</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>38.36</v>
+        <v>33.69</v>
       </c>
       <c r="Z4">
-        <v>-7.16</v>
+        <v>-7.9</v>
       </c>
       <c r="AA4">
-        <v>-5.5</v>
+        <v>-5.98</v>
       </c>
       <c r="AB4">
-        <v>-1.65</v>
+        <v>-1.92</v>
       </c>
       <c r="AC4">
-        <v>49.39</v>
+        <v>34.46</v>
       </c>
       <c r="AD4">
-        <v>48.61</v>
+        <v>45.95</v>
       </c>
       <c r="AE4">
-        <v>10.54</v>
+        <v>10.8</v>
       </c>
       <c r="AF4">
-        <v>-63.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG4">
-        <v>389.91</v>
+        <v>387.53</v>
       </c>
       <c r="AH4">
-        <v>337</v>
+        <v>334.84</v>
       </c>
       <c r="AI4">
-        <v>378.22</v>
+        <v>371.29</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>24.79</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>356.6</v>
+        <v>353.9</v>
       </c>
       <c r="D5">
-        <v>-0.68</v>
+        <v>-0.76</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-15.44</v>
+        <v>-16.08</v>
       </c>
       <c r="H5">
-        <v>21.19</v>
+        <v>20.27</v>
       </c>
       <c r="I5">
-        <v>3.62</v>
+        <v>-2.69</v>
       </c>
       <c r="J5">
-        <v>-5.95</v>
+        <v>-6.02</v>
       </c>
       <c r="K5">
-        <v>-1.26</v>
+        <v>-2.03</v>
       </c>
       <c r="L5">
-        <v>-7.23</v>
+        <v>-6.71</v>
       </c>
       <c r="M5">
-        <v>5.4</v>
+        <v>4.81</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>361.68</v>
+        <v>359.72</v>
       </c>
       <c r="Q5">
-        <v>361.1</v>
+        <v>360.24</v>
       </c>
       <c r="R5">
-        <v>373.38</v>
+        <v>373.02</v>
       </c>
       <c r="S5">
-        <v>360.53</v>
+        <v>360.23</v>
       </c>
       <c r="T5">
-        <v>-1.09</v>
+        <v>-1.76</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1307,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>43.67</v>
+        <v>41.83</v>
       </c>
       <c r="Z5">
-        <v>-4.25</v>
+        <v>-4.42</v>
       </c>
       <c r="AA5">
-        <v>-4.66</v>
+        <v>-4.61</v>
       </c>
       <c r="AB5">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
       <c r="AC5">
-        <v>75.79000000000001</v>
+        <v>65.94</v>
       </c>
       <c r="AD5">
-        <v>85.98</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="AE5">
-        <v>11.65</v>
+        <v>11.73</v>
       </c>
       <c r="AF5">
-        <v>-1.17</v>
+        <v>-21.2</v>
       </c>
       <c r="AG5">
-        <v>375.64</v>
+        <v>374.29</v>
       </c>
       <c r="AH5">
-        <v>346.57</v>
+        <v>346.19</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1343,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>26.75</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>416.55</v>
+        <v>420.05</v>
       </c>
       <c r="D6">
-        <v>4.06</v>
+        <v>0.84</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1366,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-5.91</v>
+        <v>-5.12</v>
       </c>
       <c r="H6">
-        <v>49.01</v>
+        <v>50.26</v>
       </c>
       <c r="I6">
-        <v>7.69</v>
+        <v>7.83</v>
       </c>
       <c r="J6">
-        <v>3.34</v>
+        <v>5.09</v>
       </c>
       <c r="K6">
-        <v>10.4</v>
+        <v>14.14</v>
       </c>
       <c r="L6">
-        <v>15.9</v>
+        <v>15.76</v>
       </c>
       <c r="M6">
-        <v>-10.17</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>399.69</v>
+        <v>405.79</v>
       </c>
       <c r="Q6">
-        <v>397.21</v>
+        <v>398.24</v>
       </c>
       <c r="R6">
-        <v>401.75</v>
+        <v>402.38</v>
       </c>
       <c r="S6">
-        <v>372.48</v>
+        <v>373.01</v>
       </c>
       <c r="T6">
-        <v>11.83</v>
+        <v>12.61</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>63.85</v>
+        <v>65.75</v>
       </c>
       <c r="Z6">
-        <v>0.41</v>
+        <v>2.02</v>
       </c>
       <c r="AA6">
-        <v>-0.97</v>
+        <v>-0.37</v>
       </c>
       <c r="AB6">
-        <v>1.38</v>
+        <v>2.39</v>
       </c>
       <c r="AC6">
-        <v>79.86</v>
+        <v>90.19</v>
       </c>
       <c r="AD6">
-        <v>61.14</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="AE6">
-        <v>11.96</v>
+        <v>12.37</v>
       </c>
       <c r="AF6">
-        <v>287.74</v>
+        <v>305.36</v>
       </c>
       <c r="AG6">
-        <v>412.85</v>
+        <v>416.92</v>
       </c>
       <c r="AH6">
-        <v>381.56</v>
+        <v>379.55</v>
       </c>
       <c r="AI6">
-        <v>376.69</v>
+        <v>383.27</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>27</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>702.75</v>
+        <v>708.55</v>
       </c>
       <c r="D7">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1479,46 +1479,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-3.59</v>
+        <v>-2.79</v>
       </c>
       <c r="H7">
-        <v>38.76</v>
+        <v>39.91</v>
       </c>
       <c r="I7">
-        <v>1.41</v>
+        <v>-1.62</v>
       </c>
       <c r="J7">
-        <v>10.71</v>
+        <v>11.31</v>
       </c>
       <c r="K7">
-        <v>8.32</v>
+        <v>12.75</v>
       </c>
       <c r="L7">
-        <v>11.57</v>
+        <v>12.31</v>
       </c>
       <c r="M7">
-        <v>36.15</v>
+        <v>36.5</v>
       </c>
       <c r="N7">
+        <v>88</v>
+      </c>
+      <c r="O7">
         <v>77</v>
       </c>
-      <c r="O7">
-        <v>74</v>
-      </c>
       <c r="P7">
-        <v>708.96</v>
+        <v>706.63</v>
       </c>
       <c r="Q7">
-        <v>684.61</v>
+        <v>688.21</v>
       </c>
       <c r="R7">
-        <v>630.25</v>
+        <v>632.64</v>
       </c>
       <c r="S7">
-        <v>594.9</v>
+        <v>595.58</v>
       </c>
       <c r="T7">
-        <v>18.13</v>
+        <v>18.97</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1533,34 +1533,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>59.61</v>
+        <v>61.09</v>
       </c>
       <c r="Z7">
-        <v>22.46</v>
+        <v>21.68</v>
       </c>
       <c r="AA7">
-        <v>23.78</v>
+        <v>23.36</v>
       </c>
       <c r="AB7">
-        <v>-1.32</v>
+        <v>-1.68</v>
       </c>
       <c r="AC7">
-        <v>4.07</v>
+        <v>7.87</v>
       </c>
       <c r="AD7">
-        <v>13.45</v>
+        <v>7.93</v>
       </c>
       <c r="AE7">
-        <v>26.25</v>
+        <v>26.37</v>
       </c>
       <c r="AF7">
-        <v>-2.82</v>
+        <v>-49.73</v>
       </c>
       <c r="AG7">
-        <v>740.1</v>
+        <v>739.77</v>
       </c>
       <c r="AH7">
-        <v>629.13</v>
+        <v>636.66</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1569,7 +1569,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>47.95</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>201.39</v>
+        <v>199.71</v>
       </c>
       <c r="D8">
-        <v>1.17</v>
+        <v>-0.83</v>
       </c>
       <c r="E8">
         <v>360.5</v>
@@ -1592,46 +1592,46 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.14</v>
+        <v>-44.6</v>
       </c>
       <c r="H8">
-        <v>4.67</v>
+        <v>3.8</v>
       </c>
       <c r="I8">
-        <v>4.07</v>
+        <v>2.33</v>
       </c>
       <c r="J8">
-        <v>-8.890000000000001</v>
+        <v>-8.85</v>
       </c>
       <c r="K8">
-        <v>-15.92</v>
+        <v>-16.81</v>
       </c>
       <c r="L8">
-        <v>-44.38</v>
+        <v>-44.25</v>
       </c>
       <c r="M8">
-        <v>-3.5</v>
+        <v>-3.55</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>199.26</v>
+        <v>200.17</v>
       </c>
       <c r="Q8">
-        <v>203.34</v>
+        <v>202.41</v>
       </c>
       <c r="R8">
-        <v>215.28</v>
+        <v>214.76</v>
       </c>
       <c r="S8">
-        <v>252.89</v>
+        <v>252.33</v>
       </c>
       <c r="T8">
-        <v>-20.37</v>
+        <v>-20.85</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1646,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>41.56</v>
+        <v>39.37</v>
       </c>
       <c r="Z8">
-        <v>-5.5</v>
+        <v>-5.17</v>
       </c>
       <c r="AA8">
-        <v>-6.12</v>
+        <v>-5.93</v>
       </c>
       <c r="AB8">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="AC8">
-        <v>95.38</v>
+        <v>92.06</v>
       </c>
       <c r="AD8">
-        <v>91.26000000000001</v>
+        <v>94.27</v>
       </c>
       <c r="AE8">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="AF8">
-        <v>-3.52</v>
+        <v>-62.85</v>
       </c>
       <c r="AG8">
-        <v>217.11</v>
+        <v>214.35</v>
       </c>
       <c r="AH8">
-        <v>189.56</v>
+        <v>190.48</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1682,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>43.95</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3559.3</v>
+        <v>3548.6</v>
       </c>
       <c r="D9">
-        <v>0.09</v>
+        <v>-0.3</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,46 +1705,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.86</v>
+        <v>-21.1</v>
       </c>
       <c r="H9">
-        <v>7.57</v>
+        <v>7.24</v>
       </c>
       <c r="I9">
-        <v>0.98</v>
+        <v>-0.12</v>
       </c>
       <c r="J9">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="K9">
-        <v>-9.83</v>
+        <v>-10.25</v>
       </c>
       <c r="L9">
         <v>-19.86</v>
       </c>
       <c r="M9">
-        <v>20.29</v>
+        <v>20.54</v>
       </c>
       <c r="N9">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>3573.14</v>
+        <v>3572.28</v>
       </c>
       <c r="Q9">
-        <v>3568.21</v>
+        <v>3568.19</v>
       </c>
       <c r="R9">
-        <v>3595.23</v>
+        <v>3590.81</v>
       </c>
       <c r="S9">
-        <v>3677.19</v>
+        <v>3676.27</v>
       </c>
       <c r="T9">
-        <v>-3.21</v>
+        <v>-3.47</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.64</v>
+        <v>45.24</v>
       </c>
       <c r="Z9">
-        <v>-10.9</v>
+        <v>-11.83</v>
       </c>
       <c r="AA9">
-        <v>-13.36</v>
+        <v>-13.05</v>
       </c>
       <c r="AB9">
-        <v>2.46</v>
+        <v>1.22</v>
       </c>
       <c r="AC9">
-        <v>42.32</v>
+        <v>34.13</v>
       </c>
       <c r="AD9">
-        <v>52.98</v>
+        <v>44.86</v>
       </c>
       <c r="AE9">
-        <v>61.32</v>
+        <v>59.63</v>
       </c>
       <c r="AF9">
-        <v>-41.45</v>
+        <v>-0.34</v>
       </c>
       <c r="AG9">
-        <v>3633.79</v>
+        <v>3633.8</v>
       </c>
       <c r="AH9">
-        <v>3502.62</v>
+        <v>3502.57</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1795,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>22.07</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="D10">
-        <v>0.35</v>
+        <v>-0.9</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.95</v>
+        <v>-12.75</v>
       </c>
       <c r="H10">
-        <v>17.4</v>
+        <v>16.35</v>
       </c>
       <c r="I10">
-        <v>-0.06</v>
+        <v>-1.15</v>
       </c>
       <c r="J10">
-        <v>-1.7</v>
+        <v>-3.56</v>
       </c>
       <c r="K10">
-        <v>6.53</v>
+        <v>7.37</v>
       </c>
       <c r="L10">
-        <v>1.46</v>
+        <v>0.34</v>
       </c>
       <c r="M10">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P10">
-        <v>1553.04</v>
+        <v>1549.44</v>
       </c>
       <c r="Q10">
-        <v>1573.89</v>
+        <v>1572.49</v>
       </c>
       <c r="R10">
-        <v>1592.18</v>
+        <v>1593.07</v>
       </c>
       <c r="S10">
-        <v>1518.95</v>
+        <v>1518.81</v>
       </c>
       <c r="T10">
-        <v>2.51</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1872,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>46.84</v>
+        <v>44.04</v>
       </c>
       <c r="Z10">
-        <v>-11.13</v>
+        <v>-11.63</v>
       </c>
       <c r="AA10">
-        <v>-9.32</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AB10">
-        <v>-1.81</v>
+        <v>-1.84</v>
       </c>
       <c r="AC10">
-        <v>63.88</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="AD10">
-        <v>51.99</v>
+        <v>60.09</v>
       </c>
       <c r="AE10">
-        <v>38.85</v>
+        <v>38.44</v>
       </c>
       <c r="AF10">
-        <v>-55.93</v>
+        <v>-8.56</v>
       </c>
       <c r="AG10">
-        <v>1647.92</v>
+        <v>1647.79</v>
       </c>
       <c r="AH10">
-        <v>1499.85</v>
+        <v>1497.18</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1908,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>18.8</v>
+        <v>17.42</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.61</v>
+        <v>-3.79</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.79</v>
+        <v>-1.77</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.18</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.78</v>
+        <v>-11.1</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.32</v>
+        <v>-13.37</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.65</v>
+        <v>-7.95</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.3</v>
+        <v>-10.89</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-5.46</v>
+        <v>-5.95</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.95</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.49</v>
+        <v>-6.02</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2174,13 +2174,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.21</v>
+        <v>3.34</v>
       </c>
       <c r="D11" s="5">
-        <v>3.34</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.55</v>
+        <v>5.09</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>9.970000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="D12" s="5">
-        <v>10.71</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.74</v>
+        <v>11.31</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-10.24</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="D13" s="5">
-        <v>-8.890000000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.35</v>
+        <v>-8.85</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2225,13 +2225,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.39</v>
+        <v>0.01</v>
       </c>
       <c r="D14" s="5">
-        <v>0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="E14" s="7">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2242,13 +2242,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.05</v>
+        <v>-1.7</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.7</v>
+        <v>-3.56</v>
       </c>
       <c r="E15" s="7">
-        <v>0.35</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2259,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>4.16</v>
+        <v>2.24</v>
       </c>
       <c r="D16" s="5">
-        <v>2.24</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.92</v>
+        <v>0.84</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>0.5</v>
+        <v>-1.14</v>
       </c>
       <c r="D17" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.64</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>2.95</v>
+        <v>1.03</v>
       </c>
       <c r="D18" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.92</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="D19" s="5">
-        <v>3.62</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.18</v>
+        <v>-2.69</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-6.31</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>3.37</v>
+        <v>7.69</v>
       </c>
       <c r="D20" s="5">
-        <v>7.69</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4.32</v>
+        <v>7.83</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-0.53</v>
+        <v>1.41</v>
       </c>
       <c r="D21" s="5">
-        <v>1.41</v>
+        <v>-1.62</v>
       </c>
       <c r="E21" s="7">
-        <v>1.94</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>3.47</v>
+        <v>4.07</v>
       </c>
       <c r="D22" s="5">
-        <v>4.07</v>
+        <v>2.33</v>
       </c>
       <c r="E22" s="7">
-        <v>0.6</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>-0.37</v>
+        <v>0.98</v>
       </c>
       <c r="D23" s="5">
-        <v>0.98</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" s="7">
-        <v>1.35</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>-1.54</v>
+        <v>-0.06</v>
       </c>
       <c r="D24" s="5">
-        <v>-0.06</v>
+        <v>-1.15</v>
       </c>
       <c r="E24" s="7">
-        <v>1.48</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-5.63</v>
+        <v>-9.92</v>
       </c>
       <c r="D25" s="5">
-        <v>-9.92</v>
+        <v>-9.43</v>
       </c>
       <c r="E25" s="6">
-        <v>-4.29</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>-16.2</v>
+        <v>-16.67</v>
       </c>
       <c r="D26" s="5">
-        <v>-16.67</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.47</v>
+        <v>-16.97</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>24.96</v>
+        <v>21.91</v>
       </c>
       <c r="D27" s="5">
-        <v>21.91</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-3.05</v>
+        <v>17.39</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-4.52</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>-6.23</v>
+        <v>-7.23</v>
       </c>
       <c r="D28" s="5">
-        <v>-7.23</v>
+        <v>-6.71</v>
       </c>
       <c r="E28" s="6">
-        <v>-1</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>12.62</v>
+        <v>15.9</v>
       </c>
       <c r="D29" s="5">
-        <v>15.9</v>
+        <v>15.76</v>
       </c>
       <c r="E29" s="7">
-        <v>3.28</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>10.47</v>
+        <v>11.57</v>
       </c>
       <c r="D30" s="5">
-        <v>11.57</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.1</v>
+        <v>12.31</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.74</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2514,545 +2514,545 @@
         <v>11</v>
       </c>
       <c r="C31" s="5">
-        <v>-44.14</v>
+        <v>-44.38</v>
       </c>
       <c r="D31" s="5">
-        <v>-44.38</v>
+        <v>-44.25</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.24</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="5">
-        <v>-20.21</v>
+        <v>1.46</v>
       </c>
       <c r="D32" s="5">
-        <v>-19.86</v>
+        <v>0.34</v>
       </c>
       <c r="E32" s="7">
-        <v>0.35</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>1.33</v>
+        <v>-18.24</v>
       </c>
       <c r="D33" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.13</v>
+        <v>-17.47</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.77</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-16.72</v>
+        <v>-0.96</v>
       </c>
       <c r="D34" s="5">
-        <v>-18.24</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.52</v>
+        <v>-6.27</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-5.31</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>0.24</v>
+        <v>12.14</v>
       </c>
       <c r="D35" s="5">
-        <v>-0.96</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1.2</v>
+        <v>3.45</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-8.69</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>21</v>
+        <v>-1.26</v>
       </c>
       <c r="D36" s="5">
-        <v>12.14</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-8.859999999999999</v>
+        <v>-2.03</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-0.28</v>
+        <v>10.4</v>
       </c>
       <c r="D37" s="5">
-        <v>-1.26</v>
+        <v>14.14</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.98</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>4.35</v>
+        <v>8.32</v>
       </c>
       <c r="D38" s="5">
-        <v>10.4</v>
-      </c>
-      <c r="E38" s="7">
-        <v>6.05</v>
+        <v>12.75</v>
+      </c>
+      <c r="E38" s="6">
+        <v>4.43</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>7.43</v>
+        <v>-15.92</v>
       </c>
       <c r="D39" s="5">
-        <v>8.32</v>
+        <v>-16.81</v>
       </c>
       <c r="E39" s="7">
-        <v>0.89</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>-17.1</v>
+        <v>-9.83</v>
       </c>
       <c r="D40" s="5">
-        <v>-15.92</v>
+        <v>-10.25</v>
       </c>
       <c r="E40" s="7">
-        <v>1.18</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>-9.220000000000001</v>
+        <v>6.53</v>
       </c>
       <c r="D41" s="5">
-        <v>-9.83</v>
+        <v>7.37</v>
       </c>
       <c r="E41" s="6">
-        <v>-0.61</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>9.609999999999999</v>
+        <v>-21.62</v>
       </c>
       <c r="D42" s="5">
-        <v>6.53</v>
+        <v>-20.65</v>
       </c>
       <c r="E42" s="6">
-        <v>-3.08</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-20.32</v>
+        <v>-20.18</v>
       </c>
       <c r="D43" s="5">
-        <v>-21.62</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.3</v>
+        <v>-21.56</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-19.93</v>
+        <v>-15.45</v>
       </c>
       <c r="D44" s="5">
-        <v>-20.18</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.25</v>
+        <v>-17.56</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-14.53</v>
+        <v>-15.44</v>
       </c>
       <c r="D45" s="5">
-        <v>-15.45</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.92</v>
+        <v>-16.08</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-14.86</v>
+        <v>-5.91</v>
       </c>
       <c r="D46" s="5">
-        <v>-15.44</v>
+        <v>-5.12</v>
       </c>
       <c r="E46" s="6">
-        <v>-0.58</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="5">
-        <v>-9.58</v>
+        <v>-3.59</v>
       </c>
       <c r="D47" s="5">
-        <v>-5.91</v>
-      </c>
-      <c r="E47" s="7">
-        <v>3.67</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="5">
-        <v>-4.33</v>
+        <v>-44.14</v>
       </c>
       <c r="D48" s="5">
-        <v>-3.59</v>
+        <v>-44.6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.74</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="5">
-        <v>-45.02</v>
+        <v>-20.86</v>
       </c>
       <c r="D49" s="5">
-        <v>-44.14</v>
+        <v>-21.1</v>
       </c>
       <c r="E49" s="7">
-        <v>0.88</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="5">
-        <v>-20.93</v>
+        <v>-11.95</v>
       </c>
       <c r="D50" s="5">
-        <v>-20.86</v>
+        <v>-12.75</v>
       </c>
       <c r="E50" s="7">
-        <v>0.07000000000000001</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>-12.26</v>
+        <v>384.2</v>
       </c>
       <c r="D51" s="5">
-        <v>-11.95</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.31</v>
+        <v>388.95</v>
+      </c>
+      <c r="E51" s="6">
+        <v>4.75</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>390.6</v>
+        <v>3035</v>
       </c>
       <c r="D52" s="5">
-        <v>384.2</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-6.4</v>
+        <v>2982.7</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-52.3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3044.5</v>
+        <v>348.6</v>
       </c>
       <c r="D53" s="5">
-        <v>3035</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-9.5</v>
+        <v>339.9</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>352.4</v>
+        <v>356.6</v>
       </c>
       <c r="D54" s="5">
-        <v>348.6</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-3.8</v>
+        <v>353.9</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="5">
-        <v>359.05</v>
+        <v>416.55</v>
       </c>
       <c r="D55" s="5">
-        <v>356.6</v>
+        <v>420.05</v>
       </c>
       <c r="E55" s="6">
-        <v>-2.45</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="5">
-        <v>400.3</v>
+        <v>702.75</v>
       </c>
       <c r="D56" s="5">
-        <v>416.55</v>
-      </c>
-      <c r="E56" s="7">
-        <v>16.25</v>
+        <v>708.55</v>
+      </c>
+      <c r="E56" s="6">
+        <v>5.8</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="5">
-        <v>697.35</v>
+        <v>201.39</v>
       </c>
       <c r="D57" s="5">
-        <v>702.75</v>
+        <v>199.71</v>
       </c>
       <c r="E57" s="7">
-        <v>5.4</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="5">
-        <v>199.07</v>
+        <v>3559.3</v>
       </c>
       <c r="D58" s="5">
-        <v>201.39</v>
+        <v>3548.6</v>
       </c>
       <c r="E58" s="7">
-        <v>2.32</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="5">
-        <v>3556</v>
+        <v>1557</v>
       </c>
       <c r="D59" s="5">
-        <v>3559.3</v>
+        <v>1543</v>
       </c>
       <c r="E59" s="7">
-        <v>3.3</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="5">
+        <v>23</v>
+      </c>
+      <c r="D60" s="5">
         <v>45</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1551.6</v>
-      </c>
-      <c r="D60" s="5">
-        <v>1557</v>
-      </c>
-      <c r="E60" s="7">
-        <v>5.4</v>
+      <c r="E60" s="6">
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="5">
+        <v>45</v>
+      </c>
+      <c r="D61" s="5">
         <v>34</v>
       </c>
-      <c r="D61" s="5">
-        <v>23</v>
-      </c>
-      <c r="E61" s="6">
+      <c r="E61" s="7">
         <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="5">
+        <v>99</v>
+      </c>
+      <c r="D62" s="5">
         <v>77</v>
       </c>
-      <c r="D62" s="5">
-        <v>88</v>
-      </c>
       <c r="E62" s="7">
-        <v>11</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>13</v>
@@ -3061,333 +3061,350 @@
         <v>88</v>
       </c>
       <c r="D63" s="5">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="E63" s="6">
-        <v>-11</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="5">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D64" s="5">
-        <v>34</v>
-      </c>
-      <c r="E64" s="7">
+        <v>88</v>
+      </c>
+      <c r="E64" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="5">
-        <v>46.99</v>
+        <v>34</v>
       </c>
       <c r="D65" s="5">
-        <v>41.08</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-5.91</v>
+        <v>23</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="5">
-        <v>30.18</v>
+        <v>41.08</v>
       </c>
       <c r="D66" s="5">
-        <v>29.39</v>
+        <v>46.46</v>
       </c>
       <c r="E66" s="6">
-        <v>-0.79</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="5">
-        <v>40.65</v>
+        <v>29.39</v>
       </c>
       <c r="D67" s="5">
-        <v>38.36</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-2.29</v>
+        <v>25.45</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-3.94</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="5">
-        <v>45.35</v>
+        <v>38.36</v>
       </c>
       <c r="D68" s="5">
-        <v>43.67</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-1.68</v>
+        <v>33.69</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-4.67</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="5">
-        <v>52.54</v>
+        <v>43.67</v>
       </c>
       <c r="D69" s="5">
-        <v>63.85</v>
+        <v>41.83</v>
       </c>
       <c r="E69" s="7">
-        <v>11.31</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="5">
-        <v>58.23</v>
+        <v>63.85</v>
       </c>
       <c r="D70" s="5">
-        <v>59.61</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.38</v>
+        <v>65.75</v>
+      </c>
+      <c r="E70" s="6">
+        <v>1.9</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="5">
-        <v>37.06</v>
+        <v>59.61</v>
       </c>
       <c r="D71" s="5">
-        <v>41.56</v>
-      </c>
-      <c r="E71" s="7">
-        <v>4.5</v>
+        <v>61.09</v>
+      </c>
+      <c r="E71" s="6">
+        <v>1.48</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="5">
-        <v>46.16</v>
+        <v>41.56</v>
       </c>
       <c r="D72" s="5">
-        <v>46.64</v>
+        <v>39.37</v>
       </c>
       <c r="E72" s="7">
-        <v>0.48</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="5">
-        <v>45.6</v>
+        <v>46.64</v>
       </c>
       <c r="D73" s="5">
-        <v>46.84</v>
+        <v>45.24</v>
       </c>
       <c r="E73" s="7">
-        <v>1.24</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="5">
-        <v>-32.58</v>
+        <v>46.84</v>
       </c>
       <c r="D74" s="5">
-        <v>167.41</v>
+        <v>44.04</v>
       </c>
       <c r="E74" s="7">
-        <v>199.99</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="5">
-        <v>-6.65</v>
+        <v>167.41</v>
       </c>
       <c r="D75" s="5">
-        <v>42.19</v>
+        <v>-25.5</v>
       </c>
       <c r="E75" s="7">
-        <v>48.84</v>
+        <v>-192.91</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="5">
-        <v>-5.26</v>
+        <v>42.19</v>
       </c>
       <c r="D76" s="5">
-        <v>-63.72</v>
-      </c>
-      <c r="E76" s="6">
-        <v>-58.46</v>
+        <v>0.34</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-41.85</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="5">
-        <v>-23.5</v>
+        <v>-63.72</v>
       </c>
       <c r="D77" s="5">
-        <v>-1.17</v>
-      </c>
-      <c r="E77" s="7">
-        <v>22.33</v>
+        <v>1.56</v>
+      </c>
+      <c r="E77" s="6">
+        <v>65.28</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="5">
-        <v>-36.67</v>
+        <v>-1.17</v>
       </c>
       <c r="D78" s="5">
-        <v>287.74</v>
+        <v>-21.2</v>
       </c>
       <c r="E78" s="7">
-        <v>324.41</v>
+        <v>-20.03</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="5">
-        <v>-77.27</v>
+        <v>287.74</v>
       </c>
       <c r="D79" s="5">
-        <v>-2.82</v>
-      </c>
-      <c r="E79" s="7">
-        <v>74.45</v>
+        <v>305.36</v>
+      </c>
+      <c r="E79" s="6">
+        <v>17.62</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="5">
-        <v>-68.94</v>
+        <v>-2.82</v>
       </c>
       <c r="D80" s="5">
-        <v>-3.52</v>
+        <v>-49.73</v>
       </c>
       <c r="E80" s="7">
-        <v>65.42</v>
+        <v>-46.91</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="5">
-        <v>-36.13</v>
+        <v>-3.52</v>
       </c>
       <c r="D81" s="5">
-        <v>-41.45</v>
-      </c>
-      <c r="E81" s="6">
-        <v>-5.32</v>
+        <v>-62.85</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-59.33</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="5">
-        <v>-47.9</v>
+        <v>-41.45</v>
       </c>
       <c r="D82" s="5">
+        <v>-0.34</v>
+      </c>
+      <c r="E82" s="6">
+        <v>41.11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="5">
         <v>-55.93</v>
       </c>
-      <c r="E82" s="6">
-        <v>-8.029999999999999</v>
+      <c r="D83" s="5">
+        <v>-8.56</v>
+      </c>
+      <c r="E83" s="6">
+        <v>47.37</v>
       </c>
     </row>
   </sheetData>
@@ -3446,22 +3463,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="10">
-        <v>48.16</v>
+        <v>44.16</v>
       </c>
       <c r="C2" s="11">
         <v>9</v>
       </c>
       <c r="D2" s="10">
-        <v>45.7</v>
+        <v>44.8</v>
       </c>
       <c r="E2" s="10">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.8</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="H2" s="10">
         <v>55.4</v>
@@ -3598,31 +3615,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13">
-        <v>0.3615</v>
+        <v>0.365</v>
       </c>
       <c r="B2" s="13">
-        <v>0.3292</v>
+        <v>0.3173</v>
       </c>
       <c r="C2" s="13">
-        <v>0.2029</v>
+        <v>0.2054</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1535</v>
+        <v>0.1515</v>
       </c>
       <c r="E2" s="13">
-        <v>0.1188</v>
+        <v>0.1254</v>
       </c>
       <c r="F2" s="13">
-        <v>0.05400000000000001</v>
+        <v>0.0481</v>
       </c>
       <c r="G2" s="13">
-        <v>0.0349</v>
+        <v>0.034</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.035</v>
+        <v>-0.0355</v>
       </c>
       <c r="I2" s="13">
-        <v>-0.1017</v>
+        <v>-0.09949999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.8% → -1.8%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.8%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.4 → 34.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.4</t>
+  </si>
+  <si>
+    <t>34.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,14 +422,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -902,10 +945,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>388.95</v>
+        <v>390.8</v>
       </c>
       <c r="D2">
-        <v>1.24</v>
+        <v>0.48</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +957,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-20.65</v>
+        <v>-20.28</v>
       </c>
       <c r="H2">
-        <v>3.72</v>
+        <v>4.21</v>
       </c>
       <c r="I2">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J2">
-        <v>-1.77</v>
+        <v>-1.56</v>
       </c>
       <c r="K2">
-        <v>-17.47</v>
+        <v>-14.84</v>
       </c>
       <c r="L2">
-        <v>-9.43</v>
+        <v>-10.59</v>
       </c>
       <c r="M2">
-        <v>12.54</v>
+        <v>12.41</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>389.21</v>
+        <v>389.94</v>
       </c>
       <c r="Q2">
-        <v>385.66</v>
+        <v>385.48</v>
       </c>
       <c r="R2">
-        <v>406.12</v>
+        <v>404.49</v>
       </c>
       <c r="S2">
-        <v>434.41</v>
+        <v>434.37</v>
       </c>
       <c r="T2">
-        <v>-10.47</v>
+        <v>-10.03</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +1011,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.46</v>
+        <v>48.43</v>
       </c>
       <c r="Z2">
-        <v>-5.16</v>
+        <v>-4.45</v>
       </c>
       <c r="AA2">
-        <v>-7.52</v>
+        <v>-6.9</v>
       </c>
       <c r="AB2">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AC2">
-        <v>77.59</v>
+        <v>79.12</v>
       </c>
       <c r="AD2">
-        <v>85.25</v>
+        <v>80.02</v>
       </c>
       <c r="AE2">
-        <v>9.59</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AF2">
-        <v>-25.5</v>
+        <v>-27.52</v>
       </c>
       <c r="AG2">
-        <v>396.65</v>
+        <v>395.95</v>
       </c>
       <c r="AH2">
-        <v>374.68</v>
+        <v>375.01</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1004,7 +1047,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>34.32</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1058,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2982.7</v>
+        <v>3035</v>
       </c>
       <c r="D3">
-        <v>-1.72</v>
+        <v>1.75</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1070,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-21.56</v>
+        <v>-20.18</v>
       </c>
       <c r="H3">
-        <v>1.76</v>
+        <v>3.54</v>
       </c>
       <c r="I3">
-        <v>-3.05</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J3">
-        <v>-13.37</v>
+        <v>-10.69</v>
       </c>
       <c r="K3">
-        <v>-6.27</v>
+        <v>-1.88</v>
       </c>
       <c r="L3">
-        <v>-16.97</v>
+        <v>-15.34</v>
       </c>
       <c r="M3">
-        <v>31.73</v>
+        <v>31.18</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P3">
-        <v>3033.9</v>
+        <v>3030.5</v>
       </c>
       <c r="Q3">
-        <v>3138.07</v>
+        <v>3123.32</v>
       </c>
       <c r="R3">
-        <v>3263.74</v>
+        <v>3262.09</v>
       </c>
       <c r="S3">
-        <v>3293.1</v>
+        <v>3289.87</v>
       </c>
       <c r="T3">
-        <v>-9.43</v>
+        <v>-7.75</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1124,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>25.45</v>
+        <v>34.86</v>
       </c>
       <c r="Z3">
-        <v>-78.04000000000001</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="AA3">
-        <v>-66.81</v>
+        <v>-68.59999999999999</v>
       </c>
       <c r="AB3">
-        <v>-11.23</v>
+        <v>-7.16</v>
       </c>
       <c r="AC3">
-        <v>36.52</v>
+        <v>51.59</v>
       </c>
       <c r="AD3">
-        <v>42.47</v>
+        <v>45.28</v>
       </c>
       <c r="AE3">
-        <v>61</v>
+        <v>62.36</v>
       </c>
       <c r="AF3">
-        <v>0.34</v>
+        <v>7.46</v>
       </c>
       <c r="AG3">
-        <v>3340.52</v>
+        <v>3309.19</v>
       </c>
       <c r="AH3">
-        <v>2935.61</v>
+        <v>2937.44</v>
       </c>
       <c r="AI3">
-        <v>3193.85</v>
+        <v>3192.07</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>70.72</v>
+        <v>72.29000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1171,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>339.9</v>
+        <v>333.1</v>
       </c>
       <c r="D4">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,25 +1183,25 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-17.56</v>
+        <v>-19.21</v>
       </c>
       <c r="H4">
-        <v>24.53</v>
+        <v>22.04</v>
       </c>
       <c r="I4">
-        <v>-1.68</v>
+        <v>-5.72</v>
       </c>
       <c r="J4">
-        <v>-10.89</v>
+        <v>-13.56</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>5.61</v>
       </c>
       <c r="L4">
-        <v>17.39</v>
+        <v>14.76</v>
       </c>
       <c r="M4">
-        <v>15.15</v>
+        <v>14.8</v>
       </c>
       <c r="N4">
         <v>77</v>
@@ -1167,19 +1210,19 @@
         <v>69</v>
       </c>
       <c r="P4">
-        <v>349.78</v>
+        <v>345.74</v>
       </c>
       <c r="Q4">
-        <v>361.18</v>
+        <v>358.67</v>
       </c>
       <c r="R4">
-        <v>372.46</v>
+        <v>372.69</v>
       </c>
       <c r="S4">
-        <v>344.09</v>
+        <v>343.99</v>
       </c>
       <c r="T4">
-        <v>-1.22</v>
+        <v>-3.17</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,43 +1237,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>33.69</v>
+        <v>30.56</v>
       </c>
       <c r="Z4">
-        <v>-7.9</v>
+        <v>-8.93</v>
       </c>
       <c r="AA4">
-        <v>-5.98</v>
+        <v>-6.57</v>
       </c>
       <c r="AB4">
-        <v>-1.92</v>
+        <v>-2.36</v>
       </c>
       <c r="AC4">
-        <v>34.46</v>
+        <v>17.46</v>
       </c>
       <c r="AD4">
-        <v>45.95</v>
+        <v>33.77</v>
       </c>
       <c r="AE4">
-        <v>10.8</v>
+        <v>10.83</v>
       </c>
       <c r="AF4">
-        <v>1.56</v>
+        <v>-7.69</v>
       </c>
       <c r="AG4">
-        <v>387.53</v>
+        <v>385.69</v>
       </c>
       <c r="AH4">
-        <v>334.84</v>
+        <v>331.65</v>
       </c>
       <c r="AI4">
-        <v>371.29</v>
+        <v>368.31</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>27.91</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1284,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>353.9</v>
+        <v>356.85</v>
       </c>
       <c r="D5">
-        <v>-0.76</v>
+        <v>0.83</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1296,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.08</v>
+        <v>-15.38</v>
       </c>
       <c r="H5">
-        <v>20.27</v>
+        <v>21.27</v>
       </c>
       <c r="I5">
-        <v>-2.69</v>
+        <v>-2.61</v>
       </c>
       <c r="J5">
-        <v>-6.02</v>
+        <v>-3.88</v>
       </c>
       <c r="K5">
-        <v>-2.03</v>
+        <v>-2.78</v>
       </c>
       <c r="L5">
-        <v>-6.71</v>
+        <v>-4.48</v>
       </c>
       <c r="M5">
-        <v>4.81</v>
+        <v>5.62</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>359.72</v>
+        <v>357.81</v>
       </c>
       <c r="Q5">
-        <v>360.24</v>
+        <v>359.65</v>
       </c>
       <c r="R5">
-        <v>373.02</v>
+        <v>372.61</v>
       </c>
       <c r="S5">
-        <v>360.23</v>
+        <v>360.04</v>
       </c>
       <c r="T5">
-        <v>-1.76</v>
+        <v>-0.89</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1350,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.83</v>
+        <v>44.57</v>
       </c>
       <c r="Z5">
-        <v>-4.42</v>
+        <v>-4.26</v>
       </c>
       <c r="AA5">
-        <v>-4.61</v>
+        <v>-4.54</v>
       </c>
       <c r="AB5">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="AC5">
-        <v>65.94</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AD5">
-        <v>76.26000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="AE5">
-        <v>11.73</v>
+        <v>11.71</v>
       </c>
       <c r="AF5">
-        <v>-21.2</v>
+        <v>79.8</v>
       </c>
       <c r="AG5">
-        <v>374.29</v>
+        <v>373.19</v>
       </c>
       <c r="AH5">
-        <v>346.19</v>
+        <v>346.1</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1343,7 +1386,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>27.1</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1397,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>420.05</v>
+        <v>420.25</v>
       </c>
       <c r="D6">
-        <v>0.84</v>
+        <v>0.05</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1409,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-5.12</v>
+        <v>-5.07</v>
       </c>
       <c r="H6">
-        <v>50.26</v>
+        <v>50.33</v>
       </c>
       <c r="I6">
-        <v>7.83</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>5.09</v>
+        <v>5.22</v>
       </c>
       <c r="K6">
-        <v>14.14</v>
+        <v>12.85</v>
       </c>
       <c r="L6">
-        <v>15.76</v>
+        <v>15.42</v>
       </c>
       <c r="M6">
-        <v>-9.949999999999999</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O6">
         <v>76</v>
       </c>
       <c r="P6">
-        <v>405.79</v>
+        <v>411.29</v>
       </c>
       <c r="Q6">
-        <v>398.24</v>
+        <v>399.67</v>
       </c>
       <c r="R6">
-        <v>402.38</v>
+        <v>403.02</v>
       </c>
       <c r="S6">
-        <v>373.01</v>
+        <v>373.58</v>
       </c>
       <c r="T6">
-        <v>12.61</v>
+        <v>12.49</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,43 +1463,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>65.75</v>
+        <v>65.86</v>
       </c>
       <c r="Z6">
-        <v>2.02</v>
+        <v>3.28</v>
       </c>
       <c r="AA6">
-        <v>-0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AB6">
-        <v>2.39</v>
+        <v>2.92</v>
       </c>
       <c r="AC6">
-        <v>90.19</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>76.56999999999999</v>
+        <v>90.02</v>
       </c>
       <c r="AE6">
-        <v>12.37</v>
+        <v>12.06</v>
       </c>
       <c r="AF6">
-        <v>305.36</v>
+        <v>213.95</v>
       </c>
       <c r="AG6">
-        <v>416.92</v>
+        <v>420.48</v>
       </c>
       <c r="AH6">
-        <v>379.55</v>
+        <v>378.86</v>
       </c>
       <c r="AI6">
-        <v>383.27</v>
+        <v>384.8</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>31.44</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1510,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>708.55</v>
+        <v>715.65</v>
       </c>
       <c r="D7">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1479,46 +1522,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-2.79</v>
+        <v>-1.82</v>
       </c>
       <c r="H7">
-        <v>39.91</v>
+        <v>41.31</v>
       </c>
       <c r="I7">
-        <v>-1.62</v>
+        <v>-0.26</v>
       </c>
       <c r="J7">
-        <v>11.31</v>
+        <v>12.43</v>
       </c>
       <c r="K7">
-        <v>12.75</v>
+        <v>15.54</v>
       </c>
       <c r="L7">
-        <v>12.31</v>
+        <v>16.56</v>
       </c>
       <c r="M7">
-        <v>36.5</v>
+        <v>36.69</v>
       </c>
       <c r="N7">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>706.63</v>
+        <v>706.25</v>
       </c>
       <c r="Q7">
-        <v>688.21</v>
+        <v>691.89</v>
       </c>
       <c r="R7">
-        <v>632.64</v>
+        <v>635.27</v>
       </c>
       <c r="S7">
-        <v>595.58</v>
+        <v>596.34</v>
       </c>
       <c r="T7">
-        <v>18.97</v>
+        <v>20.01</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1533,34 +1576,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>61.09</v>
+        <v>62.89</v>
       </c>
       <c r="Z7">
-        <v>21.68</v>
+        <v>21.39</v>
       </c>
       <c r="AA7">
-        <v>23.36</v>
+        <v>22.97</v>
       </c>
       <c r="AB7">
-        <v>-1.68</v>
+        <v>-1.58</v>
       </c>
       <c r="AC7">
-        <v>7.87</v>
+        <v>16.52</v>
       </c>
       <c r="AD7">
-        <v>7.93</v>
+        <v>9.49</v>
       </c>
       <c r="AE7">
-        <v>26.37</v>
+        <v>25.72</v>
       </c>
       <c r="AF7">
-        <v>-49.73</v>
+        <v>-54.18</v>
       </c>
       <c r="AG7">
-        <v>739.77</v>
+        <v>739.97</v>
       </c>
       <c r="AH7">
-        <v>636.66</v>
+        <v>643.8200000000001</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1569,7 +1612,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>45.77</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,58 +1623,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>199.71</v>
+        <v>200</v>
       </c>
       <c r="D8">
-        <v>-0.83</v>
+        <v>0.15</v>
       </c>
       <c r="E8">
-        <v>360.5</v>
+        <v>354.55</v>
       </c>
       <c r="F8">
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.6</v>
+        <v>-43.59</v>
       </c>
       <c r="H8">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I8">
-        <v>2.33</v>
+        <v>0.36</v>
       </c>
       <c r="J8">
-        <v>-8.85</v>
+        <v>-8.34</v>
       </c>
       <c r="K8">
-        <v>-16.81</v>
+        <v>-16.94</v>
       </c>
       <c r="L8">
-        <v>-44.25</v>
+        <v>-44.52</v>
       </c>
       <c r="M8">
-        <v>-3.55</v>
+        <v>-4.13</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>200.17</v>
+        <v>200.31</v>
       </c>
       <c r="Q8">
-        <v>202.41</v>
+        <v>201.85</v>
       </c>
       <c r="R8">
-        <v>214.76</v>
+        <v>214.16</v>
       </c>
       <c r="S8">
-        <v>252.33</v>
+        <v>251.78</v>
       </c>
       <c r="T8">
-        <v>-20.85</v>
+        <v>-20.57</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1689,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.37</v>
+        <v>39.96</v>
       </c>
       <c r="Z8">
-        <v>-5.17</v>
+        <v>-4.82</v>
       </c>
       <c r="AA8">
-        <v>-5.93</v>
+        <v>-5.71</v>
       </c>
       <c r="AB8">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AC8">
-        <v>92.06</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="AD8">
-        <v>94.27</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AE8">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="AF8">
-        <v>-62.85</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="AG8">
-        <v>214.35</v>
+        <v>213.08</v>
       </c>
       <c r="AH8">
-        <v>190.48</v>
+        <v>190.63</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1682,7 +1725,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>39.5</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1736,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3548.6</v>
+        <v>3545.7</v>
       </c>
       <c r="D9">
-        <v>-0.3</v>
+        <v>-0.08</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,46 +1748,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.1</v>
+        <v>-21.16</v>
       </c>
       <c r="H9">
-        <v>7.24</v>
+        <v>7.16</v>
       </c>
       <c r="I9">
-        <v>-0.12</v>
+        <v>-2.19</v>
       </c>
       <c r="J9">
         <v>-0.09</v>
       </c>
       <c r="K9">
-        <v>-10.25</v>
+        <v>-10.48</v>
       </c>
       <c r="L9">
-        <v>-19.86</v>
+        <v>-19.52</v>
       </c>
       <c r="M9">
-        <v>20.54</v>
+        <v>20.04</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="P9">
-        <v>3572.28</v>
+        <v>3556.4</v>
       </c>
       <c r="Q9">
-        <v>3568.19</v>
+        <v>3568.06</v>
       </c>
       <c r="R9">
-        <v>3590.81</v>
+        <v>3587.1</v>
       </c>
       <c r="S9">
-        <v>3676.27</v>
+        <v>3675.75</v>
       </c>
       <c r="T9">
-        <v>-3.47</v>
+        <v>-3.54</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1802,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.24</v>
+        <v>44.85</v>
       </c>
       <c r="Z9">
-        <v>-11.83</v>
+        <v>-12.66</v>
       </c>
       <c r="AA9">
-        <v>-13.05</v>
+        <v>-12.97</v>
       </c>
       <c r="AB9">
-        <v>1.22</v>
+        <v>0.32</v>
       </c>
       <c r="AC9">
-        <v>34.13</v>
+        <v>28.8</v>
       </c>
       <c r="AD9">
-        <v>44.86</v>
+        <v>35.08</v>
       </c>
       <c r="AE9">
-        <v>59.63</v>
+        <v>57.84</v>
       </c>
       <c r="AF9">
-        <v>-0.34</v>
+        <v>-43.31</v>
       </c>
       <c r="AG9">
-        <v>3633.8</v>
+        <v>3633.85</v>
       </c>
       <c r="AH9">
-        <v>3502.57</v>
+        <v>3502.26</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1795,7 +1838,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>19.34</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1849,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="D10">
-        <v>-0.9</v>
+        <v>0.32</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1861,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-12.75</v>
+        <v>-12.46</v>
       </c>
       <c r="H10">
-        <v>16.35</v>
+        <v>16.72</v>
       </c>
       <c r="I10">
-        <v>-1.15</v>
+        <v>0.71</v>
       </c>
       <c r="J10">
-        <v>-3.56</v>
+        <v>-1.46</v>
       </c>
       <c r="K10">
-        <v>7.37</v>
+        <v>7.96</v>
       </c>
       <c r="L10">
-        <v>0.34</v>
+        <v>3.91</v>
       </c>
       <c r="M10">
-        <v>3.4</v>
+        <v>4.17</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P10">
-        <v>1549.44</v>
+        <v>1551.62</v>
       </c>
       <c r="Q10">
-        <v>1572.49</v>
+        <v>1570.64</v>
       </c>
       <c r="R10">
-        <v>1593.07</v>
+        <v>1593.82</v>
       </c>
       <c r="S10">
-        <v>1518.81</v>
+        <v>1518.59</v>
       </c>
       <c r="T10">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1915,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>44.04</v>
+        <v>45.3</v>
       </c>
       <c r="Z10">
-        <v>-11.63</v>
+        <v>-11.49</v>
       </c>
       <c r="AA10">
-        <v>-9.779999999999999</v>
+        <v>-10.12</v>
       </c>
       <c r="AB10">
-        <v>-1.84</v>
+        <v>-1.36</v>
       </c>
       <c r="AC10">
-        <v>69.01000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="AD10">
-        <v>60.09</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="AE10">
-        <v>38.44</v>
+        <v>37.71</v>
       </c>
       <c r="AF10">
-        <v>-8.56</v>
+        <v>-50.07</v>
       </c>
       <c r="AG10">
-        <v>1647.79</v>
+        <v>1646.47</v>
       </c>
       <c r="AH10">
-        <v>1497.18</v>
+        <v>1494.8</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1908,7 +1951,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>17.42</v>
+        <v>16.1</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1348 +2112,1369 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-3.79</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-1.77</v>
       </c>
-      <c r="E7" s="6">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-1.56</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-13.37</v>
       </c>
-      <c r="E8" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-10.69</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-10.89</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-13.56</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-5.95</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-6.02</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-3.88</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>3.34</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>5.09</v>
       </c>
-      <c r="E11" s="6">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>5.22</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>10.71</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>11.31</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>12.43</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-8.890000000000001</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-8.85</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-8.34</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.56</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.46</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.05</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.68</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-5.72</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.61</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>7.83</v>
+      </c>
+      <c r="D20" s="6">
+        <v>7</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.62</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.26</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-0.09</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.12</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-2.19</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-1.7</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-3.56</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>2.24</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.84</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-9.43</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-10.59</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.05</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-16.97</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-15.34</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.68</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>17.39</v>
+      </c>
+      <c r="D27" s="6">
+        <v>14.76</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>3.62</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.69</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-6.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-6.71</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-4.48</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>7.69</v>
-      </c>
-      <c r="D20" s="5">
-        <v>7.83</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>15.76</v>
+      </c>
+      <c r="D29" s="6">
+        <v>15.42</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1.41</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.62</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>12.31</v>
+      </c>
+      <c r="D30" s="6">
+        <v>16.56</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>4.07</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2.33</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-44.25</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-44.52</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.12</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-19.86</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-19.52</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.91</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-17.47</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-14.84</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-6.27</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3.45</v>
+      </c>
+      <c r="D36" s="6">
+        <v>5.61</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-2.03</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-2.78</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>14.14</v>
+      </c>
+      <c r="D38" s="6">
+        <v>12.85</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>12.75</v>
+      </c>
+      <c r="D39" s="6">
+        <v>15.54</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-16.81</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-16.94</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-10.25</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-10.48</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>7.37</v>
+      </c>
+      <c r="D42" s="6">
+        <v>7.96</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-20.65</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-20.28</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-21.56</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-20.18</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-17.56</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-19.21</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-16.08</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-15.38</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-5.07</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-2.79</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-44.6</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-43.59</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-21.1</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-21.16</v>
+      </c>
+      <c r="E50" s="8">
         <v>-0.06</v>
       </c>
-      <c r="D24" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-12.75</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-12.46</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>388.95</v>
+      </c>
+      <c r="D52" s="6">
+        <v>390.8</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2982.7</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3035</v>
+      </c>
+      <c r="E53" s="7">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>339.9</v>
+      </c>
+      <c r="D54" s="6">
+        <v>333.1</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>353.9</v>
+      </c>
+      <c r="D55" s="6">
+        <v>356.85</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>420.05</v>
+      </c>
+      <c r="D56" s="6">
+        <v>420.25</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>708.55</v>
+      </c>
+      <c r="D57" s="6">
+        <v>715.65</v>
+      </c>
+      <c r="E57" s="7">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>199.71</v>
+      </c>
+      <c r="D58" s="6">
+        <v>200</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3548.6</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3545.7</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1543</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1548</v>
+      </c>
+      <c r="E60" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45</v>
+      </c>
+      <c r="D61" s="6">
+        <v>34</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>34</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45</v>
+      </c>
+      <c r="E62" s="7">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>-9.92</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-9.43</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>99</v>
+      </c>
+      <c r="D63" s="6">
+        <v>88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>88</v>
+      </c>
+      <c r="D64" s="6">
+        <v>99</v>
+      </c>
+      <c r="E64" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>46.46</v>
+      </c>
+      <c r="D65" s="6">
+        <v>48.43</v>
+      </c>
+      <c r="E65" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-16.67</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-16.97</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>25.45</v>
+      </c>
+      <c r="D66" s="6">
+        <v>34.86</v>
+      </c>
+      <c r="E66" s="7">
+        <v>9.41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>21.91</v>
-      </c>
-      <c r="D27" s="5">
-        <v>17.39</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-4.52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>33.69</v>
+      </c>
+      <c r="D67" s="6">
+        <v>30.56</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-7.23</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-6.71</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>41.83</v>
+      </c>
+      <c r="D68" s="6">
+        <v>44.57</v>
+      </c>
+      <c r="E68" s="7">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D29" s="5">
-        <v>15.76</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>65.75</v>
+      </c>
+      <c r="D69" s="6">
+        <v>65.86</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>11.57</v>
-      </c>
-      <c r="D30" s="5">
-        <v>12.31</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>61.09</v>
+      </c>
+      <c r="D70" s="6">
+        <v>62.89</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-44.38</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-44.25</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>39.37</v>
+      </c>
+      <c r="D71" s="6">
+        <v>39.96</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>45.24</v>
+      </c>
+      <c r="D72" s="6">
+        <v>44.85</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>44.04</v>
+      </c>
+      <c r="D73" s="6">
+        <v>45.3</v>
+      </c>
+      <c r="E73" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-25.5</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-27.52</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
         <v>0.34</v>
       </c>
-      <c r="E32" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-18.24</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-17.47</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-0.96</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-6.27</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-5.31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D75" s="6">
+        <v>7.46</v>
+      </c>
+      <c r="E75" s="7">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>12.14</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-8.69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-7.69</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-9.25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-1.26</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-2.03</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-21.2</v>
+      </c>
+      <c r="D77" s="6">
+        <v>79.8</v>
+      </c>
+      <c r="E77" s="7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>10.4</v>
-      </c>
-      <c r="D37" s="5">
-        <v>14.14</v>
-      </c>
-      <c r="E37" s="6">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>305.36</v>
+      </c>
+      <c r="D78" s="6">
+        <v>213.95</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-91.41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="D38" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="E38" s="6">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-49.73</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-54.18</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-4.45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-15.92</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-16.81</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-62.85</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-69.56999999999999</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-6.72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-9.83</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-10.25</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-0.34</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-43.31</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-42.97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>6.53</v>
-      </c>
-      <c r="D41" s="5">
-        <v>7.37</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-21.62</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-20.65</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-20.18</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-21.56</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-15.45</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-17.56</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-15.44</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-16.08</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-5.91</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-5.12</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-3.59</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-2.79</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-44.14</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-44.6</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-20.86</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-21.1</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-11.95</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-12.75</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>384.2</v>
-      </c>
-      <c r="D51" s="5">
-        <v>388.95</v>
-      </c>
-      <c r="E51" s="6">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>3035</v>
-      </c>
-      <c r="D52" s="5">
-        <v>2982.7</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-52.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>348.6</v>
-      </c>
-      <c r="D53" s="5">
-        <v>339.9</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-8.699999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>356.6</v>
-      </c>
-      <c r="D54" s="5">
-        <v>353.9</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>416.55</v>
-      </c>
-      <c r="D55" s="5">
-        <v>420.05</v>
-      </c>
-      <c r="E55" s="6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>702.75</v>
-      </c>
-      <c r="D56" s="5">
-        <v>708.55</v>
-      </c>
-      <c r="E56" s="6">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>201.39</v>
-      </c>
-      <c r="D57" s="5">
-        <v>199.71</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>3559.3</v>
-      </c>
-      <c r="D58" s="5">
-        <v>3548.6</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>1557</v>
-      </c>
-      <c r="D59" s="5">
-        <v>1543</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="5">
-        <v>23</v>
-      </c>
-      <c r="D60" s="5">
-        <v>45</v>
-      </c>
-      <c r="E60" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>45</v>
-      </c>
-      <c r="D61" s="5">
-        <v>34</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>99</v>
-      </c>
-      <c r="D62" s="5">
-        <v>77</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5">
-        <v>88</v>
-      </c>
-      <c r="D63" s="5">
-        <v>99</v>
-      </c>
-      <c r="E63" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="5">
-        <v>77</v>
-      </c>
-      <c r="D64" s="5">
-        <v>88</v>
-      </c>
-      <c r="E64" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="5">
-        <v>34</v>
-      </c>
-      <c r="D65" s="5">
-        <v>23</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>41.08</v>
-      </c>
-      <c r="D66" s="5">
-        <v>46.46</v>
-      </c>
-      <c r="E66" s="6">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>29.39</v>
-      </c>
-      <c r="D67" s="5">
-        <v>25.45</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>38.36</v>
-      </c>
-      <c r="D68" s="5">
-        <v>33.69</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-4.67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>43.67</v>
-      </c>
-      <c r="D69" s="5">
-        <v>41.83</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>63.85</v>
-      </c>
-      <c r="D70" s="5">
-        <v>65.75</v>
-      </c>
-      <c r="E70" s="6">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>59.61</v>
-      </c>
-      <c r="D71" s="5">
-        <v>61.09</v>
-      </c>
-      <c r="E71" s="6">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="5">
-        <v>41.56</v>
-      </c>
-      <c r="D72" s="5">
-        <v>39.37</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46.64</v>
-      </c>
-      <c r="D73" s="5">
-        <v>45.24</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="5">
-        <v>46.84</v>
-      </c>
-      <c r="D74" s="5">
-        <v>44.04</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="5">
-        <v>167.41</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-25.5</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-192.91</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>42.19</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.34</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-41.85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-63.72</v>
-      </c>
-      <c r="D77" s="5">
-        <v>1.56</v>
-      </c>
-      <c r="E77" s="6">
-        <v>65.28</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-1.17</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-21.2</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-20.03</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>287.74</v>
-      </c>
-      <c r="D79" s="5">
-        <v>305.36</v>
-      </c>
-      <c r="E79" s="6">
-        <v>17.62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-2.82</v>
-      </c>
-      <c r="D80" s="5">
-        <v>-49.73</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-46.91</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="5">
-        <v>-3.52</v>
-      </c>
-      <c r="D81" s="5">
-        <v>-62.85</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-59.33</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="5">
-        <v>-41.45</v>
-      </c>
-      <c r="D82" s="5">
-        <v>-0.34</v>
-      </c>
-      <c r="E82" s="6">
-        <v>41.11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="5">
-        <v>-55.93</v>
-      </c>
-      <c r="D83" s="5">
+      <c r="C82" s="6">
         <v>-8.56</v>
       </c>
-      <c r="E83" s="6">
-        <v>47.37</v>
+      <c r="D82" s="6">
+        <v>-50.07</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-41.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3430,60 +3494,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>44.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>44.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>46.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-3.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3585,61 +3649,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.365</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3173</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2054</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1515</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1254</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0481</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.034</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0355</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.09949999999999999</v>
+      <c r="A2" s="14">
+        <v>0.3669</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3118</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2004</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.148</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1241</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0562</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0417</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0413</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.09609999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,49 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.8% → -1.8%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.8%</t>
-  </si>
-  <si>
-    <t>-1.8%</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.4 → 34.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.4</t>
-  </si>
-  <si>
-    <t>34.9</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -346,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -945,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>390.8</v>
+        <v>383.35</v>
       </c>
       <c r="D2">
-        <v>0.48</v>
+        <v>-1.91</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -957,46 +914,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-20.28</v>
+        <v>-21.8</v>
       </c>
       <c r="H2">
-        <v>4.21</v>
+        <v>2.23</v>
       </c>
       <c r="I2">
-        <v>0.9399999999999999</v>
+        <v>-2.99</v>
       </c>
       <c r="J2">
-        <v>-1.56</v>
+        <v>-2.83</v>
       </c>
       <c r="K2">
-        <v>-14.84</v>
+        <v>-16.26</v>
       </c>
       <c r="L2">
-        <v>-10.59</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="M2">
-        <v>12.41</v>
+        <v>11.98</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>389.94</v>
+        <v>387.58</v>
       </c>
       <c r="Q2">
-        <v>385.48</v>
+        <v>385.15</v>
       </c>
       <c r="R2">
-        <v>404.49</v>
+        <v>402.68</v>
       </c>
       <c r="S2">
-        <v>434.37</v>
+        <v>434.27</v>
       </c>
       <c r="T2">
-        <v>-10.03</v>
+        <v>-11.73</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1011,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>48.43</v>
+        <v>41.76</v>
       </c>
       <c r="Z2">
-        <v>-4.45</v>
+        <v>-4.44</v>
       </c>
       <c r="AA2">
-        <v>-6.9</v>
+        <v>-6.41</v>
       </c>
       <c r="AB2">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="AC2">
-        <v>79.12</v>
+        <v>79.83</v>
       </c>
       <c r="AD2">
-        <v>80.02</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AE2">
-        <v>9.449999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AF2">
-        <v>-27.52</v>
+        <v>-33.23</v>
       </c>
       <c r="AG2">
-        <v>395.95</v>
+        <v>395.44</v>
       </c>
       <c r="AH2">
-        <v>375.01</v>
+        <v>374.86</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1047,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.07</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1058,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3035</v>
+        <v>2995</v>
       </c>
       <c r="D3">
-        <v>1.75</v>
+        <v>-1.32</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1070,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-20.18</v>
+        <v>-21.23</v>
       </c>
       <c r="H3">
-        <v>3.54</v>
+        <v>2.18</v>
       </c>
       <c r="I3">
-        <v>-0.5600000000000001</v>
+        <v>-1.97</v>
       </c>
       <c r="J3">
-        <v>-10.69</v>
+        <v>-10.06</v>
       </c>
       <c r="K3">
-        <v>-1.88</v>
+        <v>-2.4</v>
       </c>
       <c r="L3">
-        <v>-15.34</v>
+        <v>-17.14</v>
       </c>
       <c r="M3">
-        <v>31.18</v>
+        <v>30.96</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P3">
-        <v>3030.5</v>
+        <v>3018.44</v>
       </c>
       <c r="Q3">
-        <v>3123.32</v>
+        <v>3106.37</v>
       </c>
       <c r="R3">
-        <v>3262.09</v>
+        <v>3258.4</v>
       </c>
       <c r="S3">
-        <v>3289.87</v>
+        <v>3286.66</v>
       </c>
       <c r="T3">
-        <v>-7.75</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1124,43 +1081,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.86</v>
+        <v>31.58</v>
       </c>
       <c r="Z3">
-        <v>-75.76000000000001</v>
+        <v>-76.29000000000001</v>
       </c>
       <c r="AA3">
-        <v>-68.59999999999999</v>
+        <v>-70.14</v>
       </c>
       <c r="AB3">
-        <v>-7.16</v>
+        <v>-6.15</v>
       </c>
       <c r="AC3">
-        <v>51.59</v>
+        <v>58.54</v>
       </c>
       <c r="AD3">
-        <v>45.28</v>
+        <v>48.88</v>
       </c>
       <c r="AE3">
-        <v>62.36</v>
+        <v>62</v>
       </c>
       <c r="AF3">
-        <v>7.46</v>
+        <v>3.8</v>
       </c>
       <c r="AG3">
-        <v>3309.19</v>
+        <v>3272.08</v>
       </c>
       <c r="AH3">
-        <v>2937.44</v>
+        <v>2940.65</v>
       </c>
       <c r="AI3">
-        <v>3192.07</v>
+        <v>3184.76</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>72.29000000000001</v>
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1171,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>333.1</v>
+        <v>331.75</v>
       </c>
       <c r="D4">
-        <v>-2</v>
+        <v>-0.41</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1183,46 +1140,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-19.21</v>
+        <v>-19.54</v>
       </c>
       <c r="H4">
-        <v>22.04</v>
+        <v>21.54</v>
       </c>
       <c r="I4">
-        <v>-5.72</v>
+        <v>-6.47</v>
       </c>
       <c r="J4">
-        <v>-13.56</v>
+        <v>-13.46</v>
       </c>
       <c r="K4">
-        <v>5.61</v>
+        <v>5.05</v>
       </c>
       <c r="L4">
-        <v>14.76</v>
+        <v>17.31</v>
       </c>
       <c r="M4">
-        <v>14.8</v>
+        <v>14.87</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>345.74</v>
+        <v>341.15</v>
       </c>
       <c r="Q4">
-        <v>358.67</v>
+        <v>356.43</v>
       </c>
       <c r="R4">
-        <v>372.69</v>
+        <v>372.84</v>
       </c>
       <c r="S4">
-        <v>343.99</v>
+        <v>343.89</v>
       </c>
       <c r="T4">
-        <v>-3.17</v>
+        <v>-3.53</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1237,43 +1194,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>30.56</v>
+        <v>29.96</v>
       </c>
       <c r="Z4">
-        <v>-8.93</v>
+        <v>-9.75</v>
       </c>
       <c r="AA4">
-        <v>-6.57</v>
+        <v>-7.21</v>
       </c>
       <c r="AB4">
-        <v>-2.36</v>
+        <v>-2.54</v>
       </c>
       <c r="AC4">
-        <v>17.46</v>
+        <v>4.61</v>
       </c>
       <c r="AD4">
-        <v>33.77</v>
+        <v>18.84</v>
       </c>
       <c r="AE4">
-        <v>10.83</v>
+        <v>10.79</v>
       </c>
       <c r="AF4">
-        <v>-7.69</v>
+        <v>-57.17</v>
       </c>
       <c r="AG4">
-        <v>385.69</v>
+        <v>384.61</v>
       </c>
       <c r="AH4">
-        <v>331.65</v>
+        <v>328.25</v>
       </c>
       <c r="AI4">
-        <v>368.31</v>
+        <v>363.72</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>31.43</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1284,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>356.85</v>
+        <v>363.1</v>
       </c>
       <c r="D5">
-        <v>0.83</v>
+        <v>1.75</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1296,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-15.38</v>
+        <v>-13.9</v>
       </c>
       <c r="H5">
-        <v>21.27</v>
+        <v>23.4</v>
       </c>
       <c r="I5">
-        <v>-2.61</v>
+        <v>0.12</v>
       </c>
       <c r="J5">
-        <v>-3.88</v>
+        <v>-1.51</v>
       </c>
       <c r="K5">
-        <v>-2.78</v>
+        <v>-0.91</v>
       </c>
       <c r="L5">
-        <v>-4.48</v>
+        <v>-3.26</v>
       </c>
       <c r="M5">
-        <v>5.62</v>
+        <v>6.38</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>357.81</v>
+        <v>357.9</v>
       </c>
       <c r="Q5">
-        <v>359.65</v>
+        <v>359.42</v>
       </c>
       <c r="R5">
-        <v>372.61</v>
+        <v>372.41</v>
       </c>
       <c r="S5">
-        <v>360.04</v>
+        <v>359.83</v>
       </c>
       <c r="T5">
-        <v>-0.89</v>
+        <v>0.91</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1347,37 +1304,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>44.57</v>
+        <v>49.96</v>
       </c>
       <c r="Z5">
-        <v>-4.26</v>
+        <v>-3.59</v>
       </c>
       <c r="AA5">
-        <v>-4.54</v>
+        <v>-4.35</v>
       </c>
       <c r="AB5">
-        <v>0.28</v>
+        <v>0.76</v>
       </c>
       <c r="AC5">
-        <v>64.68000000000001</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AD5">
-        <v>68.8</v>
+        <v>68.53</v>
       </c>
       <c r="AE5">
-        <v>11.71</v>
+        <v>12.01</v>
       </c>
       <c r="AF5">
-        <v>79.8</v>
+        <v>45.95</v>
       </c>
       <c r="AG5">
-        <v>373.19</v>
+        <v>372.57</v>
       </c>
       <c r="AH5">
-        <v>346.1</v>
+        <v>346.28</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1386,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>25.75</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1397,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>420.25</v>
+        <v>421.8</v>
       </c>
       <c r="D6">
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1409,46 +1366,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-5.07</v>
+        <v>-4.72</v>
       </c>
       <c r="H6">
-        <v>50.33</v>
+        <v>50.89</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>5.63</v>
       </c>
       <c r="J6">
-        <v>5.22</v>
+        <v>7.71</v>
       </c>
       <c r="K6">
-        <v>12.85</v>
+        <v>12.81</v>
       </c>
       <c r="L6">
-        <v>15.42</v>
+        <v>17.44</v>
       </c>
       <c r="M6">
-        <v>-9.609999999999999</v>
+        <v>-9.76</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P6">
-        <v>411.29</v>
+        <v>415.79</v>
       </c>
       <c r="Q6">
-        <v>399.67</v>
+        <v>401.12</v>
       </c>
       <c r="R6">
-        <v>403.02</v>
+        <v>403.71</v>
       </c>
       <c r="S6">
-        <v>373.58</v>
+        <v>374.07</v>
       </c>
       <c r="T6">
-        <v>12.49</v>
+        <v>12.76</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1463,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>65.86</v>
+        <v>66.75</v>
       </c>
       <c r="Z6">
-        <v>3.28</v>
+        <v>4.35</v>
       </c>
       <c r="AA6">
-        <v>0.36</v>
+        <v>1.16</v>
       </c>
       <c r="AB6">
-        <v>2.92</v>
+        <v>3.19</v>
       </c>
       <c r="AC6">
         <v>100</v>
       </c>
       <c r="AD6">
-        <v>90.02</v>
+        <v>96.73</v>
       </c>
       <c r="AE6">
-        <v>12.06</v>
+        <v>12.43</v>
       </c>
       <c r="AF6">
-        <v>213.95</v>
+        <v>198.44</v>
       </c>
       <c r="AG6">
-        <v>420.48</v>
+        <v>423.87</v>
       </c>
       <c r="AH6">
-        <v>378.86</v>
+        <v>378.38</v>
       </c>
       <c r="AI6">
-        <v>384.8</v>
+        <v>387.98</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>35.29</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1510,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>715.65</v>
+        <v>714.35</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>-0.18</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1522,46 +1479,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-1.82</v>
+        <v>-2</v>
       </c>
       <c r="H7">
-        <v>41.31</v>
+        <v>41.05</v>
       </c>
       <c r="I7">
-        <v>-0.26</v>
+        <v>1.05</v>
       </c>
       <c r="J7">
-        <v>12.43</v>
+        <v>11.26</v>
       </c>
       <c r="K7">
-        <v>15.54</v>
+        <v>19.5</v>
       </c>
       <c r="L7">
-        <v>16.56</v>
+        <v>18.96</v>
       </c>
       <c r="M7">
-        <v>36.69</v>
+        <v>36.73</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P7">
-        <v>706.25</v>
+        <v>707.73</v>
       </c>
       <c r="Q7">
-        <v>691.89</v>
+        <v>694.52</v>
       </c>
       <c r="R7">
-        <v>635.27</v>
+        <v>637.95</v>
       </c>
       <c r="S7">
-        <v>596.34</v>
+        <v>597.15</v>
       </c>
       <c r="T7">
-        <v>20.01</v>
+        <v>19.63</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1576,34 +1533,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>62.89</v>
+        <v>62.33</v>
       </c>
       <c r="Z7">
-        <v>21.39</v>
+        <v>20.82</v>
       </c>
       <c r="AA7">
-        <v>22.97</v>
+        <v>22.54</v>
       </c>
       <c r="AB7">
-        <v>-1.58</v>
+        <v>-1.72</v>
       </c>
       <c r="AC7">
-        <v>16.52</v>
+        <v>21.56</v>
       </c>
       <c r="AD7">
-        <v>9.49</v>
+        <v>15.32</v>
       </c>
       <c r="AE7">
-        <v>25.72</v>
+        <v>25.02</v>
       </c>
       <c r="AF7">
-        <v>-54.18</v>
+        <v>-53.25</v>
       </c>
       <c r="AG7">
-        <v>739.97</v>
+        <v>741.39</v>
       </c>
       <c r="AH7">
-        <v>643.8200000000001</v>
+        <v>647.66</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1612,7 +1569,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>43.88</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1623,37 +1580,37 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>200</v>
+        <v>195.92</v>
       </c>
       <c r="D8">
-        <v>0.15</v>
+        <v>-2.04</v>
       </c>
       <c r="E8">
-        <v>354.55</v>
+        <v>354.1</v>
       </c>
       <c r="F8">
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-43.59</v>
+        <v>-44.67</v>
       </c>
       <c r="H8">
-        <v>3.95</v>
+        <v>1.83</v>
       </c>
       <c r="I8">
-        <v>0.36</v>
+        <v>-2.71</v>
       </c>
       <c r="J8">
-        <v>-8.34</v>
+        <v>-7.25</v>
       </c>
       <c r="K8">
-        <v>-16.94</v>
+        <v>-17.7</v>
       </c>
       <c r="L8">
-        <v>-44.52</v>
+        <v>-44.74</v>
       </c>
       <c r="M8">
-        <v>-4.13</v>
+        <v>-4.17</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1662,19 +1619,19 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>200.31</v>
+        <v>199.22</v>
       </c>
       <c r="Q8">
-        <v>201.85</v>
+        <v>201.08</v>
       </c>
       <c r="R8">
-        <v>214.16</v>
+        <v>213.59</v>
       </c>
       <c r="S8">
-        <v>251.78</v>
+        <v>251.21</v>
       </c>
       <c r="T8">
-        <v>-20.57</v>
+        <v>-22.01</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1689,34 +1646,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.96</v>
+        <v>34.83</v>
       </c>
       <c r="Z8">
         <v>-4.82</v>
       </c>
       <c r="AA8">
-        <v>-5.71</v>
+        <v>-5.53</v>
       </c>
       <c r="AB8">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="AC8">
-        <v>94.26000000000001</v>
+        <v>84.08</v>
       </c>
       <c r="AD8">
-        <v>93.90000000000001</v>
+        <v>90.13</v>
       </c>
       <c r="AE8">
-        <v>5.8</v>
+        <v>5.86</v>
       </c>
       <c r="AF8">
-        <v>-69.56999999999999</v>
+        <v>41.77</v>
       </c>
       <c r="AG8">
-        <v>213.08</v>
+        <v>211.65</v>
       </c>
       <c r="AH8">
-        <v>190.63</v>
+        <v>190.51</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1725,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>36.27</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1736,58 +1693,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3545.7</v>
+        <v>3552.5</v>
       </c>
       <c r="D9">
-        <v>-0.08</v>
+        <v>0.19</v>
       </c>
       <c r="E9">
-        <v>4497.5</v>
+        <v>4361.1</v>
       </c>
       <c r="F9">
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.16</v>
+        <v>-18.54</v>
       </c>
       <c r="H9">
-        <v>7.16</v>
+        <v>7.36</v>
       </c>
       <c r="I9">
-        <v>-2.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J9">
-        <v>-0.09</v>
+        <v>0.12</v>
       </c>
       <c r="K9">
-        <v>-10.48</v>
+        <v>-11.13</v>
       </c>
       <c r="L9">
-        <v>-19.52</v>
+        <v>-21.01</v>
       </c>
       <c r="M9">
-        <v>20.04</v>
+        <v>20.37</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="P9">
-        <v>3556.4</v>
+        <v>3552.42</v>
       </c>
       <c r="Q9">
-        <v>3568.06</v>
+        <v>3568.44</v>
       </c>
       <c r="R9">
-        <v>3587.1</v>
+        <v>3583.96</v>
       </c>
       <c r="S9">
-        <v>3675.75</v>
+        <v>3675.06</v>
       </c>
       <c r="T9">
-        <v>-3.54</v>
+        <v>-3.33</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1802,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.85</v>
+        <v>46.03</v>
       </c>
       <c r="Z9">
-        <v>-12.66</v>
+        <v>-12.62</v>
       </c>
       <c r="AA9">
-        <v>-12.97</v>
+        <v>-12.9</v>
       </c>
       <c r="AB9">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AC9">
-        <v>28.8</v>
+        <v>29.79</v>
       </c>
       <c r="AD9">
-        <v>35.08</v>
+        <v>30.9</v>
       </c>
       <c r="AE9">
-        <v>57.84</v>
+        <v>60.19</v>
       </c>
       <c r="AF9">
-        <v>-43.31</v>
+        <v>52.49</v>
       </c>
       <c r="AG9">
-        <v>3633.85</v>
+        <v>3633.75</v>
       </c>
       <c r="AH9">
-        <v>3502.26</v>
+        <v>3503.13</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1838,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>17.28</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1849,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1548</v>
+        <v>1542.2</v>
       </c>
       <c r="D10">
-        <v>0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1861,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-12.46</v>
+        <v>-12.79</v>
       </c>
       <c r="H10">
-        <v>16.72</v>
+        <v>16.29</v>
       </c>
       <c r="I10">
-        <v>0.71</v>
+        <v>-1.05</v>
       </c>
       <c r="J10">
-        <v>-1.46</v>
+        <v>-2.7</v>
       </c>
       <c r="K10">
-        <v>7.96</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L10">
-        <v>3.91</v>
+        <v>5.87</v>
       </c>
       <c r="M10">
-        <v>4.17</v>
+        <v>4.82</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="P10">
-        <v>1551.62</v>
+        <v>1548.36</v>
       </c>
       <c r="Q10">
-        <v>1570.64</v>
+        <v>1565.7</v>
       </c>
       <c r="R10">
-        <v>1593.82</v>
+        <v>1593.21</v>
       </c>
       <c r="S10">
-        <v>1518.59</v>
+        <v>1518.49</v>
       </c>
       <c r="T10">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1915,34 +1872,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>45.3</v>
+        <v>44.06</v>
       </c>
       <c r="Z10">
-        <v>-11.49</v>
+        <v>-11.71</v>
       </c>
       <c r="AA10">
-        <v>-10.12</v>
+        <v>-10.44</v>
       </c>
       <c r="AB10">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="AC10">
-        <v>75.83</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="AD10">
-        <v>69.56999999999999</v>
+        <v>71.86</v>
       </c>
       <c r="AE10">
-        <v>37.71</v>
+        <v>37.17</v>
       </c>
       <c r="AF10">
-        <v>-50.07</v>
+        <v>-31.77</v>
       </c>
       <c r="AG10">
-        <v>1646.47</v>
+        <v>1634.83</v>
       </c>
       <c r="AH10">
-        <v>1494.8</v>
+        <v>1496.57</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1951,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>16.1</v>
+        <v>14.62</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2112,1369 +2069,1263 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-1.56</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.83</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-10.69</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-10.06</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-13.56</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-13.46</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-3.88</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5.22</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7.71</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>12.43</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11.26</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-8.34</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-7.25</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.09</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.46</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-2.7</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-1.77</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.99</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-3.93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-13.37</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-10.69</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.97</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-10.89</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-13.56</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-5.72</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-6.47</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.88</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-2.61</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5.09</v>
-      </c>
-      <c r="D12" s="6">
-        <v>5.22</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5">
+        <v>5.63</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>11.31</v>
-      </c>
-      <c r="D13" s="6">
-        <v>12.43</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-0.26</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-8.85</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.34</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-2.71</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-2.19</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-1.05</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-10.59</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-15.34</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-17.14</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>14.76</v>
+      </c>
+      <c r="D27" s="5">
+        <v>17.31</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-4.48</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-3.26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>15.42</v>
+      </c>
+      <c r="D29" s="5">
+        <v>17.44</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>16.56</v>
+      </c>
+      <c r="D30" s="5">
+        <v>18.96</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-44.52</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-44.74</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-19.52</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-21.01</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>3.91</v>
+      </c>
+      <c r="D33" s="5">
+        <v>5.87</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-14.84</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-16.26</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-1.88</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-2.4</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>5.61</v>
+      </c>
+      <c r="D36" s="5">
+        <v>5.05</v>
+      </c>
+      <c r="E36" s="6">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="E17" s="7">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>12.85</v>
+      </c>
+      <c r="D38" s="5">
+        <v>12.81</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>15.54</v>
+      </c>
+      <c r="D39" s="5">
+        <v>19.5</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-16.94</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-17.7</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-10.48</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-11.13</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>7.96</v>
+      </c>
+      <c r="D42" s="5">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-20.28</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-21.8</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-20.18</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-21.23</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.68</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-4.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-19.21</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-19.54</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-15.38</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-13.9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>7.83</v>
-      </c>
-      <c r="D20" s="6">
-        <v>7</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-5.07</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-4.72</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-1.82</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-2</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2.33</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-43.59</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-44.67</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.12</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-2.19</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-21.16</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-18.54</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.71</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-12.46</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-12.79</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-9.43</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-10.59</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>390.8</v>
+      </c>
+      <c r="D52" s="5">
+        <v>383.35</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-7.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-16.97</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-15.34</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3035</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2995</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>17.39</v>
-      </c>
-      <c r="D27" s="6">
-        <v>14.76</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>333.1</v>
+      </c>
+      <c r="D54" s="5">
+        <v>331.75</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-6.71</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-4.48</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>356.85</v>
+      </c>
+      <c r="D55" s="5">
+        <v>363.1</v>
+      </c>
+      <c r="E55" s="7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>15.76</v>
-      </c>
-      <c r="D29" s="6">
-        <v>15.42</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>420.25</v>
+      </c>
+      <c r="D56" s="5">
+        <v>421.8</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>12.31</v>
-      </c>
-      <c r="D30" s="6">
-        <v>16.56</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>715.65</v>
+      </c>
+      <c r="D57" s="5">
+        <v>714.35</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-44.25</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-44.52</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>200</v>
+      </c>
+      <c r="D58" s="5">
+        <v>195.92</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-4.08</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-19.86</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-19.52</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>3545.7</v>
+      </c>
+      <c r="D59" s="5">
+        <v>3552.5</v>
+      </c>
+      <c r="E59" s="7">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>0.34</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.91</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1548</v>
+      </c>
+      <c r="D60" s="5">
+        <v>1542.2</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-17.47</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-14.84</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>48.43</v>
+      </c>
+      <c r="D61" s="5">
+        <v>41.76</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-6.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-6.27</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>34.86</v>
+      </c>
+      <c r="D62" s="5">
+        <v>31.58</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3.45</v>
-      </c>
-      <c r="D36" s="6">
-        <v>5.61</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>30.56</v>
+      </c>
+      <c r="D63" s="5">
+        <v>29.96</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>44.57</v>
+      </c>
+      <c r="D64" s="5">
+        <v>49.96</v>
+      </c>
+      <c r="E64" s="7">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>14.14</v>
-      </c>
-      <c r="D38" s="6">
-        <v>12.85</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>65.86</v>
+      </c>
+      <c r="D65" s="5">
+        <v>66.75</v>
+      </c>
+      <c r="E65" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>12.75</v>
-      </c>
-      <c r="D39" s="6">
-        <v>15.54</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>62.89</v>
+      </c>
+      <c r="D66" s="5">
+        <v>62.33</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-16.81</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-16.94</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>39.96</v>
+      </c>
+      <c r="D67" s="5">
+        <v>34.83</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-5.13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-10.25</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-10.48</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>44.85</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46.03</v>
+      </c>
+      <c r="E68" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>7.37</v>
-      </c>
-      <c r="D42" s="6">
-        <v>7.96</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>45.3</v>
+      </c>
+      <c r="D69" s="5">
+        <v>44.06</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-20.65</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-20.28</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-27.52</v>
+      </c>
+      <c r="D70" s="5">
+        <v>-33.23</v>
+      </c>
+      <c r="E70" s="6">
+        <v>-5.71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-21.56</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-20.18</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>7.46</v>
+      </c>
+      <c r="D71" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="E71" s="6">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-17.56</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-19.21</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-7.69</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-57.17</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-49.48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-16.08</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-15.38</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>79.8</v>
+      </c>
+      <c r="D73" s="5">
+        <v>45.95</v>
+      </c>
+      <c r="E73" s="6">
+        <v>-33.85</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-5.07</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>213.95</v>
+      </c>
+      <c r="D74" s="5">
+        <v>198.44</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-15.51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-54.18</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-53.25</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-44.6</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-43.59</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-69.56999999999999</v>
+      </c>
+      <c r="D76" s="5">
+        <v>41.77</v>
+      </c>
+      <c r="E76" s="7">
+        <v>111.34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-21.1</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-21.16</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-43.31</v>
+      </c>
+      <c r="D77" s="5">
+        <v>52.49</v>
+      </c>
+      <c r="E77" s="7">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-12.75</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-12.46</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>388.95</v>
-      </c>
-      <c r="D52" s="6">
-        <v>390.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2982.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3035</v>
-      </c>
-      <c r="E53" s="7">
-        <v>52.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>339.9</v>
-      </c>
-      <c r="D54" s="6">
-        <v>333.1</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>353.9</v>
-      </c>
-      <c r="D55" s="6">
-        <v>356.85</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>420.05</v>
-      </c>
-      <c r="D56" s="6">
-        <v>420.25</v>
-      </c>
-      <c r="E56" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>708.55</v>
-      </c>
-      <c r="D57" s="6">
-        <v>715.65</v>
-      </c>
-      <c r="E57" s="7">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>199.71</v>
-      </c>
-      <c r="D58" s="6">
-        <v>200</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>3548.6</v>
-      </c>
-      <c r="D59" s="6">
-        <v>3545.7</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1543</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1548</v>
-      </c>
-      <c r="E60" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>99</v>
-      </c>
-      <c r="D63" s="6">
-        <v>88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>88</v>
-      </c>
-      <c r="D64" s="6">
-        <v>99</v>
-      </c>
-      <c r="E64" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>46.46</v>
-      </c>
-      <c r="D65" s="6">
-        <v>48.43</v>
-      </c>
-      <c r="E65" s="7">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>25.45</v>
-      </c>
-      <c r="D66" s="6">
-        <v>34.86</v>
-      </c>
-      <c r="E66" s="7">
-        <v>9.41</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>33.69</v>
-      </c>
-      <c r="D67" s="6">
-        <v>30.56</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>41.83</v>
-      </c>
-      <c r="D68" s="6">
-        <v>44.57</v>
-      </c>
-      <c r="E68" s="7">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>65.75</v>
-      </c>
-      <c r="D69" s="6">
-        <v>65.86</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>61.09</v>
-      </c>
-      <c r="D70" s="6">
-        <v>62.89</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>39.37</v>
-      </c>
-      <c r="D71" s="6">
-        <v>39.96</v>
-      </c>
-      <c r="E71" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>45.24</v>
-      </c>
-      <c r="D72" s="6">
-        <v>44.85</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>44.04</v>
-      </c>
-      <c r="D73" s="6">
-        <v>45.3</v>
-      </c>
-      <c r="E73" s="7">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="6">
-        <v>-25.5</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-27.52</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>0.34</v>
-      </c>
-      <c r="D75" s="6">
-        <v>7.46</v>
-      </c>
-      <c r="E75" s="7">
-        <v>7.12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-7.69</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-9.25</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-21.2</v>
-      </c>
-      <c r="D77" s="6">
-        <v>79.8</v>
-      </c>
-      <c r="E77" s="7">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>305.36</v>
-      </c>
-      <c r="D78" s="6">
-        <v>213.95</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-91.41</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-49.73</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-54.18</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-62.85</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-69.56999999999999</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-6.72</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-0.34</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-43.31</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-42.97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="D82" s="6">
+      <c r="C78" s="5">
         <v>-50.07</v>
       </c>
-      <c r="E82" s="8">
-        <v>-41.51</v>
+      <c r="D78" s="5">
+        <v>-31.77</v>
+      </c>
+      <c r="E78" s="7">
+        <v>18.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3494,60 +3345,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>79</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>44.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.4</v>
-      </c>
-      <c r="E2" s="11">
-        <v>30</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-2.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>45.3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>40</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-2.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3649,61 +3500,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3669</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3118</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2004</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.148</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1241</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0562</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0417</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0413</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.09609999999999999</v>
+      <c r="A2" s="13">
+        <v>0.3673</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3096</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2037</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1487</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1198</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0638</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0482</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0417</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.09759999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -902,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>383.35</v>
+        <v>376.45</v>
       </c>
       <c r="D2">
-        <v>-1.91</v>
+        <v>-1.8</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +914,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-21.8</v>
+        <v>-23.2</v>
       </c>
       <c r="H2">
-        <v>2.23</v>
+        <v>0.39</v>
       </c>
       <c r="I2">
-        <v>-2.99</v>
+        <v>-3.62</v>
       </c>
       <c r="J2">
-        <v>-2.83</v>
+        <v>-3.46</v>
       </c>
       <c r="K2">
-        <v>-16.26</v>
+        <v>-17.97</v>
       </c>
       <c r="L2">
-        <v>-9.460000000000001</v>
+        <v>-12.56</v>
       </c>
       <c r="M2">
-        <v>11.98</v>
+        <v>11.54</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>387.58</v>
+        <v>384.75</v>
       </c>
       <c r="Q2">
-        <v>385.15</v>
+        <v>384.42</v>
       </c>
       <c r="R2">
-        <v>402.68</v>
+        <v>400.73</v>
       </c>
       <c r="S2">
-        <v>434.27</v>
+        <v>434.15</v>
       </c>
       <c r="T2">
-        <v>-11.73</v>
+        <v>-13.29</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.76</v>
+        <v>36.71</v>
       </c>
       <c r="Z2">
-        <v>-4.44</v>
+        <v>-4.93</v>
       </c>
       <c r="AA2">
-        <v>-6.41</v>
+        <v>-6.12</v>
       </c>
       <c r="AB2">
-        <v>1.97</v>
+        <v>1.19</v>
       </c>
       <c r="AC2">
-        <v>79.83</v>
+        <v>69.53</v>
       </c>
       <c r="AD2">
-        <v>78.84999999999999</v>
+        <v>76.16</v>
       </c>
       <c r="AE2">
-        <v>9.550000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="AF2">
-        <v>-33.23</v>
+        <v>-21.28</v>
       </c>
       <c r="AG2">
-        <v>395.44</v>
+        <v>395.01</v>
       </c>
       <c r="AH2">
-        <v>374.86</v>
+        <v>373.82</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>29.61</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2995</v>
+        <v>2947.8</v>
       </c>
       <c r="D3">
-        <v>-1.32</v>
+        <v>-1.58</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-21.23</v>
+        <v>-22.48</v>
       </c>
       <c r="H3">
-        <v>2.18</v>
+        <v>0.57</v>
       </c>
       <c r="I3">
-        <v>-1.97</v>
+        <v>-3.18</v>
       </c>
       <c r="J3">
-        <v>-10.06</v>
+        <v>-11.58</v>
       </c>
       <c r="K3">
-        <v>-2.4</v>
+        <v>-4.82</v>
       </c>
       <c r="L3">
-        <v>-17.14</v>
+        <v>-17.54</v>
       </c>
       <c r="M3">
-        <v>30.96</v>
+        <v>30.35</v>
       </c>
       <c r="N3">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P3">
-        <v>3018.44</v>
+        <v>2999.1</v>
       </c>
       <c r="Q3">
-        <v>3106.37</v>
+        <v>3089.66</v>
       </c>
       <c r="R3">
-        <v>3258.4</v>
+        <v>3254.05</v>
       </c>
       <c r="S3">
-        <v>3286.66</v>
+        <v>3283.25</v>
       </c>
       <c r="T3">
-        <v>-8.869999999999999</v>
+        <v>-10.22</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1081,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.58</v>
+        <v>28.2</v>
       </c>
       <c r="Z3">
-        <v>-76.29000000000001</v>
+        <v>-79.61</v>
       </c>
       <c r="AA3">
-        <v>-70.14</v>
+        <v>-72.03</v>
       </c>
       <c r="AB3">
-        <v>-6.15</v>
+        <v>-7.58</v>
       </c>
       <c r="AC3">
-        <v>58.54</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="AD3">
-        <v>48.88</v>
+        <v>59.21</v>
       </c>
       <c r="AE3">
-        <v>62</v>
+        <v>60.95</v>
       </c>
       <c r="AF3">
-        <v>3.8</v>
+        <v>62.44</v>
       </c>
       <c r="AG3">
-        <v>3272.08</v>
+        <v>3248.04</v>
       </c>
       <c r="AH3">
-        <v>2940.65</v>
+        <v>2931.27</v>
       </c>
       <c r="AI3">
-        <v>3184.76</v>
+        <v>3152.24</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>73.65000000000001</v>
+        <v>75.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>331.75</v>
+        <v>328.05</v>
       </c>
       <c r="D4">
-        <v>-0.41</v>
+        <v>-1.12</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,46 +1140,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-19.54</v>
+        <v>-20.43</v>
       </c>
       <c r="H4">
-        <v>21.54</v>
+        <v>20.19</v>
       </c>
       <c r="I4">
-        <v>-6.47</v>
+        <v>-6.91</v>
       </c>
       <c r="J4">
-        <v>-13.46</v>
+        <v>-12.89</v>
       </c>
       <c r="K4">
-        <v>5.05</v>
+        <v>4.09</v>
       </c>
       <c r="L4">
-        <v>17.31</v>
+        <v>16.27</v>
       </c>
       <c r="M4">
-        <v>14.87</v>
+        <v>14.14</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O4">
         <v>71</v>
       </c>
       <c r="P4">
-        <v>341.15</v>
+        <v>336.28</v>
       </c>
       <c r="Q4">
-        <v>356.43</v>
+        <v>354.18</v>
       </c>
       <c r="R4">
-        <v>372.84</v>
+        <v>372.95</v>
       </c>
       <c r="S4">
-        <v>343.89</v>
+        <v>343.79</v>
       </c>
       <c r="T4">
-        <v>-3.53</v>
+        <v>-4.58</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,43 +1194,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>29.96</v>
+        <v>28.33</v>
       </c>
       <c r="Z4">
-        <v>-9.75</v>
+        <v>-10.57</v>
       </c>
       <c r="AA4">
-        <v>-7.21</v>
+        <v>-7.88</v>
       </c>
       <c r="AB4">
-        <v>-2.54</v>
+        <v>-2.69</v>
       </c>
       <c r="AC4">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>18.84</v>
+        <v>7.36</v>
       </c>
       <c r="AE4">
-        <v>10.79</v>
+        <v>10.48</v>
       </c>
       <c r="AF4">
-        <v>-57.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>384.61</v>
+        <v>383.92</v>
       </c>
       <c r="AH4">
-        <v>328.25</v>
+        <v>324.44</v>
       </c>
       <c r="AI4">
-        <v>363.72</v>
+        <v>359.77</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>35.17</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>363.1</v>
+        <v>361</v>
       </c>
       <c r="D5">
-        <v>1.75</v>
+        <v>-0.58</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-13.9</v>
+        <v>-14.39</v>
       </c>
       <c r="H5">
-        <v>23.4</v>
+        <v>22.68</v>
       </c>
       <c r="I5">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="J5">
-        <v>-1.51</v>
+        <v>-1.78</v>
       </c>
       <c r="K5">
-        <v>-0.91</v>
+        <v>-3.14</v>
       </c>
       <c r="L5">
-        <v>-3.26</v>
+        <v>-2.54</v>
       </c>
       <c r="M5">
-        <v>6.38</v>
+        <v>5.62</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>357.9</v>
+        <v>358.29</v>
       </c>
       <c r="Q5">
-        <v>359.42</v>
+        <v>359.19</v>
       </c>
       <c r="R5">
-        <v>372.41</v>
+        <v>372.16</v>
       </c>
       <c r="S5">
-        <v>359.83</v>
+        <v>359.61</v>
       </c>
       <c r="T5">
-        <v>0.91</v>
+        <v>0.39</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1307,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>49.96</v>
+        <v>48.26</v>
       </c>
       <c r="Z5">
-        <v>-3.59</v>
+        <v>-3.19</v>
       </c>
       <c r="AA5">
-        <v>-4.35</v>
+        <v>-4.12</v>
       </c>
       <c r="AB5">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="AC5">
-        <v>74.95999999999999</v>
+        <v>85.47</v>
       </c>
       <c r="AD5">
-        <v>68.53</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AE5">
-        <v>12.01</v>
+        <v>11.84</v>
       </c>
       <c r="AF5">
-        <v>45.95</v>
+        <v>-4.45</v>
       </c>
       <c r="AG5">
-        <v>372.57</v>
+        <v>372.03</v>
       </c>
       <c r="AH5">
-        <v>346.28</v>
+        <v>346.35</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1343,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>25.99</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>421.8</v>
+        <v>425.7</v>
       </c>
       <c r="D6">
-        <v>0.37</v>
+        <v>0.92</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1366,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-4.72</v>
+        <v>-3.84</v>
       </c>
       <c r="H6">
-        <v>50.89</v>
+        <v>52.28</v>
       </c>
       <c r="I6">
-        <v>5.63</v>
+        <v>6.35</v>
       </c>
       <c r="J6">
-        <v>7.71</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K6">
-        <v>12.81</v>
+        <v>14.62</v>
       </c>
       <c r="L6">
-        <v>17.44</v>
+        <v>20.41</v>
       </c>
       <c r="M6">
-        <v>-9.76</v>
+        <v>-9.74</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P6">
-        <v>415.79</v>
+        <v>420.87</v>
       </c>
       <c r="Q6">
-        <v>401.12</v>
+        <v>402.83</v>
       </c>
       <c r="R6">
-        <v>403.71</v>
+        <v>404.36</v>
       </c>
       <c r="S6">
-        <v>374.07</v>
+        <v>374.57</v>
       </c>
       <c r="T6">
-        <v>12.76</v>
+        <v>13.65</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>66.75</v>
+        <v>68.95</v>
       </c>
       <c r="Z6">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA6">
-        <v>1.16</v>
+        <v>2.02</v>
       </c>
       <c r="AB6">
-        <v>3.19</v>
+        <v>3.43</v>
       </c>
       <c r="AC6">
         <v>100</v>
       </c>
       <c r="AD6">
-        <v>96.73</v>
+        <v>100</v>
       </c>
       <c r="AE6">
-        <v>12.43</v>
+        <v>13.01</v>
       </c>
       <c r="AF6">
-        <v>198.44</v>
+        <v>166.9</v>
       </c>
       <c r="AG6">
-        <v>423.87</v>
+        <v>427.58</v>
       </c>
       <c r="AH6">
-        <v>378.38</v>
+        <v>378.09</v>
       </c>
       <c r="AI6">
         <v>387.98</v>
@@ -1456,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>39.76</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>714.35</v>
+        <v>721.85</v>
       </c>
       <c r="D7">
-        <v>-0.18</v>
+        <v>1.05</v>
       </c>
       <c r="E7">
         <v>728.9</v>
@@ -1479,46 +1479,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-2</v>
+        <v>-0.97</v>
       </c>
       <c r="H7">
-        <v>41.05</v>
+        <v>42.53</v>
       </c>
       <c r="I7">
-        <v>1.05</v>
+        <v>3.51</v>
       </c>
       <c r="J7">
-        <v>11.26</v>
+        <v>9.09</v>
       </c>
       <c r="K7">
-        <v>19.5</v>
+        <v>21.1</v>
       </c>
       <c r="L7">
-        <v>18.96</v>
+        <v>19.57</v>
       </c>
       <c r="M7">
-        <v>36.73</v>
+        <v>36.95</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P7">
-        <v>707.73</v>
+        <v>712.63</v>
       </c>
       <c r="Q7">
-        <v>694.52</v>
+        <v>697.46</v>
       </c>
       <c r="R7">
-        <v>637.95</v>
+        <v>640.6900000000001</v>
       </c>
       <c r="S7">
-        <v>597.15</v>
+        <v>597.9400000000001</v>
       </c>
       <c r="T7">
-        <v>19.63</v>
+        <v>20.72</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1533,34 +1533,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>62.33</v>
+        <v>64.33</v>
       </c>
       <c r="Z7">
-        <v>20.82</v>
+        <v>20.73</v>
       </c>
       <c r="AA7">
-        <v>22.54</v>
+        <v>22.18</v>
       </c>
       <c r="AB7">
-        <v>-1.72</v>
+        <v>-1.45</v>
       </c>
       <c r="AC7">
-        <v>21.56</v>
+        <v>27.55</v>
       </c>
       <c r="AD7">
-        <v>15.32</v>
+        <v>21.88</v>
       </c>
       <c r="AE7">
-        <v>25.02</v>
+        <v>25.27</v>
       </c>
       <c r="AF7">
-        <v>-53.25</v>
+        <v>17.31</v>
       </c>
       <c r="AG7">
-        <v>741.39</v>
+        <v>743.4</v>
       </c>
       <c r="AH7">
-        <v>647.66</v>
+        <v>651.52</v>
       </c>
       <c r="AI7">
         <v>649.01</v>
@@ -1569,7 +1569,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>41.97</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,37 +1580,37 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>195.92</v>
+        <v>194.49</v>
       </c>
       <c r="D8">
-        <v>-2.04</v>
+        <v>-0.73</v>
       </c>
       <c r="E8">
-        <v>354.1</v>
+        <v>352.8</v>
       </c>
       <c r="F8">
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.67</v>
+        <v>-44.87</v>
       </c>
       <c r="H8">
-        <v>1.83</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
-        <v>-2.71</v>
+        <v>-2.3</v>
       </c>
       <c r="J8">
-        <v>-7.25</v>
+        <v>-7.99</v>
       </c>
       <c r="K8">
-        <v>-17.7</v>
+        <v>-17.89</v>
       </c>
       <c r="L8">
-        <v>-44.74</v>
+        <v>-45.07</v>
       </c>
       <c r="M8">
-        <v>-4.17</v>
+        <v>-4.54</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1619,19 +1619,19 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>199.22</v>
+        <v>198.3</v>
       </c>
       <c r="Q8">
-        <v>201.08</v>
+        <v>200.32</v>
       </c>
       <c r="R8">
-        <v>213.59</v>
+        <v>212.95</v>
       </c>
       <c r="S8">
-        <v>251.21</v>
+        <v>250.61</v>
       </c>
       <c r="T8">
-        <v>-22.01</v>
+        <v>-22.39</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1646,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.83</v>
+        <v>33.22</v>
       </c>
       <c r="Z8">
-        <v>-4.82</v>
+        <v>-4.88</v>
       </c>
       <c r="AA8">
-        <v>-5.53</v>
+        <v>-5.4</v>
       </c>
       <c r="AB8">
-        <v>0.71</v>
+        <v>0.52</v>
       </c>
       <c r="AC8">
-        <v>84.08</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="AD8">
-        <v>90.13</v>
+        <v>84.38</v>
       </c>
       <c r="AE8">
-        <v>5.86</v>
+        <v>5.73</v>
       </c>
       <c r="AF8">
-        <v>41.77</v>
+        <v>-58.2</v>
       </c>
       <c r="AG8">
-        <v>211.65</v>
+        <v>210.47</v>
       </c>
       <c r="AH8">
-        <v>190.51</v>
+        <v>190.17</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1682,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>35.96</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3552.5</v>
+        <v>3548.2</v>
       </c>
       <c r="D9">
-        <v>0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1705,46 +1705,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.54</v>
+        <v>-18.64</v>
       </c>
       <c r="H9">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="I9">
-        <v>-0.5600000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="J9">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="K9">
-        <v>-11.13</v>
+        <v>-12.14</v>
       </c>
       <c r="L9">
-        <v>-21.01</v>
+        <v>-15.6</v>
       </c>
       <c r="M9">
-        <v>20.37</v>
+        <v>20.61</v>
       </c>
       <c r="N9">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O9">
         <v>40</v>
       </c>
       <c r="P9">
-        <v>3552.42</v>
+        <v>3550.86</v>
       </c>
       <c r="Q9">
-        <v>3568.44</v>
+        <v>3567.38</v>
       </c>
       <c r="R9">
-        <v>3583.96</v>
+        <v>3581.4</v>
       </c>
       <c r="S9">
-        <v>3675.06</v>
+        <v>3674.48</v>
       </c>
       <c r="T9">
-        <v>-3.33</v>
+        <v>-3.44</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.03</v>
+        <v>45.37</v>
       </c>
       <c r="Z9">
-        <v>-12.62</v>
+        <v>-12.79</v>
       </c>
       <c r="AA9">
-        <v>-12.9</v>
+        <v>-12.88</v>
       </c>
       <c r="AB9">
-        <v>0.28</v>
+        <v>0.09</v>
       </c>
       <c r="AC9">
-        <v>29.79</v>
+        <v>32.62</v>
       </c>
       <c r="AD9">
-        <v>30.9</v>
+        <v>30.4</v>
       </c>
       <c r="AE9">
-        <v>60.19</v>
+        <v>58.38</v>
       </c>
       <c r="AF9">
-        <v>52.49</v>
+        <v>-31.11</v>
       </c>
       <c r="AG9">
-        <v>3633.75</v>
+        <v>3633.31</v>
       </c>
       <c r="AH9">
-        <v>3503.13</v>
+        <v>3501.46</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1795,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>17.82</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1542.2</v>
+        <v>1510.5</v>
       </c>
       <c r="D10">
-        <v>-0.37</v>
+        <v>-2.06</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-12.79</v>
+        <v>-14.58</v>
       </c>
       <c r="H10">
-        <v>16.29</v>
+        <v>13.9</v>
       </c>
       <c r="I10">
-        <v>-1.05</v>
+        <v>-2.65</v>
       </c>
       <c r="J10">
-        <v>-2.7</v>
+        <v>-7.95</v>
       </c>
       <c r="K10">
-        <v>9.789999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="L10">
-        <v>5.87</v>
+        <v>5.09</v>
       </c>
       <c r="M10">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="P10">
-        <v>1548.36</v>
+        <v>1540.14</v>
       </c>
       <c r="Q10">
-        <v>1565.7</v>
+        <v>1559.82</v>
       </c>
       <c r="R10">
-        <v>1593.21</v>
+        <v>1591.89</v>
       </c>
       <c r="S10">
-        <v>1518.49</v>
+        <v>1518.29</v>
       </c>
       <c r="T10">
-        <v>1.56</v>
+        <v>-0.51</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1869,37 +1869,37 @@
         <v>47</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>44.06</v>
+        <v>37.97</v>
       </c>
       <c r="Z10">
-        <v>-11.71</v>
+        <v>-14.28</v>
       </c>
       <c r="AA10">
-        <v>-10.44</v>
+        <v>-11.21</v>
       </c>
       <c r="AB10">
-        <v>-1.27</v>
+        <v>-3.07</v>
       </c>
       <c r="AC10">
-        <v>70.73999999999999</v>
+        <v>58.22</v>
       </c>
       <c r="AD10">
-        <v>71.86</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="AE10">
-        <v>37.17</v>
+        <v>37.87</v>
       </c>
       <c r="AF10">
-        <v>-31.77</v>
+        <v>76.23</v>
       </c>
       <c r="AG10">
-        <v>1634.83</v>
+        <v>1626.59</v>
       </c>
       <c r="AH10">
-        <v>1496.57</v>
+        <v>1493.06</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1908,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>14.62</v>
+        <v>15.36</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.56</v>
+        <v>-2.83</v>
       </c>
       <c r="D7" s="5">
-        <v>-2.83</v>
+        <v>-3.46</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.27</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.69</v>
+        <v>-10.06</v>
       </c>
       <c r="D8" s="5">
-        <v>-10.06</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.63</v>
+        <v>-11.58</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-13.56</v>
+        <v>-13.46</v>
       </c>
       <c r="D9" s="5">
-        <v>-13.46</v>
+        <v>-12.89</v>
       </c>
       <c r="E9" s="7">
-        <v>0.1</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.88</v>
+        <v>-1.51</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.37</v>
+        <v>-1.78</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2174,13 +2174,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>5.22</v>
+        <v>7.71</v>
       </c>
       <c r="D11" s="5">
-        <v>7.71</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E11" s="7">
-        <v>2.49</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>12.43</v>
+        <v>11.26</v>
       </c>
       <c r="D12" s="5">
-        <v>11.26</v>
+        <v>9.09</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.17</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.34</v>
+        <v>-7.25</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.25</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.09</v>
+        <v>-7.99</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2225,13 +2225,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.09</v>
+        <v>0.12</v>
       </c>
       <c r="D14" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.21</v>
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2242,13 +2242,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-1.46</v>
+        <v>-2.7</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.7</v>
+        <v>-7.95</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.24</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2259,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>0.9399999999999999</v>
+        <v>-2.99</v>
       </c>
       <c r="D16" s="5">
-        <v>-2.99</v>
+        <v>-3.62</v>
       </c>
       <c r="E16" s="6">
-        <v>-3.93</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-0.5600000000000001</v>
+        <v>-1.97</v>
       </c>
       <c r="D17" s="5">
-        <v>-1.97</v>
+        <v>-3.18</v>
       </c>
       <c r="E17" s="6">
-        <v>-1.41</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.72</v>
+        <v>-6.47</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.47</v>
+        <v>-6.91</v>
       </c>
       <c r="E18" s="6">
-        <v>-0.75</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-2.61</v>
+        <v>0.12</v>
       </c>
       <c r="D19" s="5">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="E19" s="7">
-        <v>2.73</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>7</v>
+        <v>5.63</v>
       </c>
       <c r="D20" s="5">
-        <v>5.63</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.37</v>
+        <v>6.35</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.72</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-0.26</v>
+        <v>1.05</v>
       </c>
       <c r="D21" s="5">
-        <v>1.05</v>
+        <v>3.51</v>
       </c>
       <c r="E21" s="7">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>0.36</v>
+        <v>-2.71</v>
       </c>
       <c r="D22" s="5">
-        <v>-2.71</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-3.07</v>
+        <v>-2.3</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>-2.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D23" s="5">
-        <v>-0.5600000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="E23" s="7">
-        <v>1.63</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>0.71</v>
+        <v>-1.05</v>
       </c>
       <c r="D24" s="5">
-        <v>-1.05</v>
+        <v>-2.65</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.76</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-10.59</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="D25" s="5">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.13</v>
+        <v>-12.56</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>-15.34</v>
+        <v>-17.14</v>
       </c>
       <c r="D26" s="5">
-        <v>-17.14</v>
+        <v>-17.54</v>
       </c>
       <c r="E26" s="6">
-        <v>-1.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>14.76</v>
+        <v>17.31</v>
       </c>
       <c r="D27" s="5">
-        <v>17.31</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.55</v>
+        <v>16.27</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>-4.48</v>
+        <v>-3.26</v>
       </c>
       <c r="D28" s="5">
-        <v>-3.26</v>
+        <v>-2.54</v>
       </c>
       <c r="E28" s="7">
-        <v>1.22</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>15.42</v>
+        <v>17.44</v>
       </c>
       <c r="D29" s="5">
-        <v>17.44</v>
+        <v>20.41</v>
       </c>
       <c r="E29" s="7">
-        <v>2.02</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>16.56</v>
+        <v>18.96</v>
       </c>
       <c r="D30" s="5">
-        <v>18.96</v>
+        <v>19.57</v>
       </c>
       <c r="E30" s="7">
-        <v>2.4</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2514,13 +2514,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="5">
-        <v>-44.52</v>
+        <v>-44.74</v>
       </c>
       <c r="D31" s="5">
-        <v>-44.74</v>
+        <v>-45.07</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.22</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2531,13 +2531,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="5">
-        <v>-19.52</v>
+        <v>-21.01</v>
       </c>
       <c r="D32" s="5">
-        <v>-21.01</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.49</v>
+        <v>-15.6</v>
+      </c>
+      <c r="E32" s="7">
+        <v>5.41</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2548,13 +2548,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="5">
-        <v>3.91</v>
+        <v>5.87</v>
       </c>
       <c r="D33" s="5">
-        <v>5.87</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.96</v>
+        <v>5.09</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2565,13 +2565,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-14.84</v>
+        <v>-16.26</v>
       </c>
       <c r="D34" s="5">
-        <v>-16.26</v>
+        <v>-17.97</v>
       </c>
       <c r="E34" s="6">
-        <v>-1.42</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2582,13 +2582,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-1.88</v>
+        <v>-2.4</v>
       </c>
       <c r="D35" s="5">
-        <v>-2.4</v>
+        <v>-4.82</v>
       </c>
       <c r="E35" s="6">
-        <v>-0.52</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>5.61</v>
+        <v>5.05</v>
       </c>
       <c r="D36" s="5">
-        <v>5.05</v>
+        <v>4.09</v>
       </c>
       <c r="E36" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2616,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-2.78</v>
+        <v>-0.91</v>
       </c>
       <c r="D37" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.87</v>
+        <v>-3.14</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>12.85</v>
+        <v>12.81</v>
       </c>
       <c r="D38" s="5">
-        <v>12.81</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.04</v>
+        <v>14.62</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.81</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>15.54</v>
+        <v>19.5</v>
       </c>
       <c r="D39" s="5">
-        <v>19.5</v>
+        <v>21.1</v>
       </c>
       <c r="E39" s="7">
-        <v>3.96</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2667,13 +2667,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>-16.94</v>
+        <v>-17.7</v>
       </c>
       <c r="D40" s="5">
-        <v>-17.7</v>
+        <v>-17.89</v>
       </c>
       <c r="E40" s="6">
-        <v>-0.76</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>-10.48</v>
+        <v>-11.13</v>
       </c>
       <c r="D41" s="5">
-        <v>-11.13</v>
+        <v>-12.14</v>
       </c>
       <c r="E41" s="6">
-        <v>-0.65</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2701,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="5">
-        <v>7.96</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D42" s="5">
-        <v>9.789999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="E42" s="7">
-        <v>1.83</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2718,13 +2718,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-20.28</v>
+        <v>-21.8</v>
       </c>
       <c r="D43" s="5">
-        <v>-21.8</v>
+        <v>-23.2</v>
       </c>
       <c r="E43" s="6">
-        <v>-1.52</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2735,13 +2735,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-20.18</v>
+        <v>-21.23</v>
       </c>
       <c r="D44" s="5">
-        <v>-21.23</v>
+        <v>-22.48</v>
       </c>
       <c r="E44" s="6">
-        <v>-1.05</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2752,13 +2752,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-19.21</v>
+        <v>-19.54</v>
       </c>
       <c r="D45" s="5">
-        <v>-19.54</v>
+        <v>-20.43</v>
       </c>
       <c r="E45" s="6">
-        <v>-0.33</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2769,13 +2769,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-15.38</v>
+        <v>-13.9</v>
       </c>
       <c r="D46" s="5">
-        <v>-13.9</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.48</v>
+        <v>-14.39</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2786,13 +2786,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="5">
-        <v>-5.07</v>
+        <v>-4.72</v>
       </c>
       <c r="D47" s="5">
-        <v>-4.72</v>
+        <v>-3.84</v>
       </c>
       <c r="E47" s="7">
-        <v>0.35</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2803,13 +2803,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="5">
-        <v>-1.82</v>
+        <v>-2</v>
       </c>
       <c r="D48" s="5">
-        <v>-2</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.18</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2820,13 +2820,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="5">
-        <v>-43.59</v>
+        <v>-44.67</v>
       </c>
       <c r="D49" s="5">
-        <v>-44.67</v>
+        <v>-44.87</v>
       </c>
       <c r="E49" s="6">
-        <v>-1.08</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2837,13 +2837,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="5">
-        <v>-21.16</v>
+        <v>-18.54</v>
       </c>
       <c r="D50" s="5">
-        <v>-18.54</v>
-      </c>
-      <c r="E50" s="7">
-        <v>2.62</v>
+        <v>-18.64</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2854,13 +2854,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="5">
-        <v>-12.46</v>
+        <v>-12.79</v>
       </c>
       <c r="D51" s="5">
-        <v>-12.79</v>
+        <v>-14.58</v>
       </c>
       <c r="E51" s="6">
-        <v>-0.33</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2871,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>390.8</v>
+        <v>383.35</v>
       </c>
       <c r="D52" s="5">
-        <v>383.35</v>
+        <v>376.45</v>
       </c>
       <c r="E52" s="6">
-        <v>-7.45</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2888,13 +2888,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3035</v>
+        <v>2995</v>
       </c>
       <c r="D53" s="5">
-        <v>2995</v>
+        <v>2947.8</v>
       </c>
       <c r="E53" s="6">
-        <v>-40</v>
+        <v>-47.2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2905,13 +2905,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>333.1</v>
+        <v>331.75</v>
       </c>
       <c r="D54" s="5">
-        <v>331.75</v>
+        <v>328.05</v>
       </c>
       <c r="E54" s="6">
-        <v>-1.35</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2922,13 +2922,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="5">
-        <v>356.85</v>
+        <v>363.1</v>
       </c>
       <c r="D55" s="5">
-        <v>363.1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>6.25</v>
+        <v>361</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2939,13 +2939,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="5">
-        <v>420.25</v>
+        <v>421.8</v>
       </c>
       <c r="D56" s="5">
-        <v>421.8</v>
+        <v>425.7</v>
       </c>
       <c r="E56" s="7">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2956,13 +2956,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="5">
-        <v>715.65</v>
+        <v>714.35</v>
       </c>
       <c r="D57" s="5">
-        <v>714.35</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-1.3</v>
+        <v>721.85</v>
+      </c>
+      <c r="E57" s="7">
+        <v>7.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2973,13 +2973,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="5">
-        <v>200</v>
+        <v>195.92</v>
       </c>
       <c r="D58" s="5">
-        <v>195.92</v>
+        <v>194.49</v>
       </c>
       <c r="E58" s="6">
-        <v>-4.08</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2990,13 +2990,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="5">
-        <v>3545.7</v>
+        <v>3552.5</v>
       </c>
       <c r="D59" s="5">
-        <v>3552.5</v>
-      </c>
-      <c r="E59" s="7">
-        <v>6.8</v>
+        <v>3548.2</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-4.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3007,13 +3007,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="5">
-        <v>1548</v>
+        <v>1542.2</v>
       </c>
       <c r="D60" s="5">
-        <v>1542.2</v>
+        <v>1510.5</v>
       </c>
       <c r="E60" s="6">
-        <v>-5.8</v>
+        <v>-31.7</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3021,16 +3021,16 @@
         <v>37</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C61" s="5">
-        <v>48.43</v>
+        <v>34</v>
       </c>
       <c r="D61" s="5">
-        <v>41.76</v>
+        <v>23</v>
       </c>
       <c r="E61" s="6">
-        <v>-6.67</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3038,16 +3038,16 @@
         <v>38</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="5">
-        <v>34.86</v>
+        <v>45</v>
       </c>
       <c r="D62" s="5">
-        <v>31.58</v>
+        <v>34</v>
       </c>
       <c r="E62" s="6">
-        <v>-3.28</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3055,271 +3055,356 @@
         <v>39</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="5">
-        <v>30.56</v>
+        <v>77</v>
       </c>
       <c r="D63" s="5">
-        <v>29.96</v>
+        <v>66</v>
       </c>
       <c r="E63" s="6">
-        <v>-0.6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="5">
-        <v>44.57</v>
+        <v>23</v>
       </c>
       <c r="D64" s="5">
-        <v>49.96</v>
+        <v>45</v>
       </c>
       <c r="E64" s="7">
-        <v>5.39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="5">
-        <v>65.86</v>
+        <v>66</v>
       </c>
       <c r="D65" s="5">
-        <v>66.75</v>
+        <v>77</v>
       </c>
       <c r="E65" s="7">
-        <v>0.89</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="5">
-        <v>62.89</v>
+        <v>41.76</v>
       </c>
       <c r="D66" s="5">
-        <v>62.33</v>
+        <v>36.71</v>
       </c>
       <c r="E66" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-5.05</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="5">
-        <v>39.96</v>
+        <v>31.58</v>
       </c>
       <c r="D67" s="5">
-        <v>34.83</v>
+        <v>28.2</v>
       </c>
       <c r="E67" s="6">
-        <v>-5.13</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="5">
-        <v>44.85</v>
+        <v>29.96</v>
       </c>
       <c r="D68" s="5">
-        <v>46.03</v>
-      </c>
-      <c r="E68" s="7">
-        <v>1.18</v>
+        <v>28.33</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="5">
-        <v>45.3</v>
+        <v>49.96</v>
       </c>
       <c r="D69" s="5">
-        <v>44.06</v>
+        <v>48.26</v>
       </c>
       <c r="E69" s="6">
-        <v>-1.24</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="5">
-        <v>-27.52</v>
+        <v>66.75</v>
       </c>
       <c r="D70" s="5">
-        <v>-33.23</v>
-      </c>
-      <c r="E70" s="6">
-        <v>-5.71</v>
+        <v>68.95</v>
+      </c>
+      <c r="E70" s="7">
+        <v>2.2</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="5">
-        <v>7.46</v>
+        <v>62.33</v>
       </c>
       <c r="D71" s="5">
-        <v>3.8</v>
-      </c>
-      <c r="E71" s="6">
-        <v>-3.66</v>
+        <v>64.33</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="5">
-        <v>-7.69</v>
+        <v>34.83</v>
       </c>
       <c r="D72" s="5">
-        <v>-57.17</v>
+        <v>33.22</v>
       </c>
       <c r="E72" s="6">
-        <v>-49.48</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="5">
-        <v>79.8</v>
+        <v>46.03</v>
       </c>
       <c r="D73" s="5">
-        <v>45.95</v>
+        <v>45.37</v>
       </c>
       <c r="E73" s="6">
-        <v>-33.85</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="5">
-        <v>213.95</v>
+        <v>44.06</v>
       </c>
       <c r="D74" s="5">
-        <v>198.44</v>
+        <v>37.97</v>
       </c>
       <c r="E74" s="6">
-        <v>-15.51</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="5">
-        <v>-54.18</v>
+        <v>-33.23</v>
       </c>
       <c r="D75" s="5">
-        <v>-53.25</v>
+        <v>-21.28</v>
       </c>
       <c r="E75" s="7">
-        <v>0.93</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="5">
-        <v>-69.56999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="D76" s="5">
-        <v>41.77</v>
+        <v>62.44</v>
       </c>
       <c r="E76" s="7">
-        <v>111.34</v>
+        <v>58.64</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="5">
-        <v>-43.31</v>
+        <v>-57.17</v>
       </c>
       <c r="D77" s="5">
-        <v>52.49</v>
+        <v>2.1</v>
       </c>
       <c r="E77" s="7">
-        <v>95.8</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="5">
-        <v>-50.07</v>
+        <v>45.95</v>
       </c>
       <c r="D78" s="5">
+        <v>-4.45</v>
+      </c>
+      <c r="E78" s="6">
+        <v>-50.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>198.44</v>
+      </c>
+      <c r="D79" s="5">
+        <v>166.9</v>
+      </c>
+      <c r="E79" s="6">
+        <v>-31.54</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="5">
+        <v>-53.25</v>
+      </c>
+      <c r="D80" s="5">
+        <v>17.31</v>
+      </c>
+      <c r="E80" s="7">
+        <v>70.56</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="5">
+        <v>41.77</v>
+      </c>
+      <c r="D81" s="5">
+        <v>-58.2</v>
+      </c>
+      <c r="E81" s="6">
+        <v>-99.97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="5">
+        <v>52.49</v>
+      </c>
+      <c r="D82" s="5">
+        <v>-31.11</v>
+      </c>
+      <c r="E82" s="6">
+        <v>-83.59999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="5">
         <v>-31.77</v>
       </c>
-      <c r="E78" s="7">
-        <v>18.3</v>
+      <c r="D83" s="5">
+        <v>76.23</v>
+      </c>
+      <c r="E83" s="7">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3378,22 +3463,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="10">
-        <v>48.16</v>
+        <v>44.16</v>
       </c>
       <c r="C2" s="11">
         <v>9</v>
       </c>
       <c r="D2" s="10">
-        <v>45.3</v>
+        <v>43.5</v>
       </c>
       <c r="E2" s="10">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.1</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="H2" s="10">
         <v>55.4</v>
@@ -3530,31 +3615,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13">
-        <v>0.3673</v>
+        <v>0.3695000000000001</v>
       </c>
       <c r="B2" s="13">
-        <v>0.3096</v>
+        <v>0.3035</v>
       </c>
       <c r="C2" s="13">
-        <v>0.2037</v>
+        <v>0.2061</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1487</v>
+        <v>0.1414</v>
       </c>
       <c r="E2" s="13">
-        <v>0.1198</v>
+        <v>0.1154</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0638</v>
+        <v>0.0562</v>
       </c>
       <c r="G2" s="13">
-        <v>0.0482</v>
+        <v>0.0467</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.0417</v>
+        <v>-0.0454</v>
       </c>
       <c r="I2" s="13">
-        <v>-0.09759999999999999</v>
+        <v>-0.0974</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,58 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-3.8% → -1.6%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-3.8%</t>
+  </si>
+  <si>
+    <t>-1.6%</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>69.0 → 73.8</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>69.0</t>
+  </si>
+  <si>
+    <t>73.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -230,7 +281,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,20 +315,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,21 +444,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -403,7 +469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -902,10 +968,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>376.45</v>
+        <v>386.3</v>
       </c>
       <c r="D2">
-        <v>-1.8</v>
+        <v>2.62</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +980,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-23.2</v>
+        <v>-21.2</v>
       </c>
       <c r="H2">
-        <v>0.39</v>
+        <v>3.01</v>
       </c>
       <c r="I2">
-        <v>-3.62</v>
+        <v>0.55</v>
       </c>
       <c r="J2">
-        <v>-3.46</v>
+        <v>-1.21</v>
       </c>
       <c r="K2">
-        <v>-17.97</v>
+        <v>-18.53</v>
       </c>
       <c r="L2">
-        <v>-12.56</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="M2">
-        <v>11.54</v>
+        <v>11.63</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="P2">
-        <v>384.75</v>
+        <v>385.17</v>
       </c>
       <c r="Q2">
-        <v>384.42</v>
+        <v>384.19</v>
       </c>
       <c r="R2">
-        <v>400.73</v>
+        <v>399</v>
       </c>
       <c r="S2">
-        <v>434.15</v>
+        <v>434.09</v>
       </c>
       <c r="T2">
-        <v>-13.29</v>
+        <v>-11.01</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +1034,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.71</v>
+        <v>46.63</v>
       </c>
       <c r="Z2">
-        <v>-4.93</v>
+        <v>-4.47</v>
       </c>
       <c r="AA2">
-        <v>-6.12</v>
+        <v>-5.79</v>
       </c>
       <c r="AB2">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AC2">
-        <v>69.53</v>
+        <v>67.62</v>
       </c>
       <c r="AD2">
-        <v>76.16</v>
+        <v>72.33</v>
       </c>
       <c r="AE2">
-        <v>9.58</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AF2">
-        <v>-21.28</v>
+        <v>11.03</v>
       </c>
       <c r="AG2">
-        <v>395.01</v>
+        <v>394.39</v>
       </c>
       <c r="AH2">
-        <v>373.82</v>
+        <v>373.99</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1004,7 +1070,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.38</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1081,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2947.8</v>
+        <v>2950</v>
       </c>
       <c r="D3">
-        <v>-1.58</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1093,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-22.48</v>
+        <v>-22.42</v>
       </c>
       <c r="H3">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="I3">
-        <v>-3.18</v>
+        <v>-2.8</v>
       </c>
       <c r="J3">
-        <v>-11.58</v>
+        <v>-10.12</v>
       </c>
       <c r="K3">
-        <v>-4.82</v>
+        <v>-7.1</v>
       </c>
       <c r="L3">
-        <v>-17.54</v>
+        <v>-16.43</v>
       </c>
       <c r="M3">
-        <v>30.35</v>
+        <v>30.66</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>2999.1</v>
+        <v>2982.1</v>
       </c>
       <c r="Q3">
-        <v>3089.66</v>
+        <v>3074.21</v>
       </c>
       <c r="R3">
-        <v>3254.05</v>
+        <v>3249.01</v>
       </c>
       <c r="S3">
-        <v>3283.25</v>
+        <v>3279.67</v>
       </c>
       <c r="T3">
-        <v>-10.22</v>
+        <v>-10.05</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1147,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.2</v>
+        <v>28.59</v>
       </c>
       <c r="Z3">
-        <v>-79.61</v>
+        <v>-81.13</v>
       </c>
       <c r="AA3">
-        <v>-72.03</v>
+        <v>-73.84999999999999</v>
       </c>
       <c r="AB3">
-        <v>-7.58</v>
+        <v>-7.27</v>
       </c>
       <c r="AC3">
-        <v>67.51000000000001</v>
+        <v>46.99</v>
       </c>
       <c r="AD3">
-        <v>59.21</v>
+        <v>57.68</v>
       </c>
       <c r="AE3">
         <v>60.95</v>
       </c>
       <c r="AF3">
-        <v>62.44</v>
+        <v>11.81</v>
       </c>
       <c r="AG3">
-        <v>3248.04</v>
+        <v>3223.03</v>
       </c>
       <c r="AH3">
-        <v>2931.27</v>
+        <v>2925.38</v>
       </c>
       <c r="AI3">
-        <v>3152.24</v>
+        <v>3138.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>75.33</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1194,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>328.05</v>
+        <v>324.85</v>
       </c>
       <c r="D4">
-        <v>-1.12</v>
+        <v>-0.98</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,46 +1206,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-20.43</v>
+        <v>-21.21</v>
       </c>
       <c r="H4">
-        <v>20.19</v>
+        <v>19.01</v>
       </c>
       <c r="I4">
-        <v>-6.91</v>
+        <v>-6.81</v>
       </c>
       <c r="J4">
-        <v>-12.89</v>
+        <v>-12.91</v>
       </c>
       <c r="K4">
-        <v>4.09</v>
+        <v>2.15</v>
       </c>
       <c r="L4">
-        <v>16.27</v>
+        <v>16.18</v>
       </c>
       <c r="M4">
-        <v>14.14</v>
+        <v>13.71</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>336.28</v>
+        <v>331.53</v>
       </c>
       <c r="Q4">
-        <v>354.18</v>
+        <v>352.2</v>
       </c>
       <c r="R4">
-        <v>372.95</v>
+        <v>372.45</v>
       </c>
       <c r="S4">
-        <v>343.79</v>
+        <v>343.71</v>
       </c>
       <c r="T4">
-        <v>-4.58</v>
+        <v>-5.49</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,43 +1260,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>28.33</v>
+        <v>26.97</v>
       </c>
       <c r="Z4">
-        <v>-10.57</v>
+        <v>-11.35</v>
       </c>
       <c r="AA4">
-        <v>-7.88</v>
+        <v>-8.57</v>
       </c>
       <c r="AB4">
-        <v>-2.69</v>
+        <v>-2.78</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>7.36</v>
+        <v>1.54</v>
       </c>
       <c r="AE4">
-        <v>10.48</v>
+        <v>10.49</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>-48.71</v>
       </c>
       <c r="AG4">
-        <v>383.92</v>
+        <v>384.25</v>
       </c>
       <c r="AH4">
-        <v>324.44</v>
+        <v>320.16</v>
       </c>
       <c r="AI4">
-        <v>359.77</v>
+        <v>359.42</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>38.56</v>
+        <v>41.97</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1307,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>361</v>
+        <v>360.3</v>
       </c>
       <c r="D5">
-        <v>-0.58</v>
+        <v>-0.19</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1319,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.39</v>
+        <v>-14.56</v>
       </c>
       <c r="H5">
-        <v>22.68</v>
+        <v>22.45</v>
       </c>
       <c r="I5">
-        <v>0.54</v>
+        <v>1.04</v>
       </c>
       <c r="J5">
-        <v>-1.78</v>
+        <v>-1.46</v>
       </c>
       <c r="K5">
-        <v>-3.14</v>
+        <v>-3.2</v>
       </c>
       <c r="L5">
-        <v>-2.54</v>
+        <v>-3.44</v>
       </c>
       <c r="M5">
-        <v>5.62</v>
+        <v>5.89</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>358.29</v>
+        <v>359.03</v>
       </c>
       <c r="Q5">
-        <v>359.19</v>
+        <v>359.36</v>
       </c>
       <c r="R5">
-        <v>372.16</v>
+        <v>371.98</v>
       </c>
       <c r="S5">
-        <v>359.61</v>
+        <v>359.39</v>
       </c>
       <c r="T5">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1373,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>48.26</v>
+        <v>47.68</v>
       </c>
       <c r="Z5">
-        <v>-3.19</v>
+        <v>-2.9</v>
       </c>
       <c r="AA5">
-        <v>-4.12</v>
+        <v>-3.88</v>
       </c>
       <c r="AB5">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="AC5">
-        <v>85.47</v>
+        <v>90.55</v>
       </c>
       <c r="AD5">
-        <v>75.04000000000001</v>
+        <v>83.66</v>
       </c>
       <c r="AE5">
-        <v>11.84</v>
+        <v>11.68</v>
       </c>
       <c r="AF5">
-        <v>-4.45</v>
+        <v>-3.36</v>
       </c>
       <c r="AG5">
-        <v>372.03</v>
+        <v>372.16</v>
       </c>
       <c r="AH5">
-        <v>346.35</v>
+        <v>346.56</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1343,7 +1409,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>26.11</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1420,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>425.7</v>
+        <v>435.85</v>
       </c>
       <c r="D6">
-        <v>0.92</v>
+        <v>2.38</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,70 +1432,70 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-3.84</v>
+        <v>-1.55</v>
       </c>
       <c r="H6">
-        <v>52.28</v>
+        <v>55.91</v>
       </c>
       <c r="I6">
-        <v>6.35</v>
+        <v>4.63</v>
       </c>
       <c r="J6">
-        <v>8.390000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="K6">
-        <v>14.62</v>
+        <v>12.8</v>
       </c>
       <c r="L6">
-        <v>20.41</v>
+        <v>22.43</v>
       </c>
       <c r="M6">
-        <v>-9.74</v>
+        <v>-9.5</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>420.87</v>
+        <v>424.73</v>
       </c>
       <c r="Q6">
-        <v>402.83</v>
+        <v>405.27</v>
       </c>
       <c r="R6">
-        <v>404.36</v>
+        <v>405.25</v>
       </c>
       <c r="S6">
-        <v>374.57</v>
+        <v>375.14</v>
       </c>
       <c r="T6">
-        <v>13.65</v>
+        <v>16.18</v>
       </c>
       <c r="U6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V6" t="s">
         <v>48</v>
       </c>
       <c r="W6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
-        <v>68.95</v>
+        <v>73.8</v>
       </c>
       <c r="Z6">
-        <v>5.45</v>
+        <v>7.06</v>
       </c>
       <c r="AA6">
-        <v>2.02</v>
+        <v>3.03</v>
       </c>
       <c r="AB6">
-        <v>3.43</v>
+        <v>4.03</v>
       </c>
       <c r="AC6">
         <v>100</v>
@@ -1438,25 +1504,25 @@
         <v>100</v>
       </c>
       <c r="AE6">
-        <v>13.01</v>
+        <v>13.26</v>
       </c>
       <c r="AF6">
-        <v>166.9</v>
+        <v>93.64</v>
       </c>
       <c r="AG6">
-        <v>427.58</v>
+        <v>432.94</v>
       </c>
       <c r="AH6">
-        <v>378.09</v>
+        <v>377.6</v>
       </c>
       <c r="AI6">
-        <v>387.98</v>
+        <v>391.71</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>43.9</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,58 +1533,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>721.85</v>
+        <v>737.65</v>
       </c>
       <c r="D7">
-        <v>1.05</v>
+        <v>2.19</v>
       </c>
       <c r="E7">
-        <v>728.9</v>
+        <v>737.65</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>42.53</v>
+        <v>45.65</v>
       </c>
       <c r="I7">
-        <v>3.51</v>
+        <v>4.97</v>
       </c>
       <c r="J7">
-        <v>9.09</v>
+        <v>11.23</v>
       </c>
       <c r="K7">
-        <v>21.1</v>
+        <v>21.92</v>
       </c>
       <c r="L7">
-        <v>19.57</v>
+        <v>20.8</v>
       </c>
       <c r="M7">
-        <v>36.95</v>
+        <v>37.39</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P7">
-        <v>712.63</v>
+        <v>719.61</v>
       </c>
       <c r="Q7">
-        <v>697.46</v>
+        <v>701.86</v>
       </c>
       <c r="R7">
-        <v>640.6900000000001</v>
+        <v>643.84</v>
       </c>
       <c r="S7">
-        <v>597.9400000000001</v>
+        <v>598.87</v>
       </c>
       <c r="T7">
-        <v>20.72</v>
+        <v>23.17</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1533,43 +1599,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>64.33</v>
+        <v>68.17</v>
       </c>
       <c r="Z7">
-        <v>20.73</v>
+        <v>21.68</v>
       </c>
       <c r="AA7">
-        <v>22.18</v>
+        <v>22.08</v>
       </c>
       <c r="AB7">
-        <v>-1.45</v>
+        <v>-0.4</v>
       </c>
       <c r="AC7">
-        <v>27.55</v>
+        <v>37.33</v>
       </c>
       <c r="AD7">
-        <v>21.88</v>
+        <v>28.81</v>
       </c>
       <c r="AE7">
-        <v>25.27</v>
+        <v>26.77</v>
       </c>
       <c r="AF7">
-        <v>17.31</v>
+        <v>245.95</v>
       </c>
       <c r="AG7">
-        <v>743.4</v>
+        <v>745.3</v>
       </c>
       <c r="AH7">
-        <v>651.52</v>
+        <v>658.42</v>
       </c>
       <c r="AI7">
-        <v>649.01</v>
+        <v>664.6799999999999</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>41.53</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1646,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>194.49</v>
+        <v>194.25</v>
       </c>
       <c r="D8">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E8">
         <v>352.8</v>
@@ -1592,46 +1658,46 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.87</v>
+        <v>-44.94</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="I8">
-        <v>-2.3</v>
+        <v>-3.55</v>
       </c>
       <c r="J8">
-        <v>-7.99</v>
+        <v>-7.35</v>
       </c>
       <c r="K8">
-        <v>-17.89</v>
+        <v>-18.16</v>
       </c>
       <c r="L8">
-        <v>-45.07</v>
+        <v>-44.39</v>
       </c>
       <c r="M8">
-        <v>-4.54</v>
+        <v>-4.6</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>198.3</v>
+        <v>196.87</v>
       </c>
       <c r="Q8">
-        <v>200.32</v>
+        <v>199.62</v>
       </c>
       <c r="R8">
-        <v>212.95</v>
+        <v>212.27</v>
       </c>
       <c r="S8">
-        <v>250.61</v>
+        <v>250.03</v>
       </c>
       <c r="T8">
-        <v>-22.39</v>
+        <v>-22.31</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1712,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.22</v>
+        <v>32.95</v>
       </c>
       <c r="Z8">
-        <v>-4.88</v>
+        <v>-4.89</v>
       </c>
       <c r="AA8">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AB8">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="AC8">
-        <v>74.79000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="AD8">
-        <v>84.38</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="AE8">
-        <v>5.73</v>
+        <v>5.62</v>
       </c>
       <c r="AF8">
-        <v>-58.2</v>
+        <v>-62.05</v>
       </c>
       <c r="AG8">
-        <v>210.47</v>
+        <v>209.38</v>
       </c>
       <c r="AH8">
-        <v>190.17</v>
+        <v>189.86</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1682,7 +1748,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>36.41</v>
+        <v>36.42</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1759,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3548.2</v>
+        <v>3546.2</v>
       </c>
       <c r="D9">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1705,46 +1771,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.64</v>
+        <v>-18.69</v>
       </c>
       <c r="H9">
-        <v>7.23</v>
+        <v>7.17</v>
       </c>
       <c r="I9">
-        <v>-0.22</v>
+        <v>-0.37</v>
       </c>
       <c r="J9">
-        <v>0.1</v>
+        <v>-0.65</v>
       </c>
       <c r="K9">
-        <v>-12.14</v>
+        <v>-13.58</v>
       </c>
       <c r="L9">
-        <v>-15.6</v>
+        <v>-15.27</v>
       </c>
       <c r="M9">
-        <v>20.61</v>
+        <v>20.41</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="O9">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P9">
-        <v>3550.86</v>
+        <v>3548.24</v>
       </c>
       <c r="Q9">
-        <v>3567.38</v>
+        <v>3567.81</v>
       </c>
       <c r="R9">
-        <v>3581.4</v>
+        <v>3580.19</v>
       </c>
       <c r="S9">
-        <v>3674.48</v>
+        <v>3673.79</v>
       </c>
       <c r="T9">
-        <v>-3.44</v>
+        <v>-3.47</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1825,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.37</v>
+        <v>45.04</v>
       </c>
       <c r="Z9">
-        <v>-12.79</v>
+        <v>-12.93</v>
       </c>
       <c r="AA9">
-        <v>-12.88</v>
+        <v>-12.89</v>
       </c>
       <c r="AB9">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AC9">
-        <v>32.62</v>
+        <v>35.41</v>
       </c>
       <c r="AD9">
-        <v>30.4</v>
+        <v>32.61</v>
       </c>
       <c r="AE9">
-        <v>58.38</v>
+        <v>60.11</v>
       </c>
       <c r="AF9">
-        <v>-31.11</v>
+        <v>-44.55</v>
       </c>
       <c r="AG9">
-        <v>3633.31</v>
+        <v>3633.04</v>
       </c>
       <c r="AH9">
-        <v>3501.46</v>
+        <v>3502.58</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1795,7 +1861,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>18.29</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1872,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1510.5</v>
+        <v>1524</v>
       </c>
       <c r="D10">
-        <v>-2.06</v>
+        <v>0.89</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1884,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-14.58</v>
+        <v>-13.82</v>
       </c>
       <c r="H10">
-        <v>13.9</v>
+        <v>14.91</v>
       </c>
       <c r="I10">
-        <v>-2.65</v>
+        <v>-2.12</v>
       </c>
       <c r="J10">
-        <v>-7.95</v>
+        <v>-6.39</v>
       </c>
       <c r="K10">
-        <v>13.9</v>
+        <v>7.23</v>
       </c>
       <c r="L10">
-        <v>5.09</v>
+        <v>6.62</v>
       </c>
       <c r="M10">
-        <v>4.67</v>
+        <v>5.07</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P10">
-        <v>1540.14</v>
+        <v>1533.54</v>
       </c>
       <c r="Q10">
-        <v>1559.82</v>
+        <v>1554.12</v>
       </c>
       <c r="R10">
-        <v>1591.89</v>
+        <v>1590.85</v>
       </c>
       <c r="S10">
-        <v>1518.29</v>
+        <v>1518.07</v>
       </c>
       <c r="T10">
-        <v>-0.51</v>
+        <v>0.39</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1869,37 +1935,37 @@
         <v>47</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>37.97</v>
+        <v>41.67</v>
       </c>
       <c r="Z10">
-        <v>-14.28</v>
+        <v>-15.05</v>
       </c>
       <c r="AA10">
-        <v>-11.21</v>
+        <v>-11.98</v>
       </c>
       <c r="AB10">
         <v>-3.07</v>
       </c>
       <c r="AC10">
-        <v>58.22</v>
+        <v>44.21</v>
       </c>
       <c r="AD10">
-        <v>68.26000000000001</v>
+        <v>57.72</v>
       </c>
       <c r="AE10">
-        <v>37.87</v>
+        <v>38.67</v>
       </c>
       <c r="AF10">
-        <v>76.23</v>
+        <v>54.82</v>
       </c>
       <c r="AG10">
-        <v>1626.59</v>
+        <v>1611.61</v>
       </c>
       <c r="AH10">
-        <v>1493.06</v>
+        <v>1496.64</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1908,7 +1974,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>15.36</v>
+        <v>15.65</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1348 +2135,1426 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-2.83</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-3.46</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.63</v>
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-10.06</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-11.58</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.52</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-3.46</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-1.21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-11.58</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-10.12</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-13.46</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C12" s="7">
         <v>-12.89</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="7">
+        <v>-12.91</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C13" s="7">
         <v>-1.78</v>
       </c>
-      <c r="E10" s="6">
+      <c r="D13" s="7">
+        <v>-1.46</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="D14" s="7">
+        <v>11.34</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>9.09</v>
+      </c>
+      <c r="D15" s="7">
+        <v>11.23</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-7.99</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-7.35</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.65</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-7.95</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-6.39</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-3.62</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.55</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-3.18</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-2.8</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-6.91</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-6.81</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.04</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>6.35</v>
+      </c>
+      <c r="D23" s="7">
+        <v>4.63</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>3.51</v>
+      </c>
+      <c r="D24" s="7">
+        <v>4.97</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-2.3</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-3.55</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-0.22</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-0.37</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-2.65</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-2.12</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-12.56</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-17.54</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-16.43</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>16.27</v>
+      </c>
+      <c r="D30" s="7">
+        <v>16.18</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-2.54</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-3.44</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>20.41</v>
+      </c>
+      <c r="D32" s="7">
+        <v>22.43</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>19.57</v>
+      </c>
+      <c r="D33" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-45.07</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-44.39</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-15.6</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-15.27</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>5.09</v>
+      </c>
+      <c r="D36" s="7">
+        <v>6.62</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-17.97</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-18.53</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-4.82</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-7.1</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>4.09</v>
+      </c>
+      <c r="D39" s="7">
+        <v>2.15</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-3.14</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-3.2</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>14.62</v>
+      </c>
+      <c r="D41" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>21.1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>21.92</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-17.89</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-18.16</v>
+      </c>
+      <c r="E43" s="9">
         <v>-0.27</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-12.14</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-13.58</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>13.9</v>
+      </c>
+      <c r="D45" s="7">
+        <v>7.23</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-6.67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-23.2</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-21.2</v>
+      </c>
+      <c r="E46" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-22.48</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-22.42</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-20.43</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-21.21</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-14.39</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-14.56</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>7.71</v>
-      </c>
-      <c r="D11" s="5">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-3.84</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-1.55</v>
+      </c>
+      <c r="E50" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>11.26</v>
-      </c>
-      <c r="D12" s="5">
-        <v>9.09</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-0.97</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-7.25</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-7.99</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-44.87</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-44.94</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-18.64</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-18.69</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-2.7</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-5.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-14.58</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-13.82</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-3.62</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>376.45</v>
+      </c>
+      <c r="D55" s="7">
+        <v>386.3</v>
+      </c>
+      <c r="E55" s="8">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.97</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.18</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>2947.8</v>
+      </c>
+      <c r="D56" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E56" s="8">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-6.47</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-6.91</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>328.05</v>
+      </c>
+      <c r="D57" s="7">
+        <v>324.85</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.54</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>361</v>
+      </c>
+      <c r="D58" s="7">
+        <v>360.3</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>5.63</v>
-      </c>
-      <c r="D20" s="5">
-        <v>6.35</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>425.7</v>
+      </c>
+      <c r="D59" s="7">
+        <v>435.85</v>
+      </c>
+      <c r="E59" s="8">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="D21" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>721.85</v>
+      </c>
+      <c r="D60" s="7">
+        <v>737.65</v>
+      </c>
+      <c r="E60" s="8">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-2.71</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-2.3</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>194.49</v>
+      </c>
+      <c r="D61" s="7">
+        <v>194.25</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.22</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>3548.2</v>
+      </c>
+      <c r="D62" s="7">
+        <v>3546.2</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-1.05</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-2.65</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1510.5</v>
+      </c>
+      <c r="D63" s="7">
+        <v>1524</v>
+      </c>
+      <c r="E63" s="8">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>45</v>
+      </c>
+      <c r="E64" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>66</v>
+      </c>
+      <c r="D65" s="7">
+        <v>77</v>
+      </c>
+      <c r="E65" s="8">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-12.56</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
+        <v>45</v>
+      </c>
+      <c r="D66" s="7">
+        <v>23</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7">
+        <v>77</v>
+      </c>
+      <c r="D67" s="7">
+        <v>66</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>36.71</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46.63</v>
+      </c>
+      <c r="E68" s="8">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-17.14</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-17.54</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>28.2</v>
+      </c>
+      <c r="D69" s="7">
+        <v>28.59</v>
+      </c>
+      <c r="E69" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>28.33</v>
+      </c>
+      <c r="D70" s="7">
+        <v>26.97</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>48.26</v>
+      </c>
+      <c r="D71" s="7">
+        <v>47.68</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>68.95</v>
+      </c>
+      <c r="D72" s="7">
+        <v>73.8</v>
+      </c>
+      <c r="E72" s="8">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>64.33</v>
+      </c>
+      <c r="D73" s="7">
+        <v>68.17</v>
+      </c>
+      <c r="E73" s="8">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>33.22</v>
+      </c>
+      <c r="D74" s="7">
+        <v>32.95</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>45.37</v>
+      </c>
+      <c r="D75" s="7">
+        <v>45.04</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="7">
+        <v>37.97</v>
+      </c>
+      <c r="D76" s="7">
+        <v>41.67</v>
+      </c>
+      <c r="E76" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-21.28</v>
+      </c>
+      <c r="D77" s="7">
+        <v>11.03</v>
+      </c>
+      <c r="E77" s="8">
+        <v>32.31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>62.44</v>
+      </c>
+      <c r="D78" s="7">
+        <v>11.81</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-50.63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-48.71</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-50.81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-4.45</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-3.36</v>
+      </c>
+      <c r="E80" s="8">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>166.9</v>
+      </c>
+      <c r="D81" s="7">
+        <v>93.64</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-73.26000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
         <v>17.31</v>
       </c>
-      <c r="D27" s="5">
-        <v>16.27</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-3.26</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-2.54</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>17.44</v>
-      </c>
-      <c r="D29" s="5">
-        <v>20.41</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>18.96</v>
-      </c>
-      <c r="D30" s="5">
-        <v>19.57</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D82" s="7">
+        <v>245.95</v>
+      </c>
+      <c r="E82" s="8">
+        <v>228.64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-44.74</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-45.07</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>-58.2</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-62.05</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-21.01</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-15.6</v>
-      </c>
-      <c r="E32" s="7">
-        <v>5.41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-31.11</v>
+      </c>
+      <c r="D84" s="7">
+        <v>-44.55</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-13.44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>5.87</v>
-      </c>
-      <c r="D33" s="5">
-        <v>5.09</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-16.26</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-17.97</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-2.4</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-4.82</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>5.05</v>
-      </c>
-      <c r="D36" s="5">
-        <v>4.09</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-3.14</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>12.81</v>
-      </c>
-      <c r="D38" s="5">
-        <v>14.62</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>19.5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>21.1</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-17.7</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-17.89</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-11.13</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-12.14</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="D42" s="5">
-        <v>13.9</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4.11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-21.8</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-23.2</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-21.23</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-22.48</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-19.54</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-20.43</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-13.9</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-14.39</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-4.72</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-3.84</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-2</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-0.97</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-44.67</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-44.87</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-18.54</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-18.64</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-12.79</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-14.58</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>383.35</v>
-      </c>
-      <c r="D52" s="5">
-        <v>376.45</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>2995</v>
-      </c>
-      <c r="D53" s="5">
-        <v>2947.8</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-47.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>331.75</v>
-      </c>
-      <c r="D54" s="5">
-        <v>328.05</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>363.1</v>
-      </c>
-      <c r="D55" s="5">
-        <v>361</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>421.8</v>
-      </c>
-      <c r="D56" s="5">
-        <v>425.7</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>714.35</v>
-      </c>
-      <c r="D57" s="5">
-        <v>721.85</v>
-      </c>
-      <c r="E57" s="7">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>195.92</v>
-      </c>
-      <c r="D58" s="5">
-        <v>194.49</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>3552.5</v>
-      </c>
-      <c r="D59" s="5">
-        <v>3548.2</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1542.2</v>
-      </c>
-      <c r="D60" s="5">
-        <v>1510.5</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-31.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>34</v>
-      </c>
-      <c r="D61" s="5">
-        <v>23</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>45</v>
-      </c>
-      <c r="D62" s="5">
-        <v>34</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5">
-        <v>77</v>
-      </c>
-      <c r="D63" s="5">
-        <v>66</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="5">
-        <v>23</v>
-      </c>
-      <c r="D64" s="5">
-        <v>45</v>
-      </c>
-      <c r="E64" s="7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="5">
-        <v>66</v>
-      </c>
-      <c r="D65" s="5">
-        <v>77</v>
-      </c>
-      <c r="E65" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>41.76</v>
-      </c>
-      <c r="D66" s="5">
-        <v>36.71</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>31.58</v>
-      </c>
-      <c r="D67" s="5">
-        <v>28.2</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-3.38</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>29.96</v>
-      </c>
-      <c r="D68" s="5">
-        <v>28.33</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>49.96</v>
-      </c>
-      <c r="D69" s="5">
-        <v>48.26</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>66.75</v>
-      </c>
-      <c r="D70" s="5">
-        <v>68.95</v>
-      </c>
-      <c r="E70" s="7">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>62.33</v>
-      </c>
-      <c r="D71" s="5">
-        <v>64.33</v>
-      </c>
-      <c r="E71" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="5">
-        <v>34.83</v>
-      </c>
-      <c r="D72" s="5">
-        <v>33.22</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46.03</v>
-      </c>
-      <c r="D73" s="5">
-        <v>45.37</v>
-      </c>
-      <c r="E73" s="6">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="5">
-        <v>44.06</v>
-      </c>
-      <c r="D74" s="5">
-        <v>37.97</v>
-      </c>
-      <c r="E74" s="6">
-        <v>-6.09</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="B85" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="5">
-        <v>-33.23</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-21.28</v>
-      </c>
-      <c r="E75" s="7">
-        <v>11.95</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>3.8</v>
-      </c>
-      <c r="D76" s="5">
-        <v>62.44</v>
-      </c>
-      <c r="E76" s="7">
-        <v>58.64</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-57.17</v>
-      </c>
-      <c r="D77" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="E77" s="7">
-        <v>59.27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>45.95</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-4.45</v>
-      </c>
-      <c r="E78" s="6">
-        <v>-50.4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>198.44</v>
-      </c>
-      <c r="D79" s="5">
-        <v>166.9</v>
-      </c>
-      <c r="E79" s="6">
-        <v>-31.54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-53.25</v>
-      </c>
-      <c r="D80" s="5">
-        <v>17.31</v>
-      </c>
-      <c r="E80" s="7">
-        <v>70.56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="5">
-        <v>41.77</v>
-      </c>
-      <c r="D81" s="5">
-        <v>-58.2</v>
-      </c>
-      <c r="E81" s="6">
-        <v>-99.97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="5">
-        <v>52.49</v>
-      </c>
-      <c r="D82" s="5">
-        <v>-31.11</v>
-      </c>
-      <c r="E82" s="6">
-        <v>-83.59999999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="5">
-        <v>-31.77</v>
-      </c>
-      <c r="D83" s="5">
+      <c r="C85" s="7">
         <v>76.23</v>
       </c>
-      <c r="E83" s="7">
-        <v>108</v>
+      <c r="D85" s="7">
+        <v>54.82</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-21.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3430,61 +3574,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
-        <v>44.16</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>43.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-3.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.2</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>45.7</v>
+      </c>
+      <c r="E2" s="12">
+        <v>40</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-1.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-1.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
-        <v>10</v>
+      <c r="I2" s="12">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3585,61 +3729,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3695000000000001</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3035</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2061</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1414</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1154</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0562</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0467</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0454</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.0974</v>
+      <c r="A2" s="15">
+        <v>0.3739</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3066</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2041</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1371</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1163</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.05889999999999999</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0507</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.046</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.095</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,43 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.8% → -1.6%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>73.8 → 55.8</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>73.8</t>
+  </si>
+  <si>
+    <t>55.8</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.6% → -5.9%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.6%</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>69.0 → 73.8</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>69.0</t>
-  </si>
-  <si>
-    <t>73.8</t>
+    <t>-5.9%</t>
+  </si>
+  <si>
+    <t>0.0% → -5.3%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-5.3%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -315,14 +315,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -330,6 +323,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -362,19 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -452,10 +452,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -968,10 +967,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>386.3</v>
+        <v>376.35</v>
       </c>
       <c r="D2">
-        <v>2.62</v>
+        <v>-2.58</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -980,46 +979,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-21.2</v>
+        <v>-23.23</v>
       </c>
       <c r="H2">
-        <v>3.01</v>
+        <v>0.36</v>
       </c>
       <c r="I2">
-        <v>0.55</v>
+        <v>-3.24</v>
       </c>
       <c r="J2">
-        <v>-1.21</v>
+        <v>-3.71</v>
       </c>
       <c r="K2">
-        <v>-18.53</v>
+        <v>-20.1</v>
       </c>
       <c r="L2">
-        <v>-8.949999999999999</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="M2">
-        <v>11.63</v>
+        <v>10.69</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>385.17</v>
+        <v>382.65</v>
       </c>
       <c r="Q2">
-        <v>384.19</v>
+        <v>383.76</v>
       </c>
       <c r="R2">
-        <v>399</v>
+        <v>397.08</v>
       </c>
       <c r="S2">
-        <v>434.09</v>
+        <v>433.99</v>
       </c>
       <c r="T2">
-        <v>-11.01</v>
+        <v>-13.28</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1034,34 +1033,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.63</v>
+        <v>39.84</v>
       </c>
       <c r="Z2">
-        <v>-4.47</v>
+        <v>-4.85</v>
       </c>
       <c r="AA2">
-        <v>-5.79</v>
+        <v>-5.6</v>
       </c>
       <c r="AB2">
-        <v>1.32</v>
+        <v>0.75</v>
       </c>
       <c r="AC2">
-        <v>67.62</v>
+        <v>65.59</v>
       </c>
       <c r="AD2">
-        <v>72.33</v>
+        <v>67.58</v>
       </c>
       <c r="AE2">
-        <v>9.869999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="AF2">
-        <v>11.03</v>
+        <v>0.21</v>
       </c>
       <c r="AG2">
-        <v>394.39</v>
+        <v>394.53</v>
       </c>
       <c r="AH2">
-        <v>373.99</v>
+        <v>372.98</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1070,7 +1069,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>29.26</v>
+        <v>30.06</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1081,58 +1080,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2950</v>
+        <v>2860</v>
       </c>
       <c r="D3">
-        <v>0.07000000000000001</v>
+        <v>-3.05</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
       </c>
       <c r="F3">
-        <v>2931.1</v>
+        <v>2860</v>
       </c>
       <c r="G3">
-        <v>-22.42</v>
+        <v>-24.78</v>
       </c>
       <c r="H3">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.8</v>
+        <v>-4.11</v>
       </c>
       <c r="J3">
-        <v>-10.12</v>
+        <v>-12.24</v>
       </c>
       <c r="K3">
-        <v>-7.1</v>
+        <v>-8.83</v>
       </c>
       <c r="L3">
-        <v>-16.43</v>
+        <v>-15.8</v>
       </c>
       <c r="M3">
-        <v>30.66</v>
+        <v>29.07</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P3">
-        <v>2982.1</v>
+        <v>2957.56</v>
       </c>
       <c r="Q3">
-        <v>3074.21</v>
+        <v>3057.71</v>
       </c>
       <c r="R3">
-        <v>3249.01</v>
+        <v>3242.71</v>
       </c>
       <c r="S3">
-        <v>3279.67</v>
+        <v>3275.58</v>
       </c>
       <c r="T3">
-        <v>-10.05</v>
+        <v>-12.69</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1147,43 +1146,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.59</v>
+        <v>23.14</v>
       </c>
       <c r="Z3">
-        <v>-81.13</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="AA3">
-        <v>-73.84999999999999</v>
+        <v>-76.8</v>
       </c>
       <c r="AB3">
-        <v>-7.27</v>
+        <v>-11.77</v>
       </c>
       <c r="AC3">
-        <v>46.99</v>
+        <v>24.39</v>
       </c>
       <c r="AD3">
-        <v>57.68</v>
+        <v>46.3</v>
       </c>
       <c r="AE3">
-        <v>60.95</v>
+        <v>66.45</v>
       </c>
       <c r="AF3">
-        <v>11.81</v>
+        <v>169.21</v>
       </c>
       <c r="AG3">
-        <v>3223.03</v>
+        <v>3224.56</v>
       </c>
       <c r="AH3">
-        <v>2925.38</v>
+        <v>2890.85</v>
       </c>
       <c r="AI3">
-        <v>3138.35</v>
+        <v>3069.06</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>77.06999999999999</v>
+        <v>79.31999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1194,10 +1193,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>324.85</v>
+        <v>319.75</v>
       </c>
       <c r="D4">
-        <v>-0.98</v>
+        <v>-1.57</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1206,46 +1205,46 @@
         <v>272.95</v>
       </c>
       <c r="G4">
-        <v>-21.21</v>
+        <v>-22.45</v>
       </c>
       <c r="H4">
-        <v>19.01</v>
+        <v>17.15</v>
       </c>
       <c r="I4">
-        <v>-6.81</v>
+        <v>-5.93</v>
       </c>
       <c r="J4">
-        <v>-12.91</v>
+        <v>-12.25</v>
       </c>
       <c r="K4">
-        <v>2.15</v>
+        <v>-4.28</v>
       </c>
       <c r="L4">
-        <v>16.18</v>
+        <v>14.3</v>
       </c>
       <c r="M4">
-        <v>13.71</v>
+        <v>13.22</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>331.53</v>
+        <v>327.5</v>
       </c>
       <c r="Q4">
-        <v>352.2</v>
+        <v>349.75</v>
       </c>
       <c r="R4">
-        <v>372.45</v>
+        <v>371.28</v>
       </c>
       <c r="S4">
-        <v>343.71</v>
+        <v>343.58</v>
       </c>
       <c r="T4">
-        <v>-5.49</v>
+        <v>-6.94</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1260,43 +1259,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.97</v>
+        <v>24.9</v>
       </c>
       <c r="Z4">
-        <v>-11.35</v>
+        <v>-12.24</v>
       </c>
       <c r="AA4">
-        <v>-8.57</v>
+        <v>-9.31</v>
       </c>
       <c r="AB4">
-        <v>-2.78</v>
+        <v>-2.93</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>10.49</v>
+        <v>10.45</v>
       </c>
       <c r="AF4">
-        <v>-48.71</v>
+        <v>75.02</v>
       </c>
       <c r="AG4">
-        <v>384.25</v>
+        <v>383.88</v>
       </c>
       <c r="AH4">
-        <v>320.16</v>
+        <v>315.62</v>
       </c>
       <c r="AI4">
-        <v>359.42</v>
+        <v>351.78</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>41.97</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1307,10 +1306,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>360.3</v>
+        <v>351.15</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>-2.54</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1319,46 +1318,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.56</v>
+        <v>-16.73</v>
       </c>
       <c r="H5">
-        <v>22.45</v>
+        <v>19.34</v>
       </c>
       <c r="I5">
-        <v>1.04</v>
+        <v>-0.78</v>
       </c>
       <c r="J5">
-        <v>-1.46</v>
+        <v>-1.62</v>
       </c>
       <c r="K5">
-        <v>-3.2</v>
+        <v>-5.08</v>
       </c>
       <c r="L5">
-        <v>-3.44</v>
+        <v>-2.42</v>
       </c>
       <c r="M5">
-        <v>5.89</v>
+        <v>5.54</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>359.03</v>
+        <v>358.48</v>
       </c>
       <c r="Q5">
-        <v>359.36</v>
+        <v>358.97</v>
       </c>
       <c r="R5">
-        <v>371.98</v>
+        <v>371.52</v>
       </c>
       <c r="S5">
-        <v>359.39</v>
+        <v>359.14</v>
       </c>
       <c r="T5">
-        <v>0.25</v>
+        <v>-2.23</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1370,37 +1369,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>47.68</v>
+        <v>40.77</v>
       </c>
       <c r="Z5">
-        <v>-2.9</v>
+        <v>-3.37</v>
       </c>
       <c r="AA5">
-        <v>-3.88</v>
+        <v>-3.77</v>
       </c>
       <c r="AB5">
-        <v>0.98</v>
+        <v>0.41</v>
       </c>
       <c r="AC5">
-        <v>90.55</v>
+        <v>75.53</v>
       </c>
       <c r="AD5">
-        <v>83.66</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="AE5">
-        <v>11.68</v>
+        <v>12.21</v>
       </c>
       <c r="AF5">
-        <v>-3.36</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AG5">
-        <v>372.16</v>
+        <v>372.29</v>
       </c>
       <c r="AH5">
-        <v>346.56</v>
+        <v>345.65</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1409,7 +1408,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>26.75</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1420,10 +1419,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>435.85</v>
+        <v>416.4</v>
       </c>
       <c r="D6">
-        <v>2.38</v>
+        <v>-4.46</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1432,46 +1431,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-1.55</v>
+        <v>-5.94</v>
       </c>
       <c r="H6">
-        <v>55.91</v>
+        <v>48.95</v>
       </c>
       <c r="I6">
-        <v>4.63</v>
+        <v>-0.87</v>
       </c>
       <c r="J6">
-        <v>11.34</v>
+        <v>7.54</v>
       </c>
       <c r="K6">
-        <v>12.8</v>
+        <v>5.52</v>
       </c>
       <c r="L6">
-        <v>22.43</v>
+        <v>20.61</v>
       </c>
       <c r="M6">
-        <v>-9.5</v>
+        <v>-10.29</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>424.73</v>
+        <v>424</v>
       </c>
       <c r="Q6">
-        <v>405.27</v>
+        <v>406.46</v>
       </c>
       <c r="R6">
-        <v>405.25</v>
+        <v>405.54</v>
       </c>
       <c r="S6">
-        <v>375.14</v>
+        <v>375.6</v>
       </c>
       <c r="T6">
-        <v>16.18</v>
+        <v>10.86</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1486,34 +1485,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>73.8</v>
+        <v>55.8</v>
       </c>
       <c r="Z6">
-        <v>7.06</v>
+        <v>6.69</v>
       </c>
       <c r="AA6">
-        <v>3.03</v>
+        <v>3.76</v>
       </c>
       <c r="AB6">
-        <v>4.03</v>
+        <v>2.93</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="AD6">
-        <v>100</v>
+        <v>94.17</v>
       </c>
       <c r="AE6">
-        <v>13.26</v>
+        <v>14.15</v>
       </c>
       <c r="AF6">
-        <v>93.64</v>
+        <v>20.83</v>
       </c>
       <c r="AG6">
-        <v>432.94</v>
+        <v>433.87</v>
       </c>
       <c r="AH6">
-        <v>377.6</v>
+        <v>379.06</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1522,7 +1521,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>47.85</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1533,10 +1532,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>737.65</v>
+        <v>698.75</v>
       </c>
       <c r="D7">
-        <v>2.19</v>
+        <v>-5.27</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1545,46 +1544,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-5.27</v>
       </c>
       <c r="H7">
-        <v>45.65</v>
+        <v>37.97</v>
       </c>
       <c r="I7">
-        <v>4.97</v>
+        <v>-1.38</v>
       </c>
       <c r="J7">
-        <v>11.23</v>
+        <v>7.57</v>
       </c>
       <c r="K7">
-        <v>21.92</v>
+        <v>14.54</v>
       </c>
       <c r="L7">
-        <v>20.8</v>
+        <v>17.08</v>
       </c>
       <c r="M7">
-        <v>37.39</v>
+        <v>35.4</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P7">
-        <v>719.61</v>
+        <v>717.65</v>
       </c>
       <c r="Q7">
-        <v>701.86</v>
+        <v>703.55</v>
       </c>
       <c r="R7">
-        <v>643.84</v>
+        <v>646.3099999999999</v>
       </c>
       <c r="S7">
-        <v>598.87</v>
+        <v>599.5599999999999</v>
       </c>
       <c r="T7">
-        <v>23.17</v>
+        <v>16.54</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1599,34 +1598,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>68.17</v>
+        <v>53.03</v>
       </c>
       <c r="Z7">
-        <v>21.68</v>
+        <v>19.08</v>
       </c>
       <c r="AA7">
-        <v>22.08</v>
+        <v>21.48</v>
       </c>
       <c r="AB7">
-        <v>-0.4</v>
+        <v>-2.4</v>
       </c>
       <c r="AC7">
-        <v>37.33</v>
+        <v>29.74</v>
       </c>
       <c r="AD7">
-        <v>28.81</v>
+        <v>31.54</v>
       </c>
       <c r="AE7">
-        <v>26.77</v>
+        <v>28.83</v>
       </c>
       <c r="AF7">
-        <v>245.95</v>
+        <v>-10.13</v>
       </c>
       <c r="AG7">
-        <v>745.3</v>
+        <v>743.4400000000001</v>
       </c>
       <c r="AH7">
-        <v>658.42</v>
+        <v>663.65</v>
       </c>
       <c r="AI7">
         <v>664.6799999999999</v>
@@ -1635,7 +1634,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>44.66</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1646,10 +1645,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>194.25</v>
+        <v>194.85</v>
       </c>
       <c r="D8">
-        <v>-0.12</v>
+        <v>0.31</v>
       </c>
       <c r="E8">
         <v>352.8</v>
@@ -1658,25 +1657,25 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.94</v>
+        <v>-44.77</v>
       </c>
       <c r="H8">
-        <v>0.96</v>
+        <v>1.27</v>
       </c>
       <c r="I8">
-        <v>-3.55</v>
+        <v>-2.43</v>
       </c>
       <c r="J8">
-        <v>-7.35</v>
+        <v>-6.46</v>
       </c>
       <c r="K8">
-        <v>-18.16</v>
+        <v>-17.63</v>
       </c>
       <c r="L8">
-        <v>-44.39</v>
+        <v>-43.04</v>
       </c>
       <c r="M8">
-        <v>-4.6</v>
+        <v>-4.41</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1685,19 +1684,19 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>196.87</v>
+        <v>195.9</v>
       </c>
       <c r="Q8">
-        <v>199.62</v>
+        <v>199.03</v>
       </c>
       <c r="R8">
-        <v>212.27</v>
+        <v>211.94</v>
       </c>
       <c r="S8">
-        <v>250.03</v>
+        <v>249.43</v>
       </c>
       <c r="T8">
-        <v>-22.31</v>
+        <v>-21.88</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1712,34 +1711,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.95</v>
+        <v>34.41</v>
       </c>
       <c r="Z8">
-        <v>-4.89</v>
+        <v>-4.8</v>
       </c>
       <c r="AA8">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="AB8">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="AC8">
-        <v>64.19</v>
+        <v>63.55</v>
       </c>
       <c r="AD8">
-        <v>74.34999999999999</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="AE8">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
       <c r="AF8">
-        <v>-62.05</v>
+        <v>22.76</v>
       </c>
       <c r="AG8">
-        <v>209.38</v>
+        <v>208.43</v>
       </c>
       <c r="AH8">
-        <v>189.86</v>
+        <v>189.63</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1748,7 +1747,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>36.42</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1759,10 +1758,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3546.2</v>
+        <v>3542.7</v>
       </c>
       <c r="D9">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1771,46 +1770,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.69</v>
+        <v>-18.77</v>
       </c>
       <c r="H9">
-        <v>7.17</v>
+        <v>7.07</v>
       </c>
       <c r="I9">
-        <v>-0.37</v>
+        <v>-0.17</v>
       </c>
       <c r="J9">
-        <v>-0.65</v>
+        <v>0.14</v>
       </c>
       <c r="K9">
-        <v>-13.58</v>
+        <v>-10.08</v>
       </c>
       <c r="L9">
-        <v>-15.27</v>
+        <v>-13.4</v>
       </c>
       <c r="M9">
-        <v>20.41</v>
+        <v>19.97</v>
       </c>
       <c r="N9">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P9">
-        <v>3548.24</v>
+        <v>3547.06</v>
       </c>
       <c r="Q9">
-        <v>3567.81</v>
+        <v>3567.9</v>
       </c>
       <c r="R9">
-        <v>3580.19</v>
+        <v>3579.3</v>
       </c>
       <c r="S9">
-        <v>3673.79</v>
+        <v>3672.94</v>
       </c>
       <c r="T9">
-        <v>-3.47</v>
+        <v>-3.55</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1825,34 +1824,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.04</v>
+        <v>44.44</v>
       </c>
       <c r="Z9">
-        <v>-12.93</v>
+        <v>-13.18</v>
       </c>
       <c r="AA9">
-        <v>-12.89</v>
+        <v>-12.95</v>
       </c>
       <c r="AB9">
-        <v>-0.04</v>
+        <v>-0.23</v>
       </c>
       <c r="AC9">
-        <v>35.41</v>
+        <v>32.88</v>
       </c>
       <c r="AD9">
-        <v>32.61</v>
+        <v>33.64</v>
       </c>
       <c r="AE9">
-        <v>60.11</v>
+        <v>61.63</v>
       </c>
       <c r="AF9">
-        <v>-44.55</v>
+        <v>38.46</v>
       </c>
       <c r="AG9">
-        <v>3633.04</v>
+        <v>3632.97</v>
       </c>
       <c r="AH9">
-        <v>3502.58</v>
+        <v>3502.83</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1861,7 +1860,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>15.99</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1872,10 +1871,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="D10">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1884,46 +1883,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-13.82</v>
+        <v>-13.31</v>
       </c>
       <c r="H10">
-        <v>14.91</v>
+        <v>15.59</v>
       </c>
       <c r="I10">
-        <v>-2.12</v>
+        <v>-0.65</v>
       </c>
       <c r="J10">
-        <v>-6.39</v>
+        <v>-6.41</v>
       </c>
       <c r="K10">
-        <v>7.23</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L10">
-        <v>6.62</v>
+        <v>10.04</v>
       </c>
       <c r="M10">
-        <v>5.07</v>
+        <v>5.34</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="P10">
-        <v>1533.54</v>
+        <v>1531.54</v>
       </c>
       <c r="Q10">
-        <v>1554.12</v>
+        <v>1549.62</v>
       </c>
       <c r="R10">
-        <v>1590.85</v>
+        <v>1590.29</v>
       </c>
       <c r="S10">
-        <v>1518.07</v>
+        <v>1517.84</v>
       </c>
       <c r="T10">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1938,34 +1937,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>41.67</v>
+        <v>44.06</v>
       </c>
       <c r="Z10">
-        <v>-15.05</v>
+        <v>-14.77</v>
       </c>
       <c r="AA10">
-        <v>-11.98</v>
+        <v>-12.53</v>
       </c>
       <c r="AB10">
-        <v>-3.07</v>
+        <v>-2.23</v>
       </c>
       <c r="AC10">
-        <v>44.21</v>
+        <v>39.7</v>
       </c>
       <c r="AD10">
-        <v>57.72</v>
+        <v>47.38</v>
       </c>
       <c r="AE10">
-        <v>38.67</v>
+        <v>38.96</v>
       </c>
       <c r="AF10">
-        <v>54.82</v>
+        <v>48.27</v>
       </c>
       <c r="AG10">
-        <v>1611.61</v>
+        <v>1597.73</v>
       </c>
       <c r="AH10">
-        <v>1496.64</v>
+        <v>1501.52</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1974,7 +1973,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>15.65</v>
+        <v>16.68</v>
       </c>
     </row>
   </sheetData>
@@ -2178,1383 +2177,1380 @@
         <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-10.12</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-12.24</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-12.91</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-12.25</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-1.46</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-1.62</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>11.34</v>
+      </c>
+      <c r="D13" s="6">
+        <v>7.54</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>11.23</v>
+      </c>
+      <c r="D14" s="6">
+        <v>7.57</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-7.35</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.65</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.14</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.39</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.41</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.55</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.24</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.8</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-4.11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-6.81</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-5.93</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.04</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.78</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4.63</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-0.87</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>4.97</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-6.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.55</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.43</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-0.37</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-0.17</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-2.12</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-0.65</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-16.43</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-15.8</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>16.18</v>
+      </c>
+      <c r="D29" s="6">
+        <v>14.3</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-3.44</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-2.42</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>22.43</v>
+      </c>
+      <c r="D31" s="6">
+        <v>20.61</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>20.8</v>
+      </c>
+      <c r="D32" s="6">
+        <v>17.08</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-44.39</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-43.04</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-15.27</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-13.4</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>6.62</v>
+      </c>
+      <c r="D35" s="6">
+        <v>10.04</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-18.53</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-20.1</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-7.1</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-8.83</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2.15</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-6.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-3.2</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-5.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="D40" s="6">
+        <v>5.52</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-7.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>21.92</v>
+      </c>
+      <c r="D41" s="6">
+        <v>14.54</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-7.38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-18.16</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-17.63</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-13.58</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="E43" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>7.23</v>
+      </c>
+      <c r="D44" s="6">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-21.2</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-23.23</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-22.42</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-24.78</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-21.21</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-22.45</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-14.56</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-16.73</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-5.94</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-4.39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-5.27</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-5.27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-44.94</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-44.77</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-18.69</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-18.77</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-13.82</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-13.31</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>386.3</v>
+      </c>
+      <c r="D54" s="6">
+        <v>376.35</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-9.949999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>2950</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2860</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>324.85</v>
+      </c>
+      <c r="D56" s="6">
+        <v>319.75</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>360.3</v>
+      </c>
+      <c r="D57" s="6">
+        <v>351.15</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-9.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>435.85</v>
+      </c>
+      <c r="D58" s="6">
+        <v>416.4</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-19.45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>737.65</v>
+      </c>
+      <c r="D59" s="6">
+        <v>698.75</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-38.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>194.25</v>
+      </c>
+      <c r="D60" s="6">
+        <v>194.85</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>3546.2</v>
+      </c>
+      <c r="D61" s="6">
+        <v>3542.7</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1524</v>
+      </c>
+      <c r="D62" s="6">
+        <v>1533</v>
+      </c>
+      <c r="E62" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>45</v>
+      </c>
+      <c r="D63" s="6">
+        <v>34</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>34</v>
+      </c>
+      <c r="D64" s="6">
+        <v>23</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6">
+        <v>77</v>
+      </c>
+      <c r="D65" s="6">
         <v>66</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="E65" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="6">
+        <v>23</v>
+      </c>
+      <c r="D66" s="6">
+        <v>45</v>
+      </c>
+      <c r="E66" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="6">
+        <v>66</v>
+      </c>
+      <c r="D67" s="6">
+        <v>77</v>
+      </c>
+      <c r="E67" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-3.46</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>46.63</v>
+      </c>
+      <c r="D68" s="6">
+        <v>39.84</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-6.79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-11.58</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-10.12</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>28.59</v>
+      </c>
+      <c r="D69" s="6">
+        <v>23.14</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>26.97</v>
+      </c>
+      <c r="D70" s="6">
+        <v>24.9</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>47.68</v>
+      </c>
+      <c r="D71" s="6">
+        <v>40.77</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-6.91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>73.8</v>
+      </c>
+      <c r="D72" s="6">
+        <v>55.8</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>68.17</v>
+      </c>
+      <c r="D73" s="6">
+        <v>53.03</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-15.14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="6">
+        <v>32.95</v>
+      </c>
+      <c r="D74" s="6">
+        <v>34.41</v>
+      </c>
+      <c r="E74" s="8">
         <v>1.46</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="6">
+        <v>45.04</v>
+      </c>
+      <c r="D75" s="6">
+        <v>44.44</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="6">
+        <v>41.67</v>
+      </c>
+      <c r="D76" s="6">
+        <v>44.06</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>11.03</v>
+      </c>
+      <c r="D77" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-10.82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>11.81</v>
+      </c>
+      <c r="D78" s="6">
+        <v>169.21</v>
+      </c>
+      <c r="E78" s="8">
+        <v>157.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-12.89</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-12.91</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-48.71</v>
+      </c>
+      <c r="D79" s="6">
+        <v>75.02</v>
+      </c>
+      <c r="E79" s="8">
+        <v>123.73</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-1.78</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-1.46</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-3.36</v>
+      </c>
+      <c r="D80" s="6">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E80" s="8">
+        <v>12.89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="D14" s="7">
-        <v>11.34</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>93.64</v>
+      </c>
+      <c r="D81" s="6">
+        <v>20.83</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-72.81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>9.09</v>
-      </c>
-      <c r="D15" s="7">
-        <v>11.23</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
+        <v>245.95</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-10.13</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-256.08</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-7.99</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-7.35</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B83" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="6">
+        <v>-62.05</v>
+      </c>
+      <c r="D83" s="6">
+        <v>22.76</v>
+      </c>
+      <c r="E83" s="8">
+        <v>84.81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-0.65</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="6">
+        <v>-44.55</v>
+      </c>
+      <c r="D84" s="6">
+        <v>38.46</v>
+      </c>
+      <c r="E84" s="8">
+        <v>83.01000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-7.95</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.39</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-3.62</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.55</v>
-      </c>
-      <c r="E19" s="8">
-        <v>4.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-3.18</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.8</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-6.91</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-6.81</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.54</v>
-      </c>
-      <c r="D22" s="7">
-        <v>1.04</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>6.35</v>
-      </c>
-      <c r="D23" s="7">
-        <v>4.63</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>3.51</v>
-      </c>
-      <c r="D24" s="7">
-        <v>4.97</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-2.3</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.55</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.22</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.37</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-2.65</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-2.12</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-12.56</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E28" s="8">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-17.54</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-16.43</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>16.27</v>
-      </c>
-      <c r="D30" s="7">
-        <v>16.18</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-2.54</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-3.44</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>20.41</v>
-      </c>
-      <c r="D32" s="7">
-        <v>22.43</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>19.57</v>
-      </c>
-      <c r="D33" s="7">
-        <v>20.8</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-45.07</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-44.39</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-15.6</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-15.27</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>5.09</v>
-      </c>
-      <c r="D36" s="7">
-        <v>6.62</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-17.97</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-18.53</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-4.82</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-7.1</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>4.09</v>
-      </c>
-      <c r="D39" s="7">
-        <v>2.15</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-3.14</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-3.2</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>14.62</v>
-      </c>
-      <c r="D41" s="7">
-        <v>12.8</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>21.1</v>
-      </c>
-      <c r="D42" s="7">
-        <v>21.92</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-17.89</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-18.16</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-12.14</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-13.58</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>13.9</v>
-      </c>
-      <c r="D45" s="7">
-        <v>7.23</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-6.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-23.2</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-21.2</v>
-      </c>
-      <c r="E46" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-22.48</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-22.42</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-20.43</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-21.21</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-14.39</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-14.56</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-3.84</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-1.55</v>
-      </c>
-      <c r="E50" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-0.97</v>
-      </c>
-      <c r="D51" s="7">
-        <v>0</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-44.87</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-44.94</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-18.64</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-18.69</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-14.58</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-13.82</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>376.45</v>
-      </c>
-      <c r="D55" s="7">
-        <v>386.3</v>
-      </c>
-      <c r="E55" s="8">
-        <v>9.85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>2947.8</v>
-      </c>
-      <c r="D56" s="7">
-        <v>2950</v>
-      </c>
-      <c r="E56" s="8">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>328.05</v>
-      </c>
-      <c r="D57" s="7">
-        <v>324.85</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>361</v>
-      </c>
-      <c r="D58" s="7">
-        <v>360.3</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>425.7</v>
-      </c>
-      <c r="D59" s="7">
-        <v>435.85</v>
-      </c>
-      <c r="E59" s="8">
-        <v>10.15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>721.85</v>
-      </c>
-      <c r="D60" s="7">
-        <v>737.65</v>
-      </c>
-      <c r="E60" s="8">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>194.49</v>
-      </c>
-      <c r="D61" s="7">
-        <v>194.25</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>3548.2</v>
-      </c>
-      <c r="D62" s="7">
-        <v>3546.2</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>1510.5</v>
-      </c>
-      <c r="D63" s="7">
-        <v>1524</v>
-      </c>
-      <c r="E63" s="8">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>23</v>
-      </c>
-      <c r="D64" s="7">
-        <v>45</v>
-      </c>
-      <c r="E64" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>66</v>
-      </c>
-      <c r="D65" s="7">
-        <v>77</v>
-      </c>
-      <c r="E65" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>45</v>
-      </c>
-      <c r="D66" s="7">
-        <v>23</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="7">
-        <v>77</v>
-      </c>
-      <c r="D67" s="7">
-        <v>66</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>36.71</v>
-      </c>
-      <c r="D68" s="7">
-        <v>46.63</v>
-      </c>
-      <c r="E68" s="8">
-        <v>9.92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>28.2</v>
-      </c>
-      <c r="D69" s="7">
-        <v>28.59</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>28.33</v>
-      </c>
-      <c r="D70" s="7">
-        <v>26.97</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>48.26</v>
-      </c>
-      <c r="D71" s="7">
-        <v>47.68</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>68.95</v>
-      </c>
-      <c r="D72" s="7">
-        <v>73.8</v>
-      </c>
-      <c r="E72" s="8">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>64.33</v>
-      </c>
-      <c r="D73" s="7">
-        <v>68.17</v>
-      </c>
-      <c r="E73" s="8">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>33.22</v>
-      </c>
-      <c r="D74" s="7">
-        <v>32.95</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>45.37</v>
-      </c>
-      <c r="D75" s="7">
-        <v>45.04</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="7">
-        <v>37.97</v>
-      </c>
-      <c r="D76" s="7">
-        <v>41.67</v>
-      </c>
-      <c r="E76" s="8">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="6" t="s">
+      <c r="B85" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="7">
-        <v>-21.28</v>
-      </c>
-      <c r="D77" s="7">
-        <v>11.03</v>
-      </c>
-      <c r="E77" s="8">
-        <v>32.31</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>62.44</v>
-      </c>
-      <c r="D78" s="7">
-        <v>11.81</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-50.63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-48.71</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-50.81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-4.45</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-3.36</v>
-      </c>
-      <c r="E80" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>166.9</v>
-      </c>
-      <c r="D81" s="7">
-        <v>93.64</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-73.26000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>17.31</v>
-      </c>
-      <c r="D82" s="7">
-        <v>245.95</v>
-      </c>
-      <c r="E82" s="8">
-        <v>228.64</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-58.2</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-62.05</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-31.11</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-44.55</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-13.44</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="7">
-        <v>76.23</v>
-      </c>
-      <c r="D85" s="7">
+      <c r="C85" s="6">
         <v>54.82</v>
       </c>
-      <c r="E85" s="9">
-        <v>-21.41</v>
+      <c r="D85" s="6">
+        <v>48.27</v>
+      </c>
+      <c r="E85" s="7">
+        <v>-6.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3574,60 +3570,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>44.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>45.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-1.8</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="E2" s="11">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -3729,61 +3725,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3739</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3066</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2041</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1371</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1163</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.05889999999999999</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0507</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.046</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.095</v>
+      <c r="A2" s="14">
+        <v>0.354</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2907</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1997</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1322</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1069</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0554</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0534</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0441</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1029</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,43 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.8 → 55.8</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.8</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.9 → 32.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>24.9</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>55.8 → 49.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>55.8</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.6% → -5.9%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.6%</t>
-  </si>
-  <si>
-    <t>-5.9%</t>
-  </si>
-  <si>
-    <t>0.0% → -5.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-5.3%</t>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>53.0 → 48.9</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -281,7 +281,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,7 +315,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -327,15 +327,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,19 +355,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -452,14 +439,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -468,7 +456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -967,10 +955,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>376.35</v>
+        <v>378</v>
       </c>
       <c r="D2">
-        <v>-2.58</v>
+        <v>0.44</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -979,46 +967,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-23.23</v>
+        <v>-22.89</v>
       </c>
       <c r="H2">
-        <v>0.36</v>
+        <v>0.8</v>
       </c>
       <c r="I2">
-        <v>-3.24</v>
+        <v>-3.28</v>
       </c>
       <c r="J2">
-        <v>-3.71</v>
+        <v>-1.82</v>
       </c>
       <c r="K2">
-        <v>-20.1</v>
+        <v>-19.46</v>
       </c>
       <c r="L2">
-        <v>-8.449999999999999</v>
+        <v>-5.42</v>
       </c>
       <c r="M2">
-        <v>10.69</v>
+        <v>10.45</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>382.65</v>
+        <v>380.09</v>
       </c>
       <c r="Q2">
-        <v>383.76</v>
+        <v>383.46</v>
       </c>
       <c r="R2">
-        <v>397.08</v>
+        <v>396.26</v>
       </c>
       <c r="S2">
-        <v>433.99</v>
+        <v>433.93</v>
       </c>
       <c r="T2">
-        <v>-13.28</v>
+        <v>-12.89</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1033,34 +1021,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.84</v>
+        <v>41.36</v>
       </c>
       <c r="Z2">
-        <v>-4.85</v>
+        <v>-4.97</v>
       </c>
       <c r="AA2">
-        <v>-5.6</v>
+        <v>-5.47</v>
       </c>
       <c r="AB2">
-        <v>0.75</v>
+        <v>0.51</v>
       </c>
       <c r="AC2">
-        <v>65.59</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="AD2">
-        <v>67.58</v>
+        <v>67.91</v>
       </c>
       <c r="AE2">
-        <v>10.26</v>
+        <v>9.99</v>
       </c>
       <c r="AF2">
-        <v>0.21</v>
+        <v>-64.63</v>
       </c>
       <c r="AG2">
-        <v>394.53</v>
+        <v>394.54</v>
       </c>
       <c r="AH2">
-        <v>372.98</v>
+        <v>372.38</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1069,7 +1057,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.06</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1080,58 +1068,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2860</v>
+        <v>2857.6</v>
       </c>
       <c r="D3">
-        <v>-3.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
       </c>
       <c r="F3">
-        <v>2860</v>
+        <v>2857.6</v>
       </c>
       <c r="G3">
-        <v>-24.78</v>
+        <v>-24.85</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.11</v>
+        <v>-5.85</v>
       </c>
       <c r="J3">
-        <v>-12.24</v>
+        <v>-10.42</v>
       </c>
       <c r="K3">
-        <v>-8.83</v>
+        <v>-10.73</v>
       </c>
       <c r="L3">
-        <v>-15.8</v>
+        <v>-16.4</v>
       </c>
       <c r="M3">
-        <v>29.07</v>
+        <v>28.58</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P3">
-        <v>2957.56</v>
+        <v>2922.08</v>
       </c>
       <c r="Q3">
-        <v>3057.71</v>
+        <v>3043.09</v>
       </c>
       <c r="R3">
-        <v>3242.71</v>
+        <v>3235.27</v>
       </c>
       <c r="S3">
-        <v>3275.58</v>
+        <v>3271.82</v>
       </c>
       <c r="T3">
-        <v>-12.69</v>
+        <v>-12.66</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1146,43 +1134,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>23.14</v>
+        <v>23.02</v>
       </c>
       <c r="Z3">
-        <v>-88.56999999999999</v>
+        <v>-93.58</v>
       </c>
       <c r="AA3">
-        <v>-76.8</v>
+        <v>-80.15000000000001</v>
       </c>
       <c r="AB3">
-        <v>-11.77</v>
+        <v>-13.43</v>
       </c>
       <c r="AC3">
-        <v>24.39</v>
+        <v>12.82</v>
       </c>
       <c r="AD3">
-        <v>46.3</v>
+        <v>28.07</v>
       </c>
       <c r="AE3">
-        <v>66.45</v>
+        <v>65.2</v>
       </c>
       <c r="AF3">
-        <v>169.21</v>
+        <v>50.7</v>
       </c>
       <c r="AG3">
-        <v>3224.56</v>
+        <v>3226.33</v>
       </c>
       <c r="AH3">
-        <v>2890.85</v>
+        <v>2859.84</v>
       </c>
       <c r="AI3">
-        <v>3069.06</v>
+        <v>3045.15</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>79.31999999999999</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1193,58 +1181,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>319.75</v>
+        <v>326.2</v>
       </c>
       <c r="D4">
-        <v>-1.57</v>
+        <v>2.02</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>272.95</v>
+        <v>273.4</v>
       </c>
       <c r="G4">
-        <v>-22.45</v>
+        <v>-20.88</v>
       </c>
       <c r="H4">
-        <v>17.15</v>
+        <v>19.31</v>
       </c>
       <c r="I4">
-        <v>-5.93</v>
+        <v>-2.07</v>
       </c>
       <c r="J4">
-        <v>-12.25</v>
+        <v>-11.56</v>
       </c>
       <c r="K4">
-        <v>-4.28</v>
+        <v>-1.69</v>
       </c>
       <c r="L4">
-        <v>14.3</v>
+        <v>19.51</v>
       </c>
       <c r="M4">
-        <v>13.22</v>
+        <v>13.71</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>327.5</v>
+        <v>326.12</v>
       </c>
       <c r="Q4">
-        <v>349.75</v>
+        <v>347.26</v>
       </c>
       <c r="R4">
-        <v>371.28</v>
+        <v>370.4</v>
       </c>
       <c r="S4">
-        <v>343.58</v>
+        <v>343.47</v>
       </c>
       <c r="T4">
-        <v>-6.94</v>
+        <v>-5.03</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1259,34 +1247,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>24.9</v>
+        <v>31.99</v>
       </c>
       <c r="Z4">
-        <v>-12.24</v>
+        <v>-12.28</v>
       </c>
       <c r="AA4">
-        <v>-9.31</v>
+        <v>-9.9</v>
       </c>
       <c r="AB4">
-        <v>-2.93</v>
+        <v>-2.38</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>13.76</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="AE4">
-        <v>10.45</v>
+        <v>11.17</v>
       </c>
       <c r="AF4">
-        <v>75.02</v>
+        <v>114.6</v>
       </c>
       <c r="AG4">
-        <v>383.88</v>
+        <v>380.58</v>
       </c>
       <c r="AH4">
-        <v>315.62</v>
+        <v>313.94</v>
       </c>
       <c r="AI4">
         <v>351.78</v>
@@ -1295,7 +1283,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>45.96</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1306,10 +1294,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>351.15</v>
+        <v>351.1</v>
       </c>
       <c r="D5">
-        <v>-2.54</v>
+        <v>-0.01</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1318,46 +1306,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.73</v>
+        <v>-16.74</v>
       </c>
       <c r="H5">
-        <v>19.34</v>
+        <v>19.32</v>
       </c>
       <c r="I5">
-        <v>-0.78</v>
+        <v>-1.61</v>
       </c>
       <c r="J5">
-        <v>-1.62</v>
+        <v>-2.2</v>
       </c>
       <c r="K5">
-        <v>-5.08</v>
+        <v>-5.69</v>
       </c>
       <c r="L5">
-        <v>-2.42</v>
+        <v>-1.72</v>
       </c>
       <c r="M5">
-        <v>5.54</v>
+        <v>5.69</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>358.48</v>
+        <v>357.33</v>
       </c>
       <c r="Q5">
-        <v>358.97</v>
+        <v>358.37</v>
       </c>
       <c r="R5">
-        <v>371.52</v>
+        <v>371</v>
       </c>
       <c r="S5">
-        <v>359.14</v>
+        <v>358.89</v>
       </c>
       <c r="T5">
-        <v>-2.23</v>
+        <v>-2.17</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1372,34 +1360,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.77</v>
+        <v>40.73</v>
       </c>
       <c r="Z5">
-        <v>-3.37</v>
+        <v>-3.7</v>
       </c>
       <c r="AA5">
-        <v>-3.77</v>
+        <v>-3.76</v>
       </c>
       <c r="AB5">
-        <v>0.41</v>
+        <v>0.06</v>
       </c>
       <c r="AC5">
-        <v>75.53</v>
+        <v>63.23</v>
       </c>
       <c r="AD5">
-        <v>83.84999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="AE5">
-        <v>12.21</v>
+        <v>12.17</v>
       </c>
       <c r="AF5">
-        <v>9.529999999999999</v>
+        <v>58.68</v>
       </c>
       <c r="AG5">
-        <v>372.29</v>
+        <v>371.98</v>
       </c>
       <c r="AH5">
-        <v>345.65</v>
+        <v>344.75</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1408,7 +1396,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>29.66</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1419,10 +1407,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>416.4</v>
+        <v>406.75</v>
       </c>
       <c r="D6">
-        <v>-4.46</v>
+        <v>-2.32</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1431,46 +1419,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-5.94</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="H6">
-        <v>48.95</v>
+        <v>45.5</v>
       </c>
       <c r="I6">
-        <v>-0.87</v>
+        <v>-3.21</v>
       </c>
       <c r="J6">
-        <v>7.54</v>
+        <v>3.64</v>
       </c>
       <c r="K6">
-        <v>5.52</v>
+        <v>1.87</v>
       </c>
       <c r="L6">
-        <v>20.61</v>
+        <v>17.8</v>
       </c>
       <c r="M6">
-        <v>-10.29</v>
+        <v>-11.72</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>424</v>
+        <v>421.3</v>
       </c>
       <c r="Q6">
-        <v>406.46</v>
+        <v>406.79</v>
       </c>
       <c r="R6">
-        <v>405.54</v>
+        <v>405.84</v>
       </c>
       <c r="S6">
-        <v>375.6</v>
+        <v>376.03</v>
       </c>
       <c r="T6">
-        <v>10.86</v>
+        <v>8.17</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1485,34 +1473,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>55.8</v>
+        <v>49.37</v>
       </c>
       <c r="Z6">
-        <v>6.69</v>
+        <v>5.55</v>
       </c>
       <c r="AA6">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="AB6">
-        <v>2.93</v>
+        <v>1.43</v>
       </c>
       <c r="AC6">
-        <v>82.5</v>
+        <v>58.74</v>
       </c>
       <c r="AD6">
-        <v>94.17</v>
+        <v>80.41</v>
       </c>
       <c r="AE6">
         <v>14.15</v>
       </c>
       <c r="AF6">
-        <v>20.83</v>
+        <v>-31.94</v>
       </c>
       <c r="AG6">
-        <v>433.87</v>
+        <v>434.04</v>
       </c>
       <c r="AH6">
-        <v>379.06</v>
+        <v>379.54</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1521,7 +1509,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>44.54</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1532,10 +1520,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>698.75</v>
+        <v>685.05</v>
       </c>
       <c r="D7">
-        <v>-5.27</v>
+        <v>-1.96</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1544,46 +1532,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-5.27</v>
+        <v>-7.13</v>
       </c>
       <c r="H7">
-        <v>37.97</v>
+        <v>35.27</v>
       </c>
       <c r="I7">
-        <v>-1.38</v>
+        <v>-4.28</v>
       </c>
       <c r="J7">
-        <v>7.57</v>
+        <v>3.01</v>
       </c>
       <c r="K7">
-        <v>14.54</v>
+        <v>14.56</v>
       </c>
       <c r="L7">
-        <v>17.08</v>
+        <v>15.73</v>
       </c>
       <c r="M7">
-        <v>35.4</v>
+        <v>31.1</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>717.65</v>
+        <v>711.53</v>
       </c>
       <c r="Q7">
-        <v>703.55</v>
+        <v>705.12</v>
       </c>
       <c r="R7">
-        <v>646.3099999999999</v>
+        <v>648.71</v>
       </c>
       <c r="S7">
-        <v>599.5599999999999</v>
+        <v>600.1799999999999</v>
       </c>
       <c r="T7">
-        <v>16.54</v>
+        <v>14.14</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1598,34 +1586,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>53.03</v>
+        <v>48.91</v>
       </c>
       <c r="Z7">
-        <v>19.08</v>
+        <v>15.73</v>
       </c>
       <c r="AA7">
-        <v>21.48</v>
+        <v>20.33</v>
       </c>
       <c r="AB7">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="AC7">
-        <v>29.74</v>
+        <v>18.43</v>
       </c>
       <c r="AD7">
-        <v>31.54</v>
+        <v>28.5</v>
       </c>
       <c r="AE7">
-        <v>28.83</v>
+        <v>28.58</v>
       </c>
       <c r="AF7">
-        <v>-10.13</v>
+        <v>-62.13</v>
       </c>
       <c r="AG7">
-        <v>743.4400000000001</v>
+        <v>738.6799999999999</v>
       </c>
       <c r="AH7">
-        <v>663.65</v>
+        <v>671.5700000000001</v>
       </c>
       <c r="AI7">
         <v>664.6799999999999</v>
@@ -1634,7 +1622,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>40.24</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1645,10 +1633,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>194.85</v>
+        <v>194.81</v>
       </c>
       <c r="D8">
-        <v>0.31</v>
+        <v>-0.02</v>
       </c>
       <c r="E8">
         <v>352.8</v>
@@ -1657,46 +1645,46 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.77</v>
+        <v>-44.78</v>
       </c>
       <c r="H8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="I8">
-        <v>-2.43</v>
+        <v>-2.6</v>
       </c>
       <c r="J8">
-        <v>-6.46</v>
+        <v>-5.7</v>
       </c>
       <c r="K8">
-        <v>-17.63</v>
+        <v>-16.21</v>
       </c>
       <c r="L8">
-        <v>-43.04</v>
+        <v>-44.13</v>
       </c>
       <c r="M8">
-        <v>-4.41</v>
+        <v>-4.32</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>195.9</v>
+        <v>194.86</v>
       </c>
       <c r="Q8">
-        <v>199.03</v>
+        <v>198.38</v>
       </c>
       <c r="R8">
-        <v>211.94</v>
+        <v>211.47</v>
       </c>
       <c r="S8">
-        <v>249.43</v>
+        <v>248.85</v>
       </c>
       <c r="T8">
-        <v>-21.88</v>
+        <v>-21.72</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1711,34 +1699,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.41</v>
+        <v>34.35</v>
       </c>
       <c r="Z8">
-        <v>-4.8</v>
+        <v>-4.67</v>
       </c>
       <c r="AA8">
-        <v>-5.2</v>
+        <v>-5.09</v>
       </c>
       <c r="AB8">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="AC8">
-        <v>63.55</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="AD8">
-        <v>67.51000000000001</v>
+        <v>64.33</v>
       </c>
       <c r="AE8">
-        <v>5.75</v>
+        <v>5.73</v>
       </c>
       <c r="AF8">
-        <v>22.76</v>
+        <v>-62.88</v>
       </c>
       <c r="AG8">
-        <v>208.43</v>
+        <v>206.96</v>
       </c>
       <c r="AH8">
-        <v>189.63</v>
+        <v>189.79</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1747,7 +1735,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>33.11</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1758,10 +1746,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3542.7</v>
+        <v>3532.2</v>
       </c>
       <c r="D9">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1770,46 +1758,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.77</v>
+        <v>-19.01</v>
       </c>
       <c r="H9">
-        <v>7.07</v>
+        <v>6.75</v>
       </c>
       <c r="I9">
-        <v>-0.17</v>
+        <v>-0.38</v>
       </c>
       <c r="J9">
-        <v>0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="K9">
-        <v>-10.08</v>
+        <v>-7.49</v>
       </c>
       <c r="L9">
-        <v>-13.4</v>
+        <v>-12.8</v>
       </c>
       <c r="M9">
-        <v>19.97</v>
+        <v>19.65</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>3547.06</v>
+        <v>3544.36</v>
       </c>
       <c r="Q9">
-        <v>3567.9</v>
+        <v>3566.78</v>
       </c>
       <c r="R9">
-        <v>3579.3</v>
+        <v>3578.42</v>
       </c>
       <c r="S9">
-        <v>3672.94</v>
+        <v>3671.97</v>
       </c>
       <c r="T9">
-        <v>-3.55</v>
+        <v>-3.81</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1824,34 +1812,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.44</v>
+        <v>42.61</v>
       </c>
       <c r="Z9">
-        <v>-13.18</v>
+        <v>-14.06</v>
       </c>
       <c r="AA9">
-        <v>-12.95</v>
+        <v>-13.17</v>
       </c>
       <c r="AB9">
-        <v>-0.23</v>
+        <v>-0.89</v>
       </c>
       <c r="AC9">
-        <v>32.88</v>
+        <v>26.88</v>
       </c>
       <c r="AD9">
-        <v>33.64</v>
+        <v>31.72</v>
       </c>
       <c r="AE9">
-        <v>61.63</v>
+        <v>61.75</v>
       </c>
       <c r="AF9">
-        <v>38.46</v>
+        <v>4.66</v>
       </c>
       <c r="AG9">
-        <v>3632.97</v>
+        <v>3633.57</v>
       </c>
       <c r="AH9">
-        <v>3502.83</v>
+        <v>3499.98</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1860,7 +1848,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>14.27</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1871,10 +1859,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1533</v>
+        <v>1535.9</v>
       </c>
       <c r="D10">
-        <v>0.59</v>
+        <v>0.19</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1883,46 +1871,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-13.31</v>
+        <v>-13.15</v>
       </c>
       <c r="H10">
-        <v>15.59</v>
+        <v>15.81</v>
       </c>
       <c r="I10">
-        <v>-0.65</v>
+        <v>-0.78</v>
       </c>
       <c r="J10">
-        <v>-6.41</v>
+        <v>-5.37</v>
       </c>
       <c r="K10">
-        <v>8.720000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L10">
-        <v>10.04</v>
+        <v>10.02</v>
       </c>
       <c r="M10">
-        <v>5.34</v>
+        <v>4.75</v>
       </c>
       <c r="N10">
         <v>77</v>
       </c>
       <c r="O10">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P10">
-        <v>1531.54</v>
+        <v>1529.12</v>
       </c>
       <c r="Q10">
-        <v>1549.62</v>
+        <v>1546.52</v>
       </c>
       <c r="R10">
-        <v>1590.29</v>
+        <v>1589.9</v>
       </c>
       <c r="S10">
-        <v>1517.84</v>
+        <v>1517.65</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1937,34 +1925,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>44.06</v>
+        <v>44.85</v>
       </c>
       <c r="Z10">
-        <v>-14.77</v>
+        <v>-14.14</v>
       </c>
       <c r="AA10">
-        <v>-12.53</v>
+        <v>-12.86</v>
       </c>
       <c r="AB10">
-        <v>-2.23</v>
+        <v>-1.29</v>
       </c>
       <c r="AC10">
-        <v>39.7</v>
+        <v>50.34</v>
       </c>
       <c r="AD10">
-        <v>47.38</v>
+        <v>44.75</v>
       </c>
       <c r="AE10">
-        <v>38.96</v>
+        <v>39.84</v>
       </c>
       <c r="AF10">
-        <v>48.27</v>
+        <v>85.05</v>
       </c>
       <c r="AG10">
-        <v>1597.73</v>
+        <v>1589.19</v>
       </c>
       <c r="AH10">
-        <v>1501.52</v>
+        <v>1503.85</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1973,7 +1961,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>16.68</v>
+        <v>16.29</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2154,7 +2142,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2173,42 +2161,42 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2239,1312 +2227,1227 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-1.21</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="7">
         <v>-3.71</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.5</v>
+      <c r="D9" s="7">
+        <v>-1.82</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-10.12</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="7">
         <v>-12.24</v>
       </c>
-      <c r="E10" s="7">
-        <v>-2.12</v>
+      <c r="D10" s="7">
+        <v>-10.42</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-12.91</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="7">
         <v>-12.25</v>
       </c>
+      <c r="D11" s="7">
+        <v>-11.56</v>
+      </c>
       <c r="E11" s="8">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="7">
         <v>-1.62</v>
       </c>
-      <c r="E12" s="7">
-        <v>-0.16</v>
+      <c r="D12" s="7">
+        <v>-2.2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>11.34</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="7">
         <v>7.54</v>
       </c>
-      <c r="E13" s="7">
-        <v>-3.8</v>
+      <c r="D13" s="7">
+        <v>3.64</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-3.9</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>11.23</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="7">
         <v>7.57</v>
       </c>
-      <c r="E14" s="7">
-        <v>-3.66</v>
+      <c r="D14" s="7">
+        <v>3.01</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-4.56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
-        <v>-7.35</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="7">
         <v>-6.46</v>
       </c>
+      <c r="D15" s="7">
+        <v>-5.7</v>
+      </c>
       <c r="E15" s="8">
-        <v>0.89</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-0.25</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-6.41</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-5.37</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.24</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.28</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-4.11</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-5.85</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-5.93</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-2.07</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-1.61</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.87</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.21</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-1.38</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.28</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-2.43</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-2.6</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.17</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-0.38</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
         <v>-0.65</v>
       </c>
-      <c r="D16" s="6">
-        <v>0.14</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="D26" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-8.449999999999999</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-5.42</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-15.8</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-16.4</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>14.3</v>
+      </c>
+      <c r="D29" s="7">
+        <v>19.51</v>
+      </c>
+      <c r="E29" s="8">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-2.42</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-1.72</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>20.61</v>
+      </c>
+      <c r="D31" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>17.08</v>
+      </c>
+      <c r="D32" s="7">
+        <v>15.73</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-43.04</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-44.13</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-13.4</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-12.8</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>10.04</v>
+      </c>
+      <c r="D35" s="7">
+        <v>10.02</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-20.1</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-19.46</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-8.83</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-10.73</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-4.28</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-1.69</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-5.08</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-5.69</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>5.52</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>14.54</v>
+      </c>
+      <c r="D41" s="7">
+        <v>14.56</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-17.63</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-16.21</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-10.08</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-7.49</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="D44" s="7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-23.23</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-22.89</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-24.78</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-24.85</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-22.45</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-20.88</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-16.73</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-16.74</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-5.94</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-5.27</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-7.13</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-44.77</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-44.78</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-18.77</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-19.01</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-13.31</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-13.15</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>376.35</v>
+      </c>
+      <c r="D54" s="7">
+        <v>378</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>2860</v>
+      </c>
+      <c r="D55" s="7">
+        <v>2857.6</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>319.75</v>
+      </c>
+      <c r="D56" s="7">
+        <v>326.2</v>
+      </c>
+      <c r="E56" s="8">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>351.15</v>
+      </c>
+      <c r="D57" s="7">
+        <v>351.1</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>416.4</v>
+      </c>
+      <c r="D58" s="7">
+        <v>406.75</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-9.65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>698.75</v>
+      </c>
+      <c r="D59" s="7">
+        <v>685.05</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-13.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>194.85</v>
+      </c>
+      <c r="D60" s="7">
+        <v>194.81</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>3542.7</v>
+      </c>
+      <c r="D61" s="7">
+        <v>3532.2</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1533</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1535.9</v>
+      </c>
+      <c r="E62" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>39.84</v>
+      </c>
+      <c r="D63" s="7">
+        <v>41.36</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>23.14</v>
+      </c>
+      <c r="D64" s="7">
+        <v>23.02</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="D65" s="7">
+        <v>31.99</v>
+      </c>
+      <c r="E65" s="8">
+        <v>7.09</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>40.77</v>
+      </c>
+      <c r="D66" s="7">
+        <v>40.73</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>55.8</v>
+      </c>
+      <c r="D67" s="7">
+        <v>49.37</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-6.43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>53.03</v>
+      </c>
+      <c r="D68" s="7">
+        <v>48.91</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>34.41</v>
+      </c>
+      <c r="D69" s="7">
+        <v>34.35</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>44.44</v>
+      </c>
+      <c r="D70" s="7">
+        <v>42.61</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>44.06</v>
+      </c>
+      <c r="D71" s="7">
+        <v>44.85</v>
+      </c>
+      <c r="E71" s="8">
         <v>0.79</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-64.63</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-64.84</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>169.21</v>
+      </c>
+      <c r="D73" s="7">
+        <v>50.7</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-118.51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>75.02</v>
+      </c>
+      <c r="D74" s="7">
+        <v>114.6</v>
+      </c>
+      <c r="E74" s="8">
+        <v>39.58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D75" s="7">
+        <v>58.68</v>
+      </c>
+      <c r="E75" s="8">
+        <v>49.15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>20.83</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-31.94</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-52.77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-10.13</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-62.13</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>22.76</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-62.88</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-85.64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>38.46</v>
+      </c>
+      <c r="D79" s="7">
+        <v>4.66</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-33.8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.41</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.55</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-3.24</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.8</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-4.11</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-6.81</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.93</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1.04</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4.63</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.87</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4.97</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-6.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.55</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.43</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-0.17</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-0.65</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-8.449999999999999</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-16.43</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-15.8</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>16.18</v>
-      </c>
-      <c r="D29" s="6">
-        <v>14.3</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-3.44</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>22.43</v>
-      </c>
-      <c r="D31" s="6">
-        <v>20.61</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>20.8</v>
-      </c>
-      <c r="D32" s="6">
-        <v>17.08</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-44.39</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-43.04</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-15.27</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-13.4</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>6.62</v>
-      </c>
-      <c r="D35" s="6">
-        <v>10.04</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-18.53</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-20.1</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2.15</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-4.28</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-6.43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-3.2</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="D40" s="6">
-        <v>5.52</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-7.28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>21.92</v>
-      </c>
-      <c r="D41" s="6">
-        <v>14.54</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-7.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-18.16</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-13.58</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="E43" s="8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>7.23</v>
-      </c>
-      <c r="D44" s="6">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-21.2</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-23.23</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-22.42</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-24.78</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-21.21</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-22.45</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-14.56</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-16.73</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-1.55</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-4.39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>0</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-5.27</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-5.27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-44.94</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-44.77</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-18.69</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-18.77</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-13.82</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-13.31</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>386.3</v>
-      </c>
-      <c r="D54" s="6">
-        <v>376.35</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-9.949999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>2950</v>
-      </c>
-      <c r="D55" s="6">
-        <v>2860</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>324.85</v>
-      </c>
-      <c r="D56" s="6">
-        <v>319.75</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>360.3</v>
-      </c>
-      <c r="D57" s="6">
-        <v>351.15</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-9.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>435.85</v>
-      </c>
-      <c r="D58" s="6">
-        <v>416.4</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-19.45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>737.65</v>
-      </c>
-      <c r="D59" s="6">
-        <v>698.75</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-38.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>194.25</v>
-      </c>
-      <c r="D60" s="6">
-        <v>194.85</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>3546.2</v>
-      </c>
-      <c r="D61" s="6">
-        <v>3542.7</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1524</v>
-      </c>
-      <c r="D62" s="6">
-        <v>1533</v>
-      </c>
-      <c r="E62" s="8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>45</v>
-      </c>
-      <c r="D63" s="6">
-        <v>34</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>34</v>
-      </c>
-      <c r="D64" s="6">
-        <v>23</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="6">
-        <v>77</v>
-      </c>
-      <c r="D65" s="6">
-        <v>66</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="6">
-        <v>23</v>
-      </c>
-      <c r="D66" s="6">
-        <v>45</v>
-      </c>
-      <c r="E66" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="6">
-        <v>66</v>
-      </c>
-      <c r="D67" s="6">
-        <v>77</v>
-      </c>
-      <c r="E67" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>46.63</v>
-      </c>
-      <c r="D68" s="6">
-        <v>39.84</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-6.79</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>28.59</v>
-      </c>
-      <c r="D69" s="6">
-        <v>23.14</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-5.45</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>26.97</v>
-      </c>
-      <c r="D70" s="6">
-        <v>24.9</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>47.68</v>
-      </c>
-      <c r="D71" s="6">
-        <v>40.77</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-6.91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>73.8</v>
-      </c>
-      <c r="D72" s="6">
-        <v>55.8</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>68.17</v>
-      </c>
-      <c r="D73" s="6">
-        <v>53.03</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-15.14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="6">
-        <v>32.95</v>
-      </c>
-      <c r="D74" s="6">
-        <v>34.41</v>
-      </c>
-      <c r="E74" s="8">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="6">
-        <v>45.04</v>
-      </c>
-      <c r="D75" s="6">
-        <v>44.44</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="6">
-        <v>41.67</v>
-      </c>
-      <c r="D76" s="6">
-        <v>44.06</v>
-      </c>
-      <c r="E76" s="8">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="5" t="s">
+      <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="6">
-        <v>11.03</v>
-      </c>
-      <c r="D77" s="6">
-        <v>0.21</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-10.82</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>11.81</v>
-      </c>
-      <c r="D78" s="6">
-        <v>169.21</v>
-      </c>
-      <c r="E78" s="8">
-        <v>157.4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-48.71</v>
-      </c>
-      <c r="D79" s="6">
-        <v>75.02</v>
-      </c>
-      <c r="E79" s="8">
-        <v>123.73</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-3.36</v>
-      </c>
-      <c r="D80" s="6">
-        <v>9.529999999999999</v>
+      <c r="C80" s="7">
+        <v>48.27</v>
+      </c>
+      <c r="D80" s="7">
+        <v>85.05</v>
       </c>
       <c r="E80" s="8">
-        <v>12.89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>93.64</v>
-      </c>
-      <c r="D81" s="6">
-        <v>20.83</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-72.81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>245.95</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-10.13</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-256.08</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>-62.05</v>
-      </c>
-      <c r="D83" s="6">
-        <v>22.76</v>
-      </c>
-      <c r="E83" s="8">
-        <v>84.81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="6">
-        <v>-44.55</v>
-      </c>
-      <c r="D84" s="6">
-        <v>38.46</v>
-      </c>
-      <c r="E84" s="8">
-        <v>83.01000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="6">
-        <v>54.82</v>
-      </c>
-      <c r="D85" s="6">
-        <v>48.27</v>
-      </c>
-      <c r="E85" s="7">
-        <v>-6.55</v>
+        <v>36.78</v>
       </c>
     </row>
   </sheetData>
@@ -3570,60 +3473,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>44.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>40</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>39.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-3.4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-4</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -3725,61 +3628,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.354</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2907</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1997</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1322</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1069</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0554</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0534</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0441</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1029</v>
+      <c r="A2" s="15">
+        <v>0.311</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2858</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1965</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1371</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1045</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.05690000000000001</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0475</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0432</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1172</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>24.9 → 32.0</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>49.4 → 54.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>24.9</t>
-  </si>
-  <si>
-    <t>32.0</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>55.8 → 49.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.8</t>
-  </si>
-  <si>
     <t>49.4</t>
   </si>
   <si>
-    <t>53.0 → 48.9</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>54.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -431,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -439,7 +415,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -955,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D2">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -967,46 +942,46 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-22.89</v>
+        <v>-22.68</v>
       </c>
       <c r="H2">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="I2">
-        <v>-3.28</v>
+        <v>-1.13</v>
       </c>
       <c r="J2">
-        <v>-1.82</v>
+        <v>-1.29</v>
       </c>
       <c r="K2">
-        <v>-19.46</v>
+        <v>-18.78</v>
       </c>
       <c r="L2">
-        <v>-5.42</v>
+        <v>-4.57</v>
       </c>
       <c r="M2">
-        <v>10.45</v>
+        <v>10.71</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>380.09</v>
+        <v>379.22</v>
       </c>
       <c r="Q2">
-        <v>383.46</v>
+        <v>383.14</v>
       </c>
       <c r="R2">
-        <v>396.26</v>
+        <v>395.57</v>
       </c>
       <c r="S2">
-        <v>433.93</v>
+        <v>433.88</v>
       </c>
       <c r="T2">
-        <v>-12.89</v>
+        <v>-12.65</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1021,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.36</v>
+        <v>42.32</v>
       </c>
       <c r="Z2">
-        <v>-4.97</v>
+        <v>-4.92</v>
       </c>
       <c r="AA2">
-        <v>-5.47</v>
+        <v>-5.36</v>
       </c>
       <c r="AB2">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="AC2">
-        <v>70.51000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AD2">
-        <v>67.91</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="AE2">
-        <v>9.99</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF2">
-        <v>-64.63</v>
+        <v>-62.4</v>
       </c>
       <c r="AG2">
-        <v>394.54</v>
+        <v>394.35</v>
       </c>
       <c r="AH2">
-        <v>372.38</v>
+        <v>371.93</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1057,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.76</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1068,58 +1043,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2857.6</v>
+        <v>2855</v>
       </c>
       <c r="D3">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
       </c>
       <c r="F3">
-        <v>2857.6</v>
+        <v>2855</v>
       </c>
       <c r="G3">
-        <v>-24.85</v>
+        <v>-24.92</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-5.85</v>
+        <v>-4.67</v>
       </c>
       <c r="J3">
-        <v>-10.42</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="K3">
-        <v>-10.73</v>
+        <v>-10.68</v>
       </c>
       <c r="L3">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M3">
-        <v>28.58</v>
+        <v>28.83</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>2922.08</v>
+        <v>2894.08</v>
       </c>
       <c r="Q3">
-        <v>3043.09</v>
+        <v>3027.34</v>
       </c>
       <c r="R3">
-        <v>3235.27</v>
+        <v>3229.14</v>
       </c>
       <c r="S3">
-        <v>3271.82</v>
+        <v>3267.99</v>
       </c>
       <c r="T3">
-        <v>-12.66</v>
+        <v>-12.64</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1134,43 +1109,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>23.02</v>
+        <v>22.87</v>
       </c>
       <c r="Z3">
-        <v>-93.58</v>
+        <v>-96.65000000000001</v>
       </c>
       <c r="AA3">
-        <v>-80.15000000000001</v>
+        <v>-83.45</v>
       </c>
       <c r="AB3">
-        <v>-13.43</v>
+        <v>-13.2</v>
       </c>
       <c r="AC3">
-        <v>12.82</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>28.07</v>
+        <v>12.4</v>
       </c>
       <c r="AE3">
-        <v>65.2</v>
+        <v>62.59</v>
       </c>
       <c r="AF3">
-        <v>50.7</v>
+        <v>17.89</v>
       </c>
       <c r="AG3">
-        <v>3226.33</v>
+        <v>3218.62</v>
       </c>
       <c r="AH3">
-        <v>2859.84</v>
+        <v>2836.05</v>
       </c>
       <c r="AI3">
-        <v>3045.15</v>
+        <v>3039.43</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>81.27</v>
+        <v>82.95999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1181,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>326.2</v>
+        <v>327.75</v>
       </c>
       <c r="D4">
-        <v>2.02</v>
+        <v>0.48</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1193,46 +1168,46 @@
         <v>273.4</v>
       </c>
       <c r="G4">
-        <v>-20.88</v>
+        <v>-20.51</v>
       </c>
       <c r="H4">
-        <v>19.31</v>
+        <v>19.88</v>
       </c>
       <c r="I4">
-        <v>-2.07</v>
+        <v>-1.21</v>
       </c>
       <c r="J4">
-        <v>-11.56</v>
+        <v>-12.84</v>
       </c>
       <c r="K4">
-        <v>-1.69</v>
+        <v>-1.34</v>
       </c>
       <c r="L4">
-        <v>19.51</v>
+        <v>19.05</v>
       </c>
       <c r="M4">
-        <v>13.71</v>
+        <v>14.38</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>326.12</v>
+        <v>325.32</v>
       </c>
       <c r="Q4">
-        <v>347.26</v>
+        <v>344.96</v>
       </c>
       <c r="R4">
-        <v>370.4</v>
+        <v>369.82</v>
       </c>
       <c r="S4">
-        <v>343.47</v>
+        <v>343.4</v>
       </c>
       <c r="T4">
-        <v>-5.03</v>
+        <v>-4.56</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1247,34 +1222,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>31.99</v>
+        <v>33.61</v>
       </c>
       <c r="Z4">
-        <v>-12.28</v>
+        <v>-12.05</v>
       </c>
       <c r="AA4">
-        <v>-9.9</v>
+        <v>-10.33</v>
       </c>
       <c r="AB4">
-        <v>-2.38</v>
+        <v>-1.72</v>
       </c>
       <c r="AC4">
-        <v>13.76</v>
+        <v>30.67</v>
       </c>
       <c r="AD4">
-        <v>4.59</v>
+        <v>14.81</v>
       </c>
       <c r="AE4">
-        <v>11.17</v>
+        <v>10.91</v>
       </c>
       <c r="AF4">
-        <v>114.6</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="AG4">
-        <v>380.58</v>
+        <v>376.92</v>
       </c>
       <c r="AH4">
-        <v>313.94</v>
+        <v>313</v>
       </c>
       <c r="AI4">
         <v>351.78</v>
@@ -1283,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>41.6</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1294,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>351.1</v>
+        <v>352.2</v>
       </c>
       <c r="D5">
-        <v>-0.01</v>
+        <v>0.31</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1306,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.74</v>
+        <v>-16.48</v>
       </c>
       <c r="H5">
-        <v>19.32</v>
+        <v>19.69</v>
       </c>
       <c r="I5">
-        <v>-1.61</v>
+        <v>-3</v>
       </c>
       <c r="J5">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="K5">
-        <v>-5.69</v>
+        <v>-5.04</v>
       </c>
       <c r="L5">
-        <v>-1.72</v>
+        <v>-0.33</v>
       </c>
       <c r="M5">
-        <v>5.69</v>
+        <v>5.62</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>357.33</v>
+        <v>355.15</v>
       </c>
       <c r="Q5">
-        <v>358.37</v>
+        <v>357.86</v>
       </c>
       <c r="R5">
-        <v>371</v>
+        <v>370.55</v>
       </c>
       <c r="S5">
-        <v>358.89</v>
+        <v>358.67</v>
       </c>
       <c r="T5">
-        <v>-2.17</v>
+        <v>-1.8</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1360,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.73</v>
+        <v>41.91</v>
       </c>
       <c r="Z5">
-        <v>-3.7</v>
+        <v>-3.83</v>
       </c>
       <c r="AA5">
-        <v>-3.76</v>
+        <v>-3.77</v>
       </c>
       <c r="AB5">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="AC5">
-        <v>63.23</v>
+        <v>53.79</v>
       </c>
       <c r="AD5">
-        <v>76.44</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AE5">
-        <v>12.17</v>
+        <v>11.85</v>
       </c>
       <c r="AF5">
-        <v>58.68</v>
+        <v>3.37</v>
       </c>
       <c r="AG5">
-        <v>371.98</v>
+        <v>371.6</v>
       </c>
       <c r="AH5">
-        <v>344.75</v>
+        <v>344.12</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1396,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>32.17</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1407,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>406.75</v>
+        <v>415.05</v>
       </c>
       <c r="D6">
-        <v>-2.32</v>
+        <v>2.04</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1419,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.119999999999999</v>
+        <v>-6.25</v>
       </c>
       <c r="H6">
-        <v>45.5</v>
+        <v>48.47</v>
       </c>
       <c r="I6">
-        <v>-3.21</v>
+        <v>-1.6</v>
       </c>
       <c r="J6">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="K6">
-        <v>1.87</v>
+        <v>5.88</v>
       </c>
       <c r="L6">
-        <v>17.8</v>
+        <v>20.58</v>
       </c>
       <c r="M6">
-        <v>-11.72</v>
+        <v>-10.74</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>421.3</v>
+        <v>419.95</v>
       </c>
       <c r="Q6">
-        <v>406.79</v>
+        <v>407.27</v>
       </c>
       <c r="R6">
-        <v>405.84</v>
+        <v>405.81</v>
       </c>
       <c r="S6">
-        <v>376.03</v>
+        <v>376.51</v>
       </c>
       <c r="T6">
-        <v>8.17</v>
+        <v>10.24</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1473,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>49.37</v>
+        <v>54.25</v>
       </c>
       <c r="Z6">
-        <v>5.55</v>
+        <v>5.26</v>
       </c>
       <c r="AA6">
-        <v>4.12</v>
+        <v>4.35</v>
       </c>
       <c r="AB6">
-        <v>1.43</v>
+        <v>0.91</v>
       </c>
       <c r="AC6">
-        <v>58.74</v>
+        <v>39.74</v>
       </c>
       <c r="AD6">
-        <v>80.41</v>
+        <v>60.33</v>
       </c>
       <c r="AE6">
-        <v>14.15</v>
+        <v>14.12</v>
       </c>
       <c r="AF6">
-        <v>-31.94</v>
+        <v>-57.07</v>
       </c>
       <c r="AG6">
-        <v>434.04</v>
+        <v>434.76</v>
       </c>
       <c r="AH6">
-        <v>379.54</v>
+        <v>379.79</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1509,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>39.82</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1520,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>685.05</v>
+        <v>685.7</v>
       </c>
       <c r="D7">
-        <v>-1.96</v>
+        <v>0.09</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1532,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-7.13</v>
+        <v>-7.04</v>
       </c>
       <c r="H7">
-        <v>35.27</v>
+        <v>35.39</v>
       </c>
       <c r="I7">
-        <v>-4.28</v>
+        <v>-4.01</v>
       </c>
       <c r="J7">
-        <v>3.01</v>
+        <v>4.93</v>
       </c>
       <c r="K7">
-        <v>14.56</v>
+        <v>13.76</v>
       </c>
       <c r="L7">
-        <v>15.73</v>
+        <v>14.68</v>
       </c>
       <c r="M7">
-        <v>31.1</v>
+        <v>32.28</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P7">
-        <v>711.53</v>
+        <v>705.8</v>
       </c>
       <c r="Q7">
-        <v>705.12</v>
+        <v>705</v>
       </c>
       <c r="R7">
-        <v>648.71</v>
+        <v>650.99</v>
       </c>
       <c r="S7">
-        <v>600.1799999999999</v>
+        <v>600.79</v>
       </c>
       <c r="T7">
-        <v>14.14</v>
+        <v>14.13</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1586,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>48.91</v>
+        <v>49.11</v>
       </c>
       <c r="Z7">
-        <v>15.73</v>
+        <v>12.98</v>
       </c>
       <c r="AA7">
-        <v>20.33</v>
+        <v>18.86</v>
       </c>
       <c r="AB7">
-        <v>-4.6</v>
+        <v>-5.88</v>
       </c>
       <c r="AC7">
-        <v>18.43</v>
+        <v>0.35</v>
       </c>
       <c r="AD7">
-        <v>28.5</v>
+        <v>16.17</v>
       </c>
       <c r="AE7">
-        <v>28.58</v>
+        <v>27.47</v>
       </c>
       <c r="AF7">
-        <v>-62.13</v>
+        <v>-56.74</v>
       </c>
       <c r="AG7">
-        <v>738.6799999999999</v>
+        <v>738.83</v>
       </c>
       <c r="AH7">
-        <v>671.5700000000001</v>
+        <v>671.1799999999999</v>
       </c>
       <c r="AI7">
         <v>664.6799999999999</v>
@@ -1622,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>36.22</v>
+        <v>32.73</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1633,58 +1608,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>194.81</v>
+        <v>196.71</v>
       </c>
       <c r="D8">
-        <v>-0.02</v>
+        <v>0.98</v>
       </c>
       <c r="E8">
-        <v>352.8</v>
+        <v>352.6</v>
       </c>
       <c r="F8">
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.78</v>
+        <v>-44.21</v>
       </c>
       <c r="H8">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="I8">
-        <v>-2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J8">
-        <v>-5.7</v>
+        <v>-5.39</v>
       </c>
       <c r="K8">
-        <v>-16.21</v>
+        <v>-15.61</v>
       </c>
       <c r="L8">
-        <v>-44.13</v>
+        <v>-44.24</v>
       </c>
       <c r="M8">
-        <v>-4.32</v>
+        <v>-3.42</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P8">
-        <v>194.86</v>
+        <v>195.02</v>
       </c>
       <c r="Q8">
-        <v>198.38</v>
+        <v>197.84</v>
       </c>
       <c r="R8">
-        <v>211.47</v>
+        <v>211.03</v>
       </c>
       <c r="S8">
-        <v>248.85</v>
+        <v>248.32</v>
       </c>
       <c r="T8">
-        <v>-21.72</v>
+        <v>-20.78</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1699,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.35</v>
+        <v>39.21</v>
       </c>
       <c r="Z8">
-        <v>-4.67</v>
+        <v>-4.37</v>
       </c>
       <c r="AA8">
-        <v>-5.09</v>
+        <v>-4.95</v>
       </c>
       <c r="AB8">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="AC8">
-        <v>65.26000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="AD8">
-        <v>64.33</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="AE8">
-        <v>5.73</v>
+        <v>5.53</v>
       </c>
       <c r="AF8">
-        <v>-62.88</v>
+        <v>-66.65000000000001</v>
       </c>
       <c r="AG8">
-        <v>206.96</v>
+        <v>205.32</v>
       </c>
       <c r="AH8">
-        <v>189.79</v>
+        <v>190.36</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1735,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.24</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1746,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3532.2</v>
+        <v>3537.8</v>
       </c>
       <c r="D9">
-        <v>-0.3</v>
+        <v>0.16</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1758,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.01</v>
+        <v>-18.88</v>
       </c>
       <c r="H9">
-        <v>6.75</v>
+        <v>6.92</v>
       </c>
       <c r="I9">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="J9">
-        <v>-0.25</v>
+        <v>-0.48</v>
       </c>
       <c r="K9">
-        <v>-7.49</v>
+        <v>-6.23</v>
       </c>
       <c r="L9">
-        <v>-12.8</v>
+        <v>-14.43</v>
       </c>
       <c r="M9">
-        <v>19.65</v>
+        <v>19.48</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>3544.36</v>
+        <v>3541.42</v>
       </c>
       <c r="Q9">
-        <v>3566.78</v>
+        <v>3565.78</v>
       </c>
       <c r="R9">
-        <v>3578.42</v>
+        <v>3577.79</v>
       </c>
       <c r="S9">
-        <v>3671.97</v>
+        <v>3671.18</v>
       </c>
       <c r="T9">
-        <v>-3.81</v>
+        <v>-3.63</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1812,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>42.61</v>
+        <v>43.94</v>
       </c>
       <c r="Z9">
-        <v>-14.06</v>
+        <v>-14.14</v>
       </c>
       <c r="AA9">
-        <v>-13.17</v>
+        <v>-13.37</v>
       </c>
       <c r="AB9">
-        <v>-0.89</v>
+        <v>-0.78</v>
       </c>
       <c r="AC9">
-        <v>26.88</v>
+        <v>24.48</v>
       </c>
       <c r="AD9">
-        <v>31.72</v>
+        <v>28.08</v>
       </c>
       <c r="AE9">
-        <v>61.75</v>
+        <v>60.12</v>
       </c>
       <c r="AF9">
-        <v>4.66</v>
+        <v>12.2</v>
       </c>
       <c r="AG9">
-        <v>3633.57</v>
+        <v>3633.72</v>
       </c>
       <c r="AH9">
-        <v>3499.98</v>
+        <v>3497.83</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1848,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>12.78</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1859,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1535.9</v>
+        <v>1504.5</v>
       </c>
       <c r="D10">
-        <v>0.19</v>
+        <v>-2.04</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1871,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-13.15</v>
+        <v>-14.92</v>
       </c>
       <c r="H10">
-        <v>15.81</v>
+        <v>13.44</v>
       </c>
       <c r="I10">
-        <v>-0.78</v>
+        <v>-2.44</v>
       </c>
       <c r="J10">
-        <v>-5.37</v>
+        <v>-5.85</v>
       </c>
       <c r="K10">
-        <v>9.199999999999999</v>
+        <v>3.94</v>
       </c>
       <c r="L10">
-        <v>10.02</v>
+        <v>8.57</v>
       </c>
       <c r="M10">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P10">
-        <v>1529.12</v>
+        <v>1521.58</v>
       </c>
       <c r="Q10">
-        <v>1546.52</v>
+        <v>1541.9</v>
       </c>
       <c r="R10">
-        <v>1589.9</v>
+        <v>1588.8</v>
       </c>
       <c r="S10">
-        <v>1517.65</v>
+        <v>1517.28</v>
       </c>
       <c r="T10">
-        <v>1.2</v>
+        <v>-0.84</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1922,37 +1897,37 @@
         <v>47</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>44.85</v>
+        <v>38.54</v>
       </c>
       <c r="Z10">
-        <v>-14.14</v>
+        <v>-16</v>
       </c>
       <c r="AA10">
-        <v>-12.86</v>
+        <v>-13.49</v>
       </c>
       <c r="AB10">
-        <v>-1.29</v>
+        <v>-2.52</v>
       </c>
       <c r="AC10">
-        <v>50.34</v>
+        <v>41.06</v>
       </c>
       <c r="AD10">
-        <v>44.75</v>
+        <v>43.7</v>
       </c>
       <c r="AE10">
-        <v>39.84</v>
+        <v>40.27</v>
       </c>
       <c r="AF10">
-        <v>85.05</v>
+        <v>26.02</v>
       </c>
       <c r="AG10">
-        <v>1589.19</v>
+        <v>1581.5</v>
       </c>
       <c r="AH10">
-        <v>1503.85</v>
+        <v>1502.3</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1961,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>16.29</v>
+        <v>17.98</v>
       </c>
     </row>
   </sheetData>
@@ -2142,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2160,1300 +2135,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-11.56</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-12.84</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3.64</v>
+      </c>
+      <c r="D11" s="6">
+        <v>3.68</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3.01</v>
+      </c>
+      <c r="D12" s="6">
+        <v>4.93</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-5.39</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.48</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.37</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-5.85</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.13</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.85</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.67</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.07</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.61</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.01</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-2.6</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.38</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.41</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.78</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.44</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-5.42</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-4.57</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-16.4</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-16.69</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>19.51</v>
+      </c>
+      <c r="D27" s="6">
+        <v>19.05</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-1.72</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>17.8</v>
+      </c>
+      <c r="D29" s="6">
+        <v>20.58</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>15.73</v>
+      </c>
+      <c r="D30" s="6">
+        <v>14.68</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-44.13</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-44.24</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-12.8</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-14.43</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>10.02</v>
+      </c>
+      <c r="D33" s="6">
+        <v>8.57</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-19.46</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-10.73</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-1.69</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-1.34</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-5.69</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1.87</v>
+      </c>
+      <c r="D38" s="6">
+        <v>5.88</v>
+      </c>
+      <c r="E38" s="7">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>14.56</v>
+      </c>
+      <c r="D39" s="6">
+        <v>13.76</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-16.21</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-15.61</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-7.49</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-6.23</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D42" s="6">
+        <v>3.94</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-5.26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-22.89</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-22.68</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-24.85</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-24.92</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-20.88</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-20.51</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-16.74</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-16.48</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-6.25</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-7.13</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-44.78</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-44.21</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-19.01</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-18.88</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-13.15</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-14.92</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>378</v>
+      </c>
+      <c r="D52" s="6">
+        <v>379</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2857.6</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2855</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>326.2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>327.75</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>351.1</v>
+      </c>
+      <c r="D55" s="6">
+        <v>352.2</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>406.75</v>
+      </c>
+      <c r="D56" s="6">
+        <v>415.05</v>
+      </c>
+      <c r="E56" s="7">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>685.05</v>
+      </c>
+      <c r="D57" s="6">
+        <v>685.7</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>194.81</v>
+      </c>
+      <c r="D58" s="6">
+        <v>196.71</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3532.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3537.8</v>
+      </c>
+      <c r="E59" s="7">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1535.9</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1504.5</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-31.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="D61" s="6">
+        <v>77</v>
+      </c>
+      <c r="E61" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>77</v>
+      </c>
+      <c r="D62" s="6">
+        <v>66</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>41.36</v>
+      </c>
+      <c r="D63" s="6">
+        <v>42.32</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>23.02</v>
+      </c>
+      <c r="D64" s="6">
+        <v>22.87</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>31.99</v>
+      </c>
+      <c r="D65" s="6">
+        <v>33.61</v>
+      </c>
+      <c r="E65" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>40.73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>41.91</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>49.37</v>
+      </c>
+      <c r="D67" s="6">
+        <v>54.25</v>
+      </c>
+      <c r="E67" s="7">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>48.91</v>
+      </c>
+      <c r="D68" s="6">
+        <v>49.11</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>34.35</v>
+      </c>
+      <c r="D69" s="6">
+        <v>39.21</v>
+      </c>
+      <c r="E69" s="7">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>42.61</v>
+      </c>
+      <c r="D70" s="6">
+        <v>43.94</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>44.85</v>
+      </c>
+      <c r="D71" s="6">
+        <v>38.54</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-6.31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-3.71</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-1.82</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-64.63</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-62.4</v>
+      </c>
+      <c r="E72" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-12.24</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-10.42</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>50.7</v>
+      </c>
+      <c r="D73" s="6">
+        <v>17.89</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-32.81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-12.25</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-11.56</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>114.6</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-123.49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-1.62</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.2</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>58.68</v>
+      </c>
+      <c r="D75" s="6">
+        <v>3.37</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-55.31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-31.94</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-57.07</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-25.13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-62.13</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-56.74</v>
+      </c>
+      <c r="E77" s="7">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-62.88</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-66.65000000000001</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-3.77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>4.66</v>
+      </c>
+      <c r="D79" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="E79" s="7">
         <v>7.54</v>
       </c>
-      <c r="D13" s="7">
-        <v>3.64</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>7.57</v>
-      </c>
-      <c r="D14" s="7">
-        <v>3.01</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-4.56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-6.46</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-5.7</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-0.25</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-6.41</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-5.37</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.24</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.28</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.11</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-5.85</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-5.93</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.07</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3.86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-1.61</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-0.87</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.28</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.43</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-2.6</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-0.17</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-0.38</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.65</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-8.449999999999999</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-5.42</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-15.8</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-16.4</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>14.3</v>
-      </c>
-      <c r="D29" s="7">
-        <v>19.51</v>
-      </c>
-      <c r="E29" s="8">
-        <v>5.21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-2.42</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-1.72</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>20.61</v>
-      </c>
-      <c r="D31" s="7">
-        <v>17.8</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>17.08</v>
-      </c>
-      <c r="D32" s="7">
-        <v>15.73</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-43.04</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-44.13</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-13.4</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-12.8</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>10.04</v>
-      </c>
-      <c r="D35" s="7">
-        <v>10.02</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-20.1</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-19.46</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-8.83</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-10.73</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-4.28</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-1.69</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-5.08</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-5.69</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>5.52</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-3.65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>14.54</v>
-      </c>
-      <c r="D41" s="7">
-        <v>14.56</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-17.63</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-16.21</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-10.08</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-7.49</v>
-      </c>
-      <c r="E43" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="D44" s="7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-23.23</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-22.89</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-24.78</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-24.85</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-22.45</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-20.88</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-16.73</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-16.74</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-5.94</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-5.27</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-7.13</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-44.77</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-44.78</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-18.77</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-19.01</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-13.31</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-13.15</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>376.35</v>
-      </c>
-      <c r="D54" s="7">
-        <v>378</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>2860</v>
-      </c>
-      <c r="D55" s="7">
-        <v>2857.6</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>319.75</v>
-      </c>
-      <c r="D56" s="7">
-        <v>326.2</v>
-      </c>
-      <c r="E56" s="8">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>351.15</v>
-      </c>
-      <c r="D57" s="7">
-        <v>351.1</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>416.4</v>
-      </c>
-      <c r="D58" s="7">
-        <v>406.75</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-9.65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>698.75</v>
-      </c>
-      <c r="D59" s="7">
-        <v>685.05</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-13.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>194.85</v>
-      </c>
-      <c r="D60" s="7">
-        <v>194.81</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>3542.7</v>
-      </c>
-      <c r="D61" s="7">
-        <v>3532.2</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-10.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1533</v>
-      </c>
-      <c r="D62" s="7">
-        <v>1535.9</v>
-      </c>
-      <c r="E62" s="8">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>39.84</v>
-      </c>
-      <c r="D63" s="7">
-        <v>41.36</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>23.14</v>
-      </c>
-      <c r="D64" s="7">
-        <v>23.02</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>24.9</v>
-      </c>
-      <c r="D65" s="7">
-        <v>31.99</v>
-      </c>
-      <c r="E65" s="8">
-        <v>7.09</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>40.77</v>
-      </c>
-      <c r="D66" s="7">
-        <v>40.73</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>55.8</v>
-      </c>
-      <c r="D67" s="7">
-        <v>49.37</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-6.43</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>53.03</v>
-      </c>
-      <c r="D68" s="7">
-        <v>48.91</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-4.12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>34.41</v>
-      </c>
-      <c r="D69" s="7">
-        <v>34.35</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>44.44</v>
-      </c>
-      <c r="D70" s="7">
-        <v>42.61</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>44.06</v>
-      </c>
-      <c r="D71" s="7">
-        <v>44.85</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="7">
-        <v>0.21</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-64.63</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-64.84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>169.21</v>
-      </c>
-      <c r="D73" s="7">
-        <v>50.7</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-118.51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>75.02</v>
-      </c>
-      <c r="D74" s="7">
-        <v>114.6</v>
-      </c>
-      <c r="E74" s="8">
-        <v>39.58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="D75" s="7">
-        <v>58.68</v>
-      </c>
-      <c r="E75" s="8">
-        <v>49.15</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>20.83</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-31.94</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-52.77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-10.13</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-62.13</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>22.76</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-62.88</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-85.64</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>38.46</v>
-      </c>
-      <c r="D79" s="7">
-        <v>4.66</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-33.8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>48.27</v>
-      </c>
-      <c r="D80" s="7">
+      <c r="C80" s="6">
         <v>85.05</v>
       </c>
+      <c r="D80" s="6">
+        <v>26.02</v>
+      </c>
       <c r="E80" s="8">
-        <v>36.78</v>
+        <v>-59.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3473,60 +3442,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>44.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>40.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>39.7</v>
-      </c>
-      <c r="E2" s="12">
-        <v>30</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-3.4</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>40.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>20</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-3.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -3628,61 +3597,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.311</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2858</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1965</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1371</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1045</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.05690000000000001</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0475</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0432</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1172</v>
+      <c r="A2" s="14">
+        <v>0.3228</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2883</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1948</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1438</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1071</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0562</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0473</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0342</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1074</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.4 → 54.2</t>
+    <t>49.1 → 51.4</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.4</t>
-  </si>
-  <si>
-    <t>54.2</t>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>51.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -797,7 +797,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -930,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>379</v>
+        <v>378.7</v>
       </c>
       <c r="D2">
-        <v>0.26</v>
+        <v>-0.08</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,25 +942,25 @@
         <v>375</v>
       </c>
       <c r="G2">
-        <v>-22.68</v>
+        <v>-22.75</v>
       </c>
       <c r="H2">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="I2">
-        <v>-1.13</v>
+        <v>0.6</v>
       </c>
       <c r="J2">
-        <v>-1.29</v>
+        <v>-1.73</v>
       </c>
       <c r="K2">
-        <v>-18.78</v>
+        <v>-16.05</v>
       </c>
       <c r="L2">
-        <v>-4.57</v>
+        <v>-7.11</v>
       </c>
       <c r="M2">
-        <v>10.71</v>
+        <v>10.32</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -969,19 +969,19 @@
         <v>42</v>
       </c>
       <c r="P2">
-        <v>379.22</v>
+        <v>379.67</v>
       </c>
       <c r="Q2">
-        <v>383.14</v>
+        <v>382.9</v>
       </c>
       <c r="R2">
-        <v>395.57</v>
+        <v>394.87</v>
       </c>
       <c r="S2">
-        <v>433.88</v>
+        <v>433.86</v>
       </c>
       <c r="T2">
-        <v>-12.65</v>
+        <v>-12.71</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.32</v>
+        <v>42.1</v>
       </c>
       <c r="Z2">
-        <v>-4.92</v>
+        <v>-4.85</v>
       </c>
       <c r="AA2">
-        <v>-5.36</v>
+        <v>-5.26</v>
       </c>
       <c r="AB2">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="AC2">
-        <v>65.34999999999999</v>
+        <v>56.58</v>
       </c>
       <c r="AD2">
-        <v>67.15000000000001</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="AE2">
-        <v>9.619999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AF2">
-        <v>-62.4</v>
+        <v>-12.22</v>
       </c>
       <c r="AG2">
-        <v>394.35</v>
+        <v>394.28</v>
       </c>
       <c r="AH2">
-        <v>371.93</v>
+        <v>371.52</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1032,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.36</v>
+        <v>32.73</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,58 +1043,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2855</v>
+        <v>2800</v>
       </c>
       <c r="D3">
-        <v>-0.09</v>
+        <v>-1.93</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
       </c>
       <c r="F3">
-        <v>2855</v>
+        <v>2800</v>
       </c>
       <c r="G3">
-        <v>-24.92</v>
+        <v>-26.36</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.67</v>
+        <v>-5.01</v>
       </c>
       <c r="J3">
-        <v>-9.369999999999999</v>
+        <v>-11.67</v>
       </c>
       <c r="K3">
-        <v>-10.68</v>
+        <v>-9.75</v>
       </c>
       <c r="L3">
-        <v>-16.69</v>
+        <v>-19.15</v>
       </c>
       <c r="M3">
-        <v>28.83</v>
+        <v>27.01</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P3">
-        <v>2894.08</v>
+        <v>2864.52</v>
       </c>
       <c r="Q3">
-        <v>3027.34</v>
+        <v>3009.34</v>
       </c>
       <c r="R3">
-        <v>3229.14</v>
+        <v>3220.37</v>
       </c>
       <c r="S3">
-        <v>3267.99</v>
+        <v>3263.93</v>
       </c>
       <c r="T3">
-        <v>-12.64</v>
+        <v>-14.21</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,43 +1109,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>22.87</v>
+        <v>20</v>
       </c>
       <c r="Z3">
-        <v>-96.65000000000001</v>
+        <v>-102.34</v>
       </c>
       <c r="AA3">
-        <v>-83.45</v>
+        <v>-87.23</v>
       </c>
       <c r="AB3">
-        <v>-13.2</v>
+        <v>-15.11</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>12.4</v>
+        <v>4.27</v>
       </c>
       <c r="AE3">
-        <v>62.59</v>
+        <v>62.05</v>
       </c>
       <c r="AF3">
-        <v>17.89</v>
+        <v>49.24</v>
       </c>
       <c r="AG3">
-        <v>3218.62</v>
+        <v>3215.25</v>
       </c>
       <c r="AH3">
-        <v>2836.05</v>
+        <v>2803.42</v>
       </c>
       <c r="AI3">
-        <v>3039.43</v>
+        <v>3005.1</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>82.95999999999999</v>
+        <v>84.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,58 +1156,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>327.75</v>
+        <v>321.75</v>
       </c>
       <c r="D4">
-        <v>0.48</v>
+        <v>-1.83</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>273.4</v>
+        <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-20.51</v>
+        <v>-21.96</v>
       </c>
       <c r="H4">
-        <v>19.88</v>
+        <v>16.7</v>
       </c>
       <c r="I4">
-        <v>-1.21</v>
+        <v>-1.92</v>
       </c>
       <c r="J4">
-        <v>-12.84</v>
+        <v>-13.89</v>
       </c>
       <c r="K4">
-        <v>-1.34</v>
+        <v>-2.99</v>
       </c>
       <c r="L4">
-        <v>19.05</v>
+        <v>17.68</v>
       </c>
       <c r="M4">
-        <v>14.38</v>
+        <v>13.83</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>325.32</v>
+        <v>324.06</v>
       </c>
       <c r="Q4">
-        <v>344.96</v>
+        <v>342.43</v>
       </c>
       <c r="R4">
-        <v>369.82</v>
+        <v>369</v>
       </c>
       <c r="S4">
-        <v>343.4</v>
+        <v>343.25</v>
       </c>
       <c r="T4">
-        <v>-4.56</v>
+        <v>-6.26</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1222,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>33.61</v>
+        <v>30.57</v>
       </c>
       <c r="Z4">
-        <v>-12.05</v>
+        <v>-12.21</v>
       </c>
       <c r="AA4">
-        <v>-10.33</v>
+        <v>-10.71</v>
       </c>
       <c r="AB4">
-        <v>-1.72</v>
+        <v>-1.5</v>
       </c>
       <c r="AC4">
-        <v>30.67</v>
+        <v>41.68</v>
       </c>
       <c r="AD4">
-        <v>14.81</v>
+        <v>28.71</v>
       </c>
       <c r="AE4">
-        <v>10.91</v>
+        <v>10.93</v>
       </c>
       <c r="AF4">
-        <v>-8.890000000000001</v>
+        <v>4.06</v>
       </c>
       <c r="AG4">
-        <v>376.92</v>
+        <v>373.26</v>
       </c>
       <c r="AH4">
-        <v>313</v>
+        <v>311.61</v>
       </c>
       <c r="AI4">
         <v>351.78</v>
@@ -1258,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>37.81</v>
+        <v>35.32</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>352.2</v>
+        <v>351.1</v>
       </c>
       <c r="D5">
-        <v>0.31</v>
+        <v>-0.31</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.48</v>
+        <v>-16.74</v>
       </c>
       <c r="H5">
-        <v>19.69</v>
+        <v>19.32</v>
       </c>
       <c r="I5">
-        <v>-3</v>
+        <v>-2.74</v>
       </c>
       <c r="J5">
-        <v>-3</v>
+        <v>-3.12</v>
       </c>
       <c r="K5">
-        <v>-5.04</v>
+        <v>-2.21</v>
       </c>
       <c r="L5">
-        <v>-0.33</v>
+        <v>-2.77</v>
       </c>
       <c r="M5">
-        <v>5.62</v>
+        <v>5.16</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>355.15</v>
+        <v>353.17</v>
       </c>
       <c r="Q5">
-        <v>357.86</v>
+        <v>357.4</v>
       </c>
       <c r="R5">
-        <v>370.55</v>
+        <v>369.96</v>
       </c>
       <c r="S5">
-        <v>358.67</v>
+        <v>358.43</v>
       </c>
       <c r="T5">
-        <v>-1.8</v>
+        <v>-2.05</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.91</v>
+        <v>41.03</v>
       </c>
       <c r="Z5">
-        <v>-3.83</v>
+        <v>-3.97</v>
       </c>
       <c r="AA5">
-        <v>-3.77</v>
+        <v>-3.81</v>
       </c>
       <c r="AB5">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="AC5">
-        <v>53.79</v>
+        <v>37.48</v>
       </c>
       <c r="AD5">
-        <v>64.18000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="AE5">
-        <v>11.85</v>
+        <v>11.89</v>
       </c>
       <c r="AF5">
-        <v>3.37</v>
+        <v>159.07</v>
       </c>
       <c r="AG5">
-        <v>371.6</v>
+        <v>371.42</v>
       </c>
       <c r="AH5">
-        <v>344.12</v>
+        <v>343.39</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1371,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>34.57</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>415.05</v>
+        <v>411.15</v>
       </c>
       <c r="D6">
-        <v>2.04</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-6.25</v>
+        <v>-7.13</v>
       </c>
       <c r="H6">
-        <v>48.47</v>
+        <v>47.08</v>
       </c>
       <c r="I6">
-        <v>-1.6</v>
+        <v>-3.42</v>
       </c>
       <c r="J6">
-        <v>3.68</v>
+        <v>1.43</v>
       </c>
       <c r="K6">
-        <v>5.88</v>
+        <v>7.49</v>
       </c>
       <c r="L6">
-        <v>20.58</v>
+        <v>18.08</v>
       </c>
       <c r="M6">
-        <v>-10.74</v>
+        <v>-11.18</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>419.95</v>
+        <v>417.04</v>
       </c>
       <c r="Q6">
-        <v>407.27</v>
+        <v>407.67</v>
       </c>
       <c r="R6">
-        <v>405.81</v>
+        <v>405.65</v>
       </c>
       <c r="S6">
-        <v>376.51</v>
+        <v>376.99</v>
       </c>
       <c r="T6">
-        <v>10.24</v>
+        <v>9.06</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>54.25</v>
+        <v>51.73</v>
       </c>
       <c r="Z6">
-        <v>5.26</v>
+        <v>4.66</v>
       </c>
       <c r="AA6">
-        <v>4.35</v>
+        <v>4.41</v>
       </c>
       <c r="AB6">
-        <v>0.91</v>
+        <v>0.25</v>
       </c>
       <c r="AC6">
-        <v>39.74</v>
+        <v>33.8</v>
       </c>
       <c r="AD6">
-        <v>60.33</v>
+        <v>44.1</v>
       </c>
       <c r="AE6">
-        <v>14.12</v>
+        <v>13.95</v>
       </c>
       <c r="AF6">
-        <v>-57.07</v>
+        <v>-43.16</v>
       </c>
       <c r="AG6">
-        <v>434.76</v>
+        <v>435.14</v>
       </c>
       <c r="AH6">
-        <v>379.79</v>
+        <v>380.2</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1484,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>35.09</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>685.7</v>
+        <v>692.75</v>
       </c>
       <c r="D7">
-        <v>0.09</v>
+        <v>1.03</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1507,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-7.04</v>
+        <v>-6.09</v>
       </c>
       <c r="H7">
-        <v>35.39</v>
+        <v>36.79</v>
       </c>
       <c r="I7">
-        <v>-4.01</v>
+        <v>-4.03</v>
       </c>
       <c r="J7">
-        <v>4.93</v>
+        <v>0.68</v>
       </c>
       <c r="K7">
-        <v>13.76</v>
+        <v>18.83</v>
       </c>
       <c r="L7">
-        <v>14.68</v>
+        <v>16.78</v>
       </c>
       <c r="M7">
-        <v>32.28</v>
+        <v>31.82</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>705.8</v>
+        <v>699.98</v>
       </c>
       <c r="Q7">
-        <v>705</v>
+        <v>705.1900000000001</v>
       </c>
       <c r="R7">
-        <v>650.99</v>
+        <v>653.3099999999999</v>
       </c>
       <c r="S7">
-        <v>600.79</v>
+        <v>601.45</v>
       </c>
       <c r="T7">
-        <v>14.13</v>
+        <v>15.18</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>49.11</v>
+        <v>51.36</v>
       </c>
       <c r="Z7">
-        <v>12.98</v>
+        <v>11.24</v>
       </c>
       <c r="AA7">
-        <v>18.86</v>
+        <v>17.34</v>
       </c>
       <c r="AB7">
-        <v>-5.88</v>
+        <v>-6.1</v>
       </c>
       <c r="AC7">
-        <v>0.35</v>
+        <v>4.59</v>
       </c>
       <c r="AD7">
-        <v>16.17</v>
+        <v>7.79</v>
       </c>
       <c r="AE7">
-        <v>27.47</v>
+        <v>27.45</v>
       </c>
       <c r="AF7">
-        <v>-56.74</v>
+        <v>-25.47</v>
       </c>
       <c r="AG7">
-        <v>738.83</v>
+        <v>738.6799999999999</v>
       </c>
       <c r="AH7">
-        <v>671.1799999999999</v>
+        <v>671.7</v>
       </c>
       <c r="AI7">
         <v>664.6799999999999</v>
@@ -1597,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>32.73</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>196.71</v>
+        <v>195.07</v>
       </c>
       <c r="D8">
-        <v>0.98</v>
+        <v>-0.83</v>
       </c>
       <c r="E8">
         <v>352.6</v>
@@ -1620,46 +1620,46 @@
         <v>192.4</v>
       </c>
       <c r="G8">
-        <v>-44.21</v>
+        <v>-44.68</v>
       </c>
       <c r="H8">
-        <v>2.24</v>
+        <v>1.39</v>
       </c>
       <c r="I8">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J8">
-        <v>-5.39</v>
+        <v>-5.95</v>
       </c>
       <c r="K8">
-        <v>-15.61</v>
+        <v>-15.92</v>
       </c>
       <c r="L8">
-        <v>-44.24</v>
+        <v>-44</v>
       </c>
       <c r="M8">
-        <v>-3.42</v>
+        <v>-3.9</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>195.02</v>
+        <v>195.14</v>
       </c>
       <c r="Q8">
-        <v>197.84</v>
+        <v>197.32</v>
       </c>
       <c r="R8">
-        <v>211.03</v>
+        <v>210.45</v>
       </c>
       <c r="S8">
-        <v>248.32</v>
+        <v>247.78</v>
       </c>
       <c r="T8">
-        <v>-20.78</v>
+        <v>-21.27</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.21</v>
+        <v>36.69</v>
       </c>
       <c r="Z8">
-        <v>-4.37</v>
+        <v>-4.21</v>
       </c>
       <c r="AA8">
-        <v>-4.95</v>
+        <v>-4.8</v>
       </c>
       <c r="AB8">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="AC8">
         <v>74.22</v>
       </c>
       <c r="AD8">
-        <v>67.68000000000001</v>
+        <v>71.23</v>
       </c>
       <c r="AE8">
-        <v>5.53</v>
+        <v>5.39</v>
       </c>
       <c r="AF8">
-        <v>-66.65000000000001</v>
+        <v>-74.25</v>
       </c>
       <c r="AG8">
-        <v>205.32</v>
+        <v>203.95</v>
       </c>
       <c r="AH8">
-        <v>190.36</v>
+        <v>190.69</v>
       </c>
       <c r="AI8">
         <v>210.65</v>
@@ -1710,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>27.75</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3537.8</v>
+        <v>3546.1</v>
       </c>
       <c r="D9">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1733,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.88</v>
+        <v>-18.69</v>
       </c>
       <c r="H9">
-        <v>6.92</v>
+        <v>7.17</v>
       </c>
       <c r="I9">
-        <v>-0.41</v>
+        <v>-0.06</v>
       </c>
       <c r="J9">
-        <v>-0.48</v>
+        <v>-0.33</v>
       </c>
       <c r="K9">
-        <v>-6.23</v>
+        <v>-5.28</v>
       </c>
       <c r="L9">
-        <v>-14.43</v>
+        <v>-14.13</v>
       </c>
       <c r="M9">
-        <v>19.48</v>
+        <v>19.49</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>3541.42</v>
+        <v>3541</v>
       </c>
       <c r="Q9">
-        <v>3565.78</v>
+        <v>3560.68</v>
       </c>
       <c r="R9">
-        <v>3577.79</v>
+        <v>3576.61</v>
       </c>
       <c r="S9">
-        <v>3671.18</v>
+        <v>3670.76</v>
       </c>
       <c r="T9">
-        <v>-3.63</v>
+        <v>-3.4</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.94</v>
+        <v>45.94</v>
       </c>
       <c r="Z9">
-        <v>-14.14</v>
+        <v>-13.39</v>
       </c>
       <c r="AA9">
         <v>-13.37</v>
       </c>
       <c r="AB9">
-        <v>-0.78</v>
+        <v>-0.02</v>
       </c>
       <c r="AC9">
-        <v>24.48</v>
+        <v>23.4</v>
       </c>
       <c r="AD9">
-        <v>28.08</v>
+        <v>24.92</v>
       </c>
       <c r="AE9">
-        <v>60.12</v>
+        <v>59.42</v>
       </c>
       <c r="AF9">
-        <v>12.2</v>
+        <v>22.7</v>
       </c>
       <c r="AG9">
-        <v>3633.72</v>
+        <v>3616.94</v>
       </c>
       <c r="AH9">
-        <v>3497.83</v>
+        <v>3504.42</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1823,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>11.48</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1504.5</v>
+        <v>1491.1</v>
       </c>
       <c r="D10">
-        <v>-2.04</v>
+        <v>-0.89</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-14.92</v>
+        <v>-15.68</v>
       </c>
       <c r="H10">
-        <v>13.44</v>
+        <v>12.43</v>
       </c>
       <c r="I10">
-        <v>-2.44</v>
+        <v>-1.28</v>
       </c>
       <c r="J10">
-        <v>-5.85</v>
+        <v>-6.63</v>
       </c>
       <c r="K10">
-        <v>3.94</v>
+        <v>4.36</v>
       </c>
       <c r="L10">
-        <v>8.57</v>
+        <v>6.41</v>
       </c>
       <c r="M10">
-        <v>4.73</v>
+        <v>4.07</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P10">
-        <v>1521.58</v>
+        <v>1517.7</v>
       </c>
       <c r="Q10">
-        <v>1541.9</v>
+        <v>1538.25</v>
       </c>
       <c r="R10">
-        <v>1588.8</v>
+        <v>1587.12</v>
       </c>
       <c r="S10">
-        <v>1517.28</v>
+        <v>1516.84</v>
       </c>
       <c r="T10">
-        <v>-0.84</v>
+        <v>-1.7</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,43 +1900,43 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>38.54</v>
+        <v>36.2</v>
       </c>
       <c r="Z10">
-        <v>-16</v>
+        <v>-18.34</v>
       </c>
       <c r="AA10">
-        <v>-13.49</v>
+        <v>-14.46</v>
       </c>
       <c r="AB10">
-        <v>-2.52</v>
+        <v>-3.89</v>
       </c>
       <c r="AC10">
-        <v>41.06</v>
+        <v>22.77</v>
       </c>
       <c r="AD10">
-        <v>43.7</v>
+        <v>38.06</v>
       </c>
       <c r="AE10">
-        <v>40.27</v>
+        <v>39.31</v>
       </c>
       <c r="AF10">
-        <v>26.02</v>
+        <v>-35.05</v>
       </c>
       <c r="AG10">
-        <v>1581.5</v>
+        <v>1582.45</v>
       </c>
       <c r="AH10">
-        <v>1502.3</v>
+        <v>1494.06</v>
       </c>
       <c r="AI10">
-        <v>1630.7</v>
+        <v>1617.52</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>17.98</v>
+        <v>20.47</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2169,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-1.82</v>
+        <v>-1.29</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.29</v>
+        <v>-1.73</v>
       </c>
       <c r="E7" s="7">
-        <v>0.53</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-10.42</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="D8" s="6">
-        <v>-9.369999999999999</v>
+        <v>-11.67</v>
       </c>
       <c r="E8" s="7">
-        <v>1.05</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2203,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-11.56</v>
+        <v>-12.84</v>
       </c>
       <c r="D9" s="6">
-        <v>-12.84</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.28</v>
+        <v>-13.89</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2220,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="D10" s="6">
-        <v>-3</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.8</v>
+        <v>-3.12</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="D11" s="6">
-        <v>3.68</v>
+        <v>1.43</v>
       </c>
       <c r="E11" s="7">
-        <v>0.04</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2254,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>3.01</v>
+        <v>4.93</v>
       </c>
       <c r="D12" s="6">
-        <v>4.93</v>
+        <v>0.68</v>
       </c>
       <c r="E12" s="7">
-        <v>1.92</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2271,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-5.7</v>
+        <v>-5.39</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.39</v>
+        <v>-5.95</v>
       </c>
       <c r="E13" s="7">
-        <v>0.31</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2288,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.25</v>
+        <v>-0.48</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.48</v>
+        <v>-0.33</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.23</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.37</v>
+        <v>-5.85</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.85</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.48</v>
+        <v>-6.63</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2322,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.28</v>
+        <v>-1.13</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.13</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.15</v>
+        <v>0.6</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.73</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.85</v>
+        <v>-4.67</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.67</v>
+        <v>-5.01</v>
       </c>
       <c r="E17" s="7">
-        <v>1.18</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.07</v>
+        <v>-1.21</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.21</v>
+        <v>-1.92</v>
       </c>
       <c r="E18" s="7">
-        <v>0.86</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2373,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.61</v>
+        <v>-3</v>
       </c>
       <c r="D19" s="6">
-        <v>-3</v>
+        <v>-2.74</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.39</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2390,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.21</v>
+        <v>-1.6</v>
       </c>
       <c r="D20" s="6">
-        <v>-1.6</v>
+        <v>-3.42</v>
       </c>
       <c r="E20" s="7">
-        <v>1.61</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2407,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.28</v>
+        <v>-4.01</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.01</v>
+        <v>-4.03</v>
       </c>
       <c r="E21" s="7">
-        <v>0.27</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2424,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.6</v>
+        <v>0.4</v>
       </c>
       <c r="D22" s="6">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E22" s="7">
-        <v>3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.41</v>
+        <v>-0.06</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.03</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2458,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.78</v>
+        <v>-2.44</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.44</v>
+        <v>-1.28</v>
       </c>
       <c r="E24" s="8">
-        <v>-1.66</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2475,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-5.42</v>
+        <v>-4.57</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.57</v>
+        <v>-7.11</v>
       </c>
       <c r="E25" s="7">
-        <v>0.85</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="D26" s="6">
-        <v>-16.69</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.29</v>
+        <v>-19.15</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>19.51</v>
+        <v>19.05</v>
       </c>
       <c r="D27" s="6">
-        <v>19.05</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.46</v>
+        <v>17.68</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.72</v>
+        <v>-0.33</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.33</v>
+        <v>-2.77</v>
       </c>
       <c r="E28" s="7">
-        <v>1.39</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>17.8</v>
+        <v>20.58</v>
       </c>
       <c r="D29" s="6">
-        <v>20.58</v>
+        <v>18.08</v>
       </c>
       <c r="E29" s="7">
-        <v>2.78</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>15.73</v>
+        <v>14.68</v>
       </c>
       <c r="D30" s="6">
-        <v>14.68</v>
+        <v>16.78</v>
       </c>
       <c r="E30" s="8">
-        <v>-1.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-44.13</v>
+        <v>-44.24</v>
       </c>
       <c r="D31" s="6">
-        <v>-44.24</v>
+        <v>-44</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.11</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-12.8</v>
+        <v>-14.43</v>
       </c>
       <c r="D32" s="6">
-        <v>-14.43</v>
+        <v>-14.13</v>
       </c>
       <c r="E32" s="8">
-        <v>-1.63</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>10.02</v>
+        <v>8.57</v>
       </c>
       <c r="D33" s="6">
-        <v>8.57</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.45</v>
+        <v>6.41</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-19.46</v>
+        <v>-18.78</v>
       </c>
       <c r="D34" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.68</v>
+        <v>-16.05</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2.73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-10.73</v>
+        <v>-10.68</v>
       </c>
       <c r="D35" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.05</v>
+        <v>-9.75</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.69</v>
+        <v>-1.34</v>
       </c>
       <c r="D36" s="6">
-        <v>-1.34</v>
+        <v>-2.99</v>
       </c>
       <c r="E36" s="7">
-        <v>0.35</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.69</v>
+        <v>-5.04</v>
       </c>
       <c r="D37" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.65</v>
+        <v>-2.21</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2.83</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>1.87</v>
+        <v>5.88</v>
       </c>
       <c r="D38" s="6">
-        <v>5.88</v>
-      </c>
-      <c r="E38" s="7">
-        <v>4.01</v>
+        <v>7.49</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.61</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>14.56</v>
+        <v>13.76</v>
       </c>
       <c r="D39" s="6">
-        <v>13.76</v>
+        <v>18.83</v>
       </c>
       <c r="E39" s="8">
-        <v>-0.8</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-16.21</v>
+        <v>-15.61</v>
       </c>
       <c r="D40" s="6">
-        <v>-15.61</v>
+        <v>-15.92</v>
       </c>
       <c r="E40" s="7">
-        <v>0.6</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-7.49</v>
+        <v>-6.23</v>
       </c>
       <c r="D41" s="6">
-        <v>-6.23</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.26</v>
+        <v>-5.28</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.95</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>9.199999999999999</v>
+        <v>3.94</v>
       </c>
       <c r="D42" s="6">
-        <v>3.94</v>
+        <v>4.36</v>
       </c>
       <c r="E42" s="8">
-        <v>-5.26</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-22.89</v>
+        <v>-22.68</v>
       </c>
       <c r="D43" s="6">
-        <v>-22.68</v>
+        <v>-22.75</v>
       </c>
       <c r="E43" s="7">
-        <v>0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-24.85</v>
+        <v>-24.92</v>
       </c>
       <c r="D44" s="6">
-        <v>-24.92</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-26.36</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-20.88</v>
+        <v>-20.51</v>
       </c>
       <c r="D45" s="6">
-        <v>-20.51</v>
+        <v>-21.96</v>
       </c>
       <c r="E45" s="7">
-        <v>0.37</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
+        <v>-16.48</v>
+      </c>
+      <c r="D46" s="6">
         <v>-16.74</v>
       </c>
-      <c r="D46" s="6">
-        <v>-16.48</v>
-      </c>
       <c r="E46" s="7">
-        <v>0.26</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,13 +2849,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-8.119999999999999</v>
+        <v>-6.25</v>
       </c>
       <c r="D47" s="6">
-        <v>-6.25</v>
+        <v>-7.13</v>
       </c>
       <c r="E47" s="7">
-        <v>1.87</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2866,13 +2866,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-7.13</v>
+        <v>-7.04</v>
       </c>
       <c r="D48" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.09</v>
+        <v>-6.09</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.95</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2883,13 +2883,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-44.78</v>
+        <v>-44.21</v>
       </c>
       <c r="D49" s="6">
-        <v>-44.21</v>
+        <v>-44.68</v>
       </c>
       <c r="E49" s="7">
-        <v>0.57</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2900,13 +2900,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-19.01</v>
+        <v>-18.88</v>
       </c>
       <c r="D50" s="6">
-        <v>-18.88</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.13</v>
+        <v>-18.69</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2917,13 +2917,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-13.15</v>
+        <v>-14.92</v>
       </c>
       <c r="D51" s="6">
-        <v>-14.92</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.77</v>
+        <v>-15.68</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2934,13 +2934,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D52" s="6">
-        <v>379</v>
+        <v>378.7</v>
       </c>
       <c r="E52" s="7">
-        <v>1</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2951,13 +2951,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2857.6</v>
+        <v>2855</v>
       </c>
       <c r="D53" s="6">
-        <v>2855</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2.6</v>
+        <v>2800</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-55</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2968,13 +2968,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>326.2</v>
+        <v>327.75</v>
       </c>
       <c r="D54" s="6">
-        <v>327.75</v>
+        <v>321.75</v>
       </c>
       <c r="E54" s="7">
-        <v>1.55</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
+        <v>352.2</v>
+      </c>
+      <c r="D55" s="6">
         <v>351.1</v>
       </c>
-      <c r="D55" s="6">
-        <v>352.2</v>
-      </c>
       <c r="E55" s="7">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3002,13 +3002,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>406.75</v>
+        <v>415.05</v>
       </c>
       <c r="D56" s="6">
-        <v>415.05</v>
+        <v>411.15</v>
       </c>
       <c r="E56" s="7">
-        <v>8.300000000000001</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3019,13 +3019,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>685.05</v>
+        <v>685.7</v>
       </c>
       <c r="D57" s="6">
-        <v>685.7</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.65</v>
+        <v>692.75</v>
+      </c>
+      <c r="E57" s="8">
+        <v>7.05</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3036,13 +3036,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>194.81</v>
+        <v>196.71</v>
       </c>
       <c r="D58" s="6">
-        <v>196.71</v>
+        <v>195.07</v>
       </c>
       <c r="E58" s="7">
-        <v>1.9</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3053,13 +3053,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3532.2</v>
+        <v>3537.8</v>
       </c>
       <c r="D59" s="6">
-        <v>3537.8</v>
-      </c>
-      <c r="E59" s="7">
-        <v>5.6</v>
+        <v>3546.1</v>
+      </c>
+      <c r="E59" s="8">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3070,353 +3070,319 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1535.9</v>
+        <v>1504.5</v>
       </c>
       <c r="D60" s="6">
-        <v>1504.5</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-31.4</v>
+        <v>1491.1</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-13.4</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>66</v>
+        <v>42.32</v>
       </c>
       <c r="D61" s="6">
-        <v>77</v>
+        <v>42.1</v>
       </c>
       <c r="E61" s="7">
-        <v>11</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>77</v>
+        <v>22.87</v>
       </c>
       <c r="D62" s="6">
-        <v>66</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
+        <v>20</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>41.36</v>
+        <v>33.61</v>
       </c>
       <c r="D63" s="6">
-        <v>42.32</v>
+        <v>30.57</v>
       </c>
       <c r="E63" s="7">
-        <v>0.96</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>23.02</v>
+        <v>41.91</v>
       </c>
       <c r="D64" s="6">
-        <v>22.87</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.15</v>
+        <v>41.03</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>31.99</v>
+        <v>54.25</v>
       </c>
       <c r="D65" s="6">
-        <v>33.61</v>
+        <v>51.73</v>
       </c>
       <c r="E65" s="7">
-        <v>1.62</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>40.73</v>
+        <v>49.11</v>
       </c>
       <c r="D66" s="6">
-        <v>41.91</v>
-      </c>
-      <c r="E66" s="7">
-        <v>1.18</v>
+        <v>51.36</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.25</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>49.37</v>
+        <v>39.21</v>
       </c>
       <c r="D67" s="6">
-        <v>54.25</v>
+        <v>36.69</v>
       </c>
       <c r="E67" s="7">
-        <v>4.88</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>48.91</v>
+        <v>43.94</v>
       </c>
       <c r="D68" s="6">
-        <v>49.11</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.2</v>
+        <v>45.94</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>34.35</v>
+        <v>38.54</v>
       </c>
       <c r="D69" s="6">
-        <v>39.21</v>
+        <v>36.2</v>
       </c>
       <c r="E69" s="7">
-        <v>4.86</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>42.61</v>
+        <v>-62.4</v>
       </c>
       <c r="D70" s="6">
-        <v>43.94</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.33</v>
+        <v>-12.22</v>
+      </c>
+      <c r="E70" s="8">
+        <v>50.18</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>44.85</v>
+        <v>17.89</v>
       </c>
       <c r="D71" s="6">
-        <v>38.54</v>
+        <v>49.24</v>
       </c>
       <c r="E71" s="8">
-        <v>-6.31</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>-64.63</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="D72" s="6">
-        <v>-62.4</v>
-      </c>
-      <c r="E72" s="7">
-        <v>2.23</v>
+        <v>4.06</v>
+      </c>
+      <c r="E72" s="8">
+        <v>12.95</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>50.7</v>
+        <v>3.37</v>
       </c>
       <c r="D73" s="6">
-        <v>17.89</v>
+        <v>159.07</v>
       </c>
       <c r="E73" s="8">
-        <v>-32.81</v>
+        <v>155.7</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>114.6</v>
+        <v>-57.07</v>
       </c>
       <c r="D74" s="6">
-        <v>-8.890000000000001</v>
+        <v>-43.16</v>
       </c>
       <c r="E74" s="8">
-        <v>-123.49</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>58.68</v>
+        <v>-56.74</v>
       </c>
       <c r="D75" s="6">
-        <v>3.37</v>
+        <v>-25.47</v>
       </c>
       <c r="E75" s="8">
-        <v>-55.31</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-31.94</v>
+        <v>-66.65000000000001</v>
       </c>
       <c r="D76" s="6">
-        <v>-57.07</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-25.13</v>
+        <v>-74.25</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-7.6</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-62.13</v>
+        <v>12.2</v>
       </c>
       <c r="D77" s="6">
-        <v>-56.74</v>
-      </c>
-      <c r="E77" s="7">
-        <v>5.39</v>
+        <v>22.7</v>
+      </c>
+      <c r="E77" s="8">
+        <v>10.5</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-62.88</v>
+        <v>26.02</v>
       </c>
       <c r="D78" s="6">
-        <v>-66.65000000000001</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>4.66</v>
-      </c>
-      <c r="D79" s="6">
-        <v>12.2</v>
-      </c>
-      <c r="E79" s="7">
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>85.05</v>
-      </c>
-      <c r="D80" s="6">
-        <v>26.02</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-59.03</v>
+        <v>-35.05</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-61.07</v>
       </c>
     </row>
   </sheetData>
@@ -3481,16 +3447,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>40.6</v>
+        <v>39.5</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.3</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.8</v>
+        <v>-2.4</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3627,31 +3593,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3228</v>
+        <v>0.3182</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2883</v>
+        <v>0.2701</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1948</v>
+        <v>0.1949</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1438</v>
+        <v>0.1383</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1071</v>
+        <v>0.1032</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0562</v>
+        <v>0.0516</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0473</v>
+        <v>0.0407</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0342</v>
+        <v>-0.039</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1074</v>
+        <v>-0.1118</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.1 → 51.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>51.7 → 43.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>43.0</t>
+  </si>
+  <si>
+    <t>51.4 → 38.7</t>
   </si>
   <si>
     <t>51.4</t>
+  </si>
+  <si>
+    <t>38.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,8 +426,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,58 +939,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>378.7</v>
+        <v>371.65</v>
       </c>
       <c r="D2">
-        <v>-0.08</v>
+        <v>-1.86</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>375</v>
+        <v>371.65</v>
       </c>
       <c r="G2">
-        <v>-22.75</v>
+        <v>-24.18</v>
       </c>
       <c r="H2">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.6</v>
+        <v>-3.79</v>
       </c>
       <c r="J2">
-        <v>-1.73</v>
+        <v>-3.1</v>
       </c>
       <c r="K2">
-        <v>-16.05</v>
+        <v>-19.53</v>
       </c>
       <c r="L2">
-        <v>-7.11</v>
+        <v>-8.56</v>
       </c>
       <c r="M2">
-        <v>10.32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>379.67</v>
+        <v>376.74</v>
       </c>
       <c r="Q2">
-        <v>382.9</v>
+        <v>382.31</v>
       </c>
       <c r="R2">
-        <v>394.87</v>
+        <v>394.14</v>
       </c>
       <c r="S2">
-        <v>433.86</v>
+        <v>433.78</v>
       </c>
       <c r="T2">
-        <v>-12.71</v>
+        <v>-14.32</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1005,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.1</v>
+        <v>37.18</v>
       </c>
       <c r="Z2">
-        <v>-4.85</v>
+        <v>-5.3</v>
       </c>
       <c r="AA2">
-        <v>-5.26</v>
+        <v>-5.27</v>
       </c>
       <c r="AB2">
-        <v>0.41</v>
+        <v>-0.03</v>
       </c>
       <c r="AC2">
-        <v>56.58</v>
+        <v>35.42</v>
       </c>
       <c r="AD2">
-        <v>64.15000000000001</v>
+        <v>52.45</v>
       </c>
       <c r="AE2">
-        <v>9.460000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="AF2">
-        <v>-12.22</v>
+        <v>-29.55</v>
       </c>
       <c r="AG2">
-        <v>394.28</v>
+        <v>394.75</v>
       </c>
       <c r="AH2">
-        <v>371.52</v>
+        <v>369.87</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1032,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.73</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,58 +1052,58 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2800</v>
+        <v>2751.2</v>
       </c>
       <c r="D3">
-        <v>-1.93</v>
+        <v>-1.74</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
       </c>
       <c r="F3">
-        <v>2800</v>
+        <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-26.36</v>
+        <v>-27.65</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-5.01</v>
+        <v>-6.74</v>
       </c>
       <c r="J3">
-        <v>-11.67</v>
+        <v>-12.94</v>
       </c>
       <c r="K3">
-        <v>-9.75</v>
+        <v>-10.83</v>
       </c>
       <c r="L3">
-        <v>-19.15</v>
+        <v>-20.53</v>
       </c>
       <c r="M3">
-        <v>27.01</v>
+        <v>26.58</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P3">
-        <v>2864.52</v>
+        <v>2824.76</v>
       </c>
       <c r="Q3">
-        <v>3009.34</v>
+        <v>2988.9</v>
       </c>
       <c r="R3">
-        <v>3220.37</v>
+        <v>3209.97</v>
       </c>
       <c r="S3">
-        <v>3263.93</v>
+        <v>3259.75</v>
       </c>
       <c r="T3">
-        <v>-14.21</v>
+        <v>-15.6</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,43 +1118,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>20</v>
+        <v>17.86</v>
       </c>
       <c r="Z3">
-        <v>-102.34</v>
+        <v>-109.53</v>
       </c>
       <c r="AA3">
-        <v>-87.23</v>
+        <v>-91.69</v>
       </c>
       <c r="AB3">
-        <v>-15.11</v>
+        <v>-17.84</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>62.05</v>
+        <v>62.03</v>
       </c>
       <c r="AF3">
-        <v>49.24</v>
+        <v>39.99</v>
       </c>
       <c r="AG3">
-        <v>3215.25</v>
+        <v>3212.26</v>
       </c>
       <c r="AH3">
-        <v>2803.42</v>
+        <v>2765.53</v>
       </c>
       <c r="AI3">
-        <v>3005.1</v>
+        <v>2961.3</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>84.58</v>
+        <v>86.15000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>321.75</v>
+        <v>310.5</v>
       </c>
       <c r="D4">
-        <v>-1.83</v>
+        <v>-3.5</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1177,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-21.96</v>
+        <v>-24.69</v>
       </c>
       <c r="H4">
-        <v>16.7</v>
+        <v>12.62</v>
       </c>
       <c r="I4">
-        <v>-1.92</v>
+        <v>-4.42</v>
       </c>
       <c r="J4">
-        <v>-13.89</v>
+        <v>-16.61</v>
       </c>
       <c r="K4">
-        <v>-2.99</v>
+        <v>-7.8</v>
       </c>
       <c r="L4">
-        <v>17.68</v>
+        <v>12.6</v>
       </c>
       <c r="M4">
-        <v>13.83</v>
+        <v>12.77</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>324.06</v>
+        <v>321.19</v>
       </c>
       <c r="Q4">
-        <v>342.43</v>
+        <v>339.24</v>
       </c>
       <c r="R4">
-        <v>369</v>
+        <v>367.74</v>
       </c>
       <c r="S4">
-        <v>343.25</v>
+        <v>342.98</v>
       </c>
       <c r="T4">
-        <v>-6.26</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,43 +1231,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>30.57</v>
+        <v>25.85</v>
       </c>
       <c r="Z4">
-        <v>-12.21</v>
+        <v>-13.1</v>
       </c>
       <c r="AA4">
-        <v>-10.71</v>
+        <v>-11.19</v>
       </c>
       <c r="AB4">
-        <v>-1.5</v>
+        <v>-1.91</v>
       </c>
       <c r="AC4">
-        <v>41.68</v>
+        <v>29.77</v>
       </c>
       <c r="AD4">
-        <v>28.71</v>
+        <v>34.04</v>
       </c>
       <c r="AE4">
-        <v>10.93</v>
+        <v>11.04</v>
       </c>
       <c r="AF4">
-        <v>4.06</v>
+        <v>12.77</v>
       </c>
       <c r="AG4">
-        <v>373.26</v>
+        <v>369.36</v>
       </c>
       <c r="AH4">
-        <v>311.61</v>
+        <v>309.12</v>
       </c>
       <c r="AI4">
-        <v>351.78</v>
+        <v>348.6</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>35.32</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>351.1</v>
+        <v>342.1</v>
       </c>
       <c r="D5">
-        <v>-0.31</v>
+        <v>-2.56</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,25 +1290,25 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.74</v>
+        <v>-18.88</v>
       </c>
       <c r="H5">
-        <v>19.32</v>
+        <v>16.26</v>
       </c>
       <c r="I5">
-        <v>-2.74</v>
+        <v>-5.05</v>
       </c>
       <c r="J5">
-        <v>-3.12</v>
+        <v>-5.01</v>
       </c>
       <c r="K5">
-        <v>-2.21</v>
+        <v>-7.04</v>
       </c>
       <c r="L5">
-        <v>-2.77</v>
+        <v>-6.87</v>
       </c>
       <c r="M5">
-        <v>5.16</v>
+        <v>4.85</v>
       </c>
       <c r="N5">
         <v>55</v>
@@ -1308,19 +1317,19 @@
         <v>56</v>
       </c>
       <c r="P5">
-        <v>353.17</v>
+        <v>349.53</v>
       </c>
       <c r="Q5">
-        <v>357.4</v>
+        <v>356.2</v>
       </c>
       <c r="R5">
-        <v>369.96</v>
+        <v>369.2</v>
       </c>
       <c r="S5">
-        <v>358.43</v>
+        <v>358.16</v>
       </c>
       <c r="T5">
-        <v>-2.05</v>
+        <v>-4.48</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1344,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.03</v>
+        <v>34.66</v>
       </c>
       <c r="Z5">
-        <v>-3.97</v>
+        <v>-4.76</v>
       </c>
       <c r="AA5">
-        <v>-3.81</v>
+        <v>-4</v>
       </c>
       <c r="AB5">
-        <v>-0.16</v>
+        <v>-0.76</v>
       </c>
       <c r="AC5">
-        <v>37.48</v>
+        <v>20.2</v>
       </c>
       <c r="AD5">
-        <v>51.5</v>
+        <v>37.16</v>
       </c>
       <c r="AE5">
-        <v>11.89</v>
+        <v>12.08</v>
       </c>
       <c r="AF5">
-        <v>159.07</v>
+        <v>82.44</v>
       </c>
       <c r="AG5">
-        <v>371.42</v>
+        <v>371.16</v>
       </c>
       <c r="AH5">
-        <v>343.39</v>
+        <v>341.25</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1371,7 +1380,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.12</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>411.15</v>
+        <v>395.4</v>
       </c>
       <c r="D6">
-        <v>-0.9399999999999999</v>
+        <v>-3.83</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,25 +1403,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-7.13</v>
+        <v>-10.68</v>
       </c>
       <c r="H6">
-        <v>47.08</v>
+        <v>41.44</v>
       </c>
       <c r="I6">
-        <v>-3.42</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="J6">
-        <v>1.43</v>
+        <v>-1.93</v>
       </c>
       <c r="K6">
-        <v>7.49</v>
+        <v>1.66</v>
       </c>
       <c r="L6">
-        <v>18.08</v>
+        <v>12.14</v>
       </c>
       <c r="M6">
-        <v>-11.18</v>
+        <v>-11.69</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1421,19 +1430,19 @@
         <v>74</v>
       </c>
       <c r="P6">
-        <v>417.04</v>
+        <v>408.95</v>
       </c>
       <c r="Q6">
-        <v>407.67</v>
+        <v>407</v>
       </c>
       <c r="R6">
-        <v>405.65</v>
+        <v>405.35</v>
       </c>
       <c r="S6">
-        <v>376.99</v>
+        <v>377.4</v>
       </c>
       <c r="T6">
-        <v>9.06</v>
+        <v>4.77</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1457,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.73</v>
+        <v>43.02</v>
       </c>
       <c r="Z6">
-        <v>4.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA6">
-        <v>4.41</v>
+        <v>4.1</v>
       </c>
       <c r="AB6">
-        <v>0.25</v>
+        <v>-1.22</v>
       </c>
       <c r="AC6">
-        <v>33.8</v>
+        <v>24.23</v>
       </c>
       <c r="AD6">
-        <v>44.1</v>
+        <v>32.59</v>
       </c>
       <c r="AE6">
-        <v>13.95</v>
+        <v>14.24</v>
       </c>
       <c r="AF6">
-        <v>-43.16</v>
+        <v>-20.74</v>
       </c>
       <c r="AG6">
-        <v>435.14</v>
+        <v>435</v>
       </c>
       <c r="AH6">
-        <v>380.2</v>
+        <v>379</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1484,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>31.71</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>692.75</v>
+        <v>644.25</v>
       </c>
       <c r="D7">
-        <v>1.03</v>
+        <v>-7</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1507,46 +1516,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-6.09</v>
+        <v>-12.66</v>
       </c>
       <c r="H7">
-        <v>36.79</v>
+        <v>27.21</v>
       </c>
       <c r="I7">
-        <v>-4.03</v>
+        <v>-12.66</v>
       </c>
       <c r="J7">
-        <v>0.68</v>
+        <v>-6.49</v>
       </c>
       <c r="K7">
-        <v>18.83</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>16.78</v>
+        <v>7.1</v>
       </c>
       <c r="M7">
-        <v>31.82</v>
+        <v>29.41</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>699.98</v>
+        <v>681.3</v>
       </c>
       <c r="Q7">
-        <v>705.1900000000001</v>
+        <v>703.37</v>
       </c>
       <c r="R7">
-        <v>653.3099999999999</v>
+        <v>654.71</v>
       </c>
       <c r="S7">
-        <v>601.45</v>
+        <v>601.87</v>
       </c>
       <c r="T7">
-        <v>15.18</v>
+        <v>7.04</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,43 +1570,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>51.36</v>
+        <v>38.7</v>
       </c>
       <c r="Z7">
-        <v>11.24</v>
+        <v>5.88</v>
       </c>
       <c r="AA7">
-        <v>17.34</v>
+        <v>15.04</v>
       </c>
       <c r="AB7">
-        <v>-6.1</v>
+        <v>-9.17</v>
       </c>
       <c r="AC7">
         <v>4.59</v>
       </c>
       <c r="AD7">
-        <v>7.79</v>
+        <v>3.17</v>
       </c>
       <c r="AE7">
-        <v>27.45</v>
+        <v>30.02</v>
       </c>
       <c r="AF7">
-        <v>-25.47</v>
+        <v>18.11</v>
       </c>
       <c r="AG7">
-        <v>738.6799999999999</v>
+        <v>745.36</v>
       </c>
       <c r="AH7">
-        <v>671.7</v>
+        <v>661.39</v>
       </c>
       <c r="AI7">
-        <v>664.6799999999999</v>
+        <v>762.91</v>
       </c>
       <c r="AJ7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>28.82</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1617,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>195.07</v>
+        <v>187.23</v>
       </c>
       <c r="D8">
-        <v>-0.83</v>
+        <v>-4.02</v>
       </c>
       <c r="E8">
-        <v>352.6</v>
+        <v>347.4</v>
       </c>
       <c r="F8">
-        <v>192.4</v>
+        <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-44.68</v>
+        <v>-46.11</v>
       </c>
       <c r="H8">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.3</v>
+        <v>-3.61</v>
       </c>
       <c r="J8">
-        <v>-5.95</v>
+        <v>-8.9</v>
       </c>
       <c r="K8">
-        <v>-15.92</v>
+        <v>-19.2</v>
       </c>
       <c r="L8">
-        <v>-44</v>
+        <v>-46.9</v>
       </c>
       <c r="M8">
-        <v>-3.9</v>
+        <v>-4.86</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>195.14</v>
+        <v>193.73</v>
       </c>
       <c r="Q8">
-        <v>197.32</v>
+        <v>196.4</v>
       </c>
       <c r="R8">
-        <v>210.45</v>
+        <v>209.83</v>
       </c>
       <c r="S8">
-        <v>247.78</v>
+        <v>247.19</v>
       </c>
       <c r="T8">
-        <v>-21.27</v>
+        <v>-24.26</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1683,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>36.69</v>
+        <v>27.55</v>
       </c>
       <c r="Z8">
-        <v>-4.21</v>
+        <v>-4.66</v>
       </c>
       <c r="AA8">
-        <v>-4.8</v>
+        <v>-4.77</v>
       </c>
       <c r="AB8">
-        <v>0.59</v>
+        <v>0.11</v>
       </c>
       <c r="AC8">
-        <v>74.22</v>
+        <v>51.79</v>
       </c>
       <c r="AD8">
-        <v>71.23</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="AE8">
-        <v>5.39</v>
+        <v>5.66</v>
       </c>
       <c r="AF8">
-        <v>-74.25</v>
+        <v>14.44</v>
       </c>
       <c r="AG8">
-        <v>203.95</v>
+        <v>203.25</v>
       </c>
       <c r="AH8">
-        <v>190.69</v>
+        <v>189.54</v>
       </c>
       <c r="AI8">
-        <v>210.65</v>
+        <v>207.77</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>26.47</v>
+        <v>30.59</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3546.1</v>
+        <v>3491.6</v>
       </c>
       <c r="D9">
-        <v>0.23</v>
+        <v>-1.54</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1733,46 +1742,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.69</v>
+        <v>-19.94</v>
       </c>
       <c r="H9">
-        <v>7.17</v>
+        <v>5.52</v>
       </c>
       <c r="I9">
-        <v>-0.06</v>
+        <v>-1.54</v>
       </c>
       <c r="J9">
-        <v>-0.33</v>
+        <v>-4.29</v>
       </c>
       <c r="K9">
-        <v>-5.28</v>
+        <v>-6.45</v>
       </c>
       <c r="L9">
-        <v>-14.13</v>
+        <v>-16.4</v>
       </c>
       <c r="M9">
-        <v>19.49</v>
+        <v>19.09</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P9">
-        <v>3541</v>
+        <v>3530.08</v>
       </c>
       <c r="Q9">
-        <v>3560.68</v>
+        <v>3553.63</v>
       </c>
       <c r="R9">
-        <v>3576.61</v>
+        <v>3575.27</v>
       </c>
       <c r="S9">
-        <v>3670.76</v>
+        <v>3670.38</v>
       </c>
       <c r="T9">
-        <v>-3.4</v>
+        <v>-4.87</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.94</v>
+        <v>36.69</v>
       </c>
       <c r="Z9">
-        <v>-13.39</v>
+        <v>-16.99</v>
       </c>
       <c r="AA9">
-        <v>-13.37</v>
+        <v>-14.09</v>
       </c>
       <c r="AB9">
-        <v>-0.02</v>
+        <v>-2.89</v>
       </c>
       <c r="AC9">
-        <v>23.4</v>
+        <v>17.53</v>
       </c>
       <c r="AD9">
-        <v>24.92</v>
+        <v>21.8</v>
       </c>
       <c r="AE9">
-        <v>59.42</v>
+        <v>60.25</v>
       </c>
       <c r="AF9">
-        <v>22.7</v>
+        <v>5.8</v>
       </c>
       <c r="AG9">
-        <v>3616.94</v>
+        <v>3607.22</v>
       </c>
       <c r="AH9">
-        <v>3504.42</v>
+        <v>3500.04</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1823,7 +1832,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>12.56</v>
+        <v>13.45</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1491.1</v>
+        <v>1496.2</v>
       </c>
       <c r="D10">
-        <v>-0.89</v>
+        <v>0.34</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1855,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-15.68</v>
+        <v>-15.39</v>
       </c>
       <c r="H10">
-        <v>12.43</v>
+        <v>12.82</v>
       </c>
       <c r="I10">
-        <v>-1.28</v>
+        <v>-1.82</v>
       </c>
       <c r="J10">
-        <v>-6.63</v>
+        <v>-4.34</v>
       </c>
       <c r="K10">
-        <v>4.36</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
-        <v>6.41</v>
+        <v>7.94</v>
       </c>
       <c r="M10">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P10">
-        <v>1517.7</v>
+        <v>1512.14</v>
       </c>
       <c r="Q10">
-        <v>1538.25</v>
+        <v>1535.11</v>
       </c>
       <c r="R10">
-        <v>1587.12</v>
+        <v>1584.34</v>
       </c>
       <c r="S10">
-        <v>1516.84</v>
+        <v>1516.29</v>
       </c>
       <c r="T10">
-        <v>-1.7</v>
+        <v>-1.32</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1909,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>36.2</v>
+        <v>37.75</v>
       </c>
       <c r="Z10">
-        <v>-18.34</v>
+        <v>-19.56</v>
       </c>
       <c r="AA10">
-        <v>-14.46</v>
+        <v>-15.48</v>
       </c>
       <c r="AB10">
-        <v>-3.89</v>
+        <v>-4.08</v>
       </c>
       <c r="AC10">
-        <v>22.77</v>
+        <v>6.95</v>
       </c>
       <c r="AD10">
-        <v>38.06</v>
+        <v>23.59</v>
       </c>
       <c r="AE10">
-        <v>39.31</v>
+        <v>39</v>
       </c>
       <c r="AF10">
-        <v>-35.05</v>
+        <v>-15.55</v>
       </c>
       <c r="AG10">
-        <v>1582.45</v>
+        <v>1581.95</v>
       </c>
       <c r="AH10">
-        <v>1494.06</v>
+        <v>1488.28</v>
       </c>
       <c r="AI10">
         <v>1617.52</v>
@@ -1936,7 +1945,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.47</v>
+        <v>19.97</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1260 +2144,1314 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.44</v>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-9.369999999999999</v>
+        <v>-1.73</v>
       </c>
       <c r="D8" s="6">
-        <v>-11.67</v>
+        <v>-3.1</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.3</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-12.84</v>
+        <v>-11.67</v>
       </c>
       <c r="D9" s="6">
-        <v>-13.89</v>
+        <v>-12.94</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.05</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-3</v>
+        <v>-13.89</v>
       </c>
       <c r="D10" s="6">
-        <v>-3.12</v>
+        <v>-16.61</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.12</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>3.68</v>
+        <v>-3.12</v>
       </c>
       <c r="D11" s="6">
-        <v>1.43</v>
+        <v>-5.01</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.25</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>4.93</v>
+        <v>1.43</v>
       </c>
       <c r="D12" s="6">
-        <v>0.68</v>
+        <v>-1.93</v>
       </c>
       <c r="E12" s="7">
-        <v>-4.25</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-5.39</v>
+        <v>0.68</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.95</v>
+        <v>-6.49</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.48</v>
+        <v>-5.95</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.15</v>
+        <v>-8.9</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.85</v>
+        <v>-0.33</v>
       </c>
       <c r="D15" s="6">
-        <v>-6.63</v>
+        <v>-4.29</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.78</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.13</v>
+        <v>-6.63</v>
       </c>
       <c r="D16" s="6">
-        <v>0.6</v>
+        <v>-4.34</v>
       </c>
       <c r="E16" s="8">
-        <v>1.73</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.67</v>
+        <v>0.6</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.01</v>
+        <v>-3.79</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.34</v>
+        <v>-4.39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.21</v>
+        <v>-5.01</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.92</v>
+        <v>-6.74</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.71</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3</v>
+        <v>-1.92</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.26</v>
+        <v>-4.42</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.6</v>
+        <v>-2.74</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.42</v>
+        <v>-5.05</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.82</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.01</v>
+        <v>-3.42</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.03</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.02</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>0.4</v>
+        <v>-4.03</v>
       </c>
       <c r="D22" s="6">
-        <v>0.3</v>
+        <v>-12.66</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.1</v>
+        <v>-8.630000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.41</v>
+        <v>0.3</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.06</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.35</v>
+        <v>-3.61</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.91</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.44</v>
+        <v>-0.06</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.16</v>
+        <v>-1.54</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-4.57</v>
+        <v>-1.28</v>
       </c>
       <c r="D25" s="6">
-        <v>-7.11</v>
+        <v>-1.82</v>
       </c>
       <c r="E25" s="7">
-        <v>-2.54</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-16.69</v>
+        <v>-7.11</v>
       </c>
       <c r="D26" s="6">
-        <v>-19.15</v>
+        <v>-8.56</v>
       </c>
       <c r="E26" s="7">
-        <v>-2.46</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>19.05</v>
+        <v>-19.15</v>
       </c>
       <c r="D27" s="6">
-        <v>17.68</v>
+        <v>-20.53</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.37</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.33</v>
+        <v>17.68</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.77</v>
+        <v>12.6</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.44</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>20.58</v>
+        <v>-2.77</v>
       </c>
       <c r="D29" s="6">
-        <v>18.08</v>
+        <v>-6.87</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.5</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>14.68</v>
+        <v>18.08</v>
       </c>
       <c r="D30" s="6">
-        <v>16.78</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.1</v>
+        <v>12.14</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-5.94</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-44.24</v>
+        <v>16.78</v>
       </c>
       <c r="D31" s="6">
-        <v>-44</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.24</v>
+        <v>7.1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-9.68</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-14.43</v>
+        <v>-44</v>
       </c>
       <c r="D32" s="6">
-        <v>-14.13</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.3</v>
+        <v>-46.9</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>8.57</v>
+        <v>-14.13</v>
       </c>
       <c r="D33" s="6">
-        <v>6.41</v>
+        <v>-16.4</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.16</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-18.78</v>
+        <v>6.41</v>
       </c>
       <c r="D34" s="6">
-        <v>-16.05</v>
+        <v>7.94</v>
       </c>
       <c r="E34" s="8">
-        <v>2.73</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-10.68</v>
+        <v>-16.05</v>
       </c>
       <c r="D35" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.93</v>
+        <v>-19.53</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.34</v>
+        <v>-9.75</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.99</v>
+        <v>-10.83</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.65</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.04</v>
+        <v>-2.99</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="E37" s="8">
-        <v>2.83</v>
+        <v>-7.8</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-4.81</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>5.88</v>
+        <v>-2.21</v>
       </c>
       <c r="D38" s="6">
-        <v>7.49</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.61</v>
+        <v>-7.04</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.83</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>13.76</v>
+        <v>7.49</v>
       </c>
       <c r="D39" s="6">
-        <v>18.83</v>
-      </c>
-      <c r="E39" s="8">
-        <v>5.07</v>
+        <v>1.66</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-15.61</v>
+        <v>18.83</v>
       </c>
       <c r="D40" s="6">
-        <v>-15.92</v>
+        <v>9</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.31</v>
+        <v>-9.83</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-6.23</v>
+        <v>-15.92</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.95</v>
+        <v>-19.2</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>3.94</v>
+        <v>-5.28</v>
       </c>
       <c r="D42" s="6">
-        <v>4.36</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.42</v>
+        <v>-6.45</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-22.68</v>
+        <v>4.36</v>
       </c>
       <c r="D43" s="6">
-        <v>-22.75</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.07000000000000001</v>
+        <v>4.9</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.54</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-24.92</v>
+        <v>-22.75</v>
       </c>
       <c r="D44" s="6">
-        <v>-26.36</v>
+        <v>-24.18</v>
       </c>
       <c r="E44" s="7">
-        <v>-1.44</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-20.51</v>
+        <v>-26.36</v>
       </c>
       <c r="D45" s="6">
-        <v>-21.96</v>
+        <v>-27.65</v>
       </c>
       <c r="E45" s="7">
-        <v>-1.45</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-16.48</v>
+        <v>-21.96</v>
       </c>
       <c r="D46" s="6">
-        <v>-16.74</v>
+        <v>-24.69</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.26</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-6.25</v>
+        <v>-16.74</v>
       </c>
       <c r="D47" s="6">
-        <v>-7.13</v>
+        <v>-18.88</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.88</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-7.04</v>
+        <v>-7.13</v>
       </c>
       <c r="D48" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.95</v>
+        <v>-10.68</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.55</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-44.21</v>
+        <v>-6.09</v>
       </c>
       <c r="D49" s="6">
-        <v>-44.68</v>
+        <v>-12.66</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.47</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-18.88</v>
+        <v>-44.68</v>
       </c>
       <c r="D50" s="6">
-        <v>-18.69</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.19</v>
+        <v>-46.11</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-14.92</v>
+        <v>-18.69</v>
       </c>
       <c r="D51" s="6">
-        <v>-15.68</v>
+        <v>-19.94</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.76</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>379</v>
+        <v>-15.68</v>
       </c>
       <c r="D52" s="6">
-        <v>378.7</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.3</v>
+        <v>-15.39</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2855</v>
+        <v>378.7</v>
       </c>
       <c r="D53" s="6">
-        <v>2800</v>
+        <v>371.65</v>
       </c>
       <c r="E53" s="7">
-        <v>-55</v>
+        <v>-7.05</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>327.75</v>
+        <v>2800</v>
       </c>
       <c r="D54" s="6">
-        <v>321.75</v>
+        <v>2751.2</v>
       </c>
       <c r="E54" s="7">
-        <v>-6</v>
+        <v>-48.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>352.2</v>
+        <v>321.75</v>
       </c>
       <c r="D55" s="6">
-        <v>351.1</v>
+        <v>310.5</v>
       </c>
       <c r="E55" s="7">
-        <v>-1.1</v>
+        <v>-11.25</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>415.05</v>
+        <v>351.1</v>
       </c>
       <c r="D56" s="6">
-        <v>411.15</v>
+        <v>342.1</v>
       </c>
       <c r="E56" s="7">
-        <v>-3.9</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>685.7</v>
+        <v>411.15</v>
       </c>
       <c r="D57" s="6">
-        <v>692.75</v>
-      </c>
-      <c r="E57" s="8">
-        <v>7.05</v>
+        <v>395.4</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-15.75</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>196.71</v>
+        <v>692.75</v>
       </c>
       <c r="D58" s="6">
-        <v>195.07</v>
+        <v>644.25</v>
       </c>
       <c r="E58" s="7">
-        <v>-1.64</v>
+        <v>-48.5</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3537.8</v>
+        <v>195.07</v>
       </c>
       <c r="D59" s="6">
-        <v>3546.1</v>
-      </c>
-      <c r="E59" s="8">
-        <v>8.300000000000001</v>
+        <v>187.23</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-7.84</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1504.5</v>
+        <v>3546.1</v>
       </c>
       <c r="D60" s="6">
-        <v>1491.1</v>
+        <v>3491.6</v>
       </c>
       <c r="E60" s="7">
-        <v>-13.4</v>
+        <v>-54.5</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>42.32</v>
+        <v>1491.1</v>
       </c>
       <c r="D61" s="6">
-        <v>42.1</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.22</v>
+        <v>1496.2</v>
+      </c>
+      <c r="E61" s="8">
+        <v>5.1</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>22.87</v>
+        <v>77</v>
       </c>
       <c r="D62" s="6">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E62" s="7">
-        <v>-2.87</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>33.61</v>
+        <v>66</v>
       </c>
       <c r="D63" s="6">
-        <v>30.57</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-3.04</v>
+        <v>77</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>41.91</v>
+        <v>42.1</v>
       </c>
       <c r="D64" s="6">
-        <v>41.03</v>
+        <v>37.18</v>
       </c>
       <c r="E64" s="7">
-        <v>-0.88</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>54.25</v>
+        <v>20</v>
       </c>
       <c r="D65" s="6">
-        <v>51.73</v>
+        <v>17.86</v>
       </c>
       <c r="E65" s="7">
-        <v>-2.52</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>49.11</v>
+        <v>30.57</v>
       </c>
       <c r="D66" s="6">
-        <v>51.36</v>
-      </c>
-      <c r="E66" s="8">
-        <v>2.25</v>
+        <v>25.85</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-4.72</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>39.21</v>
+        <v>41.03</v>
       </c>
       <c r="D67" s="6">
-        <v>36.69</v>
+        <v>34.66</v>
       </c>
       <c r="E67" s="7">
-        <v>-2.52</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>43.94</v>
+        <v>51.73</v>
       </c>
       <c r="D68" s="6">
-        <v>45.94</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2</v>
+        <v>43.02</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-8.710000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>38.54</v>
+        <v>51.36</v>
       </c>
       <c r="D69" s="6">
-        <v>36.2</v>
+        <v>38.7</v>
       </c>
       <c r="E69" s="7">
-        <v>-2.34</v>
+        <v>-12.66</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>-62.4</v>
+        <v>36.69</v>
       </c>
       <c r="D70" s="6">
-        <v>-12.22</v>
-      </c>
-      <c r="E70" s="8">
-        <v>50.18</v>
+        <v>27.55</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-9.140000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>17.89</v>
+        <v>45.94</v>
       </c>
       <c r="D71" s="6">
-        <v>49.24</v>
-      </c>
-      <c r="E71" s="8">
-        <v>31.35</v>
+        <v>36.69</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>-8.890000000000001</v>
+        <v>36.2</v>
       </c>
       <c r="D72" s="6">
-        <v>4.06</v>
+        <v>37.75</v>
       </c>
       <c r="E72" s="8">
-        <v>12.95</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>3.37</v>
+        <v>-12.22</v>
       </c>
       <c r="D73" s="6">
-        <v>159.07</v>
-      </c>
-      <c r="E73" s="8">
-        <v>155.7</v>
+        <v>-29.55</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-17.33</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-57.07</v>
+        <v>49.24</v>
       </c>
       <c r="D74" s="6">
-        <v>-43.16</v>
-      </c>
-      <c r="E74" s="8">
-        <v>13.91</v>
+        <v>39.99</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-56.74</v>
+        <v>4.06</v>
       </c>
       <c r="D75" s="6">
-        <v>-25.47</v>
+        <v>12.77</v>
       </c>
       <c r="E75" s="8">
-        <v>31.27</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-66.65000000000001</v>
+        <v>159.07</v>
       </c>
       <c r="D76" s="6">
-        <v>-74.25</v>
+        <v>82.44</v>
       </c>
       <c r="E76" s="7">
-        <v>-7.6</v>
+        <v>-76.63</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>12.2</v>
+        <v>-43.16</v>
       </c>
       <c r="D77" s="6">
-        <v>22.7</v>
+        <v>-20.74</v>
       </c>
       <c r="E77" s="8">
-        <v>10.5</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>26.02</v>
+        <v>-25.47</v>
       </c>
       <c r="D78" s="6">
+        <v>18.11</v>
+      </c>
+      <c r="E78" s="8">
+        <v>43.58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-74.25</v>
+      </c>
+      <c r="D79" s="6">
+        <v>14.44</v>
+      </c>
+      <c r="E79" s="8">
+        <v>88.69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>22.7</v>
+      </c>
+      <c r="D80" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-16.9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
         <v>-35.05</v>
       </c>
-      <c r="E78" s="7">
-        <v>-61.07</v>
+      <c r="D81" s="6">
+        <v>-15.55</v>
+      </c>
+      <c r="E81" s="8">
+        <v>19.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3412,28 +3475,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3447,16 +3510,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>39.5</v>
+        <v>33.3</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.6</v>
+        <v>-7.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.4</v>
+        <v>-6.1</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3593,31 +3656,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3182</v>
+        <v>0.2941</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2701</v>
+        <v>0.2658</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1949</v>
+        <v>0.1909</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1383</v>
+        <v>0.1277</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1032</v>
+        <v>0.098</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0516</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0407</v>
+        <v>0.0381</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.039</v>
+        <v>-0.0486</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1118</v>
+        <v>-0.1169</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,58 +178,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.7 → 43.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>43.0</t>
-  </si>
-  <si>
-    <t>51.4 → 38.7</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>38.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -260,13 +215,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,22 +251,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,24 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,34 +337,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2086,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,1352 +2020,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-12.94</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-13.89</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-16.61</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-3.12</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.43</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-6.49</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-7.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.95</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.29</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.63</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-4.34</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-4.39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-6.74</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.05</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-5.86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-4.03</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-8.630000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-3.61</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.06</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.54</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-7.11</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-19.15</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-20.53</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>17.68</v>
-      </c>
-      <c r="D28" s="6">
-        <v>12.6</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-5.08</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-6.87</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>18.08</v>
-      </c>
-      <c r="D30" s="6">
-        <v>12.14</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-5.94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>16.78</v>
-      </c>
-      <c r="D31" s="6">
-        <v>7.1</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-9.68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-44</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-46.9</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-14.13</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-16.4</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>6.41</v>
-      </c>
-      <c r="D34" s="6">
-        <v>7.94</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-16.05</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-19.53</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-10.83</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-4.81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-4.83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>7.49</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1.66</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-5.83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>18.83</v>
-      </c>
-      <c r="D40" s="6">
-        <v>9</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-9.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-15.92</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-19.2</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>4.36</v>
-      </c>
-      <c r="D43" s="6">
-        <v>4.9</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-22.75</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-24.18</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-26.36</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-27.65</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-21.96</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-24.69</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-16.74</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-18.88</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-7.13</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-44.68</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-46.11</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-18.69</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-19.94</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-15.68</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-15.39</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>378.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>371.65</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-7.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2800</v>
-      </c>
-      <c r="D54" s="6">
-        <v>2751.2</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-48.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>321.75</v>
-      </c>
-      <c r="D55" s="6">
-        <v>310.5</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-11.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>351.1</v>
-      </c>
-      <c r="D56" s="6">
-        <v>342.1</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>411.15</v>
-      </c>
-      <c r="D57" s="6">
-        <v>395.4</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-15.75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>692.75</v>
-      </c>
-      <c r="D58" s="6">
-        <v>644.25</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-48.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>195.07</v>
-      </c>
-      <c r="D59" s="6">
-        <v>187.23</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-7.84</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>3546.1</v>
-      </c>
-      <c r="D60" s="6">
-        <v>3491.6</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-54.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1491.1</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1496.2</v>
-      </c>
-      <c r="E61" s="8">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>77</v>
-      </c>
-      <c r="D62" s="6">
-        <v>66</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>66</v>
-      </c>
-      <c r="D63" s="6">
-        <v>77</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>42.1</v>
-      </c>
-      <c r="D64" s="6">
-        <v>37.18</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-4.92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>20</v>
-      </c>
-      <c r="D65" s="6">
-        <v>17.86</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>30.57</v>
-      </c>
-      <c r="D66" s="6">
-        <v>25.85</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-4.72</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>41.03</v>
-      </c>
-      <c r="D67" s="6">
-        <v>34.66</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-6.37</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>51.73</v>
-      </c>
-      <c r="D68" s="6">
-        <v>43.02</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-8.710000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>51.36</v>
-      </c>
-      <c r="D69" s="6">
-        <v>38.7</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-12.66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>36.69</v>
-      </c>
-      <c r="D70" s="6">
-        <v>27.55</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-9.140000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>45.94</v>
-      </c>
-      <c r="D71" s="6">
-        <v>36.69</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-9.25</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>36.2</v>
-      </c>
-      <c r="D72" s="6">
-        <v>37.75</v>
-      </c>
-      <c r="E72" s="8">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-12.22</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-29.55</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-17.33</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>49.24</v>
-      </c>
-      <c r="D74" s="6">
-        <v>39.99</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-9.25</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>4.06</v>
-      </c>
-      <c r="D75" s="6">
-        <v>12.77</v>
-      </c>
-      <c r="E75" s="8">
-        <v>8.710000000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>159.07</v>
-      </c>
-      <c r="D76" s="6">
-        <v>82.44</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-76.63</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-43.16</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-20.74</v>
-      </c>
-      <c r="E77" s="8">
-        <v>22.42</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-25.47</v>
-      </c>
-      <c r="D78" s="6">
-        <v>18.11</v>
-      </c>
-      <c r="E78" s="8">
-        <v>43.58</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-74.25</v>
-      </c>
-      <c r="D79" s="6">
-        <v>14.44</v>
-      </c>
-      <c r="E79" s="8">
-        <v>88.69</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>22.7</v>
-      </c>
-      <c r="D80" s="6">
-        <v>5.8</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-16.9</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-35.05</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-15.55</v>
-      </c>
-      <c r="E81" s="8">
-        <v>19.5</v>
+      <c r="A6" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3471,60 +2060,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
+      <c r="B1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>40.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>33.3</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-7.1</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-6.1</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>20</v>
       </c>
     </row>
@@ -3626,60 +2215,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.2941</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.2658</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.1909</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.1277</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.098</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>0.04849999999999999</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>0.0381</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="9">
         <v>-0.0486</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="9">
         <v>-0.1169</v>
       </c>
     </row>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,13 +178,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.9 → 34.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>34.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -215,11 +251,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,8 +289,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +320,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,27 +407,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -853,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>371.65</v>
+        <v>370.75</v>
       </c>
       <c r="D2">
-        <v>-1.86</v>
+        <v>-0.24</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>371.65</v>
+        <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-24.18</v>
+        <v>-24.37</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-3.79</v>
+        <v>-1.49</v>
       </c>
       <c r="J2">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="K2">
-        <v>-19.53</v>
+        <v>-20.15</v>
       </c>
       <c r="L2">
-        <v>-8.56</v>
+        <v>-8.66</v>
       </c>
       <c r="M2">
-        <v>9.800000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>376.74</v>
+        <v>375.62</v>
       </c>
       <c r="Q2">
-        <v>382.31</v>
+        <v>381.77</v>
       </c>
       <c r="R2">
-        <v>394.14</v>
+        <v>393.26</v>
       </c>
       <c r="S2">
-        <v>433.78</v>
+        <v>433.67</v>
       </c>
       <c r="T2">
-        <v>-14.32</v>
+        <v>-14.51</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -919,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.18</v>
+        <v>36.59</v>
       </c>
       <c r="Z2">
-        <v>-5.3</v>
+        <v>-5.67</v>
       </c>
       <c r="AA2">
-        <v>-5.27</v>
+        <v>-5.35</v>
       </c>
       <c r="AB2">
-        <v>-0.03</v>
+        <v>-0.32</v>
       </c>
       <c r="AC2">
-        <v>35.42</v>
+        <v>12.82</v>
       </c>
       <c r="AD2">
-        <v>52.45</v>
+        <v>34.94</v>
       </c>
       <c r="AE2">
-        <v>9.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF2">
-        <v>-29.55</v>
+        <v>-47.63</v>
       </c>
       <c r="AG2">
-        <v>394.75</v>
+        <v>395.24</v>
       </c>
       <c r="AH2">
-        <v>369.87</v>
+        <v>368.29</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -955,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>34.99</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -966,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2751.2</v>
+        <v>2796.2</v>
       </c>
       <c r="D3">
-        <v>-1.74</v>
+        <v>1.64</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -978,25 +1055,25 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-27.65</v>
+        <v>-26.46</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="I3">
-        <v>-6.74</v>
+        <v>-2.23</v>
       </c>
       <c r="J3">
-        <v>-12.94</v>
+        <v>-11.51</v>
       </c>
       <c r="K3">
-        <v>-10.83</v>
+        <v>-10.65</v>
       </c>
       <c r="L3">
-        <v>-20.53</v>
+        <v>-19.46</v>
       </c>
       <c r="M3">
-        <v>26.58</v>
+        <v>26.51</v>
       </c>
       <c r="N3">
         <v>23</v>
@@ -1005,19 +1082,19 @@
         <v>36</v>
       </c>
       <c r="P3">
-        <v>2824.76</v>
+        <v>2812</v>
       </c>
       <c r="Q3">
-        <v>2988.9</v>
+        <v>2971.21</v>
       </c>
       <c r="R3">
-        <v>3209.97</v>
+        <v>3201.45</v>
       </c>
       <c r="S3">
-        <v>3259.75</v>
+        <v>3255.72</v>
       </c>
       <c r="T3">
-        <v>-15.6</v>
+        <v>-14.11</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1032,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>17.86</v>
+        <v>25.76</v>
       </c>
       <c r="Z3">
-        <v>-109.53</v>
+        <v>-110.32</v>
       </c>
       <c r="AA3">
-        <v>-91.69</v>
+        <v>-95.41</v>
       </c>
       <c r="AB3">
-        <v>-17.84</v>
+        <v>-14.9</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>15.48</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AE3">
-        <v>62.03</v>
+        <v>62.75</v>
       </c>
       <c r="AF3">
-        <v>39.99</v>
+        <v>-48.6</v>
       </c>
       <c r="AG3">
-        <v>3212.26</v>
+        <v>3196.87</v>
       </c>
       <c r="AH3">
-        <v>2765.53</v>
+        <v>2745.54</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1068,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>86.15000000000001</v>
+        <v>85.73999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1079,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>310.5</v>
+        <v>319.45</v>
       </c>
       <c r="D4">
-        <v>-3.5</v>
+        <v>2.88</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1091,46 +1168,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-24.69</v>
+        <v>-22.52</v>
       </c>
       <c r="H4">
-        <v>12.62</v>
+        <v>15.87</v>
       </c>
       <c r="I4">
-        <v>-4.42</v>
+        <v>-0.09</v>
       </c>
       <c r="J4">
-        <v>-16.61</v>
+        <v>-14.67</v>
       </c>
       <c r="K4">
-        <v>-7.8</v>
+        <v>-6.28</v>
       </c>
       <c r="L4">
-        <v>12.6</v>
+        <v>12.42</v>
       </c>
       <c r="M4">
-        <v>12.77</v>
+        <v>13.37</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>321.19</v>
+        <v>321.13</v>
       </c>
       <c r="Q4">
-        <v>339.24</v>
+        <v>337.02</v>
       </c>
       <c r="R4">
-        <v>367.74</v>
+        <v>366.25</v>
       </c>
       <c r="S4">
-        <v>342.98</v>
+        <v>342.69</v>
       </c>
       <c r="T4">
-        <v>-9.470000000000001</v>
+        <v>-6.78</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1145,43 +1222,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>25.85</v>
+        <v>34.51</v>
       </c>
       <c r="Z4">
-        <v>-13.1</v>
+        <v>-12.93</v>
       </c>
       <c r="AA4">
-        <v>-11.19</v>
+        <v>-11.53</v>
       </c>
       <c r="AB4">
-        <v>-1.91</v>
+        <v>-1.39</v>
       </c>
       <c r="AC4">
-        <v>29.77</v>
+        <v>31.52</v>
       </c>
       <c r="AD4">
-        <v>34.04</v>
+        <v>34.32</v>
       </c>
       <c r="AE4">
-        <v>11.04</v>
+        <v>11.05</v>
       </c>
       <c r="AF4">
-        <v>12.77</v>
+        <v>-25.63</v>
       </c>
       <c r="AG4">
-        <v>369.36</v>
+        <v>366.05</v>
       </c>
       <c r="AH4">
-        <v>309.12</v>
+        <v>308</v>
       </c>
       <c r="AI4">
-        <v>348.6</v>
+        <v>348.44</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>35.97</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1192,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>342.1</v>
+        <v>349.1</v>
       </c>
       <c r="D5">
-        <v>-2.56</v>
+        <v>2.05</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1204,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-18.88</v>
+        <v>-17.22</v>
       </c>
       <c r="H5">
-        <v>16.26</v>
+        <v>18.64</v>
       </c>
       <c r="I5">
-        <v>-5.05</v>
+        <v>-0.58</v>
       </c>
       <c r="J5">
-        <v>-5.01</v>
+        <v>-4.66</v>
       </c>
       <c r="K5">
-        <v>-7.04</v>
+        <v>-7.86</v>
       </c>
       <c r="L5">
-        <v>-6.87</v>
+        <v>-4.21</v>
       </c>
       <c r="M5">
-        <v>4.85</v>
+        <v>4.94</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>349.53</v>
+        <v>349.12</v>
       </c>
       <c r="Q5">
-        <v>356.2</v>
+        <v>355.15</v>
       </c>
       <c r="R5">
-        <v>369.2</v>
+        <v>368.44</v>
       </c>
       <c r="S5">
-        <v>358.16</v>
+        <v>357.91</v>
       </c>
       <c r="T5">
-        <v>-4.48</v>
+        <v>-2.46</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1258,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>34.66</v>
+        <v>42.18</v>
       </c>
       <c r="Z5">
-        <v>-4.76</v>
+        <v>-4.77</v>
       </c>
       <c r="AA5">
-        <v>-4</v>
+        <v>-4.15</v>
       </c>
       <c r="AB5">
-        <v>-0.76</v>
+        <v>-0.61</v>
       </c>
       <c r="AC5">
-        <v>20.2</v>
+        <v>17.4</v>
       </c>
       <c r="AD5">
-        <v>37.16</v>
+        <v>25.03</v>
       </c>
       <c r="AE5">
-        <v>12.08</v>
+        <v>12.29</v>
       </c>
       <c r="AF5">
-        <v>82.44</v>
+        <v>364.92</v>
       </c>
       <c r="AG5">
-        <v>371.16</v>
+        <v>368.9</v>
       </c>
       <c r="AH5">
-        <v>341.25</v>
+        <v>341.41</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1294,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.69</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1305,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>395.4</v>
+        <v>400.35</v>
       </c>
       <c r="D6">
-        <v>-3.83</v>
+        <v>1.25</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1317,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-10.68</v>
+        <v>-9.57</v>
       </c>
       <c r="H6">
-        <v>41.44</v>
+        <v>43.21</v>
       </c>
       <c r="I6">
-        <v>-9.279999999999999</v>
+        <v>-3.85</v>
       </c>
       <c r="J6">
-        <v>-1.93</v>
+        <v>-2.08</v>
       </c>
       <c r="K6">
-        <v>1.66</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>12.14</v>
+        <v>14.5</v>
       </c>
       <c r="M6">
-        <v>-11.69</v>
+        <v>-11.28</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O6">
         <v>74</v>
       </c>
       <c r="P6">
-        <v>408.95</v>
+        <v>405.74</v>
       </c>
       <c r="Q6">
-        <v>407</v>
+        <v>406.93</v>
       </c>
       <c r="R6">
-        <v>405.35</v>
+        <v>405.17</v>
       </c>
       <c r="S6">
-        <v>377.4</v>
+        <v>377.83</v>
       </c>
       <c r="T6">
-        <v>4.77</v>
+        <v>5.96</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1371,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>43.02</v>
+        <v>46.09</v>
       </c>
       <c r="Z6">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA6">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AB6">
-        <v>-1.22</v>
+        <v>-1.8</v>
       </c>
       <c r="AC6">
-        <v>24.23</v>
+        <v>13.22</v>
       </c>
       <c r="AD6">
-        <v>32.59</v>
+        <v>23.75</v>
       </c>
       <c r="AE6">
-        <v>14.24</v>
+        <v>14.18</v>
       </c>
       <c r="AF6">
-        <v>-20.74</v>
+        <v>-39.8</v>
       </c>
       <c r="AG6">
-        <v>435</v>
+        <v>434.99</v>
       </c>
       <c r="AH6">
-        <v>379</v>
+        <v>378.86</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1407,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>30.77</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1418,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>644.25</v>
+        <v>618.1</v>
       </c>
       <c r="D7">
-        <v>-7</v>
+        <v>-4.06</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1430,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-12.66</v>
+        <v>-16.21</v>
       </c>
       <c r="H7">
-        <v>27.21</v>
+        <v>22.05</v>
       </c>
       <c r="I7">
-        <v>-12.66</v>
+        <v>-11.54</v>
       </c>
       <c r="J7">
-        <v>-6.49</v>
+        <v>-9.19</v>
       </c>
       <c r="K7">
-        <v>9</v>
+        <v>3.29</v>
       </c>
       <c r="L7">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="M7">
-        <v>29.41</v>
+        <v>26.86</v>
       </c>
       <c r="N7">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P7">
-        <v>681.3</v>
+        <v>665.17</v>
       </c>
       <c r="Q7">
-        <v>703.37</v>
+        <v>700.47</v>
       </c>
       <c r="R7">
-        <v>654.71</v>
+        <v>655.4400000000001</v>
       </c>
       <c r="S7">
-        <v>601.87</v>
+        <v>602.1799999999999</v>
       </c>
       <c r="T7">
-        <v>7.04</v>
+        <v>2.64</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1484,43 +1561,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>38.7</v>
+        <v>33.85</v>
       </c>
       <c r="Z7">
-        <v>5.88</v>
+        <v>-0.48</v>
       </c>
       <c r="AA7">
-        <v>15.04</v>
+        <v>11.94</v>
       </c>
       <c r="AB7">
-        <v>-9.17</v>
+        <v>-12.42</v>
       </c>
       <c r="AC7">
-        <v>4.59</v>
+        <v>4.24</v>
       </c>
       <c r="AD7">
-        <v>3.17</v>
+        <v>4.47</v>
       </c>
       <c r="AE7">
-        <v>30.02</v>
+        <v>30.28</v>
       </c>
       <c r="AF7">
-        <v>18.11</v>
+        <v>-7.11</v>
       </c>
       <c r="AG7">
-        <v>745.36</v>
+        <v>756.17</v>
       </c>
       <c r="AH7">
-        <v>661.39</v>
+        <v>644.77</v>
       </c>
       <c r="AI7">
-        <v>762.91</v>
+        <v>722.95</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>28.98</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1531,37 +1608,37 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>187.23</v>
+        <v>188.02</v>
       </c>
       <c r="D8">
-        <v>-4.02</v>
+        <v>0.42</v>
       </c>
       <c r="E8">
-        <v>347.4</v>
+        <v>344.1</v>
       </c>
       <c r="F8">
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-46.11</v>
+        <v>-45.36</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="I8">
-        <v>-3.61</v>
+        <v>-3.51</v>
       </c>
       <c r="J8">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
       <c r="K8">
-        <v>-19.2</v>
+        <v>-19.55</v>
       </c>
       <c r="L8">
-        <v>-46.9</v>
+        <v>-45.88</v>
       </c>
       <c r="M8">
-        <v>-4.86</v>
+        <v>-4.89</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1570,19 +1647,19 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>193.73</v>
+        <v>192.37</v>
       </c>
       <c r="Q8">
-        <v>196.4</v>
+        <v>195.83</v>
       </c>
       <c r="R8">
-        <v>209.83</v>
+        <v>209.29</v>
       </c>
       <c r="S8">
-        <v>247.19</v>
+        <v>246.58</v>
       </c>
       <c r="T8">
-        <v>-24.26</v>
+        <v>-23.75</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1597,43 +1674,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>27.55</v>
+        <v>29.46</v>
       </c>
       <c r="Z8">
-        <v>-4.66</v>
+        <v>-4.9</v>
       </c>
       <c r="AA8">
-        <v>-4.77</v>
+        <v>-4.8</v>
       </c>
       <c r="AB8">
-        <v>0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AC8">
-        <v>51.79</v>
+        <v>27.06</v>
       </c>
       <c r="AD8">
-        <v>66.73999999999999</v>
+        <v>51.02</v>
       </c>
       <c r="AE8">
-        <v>5.66</v>
+        <v>5.55</v>
       </c>
       <c r="AF8">
-        <v>14.44</v>
+        <v>16.82</v>
       </c>
       <c r="AG8">
-        <v>203.25</v>
+        <v>203.48</v>
       </c>
       <c r="AH8">
-        <v>189.54</v>
+        <v>188.18</v>
       </c>
       <c r="AI8">
-        <v>207.77</v>
+        <v>203.6</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.59</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1644,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3491.6</v>
+        <v>3439.1</v>
       </c>
       <c r="D9">
-        <v>-1.54</v>
+        <v>-1.5</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1656,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.94</v>
+        <v>-21.14</v>
       </c>
       <c r="H9">
-        <v>5.52</v>
+        <v>3.93</v>
       </c>
       <c r="I9">
-        <v>-1.54</v>
+        <v>-2.92</v>
       </c>
       <c r="J9">
-        <v>-4.29</v>
+        <v>-5.33</v>
       </c>
       <c r="K9">
-        <v>-6.45</v>
+        <v>-9</v>
       </c>
       <c r="L9">
-        <v>-16.4</v>
+        <v>-16.46</v>
       </c>
       <c r="M9">
-        <v>19.09</v>
+        <v>18.96</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P9">
-        <v>3530.08</v>
+        <v>3509.36</v>
       </c>
       <c r="Q9">
-        <v>3553.63</v>
+        <v>3545.87</v>
       </c>
       <c r="R9">
-        <v>3575.27</v>
+        <v>3572.7</v>
       </c>
       <c r="S9">
-        <v>3670.38</v>
+        <v>3669.47</v>
       </c>
       <c r="T9">
-        <v>-4.87</v>
+        <v>-6.28</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1710,43 +1787,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>36.69</v>
+        <v>30.35</v>
       </c>
       <c r="Z9">
-        <v>-16.99</v>
+        <v>-23.8</v>
       </c>
       <c r="AA9">
-        <v>-14.09</v>
+        <v>-16.04</v>
       </c>
       <c r="AB9">
-        <v>-2.89</v>
+        <v>-7.77</v>
       </c>
       <c r="AC9">
-        <v>17.53</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AD9">
-        <v>21.8</v>
+        <v>16.57</v>
       </c>
       <c r="AE9">
-        <v>60.25</v>
+        <v>62.63</v>
       </c>
       <c r="AF9">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>3607.22</v>
+        <v>3616.8</v>
       </c>
       <c r="AH9">
-        <v>3500.04</v>
+        <v>3474.94</v>
       </c>
       <c r="AI9">
-        <v>3684.57</v>
+        <v>3651.13</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>13.45</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1757,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1496.2</v>
+        <v>1514.1</v>
       </c>
       <c r="D10">
-        <v>0.34</v>
+        <v>1.2</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1769,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-15.39</v>
+        <v>-14.38</v>
       </c>
       <c r="H10">
-        <v>12.82</v>
+        <v>14.17</v>
       </c>
       <c r="I10">
-        <v>-1.82</v>
+        <v>-1.23</v>
       </c>
       <c r="J10">
-        <v>-4.34</v>
+        <v>-2.88</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>4.08</v>
       </c>
       <c r="L10">
-        <v>7.94</v>
+        <v>6.3</v>
       </c>
       <c r="M10">
-        <v>3.81</v>
+        <v>4.65</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O10">
         <v>70</v>
       </c>
       <c r="P10">
-        <v>1512.14</v>
+        <v>1508.36</v>
       </c>
       <c r="Q10">
-        <v>1535.11</v>
+        <v>1535.42</v>
       </c>
       <c r="R10">
-        <v>1584.34</v>
+        <v>1581.74</v>
       </c>
       <c r="S10">
-        <v>1516.29</v>
+        <v>1515.8</v>
       </c>
       <c r="T10">
-        <v>-1.32</v>
+        <v>-0.11</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1823,34 +1900,34 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>37.75</v>
+        <v>42.98</v>
       </c>
       <c r="Z10">
-        <v>-19.56</v>
+        <v>-18.86</v>
       </c>
       <c r="AA10">
-        <v>-15.48</v>
+        <v>-16.15</v>
       </c>
       <c r="AB10">
-        <v>-4.08</v>
+        <v>-2.71</v>
       </c>
       <c r="AC10">
-        <v>6.95</v>
+        <v>25.97</v>
       </c>
       <c r="AD10">
-        <v>23.59</v>
+        <v>18.56</v>
       </c>
       <c r="AE10">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="AF10">
-        <v>-15.55</v>
+        <v>5.53</v>
       </c>
       <c r="AG10">
-        <v>1581.95</v>
+        <v>1581.58</v>
       </c>
       <c r="AH10">
-        <v>1488.28</v>
+        <v>1489.26</v>
       </c>
       <c r="AI10">
         <v>1617.52</v>
@@ -1859,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>19.97</v>
+        <v>17.36</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2020,12 +2097,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2034,7 +2146,1294 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-3.1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-12.94</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-11.51</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-16.61</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-14.67</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.66</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-1.93</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.08</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.49</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.19</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-8.9</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-8.6</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-4.29</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-5.33</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.34</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.88</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.49</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.74</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.42</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.09</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-5.05</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-9.279999999999999</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-12.66</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-11.54</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.61</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-1.54</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-2.92</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.23</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-8.56</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-8.66</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-20.53</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-19.46</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>12.6</v>
+      </c>
+      <c r="D27" s="6">
+        <v>12.42</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-6.87</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-4.21</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>12.14</v>
+      </c>
+      <c r="D29" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>7.1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-46.9</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-45.88</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-16.4</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-16.46</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>7.94</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-19.53</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-20.15</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-10.83</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-10.65</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-6.28</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.86</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1.66</v>
+      </c>
+      <c r="D38" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>9</v>
+      </c>
+      <c r="D39" s="6">
+        <v>3.29</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-5.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-19.2</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-19.55</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-6.45</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-9</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>4.9</v>
+      </c>
+      <c r="D42" s="6">
+        <v>4.08</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-24.18</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-24.37</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-27.65</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-26.46</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-24.69</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-22.52</v>
+      </c>
+      <c r="E45" s="8">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-18.88</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-17.22</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-9.57</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-12.66</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-16.21</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-46.11</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-45.36</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-19.94</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-21.14</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-15.39</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-14.38</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>371.65</v>
+      </c>
+      <c r="D52" s="6">
+        <v>370.75</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2751.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2796.2</v>
+      </c>
+      <c r="E53" s="8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>310.5</v>
+      </c>
+      <c r="D54" s="6">
+        <v>319.45</v>
+      </c>
+      <c r="E54" s="8">
+        <v>8.949999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>342.1</v>
+      </c>
+      <c r="D55" s="6">
+        <v>349.1</v>
+      </c>
+      <c r="E55" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>395.4</v>
+      </c>
+      <c r="D56" s="6">
+        <v>400.35</v>
+      </c>
+      <c r="E56" s="8">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>644.25</v>
+      </c>
+      <c r="D57" s="6">
+        <v>618.1</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-26.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>187.23</v>
+      </c>
+      <c r="D58" s="6">
+        <v>188.02</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3491.6</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3439.1</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-52.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1496.2</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1514.1</v>
+      </c>
+      <c r="E60" s="8">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>88</v>
+      </c>
+      <c r="D61" s="6">
+        <v>99</v>
+      </c>
+      <c r="E61" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>99</v>
+      </c>
+      <c r="D62" s="6">
+        <v>77</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>77</v>
+      </c>
+      <c r="D63" s="6">
+        <v>88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>37.18</v>
+      </c>
+      <c r="D64" s="6">
+        <v>36.59</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>17.86</v>
+      </c>
+      <c r="D65" s="6">
+        <v>25.76</v>
+      </c>
+      <c r="E65" s="8">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>25.85</v>
+      </c>
+      <c r="D66" s="6">
+        <v>34.51</v>
+      </c>
+      <c r="E66" s="8">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>34.66</v>
+      </c>
+      <c r="D67" s="6">
+        <v>42.18</v>
+      </c>
+      <c r="E67" s="8">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>43.02</v>
+      </c>
+      <c r="D68" s="6">
+        <v>46.09</v>
+      </c>
+      <c r="E68" s="8">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>38.7</v>
+      </c>
+      <c r="D69" s="6">
+        <v>33.85</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-4.85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>27.55</v>
+      </c>
+      <c r="D70" s="6">
+        <v>29.46</v>
+      </c>
+      <c r="E70" s="8">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>36.69</v>
+      </c>
+      <c r="D71" s="6">
+        <v>30.35</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-6.34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>37.75</v>
+      </c>
+      <c r="D72" s="6">
+        <v>42.98</v>
+      </c>
+      <c r="E72" s="8">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-29.55</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-47.63</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-18.08</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-48.6</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-88.59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>12.77</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-25.63</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-38.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>82.44</v>
+      </c>
+      <c r="D76" s="6">
+        <v>364.92</v>
+      </c>
+      <c r="E76" s="8">
+        <v>282.48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-20.74</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-39.8</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-19.06</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>18.11</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-7.11</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-25.22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>14.44</v>
+      </c>
+      <c r="D79" s="6">
+        <v>16.82</v>
+      </c>
+      <c r="E79" s="8">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="D80" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-15.55</v>
+      </c>
+      <c r="D81" s="6">
+        <v>5.53</v>
+      </c>
+      <c r="E81" s="8">
+        <v>21.08</v>
       </c>
     </row>
   </sheetData>
@@ -2060,60 +3459,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>40.16</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="6">
-        <v>33.3</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="11">
+        <v>35.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-6.1</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="11">
+        <v>-6.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2215,61 +3614,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9">
-        <v>0.2941</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.2658</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.1909</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.1277</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.098</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.04849999999999999</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.0381</v>
-      </c>
-      <c r="H2" s="9">
-        <v>-0.0486</v>
-      </c>
-      <c r="I2" s="9">
-        <v>-0.1169</v>
+      <c r="A2" s="14">
+        <v>0.2686</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2651</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1896</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1337</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0998</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.04940000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0489</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1128</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,28 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>25.9 → 34.5</t>
+    <t>29.5 → 39.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>25.9</t>
-  </si>
-  <si>
-    <t>34.5</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>39.5</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>30.4 → 66.2</t>
+  </si>
+  <si>
+    <t>30.4</t>
+  </si>
+  <si>
+    <t>66.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +429,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +942,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>370.75</v>
+        <v>379.45</v>
       </c>
       <c r="D2">
-        <v>-0.24</v>
+        <v>2.35</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +954,46 @@
         <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-24.37</v>
+        <v>-22.59</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="I2">
-        <v>-1.49</v>
+        <v>0.38</v>
       </c>
       <c r="J2">
-        <v>-3.3</v>
+        <v>-0.58</v>
       </c>
       <c r="K2">
-        <v>-20.15</v>
+        <v>-19.16</v>
       </c>
       <c r="L2">
-        <v>-8.66</v>
+        <v>-6.3</v>
       </c>
       <c r="M2">
-        <v>9.98</v>
+        <v>10.41</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P2">
-        <v>375.62</v>
+        <v>375.91</v>
       </c>
       <c r="Q2">
-        <v>381.77</v>
+        <v>381.65</v>
       </c>
       <c r="R2">
-        <v>393.26</v>
+        <v>392.61</v>
       </c>
       <c r="S2">
-        <v>433.67</v>
+        <v>433.6</v>
       </c>
       <c r="T2">
-        <v>-14.51</v>
+        <v>-12.49</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1008,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.59</v>
+        <v>45.55</v>
       </c>
       <c r="Z2">
-        <v>-5.67</v>
+        <v>-5.2</v>
       </c>
       <c r="AA2">
-        <v>-5.35</v>
+        <v>-5.32</v>
       </c>
       <c r="AB2">
-        <v>-0.32</v>
+        <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>12.82</v>
+        <v>26.24</v>
       </c>
       <c r="AD2">
-        <v>34.94</v>
+        <v>24.83</v>
       </c>
       <c r="AE2">
-        <v>9.199999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="AF2">
-        <v>-47.63</v>
+        <v>-40.73</v>
       </c>
       <c r="AG2">
-        <v>395.24</v>
+        <v>395.16</v>
       </c>
       <c r="AH2">
-        <v>368.29</v>
+        <v>368.14</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1032,7 +1044,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>37.5</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1055,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2796.2</v>
+        <v>2813</v>
       </c>
       <c r="D3">
-        <v>1.64</v>
+        <v>0.6</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1067,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-26.46</v>
+        <v>-26.02</v>
       </c>
       <c r="H3">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="I3">
-        <v>-2.23</v>
+        <v>-1.56</v>
       </c>
       <c r="J3">
-        <v>-11.51</v>
+        <v>-10.7</v>
       </c>
       <c r="K3">
-        <v>-10.65</v>
+        <v>-10.99</v>
       </c>
       <c r="L3">
         <v>-19.46</v>
       </c>
       <c r="M3">
-        <v>26.51</v>
+        <v>26.79</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P3">
-        <v>2812</v>
+        <v>2803.08</v>
       </c>
       <c r="Q3">
-        <v>2971.21</v>
+        <v>2955.67</v>
       </c>
       <c r="R3">
-        <v>3201.45</v>
+        <v>3192.04</v>
       </c>
       <c r="S3">
-        <v>3255.72</v>
+        <v>3251.7</v>
       </c>
       <c r="T3">
-        <v>-14.11</v>
+        <v>-13.49</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1121,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>25.76</v>
+        <v>28.52</v>
       </c>
       <c r="Z3">
-        <v>-110.32</v>
+        <v>-108.34</v>
       </c>
       <c r="AA3">
-        <v>-95.41</v>
+        <v>-98</v>
       </c>
       <c r="AB3">
-        <v>-14.9</v>
+        <v>-10.34</v>
       </c>
       <c r="AC3">
-        <v>15.48</v>
+        <v>36.38</v>
       </c>
       <c r="AD3">
-        <v>5.16</v>
+        <v>17.29</v>
       </c>
       <c r="AE3">
-        <v>62.75</v>
+        <v>61.88</v>
       </c>
       <c r="AF3">
-        <v>-48.6</v>
+        <v>-20.21</v>
       </c>
       <c r="AG3">
-        <v>3196.87</v>
+        <v>3179.89</v>
       </c>
       <c r="AH3">
-        <v>2745.54</v>
+        <v>2731.44</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1145,7 +1157,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>85.73999999999999</v>
+        <v>82.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1168,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>319.45</v>
+        <v>322.4</v>
       </c>
       <c r="D4">
-        <v>2.88</v>
+        <v>0.92</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1180,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-22.52</v>
+        <v>-21.8</v>
       </c>
       <c r="H4">
-        <v>15.87</v>
+        <v>16.94</v>
       </c>
       <c r="I4">
-        <v>-0.09</v>
+        <v>-1.16</v>
       </c>
       <c r="J4">
-        <v>-14.67</v>
+        <v>-11.37</v>
       </c>
       <c r="K4">
-        <v>-6.28</v>
+        <v>-3.1</v>
       </c>
       <c r="L4">
-        <v>12.42</v>
+        <v>14.12</v>
       </c>
       <c r="M4">
-        <v>13.37</v>
+        <v>13.38</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>321.13</v>
+        <v>320.37</v>
       </c>
       <c r="Q4">
-        <v>337.02</v>
+        <v>335.18</v>
       </c>
       <c r="R4">
-        <v>366.25</v>
+        <v>364.85</v>
       </c>
       <c r="S4">
-        <v>342.69</v>
+        <v>342.33</v>
       </c>
       <c r="T4">
-        <v>-6.78</v>
+        <v>-5.82</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1234,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>34.51</v>
+        <v>37.12</v>
       </c>
       <c r="Z4">
-        <v>-12.93</v>
+        <v>-12.41</v>
       </c>
       <c r="AA4">
-        <v>-11.53</v>
+        <v>-11.71</v>
       </c>
       <c r="AB4">
-        <v>-1.39</v>
+        <v>-0.7</v>
       </c>
       <c r="AC4">
-        <v>31.52</v>
+        <v>46.37</v>
       </c>
       <c r="AD4">
-        <v>34.32</v>
+        <v>35.89</v>
       </c>
       <c r="AE4">
-        <v>11.05</v>
+        <v>11.13</v>
       </c>
       <c r="AF4">
-        <v>-25.63</v>
+        <v>-50.44</v>
       </c>
       <c r="AG4">
-        <v>366.05</v>
+        <v>362.92</v>
       </c>
       <c r="AH4">
-        <v>308</v>
+        <v>307.44</v>
       </c>
       <c r="AI4">
         <v>348.44</v>
@@ -1258,7 +1270,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>36.52</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1281,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>349.1</v>
+        <v>346.5</v>
       </c>
       <c r="D5">
-        <v>2.05</v>
+        <v>-0.74</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1293,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-17.22</v>
+        <v>-17.83</v>
       </c>
       <c r="H5">
-        <v>18.64</v>
+        <v>17.76</v>
       </c>
       <c r="I5">
-        <v>-0.58</v>
+        <v>-1.31</v>
       </c>
       <c r="J5">
-        <v>-4.66</v>
+        <v>-6.38</v>
       </c>
       <c r="K5">
-        <v>-7.86</v>
+        <v>-8.48</v>
       </c>
       <c r="L5">
-        <v>-4.21</v>
+        <v>-4.11</v>
       </c>
       <c r="M5">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="N5">
+        <v>45</v>
+      </c>
+      <c r="O5">
         <v>55</v>
       </c>
-      <c r="O5">
-        <v>57</v>
-      </c>
       <c r="P5">
-        <v>349.12</v>
+        <v>348.2</v>
       </c>
       <c r="Q5">
-        <v>355.15</v>
+        <v>354.49</v>
       </c>
       <c r="R5">
-        <v>368.44</v>
+        <v>367.66</v>
       </c>
       <c r="S5">
-        <v>357.91</v>
+        <v>357.62</v>
       </c>
       <c r="T5">
-        <v>-2.46</v>
+        <v>-3.11</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1347,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>42.18</v>
+        <v>40.32</v>
       </c>
       <c r="Z5">
-        <v>-4.77</v>
+        <v>-4.92</v>
       </c>
       <c r="AA5">
-        <v>-4.15</v>
+        <v>-4.31</v>
       </c>
       <c r="AB5">
         <v>-0.61</v>
       </c>
       <c r="AC5">
-        <v>17.4</v>
+        <v>28.73</v>
       </c>
       <c r="AD5">
-        <v>25.03</v>
+        <v>22.11</v>
       </c>
       <c r="AE5">
-        <v>12.29</v>
+        <v>12.18</v>
       </c>
       <c r="AF5">
-        <v>364.92</v>
+        <v>-55.06</v>
       </c>
       <c r="AG5">
-        <v>368.9</v>
+        <v>368.59</v>
       </c>
       <c r="AH5">
-        <v>341.41</v>
+        <v>340.4</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1371,7 +1383,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>33.12</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1394,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>400.35</v>
+        <v>398.75</v>
       </c>
       <c r="D6">
-        <v>1.25</v>
+        <v>-0.4</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1406,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.57</v>
+        <v>-9.93</v>
       </c>
       <c r="H6">
-        <v>43.21</v>
+        <v>42.64</v>
       </c>
       <c r="I6">
-        <v>-3.85</v>
+        <v>-1.97</v>
       </c>
       <c r="J6">
-        <v>-2.08</v>
+        <v>-0.75</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>4.18</v>
       </c>
       <c r="L6">
-        <v>14.5</v>
+        <v>11.01</v>
       </c>
       <c r="M6">
-        <v>-11.28</v>
+        <v>-11.88</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P6">
-        <v>405.74</v>
+        <v>404.14</v>
       </c>
       <c r="Q6">
-        <v>406.93</v>
+        <v>406.86</v>
       </c>
       <c r="R6">
-        <v>405.17</v>
+        <v>405.09</v>
       </c>
       <c r="S6">
-        <v>377.83</v>
+        <v>378.21</v>
       </c>
       <c r="T6">
-        <v>5.96</v>
+        <v>5.43</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1460,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.09</v>
+        <v>45.24</v>
       </c>
       <c r="Z6">
-        <v>1.85</v>
+        <v>0.89</v>
       </c>
       <c r="AA6">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AB6">
-        <v>-1.8</v>
+        <v>-2.21</v>
       </c>
       <c r="AC6">
-        <v>13.22</v>
+        <v>5.73</v>
       </c>
       <c r="AD6">
-        <v>23.75</v>
+        <v>14.39</v>
       </c>
       <c r="AE6">
-        <v>14.18</v>
+        <v>13.8</v>
       </c>
       <c r="AF6">
-        <v>-39.8</v>
+        <v>-51.68</v>
       </c>
       <c r="AG6">
-        <v>434.99</v>
+        <v>435</v>
       </c>
       <c r="AH6">
-        <v>378.86</v>
+        <v>378.72</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1484,7 +1496,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>30.46</v>
+        <v>30.13</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1507,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>618.1</v>
+        <v>606.75</v>
       </c>
       <c r="D7">
-        <v>-4.06</v>
+        <v>-1.84</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1507,46 +1519,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-16.21</v>
+        <v>-17.75</v>
       </c>
       <c r="H7">
-        <v>22.05</v>
+        <v>19.8</v>
       </c>
       <c r="I7">
-        <v>-11.54</v>
+        <v>-11.43</v>
       </c>
       <c r="J7">
-        <v>-9.19</v>
+        <v>-10.27</v>
       </c>
       <c r="K7">
-        <v>3.29</v>
+        <v>2.52</v>
       </c>
       <c r="L7">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="M7">
-        <v>26.86</v>
+        <v>24.08</v>
       </c>
       <c r="N7">
         <v>77</v>
       </c>
       <c r="O7">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P7">
-        <v>665.17</v>
+        <v>649.51</v>
       </c>
       <c r="Q7">
-        <v>700.47</v>
+        <v>694.86</v>
       </c>
       <c r="R7">
-        <v>655.4400000000001</v>
+        <v>656.12</v>
       </c>
       <c r="S7">
-        <v>602.1799999999999</v>
+        <v>602.47</v>
       </c>
       <c r="T7">
-        <v>2.64</v>
+        <v>0.71</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,43 +1573,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>33.85</v>
+        <v>31.98</v>
       </c>
       <c r="Z7">
-        <v>-0.48</v>
+        <v>-6.35</v>
       </c>
       <c r="AA7">
-        <v>11.94</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AB7">
-        <v>-12.42</v>
+        <v>-14.64</v>
       </c>
       <c r="AC7">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>4.47</v>
+        <v>2.94</v>
       </c>
       <c r="AE7">
-        <v>30.28</v>
+        <v>29.97</v>
       </c>
       <c r="AF7">
-        <v>-7.11</v>
+        <v>-44.63</v>
       </c>
       <c r="AG7">
-        <v>756.17</v>
+        <v>763.76</v>
       </c>
       <c r="AH7">
-        <v>644.77</v>
+        <v>625.96</v>
       </c>
       <c r="AI7">
-        <v>722.95</v>
+        <v>705.96</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.1</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1620,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>188.02</v>
+        <v>192.63</v>
       </c>
       <c r="D8">
-        <v>0.42</v>
+        <v>2.45</v>
       </c>
       <c r="E8">
-        <v>344.1</v>
+        <v>344.05</v>
       </c>
       <c r="F8">
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-45.36</v>
+        <v>-44.01</v>
       </c>
       <c r="H8">
-        <v>0.42</v>
+        <v>2.88</v>
       </c>
       <c r="I8">
-        <v>-3.51</v>
+        <v>-1.12</v>
       </c>
       <c r="J8">
-        <v>-8.6</v>
+        <v>-3.38</v>
       </c>
       <c r="K8">
-        <v>-19.55</v>
+        <v>-16.86</v>
       </c>
       <c r="L8">
-        <v>-45.88</v>
+        <v>-44.02</v>
       </c>
       <c r="M8">
-        <v>-4.89</v>
+        <v>-4.39</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P8">
-        <v>192.37</v>
+        <v>191.93</v>
       </c>
       <c r="Q8">
-        <v>195.83</v>
+        <v>195.63</v>
       </c>
       <c r="R8">
-        <v>209.29</v>
+        <v>208.83</v>
       </c>
       <c r="S8">
-        <v>246.58</v>
+        <v>245.99</v>
       </c>
       <c r="T8">
-        <v>-23.75</v>
+        <v>-21.69</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1686,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.46</v>
+        <v>39.47</v>
       </c>
       <c r="Z8">
-        <v>-4.9</v>
+        <v>-4.67</v>
       </c>
       <c r="AA8">
-        <v>-4.8</v>
+        <v>-4.77</v>
       </c>
       <c r="AB8">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="AC8">
-        <v>27.06</v>
+        <v>32.89</v>
       </c>
       <c r="AD8">
-        <v>51.02</v>
+        <v>37.24</v>
       </c>
       <c r="AE8">
-        <v>5.55</v>
+        <v>5.68</v>
       </c>
       <c r="AF8">
-        <v>16.82</v>
+        <v>21.71</v>
       </c>
       <c r="AG8">
-        <v>203.48</v>
+        <v>203.4</v>
       </c>
       <c r="AH8">
-        <v>188.18</v>
+        <v>187.86</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1710,7 +1722,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>34.65</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1733,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3439.1</v>
+        <v>3738.4</v>
       </c>
       <c r="D9">
-        <v>-1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1733,46 +1745,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.14</v>
+        <v>-14.28</v>
       </c>
       <c r="H9">
-        <v>3.93</v>
+        <v>12.98</v>
       </c>
       <c r="I9">
-        <v>-2.92</v>
+        <v>5.84</v>
       </c>
       <c r="J9">
-        <v>-5.33</v>
+        <v>4.01</v>
       </c>
       <c r="K9">
-        <v>-9</v>
+        <v>-1.35</v>
       </c>
       <c r="L9">
-        <v>-16.46</v>
+        <v>-9.32</v>
       </c>
       <c r="M9">
-        <v>18.96</v>
+        <v>20.7</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="P9">
-        <v>3509.36</v>
+        <v>3550.6</v>
       </c>
       <c r="Q9">
-        <v>3545.87</v>
+        <v>3555.24</v>
       </c>
       <c r="R9">
-        <v>3572.7</v>
+        <v>3575.31</v>
       </c>
       <c r="S9">
-        <v>3669.47</v>
+        <v>3670.12</v>
       </c>
       <c r="T9">
-        <v>-6.28</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1784,46 +1796,46 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>30.35</v>
+        <v>66.2</v>
       </c>
       <c r="Z9">
-        <v>-23.8</v>
+        <v>-5</v>
       </c>
       <c r="AA9">
-        <v>-16.04</v>
+        <v>-13.83</v>
       </c>
       <c r="AB9">
-        <v>-7.77</v>
+        <v>8.83</v>
       </c>
       <c r="AC9">
-        <v>8.779999999999999</v>
+        <v>33.33</v>
       </c>
       <c r="AD9">
-        <v>16.57</v>
+        <v>19.88</v>
       </c>
       <c r="AE9">
-        <v>62.63</v>
+        <v>94.61</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>18044.82</v>
       </c>
       <c r="AG9">
-        <v>3616.8</v>
+        <v>3666.86</v>
       </c>
       <c r="AH9">
-        <v>3474.94</v>
+        <v>3443.62</v>
       </c>
       <c r="AI9">
-        <v>3651.13</v>
+        <v>3419.66</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK9">
-        <v>17.94</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1846,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1514.1</v>
+        <v>1471</v>
       </c>
       <c r="D10">
-        <v>1.2</v>
+        <v>-2.85</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1858,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-14.38</v>
+        <v>-16.82</v>
       </c>
       <c r="H10">
-        <v>14.17</v>
+        <v>10.92</v>
       </c>
       <c r="I10">
-        <v>-1.23</v>
+        <v>-4.23</v>
       </c>
       <c r="J10">
-        <v>-2.88</v>
+        <v>-2.45</v>
       </c>
       <c r="K10">
-        <v>4.08</v>
+        <v>-2.23</v>
       </c>
       <c r="L10">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="M10">
-        <v>4.65</v>
+        <v>4.43</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P10">
-        <v>1508.36</v>
+        <v>1495.38</v>
       </c>
       <c r="Q10">
-        <v>1535.42</v>
+        <v>1532.68</v>
       </c>
       <c r="R10">
-        <v>1581.74</v>
+        <v>1577.78</v>
       </c>
       <c r="S10">
-        <v>1515.8</v>
+        <v>1514.92</v>
       </c>
       <c r="T10">
-        <v>-0.11</v>
+        <v>-2.9</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,43 +1912,43 @@
         <v>1</v>
       </c>
       <c r="Y10">
-        <v>42.98</v>
+        <v>35.29</v>
       </c>
       <c r="Z10">
-        <v>-18.86</v>
+        <v>-21.54</v>
       </c>
       <c r="AA10">
-        <v>-16.15</v>
+        <v>-17.23</v>
       </c>
       <c r="AB10">
-        <v>-2.71</v>
+        <v>-4.31</v>
       </c>
       <c r="AC10">
         <v>25.97</v>
       </c>
       <c r="AD10">
-        <v>18.56</v>
+        <v>19.63</v>
       </c>
       <c r="AE10">
-        <v>39.1</v>
+        <v>41.42</v>
       </c>
       <c r="AF10">
-        <v>5.53</v>
+        <v>119.73</v>
       </c>
       <c r="AG10">
-        <v>1581.58</v>
+        <v>1587.03</v>
       </c>
       <c r="AH10">
-        <v>1489.26</v>
+        <v>1478.33</v>
       </c>
       <c r="AI10">
-        <v>1617.52</v>
+        <v>1594.51</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>17.36</v>
+        <v>20.78</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2129,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,370 +2147,373 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.2</v>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.94</v>
+        <v>-3.3</v>
       </c>
       <c r="D8" s="6">
-        <v>-11.51</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.43</v>
+        <v>-0.58</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.72</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-16.61</v>
+        <v>-11.51</v>
       </c>
       <c r="D9" s="6">
-        <v>-14.67</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.94</v>
+        <v>-10.7</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.01</v>
+        <v>-14.67</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.35</v>
+        <v>-11.37</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.93</v>
+        <v>-4.66</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.08</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.15</v>
+        <v>-6.38</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.49</v>
+        <v>-2.08</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.19</v>
+        <v>-0.75</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.7</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-8.9</v>
+        <v>-9.19</v>
       </c>
       <c r="D13" s="6">
-        <v>-8.6</v>
+        <v>-10.27</v>
       </c>
       <c r="E13" s="8">
-        <v>0.3</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.29</v>
+        <v>-8.6</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.33</v>
+        <v>-3.38</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.04</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.34</v>
+        <v>-5.33</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.46</v>
+        <v>4.01</v>
+      </c>
+      <c r="E15" s="7">
+        <v>9.34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.79</v>
+        <v>-2.88</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.49</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.3</v>
+        <v>-2.45</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.74</v>
+        <v>-1.49</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4.51</v>
+        <v>0.38</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.42</v>
+        <v>-2.23</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.09</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.33</v>
+        <v>-1.56</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-5.05</v>
+        <v>-0.09</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.58</v>
+        <v>-1.16</v>
       </c>
       <c r="E19" s="8">
-        <v>4.47</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-9.279999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.85</v>
+        <v>-1.31</v>
       </c>
       <c r="E20" s="8">
-        <v>5.43</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-12.66</v>
+        <v>-3.85</v>
       </c>
       <c r="D21" s="6">
-        <v>-11.54</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.12</v>
+        <v>-1.97</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.88</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.61</v>
+        <v>-11.54</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.1</v>
+        <v>-11.43</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.54</v>
+        <v>-3.51</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.92</v>
+        <v>-1.12</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.38</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.82</v>
+        <v>-2.92</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.59</v>
+        <v>5.84</v>
+      </c>
+      <c r="E24" s="7">
+        <v>8.76</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-8.56</v>
+        <v>-1.23</v>
       </c>
       <c r="D25" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.1</v>
+        <v>-4.23</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-3</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-20.53</v>
+        <v>-8.66</v>
       </c>
       <c r="D26" s="6">
-        <v>-19.46</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.07</v>
+        <v>-6.3</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.36</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2524,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>12.6</v>
+        <v>12.42</v>
       </c>
       <c r="D27" s="6">
-        <v>12.42</v>
+        <v>14.12</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.18</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2541,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.87</v>
+        <v>-4.21</v>
       </c>
       <c r="D28" s="6">
-        <v>-4.21</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.66</v>
+        <v>-4.11</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2558,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>12.14</v>
+        <v>14.5</v>
       </c>
       <c r="D29" s="6">
-        <v>14.5</v>
+        <v>11.01</v>
       </c>
       <c r="E29" s="8">
-        <v>2.36</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2575,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="D30" s="6">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="E30" s="7">
-        <v>-3.7</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2592,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-46.9</v>
+        <v>-45.88</v>
       </c>
       <c r="D31" s="6">
-        <v>-45.88</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.02</v>
+        <v>-44.02</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.86</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2609,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-16.4</v>
+        <v>-16.46</v>
       </c>
       <c r="D32" s="6">
-        <v>-16.46</v>
+        <v>-9.32</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.06</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2626,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>7.94</v>
+        <v>6.3</v>
       </c>
       <c r="D33" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.64</v>
+        <v>3.3</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-3</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2643,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-19.53</v>
+        <v>-20.15</v>
       </c>
       <c r="D34" s="6">
-        <v>-20.15</v>
+        <v>-19.16</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.62</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2660,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-10.83</v>
+        <v>-10.65</v>
       </c>
       <c r="D35" s="6">
-        <v>-10.65</v>
+        <v>-10.99</v>
       </c>
       <c r="E35" s="8">
-        <v>0.18</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2677,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-7.8</v>
+        <v>-6.28</v>
       </c>
       <c r="D36" s="6">
-        <v>-6.28</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.52</v>
+        <v>-3.1</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3.18</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2694,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-7.04</v>
+        <v>-7.86</v>
       </c>
       <c r="D37" s="6">
-        <v>-7.86</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.82</v>
+        <v>-8.48</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2711,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>1.66</v>
+        <v>3.4</v>
       </c>
       <c r="D38" s="6">
-        <v>3.4</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.74</v>
+        <v>4.18</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.78</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2728,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>9</v>
+        <v>3.29</v>
       </c>
       <c r="D39" s="6">
-        <v>3.29</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-5.71</v>
+        <v>2.52</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2745,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-19.2</v>
+        <v>-19.55</v>
       </c>
       <c r="D40" s="6">
-        <v>-19.55</v>
+        <v>-16.86</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.35</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2762,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-6.45</v>
+        <v>-9</v>
       </c>
       <c r="D41" s="6">
-        <v>-9</v>
+        <v>-1.35</v>
       </c>
       <c r="E41" s="7">
-        <v>-2.55</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2779,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>4.9</v>
+        <v>4.08</v>
       </c>
       <c r="D42" s="6">
-        <v>4.08</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.82</v>
+        <v>-2.23</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-6.31</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2796,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-24.18</v>
+        <v>-24.37</v>
       </c>
       <c r="D43" s="6">
-        <v>-24.37</v>
+        <v>-22.59</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.19</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2813,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-27.65</v>
+        <v>-26.46</v>
       </c>
       <c r="D44" s="6">
-        <v>-26.46</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.19</v>
+        <v>-26.02</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2830,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-24.69</v>
+        <v>-22.52</v>
       </c>
       <c r="D45" s="6">
-        <v>-22.52</v>
-      </c>
-      <c r="E45" s="8">
-        <v>2.17</v>
+        <v>-21.8</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.72</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2847,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-18.88</v>
+        <v>-17.22</v>
       </c>
       <c r="D46" s="6">
-        <v>-17.22</v>
+        <v>-17.83</v>
       </c>
       <c r="E46" s="8">
-        <v>1.66</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,13 +2864,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-10.68</v>
+        <v>-9.57</v>
       </c>
       <c r="D47" s="6">
-        <v>-9.57</v>
+        <v>-9.93</v>
       </c>
       <c r="E47" s="8">
-        <v>1.11</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2866,13 +2881,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-12.66</v>
+        <v>-16.21</v>
       </c>
       <c r="D48" s="6">
-        <v>-16.21</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.55</v>
+        <v>-17.75</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2883,13 +2898,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-46.11</v>
+        <v>-45.36</v>
       </c>
       <c r="D49" s="6">
-        <v>-45.36</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.75</v>
+        <v>-44.01</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2900,13 +2915,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-19.94</v>
+        <v>-21.14</v>
       </c>
       <c r="D50" s="6">
-        <v>-21.14</v>
+        <v>-14.28</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.2</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2917,13 +2932,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-15.39</v>
+        <v>-14.38</v>
       </c>
       <c r="D51" s="6">
-        <v>-14.38</v>
+        <v>-16.82</v>
       </c>
       <c r="E51" s="8">
-        <v>1.01</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2934,13 +2949,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>371.65</v>
+        <v>370.75</v>
       </c>
       <c r="D52" s="6">
-        <v>370.75</v>
+        <v>379.45</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2951,13 +2966,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2751.2</v>
+        <v>2796.2</v>
       </c>
       <c r="D53" s="6">
-        <v>2796.2</v>
-      </c>
-      <c r="E53" s="8">
-        <v>45</v>
+        <v>2813</v>
+      </c>
+      <c r="E53" s="7">
+        <v>16.8</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2968,13 +2983,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>310.5</v>
+        <v>319.45</v>
       </c>
       <c r="D54" s="6">
-        <v>319.45</v>
-      </c>
-      <c r="E54" s="8">
-        <v>8.949999999999999</v>
+        <v>322.4</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2.95</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2985,13 +3000,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>342.1</v>
+        <v>349.1</v>
       </c>
       <c r="D55" s="6">
-        <v>349.1</v>
+        <v>346.5</v>
       </c>
       <c r="E55" s="8">
-        <v>7</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3002,13 +3017,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>395.4</v>
+        <v>400.35</v>
       </c>
       <c r="D56" s="6">
-        <v>400.35</v>
+        <v>398.75</v>
       </c>
       <c r="E56" s="8">
-        <v>4.95</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3019,13 +3034,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>644.25</v>
+        <v>618.1</v>
       </c>
       <c r="D57" s="6">
-        <v>618.1</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-26.15</v>
+        <v>606.75</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-11.35</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3036,13 +3051,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>187.23</v>
+        <v>188.02</v>
       </c>
       <c r="D58" s="6">
-        <v>188.02</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.79</v>
+        <v>192.63</v>
+      </c>
+      <c r="E58" s="7">
+        <v>4.61</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3053,13 +3068,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3491.6</v>
+        <v>3439.1</v>
       </c>
       <c r="D59" s="6">
-        <v>3439.1</v>
+        <v>3738.4</v>
       </c>
       <c r="E59" s="7">
-        <v>-52.5</v>
+        <v>299.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3070,376 +3085,393 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1496.2</v>
+        <v>1514.1</v>
       </c>
       <c r="D60" s="6">
-        <v>1514.1</v>
+        <v>1471</v>
       </c>
       <c r="E60" s="8">
-        <v>17.9</v>
+        <v>-43.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="6">
+        <v>66</v>
+      </c>
+      <c r="D61" s="6">
         <v>88</v>
       </c>
-      <c r="D61" s="6">
-        <v>99</v>
-      </c>
-      <c r="E61" s="8">
-        <v>11</v>
+      <c r="E61" s="7">
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D62" s="6">
-        <v>77</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-22</v>
+        <v>45</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="D63" s="6">
-        <v>88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
+        <v>55</v>
+      </c>
+      <c r="E63" s="7">
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>37.18</v>
+        <v>88</v>
       </c>
       <c r="D64" s="6">
-        <v>36.59</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.59</v>
+        <v>66</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-22</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>17.86</v>
+        <v>36.59</v>
       </c>
       <c r="D65" s="6">
-        <v>25.76</v>
-      </c>
-      <c r="E65" s="8">
-        <v>7.9</v>
+        <v>45.55</v>
+      </c>
+      <c r="E65" s="7">
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>25.85</v>
+        <v>25.76</v>
       </c>
       <c r="D66" s="6">
-        <v>34.51</v>
-      </c>
-      <c r="E66" s="8">
-        <v>8.66</v>
+        <v>28.52</v>
+      </c>
+      <c r="E66" s="7">
+        <v>2.76</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>34.66</v>
+        <v>34.51</v>
       </c>
       <c r="D67" s="6">
-        <v>42.18</v>
-      </c>
-      <c r="E67" s="8">
-        <v>7.52</v>
+        <v>37.12</v>
+      </c>
+      <c r="E67" s="7">
+        <v>2.61</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>43.02</v>
+        <v>42.18</v>
       </c>
       <c r="D68" s="6">
-        <v>46.09</v>
+        <v>40.32</v>
       </c>
       <c r="E68" s="8">
-        <v>3.07</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>38.7</v>
+        <v>46.09</v>
       </c>
       <c r="D69" s="6">
-        <v>33.85</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-4.85</v>
+        <v>45.24</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>27.55</v>
+        <v>33.85</v>
       </c>
       <c r="D70" s="6">
-        <v>29.46</v>
+        <v>31.98</v>
       </c>
       <c r="E70" s="8">
-        <v>1.91</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>36.69</v>
+        <v>29.46</v>
       </c>
       <c r="D71" s="6">
-        <v>30.35</v>
+        <v>39.47</v>
       </c>
       <c r="E71" s="7">
-        <v>-6.34</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>37.75</v>
+        <v>30.35</v>
       </c>
       <c r="D72" s="6">
-        <v>42.98</v>
-      </c>
-      <c r="E72" s="8">
-        <v>5.23</v>
+        <v>66.2</v>
+      </c>
+      <c r="E72" s="7">
+        <v>35.85</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>-29.55</v>
+        <v>42.98</v>
       </c>
       <c r="D73" s="6">
-        <v>-47.63</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-18.08</v>
+        <v>35.29</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-7.69</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>39.99</v>
+        <v>-47.63</v>
       </c>
       <c r="D74" s="6">
-        <v>-48.6</v>
+        <v>-40.73</v>
       </c>
       <c r="E74" s="7">
-        <v>-88.59</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>12.77</v>
+        <v>-48.6</v>
       </c>
       <c r="D75" s="6">
-        <v>-25.63</v>
+        <v>-20.21</v>
       </c>
       <c r="E75" s="7">
-        <v>-38.4</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>82.44</v>
+        <v>-25.63</v>
       </c>
       <c r="D76" s="6">
-        <v>364.92</v>
+        <v>-50.44</v>
       </c>
       <c r="E76" s="8">
-        <v>282.48</v>
+        <v>-24.81</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-20.74</v>
+        <v>364.92</v>
       </c>
       <c r="D77" s="6">
-        <v>-39.8</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-19.06</v>
+        <v>-55.06</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-419.98</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>18.11</v>
+        <v>-39.8</v>
       </c>
       <c r="D78" s="6">
-        <v>-7.11</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-25.22</v>
+        <v>-51.68</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-11.88</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>14.44</v>
+        <v>-7.11</v>
       </c>
       <c r="D79" s="6">
-        <v>16.82</v>
+        <v>-44.63</v>
       </c>
       <c r="E79" s="8">
-        <v>2.38</v>
+        <v>-37.52</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>5.8</v>
+        <v>16.82</v>
       </c>
       <c r="D80" s="6">
-        <v>1.8</v>
+        <v>21.71</v>
       </c>
       <c r="E80" s="7">
-        <v>-4</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-15.55</v>
+        <v>1.8</v>
       </c>
       <c r="D81" s="6">
+        <v>18044.82</v>
+      </c>
+      <c r="E81" s="7">
+        <v>18043.02</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
         <v>5.53</v>
       </c>
-      <c r="E81" s="8">
-        <v>21.08</v>
+      <c r="D82" s="6">
+        <v>119.73</v>
+      </c>
+      <c r="E82" s="7">
+        <v>114.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3463,28 +3495,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3492,22 +3524,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>40.16</v>
+        <v>44.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>35.8</v>
+        <v>41.1</v>
       </c>
       <c r="E2" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.9</v>
+        <v>-4.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-7</v>
+        <v>-6.2</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3615,10 +3647,10 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>44</v>
@@ -3644,31 +3676,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.2686</v>
+        <v>0.2679</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2651</v>
+        <v>0.2408</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1896</v>
+        <v>0.207</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1337</v>
+        <v>0.1338</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0998</v>
+        <v>0.1041</v>
       </c>
       <c r="F2" s="14">
-        <v>0.04940000000000001</v>
+        <v>0.0488</v>
       </c>
       <c r="G2" s="14">
-        <v>0.04650000000000001</v>
+        <v>0.0443</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0489</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1128</v>
+        <v>-0.1188</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,28 +196,37 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>29.5 → 39.5</t>
+    <t>28.5 → 36.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>39.5</t>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>36.3</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>30.4 → 66.2</t>
-  </si>
-  <si>
-    <t>30.4</t>
-  </si>
-  <si>
-    <t>66.2</t>
+    <t>45.2 → 51.8</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>51.8</t>
+  </si>
+  <si>
+    <t>35.3 → 51.1</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>51.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -942,10 +951,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>379.45</v>
+        <v>380.75</v>
       </c>
       <c r="D2">
-        <v>2.35</v>
+        <v>0.34</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -954,46 +963,46 @@
         <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-22.59</v>
+        <v>-22.33</v>
       </c>
       <c r="H2">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="I2">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="J2">
-        <v>-0.58</v>
+        <v>-0.28</v>
       </c>
       <c r="K2">
-        <v>-19.16</v>
+        <v>-16.97</v>
       </c>
       <c r="L2">
-        <v>-6.3</v>
+        <v>-7.63</v>
       </c>
       <c r="M2">
-        <v>10.41</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>375.91</v>
+        <v>376.26</v>
       </c>
       <c r="Q2">
-        <v>381.65</v>
+        <v>381.71</v>
       </c>
       <c r="R2">
-        <v>392.61</v>
+        <v>392.05</v>
       </c>
       <c r="S2">
-        <v>433.6</v>
+        <v>433.52</v>
       </c>
       <c r="T2">
-        <v>-12.49</v>
+        <v>-12.17</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1008,34 +1017,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.55</v>
+        <v>46.76</v>
       </c>
       <c r="Z2">
-        <v>-5.2</v>
+        <v>-4.67</v>
       </c>
       <c r="AA2">
-        <v>-5.32</v>
+        <v>-5.19</v>
       </c>
       <c r="AB2">
-        <v>0.12</v>
+        <v>0.52</v>
       </c>
       <c r="AC2">
-        <v>26.24</v>
+        <v>53.86</v>
       </c>
       <c r="AD2">
-        <v>24.83</v>
+        <v>30.98</v>
       </c>
       <c r="AE2">
-        <v>9.31</v>
+        <v>9.08</v>
       </c>
       <c r="AF2">
-        <v>-40.73</v>
+        <v>-49.42</v>
       </c>
       <c r="AG2">
-        <v>395.16</v>
+        <v>395.19</v>
       </c>
       <c r="AH2">
-        <v>368.14</v>
+        <v>368.22</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1044,7 +1053,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>34.49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,10 +1064,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2813</v>
+        <v>2864.4</v>
       </c>
       <c r="D3">
-        <v>0.6</v>
+        <v>1.83</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1067,46 +1076,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-26.02</v>
+        <v>-24.67</v>
       </c>
       <c r="H3">
-        <v>2.25</v>
+        <v>4.11</v>
       </c>
       <c r="I3">
-        <v>-1.56</v>
+        <v>0.33</v>
       </c>
       <c r="J3">
-        <v>-10.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="K3">
-        <v>-10.99</v>
+        <v>-7.4</v>
       </c>
       <c r="L3">
-        <v>-19.46</v>
+        <v>-16.4</v>
       </c>
       <c r="M3">
-        <v>26.79</v>
+        <v>25.99</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>2803.08</v>
+        <v>2804.96</v>
       </c>
       <c r="Q3">
-        <v>2955.67</v>
+        <v>2943.53</v>
       </c>
       <c r="R3">
-        <v>3192.04</v>
+        <v>3181.36</v>
       </c>
       <c r="S3">
-        <v>3251.7</v>
+        <v>3247.89</v>
       </c>
       <c r="T3">
-        <v>-13.49</v>
+        <v>-11.81</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1121,34 +1130,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.52</v>
+        <v>36.33</v>
       </c>
       <c r="Z3">
-        <v>-108.34</v>
+        <v>-101.45</v>
       </c>
       <c r="AA3">
-        <v>-98</v>
+        <v>-98.69</v>
       </c>
       <c r="AB3">
-        <v>-10.34</v>
+        <v>-2.76</v>
       </c>
       <c r="AC3">
-        <v>36.38</v>
+        <v>69.72</v>
       </c>
       <c r="AD3">
-        <v>17.29</v>
+        <v>40.53</v>
       </c>
       <c r="AE3">
-        <v>61.88</v>
+        <v>63.23</v>
       </c>
       <c r="AF3">
-        <v>-20.21</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AG3">
-        <v>3179.89</v>
+        <v>3159.38</v>
       </c>
       <c r="AH3">
-        <v>2731.44</v>
+        <v>2727.69</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1157,7 +1166,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>82.22</v>
+        <v>77.23999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1168,10 +1177,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>322.4</v>
+        <v>325.75</v>
       </c>
       <c r="D4">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1180,46 +1189,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-21.8</v>
+        <v>-20.99</v>
       </c>
       <c r="H4">
-        <v>16.94</v>
+        <v>18.15</v>
       </c>
       <c r="I4">
-        <v>-1.16</v>
+        <v>-0.61</v>
       </c>
       <c r="J4">
-        <v>-11.37</v>
+        <v>-9.32</v>
       </c>
       <c r="K4">
-        <v>-3.1</v>
+        <v>0.2</v>
       </c>
       <c r="L4">
-        <v>14.12</v>
+        <v>17.54</v>
       </c>
       <c r="M4">
-        <v>13.38</v>
+        <v>13.67</v>
       </c>
       <c r="N4">
         <v>88</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>320.37</v>
+        <v>319.97</v>
       </c>
       <c r="Q4">
-        <v>335.18</v>
+        <v>333.66</v>
       </c>
       <c r="R4">
-        <v>364.85</v>
+        <v>363.65</v>
       </c>
       <c r="S4">
-        <v>342.33</v>
+        <v>342.03</v>
       </c>
       <c r="T4">
-        <v>-5.82</v>
+        <v>-4.76</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1234,34 +1243,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.12</v>
+        <v>40.03</v>
       </c>
       <c r="Z4">
-        <v>-12.41</v>
+        <v>-11.6</v>
       </c>
       <c r="AA4">
-        <v>-11.71</v>
+        <v>-11.69</v>
       </c>
       <c r="AB4">
-        <v>-0.7</v>
+        <v>0.09</v>
       </c>
       <c r="AC4">
-        <v>46.37</v>
+        <v>77.86</v>
       </c>
       <c r="AD4">
-        <v>35.89</v>
+        <v>51.92</v>
       </c>
       <c r="AE4">
-        <v>11.13</v>
+        <v>10.87</v>
       </c>
       <c r="AF4">
-        <v>-50.44</v>
+        <v>3.16</v>
       </c>
       <c r="AG4">
-        <v>362.92</v>
+        <v>359.85</v>
       </c>
       <c r="AH4">
-        <v>307.44</v>
+        <v>307.47</v>
       </c>
       <c r="AI4">
         <v>348.44</v>
@@ -1270,7 +1279,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>34.47</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1281,10 +1290,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>346.5</v>
+        <v>350.45</v>
       </c>
       <c r="D5">
-        <v>-0.74</v>
+        <v>1.14</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1293,46 +1302,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-17.83</v>
+        <v>-16.9</v>
       </c>
       <c r="H5">
-        <v>17.76</v>
+        <v>19.1</v>
       </c>
       <c r="I5">
-        <v>-1.31</v>
+        <v>-0.5</v>
       </c>
       <c r="J5">
-        <v>-6.38</v>
+        <v>-2.56</v>
       </c>
       <c r="K5">
-        <v>-8.48</v>
+        <v>-5.89</v>
       </c>
       <c r="L5">
-        <v>-4.11</v>
+        <v>-2.65</v>
       </c>
       <c r="M5">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="N5">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>348.2</v>
+        <v>347.85</v>
       </c>
       <c r="Q5">
-        <v>354.49</v>
+        <v>354.37</v>
       </c>
       <c r="R5">
-        <v>367.66</v>
+        <v>366.81</v>
       </c>
       <c r="S5">
-        <v>357.62</v>
+        <v>357.38</v>
       </c>
       <c r="T5">
-        <v>-3.11</v>
+        <v>-1.94</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1347,34 +1356,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.32</v>
+        <v>44.33</v>
       </c>
       <c r="Z5">
-        <v>-4.92</v>
+        <v>-4.67</v>
       </c>
       <c r="AA5">
-        <v>-4.31</v>
+        <v>-4.38</v>
       </c>
       <c r="AB5">
-        <v>-0.61</v>
+        <v>-0.29</v>
       </c>
       <c r="AC5">
-        <v>28.73</v>
+        <v>49.81</v>
       </c>
       <c r="AD5">
-        <v>22.11</v>
+        <v>31.98</v>
       </c>
       <c r="AE5">
-        <v>12.18</v>
+        <v>12.09</v>
       </c>
       <c r="AF5">
-        <v>-55.06</v>
+        <v>-48.44</v>
       </c>
       <c r="AG5">
-        <v>368.59</v>
+        <v>368.56</v>
       </c>
       <c r="AH5">
-        <v>340.4</v>
+        <v>340.17</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1383,7 +1392,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.71</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,10 +1403,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>398.75</v>
+        <v>409.8</v>
       </c>
       <c r="D6">
-        <v>-0.4</v>
+        <v>2.77</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1406,46 +1415,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.93</v>
+        <v>-7.43</v>
       </c>
       <c r="H6">
-        <v>42.64</v>
+        <v>46.59</v>
       </c>
       <c r="I6">
-        <v>-1.97</v>
+        <v>-1.26</v>
       </c>
       <c r="J6">
-        <v>-0.75</v>
+        <v>2.42</v>
       </c>
       <c r="K6">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="L6">
-        <v>11.01</v>
+        <v>14.42</v>
       </c>
       <c r="M6">
-        <v>-11.88</v>
+        <v>-11.06</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>404.14</v>
+        <v>403.09</v>
       </c>
       <c r="Q6">
-        <v>406.86</v>
+        <v>407.49</v>
       </c>
       <c r="R6">
-        <v>405.09</v>
+        <v>405.1</v>
       </c>
       <c r="S6">
-        <v>378.21</v>
+        <v>378.6</v>
       </c>
       <c r="T6">
-        <v>5.43</v>
+        <v>8.24</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1460,34 +1469,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>45.24</v>
+        <v>51.84</v>
       </c>
       <c r="Z6">
-        <v>0.89</v>
+        <v>1.01</v>
       </c>
       <c r="AA6">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="AB6">
-        <v>-2.21</v>
+        <v>-1.67</v>
       </c>
       <c r="AC6">
-        <v>5.73</v>
+        <v>15.29</v>
       </c>
       <c r="AD6">
-        <v>14.39</v>
+        <v>11.41</v>
       </c>
       <c r="AE6">
-        <v>13.8</v>
+        <v>14.37</v>
       </c>
       <c r="AF6">
-        <v>-51.68</v>
+        <v>-40.87</v>
       </c>
       <c r="AG6">
-        <v>435</v>
+        <v>435.28</v>
       </c>
       <c r="AH6">
-        <v>378.72</v>
+        <v>379.7</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1496,7 +1505,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>30.13</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,10 +1516,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>606.75</v>
+        <v>590.45</v>
       </c>
       <c r="D7">
-        <v>-1.84</v>
+        <v>-2.69</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1519,46 +1528,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-17.75</v>
+        <v>-19.96</v>
       </c>
       <c r="H7">
-        <v>19.8</v>
+        <v>16.59</v>
       </c>
       <c r="I7">
-        <v>-11.43</v>
+        <v>-13.89</v>
       </c>
       <c r="J7">
-        <v>-10.27</v>
+        <v>-17.87</v>
       </c>
       <c r="K7">
-        <v>2.52</v>
+        <v>0.23</v>
       </c>
       <c r="L7">
-        <v>3.73</v>
+        <v>1.03</v>
       </c>
       <c r="M7">
-        <v>24.08</v>
+        <v>22.1</v>
       </c>
       <c r="N7">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O7">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="P7">
-        <v>649.51</v>
+        <v>630.46</v>
       </c>
       <c r="Q7">
-        <v>694.86</v>
+        <v>687.9299999999999</v>
       </c>
       <c r="R7">
-        <v>656.12</v>
+        <v>656.62</v>
       </c>
       <c r="S7">
-        <v>602.47</v>
+        <v>602.63</v>
       </c>
       <c r="T7">
-        <v>0.71</v>
+        <v>-2.02</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1570,46 +1579,46 @@
         <v>48</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>31.98</v>
+        <v>29.46</v>
       </c>
       <c r="Z7">
-        <v>-6.35</v>
+        <v>-12.19</v>
       </c>
       <c r="AA7">
-        <v>8.279999999999999</v>
+        <v>4.19</v>
       </c>
       <c r="AB7">
-        <v>-14.64</v>
+        <v>-16.37</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2.94</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>29.97</v>
+        <v>29.57</v>
       </c>
       <c r="AF7">
-        <v>-44.63</v>
+        <v>-15.9</v>
       </c>
       <c r="AG7">
-        <v>763.76</v>
+        <v>769.15</v>
       </c>
       <c r="AH7">
-        <v>625.96</v>
+        <v>606.72</v>
       </c>
       <c r="AI7">
-        <v>705.96</v>
+        <v>685.91</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>33.7</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,10 +1629,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>192.63</v>
+        <v>191.01</v>
       </c>
       <c r="D8">
-        <v>2.45</v>
+        <v>-0.84</v>
       </c>
       <c r="E8">
         <v>344.05</v>
@@ -1632,46 +1641,46 @@
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-44.01</v>
+        <v>-44.48</v>
       </c>
       <c r="H8">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="I8">
-        <v>-1.12</v>
+        <v>-2.9</v>
       </c>
       <c r="J8">
-        <v>-3.38</v>
+        <v>-2.83</v>
       </c>
       <c r="K8">
-        <v>-16.86</v>
+        <v>-15.27</v>
       </c>
       <c r="L8">
-        <v>-44.02</v>
+        <v>-43.99</v>
       </c>
       <c r="M8">
-        <v>-4.39</v>
+        <v>-4.55</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P8">
-        <v>191.93</v>
+        <v>190.79</v>
       </c>
       <c r="Q8">
-        <v>195.63</v>
+        <v>195.35</v>
       </c>
       <c r="R8">
-        <v>208.83</v>
+        <v>208.28</v>
       </c>
       <c r="S8">
-        <v>245.99</v>
+        <v>245.37</v>
       </c>
       <c r="T8">
-        <v>-21.69</v>
+        <v>-22.15</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1686,34 +1695,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.47</v>
+        <v>37.46</v>
       </c>
       <c r="Z8">
-        <v>-4.67</v>
+        <v>-4.56</v>
       </c>
       <c r="AA8">
-        <v>-4.77</v>
+        <v>-4.73</v>
       </c>
       <c r="AB8">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="AC8">
-        <v>32.89</v>
+        <v>56.46</v>
       </c>
       <c r="AD8">
-        <v>37.24</v>
+        <v>38.8</v>
       </c>
       <c r="AE8">
-        <v>5.68</v>
+        <v>5.67</v>
       </c>
       <c r="AF8">
-        <v>21.71</v>
+        <v>-47.37</v>
       </c>
       <c r="AG8">
-        <v>203.4</v>
+        <v>203.36</v>
       </c>
       <c r="AH8">
-        <v>187.86</v>
+        <v>187.33</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1722,7 +1731,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>31.51</v>
+        <v>28.79</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1742,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3738.4</v>
+        <v>3672</v>
       </c>
       <c r="D9">
-        <v>8.699999999999999</v>
+        <v>-1.78</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1745,46 +1754,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-14.28</v>
+        <v>-15.8</v>
       </c>
       <c r="H9">
-        <v>12.98</v>
+        <v>10.97</v>
       </c>
       <c r="I9">
-        <v>5.84</v>
+        <v>3.79</v>
       </c>
       <c r="J9">
-        <v>4.01</v>
+        <v>3.41</v>
       </c>
       <c r="K9">
-        <v>-1.35</v>
+        <v>-2.26</v>
       </c>
       <c r="L9">
-        <v>-9.32</v>
+        <v>-11.37</v>
       </c>
       <c r="M9">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="N9">
+        <v>45</v>
+      </c>
+      <c r="O9">
         <v>55</v>
       </c>
-      <c r="O9">
-        <v>61</v>
-      </c>
       <c r="P9">
-        <v>3550.6</v>
+        <v>3577.44</v>
       </c>
       <c r="Q9">
-        <v>3555.24</v>
+        <v>3560.04</v>
       </c>
       <c r="R9">
-        <v>3575.31</v>
+        <v>3576.18</v>
       </c>
       <c r="S9">
-        <v>3670.12</v>
+        <v>3670.45</v>
       </c>
       <c r="T9">
-        <v>1.86</v>
+        <v>0.04</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1799,43 +1808,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>66.2</v>
+        <v>58.95</v>
       </c>
       <c r="Z9">
-        <v>-5</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>-13.83</v>
+        <v>-10.16</v>
       </c>
       <c r="AB9">
-        <v>8.83</v>
+        <v>14.66</v>
       </c>
       <c r="AC9">
-        <v>33.33</v>
+        <v>59.93</v>
       </c>
       <c r="AD9">
-        <v>19.88</v>
+        <v>34.01</v>
       </c>
       <c r="AE9">
-        <v>94.61</v>
+        <v>105.31</v>
       </c>
       <c r="AF9">
-        <v>18044.82</v>
+        <v>268.21</v>
       </c>
       <c r="AG9">
-        <v>3666.86</v>
+        <v>3683.09</v>
       </c>
       <c r="AH9">
-        <v>3443.62</v>
+        <v>3436.99</v>
       </c>
       <c r="AI9">
-        <v>3419.66</v>
+        <v>3421.87</v>
       </c>
       <c r="AJ9" t="s">
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>23.96</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1846,10 +1855,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1471</v>
+        <v>1543.5</v>
       </c>
       <c r="D10">
-        <v>-2.85</v>
+        <v>4.93</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1858,46 +1867,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-16.82</v>
+        <v>-12.72</v>
       </c>
       <c r="H10">
-        <v>10.92</v>
+        <v>16.39</v>
       </c>
       <c r="I10">
-        <v>-4.23</v>
+        <v>2.59</v>
       </c>
       <c r="J10">
-        <v>-2.45</v>
+        <v>1.16</v>
       </c>
       <c r="K10">
-        <v>-2.23</v>
+        <v>3.99</v>
       </c>
       <c r="L10">
-        <v>3.3</v>
+        <v>6.96</v>
       </c>
       <c r="M10">
-        <v>4.43</v>
+        <v>5.02</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P10">
-        <v>1495.38</v>
+        <v>1503.18</v>
       </c>
       <c r="Q10">
-        <v>1532.68</v>
+        <v>1532.8</v>
       </c>
       <c r="R10">
-        <v>1577.78</v>
+        <v>1575.62</v>
       </c>
       <c r="S10">
-        <v>1514.92</v>
+        <v>1514.47</v>
       </c>
       <c r="T10">
-        <v>-2.9</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,37 +1918,37 @@
         <v>47</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>35.29</v>
+        <v>51.14</v>
       </c>
       <c r="Z10">
-        <v>-21.54</v>
+        <v>-17.61</v>
       </c>
       <c r="AA10">
-        <v>-17.23</v>
+        <v>-17.31</v>
       </c>
       <c r="AB10">
-        <v>-4.31</v>
+        <v>-0.3</v>
       </c>
       <c r="AC10">
-        <v>25.97</v>
+        <v>54.48</v>
       </c>
       <c r="AD10">
-        <v>19.63</v>
+        <v>35.48</v>
       </c>
       <c r="AE10">
-        <v>41.42</v>
+        <v>43.64</v>
       </c>
       <c r="AF10">
-        <v>119.73</v>
+        <v>56.94</v>
       </c>
       <c r="AG10">
-        <v>1587.03</v>
+        <v>1587.24</v>
       </c>
       <c r="AH10">
-        <v>1478.33</v>
+        <v>1478.37</v>
       </c>
       <c r="AI10">
         <v>1594.51</v>
@@ -1948,7 +1957,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.78</v>
+        <v>18.12</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2129,7 +2138,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2149,7 +2158,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>62</v>
@@ -2167,970 +2176,973 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.72</v>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-11.51</v>
+        <v>-0.58</v>
       </c>
       <c r="D9" s="6">
-        <v>-10.7</v>
+        <v>-0.28</v>
       </c>
       <c r="E9" s="7">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-14.67</v>
+        <v>-10.7</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.37</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="E10" s="7">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.66</v>
+        <v>-11.37</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.72</v>
+        <v>-9.32</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.05</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.08</v>
+        <v>-6.38</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.75</v>
+        <v>-2.56</v>
       </c>
       <c r="E12" s="7">
-        <v>1.33</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-9.19</v>
+        <v>-0.75</v>
       </c>
       <c r="D13" s="6">
-        <v>-10.27</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.08</v>
+        <v>2.42</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-8.6</v>
+        <v>-10.27</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="E14" s="7">
-        <v>5.22</v>
+        <v>-17.87</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-7.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.33</v>
+        <v>-3.38</v>
       </c>
       <c r="D15" s="6">
-        <v>4.01</v>
+        <v>-2.83</v>
       </c>
       <c r="E15" s="7">
-        <v>9.34</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.88</v>
+        <v>4.01</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.45</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.43</v>
+        <v>3.41</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.49</v>
+        <v>-2.45</v>
       </c>
       <c r="D17" s="6">
-        <v>0.38</v>
+        <v>1.16</v>
       </c>
       <c r="E17" s="7">
-        <v>1.87</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.23</v>
+        <v>0.38</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.56</v>
+        <v>0.46</v>
       </c>
       <c r="E18" s="7">
-        <v>0.67</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.09</v>
+        <v>-1.56</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.07</v>
+        <v>0.33</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.58</v>
+        <v>-1.16</v>
       </c>
       <c r="D20" s="6">
-        <v>-1.31</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.73</v>
+        <v>-0.61</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.85</v>
+        <v>-1.31</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.97</v>
+        <v>-0.5</v>
       </c>
       <c r="E21" s="7">
-        <v>1.88</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-11.54</v>
+        <v>-1.97</v>
       </c>
       <c r="D22" s="6">
-        <v>-11.43</v>
+        <v>-1.26</v>
       </c>
       <c r="E22" s="7">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.51</v>
+        <v>-11.43</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.39</v>
+        <v>-13.89</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.92</v>
+        <v>-1.12</v>
       </c>
       <c r="D24" s="6">
-        <v>5.84</v>
-      </c>
-      <c r="E24" s="7">
-        <v>8.76</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.23</v>
+        <v>5.84</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.23</v>
+        <v>3.79</v>
       </c>
       <c r="E25" s="8">
-        <v>-3</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-8.66</v>
+        <v>-4.23</v>
       </c>
       <c r="D26" s="6">
-        <v>-6.3</v>
+        <v>2.59</v>
       </c>
       <c r="E26" s="7">
-        <v>2.36</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>12.42</v>
+        <v>-6.3</v>
       </c>
       <c r="D27" s="6">
-        <v>14.12</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.7</v>
+        <v>-7.63</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-4.21</v>
+        <v>-19.46</v>
       </c>
       <c r="D28" s="6">
-        <v>-4.11</v>
+        <v>-16.4</v>
       </c>
       <c r="E28" s="7">
-        <v>0.1</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>14.5</v>
+        <v>14.12</v>
       </c>
       <c r="D29" s="6">
-        <v>11.01</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-3.49</v>
+        <v>17.54</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>3.4</v>
+        <v>-4.11</v>
       </c>
       <c r="D30" s="6">
-        <v>3.73</v>
+        <v>-2.65</v>
       </c>
       <c r="E30" s="7">
-        <v>0.33</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-45.88</v>
+        <v>11.01</v>
       </c>
       <c r="D31" s="6">
-        <v>-44.02</v>
+        <v>14.42</v>
       </c>
       <c r="E31" s="7">
-        <v>1.86</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-16.46</v>
+        <v>3.73</v>
       </c>
       <c r="D32" s="6">
-        <v>-9.32</v>
-      </c>
-      <c r="E32" s="7">
-        <v>7.14</v>
+        <v>1.03</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>6.3</v>
+        <v>-44.02</v>
       </c>
       <c r="D33" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-3</v>
+        <v>-43.99</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-20.15</v>
+        <v>-9.32</v>
       </c>
       <c r="D34" s="6">
-        <v>-19.16</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.99</v>
+        <v>-11.37</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6">
-        <v>-10.65</v>
+        <v>3.3</v>
       </c>
       <c r="D35" s="6">
-        <v>-10.99</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.34</v>
+        <v>6.96</v>
+      </c>
+      <c r="E35" s="7">
+        <v>3.66</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.28</v>
+        <v>-19.16</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.1</v>
+        <v>-16.97</v>
       </c>
       <c r="E36" s="7">
-        <v>3.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-7.86</v>
+        <v>-10.99</v>
       </c>
       <c r="D37" s="6">
-        <v>-8.48</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.62</v>
+        <v>-7.4</v>
+      </c>
+      <c r="E37" s="7">
+        <v>3.59</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>3.4</v>
+        <v>-3.1</v>
       </c>
       <c r="D38" s="6">
-        <v>4.18</v>
+        <v>0.2</v>
       </c>
       <c r="E38" s="7">
-        <v>0.78</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>3.29</v>
+        <v>-8.48</v>
       </c>
       <c r="D39" s="6">
-        <v>2.52</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.77</v>
+        <v>-5.89</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.59</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-19.55</v>
+        <v>4.18</v>
       </c>
       <c r="D40" s="6">
-        <v>-16.86</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.69</v>
+        <v>4.09</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-9</v>
+        <v>2.52</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.35</v>
-      </c>
-      <c r="E41" s="7">
-        <v>7.65</v>
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>4.08</v>
+        <v>-16.86</v>
       </c>
       <c r="D42" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-6.31</v>
+        <v>-15.27</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-24.37</v>
+        <v>-1.35</v>
       </c>
       <c r="D43" s="6">
-        <v>-22.59</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.78</v>
+        <v>-2.26</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="6">
-        <v>-26.46</v>
+        <v>-2.23</v>
       </c>
       <c r="D44" s="6">
-        <v>-26.02</v>
+        <v>3.99</v>
       </c>
       <c r="E44" s="7">
-        <v>0.44</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-22.52</v>
+        <v>-22.59</v>
       </c>
       <c r="D45" s="6">
-        <v>-21.8</v>
+        <v>-22.33</v>
       </c>
       <c r="E45" s="7">
-        <v>0.72</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-17.22</v>
+        <v>-26.02</v>
       </c>
       <c r="D46" s="6">
-        <v>-17.83</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.61</v>
+        <v>-24.67</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-9.57</v>
+        <v>-21.8</v>
       </c>
       <c r="D47" s="6">
-        <v>-9.93</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.36</v>
+        <v>-20.99</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-16.21</v>
+        <v>-17.83</v>
       </c>
       <c r="D48" s="6">
-        <v>-17.75</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.54</v>
+        <v>-16.9</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-45.36</v>
+        <v>-9.93</v>
       </c>
       <c r="D49" s="6">
-        <v>-44.01</v>
+        <v>-7.43</v>
       </c>
       <c r="E49" s="7">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-21.14</v>
+        <v>-17.75</v>
       </c>
       <c r="D50" s="6">
-        <v>-14.28</v>
-      </c>
-      <c r="E50" s="7">
-        <v>6.86</v>
+        <v>-19.96</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-14.38</v>
+        <v>-44.01</v>
       </c>
       <c r="D51" s="6">
-        <v>-16.82</v>
+        <v>-44.48</v>
       </c>
       <c r="E51" s="8">
-        <v>-2.44</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>370.75</v>
+        <v>-14.28</v>
       </c>
       <c r="D52" s="6">
-        <v>379.45</v>
-      </c>
-      <c r="E52" s="7">
-        <v>8.699999999999999</v>
+        <v>-15.8</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6">
-        <v>2796.2</v>
+        <v>-16.82</v>
       </c>
       <c r="D53" s="6">
-        <v>2813</v>
+        <v>-12.72</v>
       </c>
       <c r="E53" s="7">
-        <v>16.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>319.45</v>
+        <v>379.45</v>
       </c>
       <c r="D54" s="6">
-        <v>322.4</v>
+        <v>380.75</v>
       </c>
       <c r="E54" s="7">
-        <v>2.95</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>349.1</v>
+        <v>2813</v>
       </c>
       <c r="D55" s="6">
-        <v>346.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-2.6</v>
+        <v>2864.4</v>
+      </c>
+      <c r="E55" s="7">
+        <v>51.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>400.35</v>
+        <v>322.4</v>
       </c>
       <c r="D56" s="6">
-        <v>398.75</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.6</v>
+        <v>325.75</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.35</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>618.1</v>
+        <v>346.5</v>
       </c>
       <c r="D57" s="6">
-        <v>606.75</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-11.35</v>
+        <v>350.45</v>
+      </c>
+      <c r="E57" s="7">
+        <v>3.95</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>188.02</v>
+        <v>398.75</v>
       </c>
       <c r="D58" s="6">
-        <v>192.63</v>
+        <v>409.8</v>
       </c>
       <c r="E58" s="7">
-        <v>4.61</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3439.1</v>
+        <v>606.75</v>
       </c>
       <c r="D59" s="6">
-        <v>3738.4</v>
-      </c>
-      <c r="E59" s="7">
-        <v>299.3</v>
+        <v>590.45</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-16.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1514.1</v>
+        <v>192.63</v>
       </c>
       <c r="D60" s="6">
-        <v>1471</v>
+        <v>191.01</v>
       </c>
       <c r="E60" s="8">
-        <v>-43.1</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>66</v>
+        <v>3738.4</v>
       </c>
       <c r="D61" s="6">
-        <v>88</v>
-      </c>
-      <c r="E61" s="7">
-        <v>22</v>
+        <v>3672</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-66.40000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="6">
-        <v>55</v>
+        <v>1471</v>
       </c>
       <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-10</v>
+        <v>1543.5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>72.5</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
@@ -3147,331 +3159,365 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D64" s="6">
         <v>66</v>
       </c>
       <c r="E64" s="8">
-        <v>-22</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="6">
-        <v>36.59</v>
+        <v>55</v>
       </c>
       <c r="D65" s="6">
-        <v>45.55</v>
-      </c>
-      <c r="E65" s="7">
-        <v>8.960000000000001</v>
+        <v>45</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="6">
-        <v>25.76</v>
+        <v>66</v>
       </c>
       <c r="D66" s="6">
-        <v>28.52</v>
+        <v>77</v>
       </c>
       <c r="E66" s="7">
-        <v>2.76</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>34.51</v>
+        <v>45.55</v>
       </c>
       <c r="D67" s="6">
-        <v>37.12</v>
+        <v>46.76</v>
       </c>
       <c r="E67" s="7">
-        <v>2.61</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>42.18</v>
+        <v>28.52</v>
       </c>
       <c r="D68" s="6">
-        <v>40.32</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.86</v>
+        <v>36.33</v>
+      </c>
+      <c r="E68" s="7">
+        <v>7.81</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>46.09</v>
+        <v>37.12</v>
       </c>
       <c r="D69" s="6">
-        <v>45.24</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.85</v>
+        <v>40.03</v>
+      </c>
+      <c r="E69" s="7">
+        <v>2.91</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>33.85</v>
+        <v>40.32</v>
       </c>
       <c r="D70" s="6">
-        <v>31.98</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.87</v>
+        <v>44.33</v>
+      </c>
+      <c r="E70" s="7">
+        <v>4.01</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>29.46</v>
+        <v>45.24</v>
       </c>
       <c r="D71" s="6">
-        <v>39.47</v>
+        <v>51.84</v>
       </c>
       <c r="E71" s="7">
-        <v>10.01</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>30.35</v>
+        <v>31.98</v>
       </c>
       <c r="D72" s="6">
-        <v>66.2</v>
-      </c>
-      <c r="E72" s="7">
-        <v>35.85</v>
+        <v>29.46</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>42.98</v>
+        <v>39.47</v>
       </c>
       <c r="D73" s="6">
-        <v>35.29</v>
+        <v>37.46</v>
       </c>
       <c r="E73" s="8">
-        <v>-7.69</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="6">
-        <v>-47.63</v>
+        <v>66.2</v>
       </c>
       <c r="D74" s="6">
-        <v>-40.73</v>
-      </c>
-      <c r="E74" s="7">
-        <v>6.9</v>
+        <v>58.95</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-7.25</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C75" s="6">
-        <v>-48.6</v>
+        <v>35.29</v>
       </c>
       <c r="D75" s="6">
-        <v>-20.21</v>
+        <v>51.14</v>
       </c>
       <c r="E75" s="7">
-        <v>28.39</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-25.63</v>
+        <v>-40.73</v>
       </c>
       <c r="D76" s="6">
-        <v>-50.44</v>
+        <v>-49.42</v>
       </c>
       <c r="E76" s="8">
-        <v>-24.81</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>364.92</v>
+        <v>-20.21</v>
       </c>
       <c r="D77" s="6">
-        <v>-55.06</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-419.98</v>
+        <v>9.619999999999999</v>
+      </c>
+      <c r="E77" s="7">
+        <v>29.83</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-39.8</v>
+        <v>-50.44</v>
       </c>
       <c r="D78" s="6">
-        <v>-51.68</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-11.88</v>
+        <v>3.16</v>
+      </c>
+      <c r="E78" s="7">
+        <v>53.6</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-7.11</v>
+        <v>-55.06</v>
       </c>
       <c r="D79" s="6">
-        <v>-44.63</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-37.52</v>
+        <v>-48.44</v>
+      </c>
+      <c r="E79" s="7">
+        <v>6.62</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>16.82</v>
+        <v>-51.68</v>
       </c>
       <c r="D80" s="6">
-        <v>21.71</v>
+        <v>-40.87</v>
       </c>
       <c r="E80" s="7">
-        <v>4.89</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>1.8</v>
+        <v>-44.63</v>
       </c>
       <c r="D81" s="6">
-        <v>18044.82</v>
+        <v>-15.9</v>
       </c>
       <c r="E81" s="7">
-        <v>18043.02</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C82" s="6">
-        <v>5.53</v>
+        <v>21.71</v>
       </c>
       <c r="D82" s="6">
+        <v>-47.37</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-69.08</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="6">
+        <v>18044.82</v>
+      </c>
+      <c r="D83" s="6">
+        <v>268.21</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-17776.61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="6">
         <v>119.73</v>
       </c>
-      <c r="E82" s="7">
-        <v>114.2</v>
+      <c r="D84" s="6">
+        <v>56.94</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-62.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3495,28 +3541,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3530,16 +3576,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>41.1</v>
+        <v>44</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.7</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.2</v>
+        <v>-4.4</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3676,31 +3722,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.2679</v>
+        <v>0.2599</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2408</v>
+        <v>0.221</v>
       </c>
       <c r="C2" s="14">
-        <v>0.207</v>
+        <v>0.193</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1338</v>
+        <v>0.1367</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1041</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0488</v>
+        <v>0.0506</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0443</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.04389999999999999</v>
+        <v>-0.0455</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1188</v>
+        <v>-0.1106</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,37 +196,28 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>28.5 → 36.3</t>
+    <t>29.5 → 34.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>36.3</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>34.6</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.2 → 51.8</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>35.3 → 51.1</t>
-  </si>
-  <si>
-    <t>35.3</t>
-  </si>
-  <si>
-    <t>51.1</t>
+    <t>37.5 → 52.9</t>
+  </si>
+  <si>
+    <t>37.5</t>
+  </si>
+  <si>
+    <t>52.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -811,7 +802,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -951,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>380.75</v>
+        <v>380.45</v>
       </c>
       <c r="D2">
-        <v>0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -963,46 +955,46 @@
         <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-22.33</v>
+        <v>-22.39</v>
       </c>
       <c r="H2">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="I2">
         <v>0.46</v>
       </c>
       <c r="J2">
-        <v>-0.28</v>
+        <v>0.21</v>
       </c>
       <c r="K2">
-        <v>-16.97</v>
+        <v>-17.49</v>
       </c>
       <c r="L2">
-        <v>-7.63</v>
+        <v>-7.14</v>
       </c>
       <c r="M2">
-        <v>9.859999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P2">
-        <v>376.26</v>
+        <v>376.61</v>
       </c>
       <c r="Q2">
-        <v>381.71</v>
+        <v>381.98</v>
       </c>
       <c r="R2">
-        <v>392.05</v>
+        <v>391.27</v>
       </c>
       <c r="S2">
-        <v>433.52</v>
+        <v>433.47</v>
       </c>
       <c r="T2">
-        <v>-12.17</v>
+        <v>-12.23</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1017,34 +1009,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.76</v>
+        <v>46.51</v>
       </c>
       <c r="Z2">
-        <v>-4.67</v>
+        <v>-4.22</v>
       </c>
       <c r="AA2">
-        <v>-5.19</v>
+        <v>-4.99</v>
       </c>
       <c r="AB2">
-        <v>0.52</v>
+        <v>0.78</v>
       </c>
       <c r="AC2">
-        <v>53.86</v>
+        <v>81.78</v>
       </c>
       <c r="AD2">
-        <v>30.98</v>
+        <v>53.96</v>
       </c>
       <c r="AE2">
-        <v>9.08</v>
+        <v>8.75</v>
       </c>
       <c r="AF2">
-        <v>-49.42</v>
+        <v>-6.33</v>
       </c>
       <c r="AG2">
-        <v>395.19</v>
+        <v>395.11</v>
       </c>
       <c r="AH2">
-        <v>368.22</v>
+        <v>368.85</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1053,7 +1045,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2864.4</v>
+        <v>2793.7</v>
       </c>
       <c r="D3">
-        <v>1.83</v>
+        <v>-2.47</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1076,46 +1068,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-24.67</v>
+        <v>-26.53</v>
       </c>
       <c r="H3">
-        <v>4.11</v>
+        <v>1.54</v>
       </c>
       <c r="I3">
-        <v>0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="J3">
-        <v>-8.300000000000001</v>
+        <v>-10.08</v>
       </c>
       <c r="K3">
-        <v>-7.4</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L3">
-        <v>-16.4</v>
+        <v>-18.86</v>
       </c>
       <c r="M3">
-        <v>25.99</v>
+        <v>25.47</v>
       </c>
       <c r="N3">
         <v>23</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="P3">
-        <v>2804.96</v>
+        <v>2803.7</v>
       </c>
       <c r="Q3">
-        <v>2943.53</v>
+        <v>2931.74</v>
       </c>
       <c r="R3">
-        <v>3181.36</v>
+        <v>3168.66</v>
       </c>
       <c r="S3">
-        <v>3247.89</v>
+        <v>3243.68</v>
       </c>
       <c r="T3">
-        <v>-11.81</v>
+        <v>-13.87</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1130,34 +1122,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.33</v>
+        <v>31.27</v>
       </c>
       <c r="Z3">
-        <v>-101.45</v>
+        <v>-100.54</v>
       </c>
       <c r="AA3">
-        <v>-98.69</v>
+        <v>-99.06</v>
       </c>
       <c r="AB3">
-        <v>-2.76</v>
+        <v>-1.48</v>
       </c>
       <c r="AC3">
-        <v>69.72</v>
+        <v>78.44</v>
       </c>
       <c r="AD3">
-        <v>40.53</v>
+        <v>61.51</v>
       </c>
       <c r="AE3">
-        <v>63.23</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="AF3">
-        <v>9.619999999999999</v>
+        <v>19.92</v>
       </c>
       <c r="AG3">
-        <v>3159.38</v>
+        <v>3153.5</v>
       </c>
       <c r="AH3">
-        <v>2727.69</v>
+        <v>2709.99</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1166,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>77.23999999999999</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>325.75</v>
+        <v>319.45</v>
       </c>
       <c r="D4">
-        <v>1.04</v>
+        <v>-1.93</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1189,46 +1181,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-20.99</v>
+        <v>-22.52</v>
       </c>
       <c r="H4">
-        <v>18.15</v>
+        <v>15.87</v>
       </c>
       <c r="I4">
-        <v>-0.61</v>
+        <v>-0.71</v>
       </c>
       <c r="J4">
-        <v>-9.32</v>
+        <v>-10.3</v>
       </c>
       <c r="K4">
-        <v>0.2</v>
+        <v>-1.69</v>
       </c>
       <c r="L4">
-        <v>17.54</v>
+        <v>13.54</v>
       </c>
       <c r="M4">
-        <v>13.67</v>
+        <v>13.33</v>
       </c>
       <c r="N4">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>319.97</v>
+        <v>319.51</v>
       </c>
       <c r="Q4">
-        <v>333.66</v>
+        <v>332.52</v>
       </c>
       <c r="R4">
-        <v>363.65</v>
+        <v>361.93</v>
       </c>
       <c r="S4">
-        <v>342.03</v>
+        <v>341.68</v>
       </c>
       <c r="T4">
-        <v>-4.76</v>
+        <v>-6.51</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1243,34 +1235,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>40.03</v>
+        <v>36.59</v>
       </c>
       <c r="Z4">
-        <v>-11.6</v>
+        <v>-11.33</v>
       </c>
       <c r="AA4">
-        <v>-11.69</v>
+        <v>-11.62</v>
       </c>
       <c r="AB4">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="AC4">
-        <v>77.86</v>
+        <v>84.95</v>
       </c>
       <c r="AD4">
-        <v>51.92</v>
+        <v>69.72</v>
       </c>
       <c r="AE4">
-        <v>10.87</v>
+        <v>10.7</v>
       </c>
       <c r="AF4">
-        <v>3.16</v>
+        <v>-43.48</v>
       </c>
       <c r="AG4">
-        <v>359.85</v>
+        <v>359.11</v>
       </c>
       <c r="AH4">
-        <v>307.47</v>
+        <v>305.93</v>
       </c>
       <c r="AI4">
         <v>348.44</v>
@@ -1279,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>31.32</v>
+        <v>29.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>350.45</v>
+        <v>347.25</v>
       </c>
       <c r="D5">
-        <v>1.14</v>
+        <v>-0.91</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1302,46 +1294,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.9</v>
+        <v>-17.65</v>
       </c>
       <c r="H5">
-        <v>19.1</v>
+        <v>18.01</v>
       </c>
       <c r="I5">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="J5">
-        <v>-2.56</v>
+        <v>-1.64</v>
       </c>
       <c r="K5">
-        <v>-5.89</v>
+        <v>-6.57</v>
       </c>
       <c r="L5">
         <v>-2.65</v>
       </c>
       <c r="M5">
-        <v>5.06</v>
+        <v>5.27</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>347.85</v>
+        <v>347.08</v>
       </c>
       <c r="Q5">
-        <v>354.37</v>
+        <v>354.43</v>
       </c>
       <c r="R5">
-        <v>366.81</v>
+        <v>365.79</v>
       </c>
       <c r="S5">
-        <v>357.38</v>
+        <v>357.12</v>
       </c>
       <c r="T5">
-        <v>-1.94</v>
+        <v>-2.76</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1356,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>44.33</v>
+        <v>41.88</v>
       </c>
       <c r="Z5">
-        <v>-4.67</v>
+        <v>-4.68</v>
       </c>
       <c r="AA5">
-        <v>-4.38</v>
+        <v>-4.44</v>
       </c>
       <c r="AB5">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
       <c r="AC5">
-        <v>49.81</v>
+        <v>49.15</v>
       </c>
       <c r="AD5">
-        <v>31.98</v>
+        <v>42.57</v>
       </c>
       <c r="AE5">
-        <v>12.09</v>
+        <v>11.85</v>
       </c>
       <c r="AF5">
-        <v>-48.44</v>
+        <v>-54.51</v>
       </c>
       <c r="AG5">
-        <v>368.56</v>
+        <v>368.47</v>
       </c>
       <c r="AH5">
-        <v>340.17</v>
+        <v>340.39</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1392,7 +1384,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.48</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>409.8</v>
+        <v>421.5</v>
       </c>
       <c r="D6">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1415,46 +1407,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-7.43</v>
+        <v>-4.79</v>
       </c>
       <c r="H6">
-        <v>46.59</v>
+        <v>50.78</v>
       </c>
       <c r="I6">
-        <v>-1.26</v>
+        <v>2.52</v>
       </c>
       <c r="J6">
-        <v>2.42</v>
+        <v>6.12</v>
       </c>
       <c r="K6">
-        <v>4.09</v>
+        <v>8.52</v>
       </c>
       <c r="L6">
-        <v>14.42</v>
+        <v>17.9</v>
       </c>
       <c r="M6">
-        <v>-11.06</v>
+        <v>-10.59</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>403.09</v>
+        <v>405.16</v>
       </c>
       <c r="Q6">
-        <v>407.49</v>
+        <v>409.2</v>
       </c>
       <c r="R6">
-        <v>405.1</v>
+        <v>405.2</v>
       </c>
       <c r="S6">
-        <v>378.6</v>
+        <v>379.07</v>
       </c>
       <c r="T6">
-        <v>8.24</v>
+        <v>11.19</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1469,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.84</v>
+        <v>57.66</v>
       </c>
       <c r="Z6">
-        <v>1.01</v>
+        <v>2.03</v>
       </c>
       <c r="AA6">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AB6">
-        <v>-1.67</v>
+        <v>-0.52</v>
       </c>
       <c r="AC6">
-        <v>15.29</v>
+        <v>27.81</v>
       </c>
       <c r="AD6">
-        <v>11.41</v>
+        <v>16.28</v>
       </c>
       <c r="AE6">
-        <v>14.37</v>
+        <v>14.91</v>
       </c>
       <c r="AF6">
-        <v>-40.87</v>
+        <v>8.73</v>
       </c>
       <c r="AG6">
-        <v>435.28</v>
+        <v>435.94</v>
       </c>
       <c r="AH6">
-        <v>379.7</v>
+        <v>382.46</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1505,7 +1497,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>27.69</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>590.45</v>
+        <v>605.6</v>
       </c>
       <c r="D7">
-        <v>-2.69</v>
+        <v>2.57</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1528,46 +1520,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-19.96</v>
+        <v>-17.9</v>
       </c>
       <c r="H7">
-        <v>16.59</v>
+        <v>19.58</v>
       </c>
       <c r="I7">
-        <v>-13.89</v>
+        <v>-12.58</v>
       </c>
       <c r="J7">
-        <v>-17.87</v>
+        <v>-16.92</v>
       </c>
       <c r="K7">
-        <v>0.23</v>
+        <v>2.86</v>
       </c>
       <c r="L7">
-        <v>1.03</v>
+        <v>3.81</v>
       </c>
       <c r="M7">
-        <v>22.1</v>
+        <v>21.14</v>
       </c>
       <c r="N7">
         <v>66</v>
       </c>
       <c r="O7">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P7">
-        <v>630.46</v>
+        <v>613.03</v>
       </c>
       <c r="Q7">
-        <v>687.9299999999999</v>
+        <v>683.16</v>
       </c>
       <c r="R7">
-        <v>656.62</v>
+        <v>657.26</v>
       </c>
       <c r="S7">
-        <v>602.63</v>
+        <v>602.9</v>
       </c>
       <c r="T7">
-        <v>-2.02</v>
+        <v>0.45</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1579,37 +1571,37 @@
         <v>48</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7">
-        <v>29.46</v>
+        <v>34.62</v>
       </c>
       <c r="Z7">
-        <v>-12.19</v>
+        <v>-15.41</v>
       </c>
       <c r="AA7">
-        <v>4.19</v>
+        <v>0.27</v>
       </c>
       <c r="AB7">
-        <v>-16.37</v>
+        <v>-15.68</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE7">
-        <v>29.57</v>
+        <v>29.53</v>
       </c>
       <c r="AF7">
-        <v>-15.9</v>
+        <v>-6.47</v>
       </c>
       <c r="AG7">
-        <v>769.15</v>
+        <v>771.99</v>
       </c>
       <c r="AH7">
-        <v>606.72</v>
+        <v>594.33</v>
       </c>
       <c r="AI7">
         <v>685.91</v>
@@ -1618,7 +1610,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>36.94</v>
+        <v>38.14</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>191.01</v>
+        <v>200.68</v>
       </c>
       <c r="D8">
-        <v>-0.84</v>
+        <v>5.06</v>
       </c>
       <c r="E8">
         <v>344.05</v>
@@ -1641,46 +1633,46 @@
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-44.48</v>
+        <v>-41.67</v>
       </c>
       <c r="H8">
-        <v>2.02</v>
+        <v>7.18</v>
       </c>
       <c r="I8">
-        <v>-2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
-        <v>-2.83</v>
+        <v>2.01</v>
       </c>
       <c r="K8">
-        <v>-15.27</v>
+        <v>-11.18</v>
       </c>
       <c r="L8">
-        <v>-43.99</v>
+        <v>-41.34</v>
       </c>
       <c r="M8">
-        <v>-4.55</v>
+        <v>-3.74</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P8">
-        <v>190.79</v>
+        <v>191.91</v>
       </c>
       <c r="Q8">
-        <v>195.35</v>
+        <v>195.76</v>
       </c>
       <c r="R8">
-        <v>208.28</v>
+        <v>207.92</v>
       </c>
       <c r="S8">
-        <v>245.37</v>
+        <v>244.83</v>
       </c>
       <c r="T8">
-        <v>-22.15</v>
+        <v>-18.03</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1695,34 +1687,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>37.46</v>
+        <v>52.89</v>
       </c>
       <c r="Z8">
-        <v>-4.56</v>
+        <v>-3.65</v>
       </c>
       <c r="AA8">
-        <v>-4.73</v>
+        <v>-4.51</v>
       </c>
       <c r="AB8">
-        <v>0.17</v>
+        <v>0.86</v>
       </c>
       <c r="AC8">
-        <v>56.46</v>
+        <v>85.25</v>
       </c>
       <c r="AD8">
-        <v>38.8</v>
+        <v>58.2</v>
       </c>
       <c r="AE8">
-        <v>5.67</v>
+        <v>6.13</v>
       </c>
       <c r="AF8">
-        <v>-47.37</v>
+        <v>153.41</v>
       </c>
       <c r="AG8">
-        <v>203.36</v>
+        <v>203.99</v>
       </c>
       <c r="AH8">
-        <v>187.33</v>
+        <v>187.53</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1731,7 +1723,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.79</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1742,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3672</v>
+        <v>3635.9</v>
       </c>
       <c r="D9">
-        <v>-1.78</v>
+        <v>-0.98</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1754,46 +1746,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-15.8</v>
+        <v>-16.63</v>
       </c>
       <c r="H9">
-        <v>10.97</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="I9">
-        <v>3.79</v>
+        <v>2.53</v>
       </c>
       <c r="J9">
-        <v>3.41</v>
+        <v>1.68</v>
       </c>
       <c r="K9">
-        <v>-2.26</v>
+        <v>-3.54</v>
       </c>
       <c r="L9">
-        <v>-11.37</v>
+        <v>-13.09</v>
       </c>
       <c r="M9">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P9">
-        <v>3577.44</v>
+        <v>3595.4</v>
       </c>
       <c r="Q9">
-        <v>3560.04</v>
+        <v>3563.38</v>
       </c>
       <c r="R9">
-        <v>3576.18</v>
+        <v>3576.29</v>
       </c>
       <c r="S9">
-        <v>3670.45</v>
+        <v>3670.6</v>
       </c>
       <c r="T9">
-        <v>0.04</v>
+        <v>-0.95</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1805,37 +1797,37 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>58.95</v>
+        <v>55.4</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>9.01</v>
       </c>
       <c r="AA9">
-        <v>-10.16</v>
+        <v>-6.33</v>
       </c>
       <c r="AB9">
-        <v>14.66</v>
+        <v>15.34</v>
       </c>
       <c r="AC9">
-        <v>59.93</v>
+        <v>83.22</v>
       </c>
       <c r="AD9">
-        <v>34.01</v>
+        <v>58.83</v>
       </c>
       <c r="AE9">
-        <v>105.31</v>
+        <v>104.57</v>
       </c>
       <c r="AF9">
-        <v>268.21</v>
+        <v>-69.84999999999999</v>
       </c>
       <c r="AG9">
-        <v>3683.09</v>
+        <v>3691.01</v>
       </c>
       <c r="AH9">
-        <v>3436.99</v>
+        <v>3435.74</v>
       </c>
       <c r="AI9">
         <v>3421.87</v>
@@ -1844,7 +1836,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>29.19</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1543.5</v>
+        <v>1575.2</v>
       </c>
       <c r="D10">
-        <v>4.93</v>
+        <v>2.05</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1867,46 +1859,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-12.72</v>
+        <v>-10.93</v>
       </c>
       <c r="H10">
-        <v>16.39</v>
+        <v>18.78</v>
       </c>
       <c r="I10">
-        <v>2.59</v>
+        <v>5.64</v>
       </c>
       <c r="J10">
-        <v>1.16</v>
+        <v>2.22</v>
       </c>
       <c r="K10">
-        <v>3.99</v>
+        <v>5.1</v>
       </c>
       <c r="L10">
-        <v>6.96</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M10">
         <v>5.02</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P10">
-        <v>1503.18</v>
+        <v>1520</v>
       </c>
       <c r="Q10">
-        <v>1532.8</v>
+        <v>1532.77</v>
       </c>
       <c r="R10">
-        <v>1575.62</v>
+        <v>1574.14</v>
       </c>
       <c r="S10">
-        <v>1514.47</v>
+        <v>1514.19</v>
       </c>
       <c r="T10">
-        <v>1.92</v>
+        <v>4.03</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1921,34 +1913,34 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>51.14</v>
+        <v>56.19</v>
       </c>
       <c r="Z10">
-        <v>-17.61</v>
+        <v>-11.8</v>
       </c>
       <c r="AA10">
-        <v>-17.31</v>
+        <v>-16.21</v>
       </c>
       <c r="AB10">
-        <v>-0.3</v>
+        <v>4.41</v>
       </c>
       <c r="AC10">
-        <v>54.48</v>
+        <v>66.67</v>
       </c>
       <c r="AD10">
-        <v>35.48</v>
+        <v>49.04</v>
       </c>
       <c r="AE10">
-        <v>43.64</v>
+        <v>43.63</v>
       </c>
       <c r="AF10">
-        <v>56.94</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AG10">
-        <v>1587.24</v>
+        <v>1587.09</v>
       </c>
       <c r="AH10">
-        <v>1478.37</v>
+        <v>1478.45</v>
       </c>
       <c r="AI10">
         <v>1594.51</v>
@@ -1957,7 +1949,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>18.12</v>
+        <v>18.58</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2138,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2158,7 +2150,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>62</v>
@@ -2176,1348 +2168,1260 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-0.28</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.58</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.3</v>
+        <v>-10.08</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.7</v>
+        <v>-9.32</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.4</v>
+        <v>-10.3</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-11.37</v>
+        <v>-2.56</v>
       </c>
       <c r="D11" s="6">
-        <v>-9.32</v>
+        <v>-1.64</v>
       </c>
       <c r="E11" s="7">
-        <v>2.05</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.38</v>
+        <v>2.42</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.56</v>
+        <v>6.12</v>
       </c>
       <c r="E12" s="7">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.75</v>
+        <v>-17.87</v>
       </c>
       <c r="D13" s="6">
-        <v>2.42</v>
+        <v>-16.92</v>
       </c>
       <c r="E13" s="7">
-        <v>3.17</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-10.27</v>
+        <v>-2.83</v>
       </c>
       <c r="D14" s="6">
-        <v>-17.87</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-7.6</v>
+        <v>2.01</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4.84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.38</v>
+        <v>3.41</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.55</v>
+        <v>1.68</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>4.01</v>
+        <v>1.16</v>
       </c>
       <c r="D16" s="6">
-        <v>3.41</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.6</v>
+        <v>2.22</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.45</v>
+        <v>0.33</v>
       </c>
       <c r="D17" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.61</v>
+        <v>-0.23</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>0.38</v>
+        <v>-0.61</v>
       </c>
       <c r="D18" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.08</v>
+        <v>-0.71</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.56</v>
+        <v>-0.5</v>
       </c>
       <c r="D19" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.89</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.16</v>
+        <v>-1.26</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.61</v>
+        <v>2.52</v>
       </c>
       <c r="E20" s="7">
-        <v>0.55</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.31</v>
+        <v>-13.89</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.5</v>
+        <v>-12.58</v>
       </c>
       <c r="E21" s="7">
-        <v>0.8100000000000001</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.97</v>
+        <v>-2.9</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.26</v>
+        <v>2.88</v>
       </c>
       <c r="E22" s="7">
-        <v>0.71</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-11.43</v>
+        <v>3.79</v>
       </c>
       <c r="D23" s="6">
-        <v>-13.89</v>
+        <v>2.53</v>
       </c>
       <c r="E23" s="8">
-        <v>-2.46</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.12</v>
+        <v>2.59</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.78</v>
+        <v>5.64</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>5.84</v>
+        <v>-7.63</v>
       </c>
       <c r="D25" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.05</v>
+        <v>-7.14</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.49</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-4.23</v>
+        <v>-16.4</v>
       </c>
       <c r="D26" s="6">
-        <v>2.59</v>
-      </c>
-      <c r="E26" s="7">
-        <v>6.82</v>
+        <v>-18.86</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-6.3</v>
+        <v>17.54</v>
       </c>
       <c r="D27" s="6">
-        <v>-7.63</v>
+        <v>13.54</v>
       </c>
       <c r="E27" s="8">
-        <v>-1.33</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-19.46</v>
+        <v>14.42</v>
       </c>
       <c r="D28" s="6">
-        <v>-16.4</v>
+        <v>17.9</v>
       </c>
       <c r="E28" s="7">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>14.12</v>
+        <v>1.03</v>
       </c>
       <c r="D29" s="6">
-        <v>17.54</v>
+        <v>3.81</v>
       </c>
       <c r="E29" s="7">
-        <v>3.42</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.11</v>
+        <v>-43.99</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.65</v>
+        <v>-41.34</v>
       </c>
       <c r="E30" s="7">
-        <v>1.46</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>11.01</v>
+        <v>-11.37</v>
       </c>
       <c r="D31" s="6">
-        <v>14.42</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.41</v>
+        <v>-13.09</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>3.73</v>
+        <v>6.96</v>
       </c>
       <c r="D32" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.7</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.57</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-44.02</v>
+        <v>-16.97</v>
       </c>
       <c r="D33" s="6">
-        <v>-43.99</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.03</v>
+        <v>-17.49</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-9.32</v>
+        <v>-7.4</v>
       </c>
       <c r="D34" s="6">
-        <v>-11.37</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="E34" s="8">
-        <v>-2.05</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="D35" s="6">
-        <v>6.96</v>
-      </c>
-      <c r="E35" s="7">
-        <v>3.66</v>
+        <v>-1.69</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-19.16</v>
+        <v>-5.89</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.97</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.19</v>
+        <v>-6.57</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-10.99</v>
+        <v>4.09</v>
       </c>
       <c r="D37" s="6">
-        <v>-7.4</v>
+        <v>8.52</v>
       </c>
       <c r="E37" s="7">
-        <v>3.59</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-3.1</v>
+        <v>0.23</v>
       </c>
       <c r="D38" s="6">
-        <v>0.2</v>
+        <v>2.86</v>
       </c>
       <c r="E38" s="7">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-8.48</v>
+        <v>-15.27</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.89</v>
+        <v>-11.18</v>
       </c>
       <c r="E39" s="7">
-        <v>2.59</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>4.18</v>
+        <v>-2.26</v>
       </c>
       <c r="D40" s="6">
-        <v>4.09</v>
+        <v>-3.54</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.09</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>2.52</v>
+        <v>3.99</v>
       </c>
       <c r="D41" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.29</v>
+        <v>5.1</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.11</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-16.86</v>
+        <v>-22.33</v>
       </c>
       <c r="D42" s="6">
-        <v>-15.27</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.59</v>
+        <v>-22.39</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.35</v>
+        <v>-24.67</v>
       </c>
       <c r="D43" s="6">
-        <v>-2.26</v>
+        <v>-26.53</v>
       </c>
       <c r="E43" s="8">
-        <v>-0.91</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-2.23</v>
+        <v>-20.99</v>
       </c>
       <c r="D44" s="6">
-        <v>3.99</v>
-      </c>
-      <c r="E44" s="7">
-        <v>6.22</v>
+        <v>-22.52</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-22.59</v>
+        <v>-16.9</v>
       </c>
       <c r="D45" s="6">
-        <v>-22.33</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.26</v>
+        <v>-17.65</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-26.02</v>
+        <v>-7.43</v>
       </c>
       <c r="D46" s="6">
-        <v>-24.67</v>
+        <v>-4.79</v>
       </c>
       <c r="E46" s="7">
-        <v>1.35</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-21.8</v>
+        <v>-19.96</v>
       </c>
       <c r="D47" s="6">
-        <v>-20.99</v>
+        <v>-17.9</v>
       </c>
       <c r="E47" s="7">
-        <v>0.8100000000000001</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-17.83</v>
+        <v>-44.48</v>
       </c>
       <c r="D48" s="6">
-        <v>-16.9</v>
+        <v>-41.67</v>
       </c>
       <c r="E48" s="7">
-        <v>0.93</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-9.93</v>
+        <v>-15.8</v>
       </c>
       <c r="D49" s="6">
-        <v>-7.43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.5</v>
+        <v>-16.63</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-17.75</v>
+        <v>-12.72</v>
       </c>
       <c r="D50" s="6">
-        <v>-19.96</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-2.21</v>
+        <v>-10.93</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>-44.01</v>
+        <v>380.75</v>
       </c>
       <c r="D51" s="6">
-        <v>-44.48</v>
+        <v>380.45</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.47</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-14.28</v>
+        <v>2864.4</v>
       </c>
       <c r="D52" s="6">
-        <v>-15.8</v>
+        <v>2793.7</v>
       </c>
       <c r="E52" s="8">
-        <v>-1.52</v>
+        <v>-70.7</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-16.82</v>
+        <v>325.75</v>
       </c>
       <c r="D53" s="6">
-        <v>-12.72</v>
-      </c>
-      <c r="E53" s="7">
-        <v>4.1</v>
+        <v>319.45</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-6.3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>379.45</v>
+        <v>350.45</v>
       </c>
       <c r="D54" s="6">
-        <v>380.75</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1.3</v>
+        <v>347.25</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>2813</v>
+        <v>409.8</v>
       </c>
       <c r="D55" s="6">
-        <v>2864.4</v>
+        <v>421.5</v>
       </c>
       <c r="E55" s="7">
-        <v>51.4</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>322.4</v>
+        <v>590.45</v>
       </c>
       <c r="D56" s="6">
-        <v>325.75</v>
+        <v>605.6</v>
       </c>
       <c r="E56" s="7">
-        <v>3.35</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>346.5</v>
+        <v>191.01</v>
       </c>
       <c r="D57" s="6">
-        <v>350.45</v>
+        <v>200.68</v>
       </c>
       <c r="E57" s="7">
-        <v>3.95</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>398.75</v>
+        <v>3672</v>
       </c>
       <c r="D58" s="6">
-        <v>409.8</v>
-      </c>
-      <c r="E58" s="7">
-        <v>11.05</v>
+        <v>3635.9</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-36.1</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>606.75</v>
+        <v>1543.5</v>
       </c>
       <c r="D59" s="6">
-        <v>590.45</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-16.3</v>
+        <v>1575.2</v>
+      </c>
+      <c r="E59" s="7">
+        <v>31.7</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C60" s="6">
-        <v>192.63</v>
+        <v>88</v>
       </c>
       <c r="D60" s="6">
-        <v>191.01</v>
+        <v>77</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.62</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>3738.4</v>
+        <v>77</v>
       </c>
       <c r="D61" s="6">
-        <v>3672</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-66.40000000000001</v>
+        <v>88</v>
+      </c>
+      <c r="E61" s="7">
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>1471</v>
+        <v>46.76</v>
       </c>
       <c r="D62" s="6">
-        <v>1543.5</v>
-      </c>
-      <c r="E62" s="7">
-        <v>72.5</v>
+        <v>46.51</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>45</v>
+        <v>36.33</v>
       </c>
       <c r="D63" s="6">
-        <v>55</v>
-      </c>
-      <c r="E63" s="7">
-        <v>10</v>
+        <v>31.27</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-5.06</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>77</v>
+        <v>40.03</v>
       </c>
       <c r="D64" s="6">
-        <v>66</v>
+        <v>36.59</v>
       </c>
       <c r="E64" s="8">
-        <v>-11</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>55</v>
+        <v>44.33</v>
       </c>
       <c r="D65" s="6">
-        <v>45</v>
+        <v>41.88</v>
       </c>
       <c r="E65" s="8">
-        <v>-10</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>66</v>
+        <v>51.84</v>
       </c>
       <c r="D66" s="6">
-        <v>77</v>
+        <v>57.66</v>
       </c>
       <c r="E66" s="7">
-        <v>11</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>45.55</v>
+        <v>29.46</v>
       </c>
       <c r="D67" s="6">
-        <v>46.76</v>
+        <v>34.62</v>
       </c>
       <c r="E67" s="7">
-        <v>1.21</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>28.52</v>
+        <v>37.46</v>
       </c>
       <c r="D68" s="6">
-        <v>36.33</v>
+        <v>52.89</v>
       </c>
       <c r="E68" s="7">
-        <v>7.81</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>37.12</v>
+        <v>58.95</v>
       </c>
       <c r="D69" s="6">
-        <v>40.03</v>
-      </c>
-      <c r="E69" s="7">
-        <v>2.91</v>
+        <v>55.4</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-3.55</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>40.32</v>
+        <v>51.14</v>
       </c>
       <c r="D70" s="6">
-        <v>44.33</v>
+        <v>56.19</v>
       </c>
       <c r="E70" s="7">
-        <v>4.01</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>45.24</v>
+        <v>-49.42</v>
       </c>
       <c r="D71" s="6">
-        <v>51.84</v>
+        <v>-6.33</v>
       </c>
       <c r="E71" s="7">
-        <v>6.6</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>31.98</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D72" s="6">
-        <v>29.46</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-2.52</v>
+        <v>19.92</v>
+      </c>
+      <c r="E72" s="7">
+        <v>10.3</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>39.47</v>
+        <v>3.16</v>
       </c>
       <c r="D73" s="6">
-        <v>37.46</v>
+        <v>-43.48</v>
       </c>
       <c r="E73" s="8">
-        <v>-2.01</v>
+        <v>-46.64</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>66.2</v>
+        <v>-48.44</v>
       </c>
       <c r="D74" s="6">
-        <v>58.95</v>
+        <v>-54.51</v>
       </c>
       <c r="E74" s="8">
-        <v>-7.25</v>
+        <v>-6.07</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>35.29</v>
+        <v>-40.87</v>
       </c>
       <c r="D75" s="6">
-        <v>51.14</v>
+        <v>8.73</v>
       </c>
       <c r="E75" s="7">
-        <v>15.85</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-40.73</v>
+        <v>-15.9</v>
       </c>
       <c r="D76" s="6">
-        <v>-49.42</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-8.69</v>
+        <v>-6.47</v>
+      </c>
+      <c r="E76" s="7">
+        <v>9.43</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-20.21</v>
+        <v>-47.37</v>
       </c>
       <c r="D77" s="6">
-        <v>9.619999999999999</v>
+        <v>153.41</v>
       </c>
       <c r="E77" s="7">
-        <v>29.83</v>
+        <v>200.78</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-50.44</v>
+        <v>268.21</v>
       </c>
       <c r="D78" s="6">
-        <v>3.16</v>
-      </c>
-      <c r="E78" s="7">
-        <v>53.6</v>
+        <v>-69.84999999999999</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-338.06</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-55.06</v>
+        <v>56.94</v>
       </c>
       <c r="D79" s="6">
-        <v>-48.44</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E79" s="7">
-        <v>6.62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-51.68</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-40.87</v>
-      </c>
-      <c r="E80" s="7">
-        <v>10.81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-44.63</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-15.9</v>
-      </c>
-      <c r="E81" s="7">
-        <v>28.73</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>21.71</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-47.37</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-69.08</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>18044.82</v>
-      </c>
-      <c r="D83" s="6">
-        <v>268.21</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-17776.61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="6">
-        <v>119.73</v>
-      </c>
-      <c r="D84" s="6">
-        <v>56.94</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-62.79</v>
+        <v>11.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3541,28 +3445,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3576,16 +3480,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>44</v>
+        <v>45.9</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.8</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.4</v>
+        <v>-3.7</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3722,31 +3626,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.2599</v>
+        <v>0.2547</v>
       </c>
       <c r="B2" s="14">
-        <v>0.221</v>
+        <v>0.2114</v>
       </c>
       <c r="C2" s="14">
-        <v>0.193</v>
+        <v>0.192</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1367</v>
+        <v>0.1333</v>
       </c>
       <c r="E2" s="14">
-        <v>0.09859999999999999</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0506</v>
+        <v>0.0527</v>
       </c>
       <c r="G2" s="14">
         <v>0.05019999999999999</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0455</v>
+        <v>-0.0374</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1106</v>
+        <v>-0.1059</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,31 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.5 → 34.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>34.6</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>37.5 → 52.9</t>
-  </si>
-  <si>
-    <t>37.5</t>
-  </si>
-  <si>
-    <t>52.9</t>
+    <t>55.4 → 45.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>55.4</t>
+  </si>
+  <si>
+    <t>45.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -802,15 +790,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -943,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>380.45</v>
+        <v>376.6</v>
       </c>
       <c r="D2">
-        <v>-0.08</v>
+        <v>-1.01</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -955,46 +942,46 @@
         <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-22.39</v>
+        <v>-23.17</v>
       </c>
       <c r="H2">
-        <v>2.62</v>
+        <v>1.58</v>
       </c>
       <c r="I2">
-        <v>0.46</v>
+        <v>1.33</v>
       </c>
       <c r="J2">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="K2">
-        <v>-17.49</v>
+        <v>-20.31</v>
       </c>
       <c r="L2">
-        <v>-7.14</v>
+        <v>-9.68</v>
       </c>
       <c r="M2">
-        <v>9.970000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>376.61</v>
+        <v>377.6</v>
       </c>
       <c r="Q2">
-        <v>381.98</v>
+        <v>382.02</v>
       </c>
       <c r="R2">
-        <v>391.27</v>
+        <v>390.59</v>
       </c>
       <c r="S2">
-        <v>433.47</v>
+        <v>433.42</v>
       </c>
       <c r="T2">
-        <v>-12.23</v>
+        <v>-13.11</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.51</v>
+        <v>43.22</v>
       </c>
       <c r="Z2">
-        <v>-4.22</v>
+        <v>-4.13</v>
       </c>
       <c r="AA2">
-        <v>-4.99</v>
+        <v>-4.82</v>
       </c>
       <c r="AB2">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AC2">
-        <v>81.78</v>
+        <v>75.22</v>
       </c>
       <c r="AD2">
-        <v>53.96</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AE2">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AF2">
-        <v>-6.33</v>
+        <v>7.82</v>
       </c>
       <c r="AG2">
-        <v>395.11</v>
+        <v>395.08</v>
       </c>
       <c r="AH2">
-        <v>368.85</v>
+        <v>368.96</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1045,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>27.26</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2793.7</v>
+        <v>2861.7</v>
       </c>
       <c r="D3">
-        <v>-2.47</v>
+        <v>2.43</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1068,46 +1055,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-26.53</v>
+        <v>-24.74</v>
       </c>
       <c r="H3">
-        <v>1.54</v>
+        <v>4.02</v>
       </c>
       <c r="I3">
-        <v>-0.23</v>
+        <v>4.02</v>
       </c>
       <c r="J3">
-        <v>-10.08</v>
+        <v>-5.54</v>
       </c>
       <c r="K3">
-        <v>-9.380000000000001</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L3">
-        <v>-18.86</v>
+        <v>-17.17</v>
       </c>
       <c r="M3">
-        <v>25.47</v>
+        <v>26.69</v>
       </c>
       <c r="N3">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P3">
-        <v>2803.7</v>
+        <v>2825.8</v>
       </c>
       <c r="Q3">
-        <v>2931.74</v>
+        <v>2921.33</v>
       </c>
       <c r="R3">
-        <v>3168.66</v>
+        <v>3157.23</v>
       </c>
       <c r="S3">
-        <v>3243.68</v>
+        <v>3239.87</v>
       </c>
       <c r="T3">
-        <v>-13.87</v>
+        <v>-11.67</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1122,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.27</v>
+        <v>39.93</v>
       </c>
       <c r="Z3">
-        <v>-100.54</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="AA3">
-        <v>-99.06</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="AB3">
-        <v>-1.48</v>
+        <v>4.64</v>
       </c>
       <c r="AC3">
-        <v>78.44</v>
+        <v>90.87</v>
       </c>
       <c r="AD3">
-        <v>61.51</v>
+        <v>79.67</v>
       </c>
       <c r="AE3">
-        <v>64.73999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="AF3">
-        <v>19.92</v>
+        <v>4.84</v>
       </c>
       <c r="AG3">
-        <v>3153.5</v>
+        <v>3135.17</v>
       </c>
       <c r="AH3">
-        <v>2709.99</v>
+        <v>2707.49</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1158,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>71.5</v>
+        <v>66.52</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>319.45</v>
+        <v>316.15</v>
       </c>
       <c r="D4">
-        <v>-1.93</v>
+        <v>-1.03</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1181,25 +1168,25 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-22.52</v>
+        <v>-23.32</v>
       </c>
       <c r="H4">
-        <v>15.87</v>
+        <v>14.67</v>
       </c>
       <c r="I4">
-        <v>-0.71</v>
+        <v>1.82</v>
       </c>
       <c r="J4">
-        <v>-10.3</v>
+        <v>-7.64</v>
       </c>
       <c r="K4">
-        <v>-1.69</v>
+        <v>-1.77</v>
       </c>
       <c r="L4">
-        <v>13.54</v>
+        <v>12.07</v>
       </c>
       <c r="M4">
-        <v>13.33</v>
+        <v>12.84</v>
       </c>
       <c r="N4">
         <v>77</v>
@@ -1208,19 +1195,19 @@
         <v>67</v>
       </c>
       <c r="P4">
-        <v>319.51</v>
+        <v>320.64</v>
       </c>
       <c r="Q4">
-        <v>332.52</v>
+        <v>331.08</v>
       </c>
       <c r="R4">
-        <v>361.93</v>
+        <v>360.28</v>
       </c>
       <c r="S4">
-        <v>341.68</v>
+        <v>341.29</v>
       </c>
       <c r="T4">
-        <v>-6.51</v>
+        <v>-7.37</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1235,34 +1222,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>36.59</v>
+        <v>34.9</v>
       </c>
       <c r="Z4">
-        <v>-11.33</v>
+        <v>-11.26</v>
       </c>
       <c r="AA4">
-        <v>-11.62</v>
+        <v>-11.54</v>
       </c>
       <c r="AB4">
         <v>0.29</v>
       </c>
       <c r="AC4">
-        <v>84.95</v>
+        <v>81.12</v>
       </c>
       <c r="AD4">
-        <v>69.72</v>
+        <v>81.31</v>
       </c>
       <c r="AE4">
-        <v>10.7</v>
+        <v>10.42</v>
       </c>
       <c r="AF4">
-        <v>-43.48</v>
+        <v>-38.24</v>
       </c>
       <c r="AG4">
-        <v>359.11</v>
+        <v>357.94</v>
       </c>
       <c r="AH4">
-        <v>305.93</v>
+        <v>304.21</v>
       </c>
       <c r="AI4">
         <v>348.44</v>
@@ -1271,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>29.76</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>347.25</v>
+        <v>343.2</v>
       </c>
       <c r="D5">
-        <v>-0.91</v>
+        <v>-1.17</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1294,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-17.65</v>
+        <v>-18.62</v>
       </c>
       <c r="H5">
-        <v>18.01</v>
+        <v>16.64</v>
       </c>
       <c r="I5">
-        <v>-1.1</v>
+        <v>0.32</v>
       </c>
       <c r="J5">
-        <v>-1.64</v>
+        <v>-0.78</v>
       </c>
       <c r="K5">
-        <v>-6.57</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L5">
-        <v>-2.65</v>
+        <v>-7.19</v>
       </c>
       <c r="M5">
-        <v>5.27</v>
+        <v>4.74</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P5">
-        <v>347.08</v>
+        <v>347.3</v>
       </c>
       <c r="Q5">
-        <v>354.43</v>
+        <v>354.39</v>
       </c>
       <c r="R5">
-        <v>365.79</v>
+        <v>364.71</v>
       </c>
       <c r="S5">
-        <v>357.12</v>
+        <v>356.88</v>
       </c>
       <c r="T5">
-        <v>-2.76</v>
+        <v>-3.83</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1348,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.88</v>
+        <v>38.94</v>
       </c>
       <c r="Z5">
-        <v>-4.68</v>
+        <v>-4.96</v>
       </c>
       <c r="AA5">
-        <v>-4.44</v>
+        <v>-4.54</v>
       </c>
       <c r="AB5">
-        <v>-0.24</v>
+        <v>-0.41</v>
       </c>
       <c r="AC5">
-        <v>49.15</v>
+        <v>46.14</v>
       </c>
       <c r="AD5">
-        <v>42.57</v>
+        <v>48.37</v>
       </c>
       <c r="AE5">
-        <v>11.85</v>
+        <v>11.72</v>
       </c>
       <c r="AF5">
-        <v>-54.51</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>368.47</v>
+        <v>368.58</v>
       </c>
       <c r="AH5">
-        <v>340.39</v>
+        <v>340.19</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1384,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>30.31</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>421.5</v>
+        <v>411.75</v>
       </c>
       <c r="D6">
-        <v>2.86</v>
+        <v>-2.31</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1407,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-4.79</v>
+        <v>-6.99</v>
       </c>
       <c r="H6">
-        <v>50.78</v>
+        <v>47.29</v>
       </c>
       <c r="I6">
-        <v>2.52</v>
+        <v>4.14</v>
       </c>
       <c r="J6">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="K6">
-        <v>8.52</v>
+        <v>5.94</v>
       </c>
       <c r="L6">
-        <v>17.9</v>
+        <v>17.12</v>
       </c>
       <c r="M6">
-        <v>-10.59</v>
+        <v>-10.97</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P6">
-        <v>405.16</v>
+        <v>408.43</v>
       </c>
       <c r="Q6">
-        <v>409.2</v>
+        <v>410.45</v>
       </c>
       <c r="R6">
-        <v>405.2</v>
+        <v>405.02</v>
       </c>
       <c r="S6">
-        <v>379.07</v>
+        <v>379.51</v>
       </c>
       <c r="T6">
-        <v>11.19</v>
+        <v>8.49</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1461,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>57.66</v>
+        <v>52.02</v>
       </c>
       <c r="Z6">
         <v>2.03</v>
       </c>
       <c r="AA6">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB6">
-        <v>-0.52</v>
+        <v>-0.42</v>
       </c>
       <c r="AC6">
-        <v>27.81</v>
+        <v>35.15</v>
       </c>
       <c r="AD6">
-        <v>16.28</v>
+        <v>26.08</v>
       </c>
       <c r="AE6">
-        <v>14.91</v>
+        <v>14.93</v>
       </c>
       <c r="AF6">
-        <v>8.73</v>
+        <v>7.32</v>
       </c>
       <c r="AG6">
-        <v>435.94</v>
+        <v>435.03</v>
       </c>
       <c r="AH6">
-        <v>382.46</v>
+        <v>385.87</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1497,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>27.53</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>605.6</v>
+        <v>596.75</v>
       </c>
       <c r="D7">
-        <v>2.57</v>
+        <v>-1.46</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1520,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-17.9</v>
+        <v>-19.1</v>
       </c>
       <c r="H7">
-        <v>19.58</v>
+        <v>17.83</v>
       </c>
       <c r="I7">
-        <v>-12.58</v>
+        <v>-7.37</v>
       </c>
       <c r="J7">
-        <v>-16.92</v>
+        <v>-14.88</v>
       </c>
       <c r="K7">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
       <c r="L7">
-        <v>3.81</v>
+        <v>2.17</v>
       </c>
       <c r="M7">
-        <v>21.14</v>
+        <v>19.42</v>
       </c>
       <c r="N7">
         <v>66</v>
       </c>
       <c r="O7">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P7">
-        <v>613.03</v>
+        <v>603.53</v>
       </c>
       <c r="Q7">
-        <v>683.16</v>
+        <v>678.35</v>
       </c>
       <c r="R7">
-        <v>657.26</v>
+        <v>657.61</v>
       </c>
       <c r="S7">
-        <v>602.9</v>
+        <v>603.13</v>
       </c>
       <c r="T7">
-        <v>0.45</v>
+        <v>-1.06</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1571,37 +1558,37 @@
         <v>48</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>34.62</v>
+        <v>33.1</v>
       </c>
       <c r="Z7">
-        <v>-15.41</v>
+        <v>-18.47</v>
       </c>
       <c r="AA7">
-        <v>0.27</v>
+        <v>-3.48</v>
       </c>
       <c r="AB7">
-        <v>-15.68</v>
+        <v>-14.99</v>
       </c>
       <c r="AC7">
-        <v>4.44</v>
+        <v>7.57</v>
       </c>
       <c r="AD7">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="AE7">
-        <v>29.53</v>
+        <v>29.21</v>
       </c>
       <c r="AF7">
-        <v>-6.47</v>
+        <v>-16.87</v>
       </c>
       <c r="AG7">
-        <v>771.99</v>
+        <v>775.02</v>
       </c>
       <c r="AH7">
-        <v>594.33</v>
+        <v>581.6799999999999</v>
       </c>
       <c r="AI7">
         <v>685.91</v>
@@ -1610,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>38.14</v>
+        <v>38.84</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,58 +1608,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>200.68</v>
+        <v>199.48</v>
       </c>
       <c r="D8">
-        <v>5.06</v>
+        <v>-0.6</v>
       </c>
       <c r="E8">
-        <v>344.05</v>
+        <v>339.3</v>
       </c>
       <c r="F8">
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-41.67</v>
+        <v>-41.21</v>
       </c>
       <c r="H8">
-        <v>7.18</v>
+        <v>6.54</v>
       </c>
       <c r="I8">
-        <v>2.88</v>
+        <v>6.54</v>
       </c>
       <c r="J8">
-        <v>2.01</v>
+        <v>3.68</v>
       </c>
       <c r="K8">
-        <v>-11.18</v>
+        <v>-13.27</v>
       </c>
       <c r="L8">
-        <v>-41.34</v>
+        <v>-42.02</v>
       </c>
       <c r="M8">
-        <v>-3.74</v>
+        <v>-3.98</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P8">
-        <v>191.91</v>
+        <v>194.36</v>
       </c>
       <c r="Q8">
-        <v>195.76</v>
+        <v>196.06</v>
       </c>
       <c r="R8">
-        <v>207.92</v>
+        <v>207.34</v>
       </c>
       <c r="S8">
-        <v>244.83</v>
+        <v>244.28</v>
       </c>
       <c r="T8">
-        <v>-18.03</v>
+        <v>-18.34</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>52.89</v>
+        <v>51.2</v>
       </c>
       <c r="Z8">
-        <v>-3.65</v>
+        <v>-2.99</v>
       </c>
       <c r="AA8">
-        <v>-4.51</v>
+        <v>-4.21</v>
       </c>
       <c r="AB8">
-        <v>0.86</v>
+        <v>1.22</v>
       </c>
       <c r="AC8">
-        <v>85.25</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="AD8">
-        <v>58.2</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="AE8">
-        <v>6.13</v>
+        <v>6.06</v>
       </c>
       <c r="AF8">
-        <v>153.41</v>
+        <v>-36.11</v>
       </c>
       <c r="AG8">
-        <v>203.99</v>
+        <v>204.38</v>
       </c>
       <c r="AH8">
-        <v>187.53</v>
+        <v>187.74</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1723,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.35</v>
+        <v>29.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3635.9</v>
+        <v>3520.7</v>
       </c>
       <c r="D9">
-        <v>-0.98</v>
+        <v>-3.17</v>
       </c>
       <c r="E9">
         <v>4361.1</v>
@@ -1746,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-16.63</v>
+        <v>-19.27</v>
       </c>
       <c r="H9">
-        <v>9.880000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="I9">
-        <v>2.53</v>
+        <v>0.83</v>
       </c>
       <c r="J9">
-        <v>1.68</v>
+        <v>-1.36</v>
       </c>
       <c r="K9">
-        <v>-3.54</v>
+        <v>-5.65</v>
       </c>
       <c r="L9">
-        <v>-13.09</v>
+        <v>-16.97</v>
       </c>
       <c r="M9">
-        <v>19.2</v>
+        <v>18.45</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="P9">
-        <v>3595.4</v>
+        <v>3601.22</v>
       </c>
       <c r="Q9">
-        <v>3563.38</v>
+        <v>3563.17</v>
       </c>
       <c r="R9">
-        <v>3576.29</v>
+        <v>3574.73</v>
       </c>
       <c r="S9">
-        <v>3670.6</v>
+        <v>3670.21</v>
       </c>
       <c r="T9">
-        <v>-0.95</v>
+        <v>-4.07</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>55.4</v>
+        <v>45.9</v>
       </c>
       <c r="Z9">
-        <v>9.01</v>
+        <v>3.25</v>
       </c>
       <c r="AA9">
-        <v>-6.33</v>
+        <v>-4.41</v>
       </c>
       <c r="AB9">
-        <v>15.34</v>
+        <v>7.66</v>
       </c>
       <c r="AC9">
-        <v>83.22</v>
+        <v>64.34</v>
       </c>
       <c r="AD9">
-        <v>58.83</v>
+        <v>69.16</v>
       </c>
       <c r="AE9">
-        <v>104.57</v>
+        <v>108.08</v>
       </c>
       <c r="AF9">
-        <v>-69.84999999999999</v>
+        <v>-72.95</v>
       </c>
       <c r="AG9">
-        <v>3691.01</v>
+        <v>3691.07</v>
       </c>
       <c r="AH9">
-        <v>3435.74</v>
+        <v>3435.27</v>
       </c>
       <c r="AI9">
         <v>3421.87</v>
@@ -1836,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>33.68</v>
+        <v>32.56</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1575.2</v>
+        <v>1650</v>
       </c>
       <c r="D10">
-        <v>2.05</v>
+        <v>4.75</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1859,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-10.93</v>
+        <v>-6.7</v>
       </c>
       <c r="H10">
-        <v>18.78</v>
+        <v>24.42</v>
       </c>
       <c r="I10">
-        <v>5.64</v>
+        <v>10.28</v>
       </c>
       <c r="J10">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>9.25</v>
       </c>
       <c r="L10">
-        <v>8.529999999999999</v>
+        <v>14.42</v>
       </c>
       <c r="M10">
-        <v>5.02</v>
+        <v>5.3</v>
       </c>
       <c r="N10">
         <v>88</v>
       </c>
       <c r="O10">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P10">
-        <v>1520</v>
+        <v>1550.76</v>
       </c>
       <c r="Q10">
-        <v>1532.77</v>
+        <v>1537.37</v>
       </c>
       <c r="R10">
-        <v>1574.14</v>
+        <v>1574.17</v>
       </c>
       <c r="S10">
-        <v>1514.19</v>
+        <v>1514.38</v>
       </c>
       <c r="T10">
-        <v>4.03</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1913,43 +1900,43 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>56.19</v>
+        <v>65.3</v>
       </c>
       <c r="Z10">
-        <v>-11.8</v>
+        <v>-1.15</v>
       </c>
       <c r="AA10">
-        <v>-16.21</v>
+        <v>-13.19</v>
       </c>
       <c r="AB10">
-        <v>4.41</v>
+        <v>12.05</v>
       </c>
       <c r="AC10">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="AD10">
-        <v>49.04</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="AE10">
-        <v>43.63</v>
+        <v>45.86</v>
       </c>
       <c r="AF10">
-        <v>68.68000000000001</v>
+        <v>285.92</v>
       </c>
       <c r="AG10">
-        <v>1587.09</v>
+        <v>1612.34</v>
       </c>
       <c r="AH10">
-        <v>1478.45</v>
+        <v>1462.4</v>
       </c>
       <c r="AI10">
-        <v>1594.51</v>
+        <v>1485.48</v>
       </c>
       <c r="AJ10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK10">
-        <v>18.58</v>
+        <v>22.26</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2130,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2148,203 +2135,200 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.28</v>
+        <v>-10.08</v>
       </c>
       <c r="D8" s="6">
-        <v>0.21</v>
+        <v>-5.54</v>
       </c>
       <c r="E8" s="7">
-        <v>0.49</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-8.300000000000001</v>
+        <v>-10.3</v>
       </c>
       <c r="D9" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.78</v>
+        <v>-7.64</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.32</v>
+        <v>-1.64</v>
       </c>
       <c r="D10" s="6">
-        <v>-10.3</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.98</v>
+        <v>-0.78</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.56</v>
+        <v>6.12</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.64</v>
+        <v>6.33</v>
       </c>
       <c r="E11" s="7">
-        <v>0.92</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>2.42</v>
+        <v>-16.92</v>
       </c>
       <c r="D12" s="6">
-        <v>6.12</v>
+        <v>-14.88</v>
       </c>
       <c r="E12" s="7">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-17.87</v>
+        <v>2.01</v>
       </c>
       <c r="D13" s="6">
-        <v>-16.92</v>
+        <v>3.68</v>
       </c>
       <c r="E13" s="7">
-        <v>0.95</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.83</v>
+        <v>1.68</v>
       </c>
       <c r="D14" s="6">
-        <v>2.01</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4.84</v>
+        <v>-1.36</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-3.04</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>3.41</v>
+        <v>2.22</v>
       </c>
       <c r="D15" s="6">
-        <v>1.68</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.73</v>
+        <v>4.7</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.48</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>1.16</v>
+        <v>0.46</v>
       </c>
       <c r="D16" s="6">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="E16" s="7">
-        <v>1.06</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2355,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.5600000000000001</v>
+        <v>4.02</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2372,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.61</v>
+        <v>-0.71</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.71</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.1</v>
+        <v>1.82</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.53</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2389,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.6</v>
+        <v>0.32</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2406,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.26</v>
+        <v>2.52</v>
       </c>
       <c r="D20" s="6">
-        <v>2.52</v>
+        <v>4.14</v>
       </c>
       <c r="E20" s="7">
-        <v>3.78</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2423,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-13.89</v>
+        <v>-12.58</v>
       </c>
       <c r="D21" s="6">
-        <v>-12.58</v>
+        <v>-7.37</v>
       </c>
       <c r="E21" s="7">
-        <v>1.31</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2440,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.9</v>
+        <v>2.88</v>
       </c>
       <c r="D22" s="6">
-        <v>2.88</v>
+        <v>6.54</v>
       </c>
       <c r="E22" s="7">
-        <v>5.78</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2457,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>3.79</v>
+        <v>2.53</v>
       </c>
       <c r="D23" s="6">
-        <v>2.53</v>
+        <v>0.83</v>
       </c>
       <c r="E23" s="8">
-        <v>-1.26</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2474,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>2.59</v>
+        <v>5.64</v>
       </c>
       <c r="D24" s="6">
-        <v>5.64</v>
+        <v>10.28</v>
       </c>
       <c r="E24" s="7">
-        <v>3.05</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2491,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-7.63</v>
+        <v>-7.14</v>
       </c>
       <c r="D25" s="6">
-        <v>-7.14</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.49</v>
+        <v>-9.68</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2508,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-16.4</v>
+        <v>-18.86</v>
       </c>
       <c r="D26" s="6">
-        <v>-18.86</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.46</v>
+        <v>-17.17</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.69</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2525,903 +2509,920 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>17.54</v>
+        <v>13.54</v>
       </c>
       <c r="D27" s="6">
-        <v>13.54</v>
+        <v>12.07</v>
       </c>
       <c r="E27" s="8">
-        <v>-4</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>14.42</v>
+        <v>-2.65</v>
       </c>
       <c r="D28" s="6">
-        <v>17.9</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.48</v>
+        <v>-7.19</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-4.54</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>1.03</v>
+        <v>17.9</v>
       </c>
       <c r="D29" s="6">
-        <v>3.81</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.78</v>
+        <v>17.12</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-43.99</v>
+        <v>3.81</v>
       </c>
       <c r="D30" s="6">
-        <v>-41.34</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.65</v>
+        <v>2.17</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-11.37</v>
+        <v>-41.34</v>
       </c>
       <c r="D31" s="6">
-        <v>-13.09</v>
+        <v>-42.02</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.72</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>6.96</v>
+        <v>-13.09</v>
       </c>
       <c r="D32" s="6">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.57</v>
+        <v>-16.97</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-3.88</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-16.97</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="D33" s="6">
-        <v>-17.49</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.52</v>
+        <v>14.42</v>
+      </c>
+      <c r="E33" s="7">
+        <v>5.89</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-7.4</v>
+        <v>-17.49</v>
       </c>
       <c r="D34" s="6">
-        <v>-9.380000000000001</v>
+        <v>-20.31</v>
       </c>
       <c r="E34" s="8">
-        <v>-1.98</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>0.2</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.89</v>
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.17</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-5.89</v>
+        <v>-1.69</v>
       </c>
       <c r="D36" s="6">
-        <v>-6.57</v>
+        <v>-1.77</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.68</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>4.09</v>
+        <v>-6.57</v>
       </c>
       <c r="D37" s="6">
-        <v>8.52</v>
-      </c>
-      <c r="E37" s="7">
-        <v>4.43</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>0.23</v>
+        <v>8.52</v>
       </c>
       <c r="D38" s="6">
-        <v>2.86</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.63</v>
+        <v>5.94</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-15.27</v>
+        <v>2.86</v>
       </c>
       <c r="D39" s="6">
-        <v>-11.18</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4.09</v>
+        <v>2.13</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-2.26</v>
+        <v>-11.18</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.54</v>
+        <v>-13.27</v>
       </c>
       <c r="E40" s="8">
-        <v>-1.28</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>3.99</v>
+        <v>-3.54</v>
       </c>
       <c r="D41" s="6">
-        <v>5.1</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.11</v>
+        <v>-5.65</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-22.33</v>
+        <v>5.1</v>
       </c>
       <c r="D42" s="6">
-        <v>-22.39</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.06</v>
+        <v>9.25</v>
+      </c>
+      <c r="E42" s="7">
+        <v>4.15</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-24.67</v>
+        <v>-22.39</v>
       </c>
       <c r="D43" s="6">
-        <v>-26.53</v>
+        <v>-23.17</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.86</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-20.99</v>
+        <v>-26.53</v>
       </c>
       <c r="D44" s="6">
-        <v>-22.52</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.53</v>
+        <v>-24.74</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-16.9</v>
+        <v>-22.52</v>
       </c>
       <c r="D45" s="6">
-        <v>-17.65</v>
+        <v>-23.32</v>
       </c>
       <c r="E45" s="8">
-        <v>-0.75</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-7.43</v>
+        <v>-17.65</v>
       </c>
       <c r="D46" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E46" s="7">
-        <v>2.64</v>
+        <v>-18.62</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-19.96</v>
+        <v>-4.79</v>
       </c>
       <c r="D47" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="E47" s="7">
-        <v>2.06</v>
+        <v>-6.99</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-44.48</v>
+        <v>-17.9</v>
       </c>
       <c r="D48" s="6">
-        <v>-41.67</v>
-      </c>
-      <c r="E48" s="7">
-        <v>2.81</v>
+        <v>-19.1</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-15.8</v>
+        <v>-41.67</v>
       </c>
       <c r="D49" s="6">
-        <v>-16.63</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.83</v>
+        <v>-41.21</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-12.72</v>
+        <v>-16.63</v>
       </c>
       <c r="D50" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.79</v>
+        <v>-19.27</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>380.75</v>
+        <v>-10.93</v>
       </c>
       <c r="D51" s="6">
-        <v>380.45</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.3</v>
+        <v>-6.7</v>
+      </c>
+      <c r="E51" s="7">
+        <v>4.23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>2864.4</v>
+        <v>380.45</v>
       </c>
       <c r="D52" s="6">
-        <v>2793.7</v>
+        <v>376.6</v>
       </c>
       <c r="E52" s="8">
-        <v>-70.7</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>325.75</v>
+        <v>2793.7</v>
       </c>
       <c r="D53" s="6">
-        <v>319.45</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-6.3</v>
+        <v>2861.7</v>
+      </c>
+      <c r="E53" s="7">
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>350.45</v>
+        <v>319.45</v>
       </c>
       <c r="D54" s="6">
-        <v>347.25</v>
+        <v>316.15</v>
       </c>
       <c r="E54" s="8">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>409.8</v>
+        <v>347.25</v>
       </c>
       <c r="D55" s="6">
-        <v>421.5</v>
-      </c>
-      <c r="E55" s="7">
-        <v>11.7</v>
+        <v>343.2</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-4.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>590.45</v>
+        <v>421.5</v>
       </c>
       <c r="D56" s="6">
-        <v>605.6</v>
-      </c>
-      <c r="E56" s="7">
-        <v>15.15</v>
+        <v>411.75</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-9.75</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>191.01</v>
+        <v>605.6</v>
       </c>
       <c r="D57" s="6">
-        <v>200.68</v>
-      </c>
-      <c r="E57" s="7">
-        <v>9.67</v>
+        <v>596.75</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-8.85</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>3672</v>
+        <v>200.68</v>
       </c>
       <c r="D58" s="6">
-        <v>3635.9</v>
+        <v>199.48</v>
       </c>
       <c r="E58" s="8">
-        <v>-36.1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>1543.5</v>
+        <v>3635.9</v>
       </c>
       <c r="D59" s="6">
-        <v>1575.2</v>
-      </c>
-      <c r="E59" s="7">
-        <v>31.7</v>
+        <v>3520.7</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-115.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>88</v>
+        <v>1575.2</v>
       </c>
       <c r="D60" s="6">
-        <v>77</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-11</v>
+        <v>1650</v>
+      </c>
+      <c r="E60" s="7">
+        <v>74.8</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D61" s="6">
-        <v>88</v>
-      </c>
-      <c r="E61" s="7">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>46.76</v>
+        <v>23</v>
       </c>
       <c r="D62" s="6">
-        <v>46.51</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.25</v>
+        <v>34</v>
+      </c>
+      <c r="E62" s="7">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>36.33</v>
+        <v>46.51</v>
       </c>
       <c r="D63" s="6">
-        <v>31.27</v>
+        <v>43.22</v>
       </c>
       <c r="E63" s="8">
-        <v>-5.06</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>40.03</v>
+        <v>31.27</v>
       </c>
       <c r="D64" s="6">
-        <v>36.59</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-3.44</v>
+        <v>39.93</v>
+      </c>
+      <c r="E64" s="7">
+        <v>8.66</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>44.33</v>
+        <v>36.59</v>
       </c>
       <c r="D65" s="6">
-        <v>41.88</v>
+        <v>34.9</v>
       </c>
       <c r="E65" s="8">
-        <v>-2.45</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>51.84</v>
+        <v>41.88</v>
       </c>
       <c r="D66" s="6">
-        <v>57.66</v>
-      </c>
-      <c r="E66" s="7">
-        <v>5.82</v>
+        <v>38.94</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>29.46</v>
+        <v>57.66</v>
       </c>
       <c r="D67" s="6">
-        <v>34.62</v>
-      </c>
-      <c r="E67" s="7">
-        <v>5.16</v>
+        <v>52.02</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-5.64</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>37.46</v>
+        <v>34.62</v>
       </c>
       <c r="D68" s="6">
-        <v>52.89</v>
-      </c>
-      <c r="E68" s="7">
-        <v>15.43</v>
+        <v>33.1</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>58.95</v>
+        <v>52.89</v>
       </c>
       <c r="D69" s="6">
-        <v>55.4</v>
+        <v>51.2</v>
       </c>
       <c r="E69" s="8">
-        <v>-3.55</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>51.14</v>
+        <v>55.4</v>
       </c>
       <c r="D70" s="6">
-        <v>56.19</v>
-      </c>
-      <c r="E70" s="7">
-        <v>5.05</v>
+        <v>45.9</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-9.5</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>-49.42</v>
+        <v>56.19</v>
       </c>
       <c r="D71" s="6">
-        <v>-6.33</v>
+        <v>65.3</v>
       </c>
       <c r="E71" s="7">
-        <v>43.09</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>9.619999999999999</v>
+        <v>-6.33</v>
       </c>
       <c r="D72" s="6">
-        <v>19.92</v>
+        <v>7.82</v>
       </c>
       <c r="E72" s="7">
-        <v>10.3</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>3.16</v>
+        <v>19.92</v>
       </c>
       <c r="D73" s="6">
-        <v>-43.48</v>
+        <v>4.84</v>
       </c>
       <c r="E73" s="8">
-        <v>-46.64</v>
+        <v>-15.08</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-48.44</v>
+        <v>-43.48</v>
       </c>
       <c r="D74" s="6">
-        <v>-54.51</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-6.07</v>
+        <v>-38.24</v>
+      </c>
+      <c r="E74" s="7">
+        <v>5.24</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-40.87</v>
+        <v>-54.51</v>
       </c>
       <c r="D75" s="6">
-        <v>8.73</v>
+        <v>1.45</v>
       </c>
       <c r="E75" s="7">
-        <v>49.6</v>
+        <v>55.96</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-15.9</v>
+        <v>8.73</v>
       </c>
       <c r="D76" s="6">
-        <v>-6.47</v>
-      </c>
-      <c r="E76" s="7">
-        <v>9.43</v>
+        <v>7.32</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-47.37</v>
+        <v>-6.47</v>
       </c>
       <c r="D77" s="6">
-        <v>153.41</v>
-      </c>
-      <c r="E77" s="7">
-        <v>200.78</v>
+        <v>-16.87</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-10.4</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>268.21</v>
+        <v>153.41</v>
       </c>
       <c r="D78" s="6">
-        <v>-69.84999999999999</v>
+        <v>-36.11</v>
       </c>
       <c r="E78" s="8">
-        <v>-338.06</v>
+        <v>-189.52</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>56.94</v>
+        <v>-69.84999999999999</v>
       </c>
       <c r="D79" s="6">
+        <v>-72.95</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
         <v>68.68000000000001</v>
       </c>
-      <c r="E79" s="7">
-        <v>11.74</v>
+      <c r="D80" s="6">
+        <v>285.92</v>
+      </c>
+      <c r="E80" s="7">
+        <v>217.24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3445,28 +3446,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3474,22 +3475,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>44.16</v>
+        <v>40.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>45.9</v>
+        <v>44.9</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.7</v>
+        <v>-4.5</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3612,10 +3613,10 @@
         <v>37</v>
       </c>
       <c r="F1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>43</v>
@@ -3626,31 +3627,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.2547</v>
+        <v>0.2669</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2114</v>
+        <v>0.1942</v>
       </c>
       <c r="C2" s="14">
-        <v>0.192</v>
+        <v>0.1845</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1333</v>
+        <v>0.1284</v>
       </c>
       <c r="E2" s="14">
-        <v>0.09970000000000001</v>
+        <v>0.0862</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0527</v>
+        <v>0.053</v>
       </c>
       <c r="G2" s="14">
-        <v>0.05019999999999999</v>
+        <v>0.0474</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0374</v>
+        <v>-0.0398</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1059</v>
+        <v>-0.1097</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>55.4 → 45.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.4</t>
-  </si>
-  <si>
-    <t>45.9</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-6.7% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-6.7%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>65.3 → 75.6</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>65.3</t>
+  </si>
+  <si>
+    <t>75.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,20 +306,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,13 +353,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,14 +443,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -930,10 +959,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>376.6</v>
+        <v>377.2</v>
       </c>
       <c r="D2">
-        <v>-1.01</v>
+        <v>0.16</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +971,46 @@
         <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-23.17</v>
+        <v>-23.05</v>
       </c>
       <c r="H2">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="I2">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="J2">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="K2">
-        <v>-20.31</v>
+        <v>-20.37</v>
       </c>
       <c r="L2">
-        <v>-9.68</v>
+        <v>-8.26</v>
       </c>
       <c r="M2">
-        <v>8.619999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>377.6</v>
+        <v>378.89</v>
       </c>
       <c r="Q2">
-        <v>382.02</v>
+        <v>381.59</v>
       </c>
       <c r="R2">
-        <v>390.59</v>
+        <v>389.83</v>
       </c>
       <c r="S2">
-        <v>433.42</v>
+        <v>433.4</v>
       </c>
       <c r="T2">
-        <v>-13.11</v>
+        <v>-12.97</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1025,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.22</v>
+        <v>43.89</v>
       </c>
       <c r="Z2">
-        <v>-4.13</v>
+        <v>-3.96</v>
       </c>
       <c r="AA2">
-        <v>-4.82</v>
+        <v>-4.65</v>
       </c>
       <c r="AB2">
         <v>0.6899999999999999</v>
       </c>
       <c r="AC2">
-        <v>75.22</v>
+        <v>70.5</v>
       </c>
       <c r="AD2">
-        <v>70.29000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="AE2">
-        <v>8.619999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="AF2">
-        <v>7.82</v>
+        <v>-51.88</v>
       </c>
       <c r="AG2">
-        <v>395.08</v>
+        <v>394.7</v>
       </c>
       <c r="AH2">
-        <v>368.96</v>
+        <v>368.49</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1032,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>26.13</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1072,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2861.7</v>
+        <v>2920.9</v>
       </c>
       <c r="D3">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,25 +1084,25 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-24.74</v>
+        <v>-23.18</v>
       </c>
       <c r="H3">
-        <v>4.02</v>
+        <v>6.17</v>
       </c>
       <c r="I3">
-        <v>4.02</v>
+        <v>4.46</v>
       </c>
       <c r="J3">
-        <v>-5.54</v>
+        <v>-4.86</v>
       </c>
       <c r="K3">
-        <v>-8.210000000000001</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L3">
-        <v>-17.17</v>
+        <v>-15.57</v>
       </c>
       <c r="M3">
-        <v>26.69</v>
+        <v>27.19</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1082,19 +1111,19 @@
         <v>40</v>
       </c>
       <c r="P3">
-        <v>2825.8</v>
+        <v>2850.74</v>
       </c>
       <c r="Q3">
-        <v>2921.33</v>
+        <v>2913.55</v>
       </c>
       <c r="R3">
-        <v>3157.23</v>
+        <v>3146.54</v>
       </c>
       <c r="S3">
-        <v>3239.87</v>
+        <v>3236.52</v>
       </c>
       <c r="T3">
-        <v>-11.67</v>
+        <v>-9.75</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1138,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.93</v>
+        <v>46.28</v>
       </c>
       <c r="Z3">
-        <v>-93.26000000000001</v>
+        <v>-81.77</v>
       </c>
       <c r="AA3">
-        <v>-97.90000000000001</v>
+        <v>-94.68000000000001</v>
       </c>
       <c r="AB3">
-        <v>4.64</v>
+        <v>12.91</v>
       </c>
       <c r="AC3">
         <v>90.87</v>
       </c>
       <c r="AD3">
-        <v>79.67</v>
+        <v>86.72</v>
       </c>
       <c r="AE3">
-        <v>65.44</v>
+        <v>67.73</v>
       </c>
       <c r="AF3">
-        <v>4.84</v>
+        <v>-0.57</v>
       </c>
       <c r="AG3">
-        <v>3135.17</v>
+        <v>3114.55</v>
       </c>
       <c r="AH3">
-        <v>2707.49</v>
+        <v>2712.55</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1145,7 +1174,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>66.52</v>
+        <v>58.91</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1185,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>316.15</v>
+        <v>311.55</v>
       </c>
       <c r="D4">
-        <v>-1.03</v>
+        <v>-1.46</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1197,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-23.32</v>
+        <v>-24.44</v>
       </c>
       <c r="H4">
-        <v>14.67</v>
+        <v>13</v>
       </c>
       <c r="I4">
-        <v>1.82</v>
+        <v>-2.47</v>
       </c>
       <c r="J4">
-        <v>-7.64</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K4">
-        <v>-1.77</v>
+        <v>-3.9</v>
       </c>
       <c r="L4">
-        <v>12.07</v>
+        <v>9.58</v>
       </c>
       <c r="M4">
-        <v>12.84</v>
+        <v>12.5</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P4">
-        <v>320.64</v>
+        <v>319.06</v>
       </c>
       <c r="Q4">
-        <v>331.08</v>
+        <v>329.37</v>
       </c>
       <c r="R4">
-        <v>360.28</v>
+        <v>358.54</v>
       </c>
       <c r="S4">
-        <v>341.29</v>
+        <v>340.92</v>
       </c>
       <c r="T4">
-        <v>-7.37</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,43 +1251,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>34.9</v>
+        <v>32.64</v>
       </c>
       <c r="Z4">
-        <v>-11.26</v>
+        <v>-11.44</v>
       </c>
       <c r="AA4">
-        <v>-11.54</v>
+        <v>-11.52</v>
       </c>
       <c r="AB4">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="AC4">
-        <v>81.12</v>
+        <v>64.83</v>
       </c>
       <c r="AD4">
-        <v>81.31</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="AE4">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="AF4">
-        <v>-38.24</v>
+        <v>-15.21</v>
       </c>
       <c r="AG4">
-        <v>357.94</v>
+        <v>356.66</v>
       </c>
       <c r="AH4">
-        <v>304.21</v>
+        <v>302.08</v>
       </c>
       <c r="AI4">
-        <v>348.44</v>
+        <v>344.53</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>29.35</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1298,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>343.2</v>
+        <v>350</v>
       </c>
       <c r="D5">
-        <v>-1.17</v>
+        <v>1.98</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1310,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-18.62</v>
+        <v>-17</v>
       </c>
       <c r="H5">
-        <v>16.64</v>
+        <v>18.95</v>
       </c>
       <c r="I5">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="J5">
-        <v>-0.78</v>
+        <v>1.7</v>
       </c>
       <c r="K5">
-        <v>-9.029999999999999</v>
+        <v>-6.29</v>
       </c>
       <c r="L5">
-        <v>-7.19</v>
+        <v>-6.6</v>
       </c>
       <c r="M5">
-        <v>4.74</v>
+        <v>5.15</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P5">
-        <v>347.3</v>
+        <v>347.48</v>
       </c>
       <c r="Q5">
-        <v>354.39</v>
+        <v>353.7</v>
       </c>
       <c r="R5">
-        <v>364.71</v>
+        <v>364.05</v>
       </c>
       <c r="S5">
-        <v>356.88</v>
+        <v>356.7</v>
       </c>
       <c r="T5">
-        <v>-3.83</v>
+        <v>-1.88</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1364,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.94</v>
+        <v>45.82</v>
       </c>
       <c r="Z5">
-        <v>-4.96</v>
+        <v>-4.57</v>
       </c>
       <c r="AA5">
-        <v>-4.54</v>
+        <v>-4.55</v>
       </c>
       <c r="AB5">
-        <v>-0.41</v>
+        <v>-0.02</v>
       </c>
       <c r="AC5">
-        <v>46.14</v>
+        <v>49.37</v>
       </c>
       <c r="AD5">
-        <v>48.37</v>
+        <v>48.22</v>
       </c>
       <c r="AE5">
-        <v>11.72</v>
+        <v>11.78</v>
       </c>
       <c r="AF5">
-        <v>1.45</v>
+        <v>10.11</v>
       </c>
       <c r="AG5">
-        <v>368.58</v>
+        <v>367.31</v>
       </c>
       <c r="AH5">
-        <v>340.19</v>
+        <v>340.09</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1371,7 +1400,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>30.75</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1411,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>411.75</v>
+        <v>409.45</v>
       </c>
       <c r="D6">
-        <v>-2.31</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1423,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-6.99</v>
+        <v>-7.51</v>
       </c>
       <c r="H6">
-        <v>47.29</v>
+        <v>46.47</v>
       </c>
       <c r="I6">
-        <v>4.14</v>
+        <v>2.27</v>
       </c>
       <c r="J6">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="K6">
-        <v>5.94</v>
+        <v>5.71</v>
       </c>
       <c r="L6">
-        <v>17.12</v>
+        <v>16.25</v>
       </c>
       <c r="M6">
-        <v>-10.97</v>
+        <v>-11.06</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>408.43</v>
+        <v>410.25</v>
       </c>
       <c r="Q6">
-        <v>410.45</v>
+        <v>411.44</v>
       </c>
       <c r="R6">
-        <v>405.02</v>
+        <v>404.94</v>
       </c>
       <c r="S6">
-        <v>379.51</v>
+        <v>379.96</v>
       </c>
       <c r="T6">
-        <v>8.49</v>
+        <v>7.76</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1477,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>52.02</v>
+        <v>50.76</v>
       </c>
       <c r="Z6">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AA6">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AB6">
-        <v>-0.42</v>
+        <v>-0.5</v>
       </c>
       <c r="AC6">
-        <v>35.15</v>
+        <v>33.98</v>
       </c>
       <c r="AD6">
-        <v>26.08</v>
+        <v>32.31</v>
       </c>
       <c r="AE6">
-        <v>14.93</v>
+        <v>14.36</v>
       </c>
       <c r="AF6">
-        <v>7.32</v>
+        <v>-37.06</v>
       </c>
       <c r="AG6">
-        <v>435.03</v>
+        <v>433.99</v>
       </c>
       <c r="AH6">
-        <v>385.87</v>
+        <v>388.9</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1484,7 +1513,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>27.39</v>
+        <v>26.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1524,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>596.75</v>
+        <v>585.4</v>
       </c>
       <c r="D7">
-        <v>-1.46</v>
+        <v>-1.9</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1507,46 +1536,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-19.1</v>
+        <v>-20.64</v>
       </c>
       <c r="H7">
-        <v>17.83</v>
+        <v>15.59</v>
       </c>
       <c r="I7">
-        <v>-7.37</v>
+        <v>-5.29</v>
       </c>
       <c r="J7">
-        <v>-14.88</v>
+        <v>-15.52</v>
       </c>
       <c r="K7">
-        <v>2.13</v>
+        <v>0.85</v>
       </c>
       <c r="L7">
-        <v>2.17</v>
+        <v>0.53</v>
       </c>
       <c r="M7">
-        <v>19.42</v>
+        <v>18.95</v>
       </c>
       <c r="N7">
         <v>66</v>
       </c>
       <c r="O7">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P7">
-        <v>603.53</v>
+        <v>596.99</v>
       </c>
       <c r="Q7">
-        <v>678.35</v>
+        <v>671.61</v>
       </c>
       <c r="R7">
-        <v>657.61</v>
+        <v>657.67</v>
       </c>
       <c r="S7">
-        <v>603.13</v>
+        <v>603.3</v>
       </c>
       <c r="T7">
-        <v>-1.06</v>
+        <v>-2.97</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,43 +1590,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>33.1</v>
+        <v>31.2</v>
       </c>
       <c r="Z7">
-        <v>-18.47</v>
+        <v>-21.55</v>
       </c>
       <c r="AA7">
-        <v>-3.48</v>
+        <v>-7.09</v>
       </c>
       <c r="AB7">
-        <v>-14.99</v>
+        <v>-14.46</v>
       </c>
       <c r="AC7">
-        <v>7.57</v>
+        <v>9.07</v>
       </c>
       <c r="AD7">
-        <v>4</v>
+        <v>7.02</v>
       </c>
       <c r="AE7">
-        <v>29.21</v>
+        <v>28.5</v>
       </c>
       <c r="AF7">
-        <v>-16.87</v>
+        <v>-50.09</v>
       </c>
       <c r="AG7">
-        <v>775.02</v>
+        <v>774.59</v>
       </c>
       <c r="AH7">
-        <v>581.6799999999999</v>
+        <v>568.63</v>
       </c>
       <c r="AI7">
-        <v>685.91</v>
+        <v>679.1799999999999</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>38.84</v>
+        <v>40.27</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1637,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>199.48</v>
+        <v>200.97</v>
       </c>
       <c r="D8">
-        <v>-0.6</v>
+        <v>0.75</v>
       </c>
       <c r="E8">
-        <v>339.3</v>
+        <v>338.7</v>
       </c>
       <c r="F8">
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-41.21</v>
+        <v>-40.66</v>
       </c>
       <c r="H8">
-        <v>6.54</v>
+        <v>7.34</v>
       </c>
       <c r="I8">
-        <v>6.54</v>
+        <v>6.89</v>
       </c>
       <c r="J8">
-        <v>3.68</v>
+        <v>3.86</v>
       </c>
       <c r="K8">
-        <v>-13.27</v>
+        <v>-10.42</v>
       </c>
       <c r="L8">
-        <v>-42.02</v>
+        <v>-40.77</v>
       </c>
       <c r="M8">
-        <v>-3.98</v>
+        <v>-3.83</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P8">
-        <v>194.36</v>
+        <v>196.95</v>
       </c>
       <c r="Q8">
-        <v>196.06</v>
+        <v>196.35</v>
       </c>
       <c r="R8">
-        <v>207.34</v>
+        <v>206.7</v>
       </c>
       <c r="S8">
-        <v>244.28</v>
+        <v>243.75</v>
       </c>
       <c r="T8">
-        <v>-18.34</v>
+        <v>-17.55</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1703,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="Z8">
-        <v>-2.99</v>
+        <v>-2.33</v>
       </c>
       <c r="AA8">
-        <v>-4.21</v>
+        <v>-3.83</v>
       </c>
       <c r="AB8">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AC8">
-        <v>88.01000000000001</v>
+        <v>97.78</v>
       </c>
       <c r="AD8">
-        <v>76.56999999999999</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AE8">
-        <v>6.06</v>
+        <v>5.98</v>
       </c>
       <c r="AF8">
-        <v>-36.11</v>
+        <v>-55.91</v>
       </c>
       <c r="AG8">
-        <v>204.38</v>
+        <v>204.94</v>
       </c>
       <c r="AH8">
-        <v>187.74</v>
+        <v>187.76</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1710,7 +1739,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.83</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,58 +1750,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3520.7</v>
+        <v>3514.4</v>
       </c>
       <c r="D9">
-        <v>-3.17</v>
+        <v>-0.18</v>
       </c>
       <c r="E9">
-        <v>4361.1</v>
+        <v>4359.2</v>
       </c>
       <c r="F9">
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.27</v>
+        <v>-19.38</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>6.21</v>
       </c>
       <c r="I9">
-        <v>0.83</v>
+        <v>2.19</v>
       </c>
       <c r="J9">
-        <v>-1.36</v>
+        <v>-0.3</v>
       </c>
       <c r="K9">
-        <v>-5.65</v>
+        <v>-5.25</v>
       </c>
       <c r="L9">
-        <v>-16.97</v>
+        <v>-19.41</v>
       </c>
       <c r="M9">
-        <v>18.45</v>
+        <v>18.4</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P9">
-        <v>3601.22</v>
+        <v>3616.28</v>
       </c>
       <c r="Q9">
-        <v>3563.17</v>
+        <v>3561.24</v>
       </c>
       <c r="R9">
-        <v>3574.73</v>
+        <v>3572.84</v>
       </c>
       <c r="S9">
-        <v>3670.21</v>
+        <v>3669.97</v>
       </c>
       <c r="T9">
-        <v>-4.07</v>
+        <v>-4.24</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1816,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.9</v>
+        <v>45.44</v>
       </c>
       <c r="Z9">
-        <v>3.25</v>
+        <v>-1.81</v>
       </c>
       <c r="AA9">
-        <v>-4.41</v>
+        <v>-3.89</v>
       </c>
       <c r="AB9">
-        <v>7.66</v>
+        <v>2.09</v>
       </c>
       <c r="AC9">
-        <v>64.34</v>
+        <v>51.77</v>
       </c>
       <c r="AD9">
-        <v>69.16</v>
+        <v>66.44</v>
       </c>
       <c r="AE9">
-        <v>108.08</v>
+        <v>105.43</v>
       </c>
       <c r="AF9">
-        <v>-72.95</v>
+        <v>-86.11</v>
       </c>
       <c r="AG9">
-        <v>3691.07</v>
+        <v>3690.95</v>
       </c>
       <c r="AH9">
-        <v>3435.27</v>
+        <v>3431.54</v>
       </c>
       <c r="AI9">
         <v>3421.87</v>
@@ -1823,7 +1852,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>32.56</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1863,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1650</v>
+        <v>1790</v>
       </c>
       <c r="D10">
-        <v>4.75</v>
+        <v>8.48</v>
       </c>
       <c r="E10">
-        <v>1768.4</v>
+        <v>1790</v>
       </c>
       <c r="F10">
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-6.7</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>24.42</v>
+        <v>34.97</v>
       </c>
       <c r="I10">
-        <v>10.28</v>
+        <v>18.22</v>
       </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>14.89</v>
       </c>
       <c r="K10">
-        <v>9.25</v>
+        <v>13.8</v>
       </c>
       <c r="L10">
-        <v>14.42</v>
+        <v>24.66</v>
       </c>
       <c r="M10">
-        <v>5.3</v>
+        <v>7.03</v>
       </c>
       <c r="N10">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O10">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="P10">
-        <v>1550.76</v>
+        <v>1605.94</v>
       </c>
       <c r="Q10">
-        <v>1537.37</v>
+        <v>1548.82</v>
       </c>
       <c r="R10">
-        <v>1574.17</v>
+        <v>1576.97</v>
       </c>
       <c r="S10">
-        <v>1514.38</v>
+        <v>1515.27</v>
       </c>
       <c r="T10">
-        <v>8.960000000000001</v>
+        <v>18.13</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,43 +1929,43 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>65.3</v>
+        <v>75.56</v>
       </c>
       <c r="Z10">
-        <v>-1.15</v>
+        <v>18.38</v>
       </c>
       <c r="AA10">
-        <v>-13.19</v>
+        <v>-6.88</v>
       </c>
       <c r="AB10">
-        <v>12.05</v>
+        <v>25.26</v>
       </c>
       <c r="AC10">
         <v>100</v>
       </c>
       <c r="AD10">
-        <v>73.70999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="AE10">
-        <v>45.86</v>
+        <v>53.08</v>
       </c>
       <c r="AF10">
-        <v>285.92</v>
+        <v>722.5</v>
       </c>
       <c r="AG10">
-        <v>1612.34</v>
+        <v>1684.42</v>
       </c>
       <c r="AH10">
-        <v>1462.4</v>
+        <v>1413.22</v>
       </c>
       <c r="AI10">
-        <v>1485.48</v>
+        <v>1584.31</v>
       </c>
       <c r="AJ10" t="s">
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>22.26</v>
+        <v>28.6</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2146,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1294 +2164,1314 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.21</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>0.43</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>0.37</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-5.54</v>
       </c>
-      <c r="E8" s="7">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-4.86</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-10.3</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-7.64</v>
       </c>
-      <c r="E9" s="7">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6.33</v>
+      </c>
+      <c r="D12" s="7">
+        <v>5.86</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-14.88</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-15.52</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3.68</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3.86</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="E15" s="9">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="D16" s="7">
+        <v>14.89</v>
+      </c>
+      <c r="E16" s="9">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1.33</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>4.02</v>
+      </c>
+      <c r="D18" s="7">
+        <v>4.46</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.82</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.47</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>4.14</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.27</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-7.37</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-5.29</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>6.54</v>
+      </c>
+      <c r="D23" s="7">
+        <v>6.89</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="D24" s="7">
+        <v>2.19</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>10.28</v>
+      </c>
+      <c r="D25" s="7">
+        <v>18.22</v>
+      </c>
+      <c r="E25" s="9">
+        <v>7.94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-9.68</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-8.26</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-17.17</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-15.57</v>
+      </c>
+      <c r="E27" s="9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>12.07</v>
+      </c>
+      <c r="D28" s="7">
+        <v>9.58</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-7.19</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-6.6</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>17.12</v>
+      </c>
+      <c r="D30" s="7">
+        <v>16.25</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>2.17</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="E31" s="8">
         <v>-1.64</v>
       </c>
-      <c r="D10" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-42.02</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-40.77</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-16.97</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-19.41</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>14.42</v>
+      </c>
+      <c r="D34" s="7">
+        <v>24.66</v>
+      </c>
+      <c r="E34" s="9">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-20.31</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-20.37</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-1.77</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-3.9</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-6.29</v>
+      </c>
+      <c r="E38" s="9">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>6.12</v>
-      </c>
-      <c r="D11" s="6">
-        <v>6.33</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>5.94</v>
+      </c>
+      <c r="D39" s="7">
+        <v>5.71</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-16.92</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-14.88</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>2.13</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2.01</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3.68</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-13.27</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-10.42</v>
+      </c>
+      <c r="E41" s="9">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.68</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-5.65</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-5.25</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2.22</v>
-      </c>
-      <c r="D15" s="6">
-        <v>4.7</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>9.25</v>
+      </c>
+      <c r="D43" s="7">
+        <v>13.8</v>
+      </c>
+      <c r="E43" s="9">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1.33</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-23.17</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-23.05</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="D17" s="6">
-        <v>4.02</v>
-      </c>
-      <c r="E17" s="7">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-24.74</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-23.18</v>
+      </c>
+      <c r="E45" s="9">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.71</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.82</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-23.32</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-24.44</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-18.62</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-17</v>
+      </c>
+      <c r="E47" s="9">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2.52</v>
-      </c>
-      <c r="D20" s="6">
-        <v>4.14</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-6.99</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-7.51</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-12.58</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="E21" s="7">
-        <v>5.21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-19.1</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-20.64</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="D22" s="6">
-        <v>6.54</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-41.21</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-40.66</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2.53</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0.83</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-19.27</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-19.38</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>5.64</v>
-      </c>
-      <c r="D24" s="6">
-        <v>10.28</v>
-      </c>
-      <c r="E24" s="7">
-        <v>4.64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-6.7</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>376.6</v>
+      </c>
+      <c r="D53" s="7">
+        <v>377.2</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>2861.7</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2920.9</v>
+      </c>
+      <c r="E54" s="9">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>316.15</v>
+      </c>
+      <c r="D55" s="7">
+        <v>311.55</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>343.2</v>
+      </c>
+      <c r="D56" s="7">
+        <v>350</v>
+      </c>
+      <c r="E56" s="9">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>411.75</v>
+      </c>
+      <c r="D57" s="7">
+        <v>409.45</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>596.75</v>
+      </c>
+      <c r="D58" s="7">
+        <v>585.4</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-11.35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>199.48</v>
+      </c>
+      <c r="D59" s="7">
+        <v>200.97</v>
+      </c>
+      <c r="E59" s="9">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>3520.7</v>
+      </c>
+      <c r="D60" s="7">
+        <v>3514.4</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1650</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1790</v>
+      </c>
+      <c r="E61" s="9">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>99</v>
+      </c>
+      <c r="D62" s="7">
+        <v>88</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>88</v>
+      </c>
+      <c r="D63" s="7">
+        <v>99</v>
+      </c>
+      <c r="E63" s="9">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-7.14</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-9.68</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>43.22</v>
+      </c>
+      <c r="D64" s="7">
+        <v>43.89</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-18.86</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-17.17</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>39.93</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46.28</v>
+      </c>
+      <c r="E65" s="9">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>13.54</v>
-      </c>
-      <c r="D27" s="6">
-        <v>12.07</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>34.9</v>
+      </c>
+      <c r="D66" s="7">
+        <v>32.64</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-2.65</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-7.19</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-4.54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>38.94</v>
+      </c>
+      <c r="D67" s="7">
+        <v>45.82</v>
+      </c>
+      <c r="E67" s="9">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>17.9</v>
-      </c>
-      <c r="D29" s="6">
-        <v>17.12</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>52.02</v>
+      </c>
+      <c r="D68" s="7">
+        <v>50.76</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>3.81</v>
-      </c>
-      <c r="D30" s="6">
-        <v>2.17</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>33.1</v>
+      </c>
+      <c r="D69" s="7">
+        <v>31.2</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-41.34</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-42.02</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>51.2</v>
+      </c>
+      <c r="D70" s="7">
+        <v>53.2</v>
+      </c>
+      <c r="E70" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-13.09</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-16.97</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>45.9</v>
+      </c>
+      <c r="D71" s="7">
+        <v>45.44</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="D33" s="6">
-        <v>14.42</v>
-      </c>
-      <c r="E33" s="7">
-        <v>5.89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>65.3</v>
+      </c>
+      <c r="D72" s="7">
+        <v>75.56</v>
+      </c>
+      <c r="E72" s="9">
+        <v>10.26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-17.49</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-20.31</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>7.82</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-51.88</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-59.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>4.84</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-0.57</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-5.41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-1.77</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-38.24</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-15.21</v>
+      </c>
+      <c r="E75" s="9">
+        <v>23.03</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="D76" s="7">
+        <v>10.11</v>
+      </c>
+      <c r="E76" s="9">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>8.52</v>
-      </c>
-      <c r="D38" s="6">
-        <v>5.94</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>7.32</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-37.06</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-44.38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>2.86</v>
-      </c>
-      <c r="D39" s="6">
-        <v>2.13</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-16.87</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-50.09</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-33.22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-11.18</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-13.27</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-36.11</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-55.91</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-19.8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-5.65</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-72.95</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-86.11</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-13.16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>5.1</v>
-      </c>
-      <c r="D42" s="6">
-        <v>9.25</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-22.39</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-23.17</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-26.53</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-24.74</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-22.52</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-23.32</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-17.65</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.62</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-6.99</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-19.1</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-41.67</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-41.21</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-16.63</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-19.27</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="E51" s="7">
-        <v>4.23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>380.45</v>
-      </c>
-      <c r="D52" s="6">
-        <v>376.6</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2793.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>2861.7</v>
-      </c>
-      <c r="E53" s="7">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>319.45</v>
-      </c>
-      <c r="D54" s="6">
-        <v>316.15</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>347.25</v>
-      </c>
-      <c r="D55" s="6">
-        <v>343.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>421.5</v>
-      </c>
-      <c r="D56" s="6">
-        <v>411.75</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-9.75</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>605.6</v>
-      </c>
-      <c r="D57" s="6">
-        <v>596.75</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-8.85</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>200.68</v>
-      </c>
-      <c r="D58" s="6">
-        <v>199.48</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>3635.9</v>
-      </c>
-      <c r="D59" s="6">
-        <v>3520.7</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-115.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1575.2</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1650</v>
-      </c>
-      <c r="E60" s="7">
-        <v>74.8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>34</v>
-      </c>
-      <c r="D61" s="6">
-        <v>23</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>23</v>
-      </c>
-      <c r="D62" s="6">
-        <v>34</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>46.51</v>
-      </c>
-      <c r="D63" s="6">
-        <v>43.22</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>31.27</v>
-      </c>
-      <c r="D64" s="6">
-        <v>39.93</v>
-      </c>
-      <c r="E64" s="7">
-        <v>8.66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>36.59</v>
-      </c>
-      <c r="D65" s="6">
-        <v>34.9</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>41.88</v>
-      </c>
-      <c r="D66" s="6">
-        <v>38.94</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>57.66</v>
-      </c>
-      <c r="D67" s="6">
-        <v>52.02</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-5.64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>34.62</v>
-      </c>
-      <c r="D68" s="6">
-        <v>33.1</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>52.89</v>
-      </c>
-      <c r="D69" s="6">
-        <v>51.2</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>55.4</v>
-      </c>
-      <c r="D70" s="6">
-        <v>45.9</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>56.19</v>
-      </c>
-      <c r="D71" s="6">
-        <v>65.3</v>
-      </c>
-      <c r="E71" s="7">
-        <v>9.109999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-6.33</v>
-      </c>
-      <c r="D72" s="6">
-        <v>7.82</v>
-      </c>
-      <c r="E72" s="7">
-        <v>14.15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>19.92</v>
-      </c>
-      <c r="D73" s="6">
-        <v>4.84</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-15.08</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-43.48</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-38.24</v>
-      </c>
-      <c r="E74" s="7">
-        <v>5.24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-54.51</v>
-      </c>
-      <c r="D75" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="E75" s="7">
-        <v>55.96</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>8.73</v>
-      </c>
-      <c r="D76" s="6">
-        <v>7.32</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-6.47</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-16.87</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-10.4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>153.41</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-36.11</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-189.52</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-69.84999999999999</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-72.95</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>68.68000000000001</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C81" s="7">
         <v>285.92</v>
       </c>
-      <c r="E80" s="7">
-        <v>217.24</v>
+      <c r="D81" s="7">
+        <v>722.5</v>
+      </c>
+      <c r="E81" s="9">
+        <v>436.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3442,60 +3491,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>40.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>47.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-0.4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-3.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -3597,61 +3646,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.2669</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1942</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1845</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1284</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0862</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.053</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0474</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0398</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1097</v>
+      <c r="A2" s="15">
+        <v>0.2719</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1895</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.184</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.125</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.08650000000000001</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0703</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0515</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0383</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1106</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-6.7% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-6.7%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>65.3 → 75.6</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>65.3</t>
-  </si>
-  <si>
-    <t>75.6</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.8 → 44.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>53.2 → 49.0</t>
+  </si>
+  <si>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>49.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -272,7 +266,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,27 +300,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,19 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,15 +424,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -460,7 +440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -959,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>377.2</v>
+        <v>371.4</v>
       </c>
       <c r="D2">
-        <v>0.16</v>
+        <v>-1.54</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -971,46 +951,46 @@
         <v>370.75</v>
       </c>
       <c r="G2">
-        <v>-23.05</v>
+        <v>-24.24</v>
       </c>
       <c r="H2">
-        <v>1.74</v>
+        <v>0.18</v>
       </c>
       <c r="I2">
-        <v>1.74</v>
+        <v>-2.12</v>
       </c>
       <c r="J2">
-        <v>0.37</v>
+        <v>-3.71</v>
       </c>
       <c r="K2">
-        <v>-20.37</v>
+        <v>-21.61</v>
       </c>
       <c r="L2">
-        <v>-8.26</v>
+        <v>-8.57</v>
       </c>
       <c r="M2">
-        <v>8.65</v>
+        <v>6.81</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P2">
-        <v>378.89</v>
+        <v>377.28</v>
       </c>
       <c r="Q2">
-        <v>381.59</v>
+        <v>380.81</v>
       </c>
       <c r="R2">
-        <v>389.83</v>
+        <v>389.06</v>
       </c>
       <c r="S2">
-        <v>433.4</v>
+        <v>433.33</v>
       </c>
       <c r="T2">
-        <v>-12.97</v>
+        <v>-14.29</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1025,34 +1005,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.89</v>
+        <v>39.12</v>
       </c>
       <c r="Z2">
-        <v>-3.96</v>
+        <v>-4.25</v>
       </c>
       <c r="AA2">
-        <v>-4.65</v>
+        <v>-4.57</v>
       </c>
       <c r="AB2">
-        <v>0.6899999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="AC2">
-        <v>70.5</v>
+        <v>50.87</v>
       </c>
       <c r="AD2">
-        <v>75.83</v>
+        <v>65.53</v>
       </c>
       <c r="AE2">
-        <v>8.35</v>
+        <v>8.4</v>
       </c>
       <c r="AF2">
-        <v>-51.88</v>
+        <v>-42.41</v>
       </c>
       <c r="AG2">
-        <v>394.7</v>
+        <v>394.39</v>
       </c>
       <c r="AH2">
-        <v>368.49</v>
+        <v>367.22</v>
       </c>
       <c r="AI2">
         <v>398.26</v>
@@ -1061,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>25.74</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2920.9</v>
+        <v>2907</v>
       </c>
       <c r="D3">
-        <v>2.07</v>
+        <v>-0.48</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1084,46 +1064,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-23.18</v>
+        <v>-23.55</v>
       </c>
       <c r="H3">
-        <v>6.17</v>
+        <v>5.66</v>
       </c>
       <c r="I3">
-        <v>4.46</v>
+        <v>3.34</v>
       </c>
       <c r="J3">
-        <v>-4.86</v>
+        <v>-5.51</v>
       </c>
       <c r="K3">
-        <v>-8.119999999999999</v>
+        <v>-8.17</v>
       </c>
       <c r="L3">
-        <v>-15.57</v>
+        <v>-15.98</v>
       </c>
       <c r="M3">
-        <v>27.19</v>
+        <v>26.85</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O3">
         <v>40</v>
       </c>
       <c r="P3">
-        <v>2850.74</v>
+        <v>2869.54</v>
       </c>
       <c r="Q3">
-        <v>2913.55</v>
+        <v>2906.3</v>
       </c>
       <c r="R3">
-        <v>3146.54</v>
+        <v>3136.56</v>
       </c>
       <c r="S3">
-        <v>3236.52</v>
+        <v>3232.75</v>
       </c>
       <c r="T3">
-        <v>-9.75</v>
+        <v>-10.08</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1138,34 +1118,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>46.28</v>
+        <v>45.08</v>
       </c>
       <c r="Z3">
-        <v>-81.77</v>
+        <v>-72.94</v>
       </c>
       <c r="AA3">
-        <v>-94.68000000000001</v>
+        <v>-90.33</v>
       </c>
       <c r="AB3">
-        <v>12.91</v>
+        <v>17.39</v>
       </c>
       <c r="AC3">
-        <v>90.87</v>
+        <v>98.59</v>
       </c>
       <c r="AD3">
-        <v>86.72</v>
+        <v>93.44</v>
       </c>
       <c r="AE3">
-        <v>67.73</v>
+        <v>66.67</v>
       </c>
       <c r="AF3">
-        <v>-0.57</v>
+        <v>-16.42</v>
       </c>
       <c r="AG3">
-        <v>3114.55</v>
+        <v>3096.44</v>
       </c>
       <c r="AH3">
-        <v>2712.55</v>
+        <v>2716.16</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1174,7 +1154,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>58.91</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>311.55</v>
+        <v>304.9</v>
       </c>
       <c r="D4">
-        <v>-1.46</v>
+        <v>-2.13</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1197,46 +1177,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-24.44</v>
+        <v>-26.05</v>
       </c>
       <c r="H4">
-        <v>13</v>
+        <v>10.59</v>
       </c>
       <c r="I4">
-        <v>-2.47</v>
+        <v>-5.43</v>
       </c>
       <c r="J4">
-        <v>-9.710000000000001</v>
+        <v>-11.8</v>
       </c>
       <c r="K4">
-        <v>-3.9</v>
+        <v>-5.47</v>
       </c>
       <c r="L4">
-        <v>9.58</v>
+        <v>6.07</v>
       </c>
       <c r="M4">
-        <v>12.5</v>
+        <v>11.69</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P4">
-        <v>319.06</v>
+        <v>315.56</v>
       </c>
       <c r="Q4">
-        <v>329.37</v>
+        <v>326.95</v>
       </c>
       <c r="R4">
-        <v>358.54</v>
+        <v>356.86</v>
       </c>
       <c r="S4">
-        <v>340.92</v>
+        <v>340.42</v>
       </c>
       <c r="T4">
-        <v>-8.609999999999999</v>
+        <v>-10.43</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1251,43 +1231,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>32.64</v>
+        <v>29.64</v>
       </c>
       <c r="Z4">
-        <v>-11.44</v>
+        <v>-11.98</v>
       </c>
       <c r="AA4">
-        <v>-11.52</v>
+        <v>-11.61</v>
       </c>
       <c r="AB4">
-        <v>0.09</v>
+        <v>-0.36</v>
       </c>
       <c r="AC4">
-        <v>64.83</v>
+        <v>49.51</v>
       </c>
       <c r="AD4">
-        <v>76.95999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="AE4">
-        <v>10.25</v>
+        <v>10.47</v>
       </c>
       <c r="AF4">
-        <v>-15.21</v>
+        <v>35.72</v>
       </c>
       <c r="AG4">
-        <v>356.66</v>
+        <v>353.88</v>
       </c>
       <c r="AH4">
-        <v>302.08</v>
+        <v>300.01</v>
       </c>
       <c r="AI4">
-        <v>344.53</v>
+        <v>340.02</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>30.61</v>
+        <v>33.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D5">
-        <v>1.98</v>
+        <v>-1.71</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1310,46 +1290,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-17</v>
+        <v>-18.43</v>
       </c>
       <c r="H5">
-        <v>18.95</v>
+        <v>16.91</v>
       </c>
       <c r="I5">
-        <v>0.26</v>
+        <v>-0.72</v>
       </c>
       <c r="J5">
-        <v>1.7</v>
+        <v>-5.42</v>
       </c>
       <c r="K5">
-        <v>-6.29</v>
+        <v>-7.82</v>
       </c>
       <c r="L5">
-        <v>-6.6</v>
+        <v>-6.56</v>
       </c>
       <c r="M5">
-        <v>5.15</v>
+        <v>5.39</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>347.48</v>
+        <v>346.98</v>
       </c>
       <c r="Q5">
-        <v>353.7</v>
+        <v>352.58</v>
       </c>
       <c r="R5">
-        <v>364.05</v>
+        <v>363.2</v>
       </c>
       <c r="S5">
-        <v>356.7</v>
+        <v>356.45</v>
       </c>
       <c r="T5">
-        <v>-1.88</v>
+        <v>-3.49</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1364,34 +1344,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>45.82</v>
+        <v>41.39</v>
       </c>
       <c r="Z5">
-        <v>-4.57</v>
+        <v>-4.7</v>
       </c>
       <c r="AA5">
-        <v>-4.55</v>
+        <v>-4.58</v>
       </c>
       <c r="AB5">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="AC5">
-        <v>49.37</v>
+        <v>50.12</v>
       </c>
       <c r="AD5">
-        <v>48.22</v>
+        <v>48.54</v>
       </c>
       <c r="AE5">
-        <v>11.78</v>
+        <v>11.64</v>
       </c>
       <c r="AF5">
-        <v>10.11</v>
+        <v>-25.96</v>
       </c>
       <c r="AG5">
-        <v>367.31</v>
+        <v>365.45</v>
       </c>
       <c r="AH5">
-        <v>340.09</v>
+        <v>339.71</v>
       </c>
       <c r="AI5">
         <v>379.96</v>
@@ -1400,7 +1380,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.8</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>409.45</v>
+        <v>397.5</v>
       </c>
       <c r="D6">
-        <v>-0.5600000000000001</v>
+        <v>-2.92</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1423,46 +1403,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-7.51</v>
+        <v>-10.21</v>
       </c>
       <c r="H6">
-        <v>46.47</v>
+        <v>42.19</v>
       </c>
       <c r="I6">
-        <v>2.27</v>
+        <v>-0.31</v>
       </c>
       <c r="J6">
-        <v>5.86</v>
+        <v>2.04</v>
       </c>
       <c r="K6">
-        <v>5.71</v>
+        <v>1.13</v>
       </c>
       <c r="L6">
-        <v>16.25</v>
+        <v>13.72</v>
       </c>
       <c r="M6">
-        <v>-11.06</v>
+        <v>-11.39</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>410.25</v>
+        <v>410</v>
       </c>
       <c r="Q6">
-        <v>411.44</v>
+        <v>411.68</v>
       </c>
       <c r="R6">
-        <v>404.94</v>
+        <v>404.61</v>
       </c>
       <c r="S6">
-        <v>379.96</v>
+        <v>380.36</v>
       </c>
       <c r="T6">
-        <v>7.76</v>
+        <v>4.5</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1477,34 +1457,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>50.76</v>
+        <v>44.69</v>
       </c>
       <c r="Z6">
-        <v>1.82</v>
+        <v>0.68</v>
       </c>
       <c r="AA6">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>-0.5</v>
+        <v>-1.31</v>
       </c>
       <c r="AC6">
-        <v>33.98</v>
+        <v>19.94</v>
       </c>
       <c r="AD6">
-        <v>32.31</v>
+        <v>29.69</v>
       </c>
       <c r="AE6">
         <v>14.36</v>
       </c>
       <c r="AF6">
-        <v>-37.06</v>
+        <v>-36.24</v>
       </c>
       <c r="AG6">
-        <v>433.99</v>
+        <v>433.49</v>
       </c>
       <c r="AH6">
-        <v>388.9</v>
+        <v>389.88</v>
       </c>
       <c r="AI6">
         <v>391.71</v>
@@ -1513,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>26.64</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>585.4</v>
+        <v>575.05</v>
       </c>
       <c r="D7">
-        <v>-1.9</v>
+        <v>-1.77</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1536,46 +1516,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-20.64</v>
+        <v>-22.04</v>
       </c>
       <c r="H7">
-        <v>15.59</v>
+        <v>13.55</v>
       </c>
       <c r="I7">
-        <v>-5.29</v>
+        <v>-5.22</v>
       </c>
       <c r="J7">
-        <v>-15.52</v>
+        <v>-20.15</v>
       </c>
       <c r="K7">
-        <v>0.85</v>
+        <v>-1.65</v>
       </c>
       <c r="L7">
-        <v>0.53</v>
+        <v>-0.33</v>
       </c>
       <c r="M7">
-        <v>18.95</v>
+        <v>18.65</v>
       </c>
       <c r="N7">
         <v>66</v>
       </c>
       <c r="O7">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P7">
-        <v>596.99</v>
+        <v>590.65</v>
       </c>
       <c r="Q7">
-        <v>671.61</v>
+        <v>664.48</v>
       </c>
       <c r="R7">
-        <v>657.67</v>
+        <v>657.49</v>
       </c>
       <c r="S7">
-        <v>603.3</v>
+        <v>603.4299999999999</v>
       </c>
       <c r="T7">
-        <v>-2.97</v>
+        <v>-4.7</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1590,43 +1570,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>31.2</v>
+        <v>29.54</v>
       </c>
       <c r="Z7">
-        <v>-21.55</v>
+        <v>-24.55</v>
       </c>
       <c r="AA7">
-        <v>-7.09</v>
+        <v>-10.59</v>
       </c>
       <c r="AB7">
-        <v>-14.46</v>
+        <v>-13.97</v>
       </c>
       <c r="AC7">
-        <v>9.07</v>
+        <v>4.69</v>
       </c>
       <c r="AD7">
-        <v>7.02</v>
+        <v>7.11</v>
       </c>
       <c r="AE7">
-        <v>28.5</v>
+        <v>27.65</v>
       </c>
       <c r="AF7">
-        <v>-50.09</v>
+        <v>-24.63</v>
       </c>
       <c r="AG7">
-        <v>774.59</v>
+        <v>773.61</v>
       </c>
       <c r="AH7">
-        <v>568.63</v>
+        <v>555.36</v>
       </c>
       <c r="AI7">
-        <v>679.1799999999999</v>
+        <v>662.39</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>40.27</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>200.97</v>
+        <v>198.08</v>
       </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>-1.44</v>
       </c>
       <c r="E8">
         <v>338.7</v>
@@ -1649,46 +1629,46 @@
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-40.66</v>
+        <v>-41.52</v>
       </c>
       <c r="H8">
-        <v>7.34</v>
+        <v>5.8</v>
       </c>
       <c r="I8">
-        <v>6.89</v>
+        <v>2.83</v>
       </c>
       <c r="J8">
-        <v>3.86</v>
+        <v>1.49</v>
       </c>
       <c r="K8">
-        <v>-10.42</v>
+        <v>-12.57</v>
       </c>
       <c r="L8">
-        <v>-40.77</v>
+        <v>-40.83</v>
       </c>
       <c r="M8">
-        <v>-3.83</v>
+        <v>-4.43</v>
       </c>
       <c r="N8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P8">
-        <v>196.95</v>
+        <v>198.04</v>
       </c>
       <c r="Q8">
-        <v>196.35</v>
+        <v>196.29</v>
       </c>
       <c r="R8">
-        <v>206.7</v>
+        <v>206.04</v>
       </c>
       <c r="S8">
-        <v>243.75</v>
+        <v>243.21</v>
       </c>
       <c r="T8">
-        <v>-17.55</v>
+        <v>-18.56</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1703,34 +1683,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>53.2</v>
+        <v>49.01</v>
       </c>
       <c r="Z8">
-        <v>-2.33</v>
+        <v>-2.01</v>
       </c>
       <c r="AA8">
-        <v>-3.83</v>
+        <v>-3.47</v>
       </c>
       <c r="AB8">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AC8">
-        <v>97.78</v>
+        <v>92.33</v>
       </c>
       <c r="AD8">
-        <v>90.34999999999999</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="AE8">
-        <v>5.98</v>
+        <v>5.97</v>
       </c>
       <c r="AF8">
-        <v>-55.91</v>
+        <v>-32.01</v>
       </c>
       <c r="AG8">
-        <v>204.94</v>
+        <v>204.81</v>
       </c>
       <c r="AH8">
-        <v>187.76</v>
+        <v>187.77</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1739,7 +1719,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.46</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,58 +1730,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3514.4</v>
+        <v>3545</v>
       </c>
       <c r="D9">
-        <v>-0.18</v>
+        <v>0.87</v>
       </c>
       <c r="E9">
-        <v>4359.2</v>
+        <v>4337.2</v>
       </c>
       <c r="F9">
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.38</v>
+        <v>-18.27</v>
       </c>
       <c r="H9">
-        <v>6.21</v>
+        <v>7.14</v>
       </c>
       <c r="I9">
-        <v>2.19</v>
+        <v>-5.17</v>
       </c>
       <c r="J9">
-        <v>-0.3</v>
+        <v>-0.22</v>
       </c>
       <c r="K9">
-        <v>-5.25</v>
+        <v>-3.57</v>
       </c>
       <c r="L9">
-        <v>-19.41</v>
+        <v>-18.68</v>
       </c>
       <c r="M9">
-        <v>18.4</v>
+        <v>18.91</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O9">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P9">
-        <v>3616.28</v>
+        <v>3577.6</v>
       </c>
       <c r="Q9">
-        <v>3561.24</v>
+        <v>3557.24</v>
       </c>
       <c r="R9">
-        <v>3572.84</v>
+        <v>3571.82</v>
       </c>
       <c r="S9">
-        <v>3669.97</v>
+        <v>3669.87</v>
       </c>
       <c r="T9">
-        <v>-4.24</v>
+        <v>-3.4</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1816,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.44</v>
+        <v>48.15</v>
       </c>
       <c r="Z9">
-        <v>-1.81</v>
+        <v>-3.3</v>
       </c>
       <c r="AA9">
-        <v>-3.89</v>
+        <v>-3.77</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>0.47</v>
       </c>
       <c r="AC9">
-        <v>51.77</v>
+        <v>45.03</v>
       </c>
       <c r="AD9">
-        <v>66.44</v>
+        <v>53.71</v>
       </c>
       <c r="AE9">
-        <v>105.43</v>
+        <v>103.52</v>
       </c>
       <c r="AF9">
-        <v>-86.11</v>
+        <v>-82.81</v>
       </c>
       <c r="AG9">
-        <v>3690.95</v>
+        <v>3683.54</v>
       </c>
       <c r="AH9">
-        <v>3431.54</v>
+        <v>3430.94</v>
       </c>
       <c r="AI9">
         <v>3421.87</v>
@@ -1852,7 +1832,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>31.24</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1790</v>
+        <v>1779.1</v>
       </c>
       <c r="D10">
-        <v>8.48</v>
+        <v>-0.61</v>
       </c>
       <c r="E10">
         <v>1790</v>
@@ -1875,46 +1855,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="H10">
-        <v>34.97</v>
+        <v>34.15</v>
       </c>
       <c r="I10">
-        <v>18.22</v>
+        <v>20.94</v>
       </c>
       <c r="J10">
-        <v>14.89</v>
+        <v>13.97</v>
       </c>
       <c r="K10">
-        <v>13.8</v>
+        <v>12.86</v>
       </c>
       <c r="L10">
-        <v>24.66</v>
+        <v>22.46</v>
       </c>
       <c r="M10">
-        <v>7.03</v>
+        <v>6.05</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P10">
-        <v>1605.94</v>
+        <v>1667.56</v>
       </c>
       <c r="Q10">
-        <v>1548.82</v>
+        <v>1560.92</v>
       </c>
       <c r="R10">
-        <v>1576.97</v>
+        <v>1579.91</v>
       </c>
       <c r="S10">
-        <v>1515.27</v>
+        <v>1516.14</v>
       </c>
       <c r="T10">
-        <v>18.13</v>
+        <v>17.34</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1929,48 +1909,108 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>75.56</v>
+        <v>73.73</v>
       </c>
       <c r="Z10">
-        <v>18.38</v>
+        <v>32.6</v>
       </c>
       <c r="AA10">
-        <v>-6.88</v>
+        <v>1.02</v>
       </c>
       <c r="AB10">
-        <v>25.26</v>
+        <v>31.58</v>
       </c>
       <c r="AC10">
-        <v>100</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="AD10">
-        <v>88.89</v>
+        <v>99.5</v>
       </c>
       <c r="AE10">
-        <v>53.08</v>
+        <v>52.38</v>
       </c>
       <c r="AF10">
-        <v>722.5</v>
+        <v>14.25</v>
       </c>
       <c r="AG10">
-        <v>1684.42</v>
+        <v>1730.94</v>
       </c>
       <c r="AH10">
-        <v>1413.22</v>
+        <v>1390.9</v>
       </c>
       <c r="AI10">
-        <v>1584.31</v>
+        <v>1617.2</v>
       </c>
       <c r="AJ10" t="s">
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>28.6</v>
+        <v>34.09</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK10"/>
   <conditionalFormatting sqref="AF2:AF10">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D10">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J10">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K10">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1982,8 +2022,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N10">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1992,72 +2038,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T10">
@@ -2069,26 +2049,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U10">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V10">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W10">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2106,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2146,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2165,28 +2145,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2198,1274 +2178,1308 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.43</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="6">
         <v>0.37</v>
       </c>
-      <c r="E8" s="8">
+      <c r="D8" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-4.86</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-5.51</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-11.8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.42</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-7.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>5.86</v>
+      </c>
+      <c r="D12" s="6">
+        <v>2.04</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-15.52</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-20.15</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3.86</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.49</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.3</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.22</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>14.89</v>
+      </c>
+      <c r="D16" s="6">
+        <v>13.97</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1.74</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.12</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>4.46</v>
+      </c>
+      <c r="D18" s="6">
+        <v>3.34</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.47</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-5.43</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-0.72</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2.27</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.31</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-5.22</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>6.89</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.83</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4.06</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.19</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-5.17</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-7.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>18.22</v>
+      </c>
+      <c r="D25" s="6">
+        <v>20.94</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-8.26</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-8.57</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-15.57</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-15.98</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>9.58</v>
+      </c>
+      <c r="D28" s="6">
+        <v>6.07</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-6.56</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>16.25</v>
+      </c>
+      <c r="D30" s="6">
+        <v>13.72</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-40.77</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-40.83</v>
+      </c>
+      <c r="E32" s="7">
         <v>-0.06</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-19.41</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-18.68</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>24.66</v>
+      </c>
+      <c r="D34" s="6">
+        <v>22.46</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-20.37</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-21.61</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-5.54</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-4.86</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-8.17</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-7.64</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-5.47</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="E11" s="9">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-6.29</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.82</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>6.33</v>
-      </c>
-      <c r="D12" s="7">
-        <v>5.86</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>5.71</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1.13</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-4.58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-14.88</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-15.52</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-1.65</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>3.68</v>
-      </c>
-      <c r="D14" s="7">
-        <v>3.86</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-12.57</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.36</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="E15" s="9">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-5.25</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-3.57</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="D16" s="7">
-        <v>14.89</v>
-      </c>
-      <c r="E16" s="9">
-        <v>10.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>13.8</v>
+      </c>
+      <c r="D43" s="6">
+        <v>12.86</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1.33</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.74</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-23.05</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-24.24</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>4.02</v>
-      </c>
-      <c r="D18" s="7">
-        <v>4.46</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-23.18</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-23.55</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.82</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.47</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-4.29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-24.44</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-26.05</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.26</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-17</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-18.43</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>4.14</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2.27</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-7.51</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-10.21</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-7.37</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-5.29</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-20.64</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-22.04</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>6.54</v>
-      </c>
-      <c r="D23" s="7">
-        <v>6.89</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-40.66</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-41.52</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.83</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2.19</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-19.38</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-18.27</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>10.28</v>
-      </c>
-      <c r="D25" s="7">
-        <v>18.22</v>
-      </c>
-      <c r="E25" s="9">
-        <v>7.94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>377.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>371.4</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-5.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2920.9</v>
+      </c>
+      <c r="D54" s="6">
+        <v>2907</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-13.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>311.55</v>
+      </c>
+      <c r="D55" s="6">
+        <v>304.9</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-6.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>350</v>
+      </c>
+      <c r="D56" s="6">
+        <v>344</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>409.45</v>
+      </c>
+      <c r="D57" s="6">
+        <v>397.5</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-11.95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>585.4</v>
+      </c>
+      <c r="D58" s="6">
+        <v>575.05</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-10.35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>200.97</v>
+      </c>
+      <c r="D59" s="6">
+        <v>198.08</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>3514.4</v>
+      </c>
+      <c r="D60" s="6">
+        <v>3545</v>
+      </c>
+      <c r="E60" s="8">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1790</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1779.1</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>23</v>
+      </c>
+      <c r="D62" s="6">
+        <v>22</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>34</v>
+      </c>
+      <c r="D63" s="6">
+        <v>33</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>12</v>
+      </c>
+      <c r="D64" s="6">
         <v>11</v>
       </c>
-      <c r="C26" s="7">
-        <v>-9.68</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-8.26</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="E64" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6">
+        <v>45</v>
+      </c>
+      <c r="D65" s="6">
+        <v>44</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>43.89</v>
+      </c>
+      <c r="D66" s="6">
+        <v>39.12</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-4.77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-17.17</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-15.57</v>
-      </c>
-      <c r="E27" s="9">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>46.28</v>
+      </c>
+      <c r="D67" s="6">
+        <v>45.08</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>12.07</v>
-      </c>
-      <c r="D28" s="7">
-        <v>9.58</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>32.64</v>
+      </c>
+      <c r="D68" s="6">
+        <v>29.64</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-7.19</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-6.6</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>45.82</v>
+      </c>
+      <c r="D69" s="6">
+        <v>41.39</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-4.43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>17.12</v>
-      </c>
-      <c r="D30" s="7">
-        <v>16.25</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>50.76</v>
+      </c>
+      <c r="D70" s="6">
+        <v>44.69</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-6.07</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>2.17</v>
-      </c>
-      <c r="D31" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>31.2</v>
+      </c>
+      <c r="D71" s="6">
+        <v>29.54</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-42.02</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-40.77</v>
-      </c>
-      <c r="E32" s="9">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>53.2</v>
+      </c>
+      <c r="D72" s="6">
+        <v>49.01</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-16.97</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-19.41</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>45.44</v>
+      </c>
+      <c r="D73" s="6">
+        <v>48.15</v>
+      </c>
+      <c r="E73" s="8">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>14.42</v>
-      </c>
-      <c r="D34" s="7">
-        <v>24.66</v>
-      </c>
-      <c r="E34" s="9">
-        <v>10.24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="6">
+        <v>75.56</v>
+      </c>
+      <c r="D74" s="6">
+        <v>73.73</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-20.31</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-20.37</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-51.88</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-42.41</v>
+      </c>
+      <c r="E75" s="8">
+        <v>9.470000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-0.57</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-16.42</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-15.85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-1.77</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-3.9</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-15.21</v>
+      </c>
+      <c r="D77" s="6">
+        <v>35.72</v>
+      </c>
+      <c r="E77" s="8">
+        <v>50.93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-6.29</v>
-      </c>
-      <c r="E38" s="9">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>10.11</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-25.96</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-36.07</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>5.94</v>
-      </c>
-      <c r="D39" s="7">
-        <v>5.71</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-37.06</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-36.24</v>
+      </c>
+      <c r="E79" s="8">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>2.13</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-50.09</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-24.63</v>
+      </c>
+      <c r="E80" s="8">
+        <v>25.46</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-13.27</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-10.42</v>
-      </c>
-      <c r="E41" s="9">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-55.91</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-32.01</v>
+      </c>
+      <c r="E81" s="8">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-5.65</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-5.25</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-86.11</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-82.81</v>
+      </c>
+      <c r="E82" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>9.25</v>
-      </c>
-      <c r="D43" s="7">
-        <v>13.8</v>
-      </c>
-      <c r="E43" s="9">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-23.17</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-23.05</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-24.74</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-23.18</v>
-      </c>
-      <c r="E45" s="9">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-23.32</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-24.44</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-18.62</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-17</v>
-      </c>
-      <c r="E47" s="9">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-6.99</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-7.51</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-19.1</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-20.64</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-41.21</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-40.66</v>
-      </c>
-      <c r="E50" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-19.27</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-19.38</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-6.7</v>
-      </c>
-      <c r="D52" s="7">
-        <v>0</v>
-      </c>
-      <c r="E52" s="9">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>376.6</v>
-      </c>
-      <c r="D53" s="7">
-        <v>377.2</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2861.7</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2920.9</v>
-      </c>
-      <c r="E54" s="9">
-        <v>59.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>316.15</v>
-      </c>
-      <c r="D55" s="7">
-        <v>311.55</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>343.2</v>
-      </c>
-      <c r="D56" s="7">
-        <v>350</v>
-      </c>
-      <c r="E56" s="9">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>411.75</v>
-      </c>
-      <c r="D57" s="7">
-        <v>409.45</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>596.75</v>
-      </c>
-      <c r="D58" s="7">
-        <v>585.4</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-11.35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>199.48</v>
-      </c>
-      <c r="D59" s="7">
-        <v>200.97</v>
-      </c>
-      <c r="E59" s="9">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>3520.7</v>
-      </c>
-      <c r="D60" s="7">
-        <v>3514.4</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>1650</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1790</v>
-      </c>
-      <c r="E61" s="9">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>99</v>
-      </c>
-      <c r="D62" s="7">
-        <v>88</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>88</v>
-      </c>
-      <c r="D63" s="7">
-        <v>99</v>
-      </c>
-      <c r="E63" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>43.22</v>
-      </c>
-      <c r="D64" s="7">
-        <v>43.89</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>39.93</v>
-      </c>
-      <c r="D65" s="7">
-        <v>46.28</v>
-      </c>
-      <c r="E65" s="9">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>34.9</v>
-      </c>
-      <c r="D66" s="7">
-        <v>32.64</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>38.94</v>
-      </c>
-      <c r="D67" s="7">
-        <v>45.82</v>
-      </c>
-      <c r="E67" s="9">
-        <v>6.88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>52.02</v>
-      </c>
-      <c r="D68" s="7">
-        <v>50.76</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>33.1</v>
-      </c>
-      <c r="D69" s="7">
-        <v>31.2</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>51.2</v>
-      </c>
-      <c r="D70" s="7">
-        <v>53.2</v>
-      </c>
-      <c r="E70" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>45.9</v>
-      </c>
-      <c r="D71" s="7">
-        <v>45.44</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>65.3</v>
-      </c>
-      <c r="D72" s="7">
-        <v>75.56</v>
-      </c>
-      <c r="E72" s="9">
-        <v>10.26</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="7">
-        <v>7.82</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-51.88</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-59.7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>4.84</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-0.57</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-5.41</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-38.24</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-15.21</v>
-      </c>
-      <c r="E75" s="9">
-        <v>23.03</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>1.45</v>
-      </c>
-      <c r="D76" s="7">
-        <v>10.11</v>
-      </c>
-      <c r="E76" s="9">
-        <v>8.66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>7.32</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-37.06</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-44.38</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-16.87</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-50.09</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-33.22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-36.11</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-55.91</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-19.8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-72.95</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-86.11</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-13.16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>285.92</v>
-      </c>
-      <c r="D81" s="7">
+      <c r="C83" s="6">
         <v>722.5</v>
       </c>
-      <c r="E81" s="9">
-        <v>436.58</v>
+      <c r="D83" s="6">
+        <v>14.25</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-708.25</v>
       </c>
     </row>
   </sheetData>
@@ -3491,61 +3505,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>40.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>40.88</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>47.2</v>
-      </c>
-      <c r="E2" s="12">
-        <v>20</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-0.4</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-3.8</v>
-      </c>
-      <c r="H2" s="12">
-        <v>55.4</v>
-      </c>
-      <c r="I2" s="12">
-        <v>20</v>
+      <c r="D2" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="E2" s="11">
+        <v>22.2</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-5.2</v>
+      </c>
+      <c r="H2" s="11">
+        <v>55</v>
+      </c>
+      <c r="I2" s="11">
+        <v>22.2</v>
       </c>
     </row>
   </sheetData>
@@ -3646,61 +3660,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.2719</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1895</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.184</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.125</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.08650000000000001</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0703</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0515</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0383</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1106</v>
+      <c r="A2" s="14">
+        <v>0.2685</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1891</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1865</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1169</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0605</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0539</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0443</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1139</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,25 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.8 → 44.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>44.7</t>
-  </si>
-  <si>
-    <t>53.2 → 49.0</t>
-  </si>
-  <si>
-    <t>53.2</t>
+    <t>49.0 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.0</t>
+  </si>
+  <si>
+    <t>50.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -939,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>371.4</v>
+        <v>369.55</v>
       </c>
       <c r="D2">
-        <v>-1.54</v>
+        <v>-0.5</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>370.75</v>
+        <v>369.55</v>
       </c>
       <c r="G2">
-        <v>-24.24</v>
+        <v>-24.61</v>
       </c>
       <c r="H2">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.12</v>
+        <v>-2.94</v>
       </c>
       <c r="J2">
-        <v>-3.71</v>
+        <v>-4.55</v>
       </c>
       <c r="K2">
-        <v>-21.61</v>
+        <v>-21.82</v>
       </c>
       <c r="L2">
-        <v>-8.57</v>
+        <v>-9.9</v>
       </c>
       <c r="M2">
-        <v>6.81</v>
+        <v>6.97</v>
       </c>
       <c r="N2">
         <v>22</v>
       </c>
       <c r="O2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>377.28</v>
+        <v>375.04</v>
       </c>
       <c r="Q2">
-        <v>380.81</v>
+        <v>379.53</v>
       </c>
       <c r="R2">
-        <v>389.06</v>
+        <v>388.24</v>
       </c>
       <c r="S2">
-        <v>433.33</v>
+        <v>433.09</v>
       </c>
       <c r="T2">
-        <v>-14.29</v>
+        <v>-14.67</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.12</v>
+        <v>37.71</v>
       </c>
       <c r="Z2">
-        <v>-4.25</v>
+        <v>-4.57</v>
       </c>
       <c r="AA2">
         <v>-4.57</v>
       </c>
       <c r="AB2">
-        <v>0.32</v>
+        <v>-0</v>
       </c>
       <c r="AC2">
-        <v>50.87</v>
+        <v>35.88</v>
       </c>
       <c r="AD2">
-        <v>65.53</v>
+        <v>52.41</v>
       </c>
       <c r="AE2">
-        <v>8.4</v>
+        <v>8.41</v>
       </c>
       <c r="AF2">
-        <v>-42.41</v>
+        <v>-12.85</v>
       </c>
       <c r="AG2">
-        <v>394.39</v>
+        <v>392.21</v>
       </c>
       <c r="AH2">
-        <v>367.22</v>
+        <v>366.84</v>
       </c>
       <c r="AI2">
-        <v>398.26</v>
+        <v>396.4</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>27.15</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2907</v>
+        <v>2889</v>
       </c>
       <c r="D3">
-        <v>-0.48</v>
+        <v>-0.62</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1064,46 +1055,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-23.55</v>
+        <v>-24.02</v>
       </c>
       <c r="H3">
-        <v>5.66</v>
+        <v>5.01</v>
       </c>
       <c r="I3">
-        <v>3.34</v>
+        <v>0.86</v>
       </c>
       <c r="J3">
-        <v>-5.51</v>
+        <v>-5.34</v>
       </c>
       <c r="K3">
-        <v>-8.17</v>
+        <v>-9.77</v>
       </c>
       <c r="L3">
-        <v>-15.98</v>
+        <v>-17.39</v>
       </c>
       <c r="M3">
-        <v>26.85</v>
+        <v>27.27</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>2869.54</v>
+        <v>2874.46</v>
       </c>
       <c r="Q3">
-        <v>2906.3</v>
+        <v>2897.98</v>
       </c>
       <c r="R3">
-        <v>3136.56</v>
+        <v>3124.3</v>
       </c>
       <c r="S3">
-        <v>3232.75</v>
+        <v>3228.65</v>
       </c>
       <c r="T3">
-        <v>-10.08</v>
+        <v>-10.52</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1118,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>45.08</v>
+        <v>43.5</v>
       </c>
       <c r="Z3">
-        <v>-72.94</v>
+        <v>-66.63</v>
       </c>
       <c r="AA3">
-        <v>-90.33</v>
+        <v>-85.59</v>
       </c>
       <c r="AB3">
-        <v>17.39</v>
+        <v>18.96</v>
       </c>
       <c r="AC3">
-        <v>98.59</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="AD3">
-        <v>93.44</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="AE3">
-        <v>66.67</v>
+        <v>67.63</v>
       </c>
       <c r="AF3">
-        <v>-16.42</v>
+        <v>-5.75</v>
       </c>
       <c r="AG3">
-        <v>3096.44</v>
+        <v>3074.77</v>
       </c>
       <c r="AH3">
-        <v>2716.16</v>
+        <v>2721.2</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1154,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>52.59</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>304.9</v>
+        <v>297.45</v>
       </c>
       <c r="D4">
-        <v>-2.13</v>
+        <v>-2.44</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1177,46 +1168,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-26.05</v>
+        <v>-27.86</v>
       </c>
       <c r="H4">
-        <v>10.59</v>
+        <v>7.89</v>
       </c>
       <c r="I4">
-        <v>-5.43</v>
+        <v>-8.69</v>
       </c>
       <c r="J4">
-        <v>-11.8</v>
+        <v>-15.81</v>
       </c>
       <c r="K4">
-        <v>-5.47</v>
+        <v>-14.98</v>
       </c>
       <c r="L4">
-        <v>6.07</v>
+        <v>1.23</v>
       </c>
       <c r="M4">
-        <v>11.69</v>
+        <v>10.95</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="P4">
-        <v>315.56</v>
+        <v>309.9</v>
       </c>
       <c r="Q4">
-        <v>326.95</v>
+        <v>324.09</v>
       </c>
       <c r="R4">
-        <v>356.86</v>
+        <v>354.64</v>
       </c>
       <c r="S4">
-        <v>340.42</v>
+        <v>339.89</v>
       </c>
       <c r="T4">
-        <v>-10.43</v>
+        <v>-12.49</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1231,43 +1222,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>29.64</v>
+        <v>26.69</v>
       </c>
       <c r="Z4">
-        <v>-11.98</v>
+        <v>-12.86</v>
       </c>
       <c r="AA4">
-        <v>-11.61</v>
+        <v>-11.86</v>
       </c>
       <c r="AB4">
-        <v>-0.36</v>
+        <v>-1</v>
       </c>
       <c r="AC4">
-        <v>49.51</v>
+        <v>31.42</v>
       </c>
       <c r="AD4">
-        <v>65.15000000000001</v>
+        <v>48.59</v>
       </c>
       <c r="AE4">
-        <v>10.47</v>
+        <v>10.62</v>
       </c>
       <c r="AF4">
-        <v>35.72</v>
+        <v>43.84</v>
       </c>
       <c r="AG4">
-        <v>353.88</v>
+        <v>350.77</v>
       </c>
       <c r="AH4">
-        <v>300.01</v>
+        <v>297.4</v>
       </c>
       <c r="AI4">
-        <v>340.02</v>
+        <v>333.49</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>33.47</v>
+        <v>37.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>344</v>
+        <v>340.75</v>
       </c>
       <c r="D5">
-        <v>-1.71</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1290,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-18.43</v>
+        <v>-19.2</v>
       </c>
       <c r="H5">
-        <v>16.91</v>
+        <v>15.8</v>
       </c>
       <c r="I5">
-        <v>-0.72</v>
+        <v>-2.77</v>
       </c>
       <c r="J5">
-        <v>-5.42</v>
+        <v>-7</v>
       </c>
       <c r="K5">
-        <v>-7.82</v>
+        <v>-7.71</v>
       </c>
       <c r="L5">
-        <v>-6.56</v>
+        <v>-10.93</v>
       </c>
       <c r="M5">
-        <v>5.39</v>
+        <v>4.47</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>346.98</v>
+        <v>345.04</v>
       </c>
       <c r="Q5">
-        <v>352.58</v>
+        <v>351.49</v>
       </c>
       <c r="R5">
-        <v>363.2</v>
+        <v>362.29</v>
       </c>
       <c r="S5">
-        <v>356.45</v>
+        <v>356.18</v>
       </c>
       <c r="T5">
-        <v>-3.49</v>
+        <v>-4.33</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1344,43 +1335,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>41.39</v>
+        <v>39.18</v>
       </c>
       <c r="Z5">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="AA5">
-        <v>-4.58</v>
+        <v>-4.66</v>
       </c>
       <c r="AB5">
-        <v>-0.12</v>
+        <v>-0.34</v>
       </c>
       <c r="AC5">
-        <v>50.12</v>
+        <v>52.37</v>
       </c>
       <c r="AD5">
-        <v>48.54</v>
+        <v>50.62</v>
       </c>
       <c r="AE5">
-        <v>11.64</v>
+        <v>11.52</v>
       </c>
       <c r="AF5">
-        <v>-25.96</v>
+        <v>-23.46</v>
       </c>
       <c r="AG5">
-        <v>365.45</v>
+        <v>364.48</v>
       </c>
       <c r="AH5">
-        <v>339.71</v>
+        <v>338.49</v>
       </c>
       <c r="AI5">
-        <v>379.96</v>
+        <v>376.5</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>32.17</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>397.5</v>
+        <v>389.25</v>
       </c>
       <c r="D6">
-        <v>-2.92</v>
+        <v>-2.08</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1403,25 +1394,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-10.21</v>
+        <v>-12.07</v>
       </c>
       <c r="H6">
-        <v>42.19</v>
+        <v>39.24</v>
       </c>
       <c r="I6">
-        <v>-0.31</v>
+        <v>-5.01</v>
       </c>
       <c r="J6">
-        <v>2.04</v>
+        <v>-0.89</v>
       </c>
       <c r="K6">
-        <v>1.13</v>
+        <v>-0.49</v>
       </c>
       <c r="L6">
-        <v>13.72</v>
+        <v>11.93</v>
       </c>
       <c r="M6">
-        <v>-11.39</v>
+        <v>-10.67</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1430,19 +1421,19 @@
         <v>75</v>
       </c>
       <c r="P6">
-        <v>410</v>
+        <v>405.89</v>
       </c>
       <c r="Q6">
-        <v>411.68</v>
+        <v>411.18</v>
       </c>
       <c r="R6">
-        <v>404.61</v>
+        <v>404.34</v>
       </c>
       <c r="S6">
-        <v>380.36</v>
+        <v>380.73</v>
       </c>
       <c r="T6">
-        <v>4.5</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1457,43 +1448,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>44.69</v>
+        <v>41.05</v>
       </c>
       <c r="Z6">
-        <v>0.68</v>
+        <v>-0.88</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>1.42</v>
       </c>
       <c r="AB6">
-        <v>-1.31</v>
+        <v>-2.3</v>
       </c>
       <c r="AC6">
-        <v>19.94</v>
+        <v>10.19</v>
       </c>
       <c r="AD6">
-        <v>29.69</v>
+        <v>21.37</v>
       </c>
       <c r="AE6">
-        <v>14.36</v>
+        <v>14.24</v>
       </c>
       <c r="AF6">
-        <v>-36.24</v>
+        <v>-33.81</v>
       </c>
       <c r="AG6">
-        <v>433.49</v>
+        <v>434.59</v>
       </c>
       <c r="AH6">
-        <v>389.88</v>
+        <v>387.77</v>
       </c>
       <c r="AI6">
-        <v>391.71</v>
+        <v>434.57</v>
       </c>
       <c r="AJ6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK6">
-        <v>24.84</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>575.05</v>
+        <v>560.85</v>
       </c>
       <c r="D7">
-        <v>-1.77</v>
+        <v>-2.47</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1516,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-22.04</v>
+        <v>-23.97</v>
       </c>
       <c r="H7">
-        <v>13.55</v>
+        <v>10.74</v>
       </c>
       <c r="I7">
-        <v>-5.22</v>
+        <v>-5.01</v>
       </c>
       <c r="J7">
-        <v>-20.15</v>
+        <v>-21.84</v>
       </c>
       <c r="K7">
-        <v>-1.65</v>
+        <v>-3.31</v>
       </c>
       <c r="L7">
-        <v>-0.33</v>
+        <v>-3.33</v>
       </c>
       <c r="M7">
-        <v>18.65</v>
+        <v>18.78</v>
       </c>
       <c r="N7">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P7">
-        <v>590.65</v>
+        <v>584.73</v>
       </c>
       <c r="Q7">
-        <v>664.48</v>
+        <v>657.1799999999999</v>
       </c>
       <c r="R7">
-        <v>657.49</v>
+        <v>656.92</v>
       </c>
       <c r="S7">
-        <v>603.4299999999999</v>
+        <v>603.42</v>
       </c>
       <c r="T7">
-        <v>-4.7</v>
+        <v>-7.06</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1570,43 +1561,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>29.54</v>
+        <v>27.39</v>
       </c>
       <c r="Z7">
-        <v>-24.55</v>
+        <v>-27.76</v>
       </c>
       <c r="AA7">
-        <v>-10.59</v>
+        <v>-14.02</v>
       </c>
       <c r="AB7">
-        <v>-13.97</v>
+        <v>-13.74</v>
       </c>
       <c r="AC7">
-        <v>4.69</v>
+        <v>1.57</v>
       </c>
       <c r="AD7">
-        <v>7.11</v>
+        <v>5.11</v>
       </c>
       <c r="AE7">
-        <v>27.65</v>
+        <v>26.95</v>
       </c>
       <c r="AF7">
-        <v>-24.63</v>
+        <v>-42.02</v>
       </c>
       <c r="AG7">
-        <v>773.61</v>
+        <v>773.65</v>
       </c>
       <c r="AH7">
-        <v>555.36</v>
+        <v>540.71</v>
       </c>
       <c r="AI7">
-        <v>662.39</v>
+        <v>648.33</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>42.4</v>
+        <v>45.02</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>198.08</v>
+        <v>198.8</v>
       </c>
       <c r="D8">
-        <v>-1.44</v>
+        <v>0.36</v>
       </c>
       <c r="E8">
         <v>338.7</v>
@@ -1629,46 +1620,46 @@
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-41.52</v>
+        <v>-41.3</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>6.18</v>
       </c>
       <c r="I8">
-        <v>2.83</v>
+        <v>4.08</v>
       </c>
       <c r="J8">
-        <v>1.49</v>
+        <v>-0.25</v>
       </c>
       <c r="K8">
-        <v>-12.57</v>
+        <v>-12.8</v>
       </c>
       <c r="L8">
-        <v>-40.83</v>
+        <v>-40.69</v>
       </c>
       <c r="M8">
-        <v>-4.43</v>
+        <v>-3.89</v>
       </c>
       <c r="N8">
         <v>11</v>
       </c>
       <c r="O8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P8">
-        <v>198.04</v>
+        <v>199.6</v>
       </c>
       <c r="Q8">
-        <v>196.29</v>
+        <v>196.16</v>
       </c>
       <c r="R8">
-        <v>206.04</v>
+        <v>205.42</v>
       </c>
       <c r="S8">
-        <v>243.21</v>
+        <v>242.66</v>
       </c>
       <c r="T8">
-        <v>-18.56</v>
+        <v>-18.08</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>49.01</v>
+        <v>50.06</v>
       </c>
       <c r="Z8">
-        <v>-2.01</v>
+        <v>-1.68</v>
       </c>
       <c r="AA8">
-        <v>-3.47</v>
+        <v>-3.11</v>
       </c>
       <c r="AB8">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AC8">
-        <v>92.33</v>
+        <v>90.48</v>
       </c>
       <c r="AD8">
-        <v>92.70999999999999</v>
+        <v>93.53</v>
       </c>
       <c r="AE8">
-        <v>5.97</v>
+        <v>7.35</v>
       </c>
       <c r="AF8">
-        <v>-32.01</v>
+        <v>2256.52</v>
       </c>
       <c r="AG8">
-        <v>204.81</v>
+        <v>204.43</v>
       </c>
       <c r="AH8">
-        <v>187.77</v>
+        <v>187.89</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1719,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.05</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,58 +1721,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3545</v>
+        <v>3496.8</v>
       </c>
       <c r="D9">
-        <v>0.87</v>
+        <v>-1.36</v>
       </c>
       <c r="E9">
-        <v>4337.2</v>
+        <v>4119.6</v>
       </c>
       <c r="F9">
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.27</v>
+        <v>-15.12</v>
       </c>
       <c r="H9">
-        <v>7.14</v>
+        <v>5.68</v>
       </c>
       <c r="I9">
-        <v>-5.17</v>
+        <v>-4.77</v>
       </c>
       <c r="J9">
-        <v>-0.22</v>
+        <v>-3.54</v>
       </c>
       <c r="K9">
-        <v>-3.57</v>
+        <v>-3.05</v>
       </c>
       <c r="L9">
-        <v>-18.68</v>
+        <v>-19.38</v>
       </c>
       <c r="M9">
-        <v>18.91</v>
+        <v>18.08</v>
       </c>
       <c r="N9">
         <v>44</v>
       </c>
       <c r="O9">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="P9">
-        <v>3577.6</v>
+        <v>3542.56</v>
       </c>
       <c r="Q9">
-        <v>3557.24</v>
+        <v>3553.46</v>
       </c>
       <c r="R9">
-        <v>3571.82</v>
+        <v>3569.75</v>
       </c>
       <c r="S9">
-        <v>3669.87</v>
+        <v>3669.46</v>
       </c>
       <c r="T9">
-        <v>-3.4</v>
+        <v>-4.71</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.15</v>
+        <v>44.4</v>
       </c>
       <c r="Z9">
-        <v>-3.3</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AA9">
-        <v>-3.77</v>
+        <v>-4.68</v>
       </c>
       <c r="AB9">
-        <v>0.47</v>
+        <v>-3.61</v>
       </c>
       <c r="AC9">
-        <v>45.03</v>
+        <v>43.64</v>
       </c>
       <c r="AD9">
-        <v>53.71</v>
+        <v>46.81</v>
       </c>
       <c r="AE9">
-        <v>103.52</v>
+        <v>105.22</v>
       </c>
       <c r="AF9">
-        <v>-82.81</v>
+        <v>-86.41</v>
       </c>
       <c r="AG9">
-        <v>3683.54</v>
+        <v>3682.35</v>
       </c>
       <c r="AH9">
-        <v>3430.94</v>
+        <v>3424.57</v>
       </c>
       <c r="AI9">
         <v>3421.87</v>
@@ -1832,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>30.87</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1779.1</v>
+        <v>1834.7</v>
       </c>
       <c r="D10">
-        <v>-0.61</v>
+        <v>3.13</v>
       </c>
       <c r="E10">
-        <v>1790</v>
+        <v>1834.7</v>
       </c>
       <c r="F10">
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>34.15</v>
+        <v>38.34</v>
       </c>
       <c r="I10">
-        <v>20.94</v>
+        <v>18.87</v>
       </c>
       <c r="J10">
-        <v>13.97</v>
+        <v>19.36</v>
       </c>
       <c r="K10">
-        <v>12.86</v>
+        <v>16.39</v>
       </c>
       <c r="L10">
-        <v>22.46</v>
+        <v>27.07</v>
       </c>
       <c r="M10">
-        <v>6.05</v>
+        <v>6.91</v>
       </c>
       <c r="N10">
         <v>99</v>
       </c>
       <c r="O10">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="P10">
-        <v>1667.56</v>
+        <v>1725.8</v>
       </c>
       <c r="Q10">
-        <v>1560.92</v>
+        <v>1574.73</v>
       </c>
       <c r="R10">
-        <v>1579.91</v>
+        <v>1583.91</v>
       </c>
       <c r="S10">
-        <v>1516.14</v>
+        <v>1517.36</v>
       </c>
       <c r="T10">
-        <v>17.34</v>
+        <v>20.91</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,43 +1900,43 @@
         <v>2</v>
       </c>
       <c r="Y10">
-        <v>73.73</v>
+        <v>76.81</v>
       </c>
       <c r="Z10">
-        <v>32.6</v>
+        <v>47.8</v>
       </c>
       <c r="AA10">
-        <v>1.02</v>
+        <v>10.37</v>
       </c>
       <c r="AB10">
-        <v>31.58</v>
+        <v>37.43</v>
       </c>
       <c r="AC10">
         <v>98.48999999999999</v>
       </c>
       <c r="AD10">
-        <v>99.5</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="AE10">
-        <v>52.38</v>
+        <v>52.61</v>
       </c>
       <c r="AF10">
-        <v>14.25</v>
+        <v>54.99</v>
       </c>
       <c r="AG10">
-        <v>1730.94</v>
+        <v>1784.21</v>
       </c>
       <c r="AH10">
-        <v>1390.9</v>
+        <v>1365.25</v>
       </c>
       <c r="AI10">
-        <v>1617.2</v>
+        <v>1654.51</v>
       </c>
       <c r="AJ10" t="s">
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>34.09</v>
+        <v>39.39</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2126,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2144,1348 +2135,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.55</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>0.37</v>
+        <v>-5.51</v>
       </c>
       <c r="D8" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-4.08</v>
+        <v>-5.34</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.86</v>
+        <v>-11.8</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.51</v>
+        <v>-15.81</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.65</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.710000000000001</v>
+        <v>-5.42</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.8</v>
+        <v>-7</v>
       </c>
       <c r="E10" s="7">
-        <v>-2.09</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.42</v>
+        <v>-0.89</v>
       </c>
       <c r="E11" s="7">
-        <v>-7.12</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>5.86</v>
+        <v>-20.15</v>
       </c>
       <c r="D12" s="6">
-        <v>2.04</v>
+        <v>-21.84</v>
       </c>
       <c r="E12" s="7">
-        <v>-3.82</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-15.52</v>
+        <v>1.49</v>
       </c>
       <c r="D13" s="6">
-        <v>-20.15</v>
+        <v>-0.25</v>
       </c>
       <c r="E13" s="7">
-        <v>-4.63</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>3.86</v>
+        <v>-0.22</v>
       </c>
       <c r="D14" s="6">
-        <v>1.49</v>
+        <v>-3.54</v>
       </c>
       <c r="E14" s="7">
-        <v>-2.37</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.3</v>
+        <v>13.97</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.22</v>
+        <v>19.36</v>
       </c>
       <c r="E15" s="8">
-        <v>0.08</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>14.89</v>
+        <v>-2.12</v>
       </c>
       <c r="D16" s="6">
-        <v>13.97</v>
+        <v>-2.94</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.92</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>1.74</v>
+        <v>3.34</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.12</v>
+        <v>0.86</v>
       </c>
       <c r="E17" s="7">
-        <v>-3.86</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>4.46</v>
+        <v>-5.43</v>
       </c>
       <c r="D18" s="6">
-        <v>3.34</v>
+        <v>-8.69</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.12</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.47</v>
+        <v>-0.72</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.43</v>
+        <v>-2.77</v>
       </c>
       <c r="E19" s="7">
-        <v>-2.96</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.72</v>
+        <v>-5.01</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.98</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>2.27</v>
+        <v>-5.22</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.58</v>
+        <v>-5.01</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.21</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.29</v>
+        <v>2.83</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.22</v>
+        <v>4.08</v>
       </c>
       <c r="E22" s="8">
-        <v>0.07000000000000001</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>6.89</v>
+        <v>-5.17</v>
       </c>
       <c r="D23" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-4.06</v>
+        <v>-4.77</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>2.19</v>
+        <v>20.94</v>
       </c>
       <c r="D24" s="6">
-        <v>-5.17</v>
+        <v>18.87</v>
       </c>
       <c r="E24" s="7">
-        <v>-7.36</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>18.22</v>
+        <v>-8.57</v>
       </c>
       <c r="D25" s="6">
-        <v>20.94</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.72</v>
+        <v>-9.9</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-8.26</v>
+        <v>-15.98</v>
       </c>
       <c r="D26" s="6">
-        <v>-8.57</v>
+        <v>-17.39</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.31</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-15.57</v>
+        <v>6.07</v>
       </c>
       <c r="D27" s="6">
-        <v>-15.98</v>
+        <v>1.23</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.41</v>
+        <v>-4.84</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>9.58</v>
+        <v>-6.56</v>
       </c>
       <c r="D28" s="6">
-        <v>6.07</v>
+        <v>-10.93</v>
       </c>
       <c r="E28" s="7">
-        <v>-3.51</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-6.6</v>
+        <v>13.72</v>
       </c>
       <c r="D29" s="6">
-        <v>-6.56</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.04</v>
+        <v>11.93</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>16.25</v>
+        <v>-0.33</v>
       </c>
       <c r="D30" s="6">
-        <v>13.72</v>
+        <v>-3.33</v>
       </c>
       <c r="E30" s="7">
-        <v>-2.53</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>0.53</v>
+        <v>-40.83</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.86</v>
+        <v>-40.69</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-40.77</v>
+        <v>-18.68</v>
       </c>
       <c r="D32" s="6">
-        <v>-40.83</v>
+        <v>-19.38</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.06</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-19.41</v>
+        <v>22.46</v>
       </c>
       <c r="D33" s="6">
-        <v>-18.68</v>
+        <v>27.07</v>
       </c>
       <c r="E33" s="8">
-        <v>0.73</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>24.66</v>
+        <v>-21.61</v>
       </c>
       <c r="D34" s="6">
-        <v>22.46</v>
+        <v>-21.82</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.2</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-20.37</v>
+        <v>-8.17</v>
       </c>
       <c r="D35" s="6">
-        <v>-21.61</v>
+        <v>-9.77</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.24</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-8.119999999999999</v>
+        <v>-5.47</v>
       </c>
       <c r="D36" s="6">
-        <v>-8.17</v>
+        <v>-14.98</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.05</v>
+        <v>-9.51</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-3.9</v>
+        <v>-7.82</v>
       </c>
       <c r="D37" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.57</v>
+        <v>-7.71</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-6.29</v>
+        <v>1.13</v>
       </c>
       <c r="D38" s="6">
-        <v>-7.82</v>
+        <v>-0.49</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.53</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>5.71</v>
+        <v>-1.65</v>
       </c>
       <c r="D39" s="6">
-        <v>1.13</v>
+        <v>-3.31</v>
       </c>
       <c r="E39" s="7">
-        <v>-4.58</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>0.85</v>
+        <v>-12.57</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.65</v>
+        <v>-12.8</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.5</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-10.42</v>
+        <v>-3.57</v>
       </c>
       <c r="D41" s="6">
-        <v>-12.57</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.15</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.52</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-5.25</v>
+        <v>12.86</v>
       </c>
       <c r="D42" s="6">
-        <v>-3.57</v>
+        <v>16.39</v>
       </c>
       <c r="E42" s="8">
-        <v>1.68</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>13.8</v>
+        <v>-24.24</v>
       </c>
       <c r="D43" s="6">
-        <v>12.86</v>
+        <v>-24.61</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-23.05</v>
+        <v>-23.55</v>
       </c>
       <c r="D44" s="6">
-        <v>-24.24</v>
+        <v>-24.02</v>
       </c>
       <c r="E44" s="7">
-        <v>-1.19</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-23.18</v>
+        <v>-26.05</v>
       </c>
       <c r="D45" s="6">
-        <v>-23.55</v>
+        <v>-27.86</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.37</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-24.44</v>
+        <v>-18.43</v>
       </c>
       <c r="D46" s="6">
-        <v>-26.05</v>
+        <v>-19.2</v>
       </c>
       <c r="E46" s="7">
-        <v>-1.61</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-17</v>
+        <v>-10.21</v>
       </c>
       <c r="D47" s="6">
-        <v>-18.43</v>
+        <v>-12.07</v>
       </c>
       <c r="E47" s="7">
-        <v>-1.43</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-7.51</v>
+        <v>-22.04</v>
       </c>
       <c r="D48" s="6">
-        <v>-10.21</v>
+        <v>-23.97</v>
       </c>
       <c r="E48" s="7">
-        <v>-2.7</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-20.64</v>
+        <v>-41.52</v>
       </c>
       <c r="D49" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.4</v>
+        <v>-41.3</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.22</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-40.66</v>
+        <v>-18.27</v>
       </c>
       <c r="D50" s="6">
-        <v>-41.52</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.86</v>
+        <v>-15.12</v>
+      </c>
+      <c r="E50" s="8">
+        <v>3.15</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-19.38</v>
+        <v>-0.61</v>
       </c>
       <c r="D51" s="6">
-        <v>-18.27</v>
+        <v>0</v>
       </c>
       <c r="E51" s="8">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>0</v>
+        <v>371.4</v>
       </c>
       <c r="D52" s="6">
-        <v>-0.61</v>
+        <v>369.55</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.61</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>377.2</v>
+        <v>2907</v>
       </c>
       <c r="D53" s="6">
-        <v>371.4</v>
+        <v>2889</v>
       </c>
       <c r="E53" s="7">
-        <v>-5.8</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>2920.9</v>
+        <v>304.9</v>
       </c>
       <c r="D54" s="6">
-        <v>2907</v>
+        <v>297.45</v>
       </c>
       <c r="E54" s="7">
-        <v>-13.9</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>311.55</v>
+        <v>344</v>
       </c>
       <c r="D55" s="6">
-        <v>304.9</v>
+        <v>340.75</v>
       </c>
       <c r="E55" s="7">
-        <v>-6.65</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>350</v>
+        <v>397.5</v>
       </c>
       <c r="D56" s="6">
-        <v>344</v>
+        <v>389.25</v>
       </c>
       <c r="E56" s="7">
-        <v>-6</v>
+        <v>-8.25</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>409.45</v>
+        <v>575.05</v>
       </c>
       <c r="D57" s="6">
-        <v>397.5</v>
+        <v>560.85</v>
       </c>
       <c r="E57" s="7">
-        <v>-11.95</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>585.4</v>
+        <v>198.08</v>
       </c>
       <c r="D58" s="6">
-        <v>575.05</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-10.35</v>
+        <v>198.8</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.72</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>200.97</v>
+        <v>3545</v>
       </c>
       <c r="D59" s="6">
-        <v>198.08</v>
+        <v>3496.8</v>
       </c>
       <c r="E59" s="7">
-        <v>-2.89</v>
+        <v>-48.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>3514.4</v>
+        <v>1779.1</v>
       </c>
       <c r="D60" s="6">
-        <v>3545</v>
+        <v>1834.7</v>
       </c>
       <c r="E60" s="8">
-        <v>30.6</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>1790</v>
+        <v>77</v>
       </c>
       <c r="D61" s="6">
-        <v>1779.1</v>
+        <v>66</v>
       </c>
       <c r="E61" s="7">
-        <v>-10.9</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D62" s="6">
-        <v>22</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1</v>
+        <v>77</v>
+      </c>
+      <c r="E62" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>34</v>
+        <v>39.12</v>
       </c>
       <c r="D63" s="6">
-        <v>33</v>
+        <v>37.71</v>
       </c>
       <c r="E63" s="7">
-        <v>-1</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>12</v>
+        <v>45.08</v>
       </c>
       <c r="D64" s="6">
-        <v>11</v>
+        <v>43.5</v>
       </c>
       <c r="E64" s="7">
-        <v>-1</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>45</v>
+        <v>29.64</v>
       </c>
       <c r="D65" s="6">
-        <v>44</v>
+        <v>26.69</v>
       </c>
       <c r="E65" s="7">
-        <v>-1</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>43.89</v>
+        <v>41.39</v>
       </c>
       <c r="D66" s="6">
-        <v>39.12</v>
+        <v>39.18</v>
       </c>
       <c r="E66" s="7">
-        <v>-4.77</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>46.28</v>
+        <v>44.69</v>
       </c>
       <c r="D67" s="6">
-        <v>45.08</v>
+        <v>41.05</v>
       </c>
       <c r="E67" s="7">
-        <v>-1.2</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>32.64</v>
+        <v>29.54</v>
       </c>
       <c r="D68" s="6">
-        <v>29.64</v>
+        <v>27.39</v>
       </c>
       <c r="E68" s="7">
-        <v>-3</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>45.82</v>
+        <v>49.01</v>
       </c>
       <c r="D69" s="6">
-        <v>41.39</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-4.43</v>
+        <v>50.06</v>
+      </c>
+      <c r="E69" s="8">
+        <v>1.05</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>50.76</v>
+        <v>48.15</v>
       </c>
       <c r="D70" s="6">
-        <v>44.69</v>
+        <v>44.4</v>
       </c>
       <c r="E70" s="7">
-        <v>-6.07</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>31.2</v>
+        <v>73.73</v>
       </c>
       <c r="D71" s="6">
-        <v>29.54</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-1.66</v>
+        <v>76.81</v>
+      </c>
+      <c r="E71" s="8">
+        <v>3.08</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>53.2</v>
+        <v>-42.41</v>
       </c>
       <c r="D72" s="6">
-        <v>49.01</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-4.19</v>
+        <v>-12.85</v>
+      </c>
+      <c r="E72" s="8">
+        <v>29.56</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>45.44</v>
+        <v>-16.42</v>
       </c>
       <c r="D73" s="6">
-        <v>48.15</v>
+        <v>-5.75</v>
       </c>
       <c r="E73" s="8">
-        <v>2.71</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>75.56</v>
+        <v>35.72</v>
       </c>
       <c r="D74" s="6">
-        <v>73.73</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-1.83</v>
+        <v>43.84</v>
+      </c>
+      <c r="E74" s="8">
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-51.88</v>
+        <v>-25.96</v>
       </c>
       <c r="D75" s="6">
-        <v>-42.41</v>
+        <v>-23.46</v>
       </c>
       <c r="E75" s="8">
-        <v>9.470000000000001</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-0.57</v>
+        <v>-36.24</v>
       </c>
       <c r="D76" s="6">
-        <v>-16.42</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-15.85</v>
+        <v>-33.81</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2.43</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-15.21</v>
+        <v>-24.63</v>
       </c>
       <c r="D77" s="6">
-        <v>35.72</v>
-      </c>
-      <c r="E77" s="8">
-        <v>50.93</v>
+        <v>-42.02</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-17.39</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>10.11</v>
+        <v>-32.01</v>
       </c>
       <c r="D78" s="6">
-        <v>-25.96</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-36.07</v>
+        <v>2256.52</v>
+      </c>
+      <c r="E78" s="8">
+        <v>2288.53</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-37.06</v>
+        <v>-82.81</v>
       </c>
       <c r="D79" s="6">
-        <v>-36.24</v>
-      </c>
-      <c r="E79" s="8">
-        <v>0.82</v>
+        <v>-86.41</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-50.09</v>
+        <v>14.25</v>
       </c>
       <c r="D80" s="6">
-        <v>-24.63</v>
+        <v>54.99</v>
       </c>
       <c r="E80" s="8">
-        <v>25.46</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-55.91</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-32.01</v>
-      </c>
-      <c r="E81" s="8">
-        <v>23.9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-86.11</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-82.81</v>
-      </c>
-      <c r="E82" s="8">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>722.5</v>
-      </c>
-      <c r="D83" s="6">
-        <v>14.25</v>
-      </c>
-      <c r="E83" s="7">
-        <v>-708.25</v>
+        <v>40.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3509,28 +3446,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3544,16 +3481,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>44.5</v>
+        <v>43</v>
       </c>
       <c r="E2" s="11">
         <v>22.2</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.3</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.2</v>
+        <v>-6.4</v>
       </c>
       <c r="H2" s="11">
         <v>55</v>
@@ -3664,10 +3601,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>39</v>
@@ -3690,31 +3627,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.2685</v>
+        <v>0.2727</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1891</v>
+        <v>0.1878</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1865</v>
+        <v>0.1808</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1169</v>
+        <v>0.1095</v>
       </c>
       <c r="E2" s="14">
-        <v>0.06809999999999999</v>
+        <v>0.0697</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0605</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0539</v>
+        <v>0.0447</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.0443</v>
+        <v>-0.0389</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1139</v>
+        <v>-0.1067</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,31 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.0 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>50.1 → 40.9</t>
   </si>
   <si>
     <t>50.1</t>
+  </si>
+  <si>
+    <t>40.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +427,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,58 +943,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>369.55</v>
+        <v>364.65</v>
       </c>
       <c r="D2">
-        <v>-0.5</v>
+        <v>-1.33</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>369.55</v>
+        <v>364.65</v>
       </c>
       <c r="G2">
-        <v>-24.61</v>
+        <v>-25.61</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.94</v>
+        <v>-4.15</v>
       </c>
       <c r="J2">
-        <v>-4.55</v>
+        <v>-7.72</v>
       </c>
       <c r="K2">
-        <v>-21.82</v>
+        <v>-22.83</v>
       </c>
       <c r="L2">
-        <v>-9.9</v>
+        <v>-13.19</v>
       </c>
       <c r="M2">
-        <v>6.97</v>
+        <v>7.32</v>
       </c>
       <c r="N2">
         <v>22</v>
       </c>
       <c r="O2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P2">
-        <v>375.04</v>
+        <v>371.88</v>
       </c>
       <c r="Q2">
-        <v>379.53</v>
+        <v>378.23</v>
       </c>
       <c r="R2">
-        <v>388.24</v>
+        <v>387.34</v>
       </c>
       <c r="S2">
-        <v>433.09</v>
+        <v>432.77</v>
       </c>
       <c r="T2">
-        <v>-14.67</v>
+        <v>-15.74</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1009,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.71</v>
+        <v>34.2</v>
       </c>
       <c r="Z2">
-        <v>-4.57</v>
+        <v>-5.17</v>
       </c>
       <c r="AA2">
-        <v>-4.57</v>
+        <v>-4.69</v>
       </c>
       <c r="AB2">
-        <v>-0</v>
+        <v>-0.48</v>
       </c>
       <c r="AC2">
-        <v>35.88</v>
+        <v>11.96</v>
       </c>
       <c r="AD2">
-        <v>52.41</v>
+        <v>32.9</v>
       </c>
       <c r="AE2">
-        <v>8.41</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AF2">
-        <v>-12.85</v>
+        <v>-28.6</v>
       </c>
       <c r="AG2">
-        <v>392.21</v>
+        <v>391.44</v>
       </c>
       <c r="AH2">
-        <v>366.84</v>
+        <v>365.01</v>
       </c>
       <c r="AI2">
-        <v>396.4</v>
+        <v>391.31</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>29.85</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2889</v>
+        <v>2864.1</v>
       </c>
       <c r="D3">
-        <v>-0.62</v>
+        <v>-0.86</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1068,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-24.02</v>
+        <v>-24.68</v>
       </c>
       <c r="H3">
-        <v>5.01</v>
+        <v>4.1</v>
       </c>
       <c r="I3">
-        <v>0.86</v>
+        <v>2.52</v>
       </c>
       <c r="J3">
-        <v>-5.34</v>
+        <v>-6.26</v>
       </c>
       <c r="K3">
-        <v>-9.77</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L3">
-        <v>-17.39</v>
+        <v>-19.57</v>
       </c>
       <c r="M3">
-        <v>27.27</v>
+        <v>27.31</v>
       </c>
       <c r="N3">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P3">
-        <v>2874.46</v>
+        <v>2888.54</v>
       </c>
       <c r="Q3">
-        <v>2897.98</v>
+        <v>2888.96</v>
       </c>
       <c r="R3">
-        <v>3124.3</v>
+        <v>3111.25</v>
       </c>
       <c r="S3">
-        <v>3228.65</v>
+        <v>3224.16</v>
       </c>
       <c r="T3">
-        <v>-10.52</v>
+        <v>-11.17</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1122,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.5</v>
+        <v>41.34</v>
       </c>
       <c r="Z3">
-        <v>-66.63</v>
+        <v>-62.92</v>
       </c>
       <c r="AA3">
-        <v>-85.59</v>
+        <v>-81.05</v>
       </c>
       <c r="AB3">
-        <v>18.96</v>
+        <v>18.14</v>
       </c>
       <c r="AC3">
-        <v>95.31999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="AD3">
-        <v>94.93000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="AE3">
-        <v>67.63</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AF3">
-        <v>-5.75</v>
+        <v>-31.15</v>
       </c>
       <c r="AG3">
-        <v>3074.77</v>
+        <v>3052.16</v>
       </c>
       <c r="AH3">
-        <v>2721.2</v>
+        <v>2725.77</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1145,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.39</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>297.45</v>
+        <v>287.6</v>
       </c>
       <c r="D4">
-        <v>-2.44</v>
+        <v>-3.31</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1181,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-27.86</v>
+        <v>-30.24</v>
       </c>
       <c r="H4">
-        <v>7.89</v>
+        <v>4.32</v>
       </c>
       <c r="I4">
-        <v>-8.69</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="J4">
-        <v>-15.81</v>
+        <v>-18.92</v>
       </c>
       <c r="K4">
-        <v>-14.98</v>
+        <v>-23.95</v>
       </c>
       <c r="L4">
-        <v>1.23</v>
+        <v>-1.94</v>
       </c>
       <c r="M4">
-        <v>10.95</v>
+        <v>10.75</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="O4">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>309.9</v>
+        <v>303.53</v>
       </c>
       <c r="Q4">
-        <v>324.09</v>
+        <v>320.85</v>
       </c>
       <c r="R4">
-        <v>354.64</v>
+        <v>352.15</v>
       </c>
       <c r="S4">
-        <v>339.89</v>
+        <v>339.31</v>
       </c>
       <c r="T4">
-        <v>-12.49</v>
+        <v>-15.24</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,43 +1235,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.69</v>
+        <v>23.37</v>
       </c>
       <c r="Z4">
-        <v>-12.86</v>
+        <v>-14.19</v>
       </c>
       <c r="AA4">
-        <v>-11.86</v>
+        <v>-12.33</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>-1.86</v>
       </c>
       <c r="AC4">
-        <v>31.42</v>
+        <v>14.38</v>
       </c>
       <c r="AD4">
-        <v>48.59</v>
+        <v>31.77</v>
       </c>
       <c r="AE4">
-        <v>10.62</v>
+        <v>11.95</v>
       </c>
       <c r="AF4">
-        <v>43.84</v>
+        <v>665.96</v>
       </c>
       <c r="AG4">
-        <v>350.77</v>
+        <v>348.76</v>
       </c>
       <c r="AH4">
-        <v>297.4</v>
+        <v>292.93</v>
       </c>
       <c r="AI4">
-        <v>333.49</v>
+        <v>314.97</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>37.09</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>340.75</v>
+        <v>351.3</v>
       </c>
       <c r="D5">
-        <v>-0.9399999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1294,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-19.2</v>
+        <v>-16.69</v>
       </c>
       <c r="H5">
-        <v>15.8</v>
+        <v>19.39</v>
       </c>
       <c r="I5">
-        <v>-2.77</v>
+        <v>1.17</v>
       </c>
       <c r="J5">
-        <v>-7</v>
+        <v>-3.13</v>
       </c>
       <c r="K5">
-        <v>-7.71</v>
+        <v>-6.09</v>
       </c>
       <c r="L5">
-        <v>-10.93</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="M5">
-        <v>4.47</v>
+        <v>5.32</v>
       </c>
       <c r="N5">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>345.04</v>
+        <v>345.85</v>
       </c>
       <c r="Q5">
-        <v>351.49</v>
+        <v>351.1</v>
       </c>
       <c r="R5">
-        <v>362.29</v>
+        <v>361.58</v>
       </c>
       <c r="S5">
-        <v>356.18</v>
+        <v>355.97</v>
       </c>
       <c r="T5">
-        <v>-4.33</v>
+        <v>-1.31</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.18</v>
+        <v>48.74</v>
       </c>
       <c r="Z5">
-        <v>-5</v>
+        <v>-4.34</v>
       </c>
       <c r="AA5">
-        <v>-4.66</v>
+        <v>-4.6</v>
       </c>
       <c r="AB5">
-        <v>-0.34</v>
+        <v>0.26</v>
       </c>
       <c r="AC5">
-        <v>52.37</v>
+        <v>61.39</v>
       </c>
       <c r="AD5">
-        <v>50.62</v>
+        <v>54.63</v>
       </c>
       <c r="AE5">
-        <v>11.52</v>
+        <v>12.8</v>
       </c>
       <c r="AF5">
-        <v>-23.46</v>
+        <v>2066.04</v>
       </c>
       <c r="AG5">
-        <v>364.48</v>
+        <v>363.59</v>
       </c>
       <c r="AH5">
-        <v>338.49</v>
+        <v>338.6</v>
       </c>
       <c r="AI5">
         <v>376.5</v>
@@ -1371,7 +1384,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>34.35</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>389.25</v>
+        <v>383.6</v>
       </c>
       <c r="D6">
-        <v>-2.08</v>
+        <v>-1.45</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1407,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-12.07</v>
+        <v>-13.35</v>
       </c>
       <c r="H6">
-        <v>39.24</v>
+        <v>37.22</v>
       </c>
       <c r="I6">
-        <v>-5.01</v>
+        <v>-8.99</v>
       </c>
       <c r="J6">
-        <v>-0.89</v>
+        <v>-3.93</v>
       </c>
       <c r="K6">
-        <v>-0.49</v>
+        <v>-4.61</v>
       </c>
       <c r="L6">
-        <v>11.93</v>
+        <v>9.27</v>
       </c>
       <c r="M6">
-        <v>-10.67</v>
+        <v>-10.73</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P6">
-        <v>405.89</v>
+        <v>398.31</v>
       </c>
       <c r="Q6">
-        <v>411.18</v>
+        <v>410.34</v>
       </c>
       <c r="R6">
-        <v>404.34</v>
+        <v>403.78</v>
       </c>
       <c r="S6">
-        <v>380.73</v>
+        <v>381.05</v>
       </c>
       <c r="T6">
-        <v>2.24</v>
+        <v>0.67</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,43 +1461,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>41.05</v>
+        <v>38.72</v>
       </c>
       <c r="Z6">
-        <v>-0.88</v>
+        <v>-2.54</v>
       </c>
       <c r="AA6">
-        <v>1.42</v>
+        <v>0.63</v>
       </c>
       <c r="AB6">
-        <v>-2.3</v>
+        <v>-3.17</v>
       </c>
       <c r="AC6">
-        <v>10.19</v>
+        <v>1.81</v>
       </c>
       <c r="AD6">
-        <v>21.37</v>
+        <v>10.65</v>
       </c>
       <c r="AE6">
-        <v>14.24</v>
+        <v>14.15</v>
       </c>
       <c r="AF6">
-        <v>-33.81</v>
+        <v>-25.22</v>
       </c>
       <c r="AG6">
-        <v>434.59</v>
+        <v>436.43</v>
       </c>
       <c r="AH6">
-        <v>387.77</v>
+        <v>384.26</v>
       </c>
       <c r="AI6">
-        <v>434.57</v>
+        <v>428.57</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>25.56</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>560.85</v>
+        <v>539.3</v>
       </c>
       <c r="D7">
-        <v>-2.47</v>
+        <v>-3.84</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1507,97 +1520,97 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-23.97</v>
+        <v>-26.89</v>
       </c>
       <c r="H7">
-        <v>10.74</v>
+        <v>6.49</v>
       </c>
       <c r="I7">
-        <v>-5.01</v>
+        <v>-10.95</v>
       </c>
       <c r="J7">
-        <v>-21.84</v>
+        <v>-23.71</v>
       </c>
       <c r="K7">
-        <v>-3.31</v>
+        <v>-6.28</v>
       </c>
       <c r="L7">
-        <v>-3.33</v>
+        <v>-7.03</v>
       </c>
       <c r="M7">
-        <v>18.78</v>
+        <v>17.78</v>
       </c>
       <c r="N7">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O7">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P7">
-        <v>584.73</v>
+        <v>571.47</v>
       </c>
       <c r="Q7">
-        <v>657.1799999999999</v>
+        <v>649.28</v>
       </c>
       <c r="R7">
-        <v>656.92</v>
+        <v>655.55</v>
       </c>
       <c r="S7">
-        <v>603.42</v>
+        <v>603.35</v>
       </c>
       <c r="T7">
-        <v>-7.06</v>
+        <v>-10.62</v>
       </c>
       <c r="U7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
         <v>48</v>
       </c>
       <c r="W7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>27.39</v>
+        <v>24.47</v>
       </c>
       <c r="Z7">
-        <v>-27.76</v>
+        <v>-31.67</v>
       </c>
       <c r="AA7">
-        <v>-14.02</v>
+        <v>-17.55</v>
       </c>
       <c r="AB7">
-        <v>-13.74</v>
+        <v>-14.12</v>
       </c>
       <c r="AC7">
-        <v>1.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AD7">
-        <v>5.11</v>
+        <v>2.11</v>
       </c>
       <c r="AE7">
-        <v>26.95</v>
+        <v>26.87</v>
       </c>
       <c r="AF7">
-        <v>-42.02</v>
+        <v>-19.19</v>
       </c>
       <c r="AG7">
-        <v>773.65</v>
+        <v>775.33</v>
       </c>
       <c r="AH7">
-        <v>540.71</v>
+        <v>523.23</v>
       </c>
       <c r="AI7">
-        <v>648.33</v>
+        <v>630.73</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>45.02</v>
+        <v>48.31</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>198.8</v>
+        <v>191.6</v>
       </c>
       <c r="D8">
-        <v>0.36</v>
+        <v>-3.62</v>
       </c>
       <c r="E8">
         <v>338.7</v>
@@ -1620,46 +1633,46 @@
         <v>187.23</v>
       </c>
       <c r="G8">
-        <v>-41.3</v>
+        <v>-43.43</v>
       </c>
       <c r="H8">
-        <v>6.18</v>
+        <v>2.33</v>
       </c>
       <c r="I8">
-        <v>4.08</v>
+        <v>-4.52</v>
       </c>
       <c r="J8">
-        <v>-0.25</v>
+        <v>-4.85</v>
       </c>
       <c r="K8">
-        <v>-12.8</v>
+        <v>-9.49</v>
       </c>
       <c r="L8">
-        <v>-40.69</v>
+        <v>-42.37</v>
       </c>
       <c r="M8">
-        <v>-3.89</v>
+        <v>-5.09</v>
       </c>
       <c r="N8">
         <v>11</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8">
-        <v>199.6</v>
+        <v>197.79</v>
       </c>
       <c r="Q8">
-        <v>196.16</v>
+        <v>195.79</v>
       </c>
       <c r="R8">
-        <v>205.42</v>
+        <v>204.65</v>
       </c>
       <c r="S8">
-        <v>242.66</v>
+        <v>242.08</v>
       </c>
       <c r="T8">
-        <v>-18.08</v>
+        <v>-20.85</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1687,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>50.06</v>
+        <v>40.94</v>
       </c>
       <c r="Z8">
-        <v>-1.68</v>
+        <v>-1.97</v>
       </c>
       <c r="AA8">
-        <v>-3.11</v>
+        <v>-2.88</v>
       </c>
       <c r="AB8">
-        <v>1.43</v>
+        <v>0.91</v>
       </c>
       <c r="AC8">
-        <v>90.48</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AD8">
-        <v>93.53</v>
+        <v>85.78</v>
       </c>
       <c r="AE8">
-        <v>7.35</v>
+        <v>7.42</v>
       </c>
       <c r="AF8">
-        <v>2256.52</v>
+        <v>39.61</v>
       </c>
       <c r="AG8">
-        <v>204.43</v>
+        <v>204.18</v>
       </c>
       <c r="AH8">
-        <v>187.89</v>
+        <v>187.39</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1710,7 +1723,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>33.11</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,58 +1734,58 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3496.8</v>
+        <v>3403.2</v>
       </c>
       <c r="D9">
-        <v>-1.36</v>
+        <v>-2.68</v>
       </c>
       <c r="E9">
-        <v>4119.6</v>
+        <v>4103.5</v>
       </c>
       <c r="F9">
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-15.12</v>
+        <v>-17.07</v>
       </c>
       <c r="H9">
-        <v>5.68</v>
+        <v>2.85</v>
       </c>
       <c r="I9">
-        <v>-4.77</v>
+        <v>-6.4</v>
       </c>
       <c r="J9">
-        <v>-3.54</v>
+        <v>-4.74</v>
       </c>
       <c r="K9">
-        <v>-3.05</v>
+        <v>-5.13</v>
       </c>
       <c r="L9">
-        <v>-19.38</v>
+        <v>-17.39</v>
       </c>
       <c r="M9">
-        <v>18.08</v>
+        <v>18.48</v>
       </c>
       <c r="N9">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="O9">
         <v>54</v>
       </c>
       <c r="P9">
-        <v>3542.56</v>
+        <v>3496.02</v>
       </c>
       <c r="Q9">
-        <v>3553.46</v>
+        <v>3545.82</v>
       </c>
       <c r="R9">
-        <v>3569.75</v>
+        <v>3565.77</v>
       </c>
       <c r="S9">
-        <v>3669.46</v>
+        <v>3667.84</v>
       </c>
       <c r="T9">
-        <v>-4.71</v>
+        <v>-7.22</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,43 +1800,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.4</v>
+        <v>38.19</v>
       </c>
       <c r="Z9">
-        <v>-8.279999999999999</v>
+        <v>-19.56</v>
       </c>
       <c r="AA9">
-        <v>-4.68</v>
+        <v>-7.65</v>
       </c>
       <c r="AB9">
-        <v>-3.61</v>
+        <v>-11.91</v>
       </c>
       <c r="AC9">
-        <v>43.64</v>
+        <v>36.91</v>
       </c>
       <c r="AD9">
-        <v>46.81</v>
+        <v>41.86</v>
       </c>
       <c r="AE9">
-        <v>105.22</v>
+        <v>105.48</v>
       </c>
       <c r="AF9">
-        <v>-86.41</v>
+        <v>-82.3</v>
       </c>
       <c r="AG9">
-        <v>3682.35</v>
+        <v>3691.14</v>
       </c>
       <c r="AH9">
-        <v>3424.57</v>
+        <v>3400.5</v>
       </c>
       <c r="AI9">
-        <v>3421.87</v>
+        <v>3759.99</v>
       </c>
       <c r="AJ9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.77</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1834.7</v>
+        <v>1829.1</v>
       </c>
       <c r="D10">
-        <v>3.13</v>
+        <v>-0.31</v>
       </c>
       <c r="E10">
         <v>1834.7</v>
@@ -1846,25 +1859,25 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="H10">
-        <v>38.34</v>
+        <v>37.92</v>
       </c>
       <c r="I10">
-        <v>18.87</v>
+        <v>16.12</v>
       </c>
       <c r="J10">
-        <v>19.36</v>
+        <v>17.36</v>
       </c>
       <c r="K10">
-        <v>16.39</v>
+        <v>17.2</v>
       </c>
       <c r="L10">
-        <v>27.07</v>
+        <v>26.26</v>
       </c>
       <c r="M10">
-        <v>6.91</v>
+        <v>6.94</v>
       </c>
       <c r="N10">
         <v>99</v>
@@ -1873,70 +1886,70 @@
         <v>89</v>
       </c>
       <c r="P10">
-        <v>1725.8</v>
+        <v>1776.58</v>
       </c>
       <c r="Q10">
-        <v>1574.73</v>
+        <v>1588.6</v>
       </c>
       <c r="R10">
-        <v>1583.91</v>
+        <v>1587.69</v>
       </c>
       <c r="S10">
-        <v>1517.36</v>
+        <v>1518.46</v>
       </c>
       <c r="T10">
-        <v>20.91</v>
+        <v>20.46</v>
       </c>
       <c r="U10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V10" t="s">
         <v>48</v>
       </c>
       <c r="W10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10">
-        <v>76.81</v>
+        <v>75.84</v>
       </c>
       <c r="Z10">
-        <v>47.8</v>
+        <v>58.73</v>
       </c>
       <c r="AA10">
-        <v>10.37</v>
+        <v>20.04</v>
       </c>
       <c r="AB10">
-        <v>37.43</v>
+        <v>38.68</v>
       </c>
       <c r="AC10">
-        <v>98.48999999999999</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="AD10">
-        <v>98.98999999999999</v>
+        <v>98.23</v>
       </c>
       <c r="AE10">
-        <v>52.61</v>
+        <v>53.09</v>
       </c>
       <c r="AF10">
-        <v>54.99</v>
+        <v>12.17</v>
       </c>
       <c r="AG10">
-        <v>1784.21</v>
+        <v>1826.47</v>
       </c>
       <c r="AH10">
-        <v>1365.25</v>
+        <v>1350.74</v>
       </c>
       <c r="AI10">
-        <v>1654.51</v>
+        <v>1655.18</v>
       </c>
       <c r="AJ10" t="s">
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>39.39</v>
+        <v>44.11</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,1312 +2130,1443 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C11" s="7">
         <v>-4.55</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-7.72</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C12" s="7">
         <v>-5.34</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-6.26</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-11.8</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C13" s="7">
         <v>-15.81</v>
       </c>
-      <c r="E9" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-18.92</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C14" s="7">
         <v>-7</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-3.13</v>
+      </c>
+      <c r="E14" s="9">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>2.04</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C15" s="7">
         <v>-0.89</v>
       </c>
-      <c r="E11" s="7">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-20.15</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C16" s="7">
         <v>-21.84</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-23.71</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>1.49</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C17" s="7">
         <v>-0.25</v>
       </c>
-      <c r="E13" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D17" s="7">
+        <v>-4.85</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>-0.22</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C18" s="7">
         <v>-3.54</v>
       </c>
-      <c r="E14" s="7">
+      <c r="D18" s="7">
+        <v>-4.74</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="7">
+        <v>19.36</v>
+      </c>
+      <c r="D19" s="7">
+        <v>17.36</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-2.94</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.15</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.86</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.52</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-8.69</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="E23" s="9">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-5.01</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-8.99</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-3.98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-5.01</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-10.95</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-5.94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>4.08</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-4.52</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-8.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-4.77</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-6.4</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="7">
+        <v>18.87</v>
+      </c>
+      <c r="D28" s="7">
+        <v>16.12</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-9.9</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-13.19</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-3.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-17.39</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-19.57</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1.23</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-1.94</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-10.93</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E32" s="9">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>11.93</v>
+      </c>
+      <c r="D33" s="7">
+        <v>9.27</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-3.33</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-7.03</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-40.69</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-42.37</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-19.38</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-17.39</v>
+      </c>
+      <c r="E36" s="9">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="7">
+        <v>27.07</v>
+      </c>
+      <c r="D37" s="7">
+        <v>26.26</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-21.82</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-22.83</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-9.77</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-14.98</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-23.95</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-8.970000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-7.71</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-6.09</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-0.49</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-4.61</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-3.31</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-6.28</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-12.8</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-9.49</v>
+      </c>
+      <c r="E44" s="9">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-3.05</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-5.13</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="7">
+        <v>16.39</v>
+      </c>
+      <c r="D46" s="7">
+        <v>17.2</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-24.61</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-25.61</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-24.02</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-24.68</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-27.86</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-30.24</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-19.2</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-16.69</v>
+      </c>
+      <c r="E50" s="9">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-12.07</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-13.35</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-23.97</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-26.89</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-41.3</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-43.43</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-15.12</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-17.07</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0</v>
+      </c>
+      <c r="D55" s="7">
+        <v>-0.31</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>369.55</v>
+      </c>
+      <c r="D56" s="7">
+        <v>364.65</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>2889</v>
+      </c>
+      <c r="D57" s="7">
+        <v>2864.1</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-24.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>297.45</v>
+      </c>
+      <c r="D58" s="7">
+        <v>287.6</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-9.85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>340.75</v>
+      </c>
+      <c r="D59" s="7">
+        <v>351.3</v>
+      </c>
+      <c r="E59" s="9">
+        <v>10.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>389.25</v>
+      </c>
+      <c r="D60" s="7">
+        <v>383.6</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-5.65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>560.85</v>
+      </c>
+      <c r="D61" s="7">
+        <v>539.3</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-21.55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>198.8</v>
+      </c>
+      <c r="D62" s="7">
+        <v>191.6</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-7.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>3496.8</v>
+      </c>
+      <c r="D63" s="7">
+        <v>3403.2</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-93.59999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="7">
+        <v>1834.7</v>
+      </c>
+      <c r="D64" s="7">
+        <v>1829.1</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>33</v>
+      </c>
+      <c r="D65" s="7">
+        <v>44</v>
+      </c>
+      <c r="E65" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
+        <v>66</v>
+      </c>
+      <c r="D66" s="7">
+        <v>33</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7">
+        <v>55</v>
+      </c>
+      <c r="D67" s="7">
+        <v>77</v>
+      </c>
+      <c r="E67" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="7">
+        <v>77</v>
+      </c>
+      <c r="D68" s="7">
+        <v>55</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="7">
+        <v>44</v>
+      </c>
+      <c r="D69" s="7">
+        <v>66</v>
+      </c>
+      <c r="E69" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>37.71</v>
+      </c>
+      <c r="D70" s="7">
+        <v>34.2</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>43.5</v>
+      </c>
+      <c r="D71" s="7">
+        <v>41.34</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>26.69</v>
+      </c>
+      <c r="D72" s="7">
+        <v>23.37</v>
+      </c>
+      <c r="E72" s="8">
         <v>-3.32</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>39.18</v>
+      </c>
+      <c r="D73" s="7">
+        <v>48.74</v>
+      </c>
+      <c r="E73" s="9">
+        <v>9.56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>41.05</v>
+      </c>
+      <c r="D74" s="7">
+        <v>38.72</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>27.39</v>
+      </c>
+      <c r="D75" s="7">
+        <v>24.47</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="7">
+        <v>50.06</v>
+      </c>
+      <c r="D76" s="7">
+        <v>40.94</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-9.119999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="7">
+        <v>44.4</v>
+      </c>
+      <c r="D77" s="7">
+        <v>38.19</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-6.21</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>13.97</v>
-      </c>
-      <c r="D15" s="6">
-        <v>19.36</v>
-      </c>
-      <c r="E15" s="8">
-        <v>5.39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="7">
+        <v>76.81</v>
+      </c>
+      <c r="D78" s="7">
+        <v>75.84</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-12.85</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-28.6</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-15.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>3.34</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-5.75</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-31.15</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-25.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.43</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-8.69</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>43.84</v>
+      </c>
+      <c r="D81" s="7">
+        <v>665.96</v>
+      </c>
+      <c r="E81" s="9">
+        <v>622.12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.72</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-23.46</v>
+      </c>
+      <c r="D82" s="7">
+        <v>2066.04</v>
+      </c>
+      <c r="E82" s="9">
+        <v>2089.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>-33.81</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-25.22</v>
+      </c>
+      <c r="E83" s="9">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.22</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-42.02</v>
+      </c>
+      <c r="D84" s="7">
+        <v>-19.19</v>
+      </c>
+      <c r="E84" s="9">
+        <v>22.83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="D22" s="6">
-        <v>4.08</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B85" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="7">
+        <v>2256.52</v>
+      </c>
+      <c r="D85" s="7">
+        <v>39.61</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-2216.91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-5.17</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.77</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B86" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="7">
+        <v>-86.41</v>
+      </c>
+      <c r="D86" s="7">
+        <v>-82.3</v>
+      </c>
+      <c r="E86" s="9">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>20.94</v>
-      </c>
-      <c r="D24" s="6">
-        <v>18.87</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-9.9</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-15.98</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-17.39</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>6.07</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-4.84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-6.56</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-10.93</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>13.72</v>
-      </c>
-      <c r="D29" s="6">
-        <v>11.93</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-40.83</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-40.69</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-18.68</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-19.38</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>22.46</v>
-      </c>
-      <c r="D33" s="6">
-        <v>27.07</v>
-      </c>
-      <c r="E33" s="8">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-21.61</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-21.82</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.17</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-9.77</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-14.98</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-9.51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-7.82</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.71</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-0.49</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-1.65</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-12.57</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-12.8</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.57</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-3.05</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>12.86</v>
-      </c>
-      <c r="D42" s="6">
-        <v>16.39</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-24.24</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-24.61</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-23.55</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-24.02</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-26.05</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-27.86</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-18.43</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-19.2</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-12.07</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-23.97</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-41.52</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-41.3</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-18.27</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-15.12</v>
-      </c>
-      <c r="E50" s="8">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="D51" s="6">
-        <v>0</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>371.4</v>
-      </c>
-      <c r="D52" s="6">
-        <v>369.55</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2907</v>
-      </c>
-      <c r="D53" s="6">
-        <v>2889</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>304.9</v>
-      </c>
-      <c r="D54" s="6">
-        <v>297.45</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-7.45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>344</v>
-      </c>
-      <c r="D55" s="6">
-        <v>340.75</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>397.5</v>
-      </c>
-      <c r="D56" s="6">
-        <v>389.25</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-8.25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>575.05</v>
-      </c>
-      <c r="D57" s="6">
-        <v>560.85</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-14.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>198.08</v>
-      </c>
-      <c r="D58" s="6">
-        <v>198.8</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>3545</v>
-      </c>
-      <c r="D59" s="6">
-        <v>3496.8</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-48.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>1779.1</v>
-      </c>
-      <c r="D60" s="6">
-        <v>1834.7</v>
-      </c>
-      <c r="E60" s="8">
-        <v>55.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>77</v>
-      </c>
-      <c r="D61" s="6">
-        <v>66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>66</v>
-      </c>
-      <c r="D62" s="6">
-        <v>77</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>39.12</v>
-      </c>
-      <c r="D63" s="6">
-        <v>37.71</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>45.08</v>
-      </c>
-      <c r="D64" s="6">
-        <v>43.5</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>29.64</v>
-      </c>
-      <c r="D65" s="6">
-        <v>26.69</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>41.39</v>
-      </c>
-      <c r="D66" s="6">
-        <v>39.18</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>44.69</v>
-      </c>
-      <c r="D67" s="6">
-        <v>41.05</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>29.54</v>
-      </c>
-      <c r="D68" s="6">
-        <v>27.39</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>49.01</v>
-      </c>
-      <c r="D69" s="6">
-        <v>50.06</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>48.15</v>
-      </c>
-      <c r="D70" s="6">
-        <v>44.4</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>73.73</v>
-      </c>
-      <c r="D71" s="6">
-        <v>76.81</v>
-      </c>
-      <c r="E71" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B87" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-42.41</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-12.85</v>
-      </c>
-      <c r="E72" s="8">
-        <v>29.56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-16.42</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="E73" s="8">
-        <v>10.67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>35.72</v>
-      </c>
-      <c r="D74" s="6">
-        <v>43.84</v>
-      </c>
-      <c r="E74" s="8">
-        <v>8.119999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-25.96</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-23.46</v>
-      </c>
-      <c r="E75" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-36.24</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-33.81</v>
-      </c>
-      <c r="E76" s="8">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-24.63</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-42.02</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-17.39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-32.01</v>
-      </c>
-      <c r="D78" s="6">
-        <v>2256.52</v>
-      </c>
-      <c r="E78" s="8">
-        <v>2288.53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-82.81</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-86.41</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>14.25</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C87" s="7">
         <v>54.99</v>
       </c>
-      <c r="E80" s="8">
-        <v>40.74</v>
+      <c r="D87" s="7">
+        <v>12.17</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-42.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3442,60 +3586,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="F1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>40.88</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>43</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>40.6</v>
+      </c>
+      <c r="E2" s="12">
         <v>22.2</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-6.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-6.2</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-7.9</v>
+      </c>
+      <c r="H2" s="12">
         <v>55</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>22.2</v>
       </c>
     </row>
@@ -3597,61 +3741,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.2727</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1878</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1808</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1095</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0697</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.06909999999999999</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0447</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0389</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1067</v>
+      <c r="A2" s="15">
+        <v>0.2731</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1848</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1778</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1075</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0732</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0694</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0532</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0509</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1073</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,31 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.1 → 40.9</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>40.9</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>75.8 → 69.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>75.8</t>
+  </si>
+  <si>
+    <t>69.3</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.3% → -2.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-0.3%</t>
+  </si>
+  <si>
+    <t>-2.4%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -269,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,7 +306,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -315,8 +318,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,13 +353,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -427,15 +443,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -444,7 +459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -943,58 +958,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>364.65</v>
+        <v>351.55</v>
       </c>
       <c r="D2">
-        <v>-1.33</v>
+        <v>-3.59</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>364.65</v>
+        <v>351.55</v>
       </c>
       <c r="G2">
-        <v>-25.61</v>
+        <v>-28.28</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.15</v>
+        <v>-6.65</v>
       </c>
       <c r="J2">
-        <v>-7.72</v>
+        <v>-10</v>
       </c>
       <c r="K2">
-        <v>-22.83</v>
+        <v>-16.1</v>
       </c>
       <c r="L2">
-        <v>-13.19</v>
+        <v>-17.43</v>
       </c>
       <c r="M2">
-        <v>7.32</v>
+        <v>5.95</v>
       </c>
       <c r="N2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P2">
-        <v>371.88</v>
+        <v>366.87</v>
       </c>
       <c r="Q2">
-        <v>378.23</v>
+        <v>376.6</v>
       </c>
       <c r="R2">
-        <v>387.34</v>
+        <v>386.11</v>
       </c>
       <c r="S2">
-        <v>432.77</v>
+        <v>432.42</v>
       </c>
       <c r="T2">
-        <v>-15.74</v>
+        <v>-18.7</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,43 +1024,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.2</v>
+        <v>26.97</v>
       </c>
       <c r="Z2">
-        <v>-5.17</v>
+        <v>-6.62</v>
       </c>
       <c r="AA2">
-        <v>-4.69</v>
+        <v>-5.08</v>
       </c>
       <c r="AB2">
-        <v>-0.48</v>
+        <v>-1.54</v>
       </c>
       <c r="AC2">
-        <v>11.96</v>
+        <v>3.68</v>
       </c>
       <c r="AD2">
-        <v>32.9</v>
+        <v>17.17</v>
       </c>
       <c r="AE2">
-        <v>8.300000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AF2">
-        <v>-28.6</v>
+        <v>269.64</v>
       </c>
       <c r="AG2">
-        <v>391.44</v>
+        <v>394.08</v>
       </c>
       <c r="AH2">
-        <v>365.01</v>
+        <v>359.11</v>
       </c>
       <c r="AI2">
-        <v>391.31</v>
+        <v>377.4</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>33.41</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1071,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2864.1</v>
+        <v>2861.2</v>
       </c>
       <c r="D3">
-        <v>-0.86</v>
+        <v>-0.1</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1068,46 +1083,46 @@
         <v>2751.2</v>
       </c>
       <c r="G3">
-        <v>-24.68</v>
+        <v>-24.75</v>
       </c>
       <c r="H3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2.52</v>
+        <v>-0.02</v>
       </c>
       <c r="J3">
-        <v>-6.26</v>
+        <v>-6.02</v>
       </c>
       <c r="K3">
-        <v>-9.800000000000001</v>
+        <v>-11.41</v>
       </c>
       <c r="L3">
-        <v>-19.57</v>
+        <v>-21.55</v>
       </c>
       <c r="M3">
-        <v>27.31</v>
+        <v>27.24</v>
       </c>
       <c r="N3">
         <v>44</v>
       </c>
       <c r="O3">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P3">
-        <v>2888.54</v>
+        <v>2888.44</v>
       </c>
       <c r="Q3">
-        <v>2888.96</v>
+        <v>2880.27</v>
       </c>
       <c r="R3">
-        <v>3111.25</v>
+        <v>3099.27</v>
       </c>
       <c r="S3">
-        <v>3224.16</v>
+        <v>3219.46</v>
       </c>
       <c r="T3">
-        <v>-11.17</v>
+        <v>-11.13</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1122,34 +1137,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.34</v>
+        <v>41.09</v>
       </c>
       <c r="Z3">
-        <v>-62.92</v>
+        <v>-59.52</v>
       </c>
       <c r="AA3">
-        <v>-81.05</v>
+        <v>-76.75</v>
       </c>
       <c r="AB3">
-        <v>18.14</v>
+        <v>17.23</v>
       </c>
       <c r="AC3">
-        <v>89.53</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="AD3">
-        <v>94.48</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AE3">
-        <v>67.84999999999999</v>
+        <v>67.41</v>
       </c>
       <c r="AF3">
-        <v>-31.15</v>
+        <v>-11.23</v>
       </c>
       <c r="AG3">
-        <v>3052.16</v>
+        <v>3028.55</v>
       </c>
       <c r="AH3">
-        <v>2725.77</v>
+        <v>2732</v>
       </c>
       <c r="AI3">
         <v>2961.3</v>
@@ -1158,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>44.16</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1184,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>287.6</v>
+        <v>276.9</v>
       </c>
       <c r="D4">
-        <v>-3.31</v>
+        <v>-3.72</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1181,46 +1196,46 @@
         <v>275.7</v>
       </c>
       <c r="G4">
-        <v>-30.24</v>
+        <v>-32.84</v>
       </c>
       <c r="H4">
-        <v>4.32</v>
+        <v>0.44</v>
       </c>
       <c r="I4">
-        <v>-9.970000000000001</v>
+        <v>-12.41</v>
       </c>
       <c r="J4">
-        <v>-18.92</v>
+        <v>-21.42</v>
       </c>
       <c r="K4">
-        <v>-23.95</v>
+        <v>-25.23</v>
       </c>
       <c r="L4">
-        <v>-1.94</v>
+        <v>-7.73</v>
       </c>
       <c r="M4">
-        <v>10.75</v>
+        <v>10.67</v>
       </c>
       <c r="N4">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>303.53</v>
+        <v>295.68</v>
       </c>
       <c r="Q4">
-        <v>320.85</v>
+        <v>317.26</v>
       </c>
       <c r="R4">
-        <v>352.15</v>
+        <v>349.71</v>
       </c>
       <c r="S4">
-        <v>339.31</v>
+        <v>338.68</v>
       </c>
       <c r="T4">
-        <v>-15.24</v>
+        <v>-18.24</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1235,34 +1250,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>23.37</v>
+        <v>20.41</v>
       </c>
       <c r="Z4">
-        <v>-14.19</v>
+        <v>-15.92</v>
       </c>
       <c r="AA4">
-        <v>-12.33</v>
+        <v>-13.05</v>
       </c>
       <c r="AB4">
-        <v>-1.86</v>
+        <v>-2.88</v>
       </c>
       <c r="AC4">
-        <v>14.38</v>
+        <v>3.93</v>
       </c>
       <c r="AD4">
-        <v>31.77</v>
+        <v>16.58</v>
       </c>
       <c r="AE4">
-        <v>11.95</v>
+        <v>12.37</v>
       </c>
       <c r="AF4">
-        <v>665.96</v>
+        <v>25.36</v>
       </c>
       <c r="AG4">
-        <v>348.76</v>
+        <v>348.4</v>
       </c>
       <c r="AH4">
-        <v>292.93</v>
+        <v>286.12</v>
       </c>
       <c r="AI4">
         <v>314.97</v>
@@ -1271,7 +1286,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>42.61</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1297,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>351.3</v>
+        <v>335.2</v>
       </c>
       <c r="D5">
-        <v>3.1</v>
+        <v>-4.58</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1294,46 +1309,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-16.69</v>
+        <v>-20.51</v>
       </c>
       <c r="H5">
-        <v>19.39</v>
+        <v>13.92</v>
       </c>
       <c r="I5">
-        <v>1.17</v>
+        <v>-2.33</v>
       </c>
       <c r="J5">
-        <v>-3.13</v>
+        <v>-6.64</v>
       </c>
       <c r="K5">
-        <v>-6.09</v>
+        <v>-11.21</v>
       </c>
       <c r="L5">
-        <v>-8.300000000000001</v>
+        <v>-12.3</v>
       </c>
       <c r="M5">
-        <v>5.32</v>
+        <v>5.21</v>
       </c>
       <c r="N5">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>345.85</v>
+        <v>344.25</v>
       </c>
       <c r="Q5">
-        <v>351.1</v>
+        <v>350.03</v>
       </c>
       <c r="R5">
-        <v>361.58</v>
+        <v>360.63</v>
       </c>
       <c r="S5">
-        <v>355.97</v>
+        <v>355.67</v>
       </c>
       <c r="T5">
-        <v>-1.31</v>
+        <v>-5.76</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1348,34 +1363,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>48.74</v>
+        <v>38.73</v>
       </c>
       <c r="Z5">
-        <v>-4.34</v>
+        <v>-5.06</v>
       </c>
       <c r="AA5">
-        <v>-4.6</v>
+        <v>-4.69</v>
       </c>
       <c r="AB5">
-        <v>0.26</v>
+        <v>-0.37</v>
       </c>
       <c r="AC5">
-        <v>61.39</v>
+        <v>54.55</v>
       </c>
       <c r="AD5">
-        <v>54.63</v>
+        <v>56.1</v>
       </c>
       <c r="AE5">
-        <v>12.8</v>
+        <v>13.19</v>
       </c>
       <c r="AF5">
-        <v>2066.04</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="AG5">
-        <v>363.59</v>
+        <v>364.1</v>
       </c>
       <c r="AH5">
-        <v>338.6</v>
+        <v>335.95</v>
       </c>
       <c r="AI5">
         <v>376.5</v>
@@ -1384,7 +1399,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>30.43</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1410,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>383.6</v>
+        <v>370.25</v>
       </c>
       <c r="D6">
-        <v>-1.45</v>
+        <v>-3.48</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1407,46 +1422,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-13.35</v>
+        <v>-16.37</v>
       </c>
       <c r="H6">
-        <v>37.22</v>
+        <v>32.45</v>
       </c>
       <c r="I6">
-        <v>-8.99</v>
+        <v>-10.08</v>
       </c>
       <c r="J6">
-        <v>-3.93</v>
+        <v>-7.51</v>
       </c>
       <c r="K6">
-        <v>-4.61</v>
+        <v>-5.51</v>
       </c>
       <c r="L6">
-        <v>9.27</v>
+        <v>6.78</v>
       </c>
       <c r="M6">
-        <v>-10.73</v>
+        <v>-10.97</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="P6">
-        <v>398.31</v>
+        <v>390.01</v>
       </c>
       <c r="Q6">
-        <v>410.34</v>
+        <v>408.03</v>
       </c>
       <c r="R6">
-        <v>403.78</v>
+        <v>403</v>
       </c>
       <c r="S6">
-        <v>381.05</v>
+        <v>381.31</v>
       </c>
       <c r="T6">
-        <v>0.67</v>
+        <v>-2.9</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1458,37 +1473,37 @@
         <v>48</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.72</v>
+        <v>33.83</v>
       </c>
       <c r="Z6">
-        <v>-2.54</v>
+        <v>-4.88</v>
       </c>
       <c r="AA6">
-        <v>0.63</v>
+        <v>-0.48</v>
       </c>
       <c r="AB6">
-        <v>-3.17</v>
+        <v>-4.4</v>
       </c>
       <c r="AC6">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>10.65</v>
+        <v>4</v>
       </c>
       <c r="AE6">
-        <v>14.15</v>
+        <v>16.15</v>
       </c>
       <c r="AF6">
-        <v>-25.22</v>
+        <v>475.26</v>
       </c>
       <c r="AG6">
-        <v>436.43</v>
+        <v>439.46</v>
       </c>
       <c r="AH6">
-        <v>384.26</v>
+        <v>376.6</v>
       </c>
       <c r="AI6">
         <v>428.57</v>
@@ -1497,7 +1512,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>27.31</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1523,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>539.3</v>
+        <v>532.7</v>
       </c>
       <c r="D7">
-        <v>-3.84</v>
+        <v>-1.22</v>
       </c>
       <c r="E7">
         <v>737.65</v>
@@ -1520,46 +1535,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-26.89</v>
+        <v>-27.78</v>
       </c>
       <c r="H7">
-        <v>6.49</v>
+        <v>5.18</v>
       </c>
       <c r="I7">
-        <v>-10.95</v>
+        <v>-10.73</v>
       </c>
       <c r="J7">
-        <v>-23.71</v>
+        <v>-23.61</v>
       </c>
       <c r="K7">
-        <v>-6.28</v>
+        <v>-5.73</v>
       </c>
       <c r="L7">
-        <v>-7.03</v>
+        <v>-6.25</v>
       </c>
       <c r="M7">
-        <v>17.78</v>
+        <v>18.07</v>
       </c>
       <c r="N7">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O7">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P7">
-        <v>571.47</v>
+        <v>558.66</v>
       </c>
       <c r="Q7">
-        <v>649.28</v>
+        <v>640.77</v>
       </c>
       <c r="R7">
-        <v>655.55</v>
+        <v>654.3</v>
       </c>
       <c r="S7">
-        <v>603.35</v>
+        <v>603.21</v>
       </c>
       <c r="T7">
-        <v>-10.62</v>
+        <v>-11.69</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1574,43 +1589,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>24.47</v>
+        <v>23.64</v>
       </c>
       <c r="Z7">
-        <v>-31.67</v>
+        <v>-34.9</v>
       </c>
       <c r="AA7">
-        <v>-17.55</v>
+        <v>-21.02</v>
       </c>
       <c r="AB7">
-        <v>-14.12</v>
+        <v>-13.88</v>
       </c>
       <c r="AC7">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>2.11</v>
+        <v>0.54</v>
       </c>
       <c r="AE7">
-        <v>26.87</v>
+        <v>26.06</v>
       </c>
       <c r="AF7">
-        <v>-19.19</v>
+        <v>-51.07</v>
       </c>
       <c r="AG7">
-        <v>775.33</v>
+        <v>774.35</v>
       </c>
       <c r="AH7">
-        <v>523.23</v>
+        <v>507.2</v>
       </c>
       <c r="AI7">
-        <v>630.73</v>
+        <v>610.45</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>48.31</v>
+        <v>51.66</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,58 +1636,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>191.6</v>
+        <v>185.47</v>
       </c>
       <c r="D8">
-        <v>-3.62</v>
+        <v>-3.2</v>
       </c>
       <c r="E8">
         <v>338.7</v>
       </c>
       <c r="F8">
-        <v>187.23</v>
+        <v>185.47</v>
       </c>
       <c r="G8">
-        <v>-43.43</v>
+        <v>-45.24</v>
       </c>
       <c r="H8">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.52</v>
+        <v>-7.02</v>
       </c>
       <c r="J8">
-        <v>-4.85</v>
+        <v>-6.83</v>
       </c>
       <c r="K8">
-        <v>-9.49</v>
+        <v>-14.95</v>
       </c>
       <c r="L8">
-        <v>-42.37</v>
+        <v>-44.05</v>
       </c>
       <c r="M8">
-        <v>-5.09</v>
+        <v>-4.53</v>
       </c>
       <c r="N8">
         <v>11</v>
       </c>
       <c r="O8">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P8">
-        <v>197.79</v>
+        <v>194.98</v>
       </c>
       <c r="Q8">
-        <v>195.79</v>
+        <v>194.99</v>
       </c>
       <c r="R8">
-        <v>204.65</v>
+        <v>203.85</v>
       </c>
       <c r="S8">
-        <v>242.08</v>
+        <v>241.46</v>
       </c>
       <c r="T8">
-        <v>-20.85</v>
+        <v>-23.19</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,34 +1702,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>40.94</v>
+        <v>35.08</v>
       </c>
       <c r="Z8">
-        <v>-1.97</v>
+        <v>-2.67</v>
       </c>
       <c r="AA8">
-        <v>-2.88</v>
+        <v>-2.84</v>
       </c>
       <c r="AB8">
-        <v>0.91</v>
+        <v>0.17</v>
       </c>
       <c r="AC8">
-        <v>74.54000000000001</v>
+        <v>56.43</v>
       </c>
       <c r="AD8">
-        <v>85.78</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="AE8">
-        <v>7.42</v>
+        <v>7.56</v>
       </c>
       <c r="AF8">
-        <v>39.61</v>
+        <v>31.51</v>
       </c>
       <c r="AG8">
-        <v>204.18</v>
+        <v>204.13</v>
       </c>
       <c r="AH8">
-        <v>187.39</v>
+        <v>185.85</v>
       </c>
       <c r="AI8">
         <v>203.6</v>
@@ -1723,7 +1738,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>36.62</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1749,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3403.2</v>
+        <v>3405.4</v>
       </c>
       <c r="D9">
-        <v>-2.68</v>
+        <v>0.06</v>
       </c>
       <c r="E9">
         <v>4103.5</v>
@@ -1746,46 +1761,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-17.07</v>
+        <v>-17.01</v>
       </c>
       <c r="H9">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="I9">
-        <v>-6.4</v>
+        <v>-3.27</v>
       </c>
       <c r="J9">
-        <v>-4.74</v>
+        <v>-4.24</v>
       </c>
       <c r="K9">
-        <v>-5.13</v>
+        <v>-4.79</v>
       </c>
       <c r="L9">
-        <v>-17.39</v>
+        <v>-13.94</v>
       </c>
       <c r="M9">
-        <v>18.48</v>
+        <v>18.67</v>
       </c>
       <c r="N9">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O9">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P9">
-        <v>3496.02</v>
+        <v>3472.96</v>
       </c>
       <c r="Q9">
-        <v>3545.82</v>
+        <v>3538.12</v>
       </c>
       <c r="R9">
-        <v>3565.77</v>
+        <v>3561.92</v>
       </c>
       <c r="S9">
-        <v>3667.84</v>
+        <v>3666.42</v>
       </c>
       <c r="T9">
-        <v>-7.22</v>
+        <v>-7.12</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,43 +1815,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>38.19</v>
+        <v>38.41</v>
       </c>
       <c r="Z9">
-        <v>-19.56</v>
+        <v>-27.99</v>
       </c>
       <c r="AA9">
-        <v>-7.65</v>
+        <v>-11.72</v>
       </c>
       <c r="AB9">
-        <v>-11.91</v>
+        <v>-16.27</v>
       </c>
       <c r="AC9">
-        <v>36.91</v>
+        <v>27.85</v>
       </c>
       <c r="AD9">
-        <v>41.86</v>
+        <v>36.13</v>
       </c>
       <c r="AE9">
-        <v>105.48</v>
+        <v>107.51</v>
       </c>
       <c r="AF9">
-        <v>-82.3</v>
+        <v>-77.31</v>
       </c>
       <c r="AG9">
-        <v>3691.14</v>
+        <v>3696.18</v>
       </c>
       <c r="AH9">
-        <v>3400.5</v>
+        <v>3380.07</v>
       </c>
       <c r="AI9">
-        <v>3759.99</v>
+        <v>3674.58</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.15</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1862,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1829.1</v>
+        <v>1790</v>
       </c>
       <c r="D10">
-        <v>-0.31</v>
+        <v>-2.14</v>
       </c>
       <c r="E10">
         <v>1834.7</v>
@@ -1859,25 +1874,25 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-0.31</v>
+        <v>-2.44</v>
       </c>
       <c r="H10">
-        <v>37.92</v>
+        <v>34.97</v>
       </c>
       <c r="I10">
-        <v>16.12</v>
+        <v>8.48</v>
       </c>
       <c r="J10">
-        <v>17.36</v>
+        <v>15.36</v>
       </c>
       <c r="K10">
-        <v>17.2</v>
+        <v>15.05</v>
       </c>
       <c r="L10">
-        <v>26.26</v>
+        <v>24.95</v>
       </c>
       <c r="M10">
-        <v>6.94</v>
+        <v>6.39</v>
       </c>
       <c r="N10">
         <v>99</v>
@@ -1886,19 +1901,19 @@
         <v>89</v>
       </c>
       <c r="P10">
-        <v>1776.58</v>
+        <v>1804.58</v>
       </c>
       <c r="Q10">
-        <v>1588.6</v>
+        <v>1600.25</v>
       </c>
       <c r="R10">
-        <v>1587.69</v>
+        <v>1590.63</v>
       </c>
       <c r="S10">
-        <v>1518.46</v>
+        <v>1519.35</v>
       </c>
       <c r="T10">
-        <v>20.46</v>
+        <v>17.81</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1913,34 +1928,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>75.84</v>
+        <v>69.3</v>
       </c>
       <c r="Z10">
-        <v>58.73</v>
+        <v>63.49</v>
       </c>
       <c r="AA10">
-        <v>20.04</v>
+        <v>28.73</v>
       </c>
       <c r="AB10">
-        <v>38.68</v>
+        <v>34.76</v>
       </c>
       <c r="AC10">
-        <v>97.70999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AD10">
-        <v>98.23</v>
+        <v>96.47</v>
       </c>
       <c r="AE10">
-        <v>53.09</v>
+        <v>53.93</v>
       </c>
       <c r="AF10">
-        <v>12.17</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="AG10">
-        <v>1826.47</v>
+        <v>1853.9</v>
       </c>
       <c r="AH10">
-        <v>1350.74</v>
+        <v>1346.61</v>
       </c>
       <c r="AI10">
         <v>1655.18</v>
@@ -1949,7 +1964,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>44.11</v>
+        <v>47.73</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2133,19 +2148,19 @@
         <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2153,1420 +2168,1360 @@
         <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-7.72</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-10</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.02</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-18.92</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-21.42</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.13</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-6.64</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-3.93</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-7.51</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-23.71</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-23.61</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-4.85</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.83</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.74</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.24</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>17.36</v>
+      </c>
+      <c r="D16" s="6">
+        <v>15.36</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.15</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.65</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.52</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-12.41</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.33</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-10.95</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-10.73</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4.52</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-7.02</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-6.4</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.27</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>16.12</v>
+      </c>
+      <c r="D25" s="6">
+        <v>8.48</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-7.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-13.19</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-17.43</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-19.57</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-21.55</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-1.94</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-7.73</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-5.79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-12.3</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>9.27</v>
+      </c>
+      <c r="D30" s="6">
+        <v>6.78</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-7.03</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-6.25</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-42.37</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-44.05</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-17.39</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-13.94</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>26.26</v>
+      </c>
+      <c r="D34" s="6">
+        <v>24.95</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-22.83</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-16.1</v>
+      </c>
+      <c r="E35" s="8">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+  